--- a/data/VANTAGE-Technology-Radar.xlsx
+++ b/data/VANTAGE-Technology-Radar.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N43"/>
+  <dimension ref="A1:O43"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="27.88" customWidth="1" style="17" min="1" max="1"/>
@@ -516,9 +516,14 @@
           <t>Notes / Key Takeaways</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="0" t="inlineStr">
         <is>
           <t>Publication Date</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Discovery Date</t>
         </is>
       </c>
     </row>
@@ -583,6 +588,9 @@
       <c r="N2" s="18" t="n">
         <v>46162</v>
       </c>
+      <c r="O2" s="18" t="n">
+        <v>46113</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="16" t="inlineStr">
@@ -642,6 +650,9 @@
         </is>
       </c>
       <c r="M3" s="16" t="n"/>
+      <c r="O3" s="18" t="n">
+        <v>46168</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
@@ -697,6 +708,9 @@
           <t>Strong alignment with developer workflows.</t>
         </is>
       </c>
+      <c r="O4" s="18" t="n">
+        <v>46113</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
@@ -752,6 +766,9 @@
           <t>Fast-moving ecosystem.</t>
         </is>
       </c>
+      <c r="O5" s="18" t="n">
+        <v>46113</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
@@ -807,6 +824,9 @@
           <t>Becoming a de facto standard.</t>
         </is>
       </c>
+      <c r="O6" s="18" t="n">
+        <v>46113</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="16" t="inlineStr">
@@ -869,6 +889,9 @@
       <c r="N7" s="18" t="n">
         <v>45972</v>
       </c>
+      <c r="O7" s="18" t="n">
+        <v>45962</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="16" t="inlineStr">
@@ -931,6 +954,9 @@
         <is>
           <t>Technical guide to the operational life cycle of AI agents, focusing on deployment &amp; security</t>
         </is>
+      </c>
+      <c r="O8" s="18" t="n">
+        <v>45975</v>
       </c>
     </row>
     <row r="9">
@@ -987,6 +1013,9 @@
           <t>Strong enterprise alignment.</t>
         </is>
       </c>
+      <c r="O9" s="18" t="n">
+        <v>46113</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
@@ -1042,6 +1071,9 @@
           <t>Rapidly evolving.</t>
         </is>
       </c>
+      <c r="O10" s="18" t="n">
+        <v>46082</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
@@ -1097,6 +1129,9 @@
           <t>Widely used in research.</t>
         </is>
       </c>
+      <c r="O11" s="18" t="n">
+        <v>46113</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="16" t="inlineStr">
@@ -1152,6 +1187,9 @@
           <t>Strong retrieval-centric design.</t>
         </is>
       </c>
+      <c r="O12" s="18" t="n">
+        <v>46113</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
@@ -1211,6 +1249,9 @@
         <is>
           <t>Strong reproducibility focus.</t>
         </is>
+      </c>
+      <c r="O13" s="18" t="n">
+        <v>46082</v>
       </c>
     </row>
     <row r="14">
@@ -1267,6 +1308,9 @@
           <t>Good hybrid cloud/HPC support.</t>
         </is>
       </c>
+      <c r="O14" s="18" t="n">
+        <v>46082</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
@@ -1322,6 +1366,9 @@
           <t>Strong alignment with scientific workflows.</t>
         </is>
       </c>
+      <c r="O15" s="18" t="n">
+        <v>46113</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
@@ -1377,6 +1424,9 @@
           <t>Strong safety posture.</t>
         </is>
       </c>
+      <c r="O16" s="18" t="n">
+        <v>46113</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
@@ -1432,6 +1482,9 @@
           <t>Strong .NET + Python support.</t>
         </is>
       </c>
+      <c r="O17" s="18" t="n">
+        <v>46113</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
@@ -1487,6 +1540,9 @@
           <t>Good for reproducibility.</t>
         </is>
       </c>
+      <c r="O18" s="18" t="n">
+        <v>46082</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
@@ -1542,6 +1598,9 @@
           <t>Useful for risk assessment.</t>
         </is>
       </c>
+      <c r="O19" s="18" t="n">
+        <v>46113</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
@@ -1597,6 +1656,9 @@
           <t>Strong alignment with institutional risk controls.</t>
         </is>
       </c>
+      <c r="O20" s="18" t="n">
+        <v>46113</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
@@ -1652,6 +1714,9 @@
           <t>Widely adopted governance framework.</t>
         </is>
       </c>
+      <c r="O21" s="18" t="n">
+        <v>45992</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
@@ -1706,6 +1771,9 @@
           <t>Essential for secure TLAs via PagedAttention and FP8/AWQ optimization.</t>
         </is>
       </c>
+      <c r="O22" s="18" t="n">
+        <v>46113</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
@@ -1760,6 +1828,9 @@
           <t>Eliminates network dependency errors by cleanly bundling open model weights.</t>
         </is>
       </c>
+      <c r="O23" s="18" t="n">
+        <v>46113</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
@@ -1823,6 +1894,9 @@
           <t>Grammar constraints ensure localized agentic pipelines always return valid JSON/code.</t>
         </is>
       </c>
+      <c r="O24" s="18" t="n">
+        <v>46162</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
@@ -1877,6 +1951,9 @@
           <t>Solves local file parsing/RAG bottlenecks entirely within secure client networks.</t>
         </is>
       </c>
+      <c r="O25" s="18" t="n">
+        <v>46113</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
@@ -1931,6 +2008,9 @@
           <t>Outlines the exact connected-to-disconnected asset transfer workflow for enterprise GPUs.</t>
         </is>
       </c>
+      <c r="O26" s="18" t="n">
+        <v>46150</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
@@ -1985,6 +2065,9 @@
           <t>Built-in vulnerability scanning ensures agent images remain clean behind the firewall.</t>
         </is>
       </c>
+      <c r="O27" s="18" t="n">
+        <v>46150</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="16" t="inlineStr">
@@ -2039,6 +2122,9 @@
           <t>Moves past simple how-to guides into formal data isolation and local compliance frameworks.</t>
         </is>
       </c>
+      <c r="O28" s="18" t="n">
+        <v>46150</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
@@ -2102,6 +2188,9 @@
           <t>Breaks down the "Memory Wall" economics showing an on-prem breakeven velocity of ~4 months.</t>
         </is>
       </c>
+      <c r="O29" s="18" t="n">
+        <v>46054</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="16" t="inlineStr">
@@ -2160,6 +2249,9 @@
           <t>The Coalition for Secure AI (CoSAI) is an open ecosystem of AI and security experts</t>
         </is>
       </c>
+      <c r="O30" s="18" t="n">
+        <v>46174</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
@@ -2222,6 +2314,9 @@
       <c r="N31" s="18" t="n">
         <v>46119</v>
       </c>
+      <c r="O31" s="18" t="n">
+        <v>46119</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="16" t="inlineStr">
@@ -2285,6 +2380,9 @@
           <t>See blog article: https://www.docker.com/blog/the-3cs-a-framework-for-ai-agent-security/</t>
         </is>
       </c>
+      <c r="O32" s="18" t="n">
+        <v>46213</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="16" t="inlineStr">
@@ -2347,6 +2445,9 @@
         <is>
           <t>MIgrated from API Assistants  - now deprecated.</t>
         </is>
+      </c>
+      <c r="O33" s="18" t="n">
+        <v>46212</v>
       </c>
     </row>
     <row r="34">
@@ -4982,7 +5083,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="22.13" customWidth="1" style="17" min="2" max="2"/>
@@ -5054,6 +5155,11 @@
           <t>Notes / Key Takeaways</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Discovery Date</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="16" t="inlineStr">
@@ -5112,6 +5218,9 @@
         <is>
           <t>Stable API surface.</t>
         </is>
+      </c>
+      <c r="N2" s="18" t="n">
+        <v>46150</v>
       </c>
     </row>
   </sheetData>
@@ -5179,7 +5288,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="26.13" customWidth="1" style="17" min="1" max="1"/>
@@ -5242,6 +5351,11 @@
           <t>Notes / Key Takeaways</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Discovery Date</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="16" t="inlineStr">
@@ -5295,6 +5409,9 @@
           <t>Evaluates State-Of-The-Art agent performance on multi-million line codebases to assess real-world software engineering capabilities.</t>
         </is>
       </c>
+      <c r="L2" s="18" t="n">
+        <v>46216</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="16" t="inlineStr">
@@ -5343,6 +5460,9 @@
           <t>Papers with Code with State-Of-The-Art (SOTA) Codng Agent Benchmarks</t>
         </is>
       </c>
+      <c r="L3" s="18" t="n">
+        <v>46216</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
@@ -5391,6 +5511,9 @@
           <t>Addresses limitations of original SWE-bench by focusing on long-horizon, complex, multi-file software engineering tasks.</t>
         </is>
       </c>
+      <c r="L4" s="18" t="n">
+        <v>46216</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
@@ -5434,6 +5557,9 @@
           <t>Scalable framework that generates repository-level tasks from live GitHub PRs across 11 programming languages.</t>
         </is>
       </c>
+      <c r="L5" s="18" t="n">
+        <v>46216</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
@@ -5480,6 +5606,9 @@
           <t>Benchmarks agents on hard, realistic tasks within terminal/CLI environments.</t>
         </is>
       </c>
+      <c r="L6" s="18" t="n">
+        <v>46216</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="16" t="inlineStr">
@@ -5526,6 +5655,9 @@
           <t>Benchmark specifically for evaluating the code review capabilities of AI agents.</t>
         </is>
       </c>
+      <c r="L7" s="18" t="n">
+        <v>46216</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="16" t="inlineStr">
@@ -5571,6 +5703,9 @@
         <is>
           <t>Isolates the evaluation of repository exploration, context retrieval, and code localization capabilities.</t>
         </is>
+      </c>
+      <c r="L8" s="18" t="n">
+        <v>46216</v>
       </c>
     </row>
   </sheetData>

--- a/data/VANTAGE-Technology-Radar.xlsx
+++ b/data/VANTAGE-Technology-Radar.xlsx
@@ -521,7 +521,7 @@
           <t>Publication Date</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="0" t="inlineStr">
         <is>
           <t>Discovery Date</t>
         </is>
@@ -567,7 +567,7 @@
       </c>
       <c r="J2" s="16" t="inlineStr">
         <is>
-          <t>Architecture, Implementation, Deployment</t>
+          <t>Architecture; Implementation; Deployment</t>
         </is>
       </c>
       <c r="K2" s="16" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="J3" s="16" t="inlineStr">
         <is>
-          <t>Workflows, Implementation</t>
+          <t>Workflows; Implementation</t>
         </is>
       </c>
       <c r="K3" s="16" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="J4" s="16" t="inlineStr">
         <is>
-          <t>Architecture, Governance, Security</t>
+          <t>Architecture; Governance; Security</t>
         </is>
       </c>
       <c r="K4" s="16" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="J5" s="16" t="inlineStr">
         <is>
-          <t>Architecture, Implementation</t>
+          <t>Architecture; Implementation</t>
         </is>
       </c>
       <c r="K5" s="16" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
-          <t>Architecture, Governance</t>
+          <t>Architecture; Governance</t>
         </is>
       </c>
       <c r="K6" s="16" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
-          <t>Architecture, Governance</t>
+          <t>Architecture; Governance</t>
         </is>
       </c>
       <c r="K7" s="16" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
-          <t>Implementation, Security, Deployment</t>
+          <t>Implementation; Security; Deployment</t>
         </is>
       </c>
       <c r="K8" s="16" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>Architecture, Deployment</t>
+          <t>Architecture; Deployment</t>
         </is>
       </c>
       <c r="K9" s="16" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>Architecture, Implementation</t>
+          <t>Architecture; Implementation</t>
         </is>
       </c>
       <c r="K10" s="16" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>Architecture, Implementation</t>
+          <t>Architecture; Implementation</t>
         </is>
       </c>
       <c r="K11" s="16" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>Architecture, Governance</t>
+          <t>Architecture; Governance</t>
         </is>
       </c>
       <c r="K12" s="16" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>Architecture, Deployment</t>
+          <t>Architecture; Deployment</t>
         </is>
       </c>
       <c r="K13" s="16" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>Implementation, Deployment</t>
+          <t>Implementation; Deployment</t>
         </is>
       </c>
       <c r="K14" s="16" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>Implementation, Data Governance</t>
+          <t>Implementation; Data Governance</t>
         </is>
       </c>
       <c r="K15" s="16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>Architecture, Security</t>
+          <t>Architecture; Security</t>
         </is>
       </c>
       <c r="K16" s="16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>Architecture, Implementation</t>
+          <t>Architecture; Implementation</t>
         </is>
       </c>
       <c r="K17" s="16" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>Architecture, Deployment</t>
+          <t>Architecture; Deployment</t>
         </is>
       </c>
       <c r="K18" s="16" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>Self‑hosted AI, Architecture, Implementation, Deployment</t>
+          <t>Self‑hosted AI; Architecture; Implementation; Deployment</t>
         </is>
       </c>
       <c r="K22" s="16" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>Self‑hosted AI, Implementation, Deployment</t>
+          <t>Self‑hosted AI; Implementation; Deployment</t>
         </is>
       </c>
       <c r="K23" s="16" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>Self‑hosted AI, Architecture, Implementation, Deployment</t>
+          <t>Self‑hosted AI; Architecture; Implementation; Deployment</t>
         </is>
       </c>
       <c r="K24" s="16" t="inlineStr">
@@ -1933,7 +1933,7 @@
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>Self‑hosted AI, Implementation, Deployment</t>
+          <t>Self‑hosted AI; Implementation; Deployment</t>
         </is>
       </c>
       <c r="K25" s="16" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>Self‑hosted AI, Implementation, Network Isolation, Infrastructure Security</t>
+          <t>Self‑hosted AI; Implementation; Network Isolation; Infrastructure Security</t>
         </is>
       </c>
       <c r="K26" s="16" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>Self‑hosted AI, Implementation, Network Isolation, Infrastructure Security, Governance</t>
+          <t>Self‑hosted AI; Implementation; Network Isolation; Infrastructure Security; Governance</t>
         </is>
       </c>
       <c r="K27" s="16" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>Self‑hosted AI, Infrastructure Security</t>
+          <t>Self‑hosted AI; Infrastructure Security</t>
         </is>
       </c>
       <c r="K28" s="16" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>Self‑hosted AI, Architecture, Governance</t>
+          <t>Self‑hosted AI; Architecture; Governance</t>
         </is>
       </c>
       <c r="K29" s="16" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
-          <t>Infrastructure Security, Security</t>
+          <t>Infrastructure Security; Security</t>
         </is>
       </c>
       <c r="K30" s="16" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
-          <t>Infrastructure Security, Security</t>
+          <t>Infrastructure Security; Security</t>
         </is>
       </c>
       <c r="K31" s="16" t="inlineStr">
@@ -2533,7 +2533,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z78"/>
+  <dimension ref="A1:Z81"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="50.38" customWidth="1" style="17" min="1" max="1"/>
@@ -4204,105 +4204,45 @@
       <c r="Z51" s="13" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>This helps research IT teams quickly find relevant material.</t>
-        </is>
-      </c>
-      <c r="B52" s="13" t="n"/>
-      <c r="C52" s="13" t="n"/>
-      <c r="D52" s="13" t="n"/>
-      <c r="E52" s="13" t="n"/>
-      <c r="F52" s="13" t="n"/>
-      <c r="G52" s="13" t="n"/>
-      <c r="H52" s="13" t="n"/>
-      <c r="I52" s="13" t="n"/>
-      <c r="J52" s="13" t="n"/>
-      <c r="K52" s="13" t="n"/>
-      <c r="L52" s="13" t="n"/>
-      <c r="M52" s="13" t="n"/>
-      <c r="N52" s="13" t="n"/>
-      <c r="O52" s="13" t="n"/>
-      <c r="P52" s="13" t="n"/>
-      <c r="Q52" s="13" t="n"/>
-      <c r="R52" s="13" t="n"/>
-      <c r="S52" s="13" t="n"/>
-      <c r="T52" s="13" t="n"/>
-      <c r="U52" s="13" t="n"/>
-      <c r="V52" s="13" t="n"/>
-      <c r="W52" s="13" t="n"/>
-      <c r="X52" s="13" t="n"/>
-      <c r="Y52" s="13" t="n"/>
-      <c r="Z52" s="13" t="n"/>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Data Protection</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Safeguarding sensitive data specifically (EDAM ontology: "Management of sensitive data") -- distinct from the broader "Security" term above. Newly available for Topic Focus.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>9. Relevance to Research Cyberinfrastructure</t>
-        </is>
-      </c>
-      <c r="B53" s="13" t="n"/>
-      <c r="C53" s="13" t="n"/>
-      <c r="D53" s="13" t="n"/>
-      <c r="E53" s="13" t="n"/>
-      <c r="F53" s="13" t="n"/>
-      <c r="G53" s="13" t="n"/>
-      <c r="H53" s="13" t="n"/>
-      <c r="I53" s="13" t="n"/>
-      <c r="J53" s="13" t="n"/>
-      <c r="K53" s="13" t="n"/>
-      <c r="L53" s="13" t="n"/>
-      <c r="M53" s="13" t="n"/>
-      <c r="N53" s="13" t="n"/>
-      <c r="O53" s="13" t="n"/>
-      <c r="P53" s="13" t="n"/>
-      <c r="Q53" s="13" t="n"/>
-      <c r="R53" s="13" t="n"/>
-      <c r="S53" s="13" t="n"/>
-      <c r="T53" s="13" t="n"/>
-      <c r="U53" s="13" t="n"/>
-      <c r="V53" s="13" t="n"/>
-      <c r="W53" s="13" t="n"/>
-      <c r="X53" s="13" t="n"/>
-      <c r="Y53" s="13" t="n"/>
-      <c r="Z53" s="13" t="n"/>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Controlled vocabulary standard: EDAM ontology (Data management branch)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>http://edamontology.org/topic_3071 -- "Data governance" and "Workflows" above are EDAM terms (topic_3571, topic_0769). "Data Protection" above is EDAM topic_4044. Also available for future use: FAIR data (topic_4012), Data quality management (topic_3572), Data curation and archival (topic_0219), Data integration and warehousing (topic_3366). Open ontology, not a paywalled standard -- browsable at https://www.ebi.ac.uk/ols4/ontologies/edam</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>A short tag describing why this matters to research platforms:</t>
-        </is>
-      </c>
-      <c r="B54" s="13" t="n"/>
-      <c r="C54" s="13" t="n"/>
-      <c r="D54" s="13" t="n"/>
-      <c r="E54" s="13" t="n"/>
-      <c r="F54" s="13" t="n"/>
-      <c r="G54" s="13" t="n"/>
-      <c r="H54" s="13" t="n"/>
-      <c r="I54" s="13" t="n"/>
-      <c r="J54" s="13" t="n"/>
-      <c r="K54" s="13" t="n"/>
-      <c r="L54" s="13" t="n"/>
-      <c r="M54" s="13" t="n"/>
-      <c r="N54" s="13" t="n"/>
-      <c r="O54" s="13" t="n"/>
-      <c r="P54" s="13" t="n"/>
-      <c r="Q54" s="13" t="n"/>
-      <c r="R54" s="13" t="n"/>
-      <c r="S54" s="13" t="n"/>
-      <c r="T54" s="13" t="n"/>
-      <c r="U54" s="13" t="n"/>
-      <c r="V54" s="13" t="n"/>
-      <c r="W54" s="13" t="n"/>
-      <c r="X54" s="13" t="n"/>
-      <c r="Y54" s="13" t="n"/>
-      <c r="Z54" s="13" t="n"/>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Optional secondary axis: NIST AI RMF 1.0 trustworthy-AI characteristics</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>https://nvlpubs.nist.gov/nistpubs/ai/NIST.AI.100-1.pdf -- Valid and Reliable, Safe, Secure and Resilient, Accountable and Transparent, Explainable and Interpretable, Privacy-Enhanced, Fair (harmful bias managed). Optional: for AI-trustworthiness framing EDAM doesn't cover. NOTE: NIST's "Fair (harmful bias managed)" is unrelated to EDAM's "FAIR data" (Findable/Accessible/Interoperable/Reusable data principles) despite sharing the word -- do not conflate the two if both are ever used as tags.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>Examples:</t>
+          <t>This helps research IT teams quickly find relevant material.</t>
         </is>
       </c>
       <c r="B55" s="13" t="n"/>
@@ -4334,7 +4274,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>Workflow orchestration</t>
+          <t>9. Relevance to Research Cyberinfrastructure</t>
         </is>
       </c>
       <c r="B56" s="13" t="n"/>
@@ -4366,7 +4306,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>Data portal integration</t>
+          <t>A short tag describing why this matters to research platforms:</t>
         </is>
       </c>
       <c r="B57" s="13" t="n"/>
@@ -4398,7 +4338,7 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>Metadata / provenance</t>
+          <t>Examples:</t>
         </is>
       </c>
       <c r="B58" s="13" t="n"/>
@@ -4430,7 +4370,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>Multi‑agent coordination</t>
+          <t>Workflow orchestration</t>
         </is>
       </c>
       <c r="B59" s="13" t="n"/>
@@ -4462,7 +4402,7 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>HPC / cloud hybrid workflows</t>
+          <t>Data portal integration</t>
         </is>
       </c>
       <c r="B60" s="13" t="n"/>
@@ -4494,7 +4434,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>Reproducibility</t>
+          <t>Metadata / provenance</t>
         </is>
       </c>
       <c r="B61" s="13" t="n"/>
@@ -4526,7 +4466,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>Federated analysis</t>
+          <t>Multi‑agent coordination</t>
         </is>
       </c>
       <c r="B62" s="13" t="n"/>
@@ -4558,7 +4498,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>User‑facing agent interfaces</t>
+          <t>HPC / cloud hybrid workflows</t>
         </is>
       </c>
       <c r="B63" s="13" t="n"/>
@@ -4590,7 +4530,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>9. Maturity Level (Radar Standard)</t>
+          <t>Reproducibility</t>
         </is>
       </c>
       <c r="B64" s="13" t="n"/>
@@ -4622,7 +4562,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>Not about the website — about the technology described.</t>
+          <t>Federated analysis</t>
         </is>
       </c>
       <c r="B65" s="13" t="n"/>
@@ -4654,7 +4594,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>Emerging</t>
+          <t>User‑facing agent interfaces</t>
         </is>
       </c>
       <c r="B66" s="13" t="n"/>
@@ -4686,7 +4626,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>9. Maturity Level (Radar Standard)</t>
         </is>
       </c>
       <c r="B67" s="13" t="n"/>
@@ -4718,7 +4658,7 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>Mature</t>
+          <t>Not about the website — about the technology described.</t>
         </is>
       </c>
       <c r="B68" s="13" t="n"/>
@@ -4750,7 +4690,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>Deprecated</t>
+          <t>Emerging</t>
         </is>
       </c>
       <c r="B69" s="13" t="n"/>
@@ -4782,7 +4722,7 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>This helps teams know whether something is stable enough to consider.</t>
+          <t>Research</t>
         </is>
       </c>
       <c r="B70" s="13" t="n"/>
@@ -4814,7 +4754,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>10. Notes / Key Takeaways</t>
+          <t>Mature</t>
         </is>
       </c>
       <c r="B71" s="13" t="n"/>
@@ -4846,7 +4786,7 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>A short free‑text field:</t>
+          <t>Deprecated</t>
         </is>
       </c>
       <c r="B72" s="13" t="n"/>
@@ -4878,7 +4818,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>breaking changes</t>
+          <t>This helps teams know whether something is stable enough to consider.</t>
         </is>
       </c>
       <c r="B73" s="13" t="n"/>
@@ -4910,7 +4850,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>important patterns</t>
+          <t>10. Notes / Key Takeaways</t>
         </is>
       </c>
       <c r="B74" s="13" t="n"/>
@@ -4942,7 +4882,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>new capabilities</t>
+          <t>A short free‑text field:</t>
         </is>
       </c>
       <c r="B75" s="13" t="n"/>
@@ -4974,7 +4914,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>relevance to agentic workflows</t>
+          <t>breaking changes</t>
         </is>
       </c>
       <c r="B76" s="13" t="n"/>
@@ -5006,7 +4946,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>implications for research platforms</t>
+          <t>important patterns</t>
         </is>
       </c>
       <c r="B77" s="13" t="n"/>
@@ -5038,7 +4978,7 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>This is where institutional knowledge accumulates.</t>
+          <t>new capabilities</t>
         </is>
       </c>
       <c r="B78" s="13" t="n"/>
@@ -5067,6 +5007,102 @@
       <c r="Y78" s="13" t="n"/>
       <c r="Z78" s="13" t="n"/>
     </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>relevance to agentic workflows</t>
+        </is>
+      </c>
+      <c r="B79" s="13" t="n"/>
+      <c r="C79" s="13" t="n"/>
+      <c r="D79" s="13" t="n"/>
+      <c r="E79" s="13" t="n"/>
+      <c r="F79" s="13" t="n"/>
+      <c r="G79" s="13" t="n"/>
+      <c r="H79" s="13" t="n"/>
+      <c r="I79" s="13" t="n"/>
+      <c r="J79" s="13" t="n"/>
+      <c r="K79" s="13" t="n"/>
+      <c r="L79" s="13" t="n"/>
+      <c r="M79" s="13" t="n"/>
+      <c r="N79" s="13" t="n"/>
+      <c r="O79" s="13" t="n"/>
+      <c r="P79" s="13" t="n"/>
+      <c r="Q79" s="13" t="n"/>
+      <c r="R79" s="13" t="n"/>
+      <c r="S79" s="13" t="n"/>
+      <c r="T79" s="13" t="n"/>
+      <c r="U79" s="13" t="n"/>
+      <c r="V79" s="13" t="n"/>
+      <c r="W79" s="13" t="n"/>
+      <c r="X79" s="13" t="n"/>
+      <c r="Y79" s="13" t="n"/>
+      <c r="Z79" s="13" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>implications for research platforms</t>
+        </is>
+      </c>
+      <c r="B80" s="13" t="n"/>
+      <c r="C80" s="13" t="n"/>
+      <c r="D80" s="13" t="n"/>
+      <c r="E80" s="13" t="n"/>
+      <c r="F80" s="13" t="n"/>
+      <c r="G80" s="13" t="n"/>
+      <c r="H80" s="13" t="n"/>
+      <c r="I80" s="13" t="n"/>
+      <c r="J80" s="13" t="n"/>
+      <c r="K80" s="13" t="n"/>
+      <c r="L80" s="13" t="n"/>
+      <c r="M80" s="13" t="n"/>
+      <c r="N80" s="13" t="n"/>
+      <c r="O80" s="13" t="n"/>
+      <c r="P80" s="13" t="n"/>
+      <c r="Q80" s="13" t="n"/>
+      <c r="R80" s="13" t="n"/>
+      <c r="S80" s="13" t="n"/>
+      <c r="T80" s="13" t="n"/>
+      <c r="U80" s="13" t="n"/>
+      <c r="V80" s="13" t="n"/>
+      <c r="W80" s="13" t="n"/>
+      <c r="X80" s="13" t="n"/>
+      <c r="Y80" s="13" t="n"/>
+      <c r="Z80" s="13" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>This is where institutional knowledge accumulates.</t>
+        </is>
+      </c>
+      <c r="B81" s="13" t="n"/>
+      <c r="C81" s="13" t="n"/>
+      <c r="D81" s="13" t="n"/>
+      <c r="E81" s="13" t="n"/>
+      <c r="F81" s="13" t="n"/>
+      <c r="G81" s="13" t="n"/>
+      <c r="H81" s="13" t="n"/>
+      <c r="I81" s="13" t="n"/>
+      <c r="J81" s="13" t="n"/>
+      <c r="K81" s="13" t="n"/>
+      <c r="L81" s="13" t="n"/>
+      <c r="M81" s="13" t="n"/>
+      <c r="N81" s="13" t="n"/>
+      <c r="O81" s="13" t="n"/>
+      <c r="P81" s="13" t="n"/>
+      <c r="Q81" s="13" t="n"/>
+      <c r="R81" s="13" t="n"/>
+      <c r="S81" s="13" t="n"/>
+      <c r="T81" s="13" t="n"/>
+      <c r="U81" s="13" t="n"/>
+      <c r="V81" s="13" t="n"/>
+      <c r="W81" s="13" t="n"/>
+      <c r="X81" s="13" t="n"/>
+      <c r="Y81" s="13" t="n"/>
+      <c r="Z81" s="13" t="n"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A964">
     <cfRule type="expression" priority="1" dxfId="5">
@@ -5155,7 +5191,7 @@
           <t>Notes / Key Takeaways</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="0" t="inlineStr">
         <is>
           <t>Discovery Date</t>
         </is>
@@ -5351,7 +5387,7 @@
           <t>Notes / Key Takeaways</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="0" t="inlineStr">
         <is>
           <t>Discovery Date</t>
         </is>

--- a/data/VANTAGE-Technology-Radar.xlsx
+++ b/data/VANTAGE-Technology-Radar.xlsx
@@ -4,9 +4,11 @@
   <workbookPr/>
   <sheets>
     <sheet name="Knowledgebase" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Dictionary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Deprecated" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="SOTA Coding Agents Benchmarks" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Deprecated" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SOTA Coding Agents Benchmarks" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Dictionary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Vocabulary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Standards" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +26,7 @@
     <numFmt numFmtId="169" formatCode="mmmm d, yyyy"/>
     <numFmt numFmtId="170" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -57,6 +59,9 @@
       <color rgb="FF0000FF"/>
       <u val="single"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -78,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -100,6 +105,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -562,7 +571,7 @@
       </c>
       <c r="I2" s="16" t="inlineStr">
         <is>
-          <t>Hooks; Skills; MCP; Agent Framework</t>
+          <t>Hooks; Skills; MCP; Agent frameworks</t>
         </is>
       </c>
       <c r="J2" s="16" t="inlineStr">
@@ -631,7 +640,7 @@
       </c>
       <c r="I3" s="16" t="inlineStr">
         <is>
-          <t>FAIR Data; Workflow Agents;</t>
+          <t>FAIR data; Workflow Agents</t>
         </is>
       </c>
       <c r="J3" s="16" t="inlineStr">
@@ -801,7 +810,7 @@
       </c>
       <c r="I6" s="16" t="inlineStr">
         <is>
-          <t>MCP; Tooling; Server Patterns</t>
+          <t>MCP; Tools; Server Patterns</t>
         </is>
       </c>
       <c r="J6" s="16" t="inlineStr">
@@ -863,7 +872,7 @@
       </c>
       <c r="I7" s="16" t="inlineStr">
         <is>
-          <t>Model Context Protocol; Agent Patterns</t>
+          <t>MCP; Agent Patterns</t>
         </is>
       </c>
       <c r="J7" s="16" t="inlineStr">
@@ -932,7 +941,7 @@
       </c>
       <c r="I8" s="16" t="inlineStr">
         <is>
-          <t>Deployment Patterns; Workflow Automation</t>
+          <t>Deployment patterns; Workflow Automation</t>
         </is>
       </c>
       <c r="J8" s="16" t="inlineStr">
@@ -990,7 +999,7 @@
       </c>
       <c r="I9" s="16" t="inlineStr">
         <is>
-          <t>Agent Frameworks; Orchestration</t>
+          <t>Agent frameworks; Orchestration</t>
         </is>
       </c>
       <c r="J9" s="16" t="inlineStr">
@@ -1348,7 +1357,7 @@
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>Implementation; Data Governance</t>
+          <t>Implementation; Data governance</t>
         </is>
       </c>
       <c r="K15" s="16" t="inlineStr">
@@ -1575,7 +1584,7 @@
       </c>
       <c r="I19" s="16" t="inlineStr">
         <is>
-          <t>Evaluation; Guardrails</t>
+          <t>Evaluation / testing; Safety / guardrails</t>
         </is>
       </c>
       <c r="J19" s="16" t="inlineStr">
@@ -1633,7 +1642,7 @@
       </c>
       <c r="I20" s="16" t="inlineStr">
         <is>
-          <t>Guardrails; Safe Tool Use</t>
+          <t>Safety / guardrails; Safe Tool Use</t>
         </is>
       </c>
       <c r="J20" s="16" t="inlineStr">
@@ -1691,12 +1700,12 @@
       </c>
       <c r="I21" s="16" t="inlineStr">
         <is>
-          <t>Safety; Governance; Risk Controls</t>
+          <t>Safety / guardrails; Governance; Risk Controls</t>
         </is>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>Data Governance; Security</t>
+          <t>Data governance; Security</t>
         </is>
       </c>
       <c r="K21" s="16" t="inlineStr">
@@ -2160,7 +2169,7 @@
       </c>
       <c r="H29" s="16" t="inlineStr">
         <is>
-          <t>Technical Whitepaper</t>
+          <t>Whitepaper</t>
         </is>
       </c>
       <c r="I29" s="16" t="inlineStr">
@@ -2226,7 +2235,7 @@
       </c>
       <c r="I30" s="16" t="inlineStr">
         <is>
-          <t>Guardrails; Safe Tool Use</t>
+          <t>Safety / guardrails; Safe Tool Use</t>
         </is>
       </c>
       <c r="J30" s="16" t="inlineStr">
@@ -2533,2592 +2542,6 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z81"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
-  <cols>
-    <col width="50.38" customWidth="1" style="17" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Columns</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Definitions</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="n"/>
-      <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="n"/>
-      <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
-      <c r="O1" s="3" t="n"/>
-      <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="n"/>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
-      <c r="X1" s="3" t="n"/>
-      <c r="Y1" s="3" t="n"/>
-      <c r="Z1" s="3" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>1. Resource Name</t>
-        </is>
-      </c>
-      <c r="B2" s="13" t="n"/>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="n"/>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="13" t="n"/>
-      <c r="G2" s="13" t="n"/>
-      <c r="H2" s="13" t="n"/>
-      <c r="I2" s="13" t="n"/>
-      <c r="J2" s="13" t="n"/>
-      <c r="K2" s="13" t="n"/>
-      <c r="L2" s="13" t="n"/>
-      <c r="M2" s="13" t="n"/>
-      <c r="N2" s="13" t="n"/>
-      <c r="O2" s="13" t="n"/>
-      <c r="P2" s="13" t="n"/>
-      <c r="Q2" s="13" t="n"/>
-      <c r="R2" s="13" t="n"/>
-      <c r="S2" s="13" t="n"/>
-      <c r="T2" s="13" t="n"/>
-      <c r="U2" s="13" t="n"/>
-      <c r="V2" s="13" t="n"/>
-      <c r="W2" s="13" t="n"/>
-      <c r="X2" s="13" t="n"/>
-      <c r="Y2" s="13" t="n"/>
-      <c r="Z2" s="13" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Short, human‑readable name.</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="n"/>
-      <c r="C3" s="13" t="n"/>
-      <c r="D3" s="13" t="n"/>
-      <c r="E3" s="13" t="n"/>
-      <c r="F3" s="13" t="n"/>
-      <c r="G3" s="13" t="n"/>
-      <c r="H3" s="13" t="n"/>
-      <c r="I3" s="13" t="n"/>
-      <c r="J3" s="13" t="n"/>
-      <c r="K3" s="13" t="n"/>
-      <c r="L3" s="13" t="n"/>
-      <c r="M3" s="13" t="n"/>
-      <c r="N3" s="13" t="n"/>
-      <c r="O3" s="13" t="n"/>
-      <c r="P3" s="13" t="n"/>
-      <c r="Q3" s="13" t="n"/>
-      <c r="R3" s="13" t="n"/>
-      <c r="S3" s="13" t="n"/>
-      <c r="T3" s="13" t="n"/>
-      <c r="U3" s="13" t="n"/>
-      <c r="V3" s="13" t="n"/>
-      <c r="W3" s="13" t="n"/>
-      <c r="X3" s="13" t="n"/>
-      <c r="Y3" s="13" t="n"/>
-      <c r="Z3" s="13" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Example: VS Code Copilot Agents Overview</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="n"/>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="n"/>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="13" t="n"/>
-      <c r="G4" s="13" t="n"/>
-      <c r="H4" s="13" t="n"/>
-      <c r="I4" s="13" t="n"/>
-      <c r="J4" s="13" t="n"/>
-      <c r="K4" s="13" t="n"/>
-      <c r="L4" s="13" t="n"/>
-      <c r="M4" s="13" t="n"/>
-      <c r="N4" s="13" t="n"/>
-      <c r="O4" s="13" t="n"/>
-      <c r="P4" s="13" t="n"/>
-      <c r="Q4" s="13" t="n"/>
-      <c r="R4" s="13" t="n"/>
-      <c r="S4" s="13" t="n"/>
-      <c r="T4" s="13" t="n"/>
-      <c r="U4" s="13" t="n"/>
-      <c r="V4" s="13" t="n"/>
-      <c r="W4" s="13" t="n"/>
-      <c r="X4" s="13" t="n"/>
-      <c r="Y4" s="13" t="n"/>
-      <c r="Z4" s="13" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>2. URL</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="n"/>
-      <c r="C5" s="13" t="n"/>
-      <c r="D5" s="13" t="n"/>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="13" t="n"/>
-      <c r="G5" s="13" t="n"/>
-      <c r="H5" s="13" t="n"/>
-      <c r="I5" s="13" t="n"/>
-      <c r="J5" s="13" t="n"/>
-      <c r="K5" s="13" t="n"/>
-      <c r="L5" s="13" t="n"/>
-      <c r="M5" s="13" t="n"/>
-      <c r="N5" s="13" t="n"/>
-      <c r="O5" s="13" t="n"/>
-      <c r="P5" s="13" t="n"/>
-      <c r="Q5" s="13" t="n"/>
-      <c r="R5" s="13" t="n"/>
-      <c r="S5" s="13" t="n"/>
-      <c r="T5" s="13" t="n"/>
-      <c r="U5" s="13" t="n"/>
-      <c r="V5" s="13" t="n"/>
-      <c r="W5" s="13" t="n"/>
-      <c r="X5" s="13" t="n"/>
-      <c r="Y5" s="13" t="n"/>
-      <c r="Z5" s="13" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Canonical link to the resource.</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="13" t="n"/>
-      <c r="H6" s="13" t="n"/>
-      <c r="I6" s="13" t="n"/>
-      <c r="J6" s="13" t="n"/>
-      <c r="K6" s="13" t="n"/>
-      <c r="L6" s="13" t="n"/>
-      <c r="M6" s="13" t="n"/>
-      <c r="N6" s="13" t="n"/>
-      <c r="O6" s="13" t="n"/>
-      <c r="P6" s="13" t="n"/>
-      <c r="Q6" s="13" t="n"/>
-      <c r="R6" s="13" t="n"/>
-      <c r="S6" s="13" t="n"/>
-      <c r="T6" s="13" t="n"/>
-      <c r="U6" s="13" t="n"/>
-      <c r="V6" s="13" t="n"/>
-      <c r="W6" s="13" t="n"/>
-      <c r="X6" s="13" t="n"/>
-      <c r="Y6" s="13" t="n"/>
-      <c r="Z6" s="13" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>3. Source Organization</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="n"/>
-      <c r="C7" s="13" t="n"/>
-      <c r="D7" s="13" t="n"/>
-      <c r="E7" s="13" t="n"/>
-      <c r="F7" s="13" t="n"/>
-      <c r="G7" s="13" t="n"/>
-      <c r="H7" s="13" t="n"/>
-      <c r="I7" s="13" t="n"/>
-      <c r="J7" s="13" t="n"/>
-      <c r="K7" s="13" t="n"/>
-      <c r="L7" s="13" t="n"/>
-      <c r="M7" s="13" t="n"/>
-      <c r="N7" s="13" t="n"/>
-      <c r="O7" s="13" t="n"/>
-      <c r="P7" s="13" t="n"/>
-      <c r="Q7" s="13" t="n"/>
-      <c r="R7" s="13" t="n"/>
-      <c r="S7" s="13" t="n"/>
-      <c r="T7" s="13" t="n"/>
-      <c r="U7" s="13" t="n"/>
-      <c r="V7" s="13" t="n"/>
-      <c r="W7" s="13" t="n"/>
-      <c r="X7" s="13" t="n"/>
-      <c r="Y7" s="13" t="n"/>
-      <c r="Z7" s="13" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Who maintains it?</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="n"/>
-      <c r="C8" s="13" t="n"/>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="13" t="n"/>
-      <c r="F8" s="13" t="n"/>
-      <c r="G8" s="13" t="n"/>
-      <c r="H8" s="13" t="n"/>
-      <c r="I8" s="13" t="n"/>
-      <c r="J8" s="13" t="n"/>
-      <c r="K8" s="13" t="n"/>
-      <c r="L8" s="13" t="n"/>
-      <c r="M8" s="13" t="n"/>
-      <c r="N8" s="13" t="n"/>
-      <c r="O8" s="13" t="n"/>
-      <c r="P8" s="13" t="n"/>
-      <c r="Q8" s="13" t="n"/>
-      <c r="R8" s="13" t="n"/>
-      <c r="S8" s="13" t="n"/>
-      <c r="T8" s="13" t="n"/>
-      <c r="U8" s="13" t="n"/>
-      <c r="V8" s="13" t="n"/>
-      <c r="W8" s="13" t="n"/>
-      <c r="X8" s="13" t="n"/>
-      <c r="Y8" s="13" t="n"/>
-      <c r="Z8" s="13" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Examples: Microsoft, GitHub, OpenAI, Kaggle, Anthropic, Google, HuggingFace.</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="n"/>
-      <c r="C9" s="13" t="n"/>
-      <c r="D9" s="13" t="n"/>
-      <c r="E9" s="13" t="n"/>
-      <c r="F9" s="13" t="n"/>
-      <c r="G9" s="13" t="n"/>
-      <c r="H9" s="13" t="n"/>
-      <c r="I9" s="13" t="n"/>
-      <c r="J9" s="13" t="n"/>
-      <c r="K9" s="13" t="n"/>
-      <c r="L9" s="13" t="n"/>
-      <c r="M9" s="13" t="n"/>
-      <c r="N9" s="13" t="n"/>
-      <c r="O9" s="13" t="n"/>
-      <c r="P9" s="13" t="n"/>
-      <c r="Q9" s="13" t="n"/>
-      <c r="R9" s="13" t="n"/>
-      <c r="S9" s="13" t="n"/>
-      <c r="T9" s="13" t="n"/>
-      <c r="U9" s="13" t="n"/>
-      <c r="V9" s="13" t="n"/>
-      <c r="W9" s="13" t="n"/>
-      <c r="X9" s="13" t="n"/>
-      <c r="Y9" s="13" t="n"/>
-      <c r="Z9" s="13" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>This matters because some orgs update weekly, others yearly.</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
-      <c r="G10" s="13" t="n"/>
-      <c r="H10" s="13" t="n"/>
-      <c r="I10" s="13" t="n"/>
-      <c r="J10" s="13" t="n"/>
-      <c r="K10" s="13" t="n"/>
-      <c r="L10" s="13" t="n"/>
-      <c r="M10" s="13" t="n"/>
-      <c r="N10" s="13" t="n"/>
-      <c r="O10" s="13" t="n"/>
-      <c r="P10" s="13" t="n"/>
-      <c r="Q10" s="13" t="n"/>
-      <c r="R10" s="13" t="n"/>
-      <c r="S10" s="13" t="n"/>
-      <c r="T10" s="13" t="n"/>
-      <c r="U10" s="13" t="n"/>
-      <c r="V10" s="13" t="n"/>
-      <c r="W10" s="13" t="n"/>
-      <c r="X10" s="13" t="n"/>
-      <c r="Y10" s="13" t="n"/>
-      <c r="Z10" s="13" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4. Last Verified </t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="13" t="n"/>
-      <c r="D11" s="13" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="13" t="n"/>
-      <c r="G11" s="13" t="n"/>
-      <c r="H11" s="13" t="n"/>
-      <c r="I11" s="13" t="n"/>
-      <c r="J11" s="13" t="n"/>
-      <c r="K11" s="13" t="n"/>
-      <c r="L11" s="13" t="n"/>
-      <c r="M11" s="13" t="n"/>
-      <c r="N11" s="13" t="n"/>
-      <c r="O11" s="13" t="n"/>
-      <c r="P11" s="13" t="n"/>
-      <c r="Q11" s="13" t="n"/>
-      <c r="R11" s="13" t="n"/>
-      <c r="S11" s="13" t="n"/>
-      <c r="T11" s="13" t="n"/>
-      <c r="U11" s="13" t="n"/>
-      <c r="V11" s="13" t="n"/>
-      <c r="W11" s="13" t="n"/>
-      <c r="X11" s="13" t="n"/>
-      <c r="Y11" s="13" t="n"/>
-      <c r="Z11" s="13" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Date you last checked the page </t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="n"/>
-      <c r="C12" s="13" t="n"/>
-      <c r="D12" s="13" t="n"/>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="13" t="n"/>
-      <c r="G12" s="13" t="n"/>
-      <c r="H12" s="13" t="n"/>
-      <c r="I12" s="13" t="n"/>
-      <c r="J12" s="13" t="n"/>
-      <c r="K12" s="13" t="n"/>
-      <c r="L12" s="13" t="n"/>
-      <c r="M12" s="13" t="n"/>
-      <c r="N12" s="13" t="n"/>
-      <c r="O12" s="13" t="n"/>
-      <c r="P12" s="13" t="n"/>
-      <c r="Q12" s="13" t="n"/>
-      <c r="R12" s="13" t="n"/>
-      <c r="S12" s="13" t="n"/>
-      <c r="T12" s="13" t="n"/>
-      <c r="U12" s="13" t="n"/>
-      <c r="V12" s="13" t="n"/>
-      <c r="W12" s="13" t="n"/>
-      <c r="X12" s="13" t="n"/>
-      <c r="Y12" s="13" t="n"/>
-      <c r="Z12" s="13" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>5. Last Updated</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="n"/>
-      <c r="C13" s="13" t="n"/>
-      <c r="D13" s="13" t="n"/>
-      <c r="E13" s="13" t="n"/>
-      <c r="F13" s="13" t="n"/>
-      <c r="G13" s="13" t="n"/>
-      <c r="H13" s="13" t="n"/>
-      <c r="I13" s="13" t="n"/>
-      <c r="J13" s="13" t="n"/>
-      <c r="K13" s="13" t="n"/>
-      <c r="L13" s="13" t="n"/>
-      <c r="M13" s="13" t="n"/>
-      <c r="N13" s="13" t="n"/>
-      <c r="O13" s="13" t="n"/>
-      <c r="P13" s="13" t="n"/>
-      <c r="Q13" s="13" t="n"/>
-      <c r="R13" s="13" t="n"/>
-      <c r="S13" s="13" t="n"/>
-      <c r="T13" s="13" t="n"/>
-      <c r="U13" s="13" t="n"/>
-      <c r="V13" s="13" t="n"/>
-      <c r="W13" s="13" t="n"/>
-      <c r="X13" s="13" t="n"/>
-      <c r="Y13" s="13" t="n"/>
-      <c r="Z13" s="13" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> the page’s own update timestamp.</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="n"/>
-      <c r="C14" s="13" t="n"/>
-      <c r="D14" s="13" t="n"/>
-      <c r="E14" s="13" t="n"/>
-      <c r="F14" s="13" t="n"/>
-      <c r="G14" s="13" t="n"/>
-      <c r="H14" s="13" t="n"/>
-      <c r="I14" s="13" t="n"/>
-      <c r="J14" s="13" t="n"/>
-      <c r="K14" s="13" t="n"/>
-      <c r="L14" s="13" t="n"/>
-      <c r="M14" s="13" t="n"/>
-      <c r="N14" s="13" t="n"/>
-      <c r="O14" s="13" t="n"/>
-      <c r="P14" s="13" t="n"/>
-      <c r="Q14" s="13" t="n"/>
-      <c r="R14" s="13" t="n"/>
-      <c r="S14" s="13" t="n"/>
-      <c r="T14" s="13" t="n"/>
-      <c r="U14" s="13" t="n"/>
-      <c r="V14" s="13" t="n"/>
-      <c r="W14" s="13" t="n"/>
-      <c r="X14" s="13" t="n"/>
-      <c r="Y14" s="13" t="n"/>
-      <c r="Z14" s="13" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>This helps track fast‑moving agent ecosystems.</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="n"/>
-      <c r="C15" s="13" t="n"/>
-      <c r="D15" s="13" t="n"/>
-      <c r="E15" s="13" t="n"/>
-      <c r="F15" s="13" t="n"/>
-      <c r="G15" s="13" t="n"/>
-      <c r="H15" s="13" t="n"/>
-      <c r="I15" s="13" t="n"/>
-      <c r="J15" s="13" t="n"/>
-      <c r="K15" s="13" t="n"/>
-      <c r="L15" s="13" t="n"/>
-      <c r="M15" s="13" t="n"/>
-      <c r="N15" s="13" t="n"/>
-      <c r="O15" s="13" t="n"/>
-      <c r="P15" s="13" t="n"/>
-      <c r="Q15" s="13" t="n"/>
-      <c r="R15" s="13" t="n"/>
-      <c r="S15" s="13" t="n"/>
-      <c r="T15" s="13" t="n"/>
-      <c r="U15" s="13" t="n"/>
-      <c r="V15" s="13" t="n"/>
-      <c r="W15" s="13" t="n"/>
-      <c r="X15" s="13" t="n"/>
-      <c r="Y15" s="13" t="n"/>
-      <c r="Z15" s="13" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>6. Resource Type</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="n"/>
-      <c r="C16" s="13" t="n"/>
-      <c r="D16" s="13" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="13" t="n"/>
-      <c r="G16" s="13" t="n"/>
-      <c r="H16" s="13" t="n"/>
-      <c r="I16" s="13" t="n"/>
-      <c r="J16" s="13" t="n"/>
-      <c r="K16" s="13" t="n"/>
-      <c r="L16" s="13" t="n"/>
-      <c r="M16" s="13" t="n"/>
-      <c r="N16" s="13" t="n"/>
-      <c r="O16" s="13" t="n"/>
-      <c r="P16" s="13" t="n"/>
-      <c r="Q16" s="13" t="n"/>
-      <c r="R16" s="13" t="n"/>
-      <c r="S16" s="13" t="n"/>
-      <c r="T16" s="13" t="n"/>
-      <c r="U16" s="13" t="n"/>
-      <c r="V16" s="13" t="n"/>
-      <c r="W16" s="13" t="n"/>
-      <c r="X16" s="13" t="n"/>
-      <c r="Y16" s="13" t="n"/>
-      <c r="Z16" s="13" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>A simple categorical field:</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="n"/>
-      <c r="C17" s="13" t="n"/>
-      <c r="D17" s="13" t="n"/>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="13" t="n"/>
-      <c r="G17" s="13" t="n"/>
-      <c r="H17" s="13" t="n"/>
-      <c r="I17" s="13" t="n"/>
-      <c r="J17" s="13" t="n"/>
-      <c r="K17" s="13" t="n"/>
-      <c r="L17" s="13" t="n"/>
-      <c r="M17" s="13" t="n"/>
-      <c r="N17" s="13" t="n"/>
-      <c r="O17" s="13" t="n"/>
-      <c r="P17" s="13" t="n"/>
-      <c r="Q17" s="13" t="n"/>
-      <c r="R17" s="13" t="n"/>
-      <c r="S17" s="13" t="n"/>
-      <c r="T17" s="13" t="n"/>
-      <c r="U17" s="13" t="n"/>
-      <c r="V17" s="13" t="n"/>
-      <c r="W17" s="13" t="n"/>
-      <c r="X17" s="13" t="n"/>
-      <c r="Y17" s="13" t="n"/>
-      <c r="Z17" s="13" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Documentation</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="n"/>
-      <c r="C18" s="13" t="n"/>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="n"/>
-      <c r="G18" s="13" t="n"/>
-      <c r="H18" s="13" t="n"/>
-      <c r="I18" s="13" t="n"/>
-      <c r="J18" s="13" t="n"/>
-      <c r="K18" s="13" t="n"/>
-      <c r="L18" s="13" t="n"/>
-      <c r="M18" s="13" t="n"/>
-      <c r="N18" s="13" t="n"/>
-      <c r="O18" s="13" t="n"/>
-      <c r="P18" s="13" t="n"/>
-      <c r="Q18" s="13" t="n"/>
-      <c r="R18" s="13" t="n"/>
-      <c r="S18" s="13" t="n"/>
-      <c r="T18" s="13" t="n"/>
-      <c r="U18" s="13" t="n"/>
-      <c r="V18" s="13" t="n"/>
-      <c r="W18" s="13" t="n"/>
-      <c r="X18" s="13" t="n"/>
-      <c r="Y18" s="13" t="n"/>
-      <c r="Z18" s="13" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>API reference</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="n"/>
-      <c r="C19" s="13" t="n"/>
-      <c r="D19" s="13" t="n"/>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="13" t="n"/>
-      <c r="G19" s="13" t="n"/>
-      <c r="H19" s="13" t="n"/>
-      <c r="I19" s="13" t="n"/>
-      <c r="J19" s="13" t="n"/>
-      <c r="K19" s="13" t="n"/>
-      <c r="L19" s="13" t="n"/>
-      <c r="M19" s="13" t="n"/>
-      <c r="N19" s="13" t="n"/>
-      <c r="O19" s="13" t="n"/>
-      <c r="P19" s="13" t="n"/>
-      <c r="Q19" s="13" t="n"/>
-      <c r="R19" s="13" t="n"/>
-      <c r="S19" s="13" t="n"/>
-      <c r="T19" s="13" t="n"/>
-      <c r="U19" s="13" t="n"/>
-      <c r="V19" s="13" t="n"/>
-      <c r="W19" s="13" t="n"/>
-      <c r="X19" s="13" t="n"/>
-      <c r="Y19" s="13" t="n"/>
-      <c r="Z19" s="13" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Tutorial</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="n"/>
-      <c r="C20" s="13" t="n"/>
-      <c r="D20" s="13" t="n"/>
-      <c r="E20" s="13" t="n"/>
-      <c r="F20" s="13" t="n"/>
-      <c r="G20" s="13" t="n"/>
-      <c r="H20" s="13" t="n"/>
-      <c r="I20" s="13" t="n"/>
-      <c r="J20" s="13" t="n"/>
-      <c r="K20" s="13" t="n"/>
-      <c r="L20" s="13" t="n"/>
-      <c r="M20" s="13" t="n"/>
-      <c r="N20" s="13" t="n"/>
-      <c r="O20" s="13" t="n"/>
-      <c r="P20" s="13" t="n"/>
-      <c r="Q20" s="13" t="n"/>
-      <c r="R20" s="13" t="n"/>
-      <c r="S20" s="13" t="n"/>
-      <c r="T20" s="13" t="n"/>
-      <c r="U20" s="13" t="n"/>
-      <c r="V20" s="13" t="n"/>
-      <c r="W20" s="13" t="n"/>
-      <c r="X20" s="13" t="n"/>
-      <c r="Y20" s="13" t="n"/>
-      <c r="Z20" s="13" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Whitepaper</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="n"/>
-      <c r="C21" s="13" t="n"/>
-      <c r="D21" s="13" t="n"/>
-      <c r="E21" s="13" t="n"/>
-      <c r="F21" s="13" t="n"/>
-      <c r="G21" s="13" t="n"/>
-      <c r="H21" s="13" t="n"/>
-      <c r="I21" s="13" t="n"/>
-      <c r="J21" s="13" t="n"/>
-      <c r="K21" s="13" t="n"/>
-      <c r="L21" s="13" t="n"/>
-      <c r="M21" s="13" t="n"/>
-      <c r="N21" s="13" t="n"/>
-      <c r="O21" s="13" t="n"/>
-      <c r="P21" s="13" t="n"/>
-      <c r="Q21" s="13" t="n"/>
-      <c r="R21" s="13" t="n"/>
-      <c r="S21" s="13" t="n"/>
-      <c r="T21" s="13" t="n"/>
-      <c r="U21" s="13" t="n"/>
-      <c r="V21" s="13" t="n"/>
-      <c r="W21" s="13" t="n"/>
-      <c r="X21" s="13" t="n"/>
-      <c r="Y21" s="13" t="n"/>
-      <c r="Z21" s="13" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Blog post</t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="n"/>
-      <c r="C22" s="13" t="n"/>
-      <c r="D22" s="13" t="n"/>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="13" t="n"/>
-      <c r="G22" s="13" t="n"/>
-      <c r="H22" s="13" t="n"/>
-      <c r="I22" s="13" t="n"/>
-      <c r="J22" s="13" t="n"/>
-      <c r="K22" s="13" t="n"/>
-      <c r="L22" s="13" t="n"/>
-      <c r="M22" s="13" t="n"/>
-      <c r="N22" s="13" t="n"/>
-      <c r="O22" s="13" t="n"/>
-      <c r="P22" s="13" t="n"/>
-      <c r="Q22" s="13" t="n"/>
-      <c r="R22" s="13" t="n"/>
-      <c r="S22" s="13" t="n"/>
-      <c r="T22" s="13" t="n"/>
-      <c r="U22" s="13" t="n"/>
-      <c r="V22" s="13" t="n"/>
-      <c r="W22" s="13" t="n"/>
-      <c r="X22" s="13" t="n"/>
-      <c r="Y22" s="13" t="n"/>
-      <c r="Z22" s="13" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Example repo</t>
-        </is>
-      </c>
-      <c r="B23" s="13" t="n"/>
-      <c r="C23" s="13" t="n"/>
-      <c r="D23" s="13" t="n"/>
-      <c r="E23" s="13" t="n"/>
-      <c r="F23" s="13" t="n"/>
-      <c r="G23" s="13" t="n"/>
-      <c r="H23" s="13" t="n"/>
-      <c r="I23" s="13" t="n"/>
-      <c r="J23" s="13" t="n"/>
-      <c r="K23" s="13" t="n"/>
-      <c r="L23" s="13" t="n"/>
-      <c r="M23" s="13" t="n"/>
-      <c r="N23" s="13" t="n"/>
-      <c r="O23" s="13" t="n"/>
-      <c r="P23" s="13" t="n"/>
-      <c r="Q23" s="13" t="n"/>
-      <c r="R23" s="13" t="n"/>
-      <c r="S23" s="13" t="n"/>
-      <c r="T23" s="13" t="n"/>
-      <c r="U23" s="13" t="n"/>
-      <c r="V23" s="13" t="n"/>
-      <c r="W23" s="13" t="n"/>
-      <c r="X23" s="13" t="n"/>
-      <c r="Y23" s="13" t="n"/>
-      <c r="Z23" s="13" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>Governance guidance</t>
-        </is>
-      </c>
-      <c r="B24" s="13" t="n"/>
-      <c r="C24" s="13" t="n"/>
-      <c r="D24" s="13" t="n"/>
-      <c r="E24" s="13" t="n"/>
-      <c r="F24" s="13" t="n"/>
-      <c r="G24" s="13" t="n"/>
-      <c r="H24" s="13" t="n"/>
-      <c r="I24" s="13" t="n"/>
-      <c r="J24" s="13" t="n"/>
-      <c r="K24" s="13" t="n"/>
-      <c r="L24" s="13" t="n"/>
-      <c r="M24" s="13" t="n"/>
-      <c r="N24" s="13" t="n"/>
-      <c r="O24" s="13" t="n"/>
-      <c r="P24" s="13" t="n"/>
-      <c r="Q24" s="13" t="n"/>
-      <c r="R24" s="13" t="n"/>
-      <c r="S24" s="13" t="n"/>
-      <c r="T24" s="13" t="n"/>
-      <c r="U24" s="13" t="n"/>
-      <c r="V24" s="13" t="n"/>
-      <c r="W24" s="13" t="n"/>
-      <c r="X24" s="13" t="n"/>
-      <c r="Y24" s="13" t="n"/>
-      <c r="Z24" s="13" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>Architecture pattern</t>
-        </is>
-      </c>
-      <c r="B25" s="13" t="n"/>
-      <c r="C25" s="13" t="n"/>
-      <c r="D25" s="13" t="n"/>
-      <c r="E25" s="13" t="n"/>
-      <c r="F25" s="13" t="n"/>
-      <c r="G25" s="13" t="n"/>
-      <c r="H25" s="13" t="n"/>
-      <c r="I25" s="13" t="n"/>
-      <c r="J25" s="13" t="n"/>
-      <c r="K25" s="13" t="n"/>
-      <c r="L25" s="13" t="n"/>
-      <c r="M25" s="13" t="n"/>
-      <c r="N25" s="13" t="n"/>
-      <c r="O25" s="13" t="n"/>
-      <c r="P25" s="13" t="n"/>
-      <c r="Q25" s="13" t="n"/>
-      <c r="R25" s="13" t="n"/>
-      <c r="S25" s="13" t="n"/>
-      <c r="T25" s="13" t="n"/>
-      <c r="U25" s="13" t="n"/>
-      <c r="V25" s="13" t="n"/>
-      <c r="W25" s="13" t="n"/>
-      <c r="X25" s="13" t="n"/>
-      <c r="Y25" s="13" t="n"/>
-      <c r="Z25" s="13" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>This helps teams filter by what they need.</t>
-        </is>
-      </c>
-      <c r="B26" s="13" t="n"/>
-      <c r="C26" s="13" t="n"/>
-      <c r="D26" s="13" t="n"/>
-      <c r="E26" s="13" t="n"/>
-      <c r="F26" s="13" t="n"/>
-      <c r="G26" s="13" t="n"/>
-      <c r="H26" s="13" t="n"/>
-      <c r="I26" s="13" t="n"/>
-      <c r="J26" s="13" t="n"/>
-      <c r="K26" s="13" t="n"/>
-      <c r="L26" s="13" t="n"/>
-      <c r="M26" s="13" t="n"/>
-      <c r="N26" s="13" t="n"/>
-      <c r="O26" s="13" t="n"/>
-      <c r="P26" s="13" t="n"/>
-      <c r="Q26" s="13" t="n"/>
-      <c r="R26" s="13" t="n"/>
-      <c r="S26" s="13" t="n"/>
-      <c r="T26" s="13" t="n"/>
-      <c r="U26" s="13" t="n"/>
-      <c r="V26" s="13" t="n"/>
-      <c r="W26" s="13" t="n"/>
-      <c r="X26" s="13" t="n"/>
-      <c r="Y26" s="13" t="n"/>
-      <c r="Z26" s="13" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>7. Agentic Features Covered (Checklist)</t>
-        </is>
-      </c>
-      <c r="B27" s="13" t="n"/>
-      <c r="C27" s="13" t="n"/>
-      <c r="D27" s="13" t="n"/>
-      <c r="E27" s="13" t="n"/>
-      <c r="F27" s="13" t="n"/>
-      <c r="G27" s="13" t="n"/>
-      <c r="H27" s="13" t="n"/>
-      <c r="I27" s="13" t="n"/>
-      <c r="J27" s="13" t="n"/>
-      <c r="K27" s="13" t="n"/>
-      <c r="L27" s="13" t="n"/>
-      <c r="M27" s="13" t="n"/>
-      <c r="N27" s="13" t="n"/>
-      <c r="O27" s="13" t="n"/>
-      <c r="P27" s="13" t="n"/>
-      <c r="Q27" s="13" t="n"/>
-      <c r="R27" s="13" t="n"/>
-      <c r="S27" s="13" t="n"/>
-      <c r="T27" s="13" t="n"/>
-      <c r="U27" s="13" t="n"/>
-      <c r="V27" s="13" t="n"/>
-      <c r="W27" s="13" t="n"/>
-      <c r="X27" s="13" t="n"/>
-      <c r="Y27" s="13" t="n"/>
-      <c r="Z27" s="13" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Examples:</t>
-        </is>
-      </c>
-      <c r="B28" s="13" t="n"/>
-      <c r="C28" s="13" t="n"/>
-      <c r="D28" s="13" t="n"/>
-      <c r="E28" s="13" t="n"/>
-      <c r="F28" s="13" t="n"/>
-      <c r="G28" s="13" t="n"/>
-      <c r="H28" s="13" t="n"/>
-      <c r="I28" s="13" t="n"/>
-      <c r="J28" s="13" t="n"/>
-      <c r="K28" s="13" t="n"/>
-      <c r="L28" s="13" t="n"/>
-      <c r="M28" s="13" t="n"/>
-      <c r="N28" s="13" t="n"/>
-      <c r="O28" s="13" t="n"/>
-      <c r="P28" s="13" t="n"/>
-      <c r="Q28" s="13" t="n"/>
-      <c r="R28" s="13" t="n"/>
-      <c r="S28" s="13" t="n"/>
-      <c r="T28" s="13" t="n"/>
-      <c r="U28" s="13" t="n"/>
-      <c r="V28" s="13" t="n"/>
-      <c r="W28" s="13" t="n"/>
-      <c r="X28" s="13" t="n"/>
-      <c r="Y28" s="13" t="n"/>
-      <c r="Z28" s="13" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Hooks</t>
-        </is>
-      </c>
-      <c r="B29" s="13" t="n"/>
-      <c r="C29" s="13" t="n"/>
-      <c r="D29" s="13" t="n"/>
-      <c r="E29" s="13" t="n"/>
-      <c r="F29" s="13" t="n"/>
-      <c r="G29" s="13" t="n"/>
-      <c r="H29" s="13" t="n"/>
-      <c r="I29" s="13" t="n"/>
-      <c r="J29" s="13" t="n"/>
-      <c r="K29" s="13" t="n"/>
-      <c r="L29" s="13" t="n"/>
-      <c r="M29" s="13" t="n"/>
-      <c r="N29" s="13" t="n"/>
-      <c r="O29" s="13" t="n"/>
-      <c r="P29" s="13" t="n"/>
-      <c r="Q29" s="13" t="n"/>
-      <c r="R29" s="13" t="n"/>
-      <c r="S29" s="13" t="n"/>
-      <c r="T29" s="13" t="n"/>
-      <c r="U29" s="13" t="n"/>
-      <c r="V29" s="13" t="n"/>
-      <c r="W29" s="13" t="n"/>
-      <c r="X29" s="13" t="n"/>
-      <c r="Y29" s="13" t="n"/>
-      <c r="Z29" s="13" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>Skills</t>
-        </is>
-      </c>
-      <c r="B30" s="13" t="n"/>
-      <c r="C30" s="13" t="n"/>
-      <c r="D30" s="13" t="n"/>
-      <c r="E30" s="13" t="n"/>
-      <c r="F30" s="13" t="n"/>
-      <c r="G30" s="13" t="n"/>
-      <c r="H30" s="13" t="n"/>
-      <c r="I30" s="13" t="n"/>
-      <c r="J30" s="13" t="n"/>
-      <c r="K30" s="13" t="n"/>
-      <c r="L30" s="13" t="n"/>
-      <c r="M30" s="13" t="n"/>
-      <c r="N30" s="13" t="n"/>
-      <c r="O30" s="13" t="n"/>
-      <c r="P30" s="13" t="n"/>
-      <c r="Q30" s="13" t="n"/>
-      <c r="R30" s="13" t="n"/>
-      <c r="S30" s="13" t="n"/>
-      <c r="T30" s="13" t="n"/>
-      <c r="U30" s="13" t="n"/>
-      <c r="V30" s="13" t="n"/>
-      <c r="W30" s="13" t="n"/>
-      <c r="X30" s="13" t="n"/>
-      <c r="Y30" s="13" t="n"/>
-      <c r="Z30" s="13" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>MCP</t>
-        </is>
-      </c>
-      <c r="B31" s="13" t="n"/>
-      <c r="C31" s="13" t="n"/>
-      <c r="D31" s="13" t="n"/>
-      <c r="E31" s="13" t="n"/>
-      <c r="F31" s="13" t="n"/>
-      <c r="G31" s="13" t="n"/>
-      <c r="H31" s="13" t="n"/>
-      <c r="I31" s="13" t="n"/>
-      <c r="J31" s="13" t="n"/>
-      <c r="K31" s="13" t="n"/>
-      <c r="L31" s="13" t="n"/>
-      <c r="M31" s="13" t="n"/>
-      <c r="N31" s="13" t="n"/>
-      <c r="O31" s="13" t="n"/>
-      <c r="P31" s="13" t="n"/>
-      <c r="Q31" s="13" t="n"/>
-      <c r="R31" s="13" t="n"/>
-      <c r="S31" s="13" t="n"/>
-      <c r="T31" s="13" t="n"/>
-      <c r="U31" s="13" t="n"/>
-      <c r="V31" s="13" t="n"/>
-      <c r="W31" s="13" t="n"/>
-      <c r="X31" s="13" t="n"/>
-      <c r="Y31" s="13" t="n"/>
-      <c r="Z31" s="13" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Agent frameworks</t>
-        </is>
-      </c>
-      <c r="B32" s="13" t="n"/>
-      <c r="C32" s="13" t="n"/>
-      <c r="D32" s="13" t="n"/>
-      <c r="E32" s="13" t="n"/>
-      <c r="F32" s="13" t="n"/>
-      <c r="G32" s="13" t="n"/>
-      <c r="H32" s="13" t="n"/>
-      <c r="I32" s="13" t="n"/>
-      <c r="J32" s="13" t="n"/>
-      <c r="K32" s="13" t="n"/>
-      <c r="L32" s="13" t="n"/>
-      <c r="M32" s="13" t="n"/>
-      <c r="N32" s="13" t="n"/>
-      <c r="O32" s="13" t="n"/>
-      <c r="P32" s="13" t="n"/>
-      <c r="Q32" s="13" t="n"/>
-      <c r="R32" s="13" t="n"/>
-      <c r="S32" s="13" t="n"/>
-      <c r="T32" s="13" t="n"/>
-      <c r="U32" s="13" t="n"/>
-      <c r="V32" s="13" t="n"/>
-      <c r="W32" s="13" t="n"/>
-      <c r="X32" s="13" t="n"/>
-      <c r="Y32" s="13" t="n"/>
-      <c r="Z32" s="13" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Context window management</t>
-        </is>
-      </c>
-      <c r="B33" s="13" t="n"/>
-      <c r="C33" s="13" t="n"/>
-      <c r="D33" s="13" t="n"/>
-      <c r="E33" s="13" t="n"/>
-      <c r="F33" s="13" t="n"/>
-      <c r="G33" s="13" t="n"/>
-      <c r="H33" s="13" t="n"/>
-      <c r="I33" s="13" t="n"/>
-      <c r="J33" s="13" t="n"/>
-      <c r="K33" s="13" t="n"/>
-      <c r="L33" s="13" t="n"/>
-      <c r="M33" s="13" t="n"/>
-      <c r="N33" s="13" t="n"/>
-      <c r="O33" s="13" t="n"/>
-      <c r="P33" s="13" t="n"/>
-      <c r="Q33" s="13" t="n"/>
-      <c r="R33" s="13" t="n"/>
-      <c r="S33" s="13" t="n"/>
-      <c r="T33" s="13" t="n"/>
-      <c r="U33" s="13" t="n"/>
-      <c r="V33" s="13" t="n"/>
-      <c r="W33" s="13" t="n"/>
-      <c r="X33" s="13" t="n"/>
-      <c r="Y33" s="13" t="n"/>
-      <c r="Z33" s="13" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Deployment patterns</t>
-        </is>
-      </c>
-      <c r="B34" s="13" t="n"/>
-      <c r="C34" s="13" t="n"/>
-      <c r="D34" s="13" t="n"/>
-      <c r="E34" s="13" t="n"/>
-      <c r="F34" s="13" t="n"/>
-      <c r="G34" s="13" t="n"/>
-      <c r="H34" s="13" t="n"/>
-      <c r="I34" s="13" t="n"/>
-      <c r="J34" s="13" t="n"/>
-      <c r="K34" s="13" t="n"/>
-      <c r="L34" s="13" t="n"/>
-      <c r="M34" s="13" t="n"/>
-      <c r="N34" s="13" t="n"/>
-      <c r="O34" s="13" t="n"/>
-      <c r="P34" s="13" t="n"/>
-      <c r="Q34" s="13" t="n"/>
-      <c r="R34" s="13" t="n"/>
-      <c r="S34" s="13" t="n"/>
-      <c r="T34" s="13" t="n"/>
-      <c r="U34" s="13" t="n"/>
-      <c r="V34" s="13" t="n"/>
-      <c r="W34" s="13" t="n"/>
-      <c r="X34" s="13" t="n"/>
-      <c r="Y34" s="13" t="n"/>
-      <c r="Z34" s="13" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>Safety / guardrails</t>
-        </is>
-      </c>
-      <c r="B35" s="13" t="n"/>
-      <c r="C35" s="13" t="n"/>
-      <c r="D35" s="13" t="n"/>
-      <c r="E35" s="13" t="n"/>
-      <c r="F35" s="13" t="n"/>
-      <c r="G35" s="13" t="n"/>
-      <c r="H35" s="13" t="n"/>
-      <c r="I35" s="13" t="n"/>
-      <c r="J35" s="13" t="n"/>
-      <c r="K35" s="13" t="n"/>
-      <c r="L35" s="13" t="n"/>
-      <c r="M35" s="13" t="n"/>
-      <c r="N35" s="13" t="n"/>
-      <c r="O35" s="13" t="n"/>
-      <c r="P35" s="13" t="n"/>
-      <c r="Q35" s="13" t="n"/>
-      <c r="R35" s="13" t="n"/>
-      <c r="S35" s="13" t="n"/>
-      <c r="T35" s="13" t="n"/>
-      <c r="U35" s="13" t="n"/>
-      <c r="V35" s="13" t="n"/>
-      <c r="W35" s="13" t="n"/>
-      <c r="X35" s="13" t="n"/>
-      <c r="Y35" s="13" t="n"/>
-      <c r="Z35" s="13" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Evaluation / testing</t>
-        </is>
-      </c>
-      <c r="B36" s="13" t="n"/>
-      <c r="C36" s="13" t="n"/>
-      <c r="D36" s="13" t="n"/>
-      <c r="E36" s="13" t="n"/>
-      <c r="F36" s="13" t="n"/>
-      <c r="G36" s="13" t="n"/>
-      <c r="H36" s="13" t="n"/>
-      <c r="I36" s="13" t="n"/>
-      <c r="J36" s="13" t="n"/>
-      <c r="K36" s="13" t="n"/>
-      <c r="L36" s="13" t="n"/>
-      <c r="M36" s="13" t="n"/>
-      <c r="N36" s="13" t="n"/>
-      <c r="O36" s="13" t="n"/>
-      <c r="P36" s="13" t="n"/>
-      <c r="Q36" s="13" t="n"/>
-      <c r="R36" s="13" t="n"/>
-      <c r="S36" s="13" t="n"/>
-      <c r="T36" s="13" t="n"/>
-      <c r="U36" s="13" t="n"/>
-      <c r="V36" s="13" t="n"/>
-      <c r="W36" s="13" t="n"/>
-      <c r="X36" s="13" t="n"/>
-      <c r="Y36" s="13" t="n"/>
-      <c r="Z36" s="13" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>This is one of your most important columns.</t>
-        </is>
-      </c>
-      <c r="B37" s="13" t="n"/>
-      <c r="C37" s="13" t="n"/>
-      <c r="D37" s="13" t="n"/>
-      <c r="E37" s="13" t="n"/>
-      <c r="F37" s="13" t="n"/>
-      <c r="G37" s="13" t="n"/>
-      <c r="H37" s="13" t="n"/>
-      <c r="I37" s="13" t="n"/>
-      <c r="J37" s="13" t="n"/>
-      <c r="K37" s="13" t="n"/>
-      <c r="L37" s="13" t="n"/>
-      <c r="M37" s="13" t="n"/>
-      <c r="N37" s="13" t="n"/>
-      <c r="O37" s="13" t="n"/>
-      <c r="P37" s="13" t="n"/>
-      <c r="Q37" s="13" t="n"/>
-      <c r="R37" s="13" t="n"/>
-      <c r="S37" s="13" t="n"/>
-      <c r="T37" s="13" t="n"/>
-      <c r="U37" s="13" t="n"/>
-      <c r="V37" s="13" t="n"/>
-      <c r="W37" s="13" t="n"/>
-      <c r="X37" s="13" t="n"/>
-      <c r="Y37" s="13" t="n"/>
-      <c r="Z37" s="13" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>8. Topic Focus (Checklist)</t>
-        </is>
-      </c>
-      <c r="B38" s="13" t="n"/>
-      <c r="C38" s="13" t="n"/>
-      <c r="D38" s="13" t="n"/>
-      <c r="E38" s="13" t="n"/>
-      <c r="F38" s="13" t="n"/>
-      <c r="G38" s="13" t="n"/>
-      <c r="H38" s="13" t="n"/>
-      <c r="I38" s="13" t="n"/>
-      <c r="J38" s="13" t="n"/>
-      <c r="K38" s="13" t="n"/>
-      <c r="L38" s="13" t="n"/>
-      <c r="M38" s="13" t="n"/>
-      <c r="N38" s="13" t="n"/>
-      <c r="O38" s="13" t="n"/>
-      <c r="P38" s="13" t="n"/>
-      <c r="Q38" s="13" t="n"/>
-      <c r="R38" s="13" t="n"/>
-      <c r="S38" s="13" t="n"/>
-      <c r="T38" s="13" t="n"/>
-      <c r="U38" s="13" t="n"/>
-      <c r="V38" s="13" t="n"/>
-      <c r="W38" s="13" t="n"/>
-      <c r="X38" s="13" t="n"/>
-      <c r="Y38" s="13" t="n"/>
-      <c r="Z38" s="13" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>Architecture</t>
-        </is>
-      </c>
-      <c r="B39" s="13" t="n"/>
-      <c r="C39" s="13" t="n"/>
-      <c r="D39" s="13" t="n"/>
-      <c r="E39" s="13" t="n"/>
-      <c r="F39" s="13" t="n"/>
-      <c r="G39" s="13" t="n"/>
-      <c r="H39" s="13" t="n"/>
-      <c r="I39" s="13" t="n"/>
-      <c r="J39" s="13" t="n"/>
-      <c r="K39" s="13" t="n"/>
-      <c r="L39" s="13" t="n"/>
-      <c r="M39" s="13" t="n"/>
-      <c r="N39" s="13" t="n"/>
-      <c r="O39" s="13" t="n"/>
-      <c r="P39" s="13" t="n"/>
-      <c r="Q39" s="13" t="n"/>
-      <c r="R39" s="13" t="n"/>
-      <c r="S39" s="13" t="n"/>
-      <c r="T39" s="13" t="n"/>
-      <c r="U39" s="13" t="n"/>
-      <c r="V39" s="13" t="n"/>
-      <c r="W39" s="13" t="n"/>
-      <c r="X39" s="13" t="n"/>
-      <c r="Y39" s="13" t="n"/>
-      <c r="Z39" s="13" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>Security</t>
-        </is>
-      </c>
-      <c r="B40" s="13" t="n"/>
-      <c r="C40" s="13" t="n"/>
-      <c r="D40" s="13" t="n"/>
-      <c r="E40" s="13" t="n"/>
-      <c r="F40" s="13" t="n"/>
-      <c r="G40" s="13" t="n"/>
-      <c r="H40" s="13" t="n"/>
-      <c r="I40" s="13" t="n"/>
-      <c r="J40" s="13" t="n"/>
-      <c r="K40" s="13" t="n"/>
-      <c r="L40" s="13" t="n"/>
-      <c r="M40" s="13" t="n"/>
-      <c r="N40" s="13" t="n"/>
-      <c r="O40" s="13" t="n"/>
-      <c r="P40" s="13" t="n"/>
-      <c r="Q40" s="13" t="n"/>
-      <c r="R40" s="13" t="n"/>
-      <c r="S40" s="13" t="n"/>
-      <c r="T40" s="13" t="n"/>
-      <c r="U40" s="13" t="n"/>
-      <c r="V40" s="13" t="n"/>
-      <c r="W40" s="13" t="n"/>
-      <c r="X40" s="13" t="n"/>
-      <c r="Y40" s="13" t="n"/>
-      <c r="Z40" s="13" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>Data governance</t>
-        </is>
-      </c>
-      <c r="B41" s="13" t="inlineStr">
-        <is>
-          <t>Focuses specifically on the technical protocols, access controls, data-line security, and de-identification standards used to protect the integrity, quality, and privacy of information throughout its lifecycle</t>
-        </is>
-      </c>
-      <c r="C41" s="13" t="n"/>
-      <c r="D41" s="13" t="n"/>
-      <c r="E41" s="13" t="n"/>
-      <c r="F41" s="13" t="n"/>
-      <c r="G41" s="13" t="n"/>
-      <c r="H41" s="13" t="n"/>
-      <c r="I41" s="13" t="n"/>
-      <c r="J41" s="13" t="n"/>
-      <c r="K41" s="13" t="n"/>
-      <c r="L41" s="13" t="n"/>
-      <c r="M41" s="13" t="n"/>
-      <c r="N41" s="13" t="n"/>
-      <c r="O41" s="13" t="n"/>
-      <c r="P41" s="13" t="n"/>
-      <c r="Q41" s="13" t="n"/>
-      <c r="R41" s="13" t="n"/>
-      <c r="S41" s="13" t="n"/>
-      <c r="T41" s="13" t="n"/>
-      <c r="U41" s="13" t="n"/>
-      <c r="V41" s="13" t="n"/>
-      <c r="W41" s="13" t="n"/>
-      <c r="X41" s="13" t="n"/>
-      <c r="Y41" s="13" t="n"/>
-      <c r="Z41" s="13" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="B42" s="13" t="inlineStr">
-        <is>
-          <t>The overarching organizational policies, compliance frameworks, and capital allocation strategies that dictate how an enterprise manages its broader IT infrastructure, risk tolerances, and vendor choices</t>
-        </is>
-      </c>
-      <c r="C42" s="13" t="n"/>
-      <c r="D42" s="13" t="n"/>
-      <c r="E42" s="13" t="n"/>
-      <c r="F42" s="13" t="n"/>
-      <c r="G42" s="13" t="n"/>
-      <c r="H42" s="13" t="n"/>
-      <c r="I42" s="13" t="n"/>
-      <c r="J42" s="13" t="n"/>
-      <c r="K42" s="13" t="n"/>
-      <c r="L42" s="13" t="n"/>
-      <c r="M42" s="13" t="n"/>
-      <c r="N42" s="13" t="n"/>
-      <c r="O42" s="13" t="n"/>
-      <c r="P42" s="13" t="n"/>
-      <c r="Q42" s="13" t="n"/>
-      <c r="R42" s="13" t="n"/>
-      <c r="S42" s="13" t="n"/>
-      <c r="T42" s="13" t="n"/>
-      <c r="U42" s="13" t="n"/>
-      <c r="V42" s="13" t="n"/>
-      <c r="W42" s="13" t="n"/>
-      <c r="X42" s="13" t="n"/>
-      <c r="Y42" s="13" t="n"/>
-      <c r="Z42" s="13" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Implementation</t>
-        </is>
-      </c>
-      <c r="B43" s="13" t="n"/>
-      <c r="C43" s="13" t="n"/>
-      <c r="D43" s="13" t="n"/>
-      <c r="E43" s="13" t="n"/>
-      <c r="F43" s="13" t="n"/>
-      <c r="G43" s="13" t="n"/>
-      <c r="H43" s="13" t="n"/>
-      <c r="I43" s="13" t="n"/>
-      <c r="J43" s="13" t="n"/>
-      <c r="K43" s="13" t="n"/>
-      <c r="L43" s="13" t="n"/>
-      <c r="M43" s="13" t="n"/>
-      <c r="N43" s="13" t="n"/>
-      <c r="O43" s="13" t="n"/>
-      <c r="P43" s="13" t="n"/>
-      <c r="Q43" s="13" t="n"/>
-      <c r="R43" s="13" t="n"/>
-      <c r="S43" s="13" t="n"/>
-      <c r="T43" s="13" t="n"/>
-      <c r="U43" s="13" t="n"/>
-      <c r="V43" s="13" t="n"/>
-      <c r="W43" s="13" t="n"/>
-      <c r="X43" s="13" t="n"/>
-      <c r="Y43" s="13" t="n"/>
-      <c r="Z43" s="13" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>Deployment</t>
-        </is>
-      </c>
-      <c r="B44" s="13" t="inlineStr">
-        <is>
-          <t>The tactical, hands-on execution of installing, configuring, provisioning, and launching software or hardware systems within a specific operational environment</t>
-        </is>
-      </c>
-      <c r="C44" s="13" t="n"/>
-      <c r="D44" s="13" t="n"/>
-      <c r="E44" s="13" t="n"/>
-      <c r="F44" s="13" t="n"/>
-      <c r="G44" s="13" t="n"/>
-      <c r="H44" s="13" t="n"/>
-      <c r="I44" s="13" t="n"/>
-      <c r="J44" s="13" t="n"/>
-      <c r="K44" s="13" t="n"/>
-      <c r="L44" s="13" t="n"/>
-      <c r="M44" s="13" t="n"/>
-      <c r="N44" s="13" t="n"/>
-      <c r="O44" s="13" t="n"/>
-      <c r="P44" s="13" t="n"/>
-      <c r="Q44" s="13" t="n"/>
-      <c r="R44" s="13" t="n"/>
-      <c r="S44" s="13" t="n"/>
-      <c r="T44" s="13" t="n"/>
-      <c r="U44" s="13" t="n"/>
-      <c r="V44" s="13" t="n"/>
-      <c r="W44" s="13" t="n"/>
-      <c r="X44" s="13" t="n"/>
-      <c r="Y44" s="13" t="n"/>
-      <c r="Z44" s="13" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>Workflow integration</t>
-        </is>
-      </c>
-      <c r="B45" s="13" t="n"/>
-      <c r="C45" s="13" t="n"/>
-      <c r="D45" s="13" t="n"/>
-      <c r="E45" s="13" t="n"/>
-      <c r="F45" s="13" t="n"/>
-      <c r="G45" s="13" t="n"/>
-      <c r="H45" s="13" t="n"/>
-      <c r="I45" s="13" t="n"/>
-      <c r="J45" s="13" t="n"/>
-      <c r="K45" s="13" t="n"/>
-      <c r="L45" s="13" t="n"/>
-      <c r="M45" s="13" t="n"/>
-      <c r="N45" s="13" t="n"/>
-      <c r="O45" s="13" t="n"/>
-      <c r="P45" s="13" t="n"/>
-      <c r="Q45" s="13" t="n"/>
-      <c r="R45" s="13" t="n"/>
-      <c r="S45" s="13" t="n"/>
-      <c r="T45" s="13" t="n"/>
-      <c r="U45" s="13" t="n"/>
-      <c r="V45" s="13" t="n"/>
-      <c r="W45" s="13" t="n"/>
-      <c r="X45" s="13" t="n"/>
-      <c r="Y45" s="13" t="n"/>
-      <c r="Z45" s="13" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>Model selection</t>
-        </is>
-      </c>
-      <c r="B46" s="13" t="n"/>
-      <c r="C46" s="13" t="n"/>
-      <c r="D46" s="13" t="n"/>
-      <c r="E46" s="13" t="n"/>
-      <c r="F46" s="13" t="n"/>
-      <c r="G46" s="13" t="n"/>
-      <c r="H46" s="13" t="n"/>
-      <c r="I46" s="13" t="n"/>
-      <c r="J46" s="13" t="n"/>
-      <c r="K46" s="13" t="n"/>
-      <c r="L46" s="13" t="n"/>
-      <c r="M46" s="13" t="n"/>
-      <c r="N46" s="13" t="n"/>
-      <c r="O46" s="13" t="n"/>
-      <c r="P46" s="13" t="n"/>
-      <c r="Q46" s="13" t="n"/>
-      <c r="R46" s="13" t="n"/>
-      <c r="S46" s="13" t="n"/>
-      <c r="T46" s="13" t="n"/>
-      <c r="U46" s="13" t="n"/>
-      <c r="V46" s="13" t="n"/>
-      <c r="W46" s="13" t="n"/>
-      <c r="X46" s="13" t="n"/>
-      <c r="Y46" s="13" t="n"/>
-      <c r="Z46" s="13" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>Evaluation</t>
-        </is>
-      </c>
-      <c r="B47" s="13" t="n"/>
-      <c r="C47" s="13" t="n"/>
-      <c r="D47" s="13" t="n"/>
-      <c r="E47" s="13" t="n"/>
-      <c r="F47" s="13" t="n"/>
-      <c r="G47" s="13" t="n"/>
-      <c r="H47" s="13" t="n"/>
-      <c r="I47" s="13" t="n"/>
-      <c r="J47" s="13" t="n"/>
-      <c r="K47" s="13" t="n"/>
-      <c r="L47" s="13" t="n"/>
-      <c r="M47" s="13" t="n"/>
-      <c r="N47" s="13" t="n"/>
-      <c r="O47" s="13" t="n"/>
-      <c r="P47" s="13" t="n"/>
-      <c r="Q47" s="13" t="n"/>
-      <c r="R47" s="13" t="n"/>
-      <c r="S47" s="13" t="n"/>
-      <c r="T47" s="13" t="n"/>
-      <c r="U47" s="13" t="n"/>
-      <c r="V47" s="13" t="n"/>
-      <c r="W47" s="13" t="n"/>
-      <c r="X47" s="13" t="n"/>
-      <c r="Y47" s="13" t="n"/>
-      <c r="Z47" s="13" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>Architecture Compute</t>
-        </is>
-      </c>
-      <c r="B48" s="13" t="inlineStr">
-        <is>
-          <t>Physical node topologies, hardware constraints, VRAM bounds, and localized compute execution profiles.</t>
-        </is>
-      </c>
-      <c r="C48" s="13" t="n"/>
-      <c r="D48" s="13" t="n"/>
-      <c r="E48" s="13" t="n"/>
-      <c r="F48" s="13" t="n"/>
-      <c r="G48" s="13" t="n"/>
-      <c r="H48" s="13" t="n"/>
-      <c r="I48" s="13" t="n"/>
-      <c r="J48" s="13" t="n"/>
-      <c r="K48" s="13" t="n"/>
-      <c r="L48" s="13" t="n"/>
-      <c r="M48" s="13" t="n"/>
-      <c r="N48" s="13" t="n"/>
-      <c r="O48" s="13" t="n"/>
-      <c r="P48" s="13" t="n"/>
-      <c r="Q48" s="13" t="n"/>
-      <c r="R48" s="13" t="n"/>
-      <c r="S48" s="13" t="n"/>
-      <c r="T48" s="13" t="n"/>
-      <c r="U48" s="13" t="n"/>
-      <c r="V48" s="13" t="n"/>
-      <c r="W48" s="13" t="n"/>
-      <c r="X48" s="13" t="n"/>
-      <c r="Y48" s="13" t="n"/>
-      <c r="Z48" s="13" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>Network Isolation</t>
-        </is>
-      </c>
-      <c r="B49" s="13" t="inlineStr">
-        <is>
-          <t>Non-egress boundaries, air-gapped artifact staging, localized cloud VPC containers, and firewalled local registries.</t>
-        </is>
-      </c>
-      <c r="C49" s="13" t="n"/>
-      <c r="D49" s="13" t="n"/>
-      <c r="E49" s="13" t="n"/>
-      <c r="F49" s="13" t="n"/>
-      <c r="G49" s="13" t="n"/>
-      <c r="H49" s="13" t="n"/>
-      <c r="I49" s="13" t="n"/>
-      <c r="J49" s="13" t="n"/>
-      <c r="K49" s="13" t="n"/>
-      <c r="L49" s="13" t="n"/>
-      <c r="M49" s="13" t="n"/>
-      <c r="N49" s="13" t="n"/>
-      <c r="O49" s="13" t="n"/>
-      <c r="P49" s="13" t="n"/>
-      <c r="Q49" s="13" t="n"/>
-      <c r="R49" s="13" t="n"/>
-      <c r="S49" s="13" t="n"/>
-      <c r="T49" s="13" t="n"/>
-      <c r="U49" s="13" t="n"/>
-      <c r="V49" s="13" t="n"/>
-      <c r="W49" s="13" t="n"/>
-      <c r="X49" s="13" t="n"/>
-      <c r="Y49" s="13" t="n"/>
-      <c r="Z49" s="13" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>Infrastructure Security</t>
-        </is>
-      </c>
-      <c r="B50" s="13" t="inlineStr">
-        <is>
-          <t>For on-prem LLM deployments, it captures the security of the compute stack as well as the data pipelines</t>
-        </is>
-      </c>
-      <c r="C50" s="13" t="n"/>
-      <c r="D50" s="13" t="n"/>
-      <c r="E50" s="13" t="n"/>
-      <c r="F50" s="13" t="n"/>
-      <c r="G50" s="13" t="n"/>
-      <c r="H50" s="13" t="n"/>
-      <c r="I50" s="13" t="n"/>
-      <c r="J50" s="13" t="n"/>
-      <c r="K50" s="13" t="n"/>
-      <c r="L50" s="13" t="n"/>
-      <c r="M50" s="13" t="n"/>
-      <c r="N50" s="13" t="n"/>
-      <c r="O50" s="13" t="n"/>
-      <c r="P50" s="13" t="n"/>
-      <c r="Q50" s="13" t="n"/>
-      <c r="R50" s="13" t="n"/>
-      <c r="S50" s="13" t="n"/>
-      <c r="T50" s="13" t="n"/>
-      <c r="U50" s="13" t="n"/>
-      <c r="V50" s="13" t="n"/>
-      <c r="W50" s="13" t="n"/>
-      <c r="X50" s="13" t="n"/>
-      <c r="Y50" s="13" t="n"/>
-      <c r="Z50" s="13" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>Self‑hosted AI</t>
-        </is>
-      </c>
-      <c r="B51" s="13" t="inlineStr">
-        <is>
-          <t>Self‑hosted, open‑weights models in contrast to API‑based models like OpenAI, Anthropic, or Gemini</t>
-        </is>
-      </c>
-      <c r="C51" s="13" t="n"/>
-      <c r="D51" s="13" t="n"/>
-      <c r="E51" s="13" t="n"/>
-      <c r="F51" s="13" t="n"/>
-      <c r="G51" s="13" t="n"/>
-      <c r="H51" s="13" t="n"/>
-      <c r="I51" s="13" t="n"/>
-      <c r="J51" s="13" t="n"/>
-      <c r="K51" s="13" t="n"/>
-      <c r="L51" s="13" t="n"/>
-      <c r="M51" s="13" t="n"/>
-      <c r="N51" s="13" t="n"/>
-      <c r="O51" s="13" t="n"/>
-      <c r="P51" s="13" t="n"/>
-      <c r="Q51" s="13" t="n"/>
-      <c r="R51" s="13" t="n"/>
-      <c r="S51" s="13" t="n"/>
-      <c r="T51" s="13" t="n"/>
-      <c r="U51" s="13" t="n"/>
-      <c r="V51" s="13" t="n"/>
-      <c r="W51" s="13" t="n"/>
-      <c r="X51" s="13" t="n"/>
-      <c r="Y51" s="13" t="n"/>
-      <c r="Z51" s="13" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Data Protection</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Safeguarding sensitive data specifically (EDAM ontology: "Management of sensitive data") -- distinct from the broader "Security" term above. Newly available for Topic Focus.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Controlled vocabulary standard: EDAM ontology (Data management branch)</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>http://edamontology.org/topic_3071 -- "Data governance" and "Workflows" above are EDAM terms (topic_3571, topic_0769). "Data Protection" above is EDAM topic_4044. Also available for future use: FAIR data (topic_4012), Data quality management (topic_3572), Data curation and archival (topic_0219), Data integration and warehousing (topic_3366). Open ontology, not a paywalled standard -- browsable at https://www.ebi.ac.uk/ols4/ontologies/edam</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Optional secondary axis: NIST AI RMF 1.0 trustworthy-AI characteristics</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>https://nvlpubs.nist.gov/nistpubs/ai/NIST.AI.100-1.pdf -- Valid and Reliable, Safe, Secure and Resilient, Accountable and Transparent, Explainable and Interpretable, Privacy-Enhanced, Fair (harmful bias managed). Optional: for AI-trustworthiness framing EDAM doesn't cover. NOTE: NIST's "Fair (harmful bias managed)" is unrelated to EDAM's "FAIR data" (Findable/Accessible/Interoperable/Reusable data principles) despite sharing the word -- do not conflate the two if both are ever used as tags.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>This helps research IT teams quickly find relevant material.</t>
-        </is>
-      </c>
-      <c r="B55" s="13" t="n"/>
-      <c r="C55" s="13" t="n"/>
-      <c r="D55" s="13" t="n"/>
-      <c r="E55" s="13" t="n"/>
-      <c r="F55" s="13" t="n"/>
-      <c r="G55" s="13" t="n"/>
-      <c r="H55" s="13" t="n"/>
-      <c r="I55" s="13" t="n"/>
-      <c r="J55" s="13" t="n"/>
-      <c r="K55" s="13" t="n"/>
-      <c r="L55" s="13" t="n"/>
-      <c r="M55" s="13" t="n"/>
-      <c r="N55" s="13" t="n"/>
-      <c r="O55" s="13" t="n"/>
-      <c r="P55" s="13" t="n"/>
-      <c r="Q55" s="13" t="n"/>
-      <c r="R55" s="13" t="n"/>
-      <c r="S55" s="13" t="n"/>
-      <c r="T55" s="13" t="n"/>
-      <c r="U55" s="13" t="n"/>
-      <c r="V55" s="13" t="n"/>
-      <c r="W55" s="13" t="n"/>
-      <c r="X55" s="13" t="n"/>
-      <c r="Y55" s="13" t="n"/>
-      <c r="Z55" s="13" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>9. Relevance to Research Cyberinfrastructure</t>
-        </is>
-      </c>
-      <c r="B56" s="13" t="n"/>
-      <c r="C56" s="13" t="n"/>
-      <c r="D56" s="13" t="n"/>
-      <c r="E56" s="13" t="n"/>
-      <c r="F56" s="13" t="n"/>
-      <c r="G56" s="13" t="n"/>
-      <c r="H56" s="13" t="n"/>
-      <c r="I56" s="13" t="n"/>
-      <c r="J56" s="13" t="n"/>
-      <c r="K56" s="13" t="n"/>
-      <c r="L56" s="13" t="n"/>
-      <c r="M56" s="13" t="n"/>
-      <c r="N56" s="13" t="n"/>
-      <c r="O56" s="13" t="n"/>
-      <c r="P56" s="13" t="n"/>
-      <c r="Q56" s="13" t="n"/>
-      <c r="R56" s="13" t="n"/>
-      <c r="S56" s="13" t="n"/>
-      <c r="T56" s="13" t="n"/>
-      <c r="U56" s="13" t="n"/>
-      <c r="V56" s="13" t="n"/>
-      <c r="W56" s="13" t="n"/>
-      <c r="X56" s="13" t="n"/>
-      <c r="Y56" s="13" t="n"/>
-      <c r="Z56" s="13" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>A short tag describing why this matters to research platforms:</t>
-        </is>
-      </c>
-      <c r="B57" s="13" t="n"/>
-      <c r="C57" s="13" t="n"/>
-      <c r="D57" s="13" t="n"/>
-      <c r="E57" s="13" t="n"/>
-      <c r="F57" s="13" t="n"/>
-      <c r="G57" s="13" t="n"/>
-      <c r="H57" s="13" t="n"/>
-      <c r="I57" s="13" t="n"/>
-      <c r="J57" s="13" t="n"/>
-      <c r="K57" s="13" t="n"/>
-      <c r="L57" s="13" t="n"/>
-      <c r="M57" s="13" t="n"/>
-      <c r="N57" s="13" t="n"/>
-      <c r="O57" s="13" t="n"/>
-      <c r="P57" s="13" t="n"/>
-      <c r="Q57" s="13" t="n"/>
-      <c r="R57" s="13" t="n"/>
-      <c r="S57" s="13" t="n"/>
-      <c r="T57" s="13" t="n"/>
-      <c r="U57" s="13" t="n"/>
-      <c r="V57" s="13" t="n"/>
-      <c r="W57" s="13" t="n"/>
-      <c r="X57" s="13" t="n"/>
-      <c r="Y57" s="13" t="n"/>
-      <c r="Z57" s="13" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>Examples:</t>
-        </is>
-      </c>
-      <c r="B58" s="13" t="n"/>
-      <c r="C58" s="13" t="n"/>
-      <c r="D58" s="13" t="n"/>
-      <c r="E58" s="13" t="n"/>
-      <c r="F58" s="13" t="n"/>
-      <c r="G58" s="13" t="n"/>
-      <c r="H58" s="13" t="n"/>
-      <c r="I58" s="13" t="n"/>
-      <c r="J58" s="13" t="n"/>
-      <c r="K58" s="13" t="n"/>
-      <c r="L58" s="13" t="n"/>
-      <c r="M58" s="13" t="n"/>
-      <c r="N58" s="13" t="n"/>
-      <c r="O58" s="13" t="n"/>
-      <c r="P58" s="13" t="n"/>
-      <c r="Q58" s="13" t="n"/>
-      <c r="R58" s="13" t="n"/>
-      <c r="S58" s="13" t="n"/>
-      <c r="T58" s="13" t="n"/>
-      <c r="U58" s="13" t="n"/>
-      <c r="V58" s="13" t="n"/>
-      <c r="W58" s="13" t="n"/>
-      <c r="X58" s="13" t="n"/>
-      <c r="Y58" s="13" t="n"/>
-      <c r="Z58" s="13" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>Workflow orchestration</t>
-        </is>
-      </c>
-      <c r="B59" s="13" t="n"/>
-      <c r="C59" s="13" t="n"/>
-      <c r="D59" s="13" t="n"/>
-      <c r="E59" s="13" t="n"/>
-      <c r="F59" s="13" t="n"/>
-      <c r="G59" s="13" t="n"/>
-      <c r="H59" s="13" t="n"/>
-      <c r="I59" s="13" t="n"/>
-      <c r="J59" s="13" t="n"/>
-      <c r="K59" s="13" t="n"/>
-      <c r="L59" s="13" t="n"/>
-      <c r="M59" s="13" t="n"/>
-      <c r="N59" s="13" t="n"/>
-      <c r="O59" s="13" t="n"/>
-      <c r="P59" s="13" t="n"/>
-      <c r="Q59" s="13" t="n"/>
-      <c r="R59" s="13" t="n"/>
-      <c r="S59" s="13" t="n"/>
-      <c r="T59" s="13" t="n"/>
-      <c r="U59" s="13" t="n"/>
-      <c r="V59" s="13" t="n"/>
-      <c r="W59" s="13" t="n"/>
-      <c r="X59" s="13" t="n"/>
-      <c r="Y59" s="13" t="n"/>
-      <c r="Z59" s="13" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>Data portal integration</t>
-        </is>
-      </c>
-      <c r="B60" s="13" t="n"/>
-      <c r="C60" s="13" t="n"/>
-      <c r="D60" s="13" t="n"/>
-      <c r="E60" s="13" t="n"/>
-      <c r="F60" s="13" t="n"/>
-      <c r="G60" s="13" t="n"/>
-      <c r="H60" s="13" t="n"/>
-      <c r="I60" s="13" t="n"/>
-      <c r="J60" s="13" t="n"/>
-      <c r="K60" s="13" t="n"/>
-      <c r="L60" s="13" t="n"/>
-      <c r="M60" s="13" t="n"/>
-      <c r="N60" s="13" t="n"/>
-      <c r="O60" s="13" t="n"/>
-      <c r="P60" s="13" t="n"/>
-      <c r="Q60" s="13" t="n"/>
-      <c r="R60" s="13" t="n"/>
-      <c r="S60" s="13" t="n"/>
-      <c r="T60" s="13" t="n"/>
-      <c r="U60" s="13" t="n"/>
-      <c r="V60" s="13" t="n"/>
-      <c r="W60" s="13" t="n"/>
-      <c r="X60" s="13" t="n"/>
-      <c r="Y60" s="13" t="n"/>
-      <c r="Z60" s="13" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>Metadata / provenance</t>
-        </is>
-      </c>
-      <c r="B61" s="13" t="n"/>
-      <c r="C61" s="13" t="n"/>
-      <c r="D61" s="13" t="n"/>
-      <c r="E61" s="13" t="n"/>
-      <c r="F61" s="13" t="n"/>
-      <c r="G61" s="13" t="n"/>
-      <c r="H61" s="13" t="n"/>
-      <c r="I61" s="13" t="n"/>
-      <c r="J61" s="13" t="n"/>
-      <c r="K61" s="13" t="n"/>
-      <c r="L61" s="13" t="n"/>
-      <c r="M61" s="13" t="n"/>
-      <c r="N61" s="13" t="n"/>
-      <c r="O61" s="13" t="n"/>
-      <c r="P61" s="13" t="n"/>
-      <c r="Q61" s="13" t="n"/>
-      <c r="R61" s="13" t="n"/>
-      <c r="S61" s="13" t="n"/>
-      <c r="T61" s="13" t="n"/>
-      <c r="U61" s="13" t="n"/>
-      <c r="V61" s="13" t="n"/>
-      <c r="W61" s="13" t="n"/>
-      <c r="X61" s="13" t="n"/>
-      <c r="Y61" s="13" t="n"/>
-      <c r="Z61" s="13" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>Multi‑agent coordination</t>
-        </is>
-      </c>
-      <c r="B62" s="13" t="n"/>
-      <c r="C62" s="13" t="n"/>
-      <c r="D62" s="13" t="n"/>
-      <c r="E62" s="13" t="n"/>
-      <c r="F62" s="13" t="n"/>
-      <c r="G62" s="13" t="n"/>
-      <c r="H62" s="13" t="n"/>
-      <c r="I62" s="13" t="n"/>
-      <c r="J62" s="13" t="n"/>
-      <c r="K62" s="13" t="n"/>
-      <c r="L62" s="13" t="n"/>
-      <c r="M62" s="13" t="n"/>
-      <c r="N62" s="13" t="n"/>
-      <c r="O62" s="13" t="n"/>
-      <c r="P62" s="13" t="n"/>
-      <c r="Q62" s="13" t="n"/>
-      <c r="R62" s="13" t="n"/>
-      <c r="S62" s="13" t="n"/>
-      <c r="T62" s="13" t="n"/>
-      <c r="U62" s="13" t="n"/>
-      <c r="V62" s="13" t="n"/>
-      <c r="W62" s="13" t="n"/>
-      <c r="X62" s="13" t="n"/>
-      <c r="Y62" s="13" t="n"/>
-      <c r="Z62" s="13" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>HPC / cloud hybrid workflows</t>
-        </is>
-      </c>
-      <c r="B63" s="13" t="n"/>
-      <c r="C63" s="13" t="n"/>
-      <c r="D63" s="13" t="n"/>
-      <c r="E63" s="13" t="n"/>
-      <c r="F63" s="13" t="n"/>
-      <c r="G63" s="13" t="n"/>
-      <c r="H63" s="13" t="n"/>
-      <c r="I63" s="13" t="n"/>
-      <c r="J63" s="13" t="n"/>
-      <c r="K63" s="13" t="n"/>
-      <c r="L63" s="13" t="n"/>
-      <c r="M63" s="13" t="n"/>
-      <c r="N63" s="13" t="n"/>
-      <c r="O63" s="13" t="n"/>
-      <c r="P63" s="13" t="n"/>
-      <c r="Q63" s="13" t="n"/>
-      <c r="R63" s="13" t="n"/>
-      <c r="S63" s="13" t="n"/>
-      <c r="T63" s="13" t="n"/>
-      <c r="U63" s="13" t="n"/>
-      <c r="V63" s="13" t="n"/>
-      <c r="W63" s="13" t="n"/>
-      <c r="X63" s="13" t="n"/>
-      <c r="Y63" s="13" t="n"/>
-      <c r="Z63" s="13" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>Reproducibility</t>
-        </is>
-      </c>
-      <c r="B64" s="13" t="n"/>
-      <c r="C64" s="13" t="n"/>
-      <c r="D64" s="13" t="n"/>
-      <c r="E64" s="13" t="n"/>
-      <c r="F64" s="13" t="n"/>
-      <c r="G64" s="13" t="n"/>
-      <c r="H64" s="13" t="n"/>
-      <c r="I64" s="13" t="n"/>
-      <c r="J64" s="13" t="n"/>
-      <c r="K64" s="13" t="n"/>
-      <c r="L64" s="13" t="n"/>
-      <c r="M64" s="13" t="n"/>
-      <c r="N64" s="13" t="n"/>
-      <c r="O64" s="13" t="n"/>
-      <c r="P64" s="13" t="n"/>
-      <c r="Q64" s="13" t="n"/>
-      <c r="R64" s="13" t="n"/>
-      <c r="S64" s="13" t="n"/>
-      <c r="T64" s="13" t="n"/>
-      <c r="U64" s="13" t="n"/>
-      <c r="V64" s="13" t="n"/>
-      <c r="W64" s="13" t="n"/>
-      <c r="X64" s="13" t="n"/>
-      <c r="Y64" s="13" t="n"/>
-      <c r="Z64" s="13" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>Federated analysis</t>
-        </is>
-      </c>
-      <c r="B65" s="13" t="n"/>
-      <c r="C65" s="13" t="n"/>
-      <c r="D65" s="13" t="n"/>
-      <c r="E65" s="13" t="n"/>
-      <c r="F65" s="13" t="n"/>
-      <c r="G65" s="13" t="n"/>
-      <c r="H65" s="13" t="n"/>
-      <c r="I65" s="13" t="n"/>
-      <c r="J65" s="13" t="n"/>
-      <c r="K65" s="13" t="n"/>
-      <c r="L65" s="13" t="n"/>
-      <c r="M65" s="13" t="n"/>
-      <c r="N65" s="13" t="n"/>
-      <c r="O65" s="13" t="n"/>
-      <c r="P65" s="13" t="n"/>
-      <c r="Q65" s="13" t="n"/>
-      <c r="R65" s="13" t="n"/>
-      <c r="S65" s="13" t="n"/>
-      <c r="T65" s="13" t="n"/>
-      <c r="U65" s="13" t="n"/>
-      <c r="V65" s="13" t="n"/>
-      <c r="W65" s="13" t="n"/>
-      <c r="X65" s="13" t="n"/>
-      <c r="Y65" s="13" t="n"/>
-      <c r="Z65" s="13" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>User‑facing agent interfaces</t>
-        </is>
-      </c>
-      <c r="B66" s="13" t="n"/>
-      <c r="C66" s="13" t="n"/>
-      <c r="D66" s="13" t="n"/>
-      <c r="E66" s="13" t="n"/>
-      <c r="F66" s="13" t="n"/>
-      <c r="G66" s="13" t="n"/>
-      <c r="H66" s="13" t="n"/>
-      <c r="I66" s="13" t="n"/>
-      <c r="J66" s="13" t="n"/>
-      <c r="K66" s="13" t="n"/>
-      <c r="L66" s="13" t="n"/>
-      <c r="M66" s="13" t="n"/>
-      <c r="N66" s="13" t="n"/>
-      <c r="O66" s="13" t="n"/>
-      <c r="P66" s="13" t="n"/>
-      <c r="Q66" s="13" t="n"/>
-      <c r="R66" s="13" t="n"/>
-      <c r="S66" s="13" t="n"/>
-      <c r="T66" s="13" t="n"/>
-      <c r="U66" s="13" t="n"/>
-      <c r="V66" s="13" t="n"/>
-      <c r="W66" s="13" t="n"/>
-      <c r="X66" s="13" t="n"/>
-      <c r="Y66" s="13" t="n"/>
-      <c r="Z66" s="13" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>9. Maturity Level (Radar Standard)</t>
-        </is>
-      </c>
-      <c r="B67" s="13" t="n"/>
-      <c r="C67" s="13" t="n"/>
-      <c r="D67" s="13" t="n"/>
-      <c r="E67" s="13" t="n"/>
-      <c r="F67" s="13" t="n"/>
-      <c r="G67" s="13" t="n"/>
-      <c r="H67" s="13" t="n"/>
-      <c r="I67" s="13" t="n"/>
-      <c r="J67" s="13" t="n"/>
-      <c r="K67" s="13" t="n"/>
-      <c r="L67" s="13" t="n"/>
-      <c r="M67" s="13" t="n"/>
-      <c r="N67" s="13" t="n"/>
-      <c r="O67" s="13" t="n"/>
-      <c r="P67" s="13" t="n"/>
-      <c r="Q67" s="13" t="n"/>
-      <c r="R67" s="13" t="n"/>
-      <c r="S67" s="13" t="n"/>
-      <c r="T67" s="13" t="n"/>
-      <c r="U67" s="13" t="n"/>
-      <c r="V67" s="13" t="n"/>
-      <c r="W67" s="13" t="n"/>
-      <c r="X67" s="13" t="n"/>
-      <c r="Y67" s="13" t="n"/>
-      <c r="Z67" s="13" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>Not about the website — about the technology described.</t>
-        </is>
-      </c>
-      <c r="B68" s="13" t="n"/>
-      <c r="C68" s="13" t="n"/>
-      <c r="D68" s="13" t="n"/>
-      <c r="E68" s="13" t="n"/>
-      <c r="F68" s="13" t="n"/>
-      <c r="G68" s="13" t="n"/>
-      <c r="H68" s="13" t="n"/>
-      <c r="I68" s="13" t="n"/>
-      <c r="J68" s="13" t="n"/>
-      <c r="K68" s="13" t="n"/>
-      <c r="L68" s="13" t="n"/>
-      <c r="M68" s="13" t="n"/>
-      <c r="N68" s="13" t="n"/>
-      <c r="O68" s="13" t="n"/>
-      <c r="P68" s="13" t="n"/>
-      <c r="Q68" s="13" t="n"/>
-      <c r="R68" s="13" t="n"/>
-      <c r="S68" s="13" t="n"/>
-      <c r="T68" s="13" t="n"/>
-      <c r="U68" s="13" t="n"/>
-      <c r="V68" s="13" t="n"/>
-      <c r="W68" s="13" t="n"/>
-      <c r="X68" s="13" t="n"/>
-      <c r="Y68" s="13" t="n"/>
-      <c r="Z68" s="13" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>Emerging</t>
-        </is>
-      </c>
-      <c r="B69" s="13" t="n"/>
-      <c r="C69" s="13" t="n"/>
-      <c r="D69" s="13" t="n"/>
-      <c r="E69" s="13" t="n"/>
-      <c r="F69" s="13" t="n"/>
-      <c r="G69" s="13" t="n"/>
-      <c r="H69" s="13" t="n"/>
-      <c r="I69" s="13" t="n"/>
-      <c r="J69" s="13" t="n"/>
-      <c r="K69" s="13" t="n"/>
-      <c r="L69" s="13" t="n"/>
-      <c r="M69" s="13" t="n"/>
-      <c r="N69" s="13" t="n"/>
-      <c r="O69" s="13" t="n"/>
-      <c r="P69" s="13" t="n"/>
-      <c r="Q69" s="13" t="n"/>
-      <c r="R69" s="13" t="n"/>
-      <c r="S69" s="13" t="n"/>
-      <c r="T69" s="13" t="n"/>
-      <c r="U69" s="13" t="n"/>
-      <c r="V69" s="13" t="n"/>
-      <c r="W69" s="13" t="n"/>
-      <c r="X69" s="13" t="n"/>
-      <c r="Y69" s="13" t="n"/>
-      <c r="Z69" s="13" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="B70" s="13" t="n"/>
-      <c r="C70" s="13" t="n"/>
-      <c r="D70" s="13" t="n"/>
-      <c r="E70" s="13" t="n"/>
-      <c r="F70" s="13" t="n"/>
-      <c r="G70" s="13" t="n"/>
-      <c r="H70" s="13" t="n"/>
-      <c r="I70" s="13" t="n"/>
-      <c r="J70" s="13" t="n"/>
-      <c r="K70" s="13" t="n"/>
-      <c r="L70" s="13" t="n"/>
-      <c r="M70" s="13" t="n"/>
-      <c r="N70" s="13" t="n"/>
-      <c r="O70" s="13" t="n"/>
-      <c r="P70" s="13" t="n"/>
-      <c r="Q70" s="13" t="n"/>
-      <c r="R70" s="13" t="n"/>
-      <c r="S70" s="13" t="n"/>
-      <c r="T70" s="13" t="n"/>
-      <c r="U70" s="13" t="n"/>
-      <c r="V70" s="13" t="n"/>
-      <c r="W70" s="13" t="n"/>
-      <c r="X70" s="13" t="n"/>
-      <c r="Y70" s="13" t="n"/>
-      <c r="Z70" s="13" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>Mature</t>
-        </is>
-      </c>
-      <c r="B71" s="13" t="n"/>
-      <c r="C71" s="13" t="n"/>
-      <c r="D71" s="13" t="n"/>
-      <c r="E71" s="13" t="n"/>
-      <c r="F71" s="13" t="n"/>
-      <c r="G71" s="13" t="n"/>
-      <c r="H71" s="13" t="n"/>
-      <c r="I71" s="13" t="n"/>
-      <c r="J71" s="13" t="n"/>
-      <c r="K71" s="13" t="n"/>
-      <c r="L71" s="13" t="n"/>
-      <c r="M71" s="13" t="n"/>
-      <c r="N71" s="13" t="n"/>
-      <c r="O71" s="13" t="n"/>
-      <c r="P71" s="13" t="n"/>
-      <c r="Q71" s="13" t="n"/>
-      <c r="R71" s="13" t="n"/>
-      <c r="S71" s="13" t="n"/>
-      <c r="T71" s="13" t="n"/>
-      <c r="U71" s="13" t="n"/>
-      <c r="V71" s="13" t="n"/>
-      <c r="W71" s="13" t="n"/>
-      <c r="X71" s="13" t="n"/>
-      <c r="Y71" s="13" t="n"/>
-      <c r="Z71" s="13" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>Deprecated</t>
-        </is>
-      </c>
-      <c r="B72" s="13" t="n"/>
-      <c r="C72" s="13" t="n"/>
-      <c r="D72" s="13" t="n"/>
-      <c r="E72" s="13" t="n"/>
-      <c r="F72" s="13" t="n"/>
-      <c r="G72" s="13" t="n"/>
-      <c r="H72" s="13" t="n"/>
-      <c r="I72" s="13" t="n"/>
-      <c r="J72" s="13" t="n"/>
-      <c r="K72" s="13" t="n"/>
-      <c r="L72" s="13" t="n"/>
-      <c r="M72" s="13" t="n"/>
-      <c r="N72" s="13" t="n"/>
-      <c r="O72" s="13" t="n"/>
-      <c r="P72" s="13" t="n"/>
-      <c r="Q72" s="13" t="n"/>
-      <c r="R72" s="13" t="n"/>
-      <c r="S72" s="13" t="n"/>
-      <c r="T72" s="13" t="n"/>
-      <c r="U72" s="13" t="n"/>
-      <c r="V72" s="13" t="n"/>
-      <c r="W72" s="13" t="n"/>
-      <c r="X72" s="13" t="n"/>
-      <c r="Y72" s="13" t="n"/>
-      <c r="Z72" s="13" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>This helps teams know whether something is stable enough to consider.</t>
-        </is>
-      </c>
-      <c r="B73" s="13" t="n"/>
-      <c r="C73" s="13" t="n"/>
-      <c r="D73" s="13" t="n"/>
-      <c r="E73" s="13" t="n"/>
-      <c r="F73" s="13" t="n"/>
-      <c r="G73" s="13" t="n"/>
-      <c r="H73" s="13" t="n"/>
-      <c r="I73" s="13" t="n"/>
-      <c r="J73" s="13" t="n"/>
-      <c r="K73" s="13" t="n"/>
-      <c r="L73" s="13" t="n"/>
-      <c r="M73" s="13" t="n"/>
-      <c r="N73" s="13" t="n"/>
-      <c r="O73" s="13" t="n"/>
-      <c r="P73" s="13" t="n"/>
-      <c r="Q73" s="13" t="n"/>
-      <c r="R73" s="13" t="n"/>
-      <c r="S73" s="13" t="n"/>
-      <c r="T73" s="13" t="n"/>
-      <c r="U73" s="13" t="n"/>
-      <c r="V73" s="13" t="n"/>
-      <c r="W73" s="13" t="n"/>
-      <c r="X73" s="13" t="n"/>
-      <c r="Y73" s="13" t="n"/>
-      <c r="Z73" s="13" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>10. Notes / Key Takeaways</t>
-        </is>
-      </c>
-      <c r="B74" s="13" t="n"/>
-      <c r="C74" s="13" t="n"/>
-      <c r="D74" s="13" t="n"/>
-      <c r="E74" s="13" t="n"/>
-      <c r="F74" s="13" t="n"/>
-      <c r="G74" s="13" t="n"/>
-      <c r="H74" s="13" t="n"/>
-      <c r="I74" s="13" t="n"/>
-      <c r="J74" s="13" t="n"/>
-      <c r="K74" s="13" t="n"/>
-      <c r="L74" s="13" t="n"/>
-      <c r="M74" s="13" t="n"/>
-      <c r="N74" s="13" t="n"/>
-      <c r="O74" s="13" t="n"/>
-      <c r="P74" s="13" t="n"/>
-      <c r="Q74" s="13" t="n"/>
-      <c r="R74" s="13" t="n"/>
-      <c r="S74" s="13" t="n"/>
-      <c r="T74" s="13" t="n"/>
-      <c r="U74" s="13" t="n"/>
-      <c r="V74" s="13" t="n"/>
-      <c r="W74" s="13" t="n"/>
-      <c r="X74" s="13" t="n"/>
-      <c r="Y74" s="13" t="n"/>
-      <c r="Z74" s="13" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>A short free‑text field:</t>
-        </is>
-      </c>
-      <c r="B75" s="13" t="n"/>
-      <c r="C75" s="13" t="n"/>
-      <c r="D75" s="13" t="n"/>
-      <c r="E75" s="13" t="n"/>
-      <c r="F75" s="13" t="n"/>
-      <c r="G75" s="13" t="n"/>
-      <c r="H75" s="13" t="n"/>
-      <c r="I75" s="13" t="n"/>
-      <c r="J75" s="13" t="n"/>
-      <c r="K75" s="13" t="n"/>
-      <c r="L75" s="13" t="n"/>
-      <c r="M75" s="13" t="n"/>
-      <c r="N75" s="13" t="n"/>
-      <c r="O75" s="13" t="n"/>
-      <c r="P75" s="13" t="n"/>
-      <c r="Q75" s="13" t="n"/>
-      <c r="R75" s="13" t="n"/>
-      <c r="S75" s="13" t="n"/>
-      <c r="T75" s="13" t="n"/>
-      <c r="U75" s="13" t="n"/>
-      <c r="V75" s="13" t="n"/>
-      <c r="W75" s="13" t="n"/>
-      <c r="X75" s="13" t="n"/>
-      <c r="Y75" s="13" t="n"/>
-      <c r="Z75" s="13" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="3" t="inlineStr">
-        <is>
-          <t>breaking changes</t>
-        </is>
-      </c>
-      <c r="B76" s="13" t="n"/>
-      <c r="C76" s="13" t="n"/>
-      <c r="D76" s="13" t="n"/>
-      <c r="E76" s="13" t="n"/>
-      <c r="F76" s="13" t="n"/>
-      <c r="G76" s="13" t="n"/>
-      <c r="H76" s="13" t="n"/>
-      <c r="I76" s="13" t="n"/>
-      <c r="J76" s="13" t="n"/>
-      <c r="K76" s="13" t="n"/>
-      <c r="L76" s="13" t="n"/>
-      <c r="M76" s="13" t="n"/>
-      <c r="N76" s="13" t="n"/>
-      <c r="O76" s="13" t="n"/>
-      <c r="P76" s="13" t="n"/>
-      <c r="Q76" s="13" t="n"/>
-      <c r="R76" s="13" t="n"/>
-      <c r="S76" s="13" t="n"/>
-      <c r="T76" s="13" t="n"/>
-      <c r="U76" s="13" t="n"/>
-      <c r="V76" s="13" t="n"/>
-      <c r="W76" s="13" t="n"/>
-      <c r="X76" s="13" t="n"/>
-      <c r="Y76" s="13" t="n"/>
-      <c r="Z76" s="13" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="3" t="inlineStr">
-        <is>
-          <t>important patterns</t>
-        </is>
-      </c>
-      <c r="B77" s="13" t="n"/>
-      <c r="C77" s="13" t="n"/>
-      <c r="D77" s="13" t="n"/>
-      <c r="E77" s="13" t="n"/>
-      <c r="F77" s="13" t="n"/>
-      <c r="G77" s="13" t="n"/>
-      <c r="H77" s="13" t="n"/>
-      <c r="I77" s="13" t="n"/>
-      <c r="J77" s="13" t="n"/>
-      <c r="K77" s="13" t="n"/>
-      <c r="L77" s="13" t="n"/>
-      <c r="M77" s="13" t="n"/>
-      <c r="N77" s="13" t="n"/>
-      <c r="O77" s="13" t="n"/>
-      <c r="P77" s="13" t="n"/>
-      <c r="Q77" s="13" t="n"/>
-      <c r="R77" s="13" t="n"/>
-      <c r="S77" s="13" t="n"/>
-      <c r="T77" s="13" t="n"/>
-      <c r="U77" s="13" t="n"/>
-      <c r="V77" s="13" t="n"/>
-      <c r="W77" s="13" t="n"/>
-      <c r="X77" s="13" t="n"/>
-      <c r="Y77" s="13" t="n"/>
-      <c r="Z77" s="13" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="3" t="inlineStr">
-        <is>
-          <t>new capabilities</t>
-        </is>
-      </c>
-      <c r="B78" s="13" t="n"/>
-      <c r="C78" s="13" t="n"/>
-      <c r="D78" s="13" t="n"/>
-      <c r="E78" s="13" t="n"/>
-      <c r="F78" s="13" t="n"/>
-      <c r="G78" s="13" t="n"/>
-      <c r="H78" s="13" t="n"/>
-      <c r="I78" s="13" t="n"/>
-      <c r="J78" s="13" t="n"/>
-      <c r="K78" s="13" t="n"/>
-      <c r="L78" s="13" t="n"/>
-      <c r="M78" s="13" t="n"/>
-      <c r="N78" s="13" t="n"/>
-      <c r="O78" s="13" t="n"/>
-      <c r="P78" s="13" t="n"/>
-      <c r="Q78" s="13" t="n"/>
-      <c r="R78" s="13" t="n"/>
-      <c r="S78" s="13" t="n"/>
-      <c r="T78" s="13" t="n"/>
-      <c r="U78" s="13" t="n"/>
-      <c r="V78" s="13" t="n"/>
-      <c r="W78" s="13" t="n"/>
-      <c r="X78" s="13" t="n"/>
-      <c r="Y78" s="13" t="n"/>
-      <c r="Z78" s="13" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="3" t="inlineStr">
-        <is>
-          <t>relevance to agentic workflows</t>
-        </is>
-      </c>
-      <c r="B79" s="13" t="n"/>
-      <c r="C79" s="13" t="n"/>
-      <c r="D79" s="13" t="n"/>
-      <c r="E79" s="13" t="n"/>
-      <c r="F79" s="13" t="n"/>
-      <c r="G79" s="13" t="n"/>
-      <c r="H79" s="13" t="n"/>
-      <c r="I79" s="13" t="n"/>
-      <c r="J79" s="13" t="n"/>
-      <c r="K79" s="13" t="n"/>
-      <c r="L79" s="13" t="n"/>
-      <c r="M79" s="13" t="n"/>
-      <c r="N79" s="13" t="n"/>
-      <c r="O79" s="13" t="n"/>
-      <c r="P79" s="13" t="n"/>
-      <c r="Q79" s="13" t="n"/>
-      <c r="R79" s="13" t="n"/>
-      <c r="S79" s="13" t="n"/>
-      <c r="T79" s="13" t="n"/>
-      <c r="U79" s="13" t="n"/>
-      <c r="V79" s="13" t="n"/>
-      <c r="W79" s="13" t="n"/>
-      <c r="X79" s="13" t="n"/>
-      <c r="Y79" s="13" t="n"/>
-      <c r="Z79" s="13" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="3" t="inlineStr">
-        <is>
-          <t>implications for research platforms</t>
-        </is>
-      </c>
-      <c r="B80" s="13" t="n"/>
-      <c r="C80" s="13" t="n"/>
-      <c r="D80" s="13" t="n"/>
-      <c r="E80" s="13" t="n"/>
-      <c r="F80" s="13" t="n"/>
-      <c r="G80" s="13" t="n"/>
-      <c r="H80" s="13" t="n"/>
-      <c r="I80" s="13" t="n"/>
-      <c r="J80" s="13" t="n"/>
-      <c r="K80" s="13" t="n"/>
-      <c r="L80" s="13" t="n"/>
-      <c r="M80" s="13" t="n"/>
-      <c r="N80" s="13" t="n"/>
-      <c r="O80" s="13" t="n"/>
-      <c r="P80" s="13" t="n"/>
-      <c r="Q80" s="13" t="n"/>
-      <c r="R80" s="13" t="n"/>
-      <c r="S80" s="13" t="n"/>
-      <c r="T80" s="13" t="n"/>
-      <c r="U80" s="13" t="n"/>
-      <c r="V80" s="13" t="n"/>
-      <c r="W80" s="13" t="n"/>
-      <c r="X80" s="13" t="n"/>
-      <c r="Y80" s="13" t="n"/>
-      <c r="Z80" s="13" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="3" t="inlineStr">
-        <is>
-          <t>This is where institutional knowledge accumulates.</t>
-        </is>
-      </c>
-      <c r="B81" s="13" t="n"/>
-      <c r="C81" s="13" t="n"/>
-      <c r="D81" s="13" t="n"/>
-      <c r="E81" s="13" t="n"/>
-      <c r="F81" s="13" t="n"/>
-      <c r="G81" s="13" t="n"/>
-      <c r="H81" s="13" t="n"/>
-      <c r="I81" s="13" t="n"/>
-      <c r="J81" s="13" t="n"/>
-      <c r="K81" s="13" t="n"/>
-      <c r="L81" s="13" t="n"/>
-      <c r="M81" s="13" t="n"/>
-      <c r="N81" s="13" t="n"/>
-      <c r="O81" s="13" t="n"/>
-      <c r="P81" s="13" t="n"/>
-      <c r="Q81" s="13" t="n"/>
-      <c r="R81" s="13" t="n"/>
-      <c r="S81" s="13" t="n"/>
-      <c r="T81" s="13" t="n"/>
-      <c r="U81" s="13" t="n"/>
-      <c r="V81" s="13" t="n"/>
-      <c r="W81" s="13" t="n"/>
-      <c r="X81" s="13" t="n"/>
-      <c r="Y81" s="13" t="n"/>
-      <c r="Z81" s="13" t="n"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="A1:A964">
-    <cfRule type="expression" priority="1" dxfId="5">
-      <formula>REGEXMATCH(A1, "^[0-9]")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
@@ -5237,7 +2660,7 @@
       </c>
       <c r="J2" s="16" t="inlineStr">
         <is>
-          <t>Architecture, Implementation</t>
+          <t>Architecture; Implementation</t>
         </is>
       </c>
       <c r="K2" s="16" t="inlineStr">
@@ -5318,7 +2741,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -5427,7 +2850,7 @@
       </c>
       <c r="H2" s="16" t="inlineStr">
         <is>
-          <t>White paper</t>
+          <t>Whitepaper</t>
         </is>
       </c>
       <c r="I2" s="16" t="inlineStr">
@@ -5478,7 +2901,7 @@
       </c>
       <c r="H3" s="16" t="inlineStr">
         <is>
-          <t>Benchmark Colleciton</t>
+          <t>Benchmark Collection</t>
         </is>
       </c>
       <c r="I3" s="16" t="inlineStr">
@@ -5529,7 +2952,7 @@
       </c>
       <c r="H4" s="16" t="inlineStr">
         <is>
-          <t>White paper</t>
+          <t>Whitepaper</t>
         </is>
       </c>
       <c r="I4" s="16" t="inlineStr">
@@ -5575,7 +2998,7 @@
       </c>
       <c r="H5" s="16" t="inlineStr">
         <is>
-          <t>White paper</t>
+          <t>Whitepaper</t>
         </is>
       </c>
       <c r="I5" s="16" t="inlineStr">
@@ -5624,7 +3047,7 @@
       </c>
       <c r="H6" s="16" t="inlineStr">
         <is>
-          <t>White paper</t>
+          <t>Whitepaper</t>
         </is>
       </c>
       <c r="I6" s="16" t="inlineStr">
@@ -5673,7 +3096,7 @@
       </c>
       <c r="H7" s="16" t="inlineStr">
         <is>
-          <t>White paper</t>
+          <t>Whitepaper</t>
         </is>
       </c>
       <c r="I7" s="16" t="inlineStr">
@@ -5722,7 +3145,7 @@
       </c>
       <c r="H8" s="16" t="inlineStr">
         <is>
-          <t>White paper</t>
+          <t>Whitepaper</t>
         </is>
       </c>
       <c r="I8" s="16" t="inlineStr">
@@ -5772,4 +3195,2322 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" style="17" min="1" max="1"/>
+    <col width="34" customWidth="1" style="17" min="2" max="2"/>
+    <col width="46" customWidth="1" style="17" min="3" max="3"/>
+    <col width="18" customWidth="1" style="17" min="4" max="4"/>
+    <col width="10" customWidth="1" style="17" min="5" max="5"/>
+    <col width="80" customWidth="1" style="17" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="B1" s="19" t="inlineStr">
+        <is>
+          <t>Column Name</t>
+        </is>
+      </c>
+      <c r="C1" s="19" t="inlineStr">
+        <is>
+          <t>Applies To</t>
+        </is>
+      </c>
+      <c r="D1" s="19" t="inlineStr">
+        <is>
+          <t>Value Type</t>
+        </is>
+      </c>
+      <c r="E1" s="19" t="inlineStr">
+        <is>
+          <t>Separator</t>
+        </is>
+      </c>
+      <c r="F1" s="19" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="20" t="inlineStr">
+        <is>
+          <t>Resource Name</t>
+        </is>
+      </c>
+      <c r="C2" s="20" t="inlineStr">
+        <is>
+          <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
+        </is>
+      </c>
+      <c r="D2" s="20" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="E2" s="20" t="inlineStr"/>
+      <c r="F2" s="20" t="inlineStr">
+        <is>
+          <t>Short, human-readable name. Also the natural key used to match a row across sync runs. Example: VS Code Copilot Agents Overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="20" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
+        </is>
+      </c>
+      <c r="D3" s="20" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="inlineStr"/>
+      <c r="F3" s="20" t="inlineStr">
+        <is>
+          <t>Canonical link to the resource.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t>Source Organization</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="E4" s="20" t="inlineStr"/>
+      <c r="F4" s="20" t="inlineStr">
+        <is>
+          <t>Who maintains it? Examples: Microsoft, GitHub, OpenAI, Kaggle, Anthropic, Google, HuggingFace. This matters because some orgs update weekly, others yearly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>Last Verified</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr"/>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>Date a curator last checked the page. Set by a human during verification; cleared automatically when the row's content changes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>Verified By</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>Curator who last verified this row. Set by a human only, never by an agent; cleared automatically when the row's content changes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>Knowledgebase; SOTA Coding Agents Benchmarks</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>The page's own update timestamp. Helps track fast-moving agent ecosystems.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>Deprecation Date</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>Deprecated</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr"/>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>Date the resource was deprecated or superseded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>version</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr"/>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>Version string of the resource or tool (e.g. 'v0.1 DRAFT', 'Pro'). Leave blank for article-type resources with no version - use Publication Date instead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>Resource Type</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>controlled_single</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr"/>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>What kind of resource this is. Helps teams filter by what they need.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>Agentic Features Covered</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>controlled_multi</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>;</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>Which agentic capabilities the resource covers. One of the most important columns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>Topic Focus</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>Knowledgebase; Deprecated</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>controlled_multi</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>;</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>Subject areas the resource addresses. Helps research IT teams quickly find relevant material. Primary vocabulary is EDAM; NIST AI RMF characteristics are available as an optional secondary axis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>Relevance to Research Cyberinfrastructure</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>Knowledgebase; Deprecated</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr"/>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>Free-text note on why this matters to research platforms. Example themes: workflow orchestration, data portal integration, metadata / provenance, multi-agent coordination, HPC / cloud hybrid workflows, reproducibility, federated analysis, user-facing agent interfaces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>Maturity Level</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>controlled_single</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr"/>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>Not about the website - about the technology described. Helps teams know whether something is stable enough to consider.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="20" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>Notes / Key Takeaways</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr"/>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>Short free-text field: breaking changes, important patterns, new capabilities, relevance to agentic workflows, implications for research platforms. This is where institutional knowledge accumulates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>Publication Date</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>Knowledgebase</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr"/>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>Publication date for article-type resources that have no software version.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="20" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>Discovery Date</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr"/>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>Date this resource first entered the VT Radar.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F91"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" style="17" min="1" max="1"/>
+    <col width="42" customWidth="1" style="17" min="2" max="2"/>
+    <col width="80" customWidth="1" style="17" min="3" max="3"/>
+    <col width="14" customWidth="1" style="17" min="4" max="4"/>
+    <col width="14" customWidth="1" style="17" min="5" max="5"/>
+    <col width="44" customWidth="1" style="17" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>Column Name</t>
+        </is>
+      </c>
+      <c r="B1" s="19" t="inlineStr">
+        <is>
+          <t>Term</t>
+        </is>
+      </c>
+      <c r="C1" s="19" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D1" s="19" t="inlineStr">
+        <is>
+          <t>Ontology</t>
+        </is>
+      </c>
+      <c r="E1" s="19" t="inlineStr">
+        <is>
+          <t>Ontology ID</t>
+        </is>
+      </c>
+      <c r="F1" s="19" t="inlineStr">
+        <is>
+          <t>Ontology URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>Resource Type</t>
+        </is>
+      </c>
+      <c r="B2" s="20" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="C2" s="20" t="inlineStr"/>
+      <c r="D2" s="20" t="inlineStr"/>
+      <c r="E2" s="20" t="inlineStr"/>
+      <c r="F2" s="20" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="20" t="inlineStr">
+        <is>
+          <t>Resource Type</t>
+        </is>
+      </c>
+      <c r="B3" s="20" t="inlineStr">
+        <is>
+          <t>API Reference</t>
+        </is>
+      </c>
+      <c r="C3" s="20" t="inlineStr"/>
+      <c r="D3" s="20" t="inlineStr"/>
+      <c r="E3" s="20" t="inlineStr"/>
+      <c r="F3" s="20" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>Resource Type</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t>Specification</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="inlineStr"/>
+      <c r="D4" s="20" t="inlineStr"/>
+      <c r="E4" s="20" t="inlineStr"/>
+      <c r="F4" s="20" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>Resource Type</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>Whitepaper</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>Vendor or organization technical whitepaper.</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="20" t="inlineStr"/>
+      <c r="F5" s="20" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>Resource Type</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>Scientific Literature</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>Peer-reviewed publication or preprint. Distinct from a vendor Whitepaper.</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>Resource Type</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>Governance Guidance</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>Resource Type</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>Security Guidance &amp; Resources</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr"/>
+      <c r="D8" s="20" t="inlineStr"/>
+      <c r="E8" s="20" t="inlineStr"/>
+      <c r="F8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>Resource Type</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>Reference Architecture</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr"/>
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr"/>
+      <c r="F9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>Resource Type</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>Container Registry</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr"/>
+      <c r="D10" s="20" t="inlineStr"/>
+      <c r="E10" s="20" t="inlineStr"/>
+      <c r="F10" s="20" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>Resource Type</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>Enterprise Control Interface</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr"/>
+      <c r="D11" s="20" t="inlineStr"/>
+      <c r="E11" s="20" t="inlineStr"/>
+      <c r="F11" s="20" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>Resource Type</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>Inference Framework</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr"/>
+      <c r="D12" s="20" t="inlineStr"/>
+      <c r="E12" s="20" t="inlineStr"/>
+      <c r="F12" s="20" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>Resource Type</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>Local Application Sandbox</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr"/>
+      <c r="D13" s="20" t="inlineStr"/>
+      <c r="E13" s="20" t="inlineStr"/>
+      <c r="F13" s="20" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>Resource Type</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>Github Code Repository</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr"/>
+      <c r="D14" s="20" t="inlineStr"/>
+      <c r="E14" s="20" t="inlineStr"/>
+      <c r="F14" s="20" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>Resource Type</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>Benchmark Collection</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>A curated collection of benchmarks or comparison studies.</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr"/>
+      <c r="E15" s="20" t="inlineStr"/>
+      <c r="F15" s="20" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>Resource Type</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>Tutorial</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr"/>
+      <c r="D16" s="20" t="inlineStr"/>
+      <c r="E16" s="20" t="inlineStr"/>
+      <c r="F16" s="20" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="20" t="inlineStr">
+        <is>
+          <t>Resource Type</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr"/>
+      <c r="D17" s="20" t="inlineStr"/>
+      <c r="E17" s="20" t="inlineStr"/>
+      <c r="F17" s="20" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>Resource Type</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>Example Repo</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr"/>
+      <c r="D18" s="20" t="inlineStr"/>
+      <c r="E18" s="20" t="inlineStr"/>
+      <c r="F18" s="20" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t>Resource Type</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>Architecture Pattern</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr"/>
+      <c r="D19" s="20" t="inlineStr"/>
+      <c r="E19" s="20" t="inlineStr"/>
+      <c r="F19" s="20" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>Agentic Features Covered</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>Hooks</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr"/>
+      <c r="D20" s="20" t="inlineStr"/>
+      <c r="E20" s="20" t="inlineStr"/>
+      <c r="F20" s="20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="20" t="inlineStr">
+        <is>
+          <t>Agentic Features Covered</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>Skills</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr"/>
+      <c r="D21" s="20" t="inlineStr"/>
+      <c r="E21" s="20" t="inlineStr"/>
+      <c r="F21" s="20" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="20" t="inlineStr">
+        <is>
+          <t>Agentic Features Covered</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>MCP</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>Model Context Protocol.</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr"/>
+      <c r="E22" s="20" t="inlineStr"/>
+      <c r="F22" s="20" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t>Agentic Features Covered</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>Agent frameworks</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr"/>
+      <c r="D23" s="20" t="inlineStr"/>
+      <c r="E23" s="20" t="inlineStr"/>
+      <c r="F23" s="20" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>Agentic Features Covered</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>Agent Patterns</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr"/>
+      <c r="D24" s="20" t="inlineStr"/>
+      <c r="E24" s="20" t="inlineStr"/>
+      <c r="F24" s="20" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>Agentic Features Covered</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>Multi-Agent Patterns</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr"/>
+      <c r="D25" s="20" t="inlineStr"/>
+      <c r="E25" s="20" t="inlineStr"/>
+      <c r="F25" s="20" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>Agentic Features Covered</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>Context window management</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr"/>
+      <c r="D26" s="20" t="inlineStr"/>
+      <c r="E26" s="20" t="inlineStr"/>
+      <c r="F26" s="20" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t>Agentic Features Covered</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>Deployment patterns</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr"/>
+      <c r="D27" s="20" t="inlineStr"/>
+      <c r="E27" s="20" t="inlineStr"/>
+      <c r="F27" s="20" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>Agentic Features Covered</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>Safety / guardrails</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr"/>
+      <c r="D28" s="20" t="inlineStr"/>
+      <c r="E28" s="20" t="inlineStr"/>
+      <c r="F28" s="20" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>Agentic Features Covered</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>Evaluation / testing</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr"/>
+      <c r="D29" s="20" t="inlineStr"/>
+      <c r="E29" s="20" t="inlineStr"/>
+      <c r="F29" s="20" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="20" t="inlineStr">
+        <is>
+          <t>Agentic Features Covered</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>Risk Controls</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr"/>
+      <c r="D30" s="20" t="inlineStr"/>
+      <c r="E30" s="20" t="inlineStr"/>
+      <c r="F30" s="20" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>Agentic Features Covered</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>Safe Tool Use</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr"/>
+      <c r="D31" s="20" t="inlineStr"/>
+      <c r="E31" s="20" t="inlineStr"/>
+      <c r="F31" s="20" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t>Agentic Features Covered</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>Tools</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr"/>
+      <c r="D32" s="20" t="inlineStr"/>
+      <c r="E32" s="20" t="inlineStr"/>
+      <c r="F32" s="20" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t>Agentic Features Covered</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>Tool Integration</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr"/>
+      <c r="D33" s="20" t="inlineStr"/>
+      <c r="E33" s="20" t="inlineStr"/>
+      <c r="F33" s="20" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="20" t="inlineStr">
+        <is>
+          <t>Agentic Features Covered</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>Tool-Ready Endpoints</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="inlineStr"/>
+      <c r="D34" s="20" t="inlineStr"/>
+      <c r="E34" s="20" t="inlineStr"/>
+      <c r="F34" s="20" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="20" t="inlineStr">
+        <is>
+          <t>Agentic Features Covered</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
+        <is>
+          <t>Coding Agents</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="inlineStr"/>
+      <c r="D35" s="20" t="inlineStr"/>
+      <c r="E35" s="20" t="inlineStr"/>
+      <c r="F35" s="20" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="20" t="inlineStr">
+        <is>
+          <t>Agentic Features Covered</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr">
+        <is>
+          <t>Notebook Agents</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="inlineStr"/>
+      <c r="D36" s="20" t="inlineStr"/>
+      <c r="E36" s="20" t="inlineStr"/>
+      <c r="F36" s="20" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="20" t="inlineStr">
+        <is>
+          <t>Agentic Features Covered</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr">
+        <is>
+          <t>Workflow Agents</t>
+        </is>
+      </c>
+      <c r="C37" s="20" t="inlineStr"/>
+      <c r="D37" s="20" t="inlineStr"/>
+      <c r="E37" s="20" t="inlineStr"/>
+      <c r="F37" s="20" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="20" t="inlineStr">
+        <is>
+          <t>Agentic Features Covered</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t>Workflow Automation</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="inlineStr"/>
+      <c r="D38" s="20" t="inlineStr"/>
+      <c r="E38" s="20" t="inlineStr"/>
+      <c r="F38" s="20" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="20" t="inlineStr">
+        <is>
+          <t>Agentic Features Covered</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="inlineStr">
+        <is>
+          <t>Orchestration</t>
+        </is>
+      </c>
+      <c r="C39" s="20" t="inlineStr"/>
+      <c r="D39" s="20" t="inlineStr"/>
+      <c r="E39" s="20" t="inlineStr"/>
+      <c r="F39" s="20" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="20" t="inlineStr">
+        <is>
+          <t>Agentic Features Covered</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>Triggers</t>
+        </is>
+      </c>
+      <c r="C40" s="20" t="inlineStr"/>
+      <c r="D40" s="20" t="inlineStr"/>
+      <c r="E40" s="20" t="inlineStr"/>
+      <c r="F40" s="20" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="20" t="inlineStr">
+        <is>
+          <t>Agentic Features Covered</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="inlineStr">
+        <is>
+          <t>Retrieval</t>
+        </is>
+      </c>
+      <c r="C41" s="20" t="inlineStr"/>
+      <c r="D41" s="20" t="inlineStr"/>
+      <c r="E41" s="20" t="inlineStr"/>
+      <c r="F41" s="20" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="20" t="inlineStr">
+        <is>
+          <t>Agentic Features Covered</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="inlineStr">
+        <is>
+          <t>Retrieval Agents</t>
+        </is>
+      </c>
+      <c r="C42" s="20" t="inlineStr"/>
+      <c r="D42" s="20" t="inlineStr"/>
+      <c r="E42" s="20" t="inlineStr"/>
+      <c r="F42" s="20" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="20" t="inlineStr">
+        <is>
+          <t>Agentic Features Covered</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="inlineStr">
+        <is>
+          <t>Sandbox</t>
+        </is>
+      </c>
+      <c r="C43" s="20" t="inlineStr"/>
+      <c r="D43" s="20" t="inlineStr"/>
+      <c r="E43" s="20" t="inlineStr"/>
+      <c r="F43" s="20" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="20" t="inlineStr">
+        <is>
+          <t>Agentic Features Covered</t>
+        </is>
+      </c>
+      <c r="B44" s="20" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="C44" s="20" t="inlineStr"/>
+      <c r="D44" s="20" t="inlineStr"/>
+      <c r="E44" s="20" t="inlineStr"/>
+      <c r="F44" s="20" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="20" t="inlineStr">
+        <is>
+          <t>Agentic Features Covered</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="inlineStr">
+        <is>
+          <t>Cybersecurity</t>
+        </is>
+      </c>
+      <c r="C45" s="20" t="inlineStr"/>
+      <c r="D45" s="20" t="inlineStr"/>
+      <c r="E45" s="20" t="inlineStr"/>
+      <c r="F45" s="20" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="20" t="inlineStr">
+        <is>
+          <t>Agentic Features Covered</t>
+        </is>
+      </c>
+      <c r="B46" s="20" t="inlineStr">
+        <is>
+          <t>FAIR data</t>
+        </is>
+      </c>
+      <c r="C46" s="20" t="inlineStr">
+        <is>
+          <t>Findable, Accessible, Interoperable, Reusable data principles.</t>
+        </is>
+      </c>
+      <c r="D46" s="20" t="inlineStr">
+        <is>
+          <t>EDAM</t>
+        </is>
+      </c>
+      <c r="E46" s="20" t="inlineStr">
+        <is>
+          <t>topic_4012</t>
+        </is>
+      </c>
+      <c r="F46" s="20" t="inlineStr">
+        <is>
+          <t>http://edamontology.org/topic_4012</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t>Agentic Features Covered</t>
+        </is>
+      </c>
+      <c r="B47" s="20" t="inlineStr">
+        <is>
+          <t>API Integration</t>
+        </is>
+      </c>
+      <c r="C47" s="20" t="inlineStr"/>
+      <c r="D47" s="20" t="inlineStr"/>
+      <c r="E47" s="20" t="inlineStr"/>
+      <c r="F47" s="20" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="20" t="inlineStr">
+        <is>
+          <t>Agentic Features Covered</t>
+        </is>
+      </c>
+      <c r="B48" s="20" t="inlineStr">
+        <is>
+          <t>Model Integration</t>
+        </is>
+      </c>
+      <c r="C48" s="20" t="inlineStr"/>
+      <c r="D48" s="20" t="inlineStr"/>
+      <c r="E48" s="20" t="inlineStr"/>
+      <c r="F48" s="20" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="20" t="inlineStr">
+        <is>
+          <t>Agentic Features Covered</t>
+        </is>
+      </c>
+      <c r="B49" s="20" t="inlineStr">
+        <is>
+          <t>Server Integration</t>
+        </is>
+      </c>
+      <c r="C49" s="20" t="inlineStr"/>
+      <c r="D49" s="20" t="inlineStr"/>
+      <c r="E49" s="20" t="inlineStr"/>
+      <c r="F49" s="20" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="20" t="inlineStr">
+        <is>
+          <t>Agentic Features Covered</t>
+        </is>
+      </c>
+      <c r="B50" s="20" t="inlineStr">
+        <is>
+          <t>Server Patterns</t>
+        </is>
+      </c>
+      <c r="C50" s="20" t="inlineStr"/>
+      <c r="D50" s="20" t="inlineStr"/>
+      <c r="E50" s="20" t="inlineStr"/>
+      <c r="F50" s="20" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="20" t="inlineStr">
+        <is>
+          <t>Agentic Features Covered</t>
+        </is>
+      </c>
+      <c r="B51" s="20" t="inlineStr">
+        <is>
+          <t>Artifact version-locking &amp; immutable tags</t>
+        </is>
+      </c>
+      <c r="C51" s="20" t="inlineStr"/>
+      <c r="D51" s="20" t="inlineStr"/>
+      <c r="E51" s="20" t="inlineStr"/>
+      <c r="F51" s="20" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="20" t="inlineStr">
+        <is>
+          <t>Agentic Features Covered</t>
+        </is>
+      </c>
+      <c r="B52" s="20" t="inlineStr">
+        <is>
+          <t>End-to-end local reference applications</t>
+        </is>
+      </c>
+      <c r="C52" s="20" t="inlineStr"/>
+      <c r="D52" s="20" t="inlineStr"/>
+      <c r="E52" s="20" t="inlineStr"/>
+      <c r="F52" s="20" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="20" t="inlineStr">
+        <is>
+          <t>Agentic Features Covered</t>
+        </is>
+      </c>
+      <c r="B53" s="20" t="inlineStr">
+        <is>
+          <t>Grammar-based constrained sampling</t>
+        </is>
+      </c>
+      <c r="C53" s="20" t="inlineStr"/>
+      <c r="D53" s="20" t="inlineStr"/>
+      <c r="E53" s="20" t="inlineStr"/>
+      <c r="F53" s="20" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="20" t="inlineStr">
+        <is>
+          <t>Agentic Features Covered</t>
+        </is>
+      </c>
+      <c r="B54" s="20" t="inlineStr">
+        <is>
+          <t>Hardware performance scaling &amp; VRAM sizing</t>
+        </is>
+      </c>
+      <c r="C54" s="20" t="inlineStr"/>
+      <c r="D54" s="20" t="inlineStr"/>
+      <c r="E54" s="20" t="inlineStr"/>
+      <c r="F54" s="20" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="20" t="inlineStr">
+        <is>
+          <t>Agentic Features Covered</t>
+        </is>
+      </c>
+      <c r="B55" s="20" t="inlineStr">
+        <is>
+          <t>Local RAG pipelines &amp; offline functions</t>
+        </is>
+      </c>
+      <c r="C55" s="20" t="inlineStr"/>
+      <c r="D55" s="20" t="inlineStr"/>
+      <c r="E55" s="20" t="inlineStr"/>
+      <c r="F55" s="20" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="20" t="inlineStr">
+        <is>
+          <t>Agentic Features Covered</t>
+        </is>
+      </c>
+      <c r="B56" s="20" t="inlineStr">
+        <is>
+          <t>Local embedding &amp; zero-config tools</t>
+        </is>
+      </c>
+      <c r="C56" s="20" t="inlineStr"/>
+      <c r="D56" s="20" t="inlineStr"/>
+      <c r="E56" s="20" t="inlineStr"/>
+      <c r="F56" s="20" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="20" t="inlineStr">
+        <is>
+          <t>Agentic Features Covered</t>
+        </is>
+      </c>
+      <c r="B57" s="20" t="inlineStr">
+        <is>
+          <t>Parallel sampling &amp; tool-calling</t>
+        </is>
+      </c>
+      <c r="C57" s="20" t="inlineStr"/>
+      <c r="D57" s="20" t="inlineStr"/>
+      <c r="E57" s="20" t="inlineStr"/>
+      <c r="F57" s="20" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="20" t="inlineStr">
+        <is>
+          <t>Agentic Features Covered</t>
+        </is>
+      </c>
+      <c r="B58" s="20" t="inlineStr">
+        <is>
+          <t>Tensor-parallel caching &amp; optimized tool-calling</t>
+        </is>
+      </c>
+      <c r="C58" s="20" t="inlineStr"/>
+      <c r="D58" s="20" t="inlineStr"/>
+      <c r="E58" s="20" t="inlineStr"/>
+      <c r="F58" s="20" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="20" t="inlineStr">
+        <is>
+          <t>Topic Focus</t>
+        </is>
+      </c>
+      <c r="B59" s="20" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
+      <c r="C59" s="20" t="inlineStr"/>
+      <c r="D59" s="20" t="inlineStr"/>
+      <c r="E59" s="20" t="inlineStr"/>
+      <c r="F59" s="20" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="20" t="inlineStr">
+        <is>
+          <t>Topic Focus</t>
+        </is>
+      </c>
+      <c r="B60" s="20" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C60" s="20" t="inlineStr"/>
+      <c r="D60" s="20" t="inlineStr"/>
+      <c r="E60" s="20" t="inlineStr"/>
+      <c r="F60" s="20" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="20" t="inlineStr">
+        <is>
+          <t>Topic Focus</t>
+        </is>
+      </c>
+      <c r="B61" s="20" t="inlineStr">
+        <is>
+          <t>Data governance</t>
+        </is>
+      </c>
+      <c r="C61" s="20" t="inlineStr">
+        <is>
+          <t>Focuses specifically on the technical protocols, access controls, data-line security, and de-identification standards used to protect the integrity, quality, and privacy of information throughout its lifecycle</t>
+        </is>
+      </c>
+      <c r="D61" s="20" t="inlineStr">
+        <is>
+          <t>EDAM</t>
+        </is>
+      </c>
+      <c r="E61" s="20" t="inlineStr">
+        <is>
+          <t>topic_3571</t>
+        </is>
+      </c>
+      <c r="F61" s="20" t="inlineStr">
+        <is>
+          <t>http://edamontology.org/topic_3571</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="20" t="inlineStr">
+        <is>
+          <t>Topic Focus</t>
+        </is>
+      </c>
+      <c r="B62" s="20" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="C62" s="20" t="inlineStr">
+        <is>
+          <t>The overarching organizational policies, compliance frameworks, and capital allocation strategies that dictate how an enterprise manages its broader IT infrastructure, risk tolerances, and vendor choices</t>
+        </is>
+      </c>
+      <c r="D62" s="20" t="inlineStr"/>
+      <c r="E62" s="20" t="inlineStr"/>
+      <c r="F62" s="20" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="20" t="inlineStr">
+        <is>
+          <t>Topic Focus</t>
+        </is>
+      </c>
+      <c r="B63" s="20" t="inlineStr">
+        <is>
+          <t>Implementation</t>
+        </is>
+      </c>
+      <c r="C63" s="20" t="inlineStr"/>
+      <c r="D63" s="20" t="inlineStr"/>
+      <c r="E63" s="20" t="inlineStr"/>
+      <c r="F63" s="20" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="20" t="inlineStr">
+        <is>
+          <t>Topic Focus</t>
+        </is>
+      </c>
+      <c r="B64" s="20" t="inlineStr">
+        <is>
+          <t>Deployment</t>
+        </is>
+      </c>
+      <c r="C64" s="20" t="inlineStr">
+        <is>
+          <t>The tactical, hands-on execution of installing, configuring, provisioning, and launching software or hardware systems within a specific operational environment</t>
+        </is>
+      </c>
+      <c r="D64" s="20" t="inlineStr"/>
+      <c r="E64" s="20" t="inlineStr"/>
+      <c r="F64" s="20" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="20" t="inlineStr">
+        <is>
+          <t>Topic Focus</t>
+        </is>
+      </c>
+      <c r="B65" s="20" t="inlineStr">
+        <is>
+          <t>Workflows</t>
+        </is>
+      </c>
+      <c r="C65" s="20" t="inlineStr"/>
+      <c r="D65" s="20" t="inlineStr">
+        <is>
+          <t>EDAM</t>
+        </is>
+      </c>
+      <c r="E65" s="20" t="inlineStr">
+        <is>
+          <t>topic_0769</t>
+        </is>
+      </c>
+      <c r="F65" s="20" t="inlineStr">
+        <is>
+          <t>http://edamontology.org/topic_0769</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="20" t="inlineStr">
+        <is>
+          <t>Topic Focus</t>
+        </is>
+      </c>
+      <c r="B66" s="20" t="inlineStr">
+        <is>
+          <t>Workflow integration</t>
+        </is>
+      </c>
+      <c r="C66" s="20" t="inlineStr"/>
+      <c r="D66" s="20" t="inlineStr"/>
+      <c r="E66" s="20" t="inlineStr"/>
+      <c r="F66" s="20" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="20" t="inlineStr">
+        <is>
+          <t>Topic Focus</t>
+        </is>
+      </c>
+      <c r="B67" s="20" t="inlineStr">
+        <is>
+          <t>Model selection</t>
+        </is>
+      </c>
+      <c r="C67" s="20" t="inlineStr"/>
+      <c r="D67" s="20" t="inlineStr"/>
+      <c r="E67" s="20" t="inlineStr"/>
+      <c r="F67" s="20" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="20" t="inlineStr">
+        <is>
+          <t>Topic Focus</t>
+        </is>
+      </c>
+      <c r="B68" s="20" t="inlineStr">
+        <is>
+          <t>Evaluation</t>
+        </is>
+      </c>
+      <c r="C68" s="20" t="inlineStr"/>
+      <c r="D68" s="20" t="inlineStr"/>
+      <c r="E68" s="20" t="inlineStr"/>
+      <c r="F68" s="20" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="20" t="inlineStr">
+        <is>
+          <t>Topic Focus</t>
+        </is>
+      </c>
+      <c r="B69" s="20" t="inlineStr">
+        <is>
+          <t>Architecture Compute</t>
+        </is>
+      </c>
+      <c r="C69" s="20" t="inlineStr">
+        <is>
+          <t>Physical node topologies, hardware constraints, VRAM bounds, and localized compute execution profiles.</t>
+        </is>
+      </c>
+      <c r="D69" s="20" t="inlineStr"/>
+      <c r="E69" s="20" t="inlineStr"/>
+      <c r="F69" s="20" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="20" t="inlineStr">
+        <is>
+          <t>Topic Focus</t>
+        </is>
+      </c>
+      <c r="B70" s="20" t="inlineStr">
+        <is>
+          <t>Network Isolation</t>
+        </is>
+      </c>
+      <c r="C70" s="20" t="inlineStr">
+        <is>
+          <t>Non-egress boundaries, air-gapped artifact staging, localized cloud VPC containers, and firewalled local registries.</t>
+        </is>
+      </c>
+      <c r="D70" s="20" t="inlineStr"/>
+      <c r="E70" s="20" t="inlineStr"/>
+      <c r="F70" s="20" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="20" t="inlineStr">
+        <is>
+          <t>Topic Focus</t>
+        </is>
+      </c>
+      <c r="B71" s="20" t="inlineStr">
+        <is>
+          <t>Infrastructure Security</t>
+        </is>
+      </c>
+      <c r="C71" s="20" t="inlineStr">
+        <is>
+          <t>For on-prem LLM deployments, it captures the security of the compute stack as well as the data pipelines</t>
+        </is>
+      </c>
+      <c r="D71" s="20" t="inlineStr"/>
+      <c r="E71" s="20" t="inlineStr"/>
+      <c r="F71" s="20" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="20" t="inlineStr">
+        <is>
+          <t>Topic Focus</t>
+        </is>
+      </c>
+      <c r="B72" s="20" t="inlineStr">
+        <is>
+          <t>Self‑hosted AI</t>
+        </is>
+      </c>
+      <c r="C72" s="20" t="inlineStr">
+        <is>
+          <t>Self‑hosted, open‑weights models in contrast to API‑based models like OpenAI, Anthropic, or Gemini</t>
+        </is>
+      </c>
+      <c r="D72" s="20" t="inlineStr"/>
+      <c r="E72" s="20" t="inlineStr"/>
+      <c r="F72" s="20" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="20" t="inlineStr">
+        <is>
+          <t>Topic Focus</t>
+        </is>
+      </c>
+      <c r="B73" s="20" t="inlineStr">
+        <is>
+          <t>Data Protection</t>
+        </is>
+      </c>
+      <c r="C73" s="20" t="inlineStr">
+        <is>
+          <t>Safeguarding sensitive data specifically. Distinct from the broader Security term.</t>
+        </is>
+      </c>
+      <c r="D73" s="20" t="inlineStr">
+        <is>
+          <t>EDAM</t>
+        </is>
+      </c>
+      <c r="E73" s="20" t="inlineStr">
+        <is>
+          <t>topic_4044</t>
+        </is>
+      </c>
+      <c r="F73" s="20" t="inlineStr">
+        <is>
+          <t>http://edamontology.org/topic_4044</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="20" t="inlineStr">
+        <is>
+          <t>Topic Focus</t>
+        </is>
+      </c>
+      <c r="B74" s="20" t="inlineStr">
+        <is>
+          <t>FAIR data</t>
+        </is>
+      </c>
+      <c r="C74" s="20" t="inlineStr">
+        <is>
+          <t>Findable, Accessible, Interoperable, Reusable data principles.</t>
+        </is>
+      </c>
+      <c r="D74" s="20" t="inlineStr">
+        <is>
+          <t>EDAM</t>
+        </is>
+      </c>
+      <c r="E74" s="20" t="inlineStr">
+        <is>
+          <t>topic_4012</t>
+        </is>
+      </c>
+      <c r="F74" s="20" t="inlineStr">
+        <is>
+          <t>http://edamontology.org/topic_4012</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="20" t="inlineStr">
+        <is>
+          <t>Topic Focus</t>
+        </is>
+      </c>
+      <c r="B75" s="20" t="inlineStr">
+        <is>
+          <t>Data quality management</t>
+        </is>
+      </c>
+      <c r="C75" s="20" t="inlineStr"/>
+      <c r="D75" s="20" t="inlineStr">
+        <is>
+          <t>EDAM</t>
+        </is>
+      </c>
+      <c r="E75" s="20" t="inlineStr">
+        <is>
+          <t>topic_3572</t>
+        </is>
+      </c>
+      <c r="F75" s="20" t="inlineStr">
+        <is>
+          <t>http://edamontology.org/topic_3572</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="20" t="inlineStr">
+        <is>
+          <t>Topic Focus</t>
+        </is>
+      </c>
+      <c r="B76" s="20" t="inlineStr">
+        <is>
+          <t>Data curation and archival</t>
+        </is>
+      </c>
+      <c r="C76" s="20" t="inlineStr"/>
+      <c r="D76" s="20" t="inlineStr">
+        <is>
+          <t>EDAM</t>
+        </is>
+      </c>
+      <c r="E76" s="20" t="inlineStr">
+        <is>
+          <t>topic_0219</t>
+        </is>
+      </c>
+      <c r="F76" s="20" t="inlineStr">
+        <is>
+          <t>http://edamontology.org/topic_0219</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="20" t="inlineStr">
+        <is>
+          <t>Topic Focus</t>
+        </is>
+      </c>
+      <c r="B77" s="20" t="inlineStr">
+        <is>
+          <t>Data integration and warehousing</t>
+        </is>
+      </c>
+      <c r="C77" s="20" t="inlineStr"/>
+      <c r="D77" s="20" t="inlineStr">
+        <is>
+          <t>EDAM</t>
+        </is>
+      </c>
+      <c r="E77" s="20" t="inlineStr">
+        <is>
+          <t>topic_3366</t>
+        </is>
+      </c>
+      <c r="F77" s="20" t="inlineStr">
+        <is>
+          <t>http://edamontology.org/topic_3366</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="20" t="inlineStr">
+        <is>
+          <t>Topic Focus</t>
+        </is>
+      </c>
+      <c r="B78" s="20" t="inlineStr">
+        <is>
+          <t>Data architecture, analysis and design</t>
+        </is>
+      </c>
+      <c r="C78" s="20" t="inlineStr"/>
+      <c r="D78" s="20" t="inlineStr">
+        <is>
+          <t>EDAM</t>
+        </is>
+      </c>
+      <c r="E78" s="20" t="inlineStr">
+        <is>
+          <t>topic_3365</t>
+        </is>
+      </c>
+      <c r="F78" s="20" t="inlineStr">
+        <is>
+          <t>http://edamontology.org/topic_3365</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="20" t="inlineStr">
+        <is>
+          <t>Topic Focus</t>
+        </is>
+      </c>
+      <c r="B79" s="20" t="inlineStr">
+        <is>
+          <t>Data identity and mapping</t>
+        </is>
+      </c>
+      <c r="C79" s="20" t="inlineStr"/>
+      <c r="D79" s="20" t="inlineStr">
+        <is>
+          <t>EDAM</t>
+        </is>
+      </c>
+      <c r="E79" s="20" t="inlineStr">
+        <is>
+          <t>topic_3345</t>
+        </is>
+      </c>
+      <c r="F79" s="20" t="inlineStr">
+        <is>
+          <t>http://edamontology.org/topic_3345</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="20" t="inlineStr">
+        <is>
+          <t>Topic Focus</t>
+        </is>
+      </c>
+      <c r="B80" s="20" t="inlineStr">
+        <is>
+          <t>Data rescue</t>
+        </is>
+      </c>
+      <c r="C80" s="20" t="inlineStr"/>
+      <c r="D80" s="20" t="inlineStr">
+        <is>
+          <t>EDAM</t>
+        </is>
+      </c>
+      <c r="E80" s="20" t="inlineStr">
+        <is>
+          <t>topic_4011</t>
+        </is>
+      </c>
+      <c r="F80" s="20" t="inlineStr">
+        <is>
+          <t>http://edamontology.org/topic_4011</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="20" t="inlineStr">
+        <is>
+          <t>Topic Focus</t>
+        </is>
+      </c>
+      <c r="B81" s="20" t="inlineStr">
+        <is>
+          <t>Valid and Reliable</t>
+        </is>
+      </c>
+      <c r="C81" s="20" t="inlineStr">
+        <is>
+          <t>NIST AI RMF trustworthy-AI characteristic.</t>
+        </is>
+      </c>
+      <c r="D81" s="20" t="inlineStr">
+        <is>
+          <t>NIST-AI-RMF</t>
+        </is>
+      </c>
+      <c r="E81" s="20" t="inlineStr"/>
+      <c r="F81" s="20" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="20" t="inlineStr">
+        <is>
+          <t>Topic Focus</t>
+        </is>
+      </c>
+      <c r="B82" s="20" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="C82" s="20" t="inlineStr">
+        <is>
+          <t>NIST AI RMF trustworthy-AI characteristic.</t>
+        </is>
+      </c>
+      <c r="D82" s="20" t="inlineStr">
+        <is>
+          <t>NIST-AI-RMF</t>
+        </is>
+      </c>
+      <c r="E82" s="20" t="inlineStr"/>
+      <c r="F82" s="20" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="20" t="inlineStr">
+        <is>
+          <t>Topic Focus</t>
+        </is>
+      </c>
+      <c r="B83" s="20" t="inlineStr">
+        <is>
+          <t>Secure and Resilient</t>
+        </is>
+      </c>
+      <c r="C83" s="20" t="inlineStr">
+        <is>
+          <t>NIST AI RMF trustworthy-AI characteristic.</t>
+        </is>
+      </c>
+      <c r="D83" s="20" t="inlineStr">
+        <is>
+          <t>NIST-AI-RMF</t>
+        </is>
+      </c>
+      <c r="E83" s="20" t="inlineStr"/>
+      <c r="F83" s="20" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="20" t="inlineStr">
+        <is>
+          <t>Topic Focus</t>
+        </is>
+      </c>
+      <c r="B84" s="20" t="inlineStr">
+        <is>
+          <t>Accountable and Transparent</t>
+        </is>
+      </c>
+      <c r="C84" s="20" t="inlineStr">
+        <is>
+          <t>NIST AI RMF trustworthy-AI characteristic.</t>
+        </is>
+      </c>
+      <c r="D84" s="20" t="inlineStr">
+        <is>
+          <t>NIST-AI-RMF</t>
+        </is>
+      </c>
+      <c r="E84" s="20" t="inlineStr"/>
+      <c r="F84" s="20" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="20" t="inlineStr">
+        <is>
+          <t>Topic Focus</t>
+        </is>
+      </c>
+      <c r="B85" s="20" t="inlineStr">
+        <is>
+          <t>Explainable and Interpretable</t>
+        </is>
+      </c>
+      <c r="C85" s="20" t="inlineStr">
+        <is>
+          <t>NIST AI RMF trustworthy-AI characteristic.</t>
+        </is>
+      </c>
+      <c r="D85" s="20" t="inlineStr">
+        <is>
+          <t>NIST-AI-RMF</t>
+        </is>
+      </c>
+      <c r="E85" s="20" t="inlineStr"/>
+      <c r="F85" s="20" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="20" t="inlineStr">
+        <is>
+          <t>Topic Focus</t>
+        </is>
+      </c>
+      <c r="B86" s="20" t="inlineStr">
+        <is>
+          <t>Privacy-Enhanced</t>
+        </is>
+      </c>
+      <c r="C86" s="20" t="inlineStr">
+        <is>
+          <t>NIST AI RMF trustworthy-AI characteristic.</t>
+        </is>
+      </c>
+      <c r="D86" s="20" t="inlineStr">
+        <is>
+          <t>NIST-AI-RMF</t>
+        </is>
+      </c>
+      <c r="E86" s="20" t="inlineStr"/>
+      <c r="F86" s="20" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="20" t="inlineStr">
+        <is>
+          <t>Topic Focus</t>
+        </is>
+      </c>
+      <c r="B87" s="20" t="inlineStr">
+        <is>
+          <t>Fair (harmful bias managed)</t>
+        </is>
+      </c>
+      <c r="C87" s="20" t="inlineStr">
+        <is>
+          <t>NIST AI RMF trustworthy-AI characteristic: algorithmic non-discrimination. NOT the same as 'FAIR data'.</t>
+        </is>
+      </c>
+      <c r="D87" s="20" t="inlineStr">
+        <is>
+          <t>NIST-AI-RMF</t>
+        </is>
+      </c>
+      <c r="E87" s="20" t="inlineStr"/>
+      <c r="F87" s="20" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="20" t="inlineStr">
+        <is>
+          <t>Maturity Level</t>
+        </is>
+      </c>
+      <c r="B88" s="20" t="inlineStr">
+        <is>
+          <t>Emerging</t>
+        </is>
+      </c>
+      <c r="C88" s="20" t="inlineStr"/>
+      <c r="D88" s="20" t="inlineStr"/>
+      <c r="E88" s="20" t="inlineStr"/>
+      <c r="F88" s="20" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="20" t="inlineStr">
+        <is>
+          <t>Maturity Level</t>
+        </is>
+      </c>
+      <c r="B89" s="20" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="C89" s="20" t="inlineStr"/>
+      <c r="D89" s="20" t="inlineStr"/>
+      <c r="E89" s="20" t="inlineStr"/>
+      <c r="F89" s="20" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="20" t="inlineStr">
+        <is>
+          <t>Maturity Level</t>
+        </is>
+      </c>
+      <c r="B90" s="20" t="inlineStr">
+        <is>
+          <t>Mature</t>
+        </is>
+      </c>
+      <c r="C90" s="20" t="inlineStr"/>
+      <c r="D90" s="20" t="inlineStr"/>
+      <c r="E90" s="20" t="inlineStr"/>
+      <c r="F90" s="20" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="20" t="inlineStr">
+        <is>
+          <t>Maturity Level</t>
+        </is>
+      </c>
+      <c r="B91" s="20" t="inlineStr">
+        <is>
+          <t>Deprecated</t>
+        </is>
+      </c>
+      <c r="C91" s="20" t="inlineStr"/>
+      <c r="D91" s="20" t="inlineStr"/>
+      <c r="E91" s="20" t="inlineStr"/>
+      <c r="F91" s="20" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" style="17" min="1" max="1"/>
+    <col width="40" customWidth="1" style="17" min="2" max="2"/>
+    <col width="10" customWidth="1" style="17" min="3" max="3"/>
+    <col width="56" customWidth="1" style="17" min="4" max="4"/>
+    <col width="90" customWidth="1" style="17" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>Standard ID</t>
+        </is>
+      </c>
+      <c r="B1" s="19" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="19" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="D1" s="19" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="E1" s="19" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>EDAM</t>
+        </is>
+      </c>
+      <c r="B2" s="20" t="inlineStr">
+        <is>
+          <t>EDAM ontology (Data management branch)</t>
+        </is>
+      </c>
+      <c r="C2" s="20" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="D2" s="20" t="inlineStr">
+        <is>
+          <t>http://edamontology.org/topic_3071</t>
+        </is>
+      </c>
+      <c r="E2" s="20" t="inlineStr">
+        <is>
+          <t>Primary controlled vocabulary. Open OWL ontology with permanent per-term URIs. Browse: https://www.ebi.ac.uk/ols4/ontologies/edam - Download: http://edamontology.org/EDAM.owl</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="20" t="inlineStr">
+        <is>
+          <t>NIST-AI-RMF</t>
+        </is>
+      </c>
+      <c r="B3" s="20" t="inlineStr">
+        <is>
+          <t>NIST AI Risk Management Framework</t>
+        </is>
+      </c>
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D3" s="20" t="inlineStr">
+        <is>
+          <t>https://nvlpubs.nist.gov/nistpubs/ai/NIST.AI.100-1.pdf</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="inlineStr">
+        <is>
+          <t>Optional secondary axis: the seven trustworthy-AI characteristics. Document-based, so individual characteristics have no per-term URIs. WARNING: NIST's 'Fair (harmful bias managed)' concerns algorithmic non-discrimination and is UNRELATED to EDAM's 'FAIR data' (Findable / Accessible / Interoperable / Reusable data principles) despite sharing the word - do not conflate the two.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/VANTAGE-Technology-Radar.xlsx
+++ b/data/VANTAGE-Technology-Radar.xlsx
@@ -1757,7 +1757,7 @@
       </c>
       <c r="I22" s="16" t="inlineStr">
         <is>
-          <t>Parallel sampling &amp; tool-calling</t>
+          <t>Deployment patterns; Tool Integration</t>
         </is>
       </c>
       <c r="J22" s="16" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="M22" s="16" t="inlineStr">
         <is>
-          <t>Essential for secure TLAs via PagedAttention and FP8/AWQ optimization.</t>
+          <t>Essential for secure TLAs via PagedAttention and FP8/AWQ optimization. Capabilities: Parallel sampling &amp; tool-calling.</t>
         </is>
       </c>
       <c r="O22" s="18" t="n">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="I23" s="16" t="inlineStr">
         <is>
-          <t>Local embedding &amp; zero-config tools</t>
+          <t>Deployment patterns</t>
         </is>
       </c>
       <c r="J23" s="16" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M23" s="16" t="inlineStr">
         <is>
-          <t>Eliminates network dependency errors by cleanly bundling open model weights.</t>
+          <t>Eliminates network dependency errors by cleanly bundling open model weights. Capabilities: Local embedding &amp; zero-config tools.</t>
         </is>
       </c>
       <c r="O23" s="18" t="n">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="I24" s="16" t="inlineStr">
         <is>
-          <t>Grammar-based constrained sampling</t>
+          <t>Deployment patterns</t>
         </is>
       </c>
       <c r="J24" s="16" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="M24" s="16" t="inlineStr">
         <is>
-          <t>Grammar constraints ensure localized agentic pipelines always return valid JSON/code.</t>
+          <t>Grammar constraints ensure localized agentic pipelines always return valid JSON/code. Capabilities: Grammar-based constrained sampling.</t>
         </is>
       </c>
       <c r="O24" s="18" t="n">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="I25" s="16" t="inlineStr">
         <is>
-          <t>Local RAG pipelines &amp; offline functions</t>
+          <t>Retrieval</t>
         </is>
       </c>
       <c r="J25" s="16" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="M25" s="16" t="inlineStr">
         <is>
-          <t>Solves local file parsing/RAG bottlenecks entirely within secure client networks.</t>
+          <t>Solves local file parsing/RAG bottlenecks entirely within secure client networks. Capabilities: Local RAG pipelines &amp; offline functions.</t>
         </is>
       </c>
       <c r="O25" s="18" t="n">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="I26" s="16" t="inlineStr">
         <is>
-          <t>Tensor-parallel caching &amp; optimized tool-calling</t>
+          <t>Deployment patterns</t>
         </is>
       </c>
       <c r="J26" s="16" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="M26" s="16" t="inlineStr">
         <is>
-          <t>Outlines the exact connected-to-disconnected asset transfer workflow for enterprise GPUs.</t>
+          <t>Outlines the exact connected-to-disconnected asset transfer workflow for enterprise GPUs. Capabilities: Tensor-parallel caching &amp; optimized tool-calling.</t>
         </is>
       </c>
       <c r="O26" s="18" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="I27" s="16" t="inlineStr">
         <is>
-          <t>Artifact version-locking &amp; immutable tags</t>
+          <t>Deployment patterns</t>
         </is>
       </c>
       <c r="J27" s="16" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="M27" s="16" t="inlineStr">
         <is>
-          <t>Built-in vulnerability scanning ensures agent images remain clean behind the firewall.</t>
+          <t>Built-in vulnerability scanning ensures agent images remain clean behind the firewall. Capabilities: Artifact version-locking &amp; immutable tags.</t>
         </is>
       </c>
       <c r="O27" s="18" t="n">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="I28" s="16" t="inlineStr">
         <is>
-          <t>End-to-end local reference applications</t>
+          <t>Deployment patterns; Retrieval</t>
         </is>
       </c>
       <c r="J28" s="16" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="M28" s="16" t="inlineStr">
         <is>
-          <t>Moves past simple how-to guides into formal data isolation and local compliance frameworks.</t>
+          <t>Moves past simple how-to guides into formal data isolation and local compliance frameworks. Capabilities: End-to-end local reference applications.</t>
         </is>
       </c>
       <c r="O28" s="18" t="n">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="I29" s="16" t="inlineStr">
         <is>
-          <t>Hardware performance scaling &amp; VRAM sizing</t>
+          <t>Deployment patterns</t>
         </is>
       </c>
       <c r="J29" s="16" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="M29" s="16" t="inlineStr">
         <is>
-          <t>Breaks down the "Memory Wall" economics showing an on-prem breakeven velocity of ~4 months.</t>
+          <t>Breaks down the "Memory Wall" economics showing an on-prem breakeven velocity of ~4 months. Capabilities: Hardware performance scaling &amp; VRAM sizing.</t>
         </is>
       </c>
       <c r="O29" s="18" t="n">
@@ -3681,7 +3681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F91"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="17" min="1" max="1"/>
@@ -4543,12 +4543,12 @@
     <row r="51">
       <c r="A51" s="20" t="inlineStr">
         <is>
-          <t>Agentic Features Covered</t>
+          <t>Topic Focus</t>
         </is>
       </c>
       <c r="B51" s="20" t="inlineStr">
         <is>
-          <t>Artifact version-locking &amp; immutable tags</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="C51" s="20" t="inlineStr"/>
@@ -4559,12 +4559,12 @@
     <row r="52">
       <c r="A52" s="20" t="inlineStr">
         <is>
-          <t>Agentic Features Covered</t>
+          <t>Topic Focus</t>
         </is>
       </c>
       <c r="B52" s="20" t="inlineStr">
         <is>
-          <t>End-to-end local reference applications</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="C52" s="20" t="inlineStr"/>
@@ -4575,31 +4575,51 @@
     <row r="53">
       <c r="A53" s="20" t="inlineStr">
         <is>
-          <t>Agentic Features Covered</t>
+          <t>Topic Focus</t>
         </is>
       </c>
       <c r="B53" s="20" t="inlineStr">
         <is>
-          <t>Grammar-based constrained sampling</t>
-        </is>
-      </c>
-      <c r="C53" s="20" t="inlineStr"/>
-      <c r="D53" s="20" t="inlineStr"/>
-      <c r="E53" s="20" t="inlineStr"/>
-      <c r="F53" s="20" t="inlineStr"/>
+          <t>Data governance</t>
+        </is>
+      </c>
+      <c r="C53" s="20" t="inlineStr">
+        <is>
+          <t>Focuses specifically on the technical protocols, access controls, data-line security, and de-identification standards used to protect the integrity, quality, and privacy of information throughout its lifecycle</t>
+        </is>
+      </c>
+      <c r="D53" s="20" t="inlineStr">
+        <is>
+          <t>EDAM</t>
+        </is>
+      </c>
+      <c r="E53" s="20" t="inlineStr">
+        <is>
+          <t>topic_3571</t>
+        </is>
+      </c>
+      <c r="F53" s="20" t="inlineStr">
+        <is>
+          <t>http://edamontology.org/topic_3571</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="20" t="inlineStr">
         <is>
-          <t>Agentic Features Covered</t>
+          <t>Topic Focus</t>
         </is>
       </c>
       <c r="B54" s="20" t="inlineStr">
         <is>
-          <t>Hardware performance scaling &amp; VRAM sizing</t>
-        </is>
-      </c>
-      <c r="C54" s="20" t="inlineStr"/>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="C54" s="20" t="inlineStr">
+        <is>
+          <t>The overarching organizational policies, compliance frameworks, and capital allocation strategies that dictate how an enterprise manages its broader IT infrastructure, risk tolerances, and vendor choices</t>
+        </is>
+      </c>
       <c r="D54" s="20" t="inlineStr"/>
       <c r="E54" s="20" t="inlineStr"/>
       <c r="F54" s="20" t="inlineStr"/>
@@ -4607,12 +4627,12 @@
     <row r="55">
       <c r="A55" s="20" t="inlineStr">
         <is>
-          <t>Agentic Features Covered</t>
+          <t>Topic Focus</t>
         </is>
       </c>
       <c r="B55" s="20" t="inlineStr">
         <is>
-          <t>Local RAG pipelines &amp; offline functions</t>
+          <t>Implementation</t>
         </is>
       </c>
       <c r="C55" s="20" t="inlineStr"/>
@@ -4623,15 +4643,19 @@
     <row r="56">
       <c r="A56" s="20" t="inlineStr">
         <is>
-          <t>Agentic Features Covered</t>
+          <t>Topic Focus</t>
         </is>
       </c>
       <c r="B56" s="20" t="inlineStr">
         <is>
-          <t>Local embedding &amp; zero-config tools</t>
-        </is>
-      </c>
-      <c r="C56" s="20" t="inlineStr"/>
+          <t>Deployment</t>
+        </is>
+      </c>
+      <c r="C56" s="20" t="inlineStr">
+        <is>
+          <t>The tactical, hands-on execution of installing, configuring, provisioning, and launching software or hardware systems within a specific operational environment</t>
+        </is>
+      </c>
       <c r="D56" s="20" t="inlineStr"/>
       <c r="E56" s="20" t="inlineStr"/>
       <c r="F56" s="20" t="inlineStr"/>
@@ -4639,28 +4663,40 @@
     <row r="57">
       <c r="A57" s="20" t="inlineStr">
         <is>
-          <t>Agentic Features Covered</t>
+          <t>Topic Focus</t>
         </is>
       </c>
       <c r="B57" s="20" t="inlineStr">
         <is>
-          <t>Parallel sampling &amp; tool-calling</t>
+          <t>Workflows</t>
         </is>
       </c>
       <c r="C57" s="20" t="inlineStr"/>
-      <c r="D57" s="20" t="inlineStr"/>
-      <c r="E57" s="20" t="inlineStr"/>
-      <c r="F57" s="20" t="inlineStr"/>
+      <c r="D57" s="20" t="inlineStr">
+        <is>
+          <t>EDAM</t>
+        </is>
+      </c>
+      <c r="E57" s="20" t="inlineStr">
+        <is>
+          <t>topic_0769</t>
+        </is>
+      </c>
+      <c r="F57" s="20" t="inlineStr">
+        <is>
+          <t>http://edamontology.org/topic_0769</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="20" t="inlineStr">
         <is>
-          <t>Agentic Features Covered</t>
+          <t>Topic Focus</t>
         </is>
       </c>
       <c r="B58" s="20" t="inlineStr">
         <is>
-          <t>Tensor-parallel caching &amp; optimized tool-calling</t>
+          <t>Workflow integration</t>
         </is>
       </c>
       <c r="C58" s="20" t="inlineStr"/>
@@ -4676,7 +4712,7 @@
       </c>
       <c r="B59" s="20" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Model selection</t>
         </is>
       </c>
       <c r="C59" s="20" t="inlineStr"/>
@@ -4692,7 +4728,7 @@
       </c>
       <c r="B60" s="20" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Evaluation</t>
         </is>
       </c>
       <c r="C60" s="20" t="inlineStr"/>
@@ -4708,29 +4744,17 @@
       </c>
       <c r="B61" s="20" t="inlineStr">
         <is>
-          <t>Data governance</t>
+          <t>Architecture Compute</t>
         </is>
       </c>
       <c r="C61" s="20" t="inlineStr">
         <is>
-          <t>Focuses specifically on the technical protocols, access controls, data-line security, and de-identification standards used to protect the integrity, quality, and privacy of information throughout its lifecycle</t>
-        </is>
-      </c>
-      <c r="D61" s="20" t="inlineStr">
-        <is>
-          <t>EDAM</t>
-        </is>
-      </c>
-      <c r="E61" s="20" t="inlineStr">
-        <is>
-          <t>topic_3571</t>
-        </is>
-      </c>
-      <c r="F61" s="20" t="inlineStr">
-        <is>
-          <t>http://edamontology.org/topic_3571</t>
-        </is>
-      </c>
+          <t>Physical node topologies, hardware constraints, VRAM bounds, and localized compute execution profiles.</t>
+        </is>
+      </c>
+      <c r="D61" s="20" t="inlineStr"/>
+      <c r="E61" s="20" t="inlineStr"/>
+      <c r="F61" s="20" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="20" t="inlineStr">
@@ -4740,12 +4764,12 @@
       </c>
       <c r="B62" s="20" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Network Isolation</t>
         </is>
       </c>
       <c r="C62" s="20" t="inlineStr">
         <is>
-          <t>The overarching organizational policies, compliance frameworks, and capital allocation strategies that dictate how an enterprise manages its broader IT infrastructure, risk tolerances, and vendor choices</t>
+          <t>Non-egress boundaries, air-gapped artifact staging, localized cloud VPC containers, and firewalled local registries.</t>
         </is>
       </c>
       <c r="D62" s="20" t="inlineStr"/>
@@ -4760,10 +4784,14 @@
       </c>
       <c r="B63" s="20" t="inlineStr">
         <is>
-          <t>Implementation</t>
-        </is>
-      </c>
-      <c r="C63" s="20" t="inlineStr"/>
+          <t>Infrastructure Security</t>
+        </is>
+      </c>
+      <c r="C63" s="20" t="inlineStr">
+        <is>
+          <t>For on-prem LLM deployments, it captures the security of the compute stack as well as the data pipelines</t>
+        </is>
+      </c>
       <c r="D63" s="20" t="inlineStr"/>
       <c r="E63" s="20" t="inlineStr"/>
       <c r="F63" s="20" t="inlineStr"/>
@@ -4776,12 +4804,12 @@
       </c>
       <c r="B64" s="20" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Self‑hosted AI</t>
         </is>
       </c>
       <c r="C64" s="20" t="inlineStr">
         <is>
-          <t>The tactical, hands-on execution of installing, configuring, provisioning, and launching software or hardware systems within a specific operational environment</t>
+          <t>Self‑hosted, open‑weights models in contrast to API‑based models like OpenAI, Anthropic, or Gemini</t>
         </is>
       </c>
       <c r="D64" s="20" t="inlineStr"/>
@@ -4796,10 +4824,14 @@
       </c>
       <c r="B65" s="20" t="inlineStr">
         <is>
-          <t>Workflows</t>
-        </is>
-      </c>
-      <c r="C65" s="20" t="inlineStr"/>
+          <t>Data Protection</t>
+        </is>
+      </c>
+      <c r="C65" s="20" t="inlineStr">
+        <is>
+          <t>Safeguarding sensitive data specifically. Distinct from the broader Security term.</t>
+        </is>
+      </c>
       <c r="D65" s="20" t="inlineStr">
         <is>
           <t>EDAM</t>
@@ -4807,12 +4839,12 @@
       </c>
       <c r="E65" s="20" t="inlineStr">
         <is>
-          <t>topic_0769</t>
+          <t>topic_4044</t>
         </is>
       </c>
       <c r="F65" s="20" t="inlineStr">
         <is>
-          <t>http://edamontology.org/topic_0769</t>
+          <t>http://edamontology.org/topic_4044</t>
         </is>
       </c>
     </row>
@@ -4824,13 +4856,29 @@
       </c>
       <c r="B66" s="20" t="inlineStr">
         <is>
-          <t>Workflow integration</t>
-        </is>
-      </c>
-      <c r="C66" s="20" t="inlineStr"/>
-      <c r="D66" s="20" t="inlineStr"/>
-      <c r="E66" s="20" t="inlineStr"/>
-      <c r="F66" s="20" t="inlineStr"/>
+          <t>FAIR data</t>
+        </is>
+      </c>
+      <c r="C66" s="20" t="inlineStr">
+        <is>
+          <t>Findable, Accessible, Interoperable, Reusable data principles.</t>
+        </is>
+      </c>
+      <c r="D66" s="20" t="inlineStr">
+        <is>
+          <t>EDAM</t>
+        </is>
+      </c>
+      <c r="E66" s="20" t="inlineStr">
+        <is>
+          <t>topic_4012</t>
+        </is>
+      </c>
+      <c r="F66" s="20" t="inlineStr">
+        <is>
+          <t>http://edamontology.org/topic_4012</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="20" t="inlineStr">
@@ -4840,13 +4888,25 @@
       </c>
       <c r="B67" s="20" t="inlineStr">
         <is>
-          <t>Model selection</t>
+          <t>Data quality management</t>
         </is>
       </c>
       <c r="C67" s="20" t="inlineStr"/>
-      <c r="D67" s="20" t="inlineStr"/>
-      <c r="E67" s="20" t="inlineStr"/>
-      <c r="F67" s="20" t="inlineStr"/>
+      <c r="D67" s="20" t="inlineStr">
+        <is>
+          <t>EDAM</t>
+        </is>
+      </c>
+      <c r="E67" s="20" t="inlineStr">
+        <is>
+          <t>topic_3572</t>
+        </is>
+      </c>
+      <c r="F67" s="20" t="inlineStr">
+        <is>
+          <t>http://edamontology.org/topic_3572</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="20" t="inlineStr">
@@ -4856,13 +4916,25 @@
       </c>
       <c r="B68" s="20" t="inlineStr">
         <is>
-          <t>Evaluation</t>
+          <t>Data curation and archival</t>
         </is>
       </c>
       <c r="C68" s="20" t="inlineStr"/>
-      <c r="D68" s="20" t="inlineStr"/>
-      <c r="E68" s="20" t="inlineStr"/>
-      <c r="F68" s="20" t="inlineStr"/>
+      <c r="D68" s="20" t="inlineStr">
+        <is>
+          <t>EDAM</t>
+        </is>
+      </c>
+      <c r="E68" s="20" t="inlineStr">
+        <is>
+          <t>topic_0219</t>
+        </is>
+      </c>
+      <c r="F68" s="20" t="inlineStr">
+        <is>
+          <t>http://edamontology.org/topic_0219</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="20" t="inlineStr">
@@ -4872,17 +4944,25 @@
       </c>
       <c r="B69" s="20" t="inlineStr">
         <is>
-          <t>Architecture Compute</t>
-        </is>
-      </c>
-      <c r="C69" s="20" t="inlineStr">
-        <is>
-          <t>Physical node topologies, hardware constraints, VRAM bounds, and localized compute execution profiles.</t>
-        </is>
-      </c>
-      <c r="D69" s="20" t="inlineStr"/>
-      <c r="E69" s="20" t="inlineStr"/>
-      <c r="F69" s="20" t="inlineStr"/>
+          <t>Data integration and warehousing</t>
+        </is>
+      </c>
+      <c r="C69" s="20" t="inlineStr"/>
+      <c r="D69" s="20" t="inlineStr">
+        <is>
+          <t>EDAM</t>
+        </is>
+      </c>
+      <c r="E69" s="20" t="inlineStr">
+        <is>
+          <t>topic_3366</t>
+        </is>
+      </c>
+      <c r="F69" s="20" t="inlineStr">
+        <is>
+          <t>http://edamontology.org/topic_3366</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="20" t="inlineStr">
@@ -4892,17 +4972,25 @@
       </c>
       <c r="B70" s="20" t="inlineStr">
         <is>
-          <t>Network Isolation</t>
-        </is>
-      </c>
-      <c r="C70" s="20" t="inlineStr">
-        <is>
-          <t>Non-egress boundaries, air-gapped artifact staging, localized cloud VPC containers, and firewalled local registries.</t>
-        </is>
-      </c>
-      <c r="D70" s="20" t="inlineStr"/>
-      <c r="E70" s="20" t="inlineStr"/>
-      <c r="F70" s="20" t="inlineStr"/>
+          <t>Data architecture, analysis and design</t>
+        </is>
+      </c>
+      <c r="C70" s="20" t="inlineStr"/>
+      <c r="D70" s="20" t="inlineStr">
+        <is>
+          <t>EDAM</t>
+        </is>
+      </c>
+      <c r="E70" s="20" t="inlineStr">
+        <is>
+          <t>topic_3365</t>
+        </is>
+      </c>
+      <c r="F70" s="20" t="inlineStr">
+        <is>
+          <t>http://edamontology.org/topic_3365</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="20" t="inlineStr">
@@ -4912,17 +5000,25 @@
       </c>
       <c r="B71" s="20" t="inlineStr">
         <is>
-          <t>Infrastructure Security</t>
-        </is>
-      </c>
-      <c r="C71" s="20" t="inlineStr">
-        <is>
-          <t>For on-prem LLM deployments, it captures the security of the compute stack as well as the data pipelines</t>
-        </is>
-      </c>
-      <c r="D71" s="20" t="inlineStr"/>
-      <c r="E71" s="20" t="inlineStr"/>
-      <c r="F71" s="20" t="inlineStr"/>
+          <t>Data identity and mapping</t>
+        </is>
+      </c>
+      <c r="C71" s="20" t="inlineStr"/>
+      <c r="D71" s="20" t="inlineStr">
+        <is>
+          <t>EDAM</t>
+        </is>
+      </c>
+      <c r="E71" s="20" t="inlineStr">
+        <is>
+          <t>topic_3345</t>
+        </is>
+      </c>
+      <c r="F71" s="20" t="inlineStr">
+        <is>
+          <t>http://edamontology.org/topic_3345</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="20" t="inlineStr">
@@ -4932,17 +5028,25 @@
       </c>
       <c r="B72" s="20" t="inlineStr">
         <is>
-          <t>Self‑hosted AI</t>
-        </is>
-      </c>
-      <c r="C72" s="20" t="inlineStr">
-        <is>
-          <t>Self‑hosted, open‑weights models in contrast to API‑based models like OpenAI, Anthropic, or Gemini</t>
-        </is>
-      </c>
-      <c r="D72" s="20" t="inlineStr"/>
-      <c r="E72" s="20" t="inlineStr"/>
-      <c r="F72" s="20" t="inlineStr"/>
+          <t>Data rescue</t>
+        </is>
+      </c>
+      <c r="C72" s="20" t="inlineStr"/>
+      <c r="D72" s="20" t="inlineStr">
+        <is>
+          <t>EDAM</t>
+        </is>
+      </c>
+      <c r="E72" s="20" t="inlineStr">
+        <is>
+          <t>topic_4011</t>
+        </is>
+      </c>
+      <c r="F72" s="20" t="inlineStr">
+        <is>
+          <t>http://edamontology.org/topic_4011</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="20" t="inlineStr">
@@ -4952,29 +5056,21 @@
       </c>
       <c r="B73" s="20" t="inlineStr">
         <is>
-          <t>Data Protection</t>
+          <t>Valid and Reliable</t>
         </is>
       </c>
       <c r="C73" s="20" t="inlineStr">
         <is>
-          <t>Safeguarding sensitive data specifically. Distinct from the broader Security term.</t>
+          <t>NIST AI RMF trustworthy-AI characteristic.</t>
         </is>
       </c>
       <c r="D73" s="20" t="inlineStr">
         <is>
-          <t>EDAM</t>
-        </is>
-      </c>
-      <c r="E73" s="20" t="inlineStr">
-        <is>
-          <t>topic_4044</t>
-        </is>
-      </c>
-      <c r="F73" s="20" t="inlineStr">
-        <is>
-          <t>http://edamontology.org/topic_4044</t>
-        </is>
-      </c>
+          <t>NIST-AI-RMF</t>
+        </is>
+      </c>
+      <c r="E73" s="20" t="inlineStr"/>
+      <c r="F73" s="20" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="20" t="inlineStr">
@@ -4984,29 +5080,21 @@
       </c>
       <c r="B74" s="20" t="inlineStr">
         <is>
-          <t>FAIR data</t>
+          <t>Safe</t>
         </is>
       </c>
       <c r="C74" s="20" t="inlineStr">
         <is>
-          <t>Findable, Accessible, Interoperable, Reusable data principles.</t>
+          <t>NIST AI RMF trustworthy-AI characteristic.</t>
         </is>
       </c>
       <c r="D74" s="20" t="inlineStr">
         <is>
-          <t>EDAM</t>
-        </is>
-      </c>
-      <c r="E74" s="20" t="inlineStr">
-        <is>
-          <t>topic_4012</t>
-        </is>
-      </c>
-      <c r="F74" s="20" t="inlineStr">
-        <is>
-          <t>http://edamontology.org/topic_4012</t>
-        </is>
-      </c>
+          <t>NIST-AI-RMF</t>
+        </is>
+      </c>
+      <c r="E74" s="20" t="inlineStr"/>
+      <c r="F74" s="20" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="20" t="inlineStr">
@@ -5016,25 +5104,21 @@
       </c>
       <c r="B75" s="20" t="inlineStr">
         <is>
-          <t>Data quality management</t>
-        </is>
-      </c>
-      <c r="C75" s="20" t="inlineStr"/>
+          <t>Secure and Resilient</t>
+        </is>
+      </c>
+      <c r="C75" s="20" t="inlineStr">
+        <is>
+          <t>NIST AI RMF trustworthy-AI characteristic.</t>
+        </is>
+      </c>
       <c r="D75" s="20" t="inlineStr">
         <is>
-          <t>EDAM</t>
-        </is>
-      </c>
-      <c r="E75" s="20" t="inlineStr">
-        <is>
-          <t>topic_3572</t>
-        </is>
-      </c>
-      <c r="F75" s="20" t="inlineStr">
-        <is>
-          <t>http://edamontology.org/topic_3572</t>
-        </is>
-      </c>
+          <t>NIST-AI-RMF</t>
+        </is>
+      </c>
+      <c r="E75" s="20" t="inlineStr"/>
+      <c r="F75" s="20" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="20" t="inlineStr">
@@ -5044,25 +5128,21 @@
       </c>
       <c r="B76" s="20" t="inlineStr">
         <is>
-          <t>Data curation and archival</t>
-        </is>
-      </c>
-      <c r="C76" s="20" t="inlineStr"/>
+          <t>Accountable and Transparent</t>
+        </is>
+      </c>
+      <c r="C76" s="20" t="inlineStr">
+        <is>
+          <t>NIST AI RMF trustworthy-AI characteristic.</t>
+        </is>
+      </c>
       <c r="D76" s="20" t="inlineStr">
         <is>
-          <t>EDAM</t>
-        </is>
-      </c>
-      <c r="E76" s="20" t="inlineStr">
-        <is>
-          <t>topic_0219</t>
-        </is>
-      </c>
-      <c r="F76" s="20" t="inlineStr">
-        <is>
-          <t>http://edamontology.org/topic_0219</t>
-        </is>
-      </c>
+          <t>NIST-AI-RMF</t>
+        </is>
+      </c>
+      <c r="E76" s="20" t="inlineStr"/>
+      <c r="F76" s="20" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="20" t="inlineStr">
@@ -5072,25 +5152,21 @@
       </c>
       <c r="B77" s="20" t="inlineStr">
         <is>
-          <t>Data integration and warehousing</t>
-        </is>
-      </c>
-      <c r="C77" s="20" t="inlineStr"/>
+          <t>Explainable and Interpretable</t>
+        </is>
+      </c>
+      <c r="C77" s="20" t="inlineStr">
+        <is>
+          <t>NIST AI RMF trustworthy-AI characteristic.</t>
+        </is>
+      </c>
       <c r="D77" s="20" t="inlineStr">
         <is>
-          <t>EDAM</t>
-        </is>
-      </c>
-      <c r="E77" s="20" t="inlineStr">
-        <is>
-          <t>topic_3366</t>
-        </is>
-      </c>
-      <c r="F77" s="20" t="inlineStr">
-        <is>
-          <t>http://edamontology.org/topic_3366</t>
-        </is>
-      </c>
+          <t>NIST-AI-RMF</t>
+        </is>
+      </c>
+      <c r="E77" s="20" t="inlineStr"/>
+      <c r="F77" s="20" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="20" t="inlineStr">
@@ -5100,25 +5176,21 @@
       </c>
       <c r="B78" s="20" t="inlineStr">
         <is>
-          <t>Data architecture, analysis and design</t>
-        </is>
-      </c>
-      <c r="C78" s="20" t="inlineStr"/>
+          <t>Privacy-Enhanced</t>
+        </is>
+      </c>
+      <c r="C78" s="20" t="inlineStr">
+        <is>
+          <t>NIST AI RMF trustworthy-AI characteristic.</t>
+        </is>
+      </c>
       <c r="D78" s="20" t="inlineStr">
         <is>
-          <t>EDAM</t>
-        </is>
-      </c>
-      <c r="E78" s="20" t="inlineStr">
-        <is>
-          <t>topic_3365</t>
-        </is>
-      </c>
-      <c r="F78" s="20" t="inlineStr">
-        <is>
-          <t>http://edamontology.org/topic_3365</t>
-        </is>
-      </c>
+          <t>NIST-AI-RMF</t>
+        </is>
+      </c>
+      <c r="E78" s="20" t="inlineStr"/>
+      <c r="F78" s="20" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="20" t="inlineStr">
@@ -5128,285 +5200,85 @@
       </c>
       <c r="B79" s="20" t="inlineStr">
         <is>
-          <t>Data identity and mapping</t>
-        </is>
-      </c>
-      <c r="C79" s="20" t="inlineStr"/>
+          <t>Fair (harmful bias managed)</t>
+        </is>
+      </c>
+      <c r="C79" s="20" t="inlineStr">
+        <is>
+          <t>NIST AI RMF trustworthy-AI characteristic: algorithmic non-discrimination. NOT the same as 'FAIR data'.</t>
+        </is>
+      </c>
       <c r="D79" s="20" t="inlineStr">
         <is>
-          <t>EDAM</t>
-        </is>
-      </c>
-      <c r="E79" s="20" t="inlineStr">
-        <is>
-          <t>topic_3345</t>
-        </is>
-      </c>
-      <c r="F79" s="20" t="inlineStr">
-        <is>
-          <t>http://edamontology.org/topic_3345</t>
-        </is>
-      </c>
+          <t>NIST-AI-RMF</t>
+        </is>
+      </c>
+      <c r="E79" s="20" t="inlineStr"/>
+      <c r="F79" s="20" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="20" t="inlineStr">
         <is>
-          <t>Topic Focus</t>
+          <t>Maturity Level</t>
         </is>
       </c>
       <c r="B80" s="20" t="inlineStr">
         <is>
-          <t>Data rescue</t>
+          <t>Emerging</t>
         </is>
       </c>
       <c r="C80" s="20" t="inlineStr"/>
-      <c r="D80" s="20" t="inlineStr">
-        <is>
-          <t>EDAM</t>
-        </is>
-      </c>
-      <c r="E80" s="20" t="inlineStr">
-        <is>
-          <t>topic_4011</t>
-        </is>
-      </c>
-      <c r="F80" s="20" t="inlineStr">
-        <is>
-          <t>http://edamontology.org/topic_4011</t>
-        </is>
-      </c>
+      <c r="D80" s="20" t="inlineStr"/>
+      <c r="E80" s="20" t="inlineStr"/>
+      <c r="F80" s="20" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="20" t="inlineStr">
         <is>
-          <t>Topic Focus</t>
+          <t>Maturity Level</t>
         </is>
       </c>
       <c r="B81" s="20" t="inlineStr">
         <is>
-          <t>Valid and Reliable</t>
-        </is>
-      </c>
-      <c r="C81" s="20" t="inlineStr">
-        <is>
-          <t>NIST AI RMF trustworthy-AI characteristic.</t>
-        </is>
-      </c>
-      <c r="D81" s="20" t="inlineStr">
-        <is>
-          <t>NIST-AI-RMF</t>
-        </is>
-      </c>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="C81" s="20" t="inlineStr"/>
+      <c r="D81" s="20" t="inlineStr"/>
       <c r="E81" s="20" t="inlineStr"/>
       <c r="F81" s="20" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="20" t="inlineStr">
         <is>
-          <t>Topic Focus</t>
+          <t>Maturity Level</t>
         </is>
       </c>
       <c r="B82" s="20" t="inlineStr">
         <is>
-          <t>Safe</t>
-        </is>
-      </c>
-      <c r="C82" s="20" t="inlineStr">
-        <is>
-          <t>NIST AI RMF trustworthy-AI characteristic.</t>
-        </is>
-      </c>
-      <c r="D82" s="20" t="inlineStr">
-        <is>
-          <t>NIST-AI-RMF</t>
-        </is>
-      </c>
+          <t>Mature</t>
+        </is>
+      </c>
+      <c r="C82" s="20" t="inlineStr"/>
+      <c r="D82" s="20" t="inlineStr"/>
       <c r="E82" s="20" t="inlineStr"/>
       <c r="F82" s="20" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="20" t="inlineStr">
         <is>
-          <t>Topic Focus</t>
+          <t>Maturity Level</t>
         </is>
       </c>
       <c r="B83" s="20" t="inlineStr">
         <is>
-          <t>Secure and Resilient</t>
-        </is>
-      </c>
-      <c r="C83" s="20" t="inlineStr">
-        <is>
-          <t>NIST AI RMF trustworthy-AI characteristic.</t>
-        </is>
-      </c>
-      <c r="D83" s="20" t="inlineStr">
-        <is>
-          <t>NIST-AI-RMF</t>
-        </is>
-      </c>
+          <t>Deprecated</t>
+        </is>
+      </c>
+      <c r="C83" s="20" t="inlineStr"/>
+      <c r="D83" s="20" t="inlineStr"/>
       <c r="E83" s="20" t="inlineStr"/>
       <c r="F83" s="20" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="20" t="inlineStr">
-        <is>
-          <t>Topic Focus</t>
-        </is>
-      </c>
-      <c r="B84" s="20" t="inlineStr">
-        <is>
-          <t>Accountable and Transparent</t>
-        </is>
-      </c>
-      <c r="C84" s="20" t="inlineStr">
-        <is>
-          <t>NIST AI RMF trustworthy-AI characteristic.</t>
-        </is>
-      </c>
-      <c r="D84" s="20" t="inlineStr">
-        <is>
-          <t>NIST-AI-RMF</t>
-        </is>
-      </c>
-      <c r="E84" s="20" t="inlineStr"/>
-      <c r="F84" s="20" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="20" t="inlineStr">
-        <is>
-          <t>Topic Focus</t>
-        </is>
-      </c>
-      <c r="B85" s="20" t="inlineStr">
-        <is>
-          <t>Explainable and Interpretable</t>
-        </is>
-      </c>
-      <c r="C85" s="20" t="inlineStr">
-        <is>
-          <t>NIST AI RMF trustworthy-AI characteristic.</t>
-        </is>
-      </c>
-      <c r="D85" s="20" t="inlineStr">
-        <is>
-          <t>NIST-AI-RMF</t>
-        </is>
-      </c>
-      <c r="E85" s="20" t="inlineStr"/>
-      <c r="F85" s="20" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="20" t="inlineStr">
-        <is>
-          <t>Topic Focus</t>
-        </is>
-      </c>
-      <c r="B86" s="20" t="inlineStr">
-        <is>
-          <t>Privacy-Enhanced</t>
-        </is>
-      </c>
-      <c r="C86" s="20" t="inlineStr">
-        <is>
-          <t>NIST AI RMF trustworthy-AI characteristic.</t>
-        </is>
-      </c>
-      <c r="D86" s="20" t="inlineStr">
-        <is>
-          <t>NIST-AI-RMF</t>
-        </is>
-      </c>
-      <c r="E86" s="20" t="inlineStr"/>
-      <c r="F86" s="20" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="20" t="inlineStr">
-        <is>
-          <t>Topic Focus</t>
-        </is>
-      </c>
-      <c r="B87" s="20" t="inlineStr">
-        <is>
-          <t>Fair (harmful bias managed)</t>
-        </is>
-      </c>
-      <c r="C87" s="20" t="inlineStr">
-        <is>
-          <t>NIST AI RMF trustworthy-AI characteristic: algorithmic non-discrimination. NOT the same as 'FAIR data'.</t>
-        </is>
-      </c>
-      <c r="D87" s="20" t="inlineStr">
-        <is>
-          <t>NIST-AI-RMF</t>
-        </is>
-      </c>
-      <c r="E87" s="20" t="inlineStr"/>
-      <c r="F87" s="20" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="20" t="inlineStr">
-        <is>
-          <t>Maturity Level</t>
-        </is>
-      </c>
-      <c r="B88" s="20" t="inlineStr">
-        <is>
-          <t>Emerging</t>
-        </is>
-      </c>
-      <c r="C88" s="20" t="inlineStr"/>
-      <c r="D88" s="20" t="inlineStr"/>
-      <c r="E88" s="20" t="inlineStr"/>
-      <c r="F88" s="20" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="20" t="inlineStr">
-        <is>
-          <t>Maturity Level</t>
-        </is>
-      </c>
-      <c r="B89" s="20" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="C89" s="20" t="inlineStr"/>
-      <c r="D89" s="20" t="inlineStr"/>
-      <c r="E89" s="20" t="inlineStr"/>
-      <c r="F89" s="20" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="20" t="inlineStr">
-        <is>
-          <t>Maturity Level</t>
-        </is>
-      </c>
-      <c r="B90" s="20" t="inlineStr">
-        <is>
-          <t>Mature</t>
-        </is>
-      </c>
-      <c r="C90" s="20" t="inlineStr"/>
-      <c r="D90" s="20" t="inlineStr"/>
-      <c r="E90" s="20" t="inlineStr"/>
-      <c r="F90" s="20" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="20" t="inlineStr">
-        <is>
-          <t>Maturity Level</t>
-        </is>
-      </c>
-      <c r="B91" s="20" t="inlineStr">
-        <is>
-          <t>Deprecated</t>
-        </is>
-      </c>
-      <c r="C91" s="20" t="inlineStr"/>
-      <c r="D91" s="20" t="inlineStr"/>
-      <c r="E91" s="20" t="inlineStr"/>
-      <c r="F91" s="20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/VANTAGE-Technology-Radar.xlsx
+++ b/data/VANTAGE-Technology-Radar.xlsx
@@ -1337,9 +1337,7 @@
           <t>Project Jupyter</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n">
-        <v>46150</v>
-      </c>
+      <c r="D15" s="6" t="n"/>
       <c r="E15" s="7" t="n"/>
       <c r="F15" s="7" t="n">
         <v>46113</v>
@@ -1352,7 +1350,7 @@
       </c>
       <c r="I15" s="16" t="inlineStr">
         <is>
-          <t>Notebook Agents; Tool Integration</t>
+          <t>Notebook Agents; Workflow Automation</t>
         </is>
       </c>
       <c r="J15" s="16" t="inlineStr">
@@ -1743,9 +1741,7 @@
           <t>vLLM Project Team</t>
         </is>
       </c>
-      <c r="D22" s="6" t="n">
-        <v>46150</v>
-      </c>
+      <c r="D22" s="6" t="n"/>
       <c r="F22" s="7" t="n">
         <v>46113</v>
       </c>
@@ -1757,7 +1753,7 @@
       </c>
       <c r="I22" s="16" t="inlineStr">
         <is>
-          <t>Deployment patterns; Tool Integration</t>
+          <t>Deployment patterns; Tools</t>
         </is>
       </c>
       <c r="J22" s="16" t="inlineStr">
@@ -1857,14 +1853,8 @@
           <t>Georgi Gerganov</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n">
-        <v>46162</v>
-      </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>Paty Buendia</t>
-        </is>
-      </c>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="16" t="n"/>
       <c r="F24" s="14" t="n">
         <v>46162</v>
       </c>
@@ -1980,9 +1970,7 @@
           <t>NVIDIA</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n">
-        <v>46150</v>
-      </c>
+      <c r="D26" s="6" t="n"/>
       <c r="F26" s="16" t="n">
         <v>2026</v>
       </c>
@@ -1999,7 +1987,7 @@
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>Self‑hosted AI; Implementation; Network Isolation; Infrastructure Security</t>
+          <t>Self‑hosted AI; Architecture Compute; Implementation; Network Isolation; Infrastructure Security</t>
         </is>
       </c>
       <c r="K26" s="16" t="inlineStr">
@@ -2151,14 +2139,8 @@
           <t>Lenovo Press</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n">
-        <v>46157</v>
-      </c>
-      <c r="E29" s="16" t="inlineStr">
-        <is>
-          <t>Paty Buendia</t>
-        </is>
-      </c>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="16" t="n"/>
       <c r="F29" s="7" t="n">
         <v>46054</v>
       </c>
@@ -3681,7 +3663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="17" min="1" max="1"/>
@@ -4244,7 +4226,7 @@
       </c>
       <c r="B33" s="20" t="inlineStr">
         <is>
-          <t>Tool Integration</t>
+          <t>Tool-Ready Endpoints</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr"/>
@@ -4260,7 +4242,7 @@
       </c>
       <c r="B34" s="20" t="inlineStr">
         <is>
-          <t>Tool-Ready Endpoints</t>
+          <t>Coding Agents</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr"/>
@@ -4276,7 +4258,7 @@
       </c>
       <c r="B35" s="20" t="inlineStr">
         <is>
-          <t>Coding Agents</t>
+          <t>Notebook Agents</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr"/>
@@ -4292,7 +4274,7 @@
       </c>
       <c r="B36" s="20" t="inlineStr">
         <is>
-          <t>Notebook Agents</t>
+          <t>Workflow Agents</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr"/>
@@ -4308,7 +4290,7 @@
       </c>
       <c r="B37" s="20" t="inlineStr">
         <is>
-          <t>Workflow Agents</t>
+          <t>Workflow Automation</t>
         </is>
       </c>
       <c r="C37" s="20" t="inlineStr"/>
@@ -4324,7 +4306,7 @@
       </c>
       <c r="B38" s="20" t="inlineStr">
         <is>
-          <t>Workflow Automation</t>
+          <t>Orchestration</t>
         </is>
       </c>
       <c r="C38" s="20" t="inlineStr"/>
@@ -4340,7 +4322,7 @@
       </c>
       <c r="B39" s="20" t="inlineStr">
         <is>
-          <t>Orchestration</t>
+          <t>Triggers</t>
         </is>
       </c>
       <c r="C39" s="20" t="inlineStr"/>
@@ -4356,7 +4338,7 @@
       </c>
       <c r="B40" s="20" t="inlineStr">
         <is>
-          <t>Triggers</t>
+          <t>Retrieval</t>
         </is>
       </c>
       <c r="C40" s="20" t="inlineStr"/>
@@ -4372,7 +4354,7 @@
       </c>
       <c r="B41" s="20" t="inlineStr">
         <is>
-          <t>Retrieval</t>
+          <t>Retrieval Agents</t>
         </is>
       </c>
       <c r="C41" s="20" t="inlineStr"/>
@@ -4388,7 +4370,7 @@
       </c>
       <c r="B42" s="20" t="inlineStr">
         <is>
-          <t>Retrieval Agents</t>
+          <t>Sandbox</t>
         </is>
       </c>
       <c r="C42" s="20" t="inlineStr"/>
@@ -4404,7 +4386,7 @@
       </c>
       <c r="B43" s="20" t="inlineStr">
         <is>
-          <t>Sandbox</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="C43" s="20" t="inlineStr"/>
@@ -4420,7 +4402,7 @@
       </c>
       <c r="B44" s="20" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="C44" s="20" t="inlineStr"/>
@@ -4436,13 +4418,29 @@
       </c>
       <c r="B45" s="20" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
-        </is>
-      </c>
-      <c r="C45" s="20" t="inlineStr"/>
-      <c r="D45" s="20" t="inlineStr"/>
-      <c r="E45" s="20" t="inlineStr"/>
-      <c r="F45" s="20" t="inlineStr"/>
+          <t>FAIR data</t>
+        </is>
+      </c>
+      <c r="C45" s="20" t="inlineStr">
+        <is>
+          <t>Findable, Accessible, Interoperable, Reusable data principles.</t>
+        </is>
+      </c>
+      <c r="D45" s="20" t="inlineStr">
+        <is>
+          <t>EDAM</t>
+        </is>
+      </c>
+      <c r="E45" s="20" t="inlineStr">
+        <is>
+          <t>topic_4012</t>
+        </is>
+      </c>
+      <c r="F45" s="20" t="inlineStr">
+        <is>
+          <t>http://edamontology.org/topic_4012</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="20" t="inlineStr">
@@ -4452,29 +4450,13 @@
       </c>
       <c r="B46" s="20" t="inlineStr">
         <is>
-          <t>FAIR data</t>
-        </is>
-      </c>
-      <c r="C46" s="20" t="inlineStr">
-        <is>
-          <t>Findable, Accessible, Interoperable, Reusable data principles.</t>
-        </is>
-      </c>
-      <c r="D46" s="20" t="inlineStr">
-        <is>
-          <t>EDAM</t>
-        </is>
-      </c>
-      <c r="E46" s="20" t="inlineStr">
-        <is>
-          <t>topic_4012</t>
-        </is>
-      </c>
-      <c r="F46" s="20" t="inlineStr">
-        <is>
-          <t>http://edamontology.org/topic_4012</t>
-        </is>
-      </c>
+          <t>API Integration</t>
+        </is>
+      </c>
+      <c r="C46" s="20" t="inlineStr"/>
+      <c r="D46" s="20" t="inlineStr"/>
+      <c r="E46" s="20" t="inlineStr"/>
+      <c r="F46" s="20" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="20" t="inlineStr">
@@ -4484,7 +4466,7 @@
       </c>
       <c r="B47" s="20" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Model Integration</t>
         </is>
       </c>
       <c r="C47" s="20" t="inlineStr"/>
@@ -4500,7 +4482,7 @@
       </c>
       <c r="B48" s="20" t="inlineStr">
         <is>
-          <t>Model Integration</t>
+          <t>Server Integration</t>
         </is>
       </c>
       <c r="C48" s="20" t="inlineStr"/>
@@ -4516,7 +4498,7 @@
       </c>
       <c r="B49" s="20" t="inlineStr">
         <is>
-          <t>Server Integration</t>
+          <t>Server Patterns</t>
         </is>
       </c>
       <c r="C49" s="20" t="inlineStr"/>
@@ -4527,12 +4509,12 @@
     <row r="50">
       <c r="A50" s="20" t="inlineStr">
         <is>
-          <t>Agentic Features Covered</t>
+          <t>Topic Focus</t>
         </is>
       </c>
       <c r="B50" s="20" t="inlineStr">
         <is>
-          <t>Server Patterns</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="C50" s="20" t="inlineStr"/>
@@ -4548,7 +4530,7 @@
       </c>
       <c r="B51" s="20" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="C51" s="20" t="inlineStr"/>
@@ -4564,13 +4546,29 @@
       </c>
       <c r="B52" s="20" t="inlineStr">
         <is>
-          <t>Security</t>
-        </is>
-      </c>
-      <c r="C52" s="20" t="inlineStr"/>
-      <c r="D52" s="20" t="inlineStr"/>
-      <c r="E52" s="20" t="inlineStr"/>
-      <c r="F52" s="20" t="inlineStr"/>
+          <t>Data governance</t>
+        </is>
+      </c>
+      <c r="C52" s="20" t="inlineStr">
+        <is>
+          <t>Focuses specifically on the technical protocols, access controls, data-line security, and de-identification standards used to protect the integrity, quality, and privacy of information throughout its lifecycle</t>
+        </is>
+      </c>
+      <c r="D52" s="20" t="inlineStr">
+        <is>
+          <t>EDAM</t>
+        </is>
+      </c>
+      <c r="E52" s="20" t="inlineStr">
+        <is>
+          <t>topic_3571</t>
+        </is>
+      </c>
+      <c r="F52" s="20" t="inlineStr">
+        <is>
+          <t>http://edamontology.org/topic_3571</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="20" t="inlineStr">
@@ -4580,29 +4578,17 @@
       </c>
       <c r="B53" s="20" t="inlineStr">
         <is>
-          <t>Data governance</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="C53" s="20" t="inlineStr">
         <is>
-          <t>Focuses specifically on the technical protocols, access controls, data-line security, and de-identification standards used to protect the integrity, quality, and privacy of information throughout its lifecycle</t>
-        </is>
-      </c>
-      <c r="D53" s="20" t="inlineStr">
-        <is>
-          <t>EDAM</t>
-        </is>
-      </c>
-      <c r="E53" s="20" t="inlineStr">
-        <is>
-          <t>topic_3571</t>
-        </is>
-      </c>
-      <c r="F53" s="20" t="inlineStr">
-        <is>
-          <t>http://edamontology.org/topic_3571</t>
-        </is>
-      </c>
+          <t>The overarching organizational policies, compliance frameworks, and capital allocation strategies that dictate how an enterprise manages its broader IT infrastructure, risk tolerances, and vendor choices</t>
+        </is>
+      </c>
+      <c r="D53" s="20" t="inlineStr"/>
+      <c r="E53" s="20" t="inlineStr"/>
+      <c r="F53" s="20" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="20" t="inlineStr">
@@ -4612,14 +4598,10 @@
       </c>
       <c r="B54" s="20" t="inlineStr">
         <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="C54" s="20" t="inlineStr">
-        <is>
-          <t>The overarching organizational policies, compliance frameworks, and capital allocation strategies that dictate how an enterprise manages its broader IT infrastructure, risk tolerances, and vendor choices</t>
-        </is>
-      </c>
+          <t>Implementation</t>
+        </is>
+      </c>
+      <c r="C54" s="20" t="inlineStr"/>
       <c r="D54" s="20" t="inlineStr"/>
       <c r="E54" s="20" t="inlineStr"/>
       <c r="F54" s="20" t="inlineStr"/>
@@ -4632,10 +4614,14 @@
       </c>
       <c r="B55" s="20" t="inlineStr">
         <is>
-          <t>Implementation</t>
-        </is>
-      </c>
-      <c r="C55" s="20" t="inlineStr"/>
+          <t>Deployment</t>
+        </is>
+      </c>
+      <c r="C55" s="20" t="inlineStr">
+        <is>
+          <t>The tactical, hands-on execution of installing, configuring, provisioning, and launching software or hardware systems within a specific operational environment</t>
+        </is>
+      </c>
       <c r="D55" s="20" t="inlineStr"/>
       <c r="E55" s="20" t="inlineStr"/>
       <c r="F55" s="20" t="inlineStr"/>
@@ -4648,17 +4634,25 @@
       </c>
       <c r="B56" s="20" t="inlineStr">
         <is>
-          <t>Deployment</t>
-        </is>
-      </c>
-      <c r="C56" s="20" t="inlineStr">
-        <is>
-          <t>The tactical, hands-on execution of installing, configuring, provisioning, and launching software or hardware systems within a specific operational environment</t>
-        </is>
-      </c>
-      <c r="D56" s="20" t="inlineStr"/>
-      <c r="E56" s="20" t="inlineStr"/>
-      <c r="F56" s="20" t="inlineStr"/>
+          <t>Workflows</t>
+        </is>
+      </c>
+      <c r="C56" s="20" t="inlineStr"/>
+      <c r="D56" s="20" t="inlineStr">
+        <is>
+          <t>EDAM</t>
+        </is>
+      </c>
+      <c r="E56" s="20" t="inlineStr">
+        <is>
+          <t>topic_0769</t>
+        </is>
+      </c>
+      <c r="F56" s="20" t="inlineStr">
+        <is>
+          <t>http://edamontology.org/topic_0769</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="20" t="inlineStr">
@@ -4668,25 +4662,13 @@
       </c>
       <c r="B57" s="20" t="inlineStr">
         <is>
-          <t>Workflows</t>
+          <t>Model selection</t>
         </is>
       </c>
       <c r="C57" s="20" t="inlineStr"/>
-      <c r="D57" s="20" t="inlineStr">
-        <is>
-          <t>EDAM</t>
-        </is>
-      </c>
-      <c r="E57" s="20" t="inlineStr">
-        <is>
-          <t>topic_0769</t>
-        </is>
-      </c>
-      <c r="F57" s="20" t="inlineStr">
-        <is>
-          <t>http://edamontology.org/topic_0769</t>
-        </is>
-      </c>
+      <c r="D57" s="20" t="inlineStr"/>
+      <c r="E57" s="20" t="inlineStr"/>
+      <c r="F57" s="20" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="20" t="inlineStr">
@@ -4696,7 +4678,7 @@
       </c>
       <c r="B58" s="20" t="inlineStr">
         <is>
-          <t>Workflow integration</t>
+          <t>Evaluation</t>
         </is>
       </c>
       <c r="C58" s="20" t="inlineStr"/>
@@ -4712,10 +4694,14 @@
       </c>
       <c r="B59" s="20" t="inlineStr">
         <is>
-          <t>Model selection</t>
-        </is>
-      </c>
-      <c r="C59" s="20" t="inlineStr"/>
+          <t>Architecture Compute</t>
+        </is>
+      </c>
+      <c r="C59" s="20" t="inlineStr">
+        <is>
+          <t>Physical node topologies, hardware constraints, VRAM bounds, and localized compute execution profiles.</t>
+        </is>
+      </c>
       <c r="D59" s="20" t="inlineStr"/>
       <c r="E59" s="20" t="inlineStr"/>
       <c r="F59" s="20" t="inlineStr"/>
@@ -4728,10 +4714,14 @@
       </c>
       <c r="B60" s="20" t="inlineStr">
         <is>
-          <t>Evaluation</t>
-        </is>
-      </c>
-      <c r="C60" s="20" t="inlineStr"/>
+          <t>Network Isolation</t>
+        </is>
+      </c>
+      <c r="C60" s="20" t="inlineStr">
+        <is>
+          <t>Non-egress boundaries, air-gapped artifact staging, localized cloud VPC containers, and firewalled local registries.</t>
+        </is>
+      </c>
       <c r="D60" s="20" t="inlineStr"/>
       <c r="E60" s="20" t="inlineStr"/>
       <c r="F60" s="20" t="inlineStr"/>
@@ -4744,12 +4734,12 @@
       </c>
       <c r="B61" s="20" t="inlineStr">
         <is>
-          <t>Architecture Compute</t>
+          <t>Infrastructure Security</t>
         </is>
       </c>
       <c r="C61" s="20" t="inlineStr">
         <is>
-          <t>Physical node topologies, hardware constraints, VRAM bounds, and localized compute execution profiles.</t>
+          <t>For on-prem LLM deployments, it captures the security of the compute stack as well as the data pipelines</t>
         </is>
       </c>
       <c r="D61" s="20" t="inlineStr"/>
@@ -4764,12 +4754,12 @@
       </c>
       <c r="B62" s="20" t="inlineStr">
         <is>
-          <t>Network Isolation</t>
+          <t>Self‑hosted AI</t>
         </is>
       </c>
       <c r="C62" s="20" t="inlineStr">
         <is>
-          <t>Non-egress boundaries, air-gapped artifact staging, localized cloud VPC containers, and firewalled local registries.</t>
+          <t>Self‑hosted, open‑weights models in contrast to API‑based models like OpenAI, Anthropic, or Gemini</t>
         </is>
       </c>
       <c r="D62" s="20" t="inlineStr"/>
@@ -4784,17 +4774,29 @@
       </c>
       <c r="B63" s="20" t="inlineStr">
         <is>
-          <t>Infrastructure Security</t>
+          <t>Data Protection</t>
         </is>
       </c>
       <c r="C63" s="20" t="inlineStr">
         <is>
-          <t>For on-prem LLM deployments, it captures the security of the compute stack as well as the data pipelines</t>
-        </is>
-      </c>
-      <c r="D63" s="20" t="inlineStr"/>
-      <c r="E63" s="20" t="inlineStr"/>
-      <c r="F63" s="20" t="inlineStr"/>
+          <t>Safeguarding sensitive data specifically. Distinct from the broader Security term.</t>
+        </is>
+      </c>
+      <c r="D63" s="20" t="inlineStr">
+        <is>
+          <t>EDAM</t>
+        </is>
+      </c>
+      <c r="E63" s="20" t="inlineStr">
+        <is>
+          <t>topic_4044</t>
+        </is>
+      </c>
+      <c r="F63" s="20" t="inlineStr">
+        <is>
+          <t>http://edamontology.org/topic_4044</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="20" t="inlineStr">
@@ -4804,17 +4806,29 @@
       </c>
       <c r="B64" s="20" t="inlineStr">
         <is>
-          <t>Self‑hosted AI</t>
+          <t>FAIR data</t>
         </is>
       </c>
       <c r="C64" s="20" t="inlineStr">
         <is>
-          <t>Self‑hosted, open‑weights models in contrast to API‑based models like OpenAI, Anthropic, or Gemini</t>
-        </is>
-      </c>
-      <c r="D64" s="20" t="inlineStr"/>
-      <c r="E64" s="20" t="inlineStr"/>
-      <c r="F64" s="20" t="inlineStr"/>
+          <t>Findable, Accessible, Interoperable, Reusable data principles.</t>
+        </is>
+      </c>
+      <c r="D64" s="20" t="inlineStr">
+        <is>
+          <t>EDAM</t>
+        </is>
+      </c>
+      <c r="E64" s="20" t="inlineStr">
+        <is>
+          <t>topic_4012</t>
+        </is>
+      </c>
+      <c r="F64" s="20" t="inlineStr">
+        <is>
+          <t>http://edamontology.org/topic_4012</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="20" t="inlineStr">
@@ -4824,14 +4838,10 @@
       </c>
       <c r="B65" s="20" t="inlineStr">
         <is>
-          <t>Data Protection</t>
-        </is>
-      </c>
-      <c r="C65" s="20" t="inlineStr">
-        <is>
-          <t>Safeguarding sensitive data specifically. Distinct from the broader Security term.</t>
-        </is>
-      </c>
+          <t>Data quality management</t>
+        </is>
+      </c>
+      <c r="C65" s="20" t="inlineStr"/>
       <c r="D65" s="20" t="inlineStr">
         <is>
           <t>EDAM</t>
@@ -4839,12 +4849,12 @@
       </c>
       <c r="E65" s="20" t="inlineStr">
         <is>
-          <t>topic_4044</t>
+          <t>topic_3572</t>
         </is>
       </c>
       <c r="F65" s="20" t="inlineStr">
         <is>
-          <t>http://edamontology.org/topic_4044</t>
+          <t>http://edamontology.org/topic_3572</t>
         </is>
       </c>
     </row>
@@ -4856,14 +4866,10 @@
       </c>
       <c r="B66" s="20" t="inlineStr">
         <is>
-          <t>FAIR data</t>
-        </is>
-      </c>
-      <c r="C66" s="20" t="inlineStr">
-        <is>
-          <t>Findable, Accessible, Interoperable, Reusable data principles.</t>
-        </is>
-      </c>
+          <t>Data curation and archival</t>
+        </is>
+      </c>
+      <c r="C66" s="20" t="inlineStr"/>
       <c r="D66" s="20" t="inlineStr">
         <is>
           <t>EDAM</t>
@@ -4871,12 +4877,12 @@
       </c>
       <c r="E66" s="20" t="inlineStr">
         <is>
-          <t>topic_4012</t>
+          <t>topic_0219</t>
         </is>
       </c>
       <c r="F66" s="20" t="inlineStr">
         <is>
-          <t>http://edamontology.org/topic_4012</t>
+          <t>http://edamontology.org/topic_0219</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4894,7 @@
       </c>
       <c r="B67" s="20" t="inlineStr">
         <is>
-          <t>Data quality management</t>
+          <t>Data integration and warehousing</t>
         </is>
       </c>
       <c r="C67" s="20" t="inlineStr"/>
@@ -4899,12 +4905,12 @@
       </c>
       <c r="E67" s="20" t="inlineStr">
         <is>
-          <t>topic_3572</t>
+          <t>topic_3366</t>
         </is>
       </c>
       <c r="F67" s="20" t="inlineStr">
         <is>
-          <t>http://edamontology.org/topic_3572</t>
+          <t>http://edamontology.org/topic_3366</t>
         </is>
       </c>
     </row>
@@ -4916,7 +4922,7 @@
       </c>
       <c r="B68" s="20" t="inlineStr">
         <is>
-          <t>Data curation and archival</t>
+          <t>Data architecture, analysis and design</t>
         </is>
       </c>
       <c r="C68" s="20" t="inlineStr"/>
@@ -4927,12 +4933,12 @@
       </c>
       <c r="E68" s="20" t="inlineStr">
         <is>
-          <t>topic_0219</t>
+          <t>topic_3365</t>
         </is>
       </c>
       <c r="F68" s="20" t="inlineStr">
         <is>
-          <t>http://edamontology.org/topic_0219</t>
+          <t>http://edamontology.org/topic_3365</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4950,7 @@
       </c>
       <c r="B69" s="20" t="inlineStr">
         <is>
-          <t>Data integration and warehousing</t>
+          <t>Data identity and mapping</t>
         </is>
       </c>
       <c r="C69" s="20" t="inlineStr"/>
@@ -4955,12 +4961,12 @@
       </c>
       <c r="E69" s="20" t="inlineStr">
         <is>
-          <t>topic_3366</t>
+          <t>topic_3345</t>
         </is>
       </c>
       <c r="F69" s="20" t="inlineStr">
         <is>
-          <t>http://edamontology.org/topic_3366</t>
+          <t>http://edamontology.org/topic_3345</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4978,7 @@
       </c>
       <c r="B70" s="20" t="inlineStr">
         <is>
-          <t>Data architecture, analysis and design</t>
+          <t>Data rescue</t>
         </is>
       </c>
       <c r="C70" s="20" t="inlineStr"/>
@@ -4983,12 +4989,12 @@
       </c>
       <c r="E70" s="20" t="inlineStr">
         <is>
-          <t>topic_3365</t>
+          <t>topic_4011</t>
         </is>
       </c>
       <c r="F70" s="20" t="inlineStr">
         <is>
-          <t>http://edamontology.org/topic_3365</t>
+          <t>http://edamontology.org/topic_4011</t>
         </is>
       </c>
     </row>
@@ -5000,25 +5006,21 @@
       </c>
       <c r="B71" s="20" t="inlineStr">
         <is>
-          <t>Data identity and mapping</t>
-        </is>
-      </c>
-      <c r="C71" s="20" t="inlineStr"/>
+          <t>Valid and Reliable</t>
+        </is>
+      </c>
+      <c r="C71" s="20" t="inlineStr">
+        <is>
+          <t>NIST AI RMF trustworthy-AI characteristic.</t>
+        </is>
+      </c>
       <c r="D71" s="20" t="inlineStr">
         <is>
-          <t>EDAM</t>
-        </is>
-      </c>
-      <c r="E71" s="20" t="inlineStr">
-        <is>
-          <t>topic_3345</t>
-        </is>
-      </c>
-      <c r="F71" s="20" t="inlineStr">
-        <is>
-          <t>http://edamontology.org/topic_3345</t>
-        </is>
-      </c>
+          <t>NIST-AI-RMF</t>
+        </is>
+      </c>
+      <c r="E71" s="20" t="inlineStr"/>
+      <c r="F71" s="20" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="20" t="inlineStr">
@@ -5028,25 +5030,21 @@
       </c>
       <c r="B72" s="20" t="inlineStr">
         <is>
-          <t>Data rescue</t>
-        </is>
-      </c>
-      <c r="C72" s="20" t="inlineStr"/>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="C72" s="20" t="inlineStr">
+        <is>
+          <t>NIST AI RMF trustworthy-AI characteristic.</t>
+        </is>
+      </c>
       <c r="D72" s="20" t="inlineStr">
         <is>
-          <t>EDAM</t>
-        </is>
-      </c>
-      <c r="E72" s="20" t="inlineStr">
-        <is>
-          <t>topic_4011</t>
-        </is>
-      </c>
-      <c r="F72" s="20" t="inlineStr">
-        <is>
-          <t>http://edamontology.org/topic_4011</t>
-        </is>
-      </c>
+          <t>NIST-AI-RMF</t>
+        </is>
+      </c>
+      <c r="E72" s="20" t="inlineStr"/>
+      <c r="F72" s="20" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="20" t="inlineStr">
@@ -5056,7 +5054,7 @@
       </c>
       <c r="B73" s="20" t="inlineStr">
         <is>
-          <t>Valid and Reliable</t>
+          <t>Secure and Resilient</t>
         </is>
       </c>
       <c r="C73" s="20" t="inlineStr">
@@ -5080,7 +5078,7 @@
       </c>
       <c r="B74" s="20" t="inlineStr">
         <is>
-          <t>Safe</t>
+          <t>Accountable and Transparent</t>
         </is>
       </c>
       <c r="C74" s="20" t="inlineStr">
@@ -5104,7 +5102,7 @@
       </c>
       <c r="B75" s="20" t="inlineStr">
         <is>
-          <t>Secure and Resilient</t>
+          <t>Explainable and Interpretable</t>
         </is>
       </c>
       <c r="C75" s="20" t="inlineStr">
@@ -5128,7 +5126,7 @@
       </c>
       <c r="B76" s="20" t="inlineStr">
         <is>
-          <t>Accountable and Transparent</t>
+          <t>Privacy-Enhanced</t>
         </is>
       </c>
       <c r="C76" s="20" t="inlineStr">
@@ -5152,12 +5150,12 @@
       </c>
       <c r="B77" s="20" t="inlineStr">
         <is>
-          <t>Explainable and Interpretable</t>
+          <t>Fair (harmful bias managed)</t>
         </is>
       </c>
       <c r="C77" s="20" t="inlineStr">
         <is>
-          <t>NIST AI RMF trustworthy-AI characteristic.</t>
+          <t>NIST AI RMF trustworthy-AI characteristic: algorithmic non-discrimination. NOT the same as 'FAIR data'.</t>
         </is>
       </c>
       <c r="D77" s="20" t="inlineStr">
@@ -5171,48 +5169,32 @@
     <row r="78">
       <c r="A78" s="20" t="inlineStr">
         <is>
-          <t>Topic Focus</t>
+          <t>Maturity Level</t>
         </is>
       </c>
       <c r="B78" s="20" t="inlineStr">
         <is>
-          <t>Privacy-Enhanced</t>
-        </is>
-      </c>
-      <c r="C78" s="20" t="inlineStr">
-        <is>
-          <t>NIST AI RMF trustworthy-AI characteristic.</t>
-        </is>
-      </c>
-      <c r="D78" s="20" t="inlineStr">
-        <is>
-          <t>NIST-AI-RMF</t>
-        </is>
-      </c>
+          <t>Emerging</t>
+        </is>
+      </c>
+      <c r="C78" s="20" t="inlineStr"/>
+      <c r="D78" s="20" t="inlineStr"/>
       <c r="E78" s="20" t="inlineStr"/>
       <c r="F78" s="20" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="20" t="inlineStr">
         <is>
-          <t>Topic Focus</t>
+          <t>Maturity Level</t>
         </is>
       </c>
       <c r="B79" s="20" t="inlineStr">
         <is>
-          <t>Fair (harmful bias managed)</t>
-        </is>
-      </c>
-      <c r="C79" s="20" t="inlineStr">
-        <is>
-          <t>NIST AI RMF trustworthy-AI characteristic: algorithmic non-discrimination. NOT the same as 'FAIR data'.</t>
-        </is>
-      </c>
-      <c r="D79" s="20" t="inlineStr">
-        <is>
-          <t>NIST-AI-RMF</t>
-        </is>
-      </c>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="C79" s="20" t="inlineStr"/>
+      <c r="D79" s="20" t="inlineStr"/>
       <c r="E79" s="20" t="inlineStr"/>
       <c r="F79" s="20" t="inlineStr"/>
     </row>
@@ -5224,7 +5206,7 @@
       </c>
       <c r="B80" s="20" t="inlineStr">
         <is>
-          <t>Emerging</t>
+          <t>Mature</t>
         </is>
       </c>
       <c r="C80" s="20" t="inlineStr"/>
@@ -5240,45 +5222,13 @@
       </c>
       <c r="B81" s="20" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>Deprecated</t>
         </is>
       </c>
       <c r="C81" s="20" t="inlineStr"/>
       <c r="D81" s="20" t="inlineStr"/>
       <c r="E81" s="20" t="inlineStr"/>
       <c r="F81" s="20" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="20" t="inlineStr">
-        <is>
-          <t>Maturity Level</t>
-        </is>
-      </c>
-      <c r="B82" s="20" t="inlineStr">
-        <is>
-          <t>Mature</t>
-        </is>
-      </c>
-      <c r="C82" s="20" t="inlineStr"/>
-      <c r="D82" s="20" t="inlineStr"/>
-      <c r="E82" s="20" t="inlineStr"/>
-      <c r="F82" s="20" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="20" t="inlineStr">
-        <is>
-          <t>Maturity Level</t>
-        </is>
-      </c>
-      <c r="B83" s="20" t="inlineStr">
-        <is>
-          <t>Deprecated</t>
-        </is>
-      </c>
-      <c r="C83" s="20" t="inlineStr"/>
-      <c r="D83" s="20" t="inlineStr"/>
-      <c r="E83" s="20" t="inlineStr"/>
-      <c r="F83" s="20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/VANTAGE-Technology-Radar.xlsx
+++ b/data/VANTAGE-Technology-Radar.xlsx
@@ -4166,9 +4166,21 @@
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr"/>
-      <c r="D29" s="20" t="inlineStr"/>
-      <c r="E29" s="20" t="inlineStr"/>
-      <c r="F29" s="20" t="inlineStr"/>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>ACM-CCS</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>Software and its engineering~Software verification and validation~Software testing and debugging</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="inlineStr">
+        <is>
+          <t>https://dl.acm.org/ccs</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="20" t="inlineStr">
@@ -4342,9 +4354,21 @@
         </is>
       </c>
       <c r="C40" s="20" t="inlineStr"/>
-      <c r="D40" s="20" t="inlineStr"/>
-      <c r="E40" s="20" t="inlineStr"/>
-      <c r="F40" s="20" t="inlineStr"/>
+      <c r="D40" s="20" t="inlineStr">
+        <is>
+          <t>ACM-CCS</t>
+        </is>
+      </c>
+      <c r="E40" s="20" t="inlineStr">
+        <is>
+          <t>Information systems~Information retrieval</t>
+        </is>
+      </c>
+      <c r="F40" s="20" t="inlineStr">
+        <is>
+          <t>https://dl.acm.org/ccs</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="20" t="inlineStr">
@@ -4358,9 +4382,21 @@
         </is>
       </c>
       <c r="C41" s="20" t="inlineStr"/>
-      <c r="D41" s="20" t="inlineStr"/>
-      <c r="E41" s="20" t="inlineStr"/>
-      <c r="F41" s="20" t="inlineStr"/>
+      <c r="D41" s="20" t="inlineStr">
+        <is>
+          <t>ACM-CCS</t>
+        </is>
+      </c>
+      <c r="E41" s="20" t="inlineStr">
+        <is>
+          <t>Information systems~Information retrieval</t>
+        </is>
+      </c>
+      <c r="F41" s="20" t="inlineStr">
+        <is>
+          <t>https://dl.acm.org/ccs</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="20" t="inlineStr">
@@ -4406,9 +4442,21 @@
         </is>
       </c>
       <c r="C44" s="20" t="inlineStr"/>
-      <c r="D44" s="20" t="inlineStr"/>
-      <c r="E44" s="20" t="inlineStr"/>
-      <c r="F44" s="20" t="inlineStr"/>
+      <c r="D44" s="20" t="inlineStr">
+        <is>
+          <t>ACM-CCS</t>
+        </is>
+      </c>
+      <c r="E44" s="20" t="inlineStr">
+        <is>
+          <t>Security and privacy</t>
+        </is>
+      </c>
+      <c r="F44" s="20" t="inlineStr">
+        <is>
+          <t>https://dl.acm.org/ccs</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="20" t="inlineStr">
@@ -4518,9 +4566,21 @@
         </is>
       </c>
       <c r="C50" s="20" t="inlineStr"/>
-      <c r="D50" s="20" t="inlineStr"/>
-      <c r="E50" s="20" t="inlineStr"/>
-      <c r="F50" s="20" t="inlineStr"/>
+      <c r="D50" s="20" t="inlineStr">
+        <is>
+          <t>ACM-CCS</t>
+        </is>
+      </c>
+      <c r="E50" s="20" t="inlineStr">
+        <is>
+          <t>Computer systems organization~Architectures</t>
+        </is>
+      </c>
+      <c r="F50" s="20" t="inlineStr">
+        <is>
+          <t>https://dl.acm.org/ccs</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="20" t="inlineStr">
@@ -4534,9 +4594,21 @@
         </is>
       </c>
       <c r="C51" s="20" t="inlineStr"/>
-      <c r="D51" s="20" t="inlineStr"/>
-      <c r="E51" s="20" t="inlineStr"/>
-      <c r="F51" s="20" t="inlineStr"/>
+      <c r="D51" s="20" t="inlineStr">
+        <is>
+          <t>ACM-CCS</t>
+        </is>
+      </c>
+      <c r="E51" s="20" t="inlineStr">
+        <is>
+          <t>Security and privacy</t>
+        </is>
+      </c>
+      <c r="F51" s="20" t="inlineStr">
+        <is>
+          <t>https://dl.acm.org/ccs</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="20" t="inlineStr">
@@ -4682,9 +4754,21 @@
         </is>
       </c>
       <c r="C58" s="20" t="inlineStr"/>
-      <c r="D58" s="20" t="inlineStr"/>
-      <c r="E58" s="20" t="inlineStr"/>
-      <c r="F58" s="20" t="inlineStr"/>
+      <c r="D58" s="20" t="inlineStr">
+        <is>
+          <t>ACM-CCS</t>
+        </is>
+      </c>
+      <c r="E58" s="20" t="inlineStr">
+        <is>
+          <t>Software and its engineering~Software verification and validation~Software testing and debugging</t>
+        </is>
+      </c>
+      <c r="F58" s="20" t="inlineStr">
+        <is>
+          <t>https://dl.acm.org/ccs</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="20" t="inlineStr">
@@ -5241,7 +5325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="17" min="1" max="1"/>
@@ -5332,6 +5416,33 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ACM-CCS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ACM Computing Classification System (CCS 2012)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://dl.acm.org/ccs</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Cited by category path text (e.g. "Computer systems organization~Architectures"), not a numeric ID a human needs to look up -- confirmed against real paper citations. General computing/software-engineering taxonomy, not agentic-AI-specific -- predates MCP, agent frameworks, and tool-calling entirely, so it backs general CS terms (Architecture, Security, Evaluation, Retrieval) but not agent-specific ones (MCP, Hooks, Skills, Orchestration, ...). Path spellings below are from established domain knowledge, not a live verified fetch (dl.acm.org blocked automated access) -- worth spot-checking in a browser before treating as fully authoritative.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/VANTAGE-Technology-Radar.xlsx
+++ b/data/VANTAGE-Technology-Radar.xlsx
@@ -1987,7 +1987,7 @@
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>Self‑hosted AI; Architecture Compute; Implementation; Network Isolation; Infrastructure Security</t>
+          <t>Self‑hosted AI; Compute Infrastructure; Implementation; Network Isolation; Infrastructure Security</t>
         </is>
       </c>
       <c r="K26" s="16" t="inlineStr">
@@ -4674,9 +4674,21 @@
         </is>
       </c>
       <c r="C54" s="20" t="inlineStr"/>
-      <c r="D54" s="20" t="inlineStr"/>
-      <c r="E54" s="20" t="inlineStr"/>
-      <c r="F54" s="20" t="inlineStr"/>
+      <c r="D54" s="20" t="inlineStr">
+        <is>
+          <t>ACM-CCS</t>
+        </is>
+      </c>
+      <c r="E54" s="20" t="inlineStr">
+        <is>
+          <t>Software and its engineering~Software creation and management</t>
+        </is>
+      </c>
+      <c r="F54" s="20" t="inlineStr">
+        <is>
+          <t>https://dl.acm.org/ccs</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="20" t="inlineStr">
@@ -4694,9 +4706,21 @@
           <t>The tactical, hands-on execution of installing, configuring, provisioning, and launching software or hardware systems within a specific operational environment</t>
         </is>
       </c>
-      <c r="D55" s="20" t="inlineStr"/>
-      <c r="E55" s="20" t="inlineStr"/>
-      <c r="F55" s="20" t="inlineStr"/>
+      <c r="D55" s="20" t="inlineStr">
+        <is>
+          <t>NIST-AI-RMF</t>
+        </is>
+      </c>
+      <c r="E55" s="20" t="inlineStr">
+        <is>
+          <t>AI lifecycle stage: Deploy</t>
+        </is>
+      </c>
+      <c r="F55" s="20" t="inlineStr">
+        <is>
+          <t>https://nvlpubs.nist.gov/nistpubs/ai/NIST.AI.100-1.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="20" t="inlineStr">
@@ -4778,7 +4802,7 @@
       </c>
       <c r="B59" s="20" t="inlineStr">
         <is>
-          <t>Architecture Compute</t>
+          <t>Compute Infrastructure</t>
         </is>
       </c>
       <c r="C59" s="20" t="inlineStr">
@@ -5412,32 +5436,32 @@
       </c>
       <c r="E3" s="20" t="inlineStr">
         <is>
-          <t>Optional secondary axis: the seven trustworthy-AI characteristics. Document-based, so individual characteristics have no per-term URIs. WARNING: NIST's 'Fair (harmful bias managed)' concerns algorithmic non-discrimination and is UNRELATED to EDAM's 'FAIR data' (Findable / Accessible / Interoperable / Reusable data principles) despite sharing the word - do not conflate the two.</t>
+          <t>Optional secondary axis: the seven trustworthy-AI characteristics. Document-based, so individual characteristics have no per-term URIs. WARNING: NIST's 'Fair (harmful bias managed)' concerns algorithmic non-discrimination and is UNRELATED to EDAM's 'FAIR data' (Findable / Accessible / Interoperable / Reusable data principles) despite sharing the word - do not conflate the two. Also defines an AI lifecycle with named stages (plan, collect/process, build, verify, deploy, operate) -- cited here as e.g. "AI lifecycle stage: Deploy", distinct from the seven trustworthy-AI characteristics.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>ACM-CCS</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>ACM Computing Classification System (CCS 2012)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
         <is>
           <t>https://dl.acm.org/ccs</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="0" t="inlineStr">
         <is>
           <t>Cited by category path text (e.g. "Computer systems organization~Architectures"), not a numeric ID a human needs to look up -- confirmed against real paper citations. General computing/software-engineering taxonomy, not agentic-AI-specific -- predates MCP, agent frameworks, and tool-calling entirely, so it backs general CS terms (Architecture, Security, Evaluation, Retrieval) but not agent-specific ones (MCP, Hooks, Skills, Orchestration, ...). Path spellings below are from established domain knowledge, not a live verified fetch (dl.acm.org blocked automated access) -- worth spot-checking in a browser before treating as fully authoritative.</t>
         </is>

--- a/data/VANTAGE-Technology-Radar.xlsx
+++ b/data/VANTAGE-Technology-Radar.xlsx
@@ -3718,9 +3718,21 @@
         </is>
       </c>
       <c r="C2" s="20" t="inlineStr"/>
-      <c r="D2" s="20" t="inlineStr"/>
-      <c r="E2" s="20" t="inlineStr"/>
-      <c r="F2" s="20" t="inlineStr"/>
+      <c r="D2" s="20" t="inlineStr">
+        <is>
+          <t>Schema.org</t>
+        </is>
+      </c>
+      <c r="E2" s="20" t="inlineStr">
+        <is>
+          <t>schema:TechArticle</t>
+        </is>
+      </c>
+      <c r="F2" s="20" t="inlineStr">
+        <is>
+          <t>https://schema.org/TechArticle</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="inlineStr">
@@ -3734,9 +3746,21 @@
         </is>
       </c>
       <c r="C3" s="20" t="inlineStr"/>
-      <c r="D3" s="20" t="inlineStr"/>
-      <c r="E3" s="20" t="inlineStr"/>
-      <c r="F3" s="20" t="inlineStr"/>
+      <c r="D3" s="20" t="inlineStr">
+        <is>
+          <t>Schema.org</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="inlineStr">
+        <is>
+          <t>schema:APIReference</t>
+        </is>
+      </c>
+      <c r="F3" s="20" t="inlineStr">
+        <is>
+          <t>https://schema.org/APIReference</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="inlineStr">
@@ -3750,9 +3774,21 @@
         </is>
       </c>
       <c r="C4" s="20" t="inlineStr"/>
-      <c r="D4" s="20" t="inlineStr"/>
-      <c r="E4" s="20" t="inlineStr"/>
-      <c r="F4" s="20" t="inlineStr"/>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>Schema.org</t>
+        </is>
+      </c>
+      <c r="E4" s="20" t="inlineStr">
+        <is>
+          <t>schema:TechArticle</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="inlineStr">
+        <is>
+          <t>https://schema.org/TechArticle</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="inlineStr">
@@ -3770,9 +3806,21 @@
           <t>Vendor or organization technical whitepaper.</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr"/>
-      <c r="E5" s="20" t="inlineStr"/>
-      <c r="F5" s="20" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>Schema.org</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>schema:TechArticle</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>https://schema.org/TechArticle</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
@@ -3790,9 +3838,21 @@
           <t>Peer-reviewed publication or preprint. Distinct from a vendor Whitepaper.</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>Schema.org</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>schema:ScholarlyArticle</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>https://schema.org/ScholarlyArticle</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="inlineStr">
@@ -3806,9 +3866,21 @@
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>Schema.org</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>schema:TechArticle</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>https://schema.org/TechArticle</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
@@ -3822,9 +3894,21 @@
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr"/>
-      <c r="D8" s="20" t="inlineStr"/>
-      <c r="E8" s="20" t="inlineStr"/>
-      <c r="F8" s="20" t="inlineStr"/>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>Schema.org</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>schema:TechArticle</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>https://schema.org/TechArticle</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="inlineStr">
@@ -3838,9 +3922,21 @@
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr"/>
-      <c r="D9" s="20" t="inlineStr"/>
-      <c r="E9" s="20" t="inlineStr"/>
-      <c r="F9" s="20" t="inlineStr"/>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>Schema.org</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>schema:TechArticle</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>https://schema.org/TechArticle</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
@@ -3918,9 +4014,21 @@
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr"/>
-      <c r="D14" s="20" t="inlineStr"/>
-      <c r="E14" s="20" t="inlineStr"/>
-      <c r="F14" s="20" t="inlineStr"/>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>Schema.org</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>schema:SoftwareSourceCode</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>https://schema.org/SoftwareSourceCode</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="20" t="inlineStr">
@@ -3938,9 +4046,21 @@
           <t>A curated collection of benchmarks or comparison studies.</t>
         </is>
       </c>
-      <c r="D15" s="20" t="inlineStr"/>
-      <c r="E15" s="20" t="inlineStr"/>
-      <c r="F15" s="20" t="inlineStr"/>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>Schema.org</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>schema:Dataset</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>https://schema.org/Dataset</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
@@ -3970,9 +4090,21 @@
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr"/>
-      <c r="D17" s="20" t="inlineStr"/>
-      <c r="E17" s="20" t="inlineStr"/>
-      <c r="F17" s="20" t="inlineStr"/>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>Schema.org</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>schema:BlogPosting</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>https://schema.org/BlogPosting</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
@@ -3986,9 +4118,21 @@
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr"/>
-      <c r="D18" s="20" t="inlineStr"/>
-      <c r="E18" s="20" t="inlineStr"/>
-      <c r="F18" s="20" t="inlineStr"/>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>Schema.org</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>schema:SoftwareSourceCode</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>https://schema.org/SoftwareSourceCode</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="20" t="inlineStr">
@@ -4002,9 +4146,21 @@
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr"/>
-      <c r="D19" s="20" t="inlineStr"/>
-      <c r="E19" s="20" t="inlineStr"/>
-      <c r="F19" s="20" t="inlineStr"/>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>Schema.org</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>schema:TechArticle</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>https://schema.org/TechArticle</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
@@ -5349,7 +5505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="17" min="1" max="1"/>
@@ -5467,6 +5623,33 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Schema.org</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Schema.org (CreativeWork hierarchy)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://schema.org/CreativeWork</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Universal web-metadata vocabulary. Exact-type matches applied directly (e.g. APIReference, BlogPosting, ScholarlyArticle, SoftwareSourceCode, Dataset). For highly specific AI-radar terms with no exact schema.org type, the broader parent type is applied instead (e.g. several terms map to TechArticle) -- this is schema.org's own intended usage pattern (broad type + a custom category property), not a forced fit, but it means several distinct Resource Type terms intentionally share one Ontology ID here, unlike EDAM/ACM-CCS/NIST-AI-RMF where each backed term has its own distinct match.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/VANTAGE-Technology-Radar.xlsx
+++ b/data/VANTAGE-Technology-Radar.xlsx
@@ -3663,7 +3663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="17" min="1" max="1"/>
@@ -4065,12 +4065,12 @@
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>Resource Type</t>
+          <t>Agentic Features Covered</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Tutorial</t>
+          <t>Hooks</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr"/>
@@ -4081,86 +4081,54 @@
     <row r="17">
       <c r="A17" s="20" t="inlineStr">
         <is>
-          <t>Resource Type</t>
+          <t>Agentic Features Covered</t>
         </is>
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>Blog Post</t>
+          <t>Skills</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr"/>
-      <c r="D17" s="20" t="inlineStr">
-        <is>
-          <t>Schema.org</t>
-        </is>
-      </c>
-      <c r="E17" s="20" t="inlineStr">
-        <is>
-          <t>schema:BlogPosting</t>
-        </is>
-      </c>
-      <c r="F17" s="20" t="inlineStr">
-        <is>
-          <t>https://schema.org/BlogPosting</t>
-        </is>
-      </c>
+      <c r="D17" s="20" t="inlineStr"/>
+      <c r="E17" s="20" t="inlineStr"/>
+      <c r="F17" s="20" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>Resource Type</t>
+          <t>Agentic Features Covered</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Example Repo</t>
-        </is>
-      </c>
-      <c r="C18" s="20" t="inlineStr"/>
-      <c r="D18" s="20" t="inlineStr">
-        <is>
-          <t>Schema.org</t>
-        </is>
-      </c>
-      <c r="E18" s="20" t="inlineStr">
-        <is>
-          <t>schema:SoftwareSourceCode</t>
-        </is>
-      </c>
-      <c r="F18" s="20" t="inlineStr">
-        <is>
-          <t>https://schema.org/SoftwareSourceCode</t>
-        </is>
-      </c>
+          <t>MCP</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>Model Context Protocol.</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr"/>
+      <c r="E18" s="20" t="inlineStr"/>
+      <c r="F18" s="20" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="20" t="inlineStr">
         <is>
-          <t>Resource Type</t>
+          <t>Agentic Features Covered</t>
         </is>
       </c>
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>Architecture Pattern</t>
+          <t>Agent frameworks</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr"/>
-      <c r="D19" s="20" t="inlineStr">
-        <is>
-          <t>Schema.org</t>
-        </is>
-      </c>
-      <c r="E19" s="20" t="inlineStr">
-        <is>
-          <t>schema:TechArticle</t>
-        </is>
-      </c>
-      <c r="F19" s="20" t="inlineStr">
-        <is>
-          <t>https://schema.org/TechArticle</t>
-        </is>
-      </c>
+      <c r="D19" s="20" t="inlineStr"/>
+      <c r="E19" s="20" t="inlineStr"/>
+      <c r="F19" s="20" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
@@ -4170,7 +4138,7 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Hooks</t>
+          <t>Agent Patterns</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr"/>
@@ -4186,7 +4154,7 @@
       </c>
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>Skills</t>
+          <t>Multi-Agent Patterns</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr"/>
@@ -4202,14 +4170,10 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>MCP</t>
-        </is>
-      </c>
-      <c r="C22" s="20" t="inlineStr">
-        <is>
-          <t>Model Context Protocol.</t>
-        </is>
-      </c>
+          <t>Context window management</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr"/>
       <c r="D22" s="20" t="inlineStr"/>
       <c r="E22" s="20" t="inlineStr"/>
       <c r="F22" s="20" t="inlineStr"/>
@@ -4222,7 +4186,7 @@
       </c>
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>Agent frameworks</t>
+          <t>Deployment patterns</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr"/>
@@ -4238,7 +4202,7 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Agent Patterns</t>
+          <t>Safety / guardrails</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr"/>
@@ -4254,13 +4218,25 @@
       </c>
       <c r="B25" s="20" t="inlineStr">
         <is>
-          <t>Multi-Agent Patterns</t>
+          <t>Evaluation / testing</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr"/>
-      <c r="D25" s="20" t="inlineStr"/>
-      <c r="E25" s="20" t="inlineStr"/>
-      <c r="F25" s="20" t="inlineStr"/>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>ACM-CCS</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>Software and its engineering~Software verification and validation~Software testing and debugging</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>https://dl.acm.org/ccs</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
@@ -4270,7 +4246,7 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Context window management</t>
+          <t>Risk Controls</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr"/>
@@ -4286,7 +4262,7 @@
       </c>
       <c r="B27" s="20" t="inlineStr">
         <is>
-          <t>Deployment patterns</t>
+          <t>Safe Tool Use</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr"/>
@@ -4302,7 +4278,7 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Safety / guardrails</t>
+          <t>Tools</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr"/>
@@ -4318,25 +4294,13 @@
       </c>
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>Evaluation / testing</t>
+          <t>Tool-Ready Endpoints</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr"/>
-      <c r="D29" s="20" t="inlineStr">
-        <is>
-          <t>ACM-CCS</t>
-        </is>
-      </c>
-      <c r="E29" s="20" t="inlineStr">
-        <is>
-          <t>Software and its engineering~Software verification and validation~Software testing and debugging</t>
-        </is>
-      </c>
-      <c r="F29" s="20" t="inlineStr">
-        <is>
-          <t>https://dl.acm.org/ccs</t>
-        </is>
-      </c>
+      <c r="D29" s="20" t="inlineStr"/>
+      <c r="E29" s="20" t="inlineStr"/>
+      <c r="F29" s="20" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="20" t="inlineStr">
@@ -4346,7 +4310,7 @@
       </c>
       <c r="B30" s="20" t="inlineStr">
         <is>
-          <t>Risk Controls</t>
+          <t>Coding Agents</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr"/>
@@ -4362,7 +4326,7 @@
       </c>
       <c r="B31" s="20" t="inlineStr">
         <is>
-          <t>Safe Tool Use</t>
+          <t>Notebook Agents</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr"/>
@@ -4378,7 +4342,7 @@
       </c>
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t>Tools</t>
+          <t>Workflow Agents</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr"/>
@@ -4394,7 +4358,7 @@
       </c>
       <c r="B33" s="20" t="inlineStr">
         <is>
-          <t>Tool-Ready Endpoints</t>
+          <t>Workflow Automation</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr"/>
@@ -4410,7 +4374,7 @@
       </c>
       <c r="B34" s="20" t="inlineStr">
         <is>
-          <t>Coding Agents</t>
+          <t>Orchestration</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr"/>
@@ -4426,7 +4390,7 @@
       </c>
       <c r="B35" s="20" t="inlineStr">
         <is>
-          <t>Notebook Agents</t>
+          <t>Triggers</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr"/>
@@ -4442,13 +4406,25 @@
       </c>
       <c r="B36" s="20" t="inlineStr">
         <is>
-          <t>Workflow Agents</t>
+          <t>Retrieval</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr"/>
-      <c r="D36" s="20" t="inlineStr"/>
-      <c r="E36" s="20" t="inlineStr"/>
-      <c r="F36" s="20" t="inlineStr"/>
+      <c r="D36" s="20" t="inlineStr">
+        <is>
+          <t>ACM-CCS</t>
+        </is>
+      </c>
+      <c r="E36" s="20" t="inlineStr">
+        <is>
+          <t>Information systems~Information retrieval</t>
+        </is>
+      </c>
+      <c r="F36" s="20" t="inlineStr">
+        <is>
+          <t>https://dl.acm.org/ccs</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="20" t="inlineStr">
@@ -4458,13 +4434,25 @@
       </c>
       <c r="B37" s="20" t="inlineStr">
         <is>
-          <t>Workflow Automation</t>
+          <t>Retrieval Agents</t>
         </is>
       </c>
       <c r="C37" s="20" t="inlineStr"/>
-      <c r="D37" s="20" t="inlineStr"/>
-      <c r="E37" s="20" t="inlineStr"/>
-      <c r="F37" s="20" t="inlineStr"/>
+      <c r="D37" s="20" t="inlineStr">
+        <is>
+          <t>ACM-CCS</t>
+        </is>
+      </c>
+      <c r="E37" s="20" t="inlineStr">
+        <is>
+          <t>Information systems~Information retrieval</t>
+        </is>
+      </c>
+      <c r="F37" s="20" t="inlineStr">
+        <is>
+          <t>https://dl.acm.org/ccs</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="20" t="inlineStr">
@@ -4474,7 +4462,7 @@
       </c>
       <c r="B38" s="20" t="inlineStr">
         <is>
-          <t>Orchestration</t>
+          <t>Sandbox</t>
         </is>
       </c>
       <c r="C38" s="20" t="inlineStr"/>
@@ -4490,7 +4478,7 @@
       </c>
       <c r="B39" s="20" t="inlineStr">
         <is>
-          <t>Triggers</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="C39" s="20" t="inlineStr"/>
@@ -4506,7 +4494,7 @@
       </c>
       <c r="B40" s="20" t="inlineStr">
         <is>
-          <t>Retrieval</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="C40" s="20" t="inlineStr"/>
@@ -4517,7 +4505,7 @@
       </c>
       <c r="E40" s="20" t="inlineStr">
         <is>
-          <t>Information systems~Information retrieval</t>
+          <t>Security and privacy</t>
         </is>
       </c>
       <c r="F40" s="20" t="inlineStr">
@@ -4534,23 +4522,27 @@
       </c>
       <c r="B41" s="20" t="inlineStr">
         <is>
-          <t>Retrieval Agents</t>
-        </is>
-      </c>
-      <c r="C41" s="20" t="inlineStr"/>
+          <t>FAIR data</t>
+        </is>
+      </c>
+      <c r="C41" s="20" t="inlineStr">
+        <is>
+          <t>Findable, Accessible, Interoperable, Reusable data principles.</t>
+        </is>
+      </c>
       <c r="D41" s="20" t="inlineStr">
         <is>
-          <t>ACM-CCS</t>
+          <t>EDAM</t>
         </is>
       </c>
       <c r="E41" s="20" t="inlineStr">
         <is>
-          <t>Information systems~Information retrieval</t>
+          <t>topic_4012</t>
         </is>
       </c>
       <c r="F41" s="20" t="inlineStr">
         <is>
-          <t>https://dl.acm.org/ccs</t>
+          <t>http://edamontology.org/topic_4012</t>
         </is>
       </c>
     </row>
@@ -4562,7 +4554,7 @@
       </c>
       <c r="B42" s="20" t="inlineStr">
         <is>
-          <t>Sandbox</t>
+          <t>API Integration</t>
         </is>
       </c>
       <c r="C42" s="20" t="inlineStr"/>
@@ -4578,7 +4570,7 @@
       </c>
       <c r="B43" s="20" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Model Integration</t>
         </is>
       </c>
       <c r="C43" s="20" t="inlineStr"/>
@@ -4594,25 +4586,13 @@
       </c>
       <c r="B44" s="20" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Server Integration</t>
         </is>
       </c>
       <c r="C44" s="20" t="inlineStr"/>
-      <c r="D44" s="20" t="inlineStr">
-        <is>
-          <t>ACM-CCS</t>
-        </is>
-      </c>
-      <c r="E44" s="20" t="inlineStr">
-        <is>
-          <t>Security and privacy</t>
-        </is>
-      </c>
-      <c r="F44" s="20" t="inlineStr">
-        <is>
-          <t>https://dl.acm.org/ccs</t>
-        </is>
-      </c>
+      <c r="D44" s="20" t="inlineStr"/>
+      <c r="E44" s="20" t="inlineStr"/>
+      <c r="F44" s="20" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="20" t="inlineStr">
@@ -4622,90 +4602,118 @@
       </c>
       <c r="B45" s="20" t="inlineStr">
         <is>
-          <t>FAIR data</t>
-        </is>
-      </c>
-      <c r="C45" s="20" t="inlineStr">
-        <is>
-          <t>Findable, Accessible, Interoperable, Reusable data principles.</t>
-        </is>
-      </c>
-      <c r="D45" s="20" t="inlineStr">
-        <is>
-          <t>EDAM</t>
-        </is>
-      </c>
-      <c r="E45" s="20" t="inlineStr">
-        <is>
-          <t>topic_4012</t>
-        </is>
-      </c>
-      <c r="F45" s="20" t="inlineStr">
-        <is>
-          <t>http://edamontology.org/topic_4012</t>
-        </is>
-      </c>
+          <t>Server Patterns</t>
+        </is>
+      </c>
+      <c r="C45" s="20" t="inlineStr"/>
+      <c r="D45" s="20" t="inlineStr"/>
+      <c r="E45" s="20" t="inlineStr"/>
+      <c r="F45" s="20" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="20" t="inlineStr">
         <is>
-          <t>Agentic Features Covered</t>
+          <t>Topic Focus</t>
         </is>
       </c>
       <c r="B46" s="20" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="C46" s="20" t="inlineStr"/>
-      <c r="D46" s="20" t="inlineStr"/>
-      <c r="E46" s="20" t="inlineStr"/>
-      <c r="F46" s="20" t="inlineStr"/>
+      <c r="D46" s="20" t="inlineStr">
+        <is>
+          <t>ACM-CCS</t>
+        </is>
+      </c>
+      <c r="E46" s="20" t="inlineStr">
+        <is>
+          <t>Computer systems organization~Architectures</t>
+        </is>
+      </c>
+      <c r="F46" s="20" t="inlineStr">
+        <is>
+          <t>https://dl.acm.org/ccs</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>Agentic Features Covered</t>
+          <t>Topic Focus</t>
         </is>
       </c>
       <c r="B47" s="20" t="inlineStr">
         <is>
-          <t>Model Integration</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="C47" s="20" t="inlineStr"/>
-      <c r="D47" s="20" t="inlineStr"/>
-      <c r="E47" s="20" t="inlineStr"/>
-      <c r="F47" s="20" t="inlineStr"/>
+      <c r="D47" s="20" t="inlineStr">
+        <is>
+          <t>ACM-CCS</t>
+        </is>
+      </c>
+      <c r="E47" s="20" t="inlineStr">
+        <is>
+          <t>Security and privacy</t>
+        </is>
+      </c>
+      <c r="F47" s="20" t="inlineStr">
+        <is>
+          <t>https://dl.acm.org/ccs</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="20" t="inlineStr">
         <is>
-          <t>Agentic Features Covered</t>
+          <t>Topic Focus</t>
         </is>
       </c>
       <c r="B48" s="20" t="inlineStr">
         <is>
-          <t>Server Integration</t>
-        </is>
-      </c>
-      <c r="C48" s="20" t="inlineStr"/>
-      <c r="D48" s="20" t="inlineStr"/>
-      <c r="E48" s="20" t="inlineStr"/>
-      <c r="F48" s="20" t="inlineStr"/>
+          <t>Data governance</t>
+        </is>
+      </c>
+      <c r="C48" s="20" t="inlineStr">
+        <is>
+          <t>Focuses specifically on the technical protocols, access controls, data-line security, and de-identification standards used to protect the integrity, quality, and privacy of information throughout its lifecycle</t>
+        </is>
+      </c>
+      <c r="D48" s="20" t="inlineStr">
+        <is>
+          <t>EDAM</t>
+        </is>
+      </c>
+      <c r="E48" s="20" t="inlineStr">
+        <is>
+          <t>topic_3571</t>
+        </is>
+      </c>
+      <c r="F48" s="20" t="inlineStr">
+        <is>
+          <t>http://edamontology.org/topic_3571</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="20" t="inlineStr">
         <is>
-          <t>Agentic Features Covered</t>
+          <t>Topic Focus</t>
         </is>
       </c>
       <c r="B49" s="20" t="inlineStr">
         <is>
-          <t>Server Patterns</t>
-        </is>
-      </c>
-      <c r="C49" s="20" t="inlineStr"/>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="C49" s="20" t="inlineStr">
+        <is>
+          <t>The overarching organizational policies, compliance frameworks, and capital allocation strategies that dictate how an enterprise manages its broader IT infrastructure, risk tolerances, and vendor choices</t>
+        </is>
+      </c>
       <c r="D49" s="20" t="inlineStr"/>
       <c r="E49" s="20" t="inlineStr"/>
       <c r="F49" s="20" t="inlineStr"/>
@@ -4718,7 +4726,7 @@
       </c>
       <c r="B50" s="20" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Implementation</t>
         </is>
       </c>
       <c r="C50" s="20" t="inlineStr"/>
@@ -4729,7 +4737,7 @@
       </c>
       <c r="E50" s="20" t="inlineStr">
         <is>
-          <t>Computer systems organization~Architectures</t>
+          <t>Software and its engineering~Software creation and management</t>
         </is>
       </c>
       <c r="F50" s="20" t="inlineStr">
@@ -4746,23 +4754,27 @@
       </c>
       <c r="B51" s="20" t="inlineStr">
         <is>
-          <t>Security</t>
-        </is>
-      </c>
-      <c r="C51" s="20" t="inlineStr"/>
+          <t>Deployment</t>
+        </is>
+      </c>
+      <c r="C51" s="20" t="inlineStr">
+        <is>
+          <t>The tactical, hands-on execution of installing, configuring, provisioning, and launching software or hardware systems within a specific operational environment</t>
+        </is>
+      </c>
       <c r="D51" s="20" t="inlineStr">
         <is>
-          <t>ACM-CCS</t>
+          <t>NIST-AI-RMF</t>
         </is>
       </c>
       <c r="E51" s="20" t="inlineStr">
         <is>
-          <t>Security and privacy</t>
+          <t>AI lifecycle stage: Deploy</t>
         </is>
       </c>
       <c r="F51" s="20" t="inlineStr">
         <is>
-          <t>https://dl.acm.org/ccs</t>
+          <t>https://nvlpubs.nist.gov/nistpubs/ai/NIST.AI.100-1.pdf</t>
         </is>
       </c>
     </row>
@@ -4774,14 +4786,10 @@
       </c>
       <c r="B52" s="20" t="inlineStr">
         <is>
-          <t>Data governance</t>
-        </is>
-      </c>
-      <c r="C52" s="20" t="inlineStr">
-        <is>
-          <t>Focuses specifically on the technical protocols, access controls, data-line security, and de-identification standards used to protect the integrity, quality, and privacy of information throughout its lifecycle</t>
-        </is>
-      </c>
+          <t>Workflows</t>
+        </is>
+      </c>
+      <c r="C52" s="20" t="inlineStr"/>
       <c r="D52" s="20" t="inlineStr">
         <is>
           <t>EDAM</t>
@@ -4789,12 +4797,12 @@
       </c>
       <c r="E52" s="20" t="inlineStr">
         <is>
-          <t>topic_3571</t>
+          <t>topic_0769</t>
         </is>
       </c>
       <c r="F52" s="20" t="inlineStr">
         <is>
-          <t>http://edamontology.org/topic_3571</t>
+          <t>http://edamontology.org/topic_0769</t>
         </is>
       </c>
     </row>
@@ -4806,14 +4814,10 @@
       </c>
       <c r="B53" s="20" t="inlineStr">
         <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="C53" s="20" t="inlineStr">
-        <is>
-          <t>The overarching organizational policies, compliance frameworks, and capital allocation strategies that dictate how an enterprise manages its broader IT infrastructure, risk tolerances, and vendor choices</t>
-        </is>
-      </c>
+          <t>Model selection</t>
+        </is>
+      </c>
+      <c r="C53" s="20" t="inlineStr"/>
       <c r="D53" s="20" t="inlineStr"/>
       <c r="E53" s="20" t="inlineStr"/>
       <c r="F53" s="20" t="inlineStr"/>
@@ -4826,7 +4830,7 @@
       </c>
       <c r="B54" s="20" t="inlineStr">
         <is>
-          <t>Implementation</t>
+          <t>Evaluation</t>
         </is>
       </c>
       <c r="C54" s="20" t="inlineStr"/>
@@ -4837,7 +4841,7 @@
       </c>
       <c r="E54" s="20" t="inlineStr">
         <is>
-          <t>Software and its engineering~Software creation and management</t>
+          <t>Software and its engineering~Software verification and validation~Software testing and debugging</t>
         </is>
       </c>
       <c r="F54" s="20" t="inlineStr">
@@ -4854,29 +4858,17 @@
       </c>
       <c r="B55" s="20" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Compute Infrastructure</t>
         </is>
       </c>
       <c r="C55" s="20" t="inlineStr">
         <is>
-          <t>The tactical, hands-on execution of installing, configuring, provisioning, and launching software or hardware systems within a specific operational environment</t>
-        </is>
-      </c>
-      <c r="D55" s="20" t="inlineStr">
-        <is>
-          <t>NIST-AI-RMF</t>
-        </is>
-      </c>
-      <c r="E55" s="20" t="inlineStr">
-        <is>
-          <t>AI lifecycle stage: Deploy</t>
-        </is>
-      </c>
-      <c r="F55" s="20" t="inlineStr">
-        <is>
-          <t>https://nvlpubs.nist.gov/nistpubs/ai/NIST.AI.100-1.pdf</t>
-        </is>
-      </c>
+          <t>Physical node topologies, hardware constraints, VRAM bounds, and localized compute execution profiles.</t>
+        </is>
+      </c>
+      <c r="D55" s="20" t="inlineStr"/>
+      <c r="E55" s="20" t="inlineStr"/>
+      <c r="F55" s="20" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="20" t="inlineStr">
@@ -4886,25 +4878,17 @@
       </c>
       <c r="B56" s="20" t="inlineStr">
         <is>
-          <t>Workflows</t>
-        </is>
-      </c>
-      <c r="C56" s="20" t="inlineStr"/>
-      <c r="D56" s="20" t="inlineStr">
-        <is>
-          <t>EDAM</t>
-        </is>
-      </c>
-      <c r="E56" s="20" t="inlineStr">
-        <is>
-          <t>topic_0769</t>
-        </is>
-      </c>
-      <c r="F56" s="20" t="inlineStr">
-        <is>
-          <t>http://edamontology.org/topic_0769</t>
-        </is>
-      </c>
+          <t>Network Isolation</t>
+        </is>
+      </c>
+      <c r="C56" s="20" t="inlineStr">
+        <is>
+          <t>Non-egress boundaries, air-gapped artifact staging, localized cloud VPC containers, and firewalled local registries.</t>
+        </is>
+      </c>
+      <c r="D56" s="20" t="inlineStr"/>
+      <c r="E56" s="20" t="inlineStr"/>
+      <c r="F56" s="20" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="20" t="inlineStr">
@@ -4914,10 +4898,14 @@
       </c>
       <c r="B57" s="20" t="inlineStr">
         <is>
-          <t>Model selection</t>
-        </is>
-      </c>
-      <c r="C57" s="20" t="inlineStr"/>
+          <t>Infrastructure Security</t>
+        </is>
+      </c>
+      <c r="C57" s="20" t="inlineStr">
+        <is>
+          <t>For on-prem LLM deployments, it captures the security of the compute stack as well as the data pipelines</t>
+        </is>
+      </c>
       <c r="D57" s="20" t="inlineStr"/>
       <c r="E57" s="20" t="inlineStr"/>
       <c r="F57" s="20" t="inlineStr"/>
@@ -4930,25 +4918,17 @@
       </c>
       <c r="B58" s="20" t="inlineStr">
         <is>
-          <t>Evaluation</t>
-        </is>
-      </c>
-      <c r="C58" s="20" t="inlineStr"/>
-      <c r="D58" s="20" t="inlineStr">
-        <is>
-          <t>ACM-CCS</t>
-        </is>
-      </c>
-      <c r="E58" s="20" t="inlineStr">
-        <is>
-          <t>Software and its engineering~Software verification and validation~Software testing and debugging</t>
-        </is>
-      </c>
-      <c r="F58" s="20" t="inlineStr">
-        <is>
-          <t>https://dl.acm.org/ccs</t>
-        </is>
-      </c>
+          <t>Self‑hosted AI</t>
+        </is>
+      </c>
+      <c r="C58" s="20" t="inlineStr">
+        <is>
+          <t>Self‑hosted, open‑weights models in contrast to API‑based models like OpenAI, Anthropic, or Gemini</t>
+        </is>
+      </c>
+      <c r="D58" s="20" t="inlineStr"/>
+      <c r="E58" s="20" t="inlineStr"/>
+      <c r="F58" s="20" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="20" t="inlineStr">
@@ -4958,17 +4938,29 @@
       </c>
       <c r="B59" s="20" t="inlineStr">
         <is>
-          <t>Compute Infrastructure</t>
+          <t>Data Protection</t>
         </is>
       </c>
       <c r="C59" s="20" t="inlineStr">
         <is>
-          <t>Physical node topologies, hardware constraints, VRAM bounds, and localized compute execution profiles.</t>
-        </is>
-      </c>
-      <c r="D59" s="20" t="inlineStr"/>
-      <c r="E59" s="20" t="inlineStr"/>
-      <c r="F59" s="20" t="inlineStr"/>
+          <t>Safeguarding sensitive data specifically. Distinct from the broader Security term.</t>
+        </is>
+      </c>
+      <c r="D59" s="20" t="inlineStr">
+        <is>
+          <t>EDAM</t>
+        </is>
+      </c>
+      <c r="E59" s="20" t="inlineStr">
+        <is>
+          <t>topic_4044</t>
+        </is>
+      </c>
+      <c r="F59" s="20" t="inlineStr">
+        <is>
+          <t>http://edamontology.org/topic_4044</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="20" t="inlineStr">
@@ -4978,17 +4970,29 @@
       </c>
       <c r="B60" s="20" t="inlineStr">
         <is>
-          <t>Network Isolation</t>
+          <t>FAIR data</t>
         </is>
       </c>
       <c r="C60" s="20" t="inlineStr">
         <is>
-          <t>Non-egress boundaries, air-gapped artifact staging, localized cloud VPC containers, and firewalled local registries.</t>
-        </is>
-      </c>
-      <c r="D60" s="20" t="inlineStr"/>
-      <c r="E60" s="20" t="inlineStr"/>
-      <c r="F60" s="20" t="inlineStr"/>
+          <t>Findable, Accessible, Interoperable, Reusable data principles.</t>
+        </is>
+      </c>
+      <c r="D60" s="20" t="inlineStr">
+        <is>
+          <t>EDAM</t>
+        </is>
+      </c>
+      <c r="E60" s="20" t="inlineStr">
+        <is>
+          <t>topic_4012</t>
+        </is>
+      </c>
+      <c r="F60" s="20" t="inlineStr">
+        <is>
+          <t>http://edamontology.org/topic_4012</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="20" t="inlineStr">
@@ -4998,17 +5002,25 @@
       </c>
       <c r="B61" s="20" t="inlineStr">
         <is>
-          <t>Infrastructure Security</t>
-        </is>
-      </c>
-      <c r="C61" s="20" t="inlineStr">
-        <is>
-          <t>For on-prem LLM deployments, it captures the security of the compute stack as well as the data pipelines</t>
-        </is>
-      </c>
-      <c r="D61" s="20" t="inlineStr"/>
-      <c r="E61" s="20" t="inlineStr"/>
-      <c r="F61" s="20" t="inlineStr"/>
+          <t>Data quality management</t>
+        </is>
+      </c>
+      <c r="C61" s="20" t="inlineStr"/>
+      <c r="D61" s="20" t="inlineStr">
+        <is>
+          <t>EDAM</t>
+        </is>
+      </c>
+      <c r="E61" s="20" t="inlineStr">
+        <is>
+          <t>topic_3572</t>
+        </is>
+      </c>
+      <c r="F61" s="20" t="inlineStr">
+        <is>
+          <t>http://edamontology.org/topic_3572</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="20" t="inlineStr">
@@ -5018,17 +5030,25 @@
       </c>
       <c r="B62" s="20" t="inlineStr">
         <is>
-          <t>Self‑hosted AI</t>
-        </is>
-      </c>
-      <c r="C62" s="20" t="inlineStr">
-        <is>
-          <t>Self‑hosted, open‑weights models in contrast to API‑based models like OpenAI, Anthropic, or Gemini</t>
-        </is>
-      </c>
-      <c r="D62" s="20" t="inlineStr"/>
-      <c r="E62" s="20" t="inlineStr"/>
-      <c r="F62" s="20" t="inlineStr"/>
+          <t>Data curation and archival</t>
+        </is>
+      </c>
+      <c r="C62" s="20" t="inlineStr"/>
+      <c r="D62" s="20" t="inlineStr">
+        <is>
+          <t>EDAM</t>
+        </is>
+      </c>
+      <c r="E62" s="20" t="inlineStr">
+        <is>
+          <t>topic_0219</t>
+        </is>
+      </c>
+      <c r="F62" s="20" t="inlineStr">
+        <is>
+          <t>http://edamontology.org/topic_0219</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="20" t="inlineStr">
@@ -5038,14 +5058,10 @@
       </c>
       <c r="B63" s="20" t="inlineStr">
         <is>
-          <t>Data Protection</t>
-        </is>
-      </c>
-      <c r="C63" s="20" t="inlineStr">
-        <is>
-          <t>Safeguarding sensitive data specifically. Distinct from the broader Security term.</t>
-        </is>
-      </c>
+          <t>Data integration and warehousing</t>
+        </is>
+      </c>
+      <c r="C63" s="20" t="inlineStr"/>
       <c r="D63" s="20" t="inlineStr">
         <is>
           <t>EDAM</t>
@@ -5053,12 +5069,12 @@
       </c>
       <c r="E63" s="20" t="inlineStr">
         <is>
-          <t>topic_4044</t>
+          <t>topic_3366</t>
         </is>
       </c>
       <c r="F63" s="20" t="inlineStr">
         <is>
-          <t>http://edamontology.org/topic_4044</t>
+          <t>http://edamontology.org/topic_3366</t>
         </is>
       </c>
     </row>
@@ -5070,14 +5086,10 @@
       </c>
       <c r="B64" s="20" t="inlineStr">
         <is>
-          <t>FAIR data</t>
-        </is>
-      </c>
-      <c r="C64" s="20" t="inlineStr">
-        <is>
-          <t>Findable, Accessible, Interoperable, Reusable data principles.</t>
-        </is>
-      </c>
+          <t>Data architecture, analysis and design</t>
+        </is>
+      </c>
+      <c r="C64" s="20" t="inlineStr"/>
       <c r="D64" s="20" t="inlineStr">
         <is>
           <t>EDAM</t>
@@ -5085,12 +5097,12 @@
       </c>
       <c r="E64" s="20" t="inlineStr">
         <is>
-          <t>topic_4012</t>
+          <t>topic_3365</t>
         </is>
       </c>
       <c r="F64" s="20" t="inlineStr">
         <is>
-          <t>http://edamontology.org/topic_4012</t>
+          <t>http://edamontology.org/topic_3365</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5114,7 @@
       </c>
       <c r="B65" s="20" t="inlineStr">
         <is>
-          <t>Data quality management</t>
+          <t>Data identity and mapping</t>
         </is>
       </c>
       <c r="C65" s="20" t="inlineStr"/>
@@ -5113,12 +5125,12 @@
       </c>
       <c r="E65" s="20" t="inlineStr">
         <is>
-          <t>topic_3572</t>
+          <t>topic_3345</t>
         </is>
       </c>
       <c r="F65" s="20" t="inlineStr">
         <is>
-          <t>http://edamontology.org/topic_3572</t>
+          <t>http://edamontology.org/topic_3345</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5142,7 @@
       </c>
       <c r="B66" s="20" t="inlineStr">
         <is>
-          <t>Data curation and archival</t>
+          <t>Data rescue</t>
         </is>
       </c>
       <c r="C66" s="20" t="inlineStr"/>
@@ -5141,12 +5153,12 @@
       </c>
       <c r="E66" s="20" t="inlineStr">
         <is>
-          <t>topic_0219</t>
+          <t>topic_4011</t>
         </is>
       </c>
       <c r="F66" s="20" t="inlineStr">
         <is>
-          <t>http://edamontology.org/topic_0219</t>
+          <t>http://edamontology.org/topic_4011</t>
         </is>
       </c>
     </row>
@@ -5158,25 +5170,21 @@
       </c>
       <c r="B67" s="20" t="inlineStr">
         <is>
-          <t>Data integration and warehousing</t>
-        </is>
-      </c>
-      <c r="C67" s="20" t="inlineStr"/>
+          <t>Valid and Reliable</t>
+        </is>
+      </c>
+      <c r="C67" s="20" t="inlineStr">
+        <is>
+          <t>NIST AI RMF trustworthy-AI characteristic.</t>
+        </is>
+      </c>
       <c r="D67" s="20" t="inlineStr">
         <is>
-          <t>EDAM</t>
-        </is>
-      </c>
-      <c r="E67" s="20" t="inlineStr">
-        <is>
-          <t>topic_3366</t>
-        </is>
-      </c>
-      <c r="F67" s="20" t="inlineStr">
-        <is>
-          <t>http://edamontology.org/topic_3366</t>
-        </is>
-      </c>
+          <t>NIST-AI-RMF</t>
+        </is>
+      </c>
+      <c r="E67" s="20" t="inlineStr"/>
+      <c r="F67" s="20" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="20" t="inlineStr">
@@ -5186,25 +5194,21 @@
       </c>
       <c r="B68" s="20" t="inlineStr">
         <is>
-          <t>Data architecture, analysis and design</t>
-        </is>
-      </c>
-      <c r="C68" s="20" t="inlineStr"/>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="C68" s="20" t="inlineStr">
+        <is>
+          <t>NIST AI RMF trustworthy-AI characteristic.</t>
+        </is>
+      </c>
       <c r="D68" s="20" t="inlineStr">
         <is>
-          <t>EDAM</t>
-        </is>
-      </c>
-      <c r="E68" s="20" t="inlineStr">
-        <is>
-          <t>topic_3365</t>
-        </is>
-      </c>
-      <c r="F68" s="20" t="inlineStr">
-        <is>
-          <t>http://edamontology.org/topic_3365</t>
-        </is>
-      </c>
+          <t>NIST-AI-RMF</t>
+        </is>
+      </c>
+      <c r="E68" s="20" t="inlineStr"/>
+      <c r="F68" s="20" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="20" t="inlineStr">
@@ -5214,25 +5218,21 @@
       </c>
       <c r="B69" s="20" t="inlineStr">
         <is>
-          <t>Data identity and mapping</t>
-        </is>
-      </c>
-      <c r="C69" s="20" t="inlineStr"/>
+          <t>Secure and Resilient</t>
+        </is>
+      </c>
+      <c r="C69" s="20" t="inlineStr">
+        <is>
+          <t>NIST AI RMF trustworthy-AI characteristic.</t>
+        </is>
+      </c>
       <c r="D69" s="20" t="inlineStr">
         <is>
-          <t>EDAM</t>
-        </is>
-      </c>
-      <c r="E69" s="20" t="inlineStr">
-        <is>
-          <t>topic_3345</t>
-        </is>
-      </c>
-      <c r="F69" s="20" t="inlineStr">
-        <is>
-          <t>http://edamontology.org/topic_3345</t>
-        </is>
-      </c>
+          <t>NIST-AI-RMF</t>
+        </is>
+      </c>
+      <c r="E69" s="20" t="inlineStr"/>
+      <c r="F69" s="20" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="20" t="inlineStr">
@@ -5242,25 +5242,21 @@
       </c>
       <c r="B70" s="20" t="inlineStr">
         <is>
-          <t>Data rescue</t>
-        </is>
-      </c>
-      <c r="C70" s="20" t="inlineStr"/>
+          <t>Accountable and Transparent</t>
+        </is>
+      </c>
+      <c r="C70" s="20" t="inlineStr">
+        <is>
+          <t>NIST AI RMF trustworthy-AI characteristic.</t>
+        </is>
+      </c>
       <c r="D70" s="20" t="inlineStr">
         <is>
-          <t>EDAM</t>
-        </is>
-      </c>
-      <c r="E70" s="20" t="inlineStr">
-        <is>
-          <t>topic_4011</t>
-        </is>
-      </c>
-      <c r="F70" s="20" t="inlineStr">
-        <is>
-          <t>http://edamontology.org/topic_4011</t>
-        </is>
-      </c>
+          <t>NIST-AI-RMF</t>
+        </is>
+      </c>
+      <c r="E70" s="20" t="inlineStr"/>
+      <c r="F70" s="20" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="20" t="inlineStr">
@@ -5270,7 +5266,7 @@
       </c>
       <c r="B71" s="20" t="inlineStr">
         <is>
-          <t>Valid and Reliable</t>
+          <t>Explainable and Interpretable</t>
         </is>
       </c>
       <c r="C71" s="20" t="inlineStr">
@@ -5294,7 +5290,7 @@
       </c>
       <c r="B72" s="20" t="inlineStr">
         <is>
-          <t>Safe</t>
+          <t>Privacy-Enhanced</t>
         </is>
       </c>
       <c r="C72" s="20" t="inlineStr">
@@ -5318,12 +5314,12 @@
       </c>
       <c r="B73" s="20" t="inlineStr">
         <is>
-          <t>Secure and Resilient</t>
+          <t>Fair (harmful bias managed)</t>
         </is>
       </c>
       <c r="C73" s="20" t="inlineStr">
         <is>
-          <t>NIST AI RMF trustworthy-AI characteristic.</t>
+          <t>NIST AI RMF trustworthy-AI characteristic: algorithmic non-discrimination. NOT the same as 'FAIR data'.</t>
         </is>
       </c>
       <c r="D73" s="20" t="inlineStr">
@@ -5337,162 +5333,66 @@
     <row r="74">
       <c r="A74" s="20" t="inlineStr">
         <is>
-          <t>Topic Focus</t>
+          <t>Maturity Level</t>
         </is>
       </c>
       <c r="B74" s="20" t="inlineStr">
         <is>
-          <t>Accountable and Transparent</t>
-        </is>
-      </c>
-      <c r="C74" s="20" t="inlineStr">
-        <is>
-          <t>NIST AI RMF trustworthy-AI characteristic.</t>
-        </is>
-      </c>
-      <c r="D74" s="20" t="inlineStr">
-        <is>
-          <t>NIST-AI-RMF</t>
-        </is>
-      </c>
+          <t>Emerging</t>
+        </is>
+      </c>
+      <c r="C74" s="20" t="inlineStr"/>
+      <c r="D74" s="20" t="inlineStr"/>
       <c r="E74" s="20" t="inlineStr"/>
       <c r="F74" s="20" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="20" t="inlineStr">
         <is>
-          <t>Topic Focus</t>
+          <t>Maturity Level</t>
         </is>
       </c>
       <c r="B75" s="20" t="inlineStr">
         <is>
-          <t>Explainable and Interpretable</t>
-        </is>
-      </c>
-      <c r="C75" s="20" t="inlineStr">
-        <is>
-          <t>NIST AI RMF trustworthy-AI characteristic.</t>
-        </is>
-      </c>
-      <c r="D75" s="20" t="inlineStr">
-        <is>
-          <t>NIST-AI-RMF</t>
-        </is>
-      </c>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="C75" s="20" t="inlineStr"/>
+      <c r="D75" s="20" t="inlineStr"/>
       <c r="E75" s="20" t="inlineStr"/>
       <c r="F75" s="20" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="20" t="inlineStr">
         <is>
-          <t>Topic Focus</t>
+          <t>Maturity Level</t>
         </is>
       </c>
       <c r="B76" s="20" t="inlineStr">
         <is>
-          <t>Privacy-Enhanced</t>
-        </is>
-      </c>
-      <c r="C76" s="20" t="inlineStr">
-        <is>
-          <t>NIST AI RMF trustworthy-AI characteristic.</t>
-        </is>
-      </c>
-      <c r="D76" s="20" t="inlineStr">
-        <is>
-          <t>NIST-AI-RMF</t>
-        </is>
-      </c>
+          <t>Mature</t>
+        </is>
+      </c>
+      <c r="C76" s="20" t="inlineStr"/>
+      <c r="D76" s="20" t="inlineStr"/>
       <c r="E76" s="20" t="inlineStr"/>
       <c r="F76" s="20" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="20" t="inlineStr">
         <is>
-          <t>Topic Focus</t>
+          <t>Maturity Level</t>
         </is>
       </c>
       <c r="B77" s="20" t="inlineStr">
         <is>
-          <t>Fair (harmful bias managed)</t>
-        </is>
-      </c>
-      <c r="C77" s="20" t="inlineStr">
-        <is>
-          <t>NIST AI RMF trustworthy-AI characteristic: algorithmic non-discrimination. NOT the same as 'FAIR data'.</t>
-        </is>
-      </c>
-      <c r="D77" s="20" t="inlineStr">
-        <is>
-          <t>NIST-AI-RMF</t>
-        </is>
-      </c>
+          <t>Deprecated</t>
+        </is>
+      </c>
+      <c r="C77" s="20" t="inlineStr"/>
+      <c r="D77" s="20" t="inlineStr"/>
       <c r="E77" s="20" t="inlineStr"/>
       <c r="F77" s="20" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="20" t="inlineStr">
-        <is>
-          <t>Maturity Level</t>
-        </is>
-      </c>
-      <c r="B78" s="20" t="inlineStr">
-        <is>
-          <t>Emerging</t>
-        </is>
-      </c>
-      <c r="C78" s="20" t="inlineStr"/>
-      <c r="D78" s="20" t="inlineStr"/>
-      <c r="E78" s="20" t="inlineStr"/>
-      <c r="F78" s="20" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="20" t="inlineStr">
-        <is>
-          <t>Maturity Level</t>
-        </is>
-      </c>
-      <c r="B79" s="20" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="C79" s="20" t="inlineStr"/>
-      <c r="D79" s="20" t="inlineStr"/>
-      <c r="E79" s="20" t="inlineStr"/>
-      <c r="F79" s="20" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="20" t="inlineStr">
-        <is>
-          <t>Maturity Level</t>
-        </is>
-      </c>
-      <c r="B80" s="20" t="inlineStr">
-        <is>
-          <t>Mature</t>
-        </is>
-      </c>
-      <c r="C80" s="20" t="inlineStr"/>
-      <c r="D80" s="20" t="inlineStr"/>
-      <c r="E80" s="20" t="inlineStr"/>
-      <c r="F80" s="20" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="20" t="inlineStr">
-        <is>
-          <t>Maturity Level</t>
-        </is>
-      </c>
-      <c r="B81" s="20" t="inlineStr">
-        <is>
-          <t>Deprecated</t>
-        </is>
-      </c>
-      <c r="C81" s="20" t="inlineStr"/>
-      <c r="D81" s="20" t="inlineStr"/>
-      <c r="E81" s="20" t="inlineStr"/>
-      <c r="F81" s="20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5624,27 +5524,27 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t>Schema.org</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>Schema.org (CreativeWork hierarchy)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>current</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="0" t="inlineStr">
         <is>
           <t>https://schema.org/CreativeWork</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="0" t="inlineStr">
         <is>
           <t>Universal web-metadata vocabulary. Exact-type matches applied directly (e.g. APIReference, BlogPosting, ScholarlyArticle, SoftwareSourceCode, Dataset). For highly specific AI-radar terms with no exact schema.org type, the broader parent type is applied instead (e.g. several terms map to TechArticle) -- this is schema.org's own intended usage pattern (broad type + a custom category property), not a forced fit, but it means several distinct Resource Type terms intentionally share one Ontology ID here, unlike EDAM/ACM-CCS/NIST-AI-RMF where each backed term has its own distinct match.</t>
         </is>

--- a/data/VANTAGE-Technology-Radar.xlsx
+++ b/data/VANTAGE-Technology-Radar.xlsx
@@ -17,7 +17,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm"/>
     <numFmt numFmtId="166" formatCode="m/d/yyyy"/>
@@ -25,6 +25,7 @@
     <numFmt numFmtId="168" formatCode="yyyy-m"/>
     <numFmt numFmtId="169" formatCode="mmmm d, yyyy"/>
     <numFmt numFmtId="170" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="171" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -83,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -109,6 +110,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -446,13 +448,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O43"/>
+  <dimension ref="A1:Q43"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col width="27.88" customWidth="1" style="17" min="1" max="1"/>
+    <col width="10" customWidth="1" style="17" min="1" max="1"/>
     <col width="27.38" customWidth="1" style="17" min="2" max="2"/>
     <col width="16.25" customWidth="1" style="17" min="3" max="3"/>
-    <col width="9.25" customWidth="1" style="17" min="7" max="7"/>
+    <col width="20" customWidth="1" style="17" min="7" max="7"/>
     <col width="18.63" customWidth="1" style="17" min="8" max="8"/>
     <col width="37.88" customWidth="1" style="17" min="9" max="9"/>
     <col width="57.88" customWidth="1" style="17" min="10" max="10"/>
@@ -460,2016 +462,2313 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>Resource Name</t>
         </is>
       </c>
-      <c r="B1" s="16" t="inlineStr">
+      <c r="C1" s="16" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="C1" s="16" t="inlineStr">
+      <c r="D1" s="16" t="inlineStr">
         <is>
           <t>Source Organization</t>
         </is>
       </c>
-      <c r="D1" s="16" t="inlineStr">
+      <c r="E1" s="16" t="inlineStr">
         <is>
           <t>Last Verified</t>
         </is>
       </c>
-      <c r="E1" s="16" t="inlineStr">
+      <c r="F1" s="16" t="inlineStr">
         <is>
           <t>Verified By</t>
         </is>
       </c>
-      <c r="F1" s="16" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Added/Edited By</t>
+        </is>
+      </c>
+      <c r="H1" s="16" t="inlineStr">
         <is>
           <t>Last Updated</t>
         </is>
       </c>
-      <c r="G1" s="16" t="inlineStr">
+      <c r="I1" s="16" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
       </c>
-      <c r="H1" s="16" t="inlineStr">
+      <c r="J1" s="16" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="I1" s="16" t="inlineStr">
+      <c r="K1" s="16" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="J1" s="16" t="inlineStr">
+      <c r="L1" s="16" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="K1" s="16" t="inlineStr">
+      <c r="M1" s="16" t="inlineStr">
         <is>
           <t>Relevance to Research Cyberinfrastructure</t>
         </is>
       </c>
-      <c r="L1" s="16" t="inlineStr">
+      <c r="N1" s="16" t="inlineStr">
         <is>
           <t>Maturity Level</t>
         </is>
       </c>
-      <c r="M1" s="16" t="inlineStr">
+      <c r="O1" s="16" t="inlineStr">
         <is>
           <t>Notes / Key Takeaways</t>
         </is>
       </c>
-      <c r="N1" s="0" t="inlineStr">
+      <c r="P1" s="0" t="inlineStr">
         <is>
           <t>Publication Date</t>
         </is>
       </c>
-      <c r="O1" s="0" t="inlineStr">
+      <c r="Q1" s="0" t="inlineStr">
         <is>
           <t>Discovery Date</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>022e4e1c</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>VS Code Copilot Agents Overview</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>https://code.visualstudio.com/docs/copilot/agents/overview</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="E2" s="6" t="n">
         <v>46157</v>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="F2" s="7" t="n">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="n">
         <v>46113</v>
       </c>
-      <c r="G2" s="8" t="n"/>
-      <c r="H2" s="16" t="inlineStr">
+      <c r="I2" s="8" t="n"/>
+      <c r="J2" s="16" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="I2" s="16" t="inlineStr">
+      <c r="K2" s="16" t="inlineStr">
         <is>
           <t>Hooks; Skills; MCP; Agent frameworks</t>
         </is>
       </c>
-      <c r="J2" s="16" t="inlineStr">
+      <c r="L2" s="16" t="inlineStr">
         <is>
           <t>Architecture; Implementation; Deployment</t>
         </is>
       </c>
-      <c r="K2" s="16" t="inlineStr">
+      <c r="M2" s="16" t="inlineStr">
         <is>
           <t>IDE integration for agentic workflows</t>
         </is>
       </c>
-      <c r="L2" s="16" t="inlineStr">
+      <c r="N2" s="16" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="M2" s="16" t="inlineStr">
+      <c r="O2" s="16" t="inlineStr">
         <is>
           <t>Canonical reference for VS Code agent capabilities.</t>
         </is>
       </c>
-      <c r="N2" s="18" t="n">
+      <c r="P2" s="18" t="n">
         <v>46162</v>
       </c>
-      <c r="O2" s="18" t="n">
+      <c r="Q2" s="18" t="n">
         <v>46113</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>2e9b6b2d</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Data Director</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>https://docs.google.com/document/d/1mu1_U1cWqn1aP3vtW83JnX5-aGhzM49K/edit</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>Microsoft, RDA</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="E3" s="6" t="n">
         <v>46168</v>
       </c>
-      <c r="E3" s="16" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="F3" s="7" t="n">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="n">
         <v>46168</v>
       </c>
-      <c r="G3" s="16" t="inlineStr">
+      <c r="I3" s="16" t="inlineStr">
         <is>
           <t>v0.1 DRAFT</t>
         </is>
       </c>
-      <c r="H3" s="16" t="inlineStr">
+      <c r="J3" s="16" t="inlineStr">
         <is>
           <t>Specification</t>
         </is>
       </c>
-      <c r="I3" s="16" t="inlineStr">
+      <c r="K3" s="16" t="inlineStr">
         <is>
           <t>FAIR data; Workflow Agents</t>
         </is>
       </c>
-      <c r="J3" s="16" t="inlineStr">
+      <c r="L3" s="16" t="inlineStr">
         <is>
           <t>Workflows; Implementation</t>
         </is>
       </c>
-      <c r="K3" s="16" t="inlineStr">
+      <c r="M3" s="16" t="inlineStr">
         <is>
           <t>Makes data outputs FAIR at the point of publication</t>
         </is>
       </c>
-      <c r="L3" s="16" t="inlineStr">
+      <c r="N3" s="16" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="M3" s="16" t="n"/>
-      <c r="O3" s="18" t="n">
+      <c r="O3" s="16" t="n"/>
+      <c r="Q3" s="18" t="n">
         <v>46168</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>161f1860</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>Agentic AI Tool</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>https://docs.github.com/en/copilot/agents</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="7" t="n"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>46113</v>
+      </c>
+      <c r="I4" s="16" t="n"/>
+      <c r="J4" s="16" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="K4" s="16" t="inlineStr">
+        <is>
+          <t>Hooks; Skills; API Integration</t>
+        </is>
+      </c>
+      <c r="L4" s="16" t="inlineStr">
+        <is>
+          <t>Architecture; Governance; Security</t>
+        </is>
+      </c>
+      <c r="M4" s="16" t="inlineStr">
+        <is>
+          <t>Relevant for CI/CD and code-review automation</t>
+        </is>
+      </c>
+      <c r="N4" s="16" t="inlineStr">
+        <is>
+          <t>Emerging</t>
+        </is>
+      </c>
+      <c r="O4" s="16" t="inlineStr">
+        <is>
+          <t>Strong alignment with developer workflows.</t>
+        </is>
+      </c>
+      <c r="Q4" s="18" t="n">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>abbd844c</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>GitHub MCP Documentation</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>https://github.com/modelcontextprotocol</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>GitHub/OpenAI</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>46113</v>
+      </c>
+      <c r="I5" s="16" t="n"/>
+      <c r="J5" s="16" t="inlineStr">
+        <is>
+          <t>API Reference</t>
+        </is>
+      </c>
+      <c r="K5" s="16" t="inlineStr">
+        <is>
+          <t>MCP; Tools; Server Integration</t>
+        </is>
+      </c>
+      <c r="L5" s="16" t="inlineStr">
+        <is>
+          <t>Architecture; Implementation</t>
+        </is>
+      </c>
+      <c r="M5" s="16" t="inlineStr">
+        <is>
+          <t>Key for interoperable agent tools</t>
+        </is>
+      </c>
+      <c r="N5" s="16" t="inlineStr">
+        <is>
+          <t>Emerging</t>
+        </is>
+      </c>
+      <c r="O5" s="16" t="inlineStr">
+        <is>
+          <t>Fast-moving ecosystem.</t>
+        </is>
+      </c>
+      <c r="Q5" s="18" t="n">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>b71baded</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>OpenAI MCP Specification</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>https://spec.modelcontextprotocol.io</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>46113</v>
+      </c>
+      <c r="I6" s="16" t="n"/>
+      <c r="J6" s="16" t="inlineStr">
+        <is>
+          <t>Specification</t>
+        </is>
+      </c>
+      <c r="K6" s="16" t="inlineStr">
+        <is>
+          <t>MCP; Tools; Server Patterns</t>
+        </is>
+      </c>
+      <c r="L6" s="16" t="inlineStr">
+        <is>
+          <t>Architecture; Governance</t>
+        </is>
+      </c>
+      <c r="M6" s="16" t="inlineStr">
+        <is>
+          <t>Critical for cross-platform agent interoperability</t>
+        </is>
+      </c>
+      <c r="N6" s="16" t="inlineStr">
+        <is>
+          <t>Emerging</t>
+        </is>
+      </c>
+      <c r="O6" s="16" t="inlineStr">
+        <is>
+          <t>Becoming a de facto standard.</t>
+        </is>
+      </c>
+      <c r="Q6" s="18" t="n">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>2b23adbb</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>Anthropic Model Context Protocol</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://modelcontextprotocol.io/specification/2025-11-25 </t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>46182</v>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I7" s="11" t="n"/>
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="K7" s="16" t="inlineStr">
+        <is>
+          <t>MCP; Agent Patterns</t>
+        </is>
+      </c>
+      <c r="L7" s="16" t="inlineStr">
+        <is>
+          <t>Architecture; Governance</t>
+        </is>
+      </c>
+      <c r="M7" s="16" t="inlineStr">
+        <is>
+          <t>Integration between LLM applications and external data sources and tools</t>
+        </is>
+      </c>
+      <c r="N7" s="16" t="inlineStr">
+        <is>
+          <t>Emerging</t>
+        </is>
+      </c>
+      <c r="O7" s="16" t="inlineStr">
+        <is>
+          <t>Strong safety emphasis.</t>
+        </is>
+      </c>
+      <c r="P7" s="18" t="n">
+        <v>45972</v>
+      </c>
+      <c r="Q7" s="18" t="n">
+        <v>45962</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t>d6d28dfa</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>Kaggle Prototype to Production Whitepaper</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/whitepaper-prototype-to-production</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>Kaggle/Google</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>46157</v>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>45975</v>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J8" s="16" t="inlineStr">
+        <is>
+          <t>Whitepaper</t>
+        </is>
+      </c>
+      <c r="K8" s="16" t="inlineStr">
+        <is>
+          <t>Deployment patterns; Workflow Automation</t>
+        </is>
+      </c>
+      <c r="L8" s="16" t="inlineStr">
+        <is>
+          <t>Implementation; Security; Deployment</t>
+        </is>
+      </c>
+      <c r="M8" s="16" t="inlineStr">
+        <is>
+          <t>Helps teams move prototypes to production</t>
+        </is>
+      </c>
+      <c r="N8" s="16" t="inlineStr">
+        <is>
+          <t>Mature</t>
+        </is>
+      </c>
+      <c r="O8" s="16" t="inlineStr">
+        <is>
+          <t>Technical guide to the operational life cycle of AI agents, focusing on deployment &amp; security</t>
+        </is>
+      </c>
+      <c r="Q8" s="18" t="n">
+        <v>45975</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t>bfda8877</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>Google Vertex AI Agents Overview</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>https://cloud.google.com/vertex-ai/docs/agents</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>46113</v>
+      </c>
+      <c r="I9" s="16" t="n"/>
+      <c r="J9" s="16" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="K9" s="16" t="inlineStr">
+        <is>
+          <t>Agent frameworks; Orchestration</t>
+        </is>
+      </c>
+      <c r="L9" s="16" t="inlineStr">
+        <is>
+          <t>Architecture; Deployment</t>
+        </is>
+      </c>
+      <c r="M9" s="16" t="inlineStr">
+        <is>
+          <t>Useful for cloud-based scientific workflows</t>
+        </is>
+      </c>
+      <c r="N9" s="16" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="O9" s="16" t="inlineStr">
+        <is>
+          <t>Strong enterprise alignment.</t>
+        </is>
+      </c>
+      <c r="Q9" s="18" t="n">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t>f488464f</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>HuggingFace Agents Documentation</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/docs/agents</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I10" s="16" t="n"/>
+      <c r="J10" s="16" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="K10" s="16" t="inlineStr">
+        <is>
+          <t>Tools; Skills; Model Integration</t>
+        </is>
+      </c>
+      <c r="L10" s="16" t="inlineStr">
+        <is>
+          <t>Architecture; Implementation</t>
+        </is>
+      </c>
+      <c r="M10" s="16" t="inlineStr">
+        <is>
+          <t>Useful for open-source agent experimentation</t>
+        </is>
+      </c>
+      <c r="N10" s="16" t="inlineStr">
+        <is>
+          <t>Emerging</t>
+        </is>
+      </c>
+      <c r="O10" s="16" t="inlineStr">
+        <is>
+          <t>Rapidly evolving.</t>
+        </is>
+      </c>
+      <c r="Q10" s="18" t="n">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t>dbe3741e</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>LangChain Agents Overview</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>https://python.langchain.com/docs/modules/agents</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>LangChain</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>46113</v>
+      </c>
+      <c r="I11" s="16" t="n"/>
+      <c r="J11" s="16" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="K11" s="16" t="inlineStr">
+        <is>
+          <t>Tools; Skills; Multi-Agent Patterns</t>
+        </is>
+      </c>
+      <c r="L11" s="16" t="inlineStr">
+        <is>
+          <t>Architecture; Implementation</t>
+        </is>
+      </c>
+      <c r="M11" s="16" t="inlineStr">
+        <is>
+          <t>Relevant for workflow prototyping</t>
+        </is>
+      </c>
+      <c r="N11" s="16" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="O11" s="16" t="inlineStr">
+        <is>
+          <t>Widely used in research.</t>
+        </is>
+      </c>
+      <c r="Q11" s="18" t="n">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t>ddd42289</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>LlamaIndex Agents</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>https://docs.llamaindex.ai/en/stable/agent/</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>LlamaIndex</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>46113</v>
+      </c>
+      <c r="I12" s="16" t="n"/>
+      <c r="J12" s="16" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="K12" s="16" t="inlineStr">
+        <is>
+          <t>Tools; Skills; Retrieval Agents</t>
+        </is>
+      </c>
+      <c r="L12" s="16" t="inlineStr">
+        <is>
+          <t>Architecture; Governance</t>
+        </is>
+      </c>
+      <c r="M12" s="16" t="inlineStr">
+        <is>
+          <t>Useful for data-rich research platforms</t>
+        </is>
+      </c>
+      <c r="N12" s="16" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="O12" s="16" t="inlineStr">
+        <is>
+          <t>Strong retrieval-centric design.</t>
+        </is>
+      </c>
+      <c r="Q12" s="18" t="n">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t>c7e95f61</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>Dagster Automation/Agent Patterns</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>https://docs.dagster.io/getting-started/ai-tools</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>Dagster Labs</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="n">
+        <v>46082</v>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>1.3.15</t>
+        </is>
+      </c>
+      <c r="J13" s="16" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="K13" s="16" t="inlineStr">
+        <is>
+          <t>Workflow Automation; Orchestration</t>
+        </is>
+      </c>
+      <c r="L13" s="16" t="inlineStr">
+        <is>
+          <t>Architecture; Deployment</t>
+        </is>
+      </c>
+      <c r="M13" s="16" t="inlineStr">
+        <is>
+          <t>Relevant for scientific pipelines</t>
+        </is>
+      </c>
+      <c r="N13" s="16" t="inlineStr">
+        <is>
+          <t>Mature</t>
+        </is>
+      </c>
+      <c r="O13" s="16" t="inlineStr">
+        <is>
+          <t>Strong reproducibility focus.</t>
+        </is>
+      </c>
+      <c r="Q13" s="18" t="n">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t>73426de0</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>Prefect Automations/Agents</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>https://docs.prefect.io/latest/concepts/automations/</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>Prefect</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I14" s="16" t="n"/>
+      <c r="J14" s="16" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="K14" s="16" t="inlineStr">
+        <is>
+          <t>Workflow Agents; Triggers</t>
+        </is>
+      </c>
+      <c r="L14" s="16" t="inlineStr">
+        <is>
+          <t>Implementation; Deployment</t>
+        </is>
+      </c>
+      <c r="M14" s="16" t="inlineStr">
+        <is>
+          <t>Useful for data processing pipelines</t>
+        </is>
+      </c>
+      <c r="N14" s="16" t="inlineStr">
+        <is>
+          <t>Mature</t>
+        </is>
+      </c>
+      <c r="O14" s="16" t="inlineStr">
+        <is>
+          <t>Good hybrid cloud/HPC support.</t>
+        </is>
+      </c>
+      <c r="Q14" s="18" t="n">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t>3294a13f</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>Jupyter AI</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>https://jupyter-ai.readthedocs.io</t>
+        </is>
+      </c>
+      <c r="D15" s="16" t="inlineStr">
+        <is>
+          <t>Project Jupyter</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>46113</v>
+      </c>
+      <c r="I15" s="16" t="n"/>
+      <c r="J15" s="16" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="K15" s="16" t="inlineStr">
+        <is>
+          <t>Notebook Agents; Workflow Automation</t>
+        </is>
+      </c>
+      <c r="L15" s="16" t="inlineStr">
+        <is>
+          <t>Implementation; Data governance</t>
+        </is>
+      </c>
+      <c r="M15" s="16" t="inlineStr">
+        <is>
+          <t>Relevant for research notebooks</t>
+        </is>
+      </c>
+      <c r="N15" s="16" t="inlineStr">
+        <is>
+          <t>Emerging</t>
+        </is>
+      </c>
+      <c r="O15" s="16" t="inlineStr">
+        <is>
+          <t>Strong alignment with scientific workflows.</t>
+        </is>
+      </c>
+      <c r="Q15" s="18" t="n">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t>f51ea180</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>Anthropic Tools API</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>https://docs.anthropic.com/en/docs/tools</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>46113</v>
+      </c>
+      <c r="I16" s="16" t="n"/>
+      <c r="J16" s="16" t="inlineStr">
+        <is>
+          <t>API Reference</t>
+        </is>
+      </c>
+      <c r="K16" s="16" t="inlineStr">
+        <is>
+          <t>Tools; Skills</t>
+        </is>
+      </c>
+      <c r="L16" s="16" t="inlineStr">
+        <is>
+          <t>Architecture; Security</t>
+        </is>
+      </c>
+      <c r="M16" s="16" t="inlineStr">
+        <is>
+          <t>Useful for safe tool-calling agents</t>
+        </is>
+      </c>
+      <c r="N16" s="16" t="inlineStr">
+        <is>
+          <t>Emerging</t>
+        </is>
+      </c>
+      <c r="O16" s="16" t="inlineStr">
+        <is>
+          <t>Strong safety posture.</t>
+        </is>
+      </c>
+      <c r="Q16" s="18" t="n">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t>89f36cc1</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>Microsoft Semantic Kernel Agents</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>https://learn.microsoft.com/semantic-kernel/agents</t>
+        </is>
+      </c>
+      <c r="D17" s="16" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="7" t="n"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>46113</v>
+      </c>
+      <c r="I17" s="16" t="n"/>
+      <c r="J17" s="16" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="K17" s="16" t="inlineStr">
+        <is>
+          <t>Skills; Tools; Orchestration</t>
+        </is>
+      </c>
+      <c r="L17" s="16" t="inlineStr">
+        <is>
+          <t>Architecture; Implementation</t>
+        </is>
+      </c>
+      <c r="M17" s="16" t="inlineStr">
+        <is>
+          <t>Useful for enterprise-grade agent workflows</t>
+        </is>
+      </c>
+      <c r="N17" s="16" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="O17" s="16" t="inlineStr">
+        <is>
+          <t>Strong .NET + Python support.</t>
+        </is>
+      </c>
+      <c r="Q17" s="18" t="n">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t>4ccfda21</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>HuggingFace Inference Endpoints</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/inference-endpoints</t>
+        </is>
+      </c>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I18" s="16" t="n"/>
+      <c r="J18" s="16" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="K18" s="16" t="inlineStr">
+        <is>
+          <t>Model Integration; Tool-Ready Endpoints</t>
+        </is>
+      </c>
+      <c r="L18" s="16" t="inlineStr">
+        <is>
+          <t>Architecture; Deployment</t>
+        </is>
+      </c>
+      <c r="M18" s="16" t="inlineStr">
+        <is>
+          <t>Useful for hosted inference in research</t>
+        </is>
+      </c>
+      <c r="N18" s="16" t="inlineStr">
+        <is>
+          <t>Mature</t>
+        </is>
+      </c>
+      <c r="O18" s="16" t="inlineStr">
+        <is>
+          <t>Good for reproducibility.</t>
+        </is>
+      </c>
+      <c r="Q18" s="18" t="n">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t>2e24be4d</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>OpenAI Evaluations (Evals)</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>https://platform.openai.com/docs/guides/evals</t>
+        </is>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="7" t="n"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>46113</v>
+      </c>
+      <c r="I19" s="16" t="n"/>
+      <c r="J19" s="16" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="K19" s="16" t="inlineStr">
+        <is>
+          <t>Evaluation / testing; Safety / guardrails</t>
+        </is>
+      </c>
+      <c r="L19" s="16" t="inlineStr">
+        <is>
+          <t>Security; Governance</t>
+        </is>
+      </c>
+      <c r="M19" s="16" t="inlineStr">
+        <is>
+          <t>Relevant for agent safety in research platforms</t>
+        </is>
+      </c>
+      <c r="N19" s="16" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="O19" s="16" t="inlineStr">
+        <is>
+          <t>Useful for risk assessment.</t>
+        </is>
+      </c>
+      <c r="Q19" s="18" t="n">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t>6b9e7398</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>Anthropic Safety Guidelines</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>https://docs.anthropic.com/en/docs/safety</t>
+        </is>
+      </c>
+      <c r="D20" s="16" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>46113</v>
+      </c>
+      <c r="I20" s="16" t="n"/>
+      <c r="J20" s="16" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="K20" s="16" t="inlineStr">
+        <is>
+          <t>Safety / guardrails; Safe Tool Use</t>
+        </is>
+      </c>
+      <c r="L20" s="16" t="inlineStr">
+        <is>
+          <t>Governance; Security</t>
+        </is>
+      </c>
+      <c r="M20" s="16" t="inlineStr">
+        <is>
+          <t>Useful for research governance teams</t>
+        </is>
+      </c>
+      <c r="N20" s="16" t="inlineStr">
+        <is>
+          <t>Mature</t>
+        </is>
+      </c>
+      <c r="O20" s="16" t="inlineStr">
+        <is>
+          <t>Strong alignment with institutional risk controls.</t>
+        </is>
+      </c>
+      <c r="Q20" s="18" t="n">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t>69804f39</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>Microsoft Responsible AI Standard</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>https://www.microsoft.com/ai/responsible-ai</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="12" t="n"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I21" s="16" t="n"/>
+      <c r="J21" s="16" t="inlineStr">
+        <is>
+          <t>Governance Guidance</t>
+        </is>
+      </c>
+      <c r="K21" s="16" t="inlineStr">
+        <is>
+          <t>Safety / guardrails; Governance; Risk Controls</t>
+        </is>
+      </c>
+      <c r="L21" s="16" t="inlineStr">
+        <is>
+          <t>Data governance; Security</t>
+        </is>
+      </c>
+      <c r="M21" s="16" t="inlineStr">
+        <is>
+          <t>Relevant for institutional AI governance</t>
+        </is>
+      </c>
+      <c r="N21" s="16" t="inlineStr">
+        <is>
+          <t>Mature</t>
+        </is>
+      </c>
+      <c r="O21" s="16" t="inlineStr">
+        <is>
+          <t>Widely adopted governance framework.</t>
+        </is>
+      </c>
+      <c r="Q21" s="18" t="n">
+        <v>45992</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t>3758624e</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>vLLM Documentation</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>https://docs.vllm.ai</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
+        <is>
+          <t>vLLM Project Team</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="n"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="n">
+        <v>46113</v>
+      </c>
+      <c r="I22" s="16" t="n"/>
+      <c r="J22" s="16" t="inlineStr">
+        <is>
+          <t>Inference Framework</t>
+        </is>
+      </c>
+      <c r="K22" s="16" t="inlineStr">
+        <is>
+          <t>Deployment patterns; Tools</t>
+        </is>
+      </c>
+      <c r="L22" s="16" t="inlineStr">
+        <is>
+          <t>Self‑hosted AI; Architecture; Implementation; Deployment</t>
+        </is>
+      </c>
+      <c r="M22" s="16" t="inlineStr">
+        <is>
+          <t>High (Industry-standard VPC runtime engine)</t>
+        </is>
+      </c>
+      <c r="N22" s="16" t="inlineStr">
+        <is>
+          <t>Mature</t>
+        </is>
+      </c>
+      <c r="O22" s="16" t="inlineStr">
+        <is>
+          <t>Essential for secure TLAs via PagedAttention and FP8/AWQ optimization. Capabilities: Parallel sampling &amp; tool-calling.</t>
+        </is>
+      </c>
+      <c r="Q22" s="18" t="n">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="inlineStr">
+        <is>
+          <t>8a50b5eb</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>Ollama Documentation</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>https://github.com/ollama/ollama</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="inlineStr">
+        <is>
+          <t>Ollama Community</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="n"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="n">
+        <v>46113</v>
+      </c>
+      <c r="I23" s="16" t="n"/>
+      <c r="J23" s="16" t="inlineStr">
+        <is>
+          <t>Local Application Sandbox</t>
+        </is>
+      </c>
+      <c r="K23" s="16" t="inlineStr">
+        <is>
+          <t>Deployment patterns</t>
+        </is>
+      </c>
+      <c r="L23" s="16" t="inlineStr">
+        <is>
+          <t>Self‑hosted AI; Implementation; Deployment</t>
+        </is>
+      </c>
+      <c r="M23" s="16" t="inlineStr">
+        <is>
+          <t>Medium-High (Local workstation co-pilot)</t>
+        </is>
+      </c>
+      <c r="N23" s="16" t="inlineStr">
+        <is>
+          <t>Mature</t>
+        </is>
+      </c>
+      <c r="O23" s="16" t="inlineStr">
+        <is>
+          <t>Eliminates network dependency errors by cleanly bundling open model weights. Capabilities: Local embedding &amp; zero-config tools.</t>
+        </is>
+      </c>
+      <c r="Q23" s="18" t="n">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="inlineStr">
+        <is>
+          <t>763797cd</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Llama.cpp </t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>https://github.com/ggerganov/llama.cpp</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>Georgi Gerganov</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="16" t="n"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H24" s="14" t="n">
+        <v>46162</v>
+      </c>
+      <c r="I24" s="16" t="inlineStr">
+        <is>
+          <t>b9253</t>
+        </is>
+      </c>
+      <c r="J24" s="16" t="inlineStr">
+        <is>
+          <t>Github Code Repository</t>
+        </is>
+      </c>
+      <c r="K24" s="16" t="inlineStr">
+        <is>
+          <t>Deployment patterns</t>
+        </is>
+      </c>
+      <c r="L24" s="16" t="inlineStr">
+        <is>
+          <t>Self‑hosted AI; Architecture; Implementation; Deployment</t>
+        </is>
+      </c>
+      <c r="M24" s="16" t="inlineStr">
+        <is>
+          <t>High (Enables reasoning on variable local hardware)</t>
+        </is>
+      </c>
+      <c r="N24" s="16" t="inlineStr">
+        <is>
+          <t>Mature</t>
+        </is>
+      </c>
+      <c r="O24" s="16" t="inlineStr">
+        <is>
+          <t>Grammar constraints ensure localized agentic pipelines always return valid JSON/code. Capabilities: Grammar-based constrained sampling.</t>
+        </is>
+      </c>
+      <c r="Q24" s="18" t="n">
+        <v>46162</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="inlineStr">
+        <is>
+          <t>2d2470f7</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>Open WebUI Documentation</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>https://docs.openwebui.com</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="inlineStr">
+        <is>
+          <t>Open WebUI Core Team</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="n"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="n">
+        <v>46113</v>
+      </c>
+      <c r="I25" s="16" t="n"/>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>Enterprise Control Interface</t>
+        </is>
+      </c>
+      <c r="K25" s="16" t="inlineStr">
+        <is>
+          <t>Retrieval</t>
+        </is>
+      </c>
+      <c r="L25" s="16" t="inlineStr">
+        <is>
+          <t>Self‑hosted AI; Implementation; Deployment</t>
+        </is>
+      </c>
+      <c r="M25" s="16" t="inlineStr">
+        <is>
+          <t>High (Enterprise-grade firewall interface)</t>
+        </is>
+      </c>
+      <c r="N25" s="16" t="inlineStr">
+        <is>
+          <t>Mature</t>
+        </is>
+      </c>
+      <c r="O25" s="16" t="inlineStr">
+        <is>
+          <t>Solves local file parsing/RAG bottlenecks entirely within secure client networks. Capabilities: Local RAG pipelines &amp; offline functions.</t>
+        </is>
+      </c>
+      <c r="Q25" s="18" t="n">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="inlineStr">
+        <is>
+          <t>eb79015c</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>NVIDIA NIM Air-Gap Deployment Guide</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>https://docs.nvidia.com/nim/large-language-models/latest/deploy-air-gap.html</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="n"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H26" s="16" t="n">
+        <v>2026</v>
+      </c>
+      <c r="I26" s="16" t="n"/>
+      <c r="J26" s="16" t="inlineStr">
+        <is>
+          <t>Reference Architecture</t>
+        </is>
+      </c>
+      <c r="K26" s="16" t="inlineStr">
+        <is>
+          <t>Deployment patterns</t>
+        </is>
+      </c>
+      <c r="L26" s="16" t="inlineStr">
+        <is>
+          <t>Self‑hosted AI; Compute Infrastructure; Implementation; Network Isolation; Infrastructure Security</t>
+        </is>
+      </c>
+      <c r="M26" s="16" t="inlineStr">
+        <is>
+          <t>Critical (Standardizes secure distribution of optimized weights)</t>
+        </is>
+      </c>
+      <c r="N26" s="16" t="inlineStr">
+        <is>
+          <t>Mature</t>
+        </is>
+      </c>
+      <c r="O26" s="16" t="inlineStr">
+        <is>
+          <t>Outlines the exact connected-to-disconnected asset transfer workflow for enterprise GPUs. Capabilities: Tensor-parallel caching &amp; optimized tool-calling.</t>
+        </is>
+      </c>
+      <c r="Q26" s="18" t="n">
         <v>46150</v>
       </c>
-      <c r="E4" s="7" t="n"/>
-      <c r="F4" s="7" t="n">
-        <v>46113</v>
-      </c>
-      <c r="G4" s="16" t="n"/>
-      <c r="H4" s="16" t="inlineStr">
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="inlineStr">
+        <is>
+          <t>80527de7</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>Harbor User Documentation</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>https://goharbor.io/docs/</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="inlineStr">
+        <is>
+          <t>Cloud Native Computing Foundation (CNCF)</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="n"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H27" s="16" t="n">
+        <v>2026</v>
+      </c>
+      <c r="I27" s="16" t="n"/>
+      <c r="J27" s="16" t="inlineStr">
+        <is>
+          <t>Container Registry</t>
+        </is>
+      </c>
+      <c r="K27" s="16" t="inlineStr">
+        <is>
+          <t>Deployment patterns</t>
+        </is>
+      </c>
+      <c r="L27" s="16" t="inlineStr">
+        <is>
+          <t>Self‑hosted AI; Implementation; Network Isolation; Infrastructure Security; Governance</t>
+        </is>
+      </c>
+      <c r="M27" s="16" t="inlineStr">
+        <is>
+          <t>High (Necessary foundation for secure cluster registries)</t>
+        </is>
+      </c>
+      <c r="N27" s="16" t="inlineStr">
+        <is>
+          <t>Mature</t>
+        </is>
+      </c>
+      <c r="O27" s="16" t="inlineStr">
+        <is>
+          <t>Built-in vulnerability scanning ensures agent images remain clean behind the firewall. Capabilities: Artifact version-locking &amp; immutable tags.</t>
+        </is>
+      </c>
+      <c r="Q27" s="18" t="n">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="inlineStr">
+        <is>
+          <t>b4b5a468</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>AI Engineering Blueprint for On-Premises RAG Systems</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2604.01395</t>
+        </is>
+      </c>
+      <c r="D28" s="16" t="inlineStr">
+        <is>
+          <t>arXiv (2604.01395)</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="n"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H28" s="16" t="n">
+        <v>2026</v>
+      </c>
+      <c r="I28" s="16" t="n"/>
+      <c r="J28" s="16" t="inlineStr">
+        <is>
+          <t>Scientific Literature</t>
+        </is>
+      </c>
+      <c r="K28" s="16" t="inlineStr">
+        <is>
+          <t>Deployment patterns; Retrieval</t>
+        </is>
+      </c>
+      <c r="L28" s="16" t="inlineStr">
+        <is>
+          <t>Self‑hosted AI; Infrastructure Security</t>
+        </is>
+      </c>
+      <c r="M28" s="16" t="inlineStr">
+        <is>
+          <t>High (Academic/industry validated system design blueprint)</t>
+        </is>
+      </c>
+      <c r="N28" s="16" t="inlineStr">
+        <is>
+          <t>Emerging</t>
+        </is>
+      </c>
+      <c r="O28" s="16" t="inlineStr">
+        <is>
+          <t>Moves past simple how-to guides into formal data isolation and local compliance frameworks. Capabilities: End-to-end local reference applications.</t>
+        </is>
+      </c>
+      <c r="Q28" s="18" t="n">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="inlineStr">
+        <is>
+          <t>0d0a50a7</t>
+        </is>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>On-Premise vs Cloud: GenAI TCO (2026 Edition)</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://lenovopress.lenovo.com/lp2368-on-premise-vs-cloud-generative-ai-total-cost-of-ownership-2026-edition </t>
+        </is>
+      </c>
+      <c r="D29" s="16" t="inlineStr">
+        <is>
+          <t>Lenovo Press</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="16" t="n"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I29" s="16" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J29" s="16" t="inlineStr">
+        <is>
+          <t>Whitepaper</t>
+        </is>
+      </c>
+      <c r="K29" s="16" t="inlineStr">
+        <is>
+          <t>Deployment patterns</t>
+        </is>
+      </c>
+      <c r="L29" s="16" t="inlineStr">
+        <is>
+          <t>Self‑hosted AI; Architecture; Governance</t>
+        </is>
+      </c>
+      <c r="M29" s="16" t="inlineStr">
+        <is>
+          <t>High (Mandatory for spec'ing out server node VRAM limits)</t>
+        </is>
+      </c>
+      <c r="N29" s="16" t="inlineStr">
+        <is>
+          <t>Mature</t>
+        </is>
+      </c>
+      <c r="O29" s="16" t="inlineStr">
+        <is>
+          <t>Breaks down the "Memory Wall" economics showing an on-prem breakeven velocity of ~4 months. Capabilities: Hardware performance scaling &amp; VRAM sizing.</t>
+        </is>
+      </c>
+      <c r="Q29" s="18" t="n">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="inlineStr">
+        <is>
+          <t>359b5ac8</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coalition for Secure AI (CoSAI) </t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>https://www.coalitionforsecureai.org/</t>
+        </is>
+      </c>
+      <c r="D30" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coalition for Secure AI (CoSAI) </t>
+        </is>
+      </c>
+      <c r="E30" s="14" t="n">
+        <v>46174</v>
+      </c>
+      <c r="F30" s="16" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H30" s="14" t="n">
+        <v>46174</v>
+      </c>
+      <c r="J30" s="16" t="inlineStr">
+        <is>
+          <t>Security Guidance &amp; Resources</t>
+        </is>
+      </c>
+      <c r="K30" s="16" t="inlineStr">
+        <is>
+          <t>Safety / guardrails; Safe Tool Use</t>
+        </is>
+      </c>
+      <c r="L30" s="16" t="inlineStr">
+        <is>
+          <t>Infrastructure Security; Security</t>
+        </is>
+      </c>
+      <c r="M30" s="16" t="inlineStr">
+        <is>
+          <t>Relevant security expertise and best practices for secure AI development and deployment</t>
+        </is>
+      </c>
+      <c r="N30" s="16" t="inlineStr">
+        <is>
+          <t>Emerging</t>
+        </is>
+      </c>
+      <c r="O30" s="16" t="inlineStr">
+        <is>
+          <t>The Coalition for Secure AI (CoSAI) is an open ecosystem of AI and security experts</t>
+        </is>
+      </c>
+      <c r="Q30" s="18" t="n">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="inlineStr">
+        <is>
+          <t>5f3954c2</t>
+        </is>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>Anthropic Project Glasswing</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/glasswing</t>
+        </is>
+      </c>
+      <c r="D31" s="16" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="n">
+        <v>46182</v>
+      </c>
+      <c r="F31" s="16" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H31" s="14" t="n">
+        <v>46119</v>
+      </c>
+      <c r="I31" s="15" t="n"/>
+      <c r="J31" s="16" t="inlineStr">
+        <is>
+          <t>Security Guidance &amp; Resources</t>
+        </is>
+      </c>
+      <c r="K31" s="16" t="inlineStr">
+        <is>
+          <t>Cybersecurity</t>
+        </is>
+      </c>
+      <c r="L31" s="16" t="inlineStr">
+        <is>
+          <t>Infrastructure Security; Security</t>
+        </is>
+      </c>
+      <c r="M31" s="16" t="inlineStr">
+        <is>
+          <t>AI models that find high-severity vulnerabilities</t>
+        </is>
+      </c>
+      <c r="N31" s="16" t="inlineStr">
+        <is>
+          <t>Emerging</t>
+        </is>
+      </c>
+      <c r="O31" s="5" t="inlineStr">
+        <is>
+          <t>See Claude Mythos Preview</t>
+        </is>
+      </c>
+      <c r="P31" s="18" t="n">
+        <v>46119</v>
+      </c>
+      <c r="Q31" s="18" t="n">
+        <v>46119</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="inlineStr">
+        <is>
+          <t>1c277820</t>
+        </is>
+      </c>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>Docker AI Governance &amp; Sandboxes</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>https://docs.docker.com/ai/sandboxes/governance/org/</t>
+        </is>
+      </c>
+      <c r="D32" s="16" t="inlineStr">
+        <is>
+          <t>Docker</t>
+        </is>
+      </c>
+      <c r="E32" s="14" t="n">
+        <v>46219</v>
+      </c>
+      <c r="F32" s="16" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H32" s="14" t="n">
+        <v>46213</v>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>0.35.0</t>
+        </is>
+      </c>
+      <c r="J32" s="16" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="I4" s="16" t="inlineStr">
-        <is>
-          <t>Hooks; Skills; API Integration</t>
-        </is>
-      </c>
-      <c r="J4" s="16" t="inlineStr">
-        <is>
-          <t>Architecture; Governance; Security</t>
-        </is>
-      </c>
-      <c r="K4" s="16" t="inlineStr">
-        <is>
-          <t>Relevant for CI/CD and code-review automation</t>
-        </is>
-      </c>
-      <c r="L4" s="16" t="inlineStr">
+      <c r="K32" s="16" t="inlineStr">
+        <is>
+          <t>Sandbox; MCP</t>
+        </is>
+      </c>
+      <c r="L32" s="16" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="M32" s="16" t="inlineStr">
+        <is>
+          <t>Good AI governance topics</t>
+        </is>
+      </c>
+      <c r="N32" s="16" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="O32" s="16" t="inlineStr">
+        <is>
+          <t>See blog article: https://www.docker.com/blog/the-3cs-a-framework-for-ai-agent-security/</t>
+        </is>
+      </c>
+      <c r="Q32" s="18" t="n">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="inlineStr">
+        <is>
+          <t>b39dc1d1</t>
+        </is>
+      </c>
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t>Responses API</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/guides/migrate-to-responses</t>
+        </is>
+      </c>
+      <c r="D33" s="16" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="E33" s="14" t="n">
+        <v>46220</v>
+      </c>
+      <c r="F33" s="16" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H33" s="14" t="n">
+        <v>46212</v>
+      </c>
+      <c r="I33" s="16" t="inlineStr">
+        <is>
+          <t>GPT-5.6</t>
+        </is>
+      </c>
+      <c r="J33" s="16" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="K33" s="16" t="inlineStr">
+        <is>
+          <t>Tools; Skills; Retrieval</t>
+        </is>
+      </c>
+      <c r="L33" s="16" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
+      <c r="M33" s="16" t="inlineStr">
+        <is>
+          <t>Useful for domain-specific agents</t>
+        </is>
+      </c>
+      <c r="N33" s="16" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="M4" s="16" t="inlineStr">
-        <is>
-          <t>Strong alignment with developer workflows.</t>
-        </is>
-      </c>
-      <c r="O4" s="18" t="n">
-        <v>46113</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="16" t="inlineStr">
-        <is>
-          <t>GitHub MCP Documentation</t>
-        </is>
-      </c>
-      <c r="B5" s="16" t="inlineStr">
-        <is>
-          <t>https://github.com/modelcontextprotocol</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>GitHub/OpenAI</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>46150</v>
-      </c>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="7" t="n">
-        <v>46113</v>
-      </c>
-      <c r="G5" s="16" t="n"/>
-      <c r="H5" s="16" t="inlineStr">
-        <is>
-          <t>API Reference</t>
-        </is>
-      </c>
-      <c r="I5" s="16" t="inlineStr">
-        <is>
-          <t>MCP; Tools; Server Integration</t>
-        </is>
-      </c>
-      <c r="J5" s="16" t="inlineStr">
-        <is>
-          <t>Architecture; Implementation</t>
-        </is>
-      </c>
-      <c r="K5" s="16" t="inlineStr">
-        <is>
-          <t>Key for interoperable agent tools</t>
-        </is>
-      </c>
-      <c r="L5" s="16" t="inlineStr">
-        <is>
-          <t>Emerging</t>
-        </is>
-      </c>
-      <c r="M5" s="16" t="inlineStr">
-        <is>
-          <t>Fast-moving ecosystem.</t>
-        </is>
-      </c>
-      <c r="O5" s="18" t="n">
-        <v>46113</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>OpenAI MCP Specification</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>https://spec.modelcontextprotocol.io</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>46150</v>
-      </c>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7" t="n">
-        <v>46113</v>
-      </c>
-      <c r="G6" s="16" t="n"/>
-      <c r="H6" s="16" t="inlineStr">
-        <is>
-          <t>Specification</t>
-        </is>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>MCP; Tools; Server Patterns</t>
-        </is>
-      </c>
-      <c r="J6" s="16" t="inlineStr">
-        <is>
-          <t>Architecture; Governance</t>
-        </is>
-      </c>
-      <c r="K6" s="16" t="inlineStr">
-        <is>
-          <t>Critical for cross-platform agent interoperability</t>
-        </is>
-      </c>
-      <c r="L6" s="16" t="inlineStr">
-        <is>
-          <t>Emerging</t>
-        </is>
-      </c>
-      <c r="M6" s="16" t="inlineStr">
-        <is>
-          <t>Becoming a de facto standard.</t>
-        </is>
-      </c>
-      <c r="O6" s="18" t="n">
-        <v>46113</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>Anthropic Model Context Protocol</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://modelcontextprotocol.io/specification/2025-11-25 </t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>46182</v>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>Paty Buendia</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>45962</v>
-      </c>
-      <c r="G7" s="11" t="n"/>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>Documentation</t>
-        </is>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>MCP; Agent Patterns</t>
-        </is>
-      </c>
-      <c r="J7" s="16" t="inlineStr">
-        <is>
-          <t>Architecture; Governance</t>
-        </is>
-      </c>
-      <c r="K7" s="16" t="inlineStr">
-        <is>
-          <t>Integration between LLM applications and external data sources and tools</t>
-        </is>
-      </c>
-      <c r="L7" s="16" t="inlineStr">
-        <is>
-          <t>Emerging</t>
-        </is>
-      </c>
-      <c r="M7" s="16" t="inlineStr">
-        <is>
-          <t>Strong safety emphasis.</t>
-        </is>
-      </c>
-      <c r="N7" s="18" t="n">
-        <v>45972</v>
-      </c>
-      <c r="O7" s="18" t="n">
-        <v>45962</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>Kaggle Prototype to Production Whitepaper</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>https://www.kaggle.com/whitepaper-prototype-to-production</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>Kaggle/Google</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>46157</v>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>Paty Buendia</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>45975</v>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>Whitepaper</t>
-        </is>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>Deployment patterns; Workflow Automation</t>
-        </is>
-      </c>
-      <c r="J8" s="16" t="inlineStr">
-        <is>
-          <t>Implementation; Security; Deployment</t>
-        </is>
-      </c>
-      <c r="K8" s="16" t="inlineStr">
-        <is>
-          <t>Helps teams move prototypes to production</t>
-        </is>
-      </c>
-      <c r="L8" s="16" t="inlineStr">
-        <is>
-          <t>Mature</t>
-        </is>
-      </c>
-      <c r="M8" s="16" t="inlineStr">
-        <is>
-          <t>Technical guide to the operational life cycle of AI agents, focusing on deployment &amp; security</t>
-        </is>
-      </c>
-      <c r="O8" s="18" t="n">
-        <v>45975</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>Google Vertex AI Agents Overview</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>https://cloud.google.com/vertex-ai/docs/agents</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>46150</v>
-      </c>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n">
-        <v>46113</v>
-      </c>
-      <c r="G9" s="16" t="n"/>
-      <c r="H9" s="16" t="inlineStr">
-        <is>
-          <t>Documentation</t>
-        </is>
-      </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>Agent frameworks; Orchestration</t>
-        </is>
-      </c>
-      <c r="J9" s="16" t="inlineStr">
-        <is>
-          <t>Architecture; Deployment</t>
-        </is>
-      </c>
-      <c r="K9" s="16" t="inlineStr">
-        <is>
-          <t>Useful for cloud-based scientific workflows</t>
-        </is>
-      </c>
-      <c r="L9" s="16" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="M9" s="16" t="inlineStr">
-        <is>
-          <t>Strong enterprise alignment.</t>
-        </is>
-      </c>
-      <c r="O9" s="18" t="n">
-        <v>46113</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>HuggingFace Agents Documentation</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/docs/agents</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>HuggingFace</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>46150</v>
-      </c>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7" t="n">
-        <v>46082</v>
-      </c>
-      <c r="G10" s="16" t="n"/>
-      <c r="H10" s="16" t="inlineStr">
-        <is>
-          <t>Documentation</t>
-        </is>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>Tools; Skills; Model Integration</t>
-        </is>
-      </c>
-      <c r="J10" s="16" t="inlineStr">
-        <is>
-          <t>Architecture; Implementation</t>
-        </is>
-      </c>
-      <c r="K10" s="16" t="inlineStr">
-        <is>
-          <t>Useful for open-source agent experimentation</t>
-        </is>
-      </c>
-      <c r="L10" s="16" t="inlineStr">
-        <is>
-          <t>Emerging</t>
-        </is>
-      </c>
-      <c r="M10" s="16" t="inlineStr">
-        <is>
-          <t>Rapidly evolving.</t>
-        </is>
-      </c>
-      <c r="O10" s="18" t="n">
-        <v>46082</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="16" t="inlineStr">
-        <is>
-          <t>LangChain Agents Overview</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>https://python.langchain.com/docs/modules/agents</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>LangChain</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>46150</v>
-      </c>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n">
-        <v>46113</v>
-      </c>
-      <c r="G11" s="16" t="n"/>
-      <c r="H11" s="16" t="inlineStr">
-        <is>
-          <t>Documentation</t>
-        </is>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>Tools; Skills; Multi-Agent Patterns</t>
-        </is>
-      </c>
-      <c r="J11" s="16" t="inlineStr">
-        <is>
-          <t>Architecture; Implementation</t>
-        </is>
-      </c>
-      <c r="K11" s="16" t="inlineStr">
-        <is>
-          <t>Relevant for workflow prototyping</t>
-        </is>
-      </c>
-      <c r="L11" s="16" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="M11" s="16" t="inlineStr">
-        <is>
-          <t>Widely used in research.</t>
-        </is>
-      </c>
-      <c r="O11" s="18" t="n">
-        <v>46113</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>LlamaIndex Agents</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>https://docs.llamaindex.ai/en/stable/agent/</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>LlamaIndex</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>46150</v>
-      </c>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n">
-        <v>46113</v>
-      </c>
-      <c r="G12" s="16" t="n"/>
-      <c r="H12" s="16" t="inlineStr">
-        <is>
-          <t>Documentation</t>
-        </is>
-      </c>
-      <c r="I12" s="16" t="inlineStr">
-        <is>
-          <t>Tools; Skills; Retrieval Agents</t>
-        </is>
-      </c>
-      <c r="J12" s="16" t="inlineStr">
-        <is>
-          <t>Architecture; Governance</t>
-        </is>
-      </c>
-      <c r="K12" s="16" t="inlineStr">
-        <is>
-          <t>Useful for data-rich research platforms</t>
-        </is>
-      </c>
-      <c r="L12" s="16" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="M12" s="16" t="inlineStr">
-        <is>
-          <t>Strong retrieval-centric design.</t>
-        </is>
-      </c>
-      <c r="O12" s="18" t="n">
-        <v>46113</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>Dagster Automation/Agent Patterns</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>https://docs.dagster.io/getting-started/ai-tools</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>Dagster Labs</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>Paty Buendia</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>46082</v>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>1.3.15</t>
-        </is>
-      </c>
-      <c r="H13" s="16" t="inlineStr">
-        <is>
-          <t>Documentation</t>
-        </is>
-      </c>
-      <c r="I13" s="16" t="inlineStr">
-        <is>
-          <t>Workflow Automation; Orchestration</t>
-        </is>
-      </c>
-      <c r="J13" s="16" t="inlineStr">
-        <is>
-          <t>Architecture; Deployment</t>
-        </is>
-      </c>
-      <c r="K13" s="16" t="inlineStr">
-        <is>
-          <t>Relevant for scientific pipelines</t>
-        </is>
-      </c>
-      <c r="L13" s="16" t="inlineStr">
-        <is>
-          <t>Mature</t>
-        </is>
-      </c>
-      <c r="M13" s="16" t="inlineStr">
-        <is>
-          <t>Strong reproducibility focus.</t>
-        </is>
-      </c>
-      <c r="O13" s="18" t="n">
-        <v>46082</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>Prefect Automations/Agents</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>https://docs.prefect.io/latest/concepts/automations/</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>Prefect</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>46150</v>
-      </c>
-      <c r="E14" s="7" t="n"/>
-      <c r="F14" s="7" t="n">
-        <v>46082</v>
-      </c>
-      <c r="G14" s="16" t="n"/>
-      <c r="H14" s="16" t="inlineStr">
-        <is>
-          <t>Documentation</t>
-        </is>
-      </c>
-      <c r="I14" s="16" t="inlineStr">
-        <is>
-          <t>Workflow Agents; Triggers</t>
-        </is>
-      </c>
-      <c r="J14" s="16" t="inlineStr">
-        <is>
-          <t>Implementation; Deployment</t>
-        </is>
-      </c>
-      <c r="K14" s="16" t="inlineStr">
-        <is>
-          <t>Useful for data processing pipelines</t>
-        </is>
-      </c>
-      <c r="L14" s="16" t="inlineStr">
-        <is>
-          <t>Mature</t>
-        </is>
-      </c>
-      <c r="M14" s="16" t="inlineStr">
-        <is>
-          <t>Good hybrid cloud/HPC support.</t>
-        </is>
-      </c>
-      <c r="O14" s="18" t="n">
-        <v>46082</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t>Jupyter AI</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>https://jupyter-ai.readthedocs.io</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>Project Jupyter</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7" t="n">
-        <v>46113</v>
-      </c>
-      <c r="G15" s="16" t="n"/>
-      <c r="H15" s="16" t="inlineStr">
-        <is>
-          <t>Documentation</t>
-        </is>
-      </c>
-      <c r="I15" s="16" t="inlineStr">
-        <is>
-          <t>Notebook Agents; Workflow Automation</t>
-        </is>
-      </c>
-      <c r="J15" s="16" t="inlineStr">
-        <is>
-          <t>Implementation; Data governance</t>
-        </is>
-      </c>
-      <c r="K15" s="16" t="inlineStr">
-        <is>
-          <t>Relevant for research notebooks</t>
-        </is>
-      </c>
-      <c r="L15" s="16" t="inlineStr">
-        <is>
-          <t>Emerging</t>
-        </is>
-      </c>
-      <c r="M15" s="16" t="inlineStr">
-        <is>
-          <t>Strong alignment with scientific workflows.</t>
-        </is>
-      </c>
-      <c r="O15" s="18" t="n">
-        <v>46113</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="16" t="inlineStr">
-        <is>
-          <t>Anthropic Tools API</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>https://docs.anthropic.com/en/docs/tools</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>46150</v>
-      </c>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="7" t="n">
-        <v>46113</v>
-      </c>
-      <c r="G16" s="16" t="n"/>
-      <c r="H16" s="16" t="inlineStr">
-        <is>
-          <t>API Reference</t>
-        </is>
-      </c>
-      <c r="I16" s="16" t="inlineStr">
-        <is>
-          <t>Tools; Skills</t>
-        </is>
-      </c>
-      <c r="J16" s="16" t="inlineStr">
-        <is>
-          <t>Architecture; Security</t>
-        </is>
-      </c>
-      <c r="K16" s="16" t="inlineStr">
-        <is>
-          <t>Useful for safe tool-calling agents</t>
-        </is>
-      </c>
-      <c r="L16" s="16" t="inlineStr">
-        <is>
-          <t>Emerging</t>
-        </is>
-      </c>
-      <c r="M16" s="16" t="inlineStr">
-        <is>
-          <t>Strong safety posture.</t>
-        </is>
-      </c>
-      <c r="O16" s="18" t="n">
-        <v>46113</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="16" t="inlineStr">
-        <is>
-          <t>Microsoft Semantic Kernel Agents</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>https://learn.microsoft.com/semantic-kernel/agents</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>46150</v>
-      </c>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n">
-        <v>46113</v>
-      </c>
-      <c r="G17" s="16" t="n"/>
-      <c r="H17" s="16" t="inlineStr">
-        <is>
-          <t>Documentation</t>
-        </is>
-      </c>
-      <c r="I17" s="16" t="inlineStr">
-        <is>
-          <t>Skills; Tools; Orchestration</t>
-        </is>
-      </c>
-      <c r="J17" s="16" t="inlineStr">
-        <is>
-          <t>Architecture; Implementation</t>
-        </is>
-      </c>
-      <c r="K17" s="16" t="inlineStr">
-        <is>
-          <t>Useful for enterprise-grade agent workflows</t>
-        </is>
-      </c>
-      <c r="L17" s="16" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="M17" s="16" t="inlineStr">
-        <is>
-          <t>Strong .NET + Python support.</t>
-        </is>
-      </c>
-      <c r="O17" s="18" t="n">
-        <v>46113</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="16" t="inlineStr">
-        <is>
-          <t>HuggingFace Inference Endpoints</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/inference-endpoints</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>HuggingFace</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>46150</v>
-      </c>
-      <c r="E18" s="7" t="n"/>
-      <c r="F18" s="7" t="n">
-        <v>46082</v>
-      </c>
-      <c r="G18" s="16" t="n"/>
-      <c r="H18" s="16" t="inlineStr">
-        <is>
-          <t>Documentation</t>
-        </is>
-      </c>
-      <c r="I18" s="16" t="inlineStr">
-        <is>
-          <t>Model Integration; Tool-Ready Endpoints</t>
-        </is>
-      </c>
-      <c r="J18" s="16" t="inlineStr">
-        <is>
-          <t>Architecture; Deployment</t>
-        </is>
-      </c>
-      <c r="K18" s="16" t="inlineStr">
-        <is>
-          <t>Useful for hosted inference in research</t>
-        </is>
-      </c>
-      <c r="L18" s="16" t="inlineStr">
-        <is>
-          <t>Mature</t>
-        </is>
-      </c>
-      <c r="M18" s="16" t="inlineStr">
-        <is>
-          <t>Good for reproducibility.</t>
-        </is>
-      </c>
-      <c r="O18" s="18" t="n">
-        <v>46082</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>OpenAI Evaluations (Evals)</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>https://platform.openai.com/docs/guides/evals</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>46150</v>
-      </c>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="7" t="n">
-        <v>46113</v>
-      </c>
-      <c r="G19" s="16" t="n"/>
-      <c r="H19" s="16" t="inlineStr">
-        <is>
-          <t>Documentation</t>
-        </is>
-      </c>
-      <c r="I19" s="16" t="inlineStr">
-        <is>
-          <t>Evaluation / testing; Safety / guardrails</t>
-        </is>
-      </c>
-      <c r="J19" s="16" t="inlineStr">
-        <is>
-          <t>Security; Governance</t>
-        </is>
-      </c>
-      <c r="K19" s="16" t="inlineStr">
-        <is>
-          <t>Relevant for agent safety in research platforms</t>
-        </is>
-      </c>
-      <c r="L19" s="16" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="M19" s="16" t="inlineStr">
-        <is>
-          <t>Useful for risk assessment.</t>
-        </is>
-      </c>
-      <c r="O19" s="18" t="n">
-        <v>46113</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>Anthropic Safety Guidelines</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>https://docs.anthropic.com/en/docs/safety</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="n">
-        <v>46150</v>
-      </c>
-      <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="n">
-        <v>46113</v>
-      </c>
-      <c r="G20" s="16" t="n"/>
-      <c r="H20" s="16" t="inlineStr">
-        <is>
-          <t>Documentation</t>
-        </is>
-      </c>
-      <c r="I20" s="16" t="inlineStr">
-        <is>
-          <t>Safety / guardrails; Safe Tool Use</t>
-        </is>
-      </c>
-      <c r="J20" s="16" t="inlineStr">
-        <is>
-          <t>Governance; Security</t>
-        </is>
-      </c>
-      <c r="K20" s="16" t="inlineStr">
-        <is>
-          <t>Useful for research governance teams</t>
-        </is>
-      </c>
-      <c r="L20" s="16" t="inlineStr">
-        <is>
-          <t>Mature</t>
-        </is>
-      </c>
-      <c r="M20" s="16" t="inlineStr">
-        <is>
-          <t>Strong alignment with institutional risk controls.</t>
-        </is>
-      </c>
-      <c r="O20" s="18" t="n">
-        <v>46113</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t>Microsoft Responsible AI Standard</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>https://www.microsoft.com/ai/responsible-ai</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="n">
-        <v>46150</v>
-      </c>
-      <c r="E21" s="12" t="n"/>
-      <c r="F21" s="12" t="n">
-        <v>45992</v>
-      </c>
-      <c r="G21" s="16" t="n"/>
-      <c r="H21" s="16" t="inlineStr">
-        <is>
-          <t>Governance Guidance</t>
-        </is>
-      </c>
-      <c r="I21" s="16" t="inlineStr">
-        <is>
-          <t>Safety / guardrails; Governance; Risk Controls</t>
-        </is>
-      </c>
-      <c r="J21" s="16" t="inlineStr">
-        <is>
-          <t>Data governance; Security</t>
-        </is>
-      </c>
-      <c r="K21" s="16" t="inlineStr">
-        <is>
-          <t>Relevant for institutional AI governance</t>
-        </is>
-      </c>
-      <c r="L21" s="16" t="inlineStr">
-        <is>
-          <t>Mature</t>
-        </is>
-      </c>
-      <c r="M21" s="16" t="inlineStr">
-        <is>
-          <t>Widely adopted governance framework.</t>
-        </is>
-      </c>
-      <c r="O21" s="18" t="n">
-        <v>45992</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="16" t="inlineStr">
-        <is>
-          <t>vLLM Documentation</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>https://docs.vllm.ai</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>vLLM Project Team</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="n"/>
-      <c r="F22" s="7" t="n">
-        <v>46113</v>
-      </c>
-      <c r="G22" s="16" t="n"/>
-      <c r="H22" s="16" t="inlineStr">
-        <is>
-          <t>Inference Framework</t>
-        </is>
-      </c>
-      <c r="I22" s="16" t="inlineStr">
-        <is>
-          <t>Deployment patterns; Tools</t>
-        </is>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>Self‑hosted AI; Architecture; Implementation; Deployment</t>
-        </is>
-      </c>
-      <c r="K22" s="16" t="inlineStr">
-        <is>
-          <t>High (Industry-standard VPC runtime engine)</t>
-        </is>
-      </c>
-      <c r="L22" s="16" t="inlineStr">
-        <is>
-          <t>Mature</t>
-        </is>
-      </c>
-      <c r="M22" s="16" t="inlineStr">
-        <is>
-          <t>Essential for secure TLAs via PagedAttention and FP8/AWQ optimization. Capabilities: Parallel sampling &amp; tool-calling.</t>
-        </is>
-      </c>
-      <c r="O22" s="18" t="n">
-        <v>46113</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="16" t="inlineStr">
-        <is>
-          <t>Ollama Documentation</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>https://github.com/ollama/ollama</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>Ollama Community</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>46150</v>
-      </c>
-      <c r="F23" s="7" t="n">
-        <v>46113</v>
-      </c>
-      <c r="G23" s="16" t="n"/>
-      <c r="H23" s="16" t="inlineStr">
-        <is>
-          <t>Local Application Sandbox</t>
-        </is>
-      </c>
-      <c r="I23" s="16" t="inlineStr">
-        <is>
-          <t>Deployment patterns</t>
-        </is>
-      </c>
-      <c r="J23" s="16" t="inlineStr">
-        <is>
-          <t>Self‑hosted AI; Implementation; Deployment</t>
-        </is>
-      </c>
-      <c r="K23" s="16" t="inlineStr">
-        <is>
-          <t>Medium-High (Local workstation co-pilot)</t>
-        </is>
-      </c>
-      <c r="L23" s="16" t="inlineStr">
-        <is>
-          <t>Mature</t>
-        </is>
-      </c>
-      <c r="M23" s="16" t="inlineStr">
-        <is>
-          <t>Eliminates network dependency errors by cleanly bundling open model weights. Capabilities: Local embedding &amp; zero-config tools.</t>
-        </is>
-      </c>
-      <c r="O23" s="18" t="n">
-        <v>46113</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Llama.cpp </t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>https://github.com/ggerganov/llama.cpp</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>Georgi Gerganov</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="n"/>
-      <c r="E24" s="16" t="n"/>
-      <c r="F24" s="14" t="n">
-        <v>46162</v>
-      </c>
-      <c r="G24" s="16" t="inlineStr">
-        <is>
-          <t>b9253</t>
-        </is>
-      </c>
-      <c r="H24" s="16" t="inlineStr">
-        <is>
-          <t>Github Code Repository</t>
-        </is>
-      </c>
-      <c r="I24" s="16" t="inlineStr">
-        <is>
-          <t>Deployment patterns</t>
-        </is>
-      </c>
-      <c r="J24" s="16" t="inlineStr">
-        <is>
-          <t>Self‑hosted AI; Architecture; Implementation; Deployment</t>
-        </is>
-      </c>
-      <c r="K24" s="16" t="inlineStr">
-        <is>
-          <t>High (Enables reasoning on variable local hardware)</t>
-        </is>
-      </c>
-      <c r="L24" s="16" t="inlineStr">
-        <is>
-          <t>Mature</t>
-        </is>
-      </c>
-      <c r="M24" s="16" t="inlineStr">
-        <is>
-          <t>Grammar constraints ensure localized agentic pipelines always return valid JSON/code. Capabilities: Grammar-based constrained sampling.</t>
-        </is>
-      </c>
-      <c r="O24" s="18" t="n">
-        <v>46162</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="16" t="inlineStr">
-        <is>
-          <t>Open WebUI Documentation</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>https://docs.openwebui.com</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>Open WebUI Core Team</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>46150</v>
-      </c>
-      <c r="F25" s="7" t="n">
-        <v>46113</v>
-      </c>
-      <c r="G25" s="16" t="n"/>
-      <c r="H25" s="16" t="inlineStr">
-        <is>
-          <t>Enterprise Control Interface</t>
-        </is>
-      </c>
-      <c r="I25" s="16" t="inlineStr">
-        <is>
-          <t>Retrieval</t>
-        </is>
-      </c>
-      <c r="J25" s="16" t="inlineStr">
-        <is>
-          <t>Self‑hosted AI; Implementation; Deployment</t>
-        </is>
-      </c>
-      <c r="K25" s="16" t="inlineStr">
-        <is>
-          <t>High (Enterprise-grade firewall interface)</t>
-        </is>
-      </c>
-      <c r="L25" s="16" t="inlineStr">
-        <is>
-          <t>Mature</t>
-        </is>
-      </c>
-      <c r="M25" s="16" t="inlineStr">
-        <is>
-          <t>Solves local file parsing/RAG bottlenecks entirely within secure client networks. Capabilities: Local RAG pipelines &amp; offline functions.</t>
-        </is>
-      </c>
-      <c r="O25" s="18" t="n">
-        <v>46113</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="16" t="inlineStr">
-        <is>
-          <t>NVIDIA NIM Air-Gap Deployment Guide</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>https://docs.nvidia.com/nim/large-language-models/latest/deploy-air-gap.html</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>NVIDIA</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="n"/>
-      <c r="F26" s="16" t="n">
-        <v>2026</v>
-      </c>
-      <c r="G26" s="16" t="n"/>
-      <c r="H26" s="16" t="inlineStr">
-        <is>
-          <t>Reference Architecture</t>
-        </is>
-      </c>
-      <c r="I26" s="16" t="inlineStr">
-        <is>
-          <t>Deployment patterns</t>
-        </is>
-      </c>
-      <c r="J26" s="16" t="inlineStr">
-        <is>
-          <t>Self‑hosted AI; Compute Infrastructure; Implementation; Network Isolation; Infrastructure Security</t>
-        </is>
-      </c>
-      <c r="K26" s="16" t="inlineStr">
-        <is>
-          <t>Critical (Standardizes secure distribution of optimized weights)</t>
-        </is>
-      </c>
-      <c r="L26" s="16" t="inlineStr">
-        <is>
-          <t>Mature</t>
-        </is>
-      </c>
-      <c r="M26" s="16" t="inlineStr">
-        <is>
-          <t>Outlines the exact connected-to-disconnected asset transfer workflow for enterprise GPUs. Capabilities: Tensor-parallel caching &amp; optimized tool-calling.</t>
-        </is>
-      </c>
-      <c r="O26" s="18" t="n">
-        <v>46150</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="16" t="inlineStr">
-        <is>
-          <t>Harbor User Documentation</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>https://goharbor.io/docs/</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>Cloud Native Computing Foundation (CNCF)</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="n">
-        <v>46150</v>
-      </c>
-      <c r="F27" s="16" t="n">
-        <v>2026</v>
-      </c>
-      <c r="G27" s="16" t="n"/>
-      <c r="H27" s="16" t="inlineStr">
-        <is>
-          <t>Container Registry</t>
-        </is>
-      </c>
-      <c r="I27" s="16" t="inlineStr">
-        <is>
-          <t>Deployment patterns</t>
-        </is>
-      </c>
-      <c r="J27" s="16" t="inlineStr">
-        <is>
-          <t>Self‑hosted AI; Implementation; Network Isolation; Infrastructure Security; Governance</t>
-        </is>
-      </c>
-      <c r="K27" s="16" t="inlineStr">
-        <is>
-          <t>High (Necessary foundation for secure cluster registries)</t>
-        </is>
-      </c>
-      <c r="L27" s="16" t="inlineStr">
-        <is>
-          <t>Mature</t>
-        </is>
-      </c>
-      <c r="M27" s="16" t="inlineStr">
-        <is>
-          <t>Built-in vulnerability scanning ensures agent images remain clean behind the firewall. Capabilities: Artifact version-locking &amp; immutable tags.</t>
-        </is>
-      </c>
-      <c r="O27" s="18" t="n">
-        <v>46150</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="16" t="inlineStr">
-        <is>
-          <t>AI Engineering Blueprint for On-Premises RAG Systems</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2604.01395</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>arXiv (2604.01395)</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="n">
-        <v>46150</v>
-      </c>
-      <c r="F28" s="16" t="n">
-        <v>2026</v>
-      </c>
-      <c r="G28" s="16" t="n"/>
-      <c r="H28" s="16" t="inlineStr">
-        <is>
-          <t>Scientific Literature</t>
-        </is>
-      </c>
-      <c r="I28" s="16" t="inlineStr">
-        <is>
-          <t>Deployment patterns; Retrieval</t>
-        </is>
-      </c>
-      <c r="J28" s="16" t="inlineStr">
-        <is>
-          <t>Self‑hosted AI; Infrastructure Security</t>
-        </is>
-      </c>
-      <c r="K28" s="16" t="inlineStr">
-        <is>
-          <t>High (Academic/industry validated system design blueprint)</t>
-        </is>
-      </c>
-      <c r="L28" s="16" t="inlineStr">
-        <is>
-          <t>Emerging</t>
-        </is>
-      </c>
-      <c r="M28" s="16" t="inlineStr">
-        <is>
-          <t>Moves past simple how-to guides into formal data isolation and local compliance frameworks. Capabilities: End-to-end local reference applications.</t>
-        </is>
-      </c>
-      <c r="O28" s="18" t="n">
-        <v>46150</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="16" t="inlineStr">
-        <is>
-          <t>On-Premise vs Cloud: GenAI TCO (2026 Edition)</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://lenovopress.lenovo.com/lp2368-on-premise-vs-cloud-generative-ai-total-cost-of-ownership-2026-edition </t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>Lenovo Press</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="16" t="n"/>
-      <c r="F29" s="7" t="n">
-        <v>46054</v>
-      </c>
-      <c r="G29" s="16" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H29" s="16" t="inlineStr">
-        <is>
-          <t>Whitepaper</t>
-        </is>
-      </c>
-      <c r="I29" s="16" t="inlineStr">
-        <is>
-          <t>Deployment patterns</t>
-        </is>
-      </c>
-      <c r="J29" s="16" t="inlineStr">
-        <is>
-          <t>Self‑hosted AI; Architecture; Governance</t>
-        </is>
-      </c>
-      <c r="K29" s="16" t="inlineStr">
-        <is>
-          <t>High (Mandatory for spec'ing out server node VRAM limits)</t>
-        </is>
-      </c>
-      <c r="L29" s="16" t="inlineStr">
-        <is>
-          <t>Mature</t>
-        </is>
-      </c>
-      <c r="M29" s="16" t="inlineStr">
-        <is>
-          <t>Breaks down the "Memory Wall" economics showing an on-prem breakeven velocity of ~4 months. Capabilities: Hardware performance scaling &amp; VRAM sizing.</t>
-        </is>
-      </c>
-      <c r="O29" s="18" t="n">
-        <v>46054</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Coalition for Secure AI (CoSAI) </t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>https://www.coalitionforsecureai.org/</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Coalition for Secure AI (CoSAI) </t>
-        </is>
-      </c>
-      <c r="D30" s="14" t="n">
-        <v>46174</v>
-      </c>
-      <c r="E30" s="16" t="inlineStr">
-        <is>
-          <t>Paty Buendia</t>
-        </is>
-      </c>
-      <c r="F30" s="14" t="n">
-        <v>46174</v>
-      </c>
-      <c r="H30" s="16" t="inlineStr">
-        <is>
-          <t>Security Guidance &amp; Resources</t>
-        </is>
-      </c>
-      <c r="I30" s="16" t="inlineStr">
-        <is>
-          <t>Safety / guardrails; Safe Tool Use</t>
-        </is>
-      </c>
-      <c r="J30" s="16" t="inlineStr">
-        <is>
-          <t>Infrastructure Security; Security</t>
-        </is>
-      </c>
-      <c r="K30" s="16" t="inlineStr">
-        <is>
-          <t>Relevant security expertise and best practices for secure AI development and deployment</t>
-        </is>
-      </c>
-      <c r="L30" s="16" t="inlineStr">
-        <is>
-          <t>Emerging</t>
-        </is>
-      </c>
-      <c r="M30" s="16" t="inlineStr">
-        <is>
-          <t>The Coalition for Secure AI (CoSAI) is an open ecosystem of AI and security experts</t>
-        </is>
-      </c>
-      <c r="O30" s="18" t="n">
-        <v>46174</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="16" t="inlineStr">
-        <is>
-          <t>Anthropic Project Glasswing</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>https://www.anthropic.com/glasswing</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="D31" s="14" t="n">
-        <v>46182</v>
-      </c>
-      <c r="E31" s="16" t="inlineStr">
-        <is>
-          <t>Paty Buendia</t>
-        </is>
-      </c>
-      <c r="F31" s="14" t="n">
-        <v>46119</v>
-      </c>
-      <c r="G31" s="15" t="n"/>
-      <c r="H31" s="16" t="inlineStr">
-        <is>
-          <t>Security Guidance &amp; Resources</t>
-        </is>
-      </c>
-      <c r="I31" s="16" t="inlineStr">
-        <is>
-          <t>Cybersecurity</t>
-        </is>
-      </c>
-      <c r="J31" s="16" t="inlineStr">
-        <is>
-          <t>Infrastructure Security; Security</t>
-        </is>
-      </c>
-      <c r="K31" s="16" t="inlineStr">
-        <is>
-          <t>AI models that find high-severity vulnerabilities</t>
-        </is>
-      </c>
-      <c r="L31" s="16" t="inlineStr">
-        <is>
-          <t>Emerging</t>
-        </is>
-      </c>
-      <c r="M31" s="5" t="inlineStr">
-        <is>
-          <t>See Claude Mythos Preview</t>
-        </is>
-      </c>
-      <c r="N31" s="18" t="n">
-        <v>46119</v>
-      </c>
-      <c r="O31" s="18" t="n">
-        <v>46119</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="16" t="inlineStr">
-        <is>
-          <t>Docker AI Governance &amp; Sandboxes</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>https://docs.docker.com/ai/sandboxes/governance/org/</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>Docker</t>
-        </is>
-      </c>
-      <c r="D32" s="14" t="n">
-        <v>46219</v>
-      </c>
-      <c r="E32" s="16" t="inlineStr">
-        <is>
-          <t>Paty Buendia</t>
-        </is>
-      </c>
-      <c r="F32" s="14" t="n">
-        <v>46213</v>
-      </c>
-      <c r="G32" s="9" t="inlineStr">
-        <is>
-          <t>0.35.0</t>
-        </is>
-      </c>
-      <c r="H32" s="16" t="inlineStr">
-        <is>
-          <t>Documentation</t>
-        </is>
-      </c>
-      <c r="I32" s="16" t="inlineStr">
-        <is>
-          <t>Sandbox; MCP</t>
-        </is>
-      </c>
-      <c r="J32" s="16" t="inlineStr">
-        <is>
-          <t>Security</t>
-        </is>
-      </c>
-      <c r="K32" s="16" t="inlineStr">
-        <is>
-          <t>Good AI governance topics</t>
-        </is>
-      </c>
-      <c r="L32" s="16" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="M32" s="16" t="inlineStr">
-        <is>
-          <t>See blog article: https://www.docker.com/blog/the-3cs-a-framework-for-ai-agent-security/</t>
-        </is>
-      </c>
-      <c r="O32" s="18" t="n">
-        <v>46213</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="16" t="inlineStr">
-        <is>
-          <t>Responses API</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>https://developers.openai.com/api/docs/guides/migrate-to-responses</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="D33" s="14" t="n">
-        <v>46220</v>
-      </c>
-      <c r="E33" s="16" t="inlineStr">
-        <is>
-          <t>Paty Buendia</t>
-        </is>
-      </c>
-      <c r="F33" s="14" t="n">
+      <c r="O33" s="16" t="inlineStr">
+        <is>
+          <t>MIgrated from API Assistants  - now deprecated.</t>
+        </is>
+      </c>
+      <c r="Q33" s="18" t="n">
         <v>46212</v>
       </c>
-      <c r="G33" s="16" t="inlineStr">
-        <is>
-          <t>GPT-5.6</t>
-        </is>
-      </c>
-      <c r="H33" s="16" t="inlineStr">
-        <is>
-          <t>Documentation</t>
-        </is>
-      </c>
-      <c r="I33" s="16" t="inlineStr">
-        <is>
-          <t>Tools; Skills; Retrieval</t>
-        </is>
-      </c>
-      <c r="J33" s="16" t="inlineStr">
-        <is>
-          <t>Architecture</t>
-        </is>
-      </c>
-      <c r="K33" s="16" t="inlineStr">
-        <is>
-          <t>Useful for domain-specific agents</t>
-        </is>
-      </c>
-      <c r="L33" s="16" t="inlineStr">
-        <is>
-          <t>Emerging</t>
-        </is>
-      </c>
-      <c r="M33" s="16" t="inlineStr">
-        <is>
-          <t>MIgrated from API Assistants  - now deprecated.</t>
-        </is>
-      </c>
-      <c r="O33" s="18" t="n">
-        <v>46212</v>
-      </c>
     </row>
     <row r="34">
-      <c r="J34" s="16" t="n"/>
+      <c r="L34" s="16" t="n"/>
     </row>
     <row r="35">
-      <c r="J35" s="16" t="n"/>
+      <c r="L35" s="16" t="n"/>
     </row>
     <row r="36">
-      <c r="J36" s="16" t="n"/>
+      <c r="L36" s="16" t="n"/>
     </row>
     <row r="37">
-      <c r="J37" s="16" t="n"/>
+      <c r="L37" s="16" t="n"/>
     </row>
     <row r="38">
-      <c r="J38" s="16" t="n"/>
+      <c r="L38" s="16" t="n"/>
     </row>
     <row r="39">
-      <c r="J39" s="16" t="n"/>
+      <c r="L39" s="16" t="n"/>
     </row>
     <row r="40">
-      <c r="J40" s="16" t="n"/>
+      <c r="L40" s="16" t="n"/>
     </row>
     <row r="41">
-      <c r="J41" s="16" t="n"/>
+      <c r="L41" s="16" t="n"/>
     </row>
     <row r="42">
-      <c r="J42" s="16" t="n"/>
+      <c r="L42" s="16" t="n"/>
     </row>
     <row r="43">
-      <c r="J43" s="16" t="n"/>
+      <c r="L43" s="16" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="L1:L994">
@@ -2493,11 +2792,6 @@
       <formula>LEN(TRIM(J1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation sqref="J2:J994" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>"Architecture,Deployment,Governance,Implementation,Security,Data Governance,Network Isolation,Infrastructure Security,Self‑hosted AI,Workflows,Architecture, Deployment,Architecture, Governance,Architecture, Governance, Security,Architecture, Implementation"&amp;",Architecture, Implementation, Deployment,Architecture, Security,Data Governance; Security,Governance; Security,Implementation, Data Governance,Implementation, Deployment,Implementation, Network Isolation, Infrastructure Security,Implementation, Network I"&amp;"solation, Infrastructure Security, Governance,Implementation, Security, Deployment,Security; Governance"</formula1>
-    </dataValidation>
-  </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId2"/>
@@ -2524,143 +2818,165 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
+    <col width="10" customWidth="1" style="17" min="1" max="1"/>
     <col width="22.13" customWidth="1" style="17" min="2" max="2"/>
+    <col width="20" customWidth="1" style="17" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>Resource Name</t>
         </is>
       </c>
-      <c r="B1" s="16" t="inlineStr">
+      <c r="C1" s="16" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="C1" s="16" t="inlineStr">
+      <c r="D1" s="16" t="inlineStr">
         <is>
           <t>Source Organization</t>
         </is>
       </c>
-      <c r="D1" s="16" t="inlineStr">
+      <c r="E1" s="16" t="inlineStr">
         <is>
           <t>Last Verified</t>
         </is>
       </c>
-      <c r="E1" s="16" t="inlineStr">
+      <c r="F1" s="16" t="inlineStr">
         <is>
           <t>Verified By</t>
         </is>
       </c>
-      <c r="F1" s="16" t="inlineStr">
-        <is>
-          <t>Deprecation Date</t>
-        </is>
-      </c>
-      <c r="G1" s="16" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Added/Edited By</t>
+        </is>
+      </c>
+      <c r="H1" s="16" t="inlineStr">
+        <is>
+          <t>Deprecation Date / Last Updated</t>
+        </is>
+      </c>
+      <c r="I1" s="16" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
       </c>
-      <c r="H1" s="16" t="inlineStr">
+      <c r="J1" s="16" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="I1" s="16" t="inlineStr">
+      <c r="K1" s="16" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="J1" s="16" t="inlineStr">
+      <c r="L1" s="16" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="K1" s="16" t="inlineStr">
+      <c r="M1" s="16" t="inlineStr">
         <is>
           <t>Relevance to Research Cyberinfrastructure</t>
         </is>
       </c>
-      <c r="L1" s="16" t="inlineStr">
+      <c r="N1" s="16" t="inlineStr">
         <is>
           <t>Maturity Level</t>
         </is>
       </c>
-      <c r="M1" s="16" t="inlineStr">
+      <c r="O1" s="16" t="inlineStr">
         <is>
           <t>Notes / Key Takeaways</t>
         </is>
       </c>
-      <c r="N1" s="0" t="inlineStr">
+      <c r="P1" s="0" t="inlineStr">
         <is>
           <t>Discovery Date</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>805047b4</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>OpenAI Assistants API</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>https://platform.openai.com/docs/assistants</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr">
         <is>
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="E2" s="6" t="n">
         <v>46150</v>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="F2" s="7" t="n">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="n">
         <v>46260</v>
       </c>
-      <c r="G2" s="16" t="n"/>
-      <c r="H2" s="16" t="inlineStr">
+      <c r="I2" s="16" t="n"/>
+      <c r="J2" s="16" t="inlineStr">
         <is>
           <t>API Reference</t>
         </is>
       </c>
-      <c r="I2" s="16" t="inlineStr">
+      <c r="K2" s="16" t="inlineStr">
         <is>
           <t>Tools; Skills; Retrieval</t>
         </is>
       </c>
-      <c r="J2" s="16" t="inlineStr">
+      <c r="L2" s="16" t="inlineStr">
         <is>
           <t>Architecture; Implementation</t>
         </is>
       </c>
-      <c r="K2" s="16" t="inlineStr">
+      <c r="M2" s="16" t="inlineStr">
         <is>
           <t>Useful for domain-specific agents</t>
         </is>
       </c>
-      <c r="L2" s="16" t="inlineStr">
+      <c r="N2" s="16" t="inlineStr">
         <is>
           <t>Deprecated</t>
         </is>
       </c>
-      <c r="M2" s="16" t="inlineStr">
+      <c r="O2" s="16" t="inlineStr">
         <is>
           <t>Stable API surface.</t>
         </is>
       </c>
-      <c r="N2" s="18" t="n">
+      <c r="P2" s="18" t="n">
         <v>46150</v>
       </c>
     </row>
@@ -2729,423 +3045,494 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col width="26.13" customWidth="1" style="17" min="1" max="1"/>
+    <col width="10" customWidth="1" style="17" min="1" max="1"/>
     <col width="29.88" customWidth="1" style="17" min="3" max="3"/>
+    <col width="20" customWidth="1" style="17" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>Resource Name</t>
         </is>
       </c>
-      <c r="B1" s="16" t="inlineStr">
+      <c r="C1" s="16" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="C1" s="16" t="inlineStr">
+      <c r="D1" s="16" t="inlineStr">
         <is>
           <t>Source Organization</t>
         </is>
       </c>
-      <c r="D1" s="16" t="inlineStr">
+      <c r="E1" s="16" t="inlineStr">
         <is>
           <t>Last Verified</t>
         </is>
       </c>
-      <c r="E1" s="16" t="inlineStr">
+      <c r="F1" s="16" t="inlineStr">
         <is>
           <t>Verified By</t>
         </is>
       </c>
-      <c r="F1" s="16" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Added/Edited By</t>
+        </is>
+      </c>
+      <c r="H1" s="16" t="inlineStr">
         <is>
           <t>Last Updated</t>
         </is>
       </c>
-      <c r="G1" s="16" t="inlineStr">
+      <c r="I1" s="16" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
       </c>
-      <c r="H1" s="16" t="inlineStr">
+      <c r="J1" s="16" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="I1" s="16" t="inlineStr">
+      <c r="K1" s="16" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="J1" s="16" t="inlineStr">
+      <c r="L1" s="16" t="inlineStr">
         <is>
           <t>Maturity Level</t>
         </is>
       </c>
-      <c r="K1" s="16" t="inlineStr">
+      <c r="M1" s="16" t="inlineStr">
         <is>
           <t>Notes / Key Takeaways</t>
         </is>
       </c>
-      <c r="L1" s="0" t="inlineStr">
+      <c r="N1" s="0" t="inlineStr">
         <is>
           <t>Discovery Date</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>ba114fad</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>Databricks Coding Agent Benchmark</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>https://www.databricks.com/blog/benchmarking-coding-agents-databricks-multi-million-line-codebase</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr">
         <is>
           <t>Databricks</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="E2" s="6" t="n">
         <v>46216</v>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H2" s="16" t="n">
         <v>2024</v>
       </c>
-      <c r="G2" s="16" t="inlineStr">
+      <c r="I2" s="16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H2" s="16" t="inlineStr">
+      <c r="J2" s="16" t="inlineStr">
         <is>
           <t>Whitepaper</t>
         </is>
       </c>
-      <c r="I2" s="16" t="inlineStr">
+      <c r="K2" s="16" t="inlineStr">
         <is>
           <t>Coding Agents</t>
         </is>
       </c>
-      <c r="J2" s="16" t="inlineStr">
+      <c r="L2" s="16" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="K2" s="16" t="inlineStr">
+      <c r="M2" s="16" t="inlineStr">
         <is>
           <t>Evaluates State-Of-The-Art agent performance on multi-million line codebases to assess real-world software engineering capabilities.</t>
         </is>
       </c>
-      <c r="L2" s="18" t="n">
+      <c r="N2" s="18" t="n">
         <v>46216</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>4c170f7e</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Papers with Code </t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>https://paperswithcode.co/tasks/coding-agents</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>Hugging Face</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="E3" s="6" t="n">
         <v>46216</v>
       </c>
-      <c r="E3" s="16" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H3" s="16" t="n">
         <v>2026</v>
       </c>
-      <c r="H3" s="16" t="inlineStr">
+      <c r="J3" s="16" t="inlineStr">
         <is>
           <t>Benchmark Collection</t>
         </is>
       </c>
-      <c r="I3" s="16" t="inlineStr">
+      <c r="K3" s="16" t="inlineStr">
         <is>
           <t>Coding Agents</t>
         </is>
       </c>
-      <c r="J3" s="16" t="inlineStr">
+      <c r="L3" s="16" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="K3" s="16" t="inlineStr">
+      <c r="M3" s="16" t="inlineStr">
         <is>
           <t>Papers with Code with State-Of-The-Art (SOTA) Codng Agent Benchmarks</t>
         </is>
       </c>
-      <c r="L3" s="18" t="n">
+      <c r="N3" s="18" t="n">
         <v>46216</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>b9ed03e7</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>SWE-Bench Pro</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>https://openreview.net/forum?id=9R2iUHhVfr</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>SWE-bench Team</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="E4" s="6" t="n"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H4" s="16" t="n">
+        <v>2025</v>
+      </c>
+      <c r="I4" s="16" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="J4" s="16" t="inlineStr">
+        <is>
+          <t>Whitepaper</t>
+        </is>
+      </c>
+      <c r="K4" s="16" t="inlineStr">
+        <is>
+          <t>Coding Agents</t>
+        </is>
+      </c>
+      <c r="L4" s="16" t="inlineStr">
+        <is>
+          <t>Mature</t>
+        </is>
+      </c>
+      <c r="M4" s="16" t="inlineStr">
+        <is>
+          <t>Addresses limitations of original SWE-bench by focusing on long-horizon, complex, multi-file software engineering tasks.</t>
+        </is>
+      </c>
+      <c r="N4" s="18" t="n">
         <v>46216</v>
       </c>
-      <c r="F4" s="16" t="n">
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>f487cdc5</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>SWE-Bench++</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2512.17419</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>Academic Researchers</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="n"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H5" s="16" t="n">
         <v>2025</v>
       </c>
-      <c r="G4" s="16" t="inlineStr">
-        <is>
-          <t>Pro</t>
-        </is>
-      </c>
-      <c r="H4" s="16" t="inlineStr">
+      <c r="J5" s="16" t="inlineStr">
         <is>
           <t>Whitepaper</t>
         </is>
       </c>
-      <c r="I4" s="16" t="inlineStr">
+      <c r="K5" s="16" t="inlineStr">
         <is>
           <t>Coding Agents</t>
         </is>
       </c>
-      <c r="J4" s="16" t="inlineStr">
+      <c r="L5" s="16" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="M5" s="16" t="inlineStr">
+        <is>
+          <t>Scalable framework that generates repository-level tasks from live GitHub PRs across 11 programming languages.</t>
+        </is>
+      </c>
+      <c r="N5" s="18" t="n">
+        <v>46216</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>f37d4051</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>Terminal-Bench</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2601.11868</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>CISPA / Academic Researchers</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="n"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H6" s="16" t="n">
+        <v>2026</v>
+      </c>
+      <c r="I6" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" s="16" t="inlineStr">
+        <is>
+          <t>Whitepaper</t>
+        </is>
+      </c>
+      <c r="K6" s="16" t="inlineStr">
+        <is>
+          <t>Coding Agents</t>
+        </is>
+      </c>
+      <c r="L6" s="16" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="K4" s="16" t="inlineStr">
-        <is>
-          <t>Addresses limitations of original SWE-bench by focusing on long-horizon, complex, multi-file software engineering tasks.</t>
-        </is>
-      </c>
-      <c r="L4" s="18" t="n">
+      <c r="M6" s="16" t="inlineStr">
+        <is>
+          <t>Benchmarks agents on hard, realistic tasks within terminal/CLI environments.</t>
+        </is>
+      </c>
+      <c r="N6" s="18" t="n">
         <v>46216</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="16" t="inlineStr">
-        <is>
-          <t>SWE-Bench++</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2512.17419</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>acbc7354</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>c-CRAB</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2603.23448</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>Academic Researchers</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="E7" s="6" t="n"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H7" s="16" t="n">
+        <v>2026</v>
+      </c>
+      <c r="I7" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <t>Whitepaper</t>
+        </is>
+      </c>
+      <c r="K7" s="16" t="inlineStr">
+        <is>
+          <t>Coding Agents</t>
+        </is>
+      </c>
+      <c r="L7" s="16" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="M7" s="16" t="inlineStr">
+        <is>
+          <t>Benchmark specifically for evaluating the code review capabilities of AI agents.</t>
+        </is>
+      </c>
+      <c r="N7" s="18" t="n">
         <v>46216</v>
       </c>
-      <c r="F5" s="16" t="n">
-        <v>2025</v>
-      </c>
-      <c r="H5" s="16" t="inlineStr">
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t>edd19b89</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>SWE-Explore</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2606.07297</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>Academic Researchers</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="n"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H8" s="16" t="n">
+        <v>2026</v>
+      </c>
+      <c r="I8" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="16" t="inlineStr">
         <is>
           <t>Whitepaper</t>
         </is>
       </c>
-      <c r="I5" s="16" t="inlineStr">
+      <c r="K8" s="16" t="inlineStr">
         <is>
           <t>Coding Agents</t>
         </is>
       </c>
-      <c r="J5" s="16" t="inlineStr">
+      <c r="L8" s="16" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="K5" s="16" t="inlineStr">
-        <is>
-          <t>Scalable framework that generates repository-level tasks from live GitHub PRs across 11 programming languages.</t>
-        </is>
-      </c>
-      <c r="L5" s="18" t="n">
-        <v>46216</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>Terminal-Bench</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2601.11868</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>CISPA / Academic Researchers</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>46216</v>
-      </c>
-      <c r="F6" s="16" t="n">
-        <v>2026</v>
-      </c>
-      <c r="G6" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" s="16" t="inlineStr">
-        <is>
-          <t>Whitepaper</t>
-        </is>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>Coding Agents</t>
-        </is>
-      </c>
-      <c r="J6" s="16" t="inlineStr">
-        <is>
-          <t>Mature</t>
-        </is>
-      </c>
-      <c r="K6" s="16" t="inlineStr">
-        <is>
-          <t>Benchmarks agents on hard, realistic tasks within terminal/CLI environments.</t>
-        </is>
-      </c>
-      <c r="L6" s="18" t="n">
-        <v>46216</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>c-CRAB</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2603.23448</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Academic Researchers</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>46216</v>
-      </c>
-      <c r="F7" s="16" t="n">
-        <v>2026</v>
-      </c>
-      <c r="G7" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>Whitepaper</t>
-        </is>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>Coding Agents</t>
-        </is>
-      </c>
-      <c r="J7" s="16" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="K7" s="16" t="inlineStr">
-        <is>
-          <t>Benchmark specifically for evaluating the code review capabilities of AI agents.</t>
-        </is>
-      </c>
-      <c r="L7" s="18" t="n">
-        <v>46216</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>SWE-Explore</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2606.07297</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>Academic Researchers</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>46216</v>
-      </c>
-      <c r="F8" s="16" t="n">
-        <v>2026</v>
-      </c>
-      <c r="G8" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>Whitepaper</t>
-        </is>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>Coding Agents</t>
-        </is>
-      </c>
-      <c r="J8" s="16" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="K8" s="16" t="inlineStr">
+      <c r="M8" s="16" t="inlineStr">
         <is>
           <t>Isolates the evaluation of repository exploration, context retrieval, and code localization capabilities.</t>
         </is>
       </c>
-      <c r="L8" s="18" t="n">
+      <c r="N8" s="18" t="n">
         <v>46216</v>
       </c>
     </row>
@@ -3185,7 +3572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" style="17" min="1" max="1"/>
@@ -3229,28 +3616,27 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="20" t="n">
+      <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="inlineStr">
-        <is>
-          <t>Resource Name</t>
-        </is>
-      </c>
-      <c r="C2" s="20" t="inlineStr">
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
         <is>
           <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
         </is>
       </c>
-      <c r="D2" s="20" t="inlineStr">
-        <is>
-          <t>free_text</t>
-        </is>
-      </c>
-      <c r="E2" s="20" t="inlineStr"/>
-      <c r="F2" s="20" t="inlineStr">
-        <is>
-          <t>Short, human-readable name. Also the natural key used to match a row across sync runs. Example: VS Code Copilot Agents Overview</t>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>System-generated unique identifier, independent of Resource Name. Auto-assigned by xlsx_to_json.py the first time it sees a row with this cell blank (new rows, and every existing row during this migration) -- don't fill it in by hand. The one exception: when moving a row to a different sheet (e.g. Knowledgebase -&gt; Deprecated), copy its ID along with the rest of the row so the sync scripts recognize it as the same resource rather than a deletion plus a new entry.</t>
         </is>
       </c>
     </row>
@@ -3260,7 +3646,7 @@
       </c>
       <c r="B3" s="20" t="inlineStr">
         <is>
-          <t>URL</t>
+          <t>Resource Name</t>
         </is>
       </c>
       <c r="C3" s="20" t="inlineStr">
@@ -3276,7 +3662,7 @@
       <c r="E3" s="20" t="inlineStr"/>
       <c r="F3" s="20" t="inlineStr">
         <is>
-          <t>Canonical link to the resource.</t>
+          <t>Short, human-readable name. Also the natural key used to match a row across sync runs. Example: VS Code Copilot Agents Overview</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3672,7 @@
       </c>
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t>Source Organization</t>
+          <t>URL</t>
         </is>
       </c>
       <c r="C4" s="20" t="inlineStr">
@@ -3302,7 +3688,7 @@
       <c r="E4" s="20" t="inlineStr"/>
       <c r="F4" s="20" t="inlineStr">
         <is>
-          <t>Who maintains it? Examples: Microsoft, GitHub, OpenAI, Kaggle, Anthropic, Google, HuggingFace. This matters because some orgs update weekly, others yearly.</t>
+          <t>Canonical link to the resource.</t>
         </is>
       </c>
     </row>
@@ -3312,7 +3698,7 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>Last Verified</t>
+          <t>Source Organization</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -3322,13 +3708,13 @@
       </c>
       <c r="D5" s="20" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>free_text</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr"/>
       <c r="F5" s="20" t="inlineStr">
         <is>
-          <t>Date a curator last checked the page. Set by a human during verification; cleared automatically when the row's content changes.</t>
+          <t>Who maintains it? Examples: Microsoft, GitHub, OpenAI, Kaggle, Anthropic, Google, HuggingFace. This matters because some orgs update weekly, others yearly.</t>
         </is>
       </c>
     </row>
@@ -3338,7 +3724,7 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Verified By</t>
+          <t>Last Verified</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -3348,13 +3734,13 @@
       </c>
       <c r="D6" s="20" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>date</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr"/>
       <c r="F6" s="20" t="inlineStr">
         <is>
-          <t>Curator who last verified this row. Set by a human only, never by an agent; cleared automatically when the row's content changes.</t>
+          <t>Date a curator last checked the page. Set by a human during verification; cleared automatically when the row's content changes.</t>
         </is>
       </c>
     </row>
@@ -3364,49 +3750,48 @@
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>Last Updated</t>
+          <t>Verified By</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
         <is>
-          <t>Knowledgebase; SOTA Coding Agents Benchmarks</t>
+          <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>person</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr"/>
       <c r="F7" s="20" t="inlineStr">
         <is>
-          <t>The page's own update timestamp. Helps track fast-moving agent ecosystems.</t>
+          <t>Curator who last verified this row. Set by a human only, never by an agent; cleared automatically when the row's content changes.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="n">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>Deprecation Date</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>Deprecated</t>
-        </is>
-      </c>
-      <c r="D8" s="20" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="E8" s="20" t="inlineStr"/>
-      <c r="F8" s="20" t="inlineStr">
-        <is>
-          <t>Date the resource was deprecated or superseded.</t>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Added/Edited By</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>actor</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Who last added or edited this row's content -- a human curator's name, an AI agent's name (tagged '(requested by ...)' if invoked interactively, '(autonomous, ...)' if it ran on a schedule with no human present), or a GitHub handle for a direct xlsx upload. Distinct from Verified By, which is restricted to human review.</t>
         </is>
       </c>
     </row>
@@ -3416,23 +3801,23 @@
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>Version</t>
+          <t>Last Updated</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
+          <t>Knowledgebase; SOTA Coding Agents Benchmarks</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>date</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr"/>
       <c r="F9" s="20" t="inlineStr">
         <is>
-          <t>Version string of the resource or tool (e.g. 'v0.1 DRAFT', 'Pro'). Leave blank for article-type resources with no version - use Publication Date instead.</t>
+          <t>The page's own update timestamp. Helps track fast-moving agent ecosystems.</t>
         </is>
       </c>
     </row>
@@ -3442,23 +3827,23 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Resource Type</t>
+          <t>Deprecation Date / Last Updated</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
+          <t>Deprecated</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>controlled_single</t>
+          <t>date</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr"/>
       <c r="F10" s="20" t="inlineStr">
         <is>
-          <t>What kind of resource this is. Helps teams filter by what they need.</t>
+          <t>Most recent known date for this row, whichever kind of event produced it: when the resource was confirmed deprecated, or, absent that, whenever the row was last touched. An exact deprecation date isn't always knowable at the time a row is added or edited.</t>
         </is>
       </c>
     </row>
@@ -3468,7 +3853,7 @@
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>Agentic Features Covered</t>
+          <t>Version</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -3478,17 +3863,13 @@
       </c>
       <c r="D11" s="20" t="inlineStr">
         <is>
-          <t>controlled_multi</t>
-        </is>
-      </c>
-      <c r="E11" s="20" t="inlineStr">
-        <is>
-          <t>;</t>
-        </is>
-      </c>
+          <t>version</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr"/>
       <c r="F11" s="20" t="inlineStr">
         <is>
-          <t>Which agentic capabilities the resource covers. One of the most important columns.</t>
+          <t>Version string of the resource or tool (e.g. 'v0.1 DRAFT', 'Pro'). Leave blank for article-type resources with no version - use Publication Date instead.</t>
         </is>
       </c>
     </row>
@@ -3498,27 +3879,23 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Topic Focus</t>
+          <t>Resource Type</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>Knowledgebase; Deprecated</t>
+          <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>controlled_multi</t>
-        </is>
-      </c>
-      <c r="E12" s="20" t="inlineStr">
-        <is>
-          <t>;</t>
-        </is>
-      </c>
+          <t>controlled_single</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr"/>
       <c r="F12" s="20" t="inlineStr">
         <is>
-          <t>Subject areas the resource addresses. Helps research IT teams quickly find relevant material. Primary vocabulary is EDAM; NIST AI RMF characteristics are available as an optional secondary axis.</t>
+          <t>What kind of resource this is. Helps teams filter by what they need.</t>
         </is>
       </c>
     </row>
@@ -3528,23 +3905,27 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>Relevance to Research Cyberinfrastructure</t>
+          <t>Agentic Features Covered</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>Knowledgebase; Deprecated</t>
+          <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
         <is>
-          <t>free_text</t>
-        </is>
-      </c>
-      <c r="E13" s="20" t="inlineStr"/>
+          <t>controlled_multi</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>;</t>
+        </is>
+      </c>
       <c r="F13" s="20" t="inlineStr">
         <is>
-          <t>Free-text note on why this matters to research platforms. Example themes: workflow orchestration, data portal integration, metadata / provenance, multi-agent coordination, HPC / cloud hybrid workflows, reproducibility, federated analysis, user-facing agent interfaces.</t>
+          <t>Which agentic capabilities the resource covers. One of the most important columns.</t>
         </is>
       </c>
     </row>
@@ -3554,23 +3935,27 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Maturity Level</t>
+          <t>Topic Focus</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
+          <t>Knowledgebase; Deprecated</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>controlled_single</t>
-        </is>
-      </c>
-      <c r="E14" s="20" t="inlineStr"/>
+          <t>controlled_multi</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>;</t>
+        </is>
+      </c>
       <c r="F14" s="20" t="inlineStr">
         <is>
-          <t>Not about the website - about the technology described. Helps teams know whether something is stable enough to consider.</t>
+          <t>Subject areas the resource addresses. Helps research IT teams quickly find relevant material. Primary vocabulary is EDAM; NIST AI RMF characteristics are available as an optional secondary axis.</t>
         </is>
       </c>
     </row>
@@ -3580,12 +3965,12 @@
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>Notes / Key Takeaways</t>
+          <t>Relevance to Research Cyberinfrastructure</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
+          <t>Knowledgebase; Deprecated</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -3596,7 +3981,7 @@
       <c r="E15" s="20" t="inlineStr"/>
       <c r="F15" s="20" t="inlineStr">
         <is>
-          <t>Short free-text field: breaking changes, important patterns, new capabilities, relevance to agentic workflows, implications for research platforms. This is where institutional knowledge accumulates.</t>
+          <t>Free-text note on why this matters to research platforms. Example themes: workflow orchestration, data portal integration, metadata / provenance, multi-agent coordination, HPC / cloud hybrid workflows, reproducibility, federated analysis, user-facing agent interfaces.</t>
         </is>
       </c>
     </row>
@@ -3606,23 +3991,23 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Publication Date</t>
+          <t>Maturity Level</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>Knowledgebase</t>
+          <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>controlled_single</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr"/>
       <c r="F16" s="20" t="inlineStr">
         <is>
-          <t>Publication date for article-type resources that have no software version.</t>
+          <t>Not about the website - about the technology described. Helps teams know whether something is stable enough to consider.</t>
         </is>
       </c>
     </row>
@@ -3632,7 +4017,7 @@
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>Discovery Date</t>
+          <t>Notes / Key Takeaways</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -3642,11 +4027,63 @@
       </c>
       <c r="D17" s="20" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>free_text</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr"/>
       <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>Short free-text field: breaking changes, important patterns, new capabilities, relevance to agentic workflows, implications for research platforms. This is where institutional knowledge accumulates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="20" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>Publication Date</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>Knowledgebase</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr"/>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>Publication date for article-type resources that have no software version.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>Discovery Date</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr"/>
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>Date this resource first entered the VT Radar.</t>
         </is>

--- a/data/VANTAGE-Technology-Radar.xlsx
+++ b/data/VANTAGE-Technology-Radar.xlsx
@@ -2,9 +2,6 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1515" yWindow="1515" windowWidth="24705" windowHeight="12345" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
   <sheets>
     <sheet name="Knowledgebase" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Deprecated" sheetId="2" state="visible" r:id="rId2"/>
@@ -14,21 +11,23 @@
     <sheet name="Standards" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm"/>
-    <numFmt numFmtId="166" formatCode="m\-d\-yyyy"/>
-    <numFmt numFmtId="167" formatCode="yyyy\-m"/>
-    <numFmt numFmtId="168" formatCode="mmmm\ d\,\ yyyy"/>
-    <numFmt numFmtId="169" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
+  <numFmts count="8">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm"/>
+    <numFmt numFmtId="166" formatCode="m/d/yyyy"/>
+    <numFmt numFmtId="167" formatCode="m-d-yyyy"/>
+    <numFmt numFmtId="168" formatCode="yyyy-m"/>
+    <numFmt numFmtId="169" formatCode="mmmm d, yyyy"/>
+    <numFmt numFmtId="170" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="171" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -38,32 +37,31 @@
     <font>
       <name val="Arial"/>
       <color theme="1"/>
-      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color theme="1"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <color rgb="FF0000FF"/>
-      <sz val="10"/>
       <u val="single"/>
     </font>
     <font>
-      <name val="Arial"/>
       <color rgb="FF0000FF"/>
-      <sz val="10"/>
       <u val="single"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color theme="10"/>
-      <sz val="10"/>
-      <u val="single"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -71,7 +69,7 @@
       <patternFill/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -81,189 +79,104 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="22">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="6">
     <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB7E1CD"/>
+          <bgColor rgb="FFB7E1CD"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFA4C2F4"/>
+          <bgColor rgb="FFA4C2F4"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFE599"/>
           <bgColor rgb="FFFFE599"/>
         </patternFill>
       </fill>
+      <border/>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFA4C2F4"/>
-          <bgColor rgb="FFA4C2F4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB7E1CD"/>
-          <bgColor rgb="FFB7E1CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
+      <font/>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFD9D2E9"/>
           <bgColor rgb="FFD9D2E9"/>
         </patternFill>
       </fill>
+      <border/>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFA4C2F4"/>
-          <bgColor rgb="FFA4C2F4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB7E1CD"/>
-          <bgColor rgb="FFB7E1CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
+      <font/>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFDD7E6B"/>
           <bgColor rgb="FFDD7E6B"/>
         </patternFill>
       </fill>
+      <border/>
     </dxf>
     <dxf>
+      <font/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFE599"/>
-          <bgColor rgb="FFFFE599"/>
+          <fgColor rgb="FFB4A7D6"/>
+          <bgColor rgb="FFB4A7D6"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFA4C2F4"/>
-          <bgColor rgb="FFA4C2F4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB7E1CD"/>
-          <bgColor rgb="FFB7E1CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFE599"/>
-          <bgColor rgb="FFFFE599"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB7E1CD"/>
-          <bgColor rgb="FFB7E1CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFE599"/>
-          <bgColor rgb="FFFFE599"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFA4C2F4"/>
-          <bgColor rgb="FFA4C2F4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB7E1CD"/>
-          <bgColor rgb="FFB7E1CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB7E1CD"/>
-          <bgColor rgb="FFB7E1CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
+      <border/>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -336,7 +249,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -526,8 +439,6 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -538,45 +449,45 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Q43"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="27.42578125" customWidth="1" min="2" max="2"/>
-    <col width="16.28515625" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="18.5703125" customWidth="1" min="8" max="8"/>
-    <col width="37.85546875" customWidth="1" min="9" max="9"/>
-    <col width="57.85546875" customWidth="1" min="10" max="10"/>
-    <col width="44.140625" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" style="17" min="1" max="1"/>
+    <col width="27.38" customWidth="1" style="17" min="2" max="2"/>
+    <col width="16.25" customWidth="1" style="17" min="3" max="3"/>
+    <col width="20" customWidth="1" style="17" min="7" max="7"/>
+    <col width="18.63" customWidth="1" style="17" min="8" max="8"/>
+    <col width="37.88" customWidth="1" style="17" min="9" max="9"/>
+    <col width="57.88" customWidth="1" style="17" min="10" max="10"/>
+    <col width="44.13" customWidth="1" style="17" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>Resource Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="16" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="16" t="inlineStr">
         <is>
           <t>Source Organization</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="16" t="inlineStr">
         <is>
           <t>Last Verified</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="16" t="inlineStr">
         <is>
           <t>Verified By</t>
         </is>
@@ -586,82 +497,82 @@
           <t>Added/Edited By</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="16" t="inlineStr">
         <is>
           <t>Last Updated</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="16" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="16" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="16" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="16" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="16" t="inlineStr">
         <is>
           <t>Relevance to Research Cyberinfrastructure</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="16" t="inlineStr">
         <is>
           <t>Maturity Level</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="16" t="inlineStr">
         <is>
           <t>Notes / Key Takeaways</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="0" t="inlineStr">
         <is>
           <t>Publication Date</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="0" t="inlineStr">
         <is>
           <t>Discovery Date</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>022e4e1c</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>VS Code Copilot Agents Overview</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>https://code.visualstudio.com/docs/copilot/agents/overview</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="6" t="n">
         <v>46157</v>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
@@ -671,72 +582,72 @@
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="H2" s="7" t="n">
         <v>46113</v>
       </c>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="I2" s="8" t="n"/>
+      <c r="J2" s="16" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="K2" s="16" t="inlineStr">
         <is>
           <t>Hooks; Skills; MCP; Agent frameworks</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="L2" s="16" t="inlineStr">
         <is>
           <t>Architecture; Implementation; Deployment</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="M2" s="16" t="inlineStr">
         <is>
           <t>IDE integration for agentic workflows</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="N2" s="16" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="O2" s="16" t="inlineStr">
         <is>
           <t>Canonical reference for VS Code agent capabilities.</t>
         </is>
       </c>
-      <c r="P2" s="11" t="n">
+      <c r="P2" s="18" t="n">
         <v>46162</v>
       </c>
-      <c r="Q2" s="11" t="n">
+      <c r="Q2" s="18" t="n">
         <v>46113</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>2e9b6b2d</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Data Director</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>https://docs.google.com/document/d/1mu1_U1cWqn1aP3vtW83JnX5-aGhzM49K/edit</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>Microsoft, RDA</t>
         </is>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="6" t="n">
         <v>46168</v>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
@@ -746,267 +657,267 @@
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="H3" s="7" t="n">
         <v>46168</v>
       </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="I3" s="16" t="inlineStr">
         <is>
           <t>v0.1 DRAFT</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
+      <c r="J3" s="16" t="inlineStr">
         <is>
           <t>Specification</t>
         </is>
       </c>
-      <c r="K3" s="1" t="inlineStr">
+      <c r="K3" s="16" t="inlineStr">
         <is>
           <t>FAIR data; Workflow Agents</t>
         </is>
       </c>
-      <c r="L3" s="1" t="inlineStr">
+      <c r="L3" s="16" t="inlineStr">
         <is>
           <t>Workflows; Implementation</t>
         </is>
       </c>
-      <c r="M3" s="1" t="inlineStr">
+      <c r="M3" s="16" t="inlineStr">
         <is>
           <t>Makes data outputs FAIR at the point of publication</t>
         </is>
       </c>
-      <c r="N3" s="1" t="inlineStr">
+      <c r="N3" s="16" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="O3" s="1" t="n"/>
-      <c r="Q3" s="11" t="n">
+      <c r="O3" s="16" t="n"/>
+      <c r="Q3" s="18" t="n">
         <v>46168</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>161f1860</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>Agentic AI Tool</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>https://docs.github.com/en/copilot/agents</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="4" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="7" t="n"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="H4" s="7" t="n">
         <v>46113</v>
       </c>
-      <c r="I4" s="1" t="n"/>
-      <c r="J4" s="1" t="inlineStr">
+      <c r="I4" s="16" t="n"/>
+      <c r="J4" s="16" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K4" s="1" t="inlineStr">
+      <c r="K4" s="16" t="inlineStr">
         <is>
           <t>Hooks; Skills; API Integration</t>
         </is>
       </c>
-      <c r="L4" s="1" t="inlineStr">
+      <c r="L4" s="16" t="inlineStr">
         <is>
           <t>Architecture; Governance; Security</t>
         </is>
       </c>
-      <c r="M4" s="1" t="inlineStr">
+      <c r="M4" s="16" t="inlineStr">
         <is>
           <t>Relevant for CI/CD and code-review automation</t>
         </is>
       </c>
-      <c r="N4" s="1" t="inlineStr">
+      <c r="N4" s="16" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="O4" s="1" t="inlineStr">
+      <c r="O4" s="16" t="inlineStr">
         <is>
           <t>Strong alignment with developer workflows.</t>
         </is>
       </c>
-      <c r="Q4" s="11" t="n">
+      <c r="Q4" s="18" t="n">
         <v>46113</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t>abbd844c</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>GitHub MCP Documentation</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>https://github.com/modelcontextprotocol</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>GitHub/OpenAI</t>
         </is>
       </c>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="4" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="7" t="n"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="H5" s="7" t="n">
         <v>46113</v>
       </c>
-      <c r="I5" s="1" t="n"/>
-      <c r="J5" s="1" t="inlineStr">
+      <c r="I5" s="16" t="n"/>
+      <c r="J5" s="16" t="inlineStr">
         <is>
           <t>API Reference</t>
         </is>
       </c>
-      <c r="K5" s="1" t="inlineStr">
+      <c r="K5" s="16" t="inlineStr">
         <is>
           <t>MCP; Tools; Server Integration</t>
         </is>
       </c>
-      <c r="L5" s="1" t="inlineStr">
+      <c r="L5" s="16" t="inlineStr">
         <is>
           <t>Architecture; Implementation</t>
         </is>
       </c>
-      <c r="M5" s="1" t="inlineStr">
+      <c r="M5" s="16" t="inlineStr">
         <is>
           <t>Key for interoperable agent tools</t>
         </is>
       </c>
-      <c r="N5" s="1" t="inlineStr">
+      <c r="N5" s="16" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="O5" s="1" t="inlineStr">
+      <c r="O5" s="16" t="inlineStr">
         <is>
           <t>Fast-moving ecosystem.</t>
         </is>
       </c>
-      <c r="Q5" s="11" t="n">
+      <c r="Q5" s="18" t="n">
         <v>46113</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="0" t="inlineStr">
         <is>
           <t>b71baded</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>OpenAI MCP Specification</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>https://spec.modelcontextprotocol.io</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="4" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="7" t="n"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="H6" s="7" t="n">
         <v>46113</v>
       </c>
-      <c r="I6" s="1" t="n"/>
-      <c r="J6" s="1" t="inlineStr">
+      <c r="I6" s="16" t="n"/>
+      <c r="J6" s="16" t="inlineStr">
         <is>
           <t>Specification</t>
         </is>
       </c>
-      <c r="K6" s="1" t="inlineStr">
+      <c r="K6" s="16" t="inlineStr">
         <is>
           <t>MCP; Tools; Server Patterns</t>
         </is>
       </c>
-      <c r="L6" s="1" t="inlineStr">
+      <c r="L6" s="16" t="inlineStr">
         <is>
           <t>Architecture; Governance</t>
         </is>
       </c>
-      <c r="M6" s="1" t="inlineStr">
+      <c r="M6" s="16" t="inlineStr">
         <is>
           <t>Critical for cross-platform agent interoperability</t>
         </is>
       </c>
-      <c r="N6" s="1" t="inlineStr">
+      <c r="N6" s="16" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="O6" s="1" t="inlineStr">
+      <c r="O6" s="16" t="inlineStr">
         <is>
           <t>Becoming a de facto standard.</t>
         </is>
       </c>
-      <c r="Q6" s="11" t="n">
+      <c r="Q6" s="18" t="n">
         <v>46113</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="0" t="inlineStr">
         <is>
           <t>2b23adbb</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>Anthropic Model Context Protocol</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">https://modelcontextprotocol.io/specification/2025-11-25 </t>
         </is>
       </c>
-      <c r="D7" s="1" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>Anthropic</t>
         </is>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="6" t="n">
         <v>46182</v>
       </c>
-      <c r="F7" s="1" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
@@ -1016,72 +927,72 @@
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="H7" s="7" t="n">
         <v>45962</v>
       </c>
-      <c r="I7" s="7" t="n"/>
-      <c r="J7" s="1" t="inlineStr">
+      <c r="I7" s="11" t="n"/>
+      <c r="J7" s="16" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K7" s="1" t="inlineStr">
+      <c r="K7" s="16" t="inlineStr">
         <is>
           <t>MCP; Agent Patterns</t>
         </is>
       </c>
-      <c r="L7" s="1" t="inlineStr">
+      <c r="L7" s="16" t="inlineStr">
         <is>
           <t>Architecture; Governance</t>
         </is>
       </c>
-      <c r="M7" s="1" t="inlineStr">
+      <c r="M7" s="16" t="inlineStr">
         <is>
           <t>Integration between LLM applications and external data sources and tools</t>
         </is>
       </c>
-      <c r="N7" s="1" t="inlineStr">
+      <c r="N7" s="16" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="O7" s="1" t="inlineStr">
+      <c r="O7" s="16" t="inlineStr">
         <is>
           <t>Strong safety emphasis.</t>
         </is>
       </c>
-      <c r="P7" s="11" t="n">
+      <c r="P7" s="18" t="n">
         <v>45972</v>
       </c>
-      <c r="Q7" s="11" t="n">
+      <c r="Q7" s="18" t="n">
         <v>45962</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="0" t="inlineStr">
         <is>
           <t>d6d28dfa</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>Kaggle Prototype to Production Whitepaper</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>https://www.kaggle.com/whitepaper-prototype-to-production</t>
         </is>
       </c>
-      <c r="D8" s="1" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>Kaggle/Google</t>
         </is>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="6" t="n">
         <v>46157</v>
       </c>
-      <c r="F8" s="1" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
@@ -1091,337 +1002,337 @@
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="H8" s="7" t="n">
         <v>45975</v>
       </c>
-      <c r="I8" s="1" t="inlineStr">
+      <c r="I8" s="16" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="J8" s="1" t="inlineStr">
+      <c r="J8" s="16" t="inlineStr">
         <is>
           <t>Whitepaper</t>
         </is>
       </c>
-      <c r="K8" s="1" t="inlineStr">
+      <c r="K8" s="16" t="inlineStr">
         <is>
           <t>Deployment patterns; Workflow Automation</t>
         </is>
       </c>
-      <c r="L8" s="1" t="inlineStr">
+      <c r="L8" s="16" t="inlineStr">
         <is>
           <t>Implementation; Security; Deployment</t>
         </is>
       </c>
-      <c r="M8" s="1" t="inlineStr">
+      <c r="M8" s="16" t="inlineStr">
         <is>
           <t>Helps teams move prototypes to production</t>
         </is>
       </c>
-      <c r="N8" s="1" t="inlineStr">
+      <c r="N8" s="16" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="O8" s="1" t="inlineStr">
+      <c r="O8" s="16" t="inlineStr">
         <is>
           <t>Technical guide to the operational life cycle of AI agents, focusing on deployment &amp; security</t>
         </is>
       </c>
-      <c r="Q8" s="11" t="n">
+      <c r="Q8" s="18" t="n">
         <v>45975</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="0" t="inlineStr">
         <is>
           <t>bfda8877</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>Google Vertex AI Agents Overview</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>https://cloud.google.com/vertex-ai/docs/agents</t>
         </is>
       </c>
-      <c r="D9" s="1" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="4" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="7" t="n"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H9" s="4" t="n">
+      <c r="H9" s="7" t="n">
         <v>46113</v>
       </c>
-      <c r="I9" s="1" t="n"/>
-      <c r="J9" s="1" t="inlineStr">
+      <c r="I9" s="16" t="n"/>
+      <c r="J9" s="16" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K9" s="1" t="inlineStr">
+      <c r="K9" s="16" t="inlineStr">
         <is>
           <t>Agent frameworks; Orchestration</t>
         </is>
       </c>
-      <c r="L9" s="1" t="inlineStr">
+      <c r="L9" s="16" t="inlineStr">
         <is>
           <t>Architecture; Deployment</t>
         </is>
       </c>
-      <c r="M9" s="1" t="inlineStr">
+      <c r="M9" s="16" t="inlineStr">
         <is>
           <t>Useful for cloud-based scientific workflows</t>
         </is>
       </c>
-      <c r="N9" s="1" t="inlineStr">
+      <c r="N9" s="16" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="O9" s="1" t="inlineStr">
+      <c r="O9" s="16" t="inlineStr">
         <is>
           <t>Strong enterprise alignment.</t>
         </is>
       </c>
-      <c r="Q9" s="11" t="n">
+      <c r="Q9" s="18" t="n">
         <v>46113</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="0" t="inlineStr">
         <is>
           <t>f488464f</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>HuggingFace Agents Documentation</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>https://huggingface.co/docs/agents</t>
         </is>
       </c>
-      <c r="D10" s="1" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>HuggingFace</t>
         </is>
       </c>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="4" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="7" t="n"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="H10" s="7" t="n">
         <v>46082</v>
       </c>
-      <c r="I10" s="1" t="n"/>
-      <c r="J10" s="1" t="inlineStr">
+      <c r="I10" s="16" t="n"/>
+      <c r="J10" s="16" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K10" s="1" t="inlineStr">
+      <c r="K10" s="16" t="inlineStr">
         <is>
           <t>Tools; Skills; Model Integration</t>
         </is>
       </c>
-      <c r="L10" s="1" t="inlineStr">
+      <c r="L10" s="16" t="inlineStr">
         <is>
           <t>Architecture; Implementation</t>
         </is>
       </c>
-      <c r="M10" s="1" t="inlineStr">
+      <c r="M10" s="16" t="inlineStr">
         <is>
           <t>Useful for open-source agent experimentation</t>
         </is>
       </c>
-      <c r="N10" s="1" t="inlineStr">
+      <c r="N10" s="16" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="O10" s="1" t="inlineStr">
+      <c r="O10" s="16" t="inlineStr">
         <is>
           <t>Rapidly evolving.</t>
         </is>
       </c>
-      <c r="Q10" s="11" t="n">
+      <c r="Q10" s="18" t="n">
         <v>46082</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="0" t="inlineStr">
         <is>
           <t>dbe3741e</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>LangChain Agents Overview</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>https://python.langchain.com/docs/modules/agents</t>
         </is>
       </c>
-      <c r="D11" s="1" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>LangChain</t>
         </is>
       </c>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="4" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="7" t="n"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="H11" s="7" t="n">
         <v>46113</v>
       </c>
-      <c r="I11" s="1" t="n"/>
-      <c r="J11" s="1" t="inlineStr">
+      <c r="I11" s="16" t="n"/>
+      <c r="J11" s="16" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K11" s="1" t="inlineStr">
+      <c r="K11" s="16" t="inlineStr">
         <is>
           <t>Tools; Skills; Multi-Agent Patterns</t>
         </is>
       </c>
-      <c r="L11" s="1" t="inlineStr">
+      <c r="L11" s="16" t="inlineStr">
         <is>
           <t>Architecture; Implementation</t>
         </is>
       </c>
-      <c r="M11" s="1" t="inlineStr">
+      <c r="M11" s="16" t="inlineStr">
         <is>
           <t>Relevant for workflow prototyping</t>
         </is>
       </c>
-      <c r="N11" s="1" t="inlineStr">
+      <c r="N11" s="16" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="O11" s="1" t="inlineStr">
+      <c r="O11" s="16" t="inlineStr">
         <is>
           <t>Widely used in research.</t>
         </is>
       </c>
-      <c r="Q11" s="11" t="n">
+      <c r="Q11" s="18" t="n">
         <v>46113</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="0" t="inlineStr">
         <is>
           <t>ddd42289</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>LlamaIndex Agents</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>https://docs.llamaindex.ai/en/stable/agent/</t>
         </is>
       </c>
-      <c r="D12" s="1" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>LlamaIndex</t>
         </is>
       </c>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="4" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="7" t="n"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H12" s="4" t="n">
+      <c r="H12" s="7" t="n">
         <v>46113</v>
       </c>
-      <c r="I12" s="1" t="n"/>
-      <c r="J12" s="1" t="inlineStr">
+      <c r="I12" s="16" t="n"/>
+      <c r="J12" s="16" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K12" s="1" t="inlineStr">
+      <c r="K12" s="16" t="inlineStr">
         <is>
           <t>Tools; Skills; Retrieval Agents</t>
         </is>
       </c>
-      <c r="L12" s="1" t="inlineStr">
+      <c r="L12" s="16" t="inlineStr">
         <is>
           <t>Architecture; Governance</t>
         </is>
       </c>
-      <c r="M12" s="1" t="inlineStr">
+      <c r="M12" s="16" t="inlineStr">
         <is>
           <t>Useful for data-rich research platforms</t>
         </is>
       </c>
-      <c r="N12" s="1" t="inlineStr">
+      <c r="N12" s="16" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="O12" s="1" t="inlineStr">
+      <c r="O12" s="16" t="inlineStr">
         <is>
           <t>Strong retrieval-centric design.</t>
         </is>
       </c>
-      <c r="Q12" s="11" t="n">
+      <c r="Q12" s="18" t="n">
         <v>46113</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="0" t="inlineStr">
         <is>
           <t>c7e95f61</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>Dagster Automation/Agent Patterns</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>https://docs.dagster.io/getting-started/ai-tools</t>
         </is>
       </c>
-      <c r="D13" s="1" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>Dagster Labs</t>
         </is>
       </c>
-      <c r="E13" s="14" t="n">
+      <c r="E13" s="21" t="n">
         <v>46082</v>
       </c>
-      <c r="F13" s="1" t="inlineStr">
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
@@ -1431,1196 +1342,1202 @@
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="H13" s="7" t="n">
         <v>46082</v>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>1.3.15</t>
         </is>
       </c>
-      <c r="J13" s="1" t="inlineStr">
+      <c r="J13" s="16" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K13" s="1" t="inlineStr">
+      <c r="K13" s="16" t="inlineStr">
         <is>
           <t>Workflow Automation; Orchestration</t>
         </is>
       </c>
-      <c r="L13" s="1" t="inlineStr">
+      <c r="L13" s="16" t="inlineStr">
         <is>
           <t>Architecture; Deployment</t>
         </is>
       </c>
-      <c r="M13" s="1" t="inlineStr">
+      <c r="M13" s="16" t="inlineStr">
         <is>
           <t>Relevant for scientific pipelines</t>
         </is>
       </c>
-      <c r="N13" s="1" t="inlineStr">
+      <c r="N13" s="16" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="O13" s="1" t="inlineStr">
+      <c r="O13" s="16" t="inlineStr">
         <is>
           <t>Strong reproducibility focus.</t>
         </is>
       </c>
-      <c r="Q13" s="11" t="n">
+      <c r="Q13" s="18" t="n">
         <v>46082</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="0" t="inlineStr">
         <is>
           <t>73426de0</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>Prefect Automations/Agents</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>https://docs.prefect.io/latest/concepts/automations/</t>
         </is>
       </c>
-      <c r="D14" s="1" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t>Prefect</t>
         </is>
       </c>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="4" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="7" t="n"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H14" s="4" t="n">
+      <c r="H14" s="7" t="n">
         <v>46082</v>
       </c>
-      <c r="I14" s="1" t="n"/>
-      <c r="J14" s="1" t="inlineStr">
+      <c r="I14" s="16" t="n"/>
+      <c r="J14" s="16" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K14" s="1" t="inlineStr">
+      <c r="K14" s="16" t="inlineStr">
         <is>
           <t>Workflow Agents; Triggers</t>
         </is>
       </c>
-      <c r="L14" s="1" t="inlineStr">
+      <c r="L14" s="16" t="inlineStr">
         <is>
           <t>Implementation; Deployment</t>
         </is>
       </c>
-      <c r="M14" s="1" t="inlineStr">
+      <c r="M14" s="16" t="inlineStr">
         <is>
           <t>Useful for data processing pipelines</t>
         </is>
       </c>
-      <c r="N14" s="1" t="inlineStr">
+      <c r="N14" s="16" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="O14" s="1" t="inlineStr">
+      <c r="O14" s="16" t="inlineStr">
         <is>
           <t>Good hybrid cloud/HPC support.</t>
         </is>
       </c>
-      <c r="Q14" s="11" t="n">
+      <c r="Q14" s="18" t="n">
         <v>46082</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="0" t="inlineStr">
         <is>
           <t>3294a13f</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>Jupyter AI</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>https://jupyter-ai.readthedocs.io</t>
         </is>
       </c>
-      <c r="D15" s="1" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>Project Jupyter</t>
         </is>
       </c>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="4" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="7" t="n"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H15" s="4" t="n">
+      <c r="H15" s="7" t="n">
         <v>46113</v>
       </c>
-      <c r="I15" s="1" t="n"/>
-      <c r="J15" s="1" t="inlineStr">
+      <c r="I15" s="16" t="n"/>
+      <c r="J15" s="16" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K15" s="1" t="inlineStr">
+      <c r="K15" s="16" t="inlineStr">
         <is>
           <t>Notebook Agents; Workflow Automation</t>
         </is>
       </c>
-      <c r="L15" s="1" t="inlineStr">
+      <c r="L15" s="16" t="inlineStr">
         <is>
           <t>Implementation; Data governance</t>
         </is>
       </c>
-      <c r="M15" s="1" t="inlineStr">
+      <c r="M15" s="16" t="inlineStr">
         <is>
           <t>Relevant for research notebooks</t>
         </is>
       </c>
-      <c r="N15" s="1" t="inlineStr">
+      <c r="N15" s="16" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="O15" s="1" t="inlineStr">
+      <c r="O15" s="16" t="inlineStr">
         <is>
           <t>Strong alignment with scientific workflows.</t>
         </is>
       </c>
-      <c r="Q15" s="11" t="n">
+      <c r="Q15" s="18" t="n">
         <v>46113</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="0" t="inlineStr">
         <is>
           <t>f51ea180</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>Anthropic Tools API</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>https://docs.anthropic.com/en/docs/tools</t>
         </is>
       </c>
-      <c r="D16" s="1" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>Anthropic</t>
         </is>
       </c>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="4" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="7" t="n"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H16" s="4" t="n">
+      <c r="H16" s="7" t="n">
         <v>46113</v>
       </c>
-      <c r="I16" s="1" t="n"/>
-      <c r="J16" s="1" t="inlineStr">
+      <c r="I16" s="16" t="n"/>
+      <c r="J16" s="16" t="inlineStr">
         <is>
           <t>API Reference</t>
         </is>
       </c>
-      <c r="K16" s="1" t="inlineStr">
+      <c r="K16" s="16" t="inlineStr">
         <is>
           <t>Tools; Skills</t>
         </is>
       </c>
-      <c r="L16" s="1" t="inlineStr">
+      <c r="L16" s="16" t="inlineStr">
         <is>
           <t>Architecture; Security</t>
         </is>
       </c>
-      <c r="M16" s="1" t="inlineStr">
+      <c r="M16" s="16" t="inlineStr">
         <is>
           <t>Useful for safe tool-calling agents</t>
         </is>
       </c>
-      <c r="N16" s="1" t="inlineStr">
+      <c r="N16" s="16" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="O16" s="1" t="inlineStr">
+      <c r="O16" s="16" t="inlineStr">
         <is>
           <t>Strong safety posture.</t>
         </is>
       </c>
-      <c r="Q16" s="11" t="n">
+      <c r="Q16" s="18" t="n">
         <v>46113</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="0" t="inlineStr">
         <is>
           <t>89f36cc1</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>Microsoft Semantic Kernel Agents</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t>https://learn.microsoft.com/semantic-kernel/agents</t>
         </is>
       </c>
-      <c r="D17" s="1" t="inlineStr">
+      <c r="D17" s="16" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="4" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="7" t="n"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H17" s="4" t="n">
+      <c r="H17" s="7" t="n">
         <v>46113</v>
       </c>
-      <c r="I17" s="1" t="n"/>
-      <c r="J17" s="1" t="inlineStr">
+      <c r="I17" s="16" t="n"/>
+      <c r="J17" s="16" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K17" s="1" t="inlineStr">
+      <c r="K17" s="16" t="inlineStr">
         <is>
           <t>Skills; Tools; Orchestration</t>
         </is>
       </c>
-      <c r="L17" s="1" t="inlineStr">
+      <c r="L17" s="16" t="inlineStr">
         <is>
           <t>Architecture; Implementation</t>
         </is>
       </c>
-      <c r="M17" s="1" t="inlineStr">
+      <c r="M17" s="16" t="inlineStr">
         <is>
           <t>Useful for enterprise-grade agent workflows</t>
         </is>
       </c>
-      <c r="N17" s="1" t="inlineStr">
+      <c r="N17" s="16" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="O17" s="1" t="inlineStr">
+      <c r="O17" s="16" t="inlineStr">
         <is>
           <t>Strong .NET + Python support.</t>
         </is>
       </c>
-      <c r="Q17" s="11" t="n">
+      <c r="Q17" s="18" t="n">
         <v>46113</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="0" t="inlineStr">
         <is>
           <t>4ccfda21</t>
         </is>
       </c>
-      <c r="B18" s="1" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>HuggingFace Inference Endpoints</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>https://huggingface.co/inference-endpoints</t>
         </is>
       </c>
-      <c r="D18" s="1" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>HuggingFace</t>
         </is>
       </c>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="4" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="7" t="n"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H18" s="4" t="n">
+      <c r="H18" s="7" t="n">
         <v>46082</v>
       </c>
-      <c r="I18" s="1" t="n"/>
-      <c r="J18" s="1" t="inlineStr">
+      <c r="I18" s="16" t="n"/>
+      <c r="J18" s="16" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K18" s="1" t="inlineStr">
+      <c r="K18" s="16" t="inlineStr">
         <is>
           <t>Model Integration; Tool-Ready Endpoints</t>
         </is>
       </c>
-      <c r="L18" s="1" t="inlineStr">
+      <c r="L18" s="16" t="inlineStr">
         <is>
           <t>Architecture; Deployment</t>
         </is>
       </c>
-      <c r="M18" s="1" t="inlineStr">
+      <c r="M18" s="16" t="inlineStr">
         <is>
           <t>Useful for hosted inference in research</t>
         </is>
       </c>
-      <c r="N18" s="1" t="inlineStr">
+      <c r="N18" s="16" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="O18" s="1" t="inlineStr">
+      <c r="O18" s="16" t="inlineStr">
         <is>
           <t>Good for reproducibility.</t>
         </is>
       </c>
-      <c r="Q18" s="11" t="n">
+      <c r="Q18" s="18" t="n">
         <v>46082</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="0" t="inlineStr">
         <is>
           <t>2e24be4d</t>
         </is>
       </c>
-      <c r="B19" s="1" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>OpenAI Evaluations (Evals)</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>https://platform.openai.com/docs/guides/evals</t>
         </is>
       </c>
-      <c r="D19" s="1" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="4" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="7" t="n"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H19" s="4" t="n">
+      <c r="H19" s="7" t="n">
         <v>46113</v>
       </c>
-      <c r="I19" s="1" t="n"/>
-      <c r="J19" s="1" t="inlineStr">
+      <c r="I19" s="16" t="n"/>
+      <c r="J19" s="16" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K19" s="1" t="inlineStr">
+      <c r="K19" s="16" t="inlineStr">
         <is>
           <t>Evaluation / testing; Safety / guardrails</t>
         </is>
       </c>
-      <c r="L19" s="1" t="inlineStr">
+      <c r="L19" s="16" t="inlineStr">
         <is>
           <t>Security; Governance</t>
         </is>
       </c>
-      <c r="M19" s="1" t="inlineStr">
+      <c r="M19" s="16" t="inlineStr">
         <is>
           <t>Relevant for agent safety in research platforms</t>
         </is>
       </c>
-      <c r="N19" s="1" t="inlineStr">
+      <c r="N19" s="16" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="O19" s="1" t="inlineStr">
+      <c r="O19" s="16" t="inlineStr">
         <is>
           <t>Useful for risk assessment.</t>
         </is>
       </c>
-      <c r="Q19" s="11" t="n">
+      <c r="Q19" s="18" t="n">
         <v>46113</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="0" t="inlineStr">
         <is>
           <t>6b9e7398</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>Anthropic Safety Guidelines</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr">
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>https://docs.anthropic.com/en/docs/safety</t>
         </is>
       </c>
-      <c r="D20" s="1" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>Anthropic</t>
         </is>
       </c>
-      <c r="E20" s="3" t="n"/>
-      <c r="F20" s="4" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="7" t="n"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H20" s="4" t="n">
+      <c r="H20" s="7" t="n">
         <v>46113</v>
       </c>
-      <c r="I20" s="1" t="n"/>
-      <c r="J20" s="1" t="inlineStr">
+      <c r="I20" s="16" t="n"/>
+      <c r="J20" s="16" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K20" s="1" t="inlineStr">
+      <c r="K20" s="16" t="inlineStr">
         <is>
           <t>Safety / guardrails; Safe Tool Use</t>
         </is>
       </c>
-      <c r="L20" s="1" t="inlineStr">
+      <c r="L20" s="16" t="inlineStr">
         <is>
           <t>Governance; Security</t>
         </is>
       </c>
-      <c r="M20" s="1" t="inlineStr">
+      <c r="M20" s="16" t="inlineStr">
         <is>
           <t>Useful for research governance teams</t>
         </is>
       </c>
-      <c r="N20" s="1" t="inlineStr">
+      <c r="N20" s="16" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="O20" s="1" t="inlineStr">
+      <c r="O20" s="16" t="inlineStr">
         <is>
           <t>Strong alignment with institutional risk controls.</t>
         </is>
       </c>
-      <c r="Q20" s="11" t="n">
+      <c r="Q20" s="18" t="n">
         <v>46113</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="0" t="inlineStr">
         <is>
           <t>69804f39</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>Microsoft Responsible AI Standard</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>https://www.microsoft.com/ai/responsible-ai</t>
         </is>
       </c>
-      <c r="D21" s="1" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="E21" s="3" t="n"/>
-      <c r="F21" s="8" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="12" t="n"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H21" s="8" t="n">
+      <c r="H21" s="12" t="n">
         <v>45992</v>
       </c>
-      <c r="I21" s="1" t="n"/>
-      <c r="J21" s="1" t="inlineStr">
+      <c r="I21" s="16" t="n"/>
+      <c r="J21" s="16" t="inlineStr">
         <is>
           <t>Governance Guidance</t>
         </is>
       </c>
-      <c r="K21" s="1" t="inlineStr">
+      <c r="K21" s="16" t="inlineStr">
         <is>
           <t>Safety / guardrails; Governance; Risk Controls</t>
         </is>
       </c>
-      <c r="L21" s="1" t="inlineStr">
+      <c r="L21" s="16" t="inlineStr">
         <is>
           <t>Data governance; Security</t>
         </is>
       </c>
-      <c r="M21" s="1" t="inlineStr">
+      <c r="M21" s="16" t="inlineStr">
         <is>
           <t>Relevant for institutional AI governance</t>
         </is>
       </c>
-      <c r="N21" s="1" t="inlineStr">
+      <c r="N21" s="16" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="O21" s="1" t="inlineStr">
+      <c r="O21" s="16" t="inlineStr">
         <is>
           <t>Widely adopted governance framework.</t>
         </is>
       </c>
-      <c r="Q21" s="11" t="n">
+      <c r="Q21" s="18" t="n">
         <v>45992</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="0" t="inlineStr">
         <is>
           <t>3758624e</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>vLLM Documentation</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
         <is>
           <t>https://docs.vllm.ai</t>
         </is>
       </c>
-      <c r="D22" s="1" t="inlineStr">
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t>vLLM Project Team</t>
         </is>
       </c>
-      <c r="E22" s="3" t="n"/>
+      <c r="E22" s="6" t="n"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H22" s="4" t="n">
+      <c r="H22" s="7" t="n">
         <v>46113</v>
       </c>
-      <c r="I22" s="1" t="n"/>
-      <c r="J22" s="1" t="inlineStr">
+      <c r="I22" s="16" t="n"/>
+      <c r="J22" s="16" t="inlineStr">
         <is>
           <t>Inference Framework</t>
         </is>
       </c>
-      <c r="K22" s="1" t="inlineStr">
+      <c r="K22" s="16" t="inlineStr">
         <is>
           <t>Deployment patterns; Tools</t>
         </is>
       </c>
-      <c r="L22" s="1" t="inlineStr">
+      <c r="L22" s="16" t="inlineStr">
         <is>
           <t>Self‑hosted AI; Architecture; Implementation; Deployment</t>
         </is>
       </c>
-      <c r="M22" s="1" t="inlineStr">
+      <c r="M22" s="16" t="inlineStr">
         <is>
           <t>High (Industry-standard VPC runtime engine)</t>
         </is>
       </c>
-      <c r="N22" s="1" t="inlineStr">
+      <c r="N22" s="16" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="O22" s="1" t="inlineStr">
+      <c r="O22" s="16" t="inlineStr">
         <is>
           <t>Essential for secure TLAs via PagedAttention and FP8/AWQ optimization. Capabilities: Parallel sampling &amp; tool-calling.</t>
         </is>
       </c>
-      <c r="Q22" s="11" t="n">
+      <c r="Q22" s="18" t="n">
         <v>46113</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="0" t="inlineStr">
         <is>
           <t>8a50b5eb</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>Ollama Documentation</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C23" s="16" t="inlineStr">
         <is>
           <t>https://github.com/ollama/ollama</t>
         </is>
       </c>
-      <c r="D23" s="1" t="inlineStr">
+      <c r="D23" s="16" t="inlineStr">
         <is>
           <t>Ollama Community</t>
         </is>
       </c>
-      <c r="E23" s="3" t="n"/>
+      <c r="E23" s="6" t="n"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H23" s="4" t="n">
+      <c r="H23" s="7" t="n">
         <v>46113</v>
       </c>
-      <c r="I23" s="1" t="n"/>
-      <c r="J23" s="1" t="inlineStr">
+      <c r="I23" s="16" t="n"/>
+      <c r="J23" s="16" t="inlineStr">
         <is>
           <t>Local Application Sandbox</t>
         </is>
       </c>
-      <c r="K23" s="1" t="inlineStr">
+      <c r="K23" s="16" t="inlineStr">
         <is>
           <t>Deployment patterns</t>
         </is>
       </c>
-      <c r="L23" s="1" t="inlineStr">
+      <c r="L23" s="16" t="inlineStr">
         <is>
           <t>Self‑hosted AI; Implementation; Deployment</t>
         </is>
       </c>
-      <c r="M23" s="1" t="inlineStr">
+      <c r="M23" s="16" t="inlineStr">
         <is>
           <t>Medium-High (Local workstation co-pilot)</t>
         </is>
       </c>
-      <c r="N23" s="1" t="inlineStr">
+      <c r="N23" s="16" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="O23" s="1" t="inlineStr">
+      <c r="O23" s="16" t="inlineStr">
         <is>
           <t>Eliminates network dependency errors by cleanly bundling open model weights. Capabilities: Local embedding &amp; zero-config tools.</t>
         </is>
       </c>
-      <c r="Q23" s="11" t="n">
+      <c r="Q23" s="18" t="n">
         <v>46113</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="0" t="inlineStr">
         <is>
           <t>763797cd</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Llama.cpp </t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>https://github.com/ggerganov/llama.cpp</t>
         </is>
       </c>
-      <c r="D24" s="1" t="inlineStr">
+      <c r="D24" s="16" t="inlineStr">
         <is>
           <t>Georgi Gerganov</t>
         </is>
       </c>
-      <c r="E24" s="3" t="n"/>
-      <c r="F24" s="1" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="16" t="n"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H24" s="9" t="n">
+      <c r="H24" s="14" t="n">
         <v>46162</v>
       </c>
-      <c r="I24" s="1" t="inlineStr">
+      <c r="I24" s="16" t="inlineStr">
         <is>
           <t>b9253</t>
         </is>
       </c>
-      <c r="J24" s="1" t="inlineStr">
+      <c r="J24" s="16" t="inlineStr">
         <is>
           <t>Github Code Repository</t>
         </is>
       </c>
-      <c r="K24" s="1" t="inlineStr">
+      <c r="K24" s="16" t="inlineStr">
         <is>
           <t>Deployment patterns</t>
         </is>
       </c>
-      <c r="L24" s="1" t="inlineStr">
+      <c r="L24" s="16" t="inlineStr">
         <is>
           <t>Self‑hosted AI; Architecture; Implementation; Deployment</t>
         </is>
       </c>
-      <c r="M24" s="1" t="inlineStr">
+      <c r="M24" s="16" t="inlineStr">
         <is>
           <t>High (Enables reasoning on variable local hardware)</t>
         </is>
       </c>
-      <c r="N24" s="1" t="inlineStr">
+      <c r="N24" s="16" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="O24" s="1" t="inlineStr">
+      <c r="O24" s="16" t="inlineStr">
         <is>
           <t>Grammar constraints ensure localized agentic pipelines always return valid JSON/code. Capabilities: Grammar-based constrained sampling.</t>
         </is>
       </c>
-      <c r="Q24" s="11" t="n">
+      <c r="Q24" s="18" t="n">
         <v>46162</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="0" t="inlineStr">
         <is>
           <t>2d2470f7</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
+      <c r="B25" s="16" t="inlineStr">
         <is>
           <t>Open WebUI Documentation</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C25" s="16" t="inlineStr">
         <is>
           <t>https://docs.openwebui.com</t>
         </is>
       </c>
-      <c r="D25" s="1" t="inlineStr">
+      <c r="D25" s="16" t="inlineStr">
         <is>
           <t>Open WebUI Core Team</t>
         </is>
       </c>
-      <c r="E25" s="3" t="n"/>
+      <c r="E25" s="6" t="n"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H25" s="4" t="n">
+      <c r="H25" s="7" t="n">
         <v>46113</v>
       </c>
-      <c r="I25" s="1" t="n"/>
-      <c r="J25" s="1" t="inlineStr">
+      <c r="I25" s="16" t="n"/>
+      <c r="J25" s="16" t="inlineStr">
         <is>
           <t>Enterprise Control Interface</t>
         </is>
       </c>
-      <c r="K25" s="1" t="inlineStr">
+      <c r="K25" s="16" t="inlineStr">
         <is>
           <t>Retrieval</t>
         </is>
       </c>
-      <c r="L25" s="1" t="inlineStr">
+      <c r="L25" s="16" t="inlineStr">
         <is>
           <t>Self‑hosted AI; Implementation; Deployment</t>
         </is>
       </c>
-      <c r="M25" s="1" t="inlineStr">
+      <c r="M25" s="16" t="inlineStr">
         <is>
           <t>High (Enterprise-grade firewall interface)</t>
         </is>
       </c>
-      <c r="N25" s="1" t="inlineStr">
+      <c r="N25" s="16" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="O25" s="1" t="inlineStr">
+      <c r="O25" s="16" t="inlineStr">
         <is>
           <t>Solves local file parsing/RAG bottlenecks entirely within secure client networks. Capabilities: Local RAG pipelines &amp; offline functions.</t>
         </is>
       </c>
-      <c r="Q25" s="11" t="n">
+      <c r="Q25" s="18" t="n">
         <v>46113</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="0" t="inlineStr">
         <is>
           <t>eb79015c</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t>NVIDIA NIM Air-Gap Deployment Guide</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C26" s="16" t="inlineStr">
         <is>
           <t>https://docs.nvidia.com/nim/large-language-models/latest/deploy-air-gap.html</t>
         </is>
       </c>
-      <c r="D26" s="1" t="inlineStr">
+      <c r="D26" s="16" t="inlineStr">
         <is>
           <t>NVIDIA</t>
         </is>
       </c>
-      <c r="E26" s="3" t="n"/>
+      <c r="E26" s="6" t="n"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H26" s="1" t="n">
+      <c r="H26" s="16" t="n">
         <v>2026</v>
       </c>
-      <c r="I26" s="1" t="n"/>
-      <c r="J26" s="1" t="inlineStr">
+      <c r="I26" s="16" t="n"/>
+      <c r="J26" s="16" t="inlineStr">
         <is>
           <t>Reference Architecture</t>
         </is>
       </c>
-      <c r="K26" s="1" t="inlineStr">
+      <c r="K26" s="16" t="inlineStr">
         <is>
           <t>Deployment patterns</t>
         </is>
       </c>
-      <c r="L26" s="1" t="inlineStr">
+      <c r="L26" s="16" t="inlineStr">
         <is>
           <t>Self‑hosted AI; Compute Infrastructure; Implementation; Network Isolation; Infrastructure Security</t>
         </is>
       </c>
-      <c r="M26" s="1" t="inlineStr">
+      <c r="M26" s="16" t="inlineStr">
         <is>
           <t>Critical (Standardizes secure distribution of optimized weights)</t>
         </is>
       </c>
-      <c r="N26" s="1" t="inlineStr">
+      <c r="N26" s="16" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="O26" s="1" t="inlineStr">
+      <c r="O26" s="16" t="inlineStr">
         <is>
           <t>Outlines the exact connected-to-disconnected asset transfer workflow for enterprise GPUs. Capabilities: Tensor-parallel caching &amp; optimized tool-calling.</t>
         </is>
       </c>
-      <c r="Q26" s="11" t="n">
+      <c r="Q26" s="18" t="n">
         <v>46150</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="0" t="inlineStr">
         <is>
           <t>80527de7</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>Harbor User Documentation</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C27" s="16" t="inlineStr">
         <is>
           <t>https://goharbor.io/docs/</t>
         </is>
       </c>
-      <c r="D27" s="1" t="inlineStr">
+      <c r="D27" s="16" t="inlineStr">
         <is>
           <t>Cloud Native Computing Foundation (CNCF)</t>
         </is>
       </c>
-      <c r="E27" s="3" t="n"/>
+      <c r="E27" s="6" t="n"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H27" s="1" t="n">
+      <c r="H27" s="16" t="n">
         <v>2026</v>
       </c>
-      <c r="I27" s="1" t="n"/>
-      <c r="J27" s="1" t="inlineStr">
+      <c r="I27" s="16" t="n"/>
+      <c r="J27" s="16" t="inlineStr">
         <is>
           <t>Container Registry</t>
         </is>
       </c>
-      <c r="K27" s="1" t="inlineStr">
+      <c r="K27" s="16" t="inlineStr">
         <is>
           <t>Deployment patterns</t>
         </is>
       </c>
-      <c r="L27" s="1" t="inlineStr">
+      <c r="L27" s="16" t="inlineStr">
         <is>
           <t>Self‑hosted AI; Implementation; Network Isolation; Infrastructure Security; Governance</t>
         </is>
       </c>
-      <c r="M27" s="1" t="inlineStr">
+      <c r="M27" s="16" t="inlineStr">
         <is>
           <t>High (Necessary foundation for secure cluster registries)</t>
         </is>
       </c>
-      <c r="N27" s="1" t="inlineStr">
+      <c r="N27" s="16" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="O27" s="1" t="inlineStr">
+      <c r="O27" s="16" t="inlineStr">
         <is>
           <t>Built-in vulnerability scanning ensures agent images remain clean behind the firewall. Capabilities: Artifact version-locking &amp; immutable tags.</t>
         </is>
       </c>
-      <c r="Q27" s="11" t="n">
+      <c r="Q27" s="18" t="n">
         <v>46150</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="0" t="inlineStr">
         <is>
           <t>b4b5a468</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>AI Engineering Blueprint for On-Premises RAG Systems</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C28" s="16" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2604.01395</t>
         </is>
       </c>
-      <c r="D28" s="1" t="inlineStr">
+      <c r="D28" s="16" t="inlineStr">
         <is>
           <t>arXiv (2604.01395)</t>
         </is>
       </c>
-      <c r="E28" s="3" t="n"/>
+      <c r="E28" s="6" t="n"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H28" s="1" t="n">
+      <c r="H28" s="16" t="n">
         <v>2026</v>
       </c>
-      <c r="I28" s="1" t="n"/>
-      <c r="J28" s="1" t="inlineStr">
+      <c r="I28" s="16" t="n"/>
+      <c r="J28" s="16" t="inlineStr">
         <is>
           <t>Scientific Literature</t>
         </is>
       </c>
-      <c r="K28" s="1" t="inlineStr">
+      <c r="K28" s="16" t="inlineStr">
         <is>
           <t>Deployment patterns; Retrieval</t>
         </is>
       </c>
-      <c r="L28" s="1" t="inlineStr">
+      <c r="L28" s="16" t="inlineStr">
         <is>
           <t>Self‑hosted AI; Infrastructure Security</t>
         </is>
       </c>
-      <c r="M28" s="1" t="inlineStr">
+      <c r="M28" s="16" t="inlineStr">
         <is>
           <t>High (Academic/industry validated system design blueprint)</t>
         </is>
       </c>
-      <c r="N28" s="1" t="inlineStr">
+      <c r="N28" s="16" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="O28" s="1" t="inlineStr">
+      <c r="O28" s="16" t="inlineStr">
         <is>
           <t>Moves past simple how-to guides into formal data isolation and local compliance frameworks. Capabilities: End-to-end local reference applications.</t>
         </is>
       </c>
-      <c r="Q28" s="11" t="n">
+      <c r="Q28" s="18" t="n">
         <v>46150</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="0" t="inlineStr">
         <is>
           <t>0d0a50a7</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>On-Premise vs Cloud: GenAI TCO (2026 Edition)</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">https://lenovopress.lenovo.com/lp2368-on-premise-vs-cloud-generative-ai-total-cost-of-ownership-2026-edition </t>
         </is>
       </c>
-      <c r="D29" s="1" t="inlineStr">
+      <c r="D29" s="16" t="inlineStr">
         <is>
           <t>Lenovo Press</t>
         </is>
       </c>
-      <c r="E29" s="3" t="n"/>
-      <c r="F29" s="1" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="16" t="n"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>@biddyman11</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="n">
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="n">
         <v>46054</v>
       </c>
-      <c r="I29" s="1" t="inlineStr">
+      <c r="I29" s="16" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="J29" s="1" t="inlineStr">
+      <c r="J29" s="16" t="inlineStr">
         <is>
           <t>Whitepaper</t>
         </is>
       </c>
-      <c r="K29" s="1" t="inlineStr">
+      <c r="K29" s="16" t="inlineStr">
         <is>
           <t>Deployment patterns</t>
         </is>
       </c>
-      <c r="L29" s="1" t="inlineStr">
+      <c r="L29" s="16" t="inlineStr">
         <is>
           <t>Self‑hosted AI; Architecture; Governance</t>
         </is>
       </c>
-      <c r="M29" s="1" t="inlineStr">
+      <c r="M29" s="16" t="inlineStr">
         <is>
           <t>High (Mandatory for spec'ing out server node VRAM limits)</t>
         </is>
       </c>
-      <c r="N29" s="1" t="inlineStr">
+      <c r="N29" s="16" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="O29" s="1" t="inlineStr">
-        <is>
-          <t>Discusses a "Token Economics" framework. Breaks down the "Memory Wall" economics showing an on-prem breakeven velocity of ~4 months. Capabilities: Hardware performance scaling &amp; VRAM sizing.</t>
-        </is>
-      </c>
-      <c r="Q29" s="11" t="n">
+      <c r="O29" s="16" t="inlineStr">
+        <is>
+          <t>Breaks down the "Memory Wall" economics showing an on-prem breakeven velocity of ~4 months. Capabilities: Hardware performance scaling &amp; VRAM sizing.</t>
+        </is>
+      </c>
+      <c r="Q29" s="18" t="n">
         <v>46054</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="0" t="inlineStr">
         <is>
           <t>359b5ac8</t>
         </is>
       </c>
-      <c r="B30" s="1" t="inlineStr">
+      <c r="B30" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Coalition for Secure AI (CoSAI) </t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>https://www.coalitionforsecureai.org/</t>
         </is>
       </c>
-      <c r="D30" s="1" t="inlineStr">
+      <c r="D30" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Coalition for Secure AI (CoSAI) </t>
         </is>
       </c>
-      <c r="E30" s="9" t="n"/>
-      <c r="F30" s="1" t="n"/>
+      <c r="E30" s="14" t="n">
+        <v>46174</v>
+      </c>
+      <c r="F30" s="16" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>@biddyman11</t>
-        </is>
-      </c>
-      <c r="H30" s="9" t="n">
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H30" s="14" t="n">
         <v>46174</v>
       </c>
-      <c r="J30" s="1" t="inlineStr">
+      <c r="J30" s="16" t="inlineStr">
         <is>
           <t>Security Guidance &amp; Resources</t>
         </is>
       </c>
-      <c r="K30" s="1" t="inlineStr">
+      <c r="K30" s="16" t="inlineStr">
         <is>
           <t>Safety / guardrails; Safe Tool Use</t>
         </is>
       </c>
-      <c r="L30" s="1" t="inlineStr">
+      <c r="L30" s="16" t="inlineStr">
         <is>
           <t>Infrastructure Security; Security</t>
         </is>
       </c>
-      <c r="M30" s="1" t="inlineStr">
+      <c r="M30" s="16" t="inlineStr">
         <is>
           <t>Relevant security expertise and best practices for secure AI development and deployment</t>
         </is>
       </c>
-      <c r="N30" s="1" t="inlineStr">
+      <c r="N30" s="16" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="O30" s="1" t="inlineStr">
-        <is>
-          <t>The Coalition for Secure AI (CoSAI) is an open ecosystem of AI and security experts. See https://github.com/cosai-oasis/ws2-defenders</t>
-        </is>
-      </c>
-      <c r="Q30" s="11" t="n">
+      <c r="O30" s="16" t="inlineStr">
+        <is>
+          <t>The Coalition for Secure AI (CoSAI) is an open ecosystem of AI and security experts</t>
+        </is>
+      </c>
+      <c r="Q30" s="18" t="n">
         <v>46174</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="0" t="inlineStr">
         <is>
           <t>5f3954c2</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
+      <c r="B31" s="16" t="inlineStr">
         <is>
           <t>Anthropic Project Glasswing</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>https://www.anthropic.com/glasswing</t>
         </is>
       </c>
-      <c r="D31" s="1" t="inlineStr">
+      <c r="D31" s="16" t="inlineStr">
         <is>
           <t>Anthropic</t>
         </is>
       </c>
-      <c r="E31" s="9" t="n">
+      <c r="E31" s="14" t="n">
         <v>46182</v>
       </c>
-      <c r="F31" s="1" t="inlineStr">
+      <c r="F31" s="16" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
@@ -2630,72 +2547,72 @@
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H31" s="9" t="n">
+      <c r="H31" s="14" t="n">
         <v>46119</v>
       </c>
-      <c r="I31" s="10" t="n"/>
-      <c r="J31" s="1" t="inlineStr">
+      <c r="I31" s="15" t="n"/>
+      <c r="J31" s="16" t="inlineStr">
         <is>
           <t>Security Guidance &amp; Resources</t>
         </is>
       </c>
-      <c r="K31" s="1" t="inlineStr">
+      <c r="K31" s="16" t="inlineStr">
         <is>
           <t>Cybersecurity</t>
         </is>
       </c>
-      <c r="L31" s="1" t="inlineStr">
+      <c r="L31" s="16" t="inlineStr">
         <is>
           <t>Infrastructure Security; Security</t>
         </is>
       </c>
-      <c r="M31" s="1" t="inlineStr">
+      <c r="M31" s="16" t="inlineStr">
         <is>
           <t>AI models that find high-severity vulnerabilities</t>
         </is>
       </c>
-      <c r="N31" s="1" t="inlineStr">
+      <c r="N31" s="16" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="O31" s="2" t="inlineStr">
+      <c r="O31" s="5" t="inlineStr">
         <is>
           <t>See Claude Mythos Preview</t>
         </is>
       </c>
-      <c r="P31" s="11" t="n">
+      <c r="P31" s="18" t="n">
         <v>46119</v>
       </c>
-      <c r="Q31" s="11" t="n">
+      <c r="Q31" s="18" t="n">
         <v>46119</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="0" t="inlineStr">
         <is>
           <t>1c277820</t>
         </is>
       </c>
-      <c r="B32" s="1" t="inlineStr">
+      <c r="B32" s="16" t="inlineStr">
         <is>
           <t>Docker AI Governance &amp; Sandboxes</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>https://docs.docker.com/ai/sandboxes/governance/org/</t>
         </is>
       </c>
-      <c r="D32" s="1" t="inlineStr">
+      <c r="D32" s="16" t="inlineStr">
         <is>
           <t>Docker</t>
         </is>
       </c>
-      <c r="E32" s="9" t="n">
+      <c r="E32" s="14" t="n">
         <v>46219</v>
       </c>
-      <c r="F32" s="1" t="inlineStr">
+      <c r="F32" s="16" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
@@ -2705,73 +2622,73 @@
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H32" s="9" t="n">
+      <c r="H32" s="14" t="n">
         <v>46213</v>
       </c>
-      <c r="I32" s="6" t="inlineStr">
+      <c r="I32" s="9" t="inlineStr">
         <is>
           <t>0.35.0</t>
         </is>
       </c>
-      <c r="J32" s="1" t="inlineStr">
+      <c r="J32" s="16" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K32" s="1" t="inlineStr">
+      <c r="K32" s="16" t="inlineStr">
         <is>
           <t>Sandbox; MCP</t>
         </is>
       </c>
-      <c r="L32" s="1" t="inlineStr">
+      <c r="L32" s="16" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="M32" s="1" t="inlineStr">
+      <c r="M32" s="16" t="inlineStr">
         <is>
           <t>Good AI governance topics</t>
         </is>
       </c>
-      <c r="N32" s="1" t="inlineStr">
+      <c r="N32" s="16" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="O32" s="1" t="inlineStr">
+      <c r="O32" s="16" t="inlineStr">
         <is>
           <t>See blog article: https://www.docker.com/blog/the-3cs-a-framework-for-ai-agent-security/</t>
         </is>
       </c>
-      <c r="Q32" s="11" t="n">
+      <c r="Q32" s="18" t="n">
         <v>46213</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="0" t="inlineStr">
         <is>
           <t>b39dc1d1</t>
         </is>
       </c>
-      <c r="B33" s="1" t="inlineStr">
+      <c r="B33" s="16" t="inlineStr">
         <is>
           <t>Responses API</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>https://developers.openai.com/api/docs/guides/migrate-to-responses</t>
         </is>
       </c>
-      <c r="D33" s="1" t="inlineStr">
+      <c r="D33" s="16" t="inlineStr">
         <is>
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="E33" s="9" t="n">
+      <c r="E33" s="14" t="n">
         <v>46220</v>
       </c>
-      <c r="F33" s="1" t="inlineStr">
+      <c r="F33" s="16" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
@@ -2781,98 +2698,98 @@
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H33" s="9" t="n">
+      <c r="H33" s="14" t="n">
         <v>46212</v>
       </c>
-      <c r="I33" s="1" t="inlineStr">
+      <c r="I33" s="16" t="inlineStr">
         <is>
           <t>GPT-5.6</t>
         </is>
       </c>
-      <c r="J33" s="1" t="inlineStr">
+      <c r="J33" s="16" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K33" s="1" t="inlineStr">
+      <c r="K33" s="16" t="inlineStr">
         <is>
           <t>Tools; Skills; Retrieval</t>
         </is>
       </c>
-      <c r="L33" s="1" t="inlineStr">
+      <c r="L33" s="16" t="inlineStr">
         <is>
           <t>Architecture</t>
         </is>
       </c>
-      <c r="M33" s="1" t="inlineStr">
+      <c r="M33" s="16" t="inlineStr">
         <is>
           <t>Useful for domain-specific agents</t>
         </is>
       </c>
-      <c r="N33" s="1" t="inlineStr">
+      <c r="N33" s="16" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="O33" s="1" t="inlineStr">
+      <c r="O33" s="16" t="inlineStr">
         <is>
           <t>MIgrated from API Assistants  - now deprecated.</t>
         </is>
       </c>
-      <c r="Q33" s="11" t="n">
+      <c r="Q33" s="18" t="n">
         <v>46212</v>
       </c>
     </row>
     <row r="34">
-      <c r="L34" s="1" t="n"/>
+      <c r="L34" s="16" t="n"/>
     </row>
     <row r="35">
-      <c r="L35" s="1" t="n"/>
+      <c r="L35" s="16" t="n"/>
     </row>
     <row r="36">
-      <c r="L36" s="1" t="n"/>
+      <c r="L36" s="16" t="n"/>
     </row>
     <row r="37">
-      <c r="L37" s="1" t="n"/>
+      <c r="L37" s="16" t="n"/>
     </row>
     <row r="38">
-      <c r="L38" s="1" t="n"/>
+      <c r="L38" s="16" t="n"/>
     </row>
     <row r="39">
-      <c r="L39" s="1" t="n"/>
+      <c r="L39" s="16" t="n"/>
     </row>
     <row r="40">
-      <c r="L40" s="1" t="n"/>
+      <c r="L40" s="16" t="n"/>
     </row>
     <row r="41">
-      <c r="L41" s="1" t="n"/>
+      <c r="L41" s="16" t="n"/>
     </row>
     <row r="42">
-      <c r="L42" s="1" t="n"/>
+      <c r="L42" s="16" t="n"/>
     </row>
     <row r="43">
-      <c r="L43" s="1" t="n"/>
+      <c r="L43" s="16" t="n"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D1:D12 D14:D994 F24 F30:F33 G32">
-    <cfRule type="expression" priority="4" dxfId="3">
-      <formula>D1&gt;46151</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J1:J994">
-    <cfRule type="notContainsBlanks" priority="5" dxfId="2">
-      <formula>LEN(TRIM(J1))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="L1:L994">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Emerging"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
       <formula>"Mature"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"Research"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1:D12 D14:D994 F24 F30:F33 G32">
+    <cfRule type="expression" priority="4" dxfId="3">
+      <formula>D1&gt;46151.0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J1:J994">
+    <cfRule type="notContainsBlanks" priority="5" dxfId="0">
+      <formula>LEN(TRIM(J1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -2882,15 +2799,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" location="0350" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" location="0350" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2903,40 +2819,40 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:P2"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="22.140625" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" style="17" min="1" max="1"/>
+    <col width="22.13" customWidth="1" style="17" min="2" max="2"/>
+    <col width="20" customWidth="1" style="17" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>Resource Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="16" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="16" t="inlineStr">
         <is>
           <t>Source Organization</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="16" t="inlineStr">
         <is>
           <t>Last Verified</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="16" t="inlineStr">
         <is>
           <t>Verified By</t>
         </is>
@@ -2946,77 +2862,77 @@
           <t>Added/Edited By</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="16" t="inlineStr">
         <is>
           <t>Deprecation Date / Last Updated</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="16" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="16" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="16" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="16" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="16" t="inlineStr">
         <is>
           <t>Relevance to Research Cyberinfrastructure</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="16" t="inlineStr">
         <is>
           <t>Maturity Level</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="16" t="inlineStr">
         <is>
           <t>Notes / Key Takeaways</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="0" t="inlineStr">
         <is>
           <t>Discovery Date</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>805047b4</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>OpenAI Assistants API</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>https://platform.openai.com/docs/assistants</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr">
         <is>
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="6" t="n">
         <v>46150</v>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
@@ -3026,84 +2942,89 @@
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="H2" s="7" t="n">
         <v>46260</v>
       </c>
-      <c r="I2" s="1" t="n"/>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="I2" s="16" t="n"/>
+      <c r="J2" s="16" t="inlineStr">
         <is>
           <t>API Reference</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="K2" s="16" t="inlineStr">
         <is>
           <t>Tools; Skills; Retrieval</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="L2" s="16" t="inlineStr">
         <is>
           <t>Architecture; Implementation</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="M2" s="16" t="inlineStr">
         <is>
           <t>Useful for domain-specific agents</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="N2" s="16" t="inlineStr">
         <is>
           <t>Deprecated</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="O2" s="16" t="inlineStr">
         <is>
           <t>Stable API surface.</t>
         </is>
       </c>
-      <c r="P2" s="11" t="n">
+      <c r="P2" s="18" t="n">
         <v>46150</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D1:D2">
-    <cfRule type="expression" priority="5" dxfId="3">
-      <formula>D1&gt;46151</formula>
+  <conditionalFormatting sqref="L2">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"Emerging"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"Mature"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L1:L2">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>"Research"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:J2">
-    <cfRule type="notContainsBlanks" priority="4" dxfId="2">
+    <cfRule type="notContainsBlanks" priority="4" dxfId="0">
       <formula>LEN(TRIM(J1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1">
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="0">
-      <formula>"Adolescent"</formula>
+  <conditionalFormatting sqref="D2">
+    <cfRule type="expression" priority="5" dxfId="3">
+      <formula>D2&gt;46151.0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:L1">
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
       <formula>"Emerging"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="7" operator="equal" dxfId="1">
       <formula>"Mature"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L1:L2">
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="0">
-      <formula>"Research"</formula>
+  <conditionalFormatting sqref="K1">
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="2">
+      <formula>"Adolescent"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1">
+    <cfRule type="expression" priority="9" dxfId="3">
+      <formula>D1&gt;46151.0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1:L993">
-    <cfRule type="cellIs" priority="10" operator="equal" dxfId="6">
+    <cfRule type="cellIs" priority="10" operator="equal" dxfId="4">
       <formula>"Deprecated"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="2">
-      <formula>"Emerging"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
-      <formula>"Mature"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -3125,40 +3046,40 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N8"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="29.85546875" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" style="17" min="1" max="1"/>
+    <col width="29.88" customWidth="1" style="17" min="3" max="3"/>
+    <col width="20" customWidth="1" style="17" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>Resource Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="16" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="16" t="inlineStr">
         <is>
           <t>Source Organization</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="16" t="inlineStr">
         <is>
           <t>Last Verified</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="16" t="inlineStr">
         <is>
           <t>Verified By</t>
         </is>
@@ -3168,67 +3089,67 @@
           <t>Added/Edited By</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="16" t="inlineStr">
         <is>
           <t>Last Updated</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="16" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="16" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="16" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="16" t="inlineStr">
         <is>
           <t>Maturity Level</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="16" t="inlineStr">
         <is>
           <t>Notes / Key Takeaways</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="0" t="inlineStr">
         <is>
           <t>Discovery Date</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>ba114fad</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>Databricks Coding Agent Benchmark</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>https://www.databricks.com/blog/benchmarking-coding-agents-databricks-multi-million-line-codebase</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr">
         <is>
           <t>Databricks</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="6" t="n">
         <v>46216</v>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
@@ -3238,63 +3159,63 @@
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H2" s="1" t="n">
+      <c r="H2" s="16" t="n">
         <v>2024</v>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="I2" s="16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="J2" s="16" t="inlineStr">
         <is>
           <t>Whitepaper</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="K2" s="16" t="inlineStr">
         <is>
           <t>Coding Agents</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="L2" s="16" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="M2" s="16" t="inlineStr">
         <is>
           <t>Evaluates State-Of-The-Art agent performance on multi-million line codebases to assess real-world software engineering capabilities.</t>
         </is>
       </c>
-      <c r="N2" s="11" t="n">
+      <c r="N2" s="18" t="n">
         <v>46216</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>4c170f7e</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Papers with Code </t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>https://paperswithcode.co/tasks/coding-agents</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>Hugging Face</t>
         </is>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="6" t="n">
         <v>46216</v>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
@@ -3304,332 +3225,332 @@
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H3" s="1" t="n">
+      <c r="H3" s="16" t="n">
         <v>2026</v>
       </c>
-      <c r="J3" s="1" t="inlineStr">
+      <c r="J3" s="16" t="inlineStr">
         <is>
           <t>Benchmark Collection</t>
         </is>
       </c>
-      <c r="K3" s="1" t="inlineStr">
+      <c r="K3" s="16" t="inlineStr">
         <is>
           <t>Coding Agents</t>
         </is>
       </c>
-      <c r="L3" s="1" t="inlineStr">
+      <c r="L3" s="16" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="M3" s="1" t="inlineStr">
+      <c r="M3" s="16" t="inlineStr">
         <is>
           <t>Papers with Code with State-Of-The-Art (SOTA) Codng Agent Benchmarks</t>
         </is>
       </c>
-      <c r="N3" s="11" t="n">
+      <c r="N3" s="18" t="n">
         <v>46216</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>b9ed03e7</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>SWE-Bench Pro</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>https://openreview.net/forum?id=9R2iUHhVfr</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>SWE-bench Team</t>
         </is>
       </c>
-      <c r="E4" s="3" t="n"/>
+      <c r="E4" s="6" t="n"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H4" s="1" t="n">
+      <c r="H4" s="16" t="n">
         <v>2025</v>
       </c>
-      <c r="I4" s="1" t="inlineStr">
+      <c r="I4" s="16" t="inlineStr">
         <is>
           <t>Pro</t>
         </is>
       </c>
-      <c r="J4" s="1" t="inlineStr">
+      <c r="J4" s="16" t="inlineStr">
         <is>
           <t>Whitepaper</t>
         </is>
       </c>
-      <c r="K4" s="1" t="inlineStr">
+      <c r="K4" s="16" t="inlineStr">
         <is>
           <t>Coding Agents</t>
         </is>
       </c>
-      <c r="L4" s="1" t="inlineStr">
+      <c r="L4" s="16" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="M4" s="1" t="inlineStr">
+      <c r="M4" s="16" t="inlineStr">
         <is>
           <t>Addresses limitations of original SWE-bench by focusing on long-horizon, complex, multi-file software engineering tasks.</t>
         </is>
       </c>
-      <c r="N4" s="11" t="n">
+      <c r="N4" s="18" t="n">
         <v>46216</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t>f487cdc5</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>SWE-Bench++</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2512.17419</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>Academic Researchers</t>
         </is>
       </c>
-      <c r="E5" s="3" t="n"/>
+      <c r="E5" s="6" t="n"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H5" s="1" t="n">
+      <c r="H5" s="16" t="n">
         <v>2025</v>
       </c>
-      <c r="J5" s="1" t="inlineStr">
+      <c r="J5" s="16" t="inlineStr">
         <is>
           <t>Whitepaper</t>
         </is>
       </c>
-      <c r="K5" s="1" t="inlineStr">
+      <c r="K5" s="16" t="inlineStr">
         <is>
           <t>Coding Agents</t>
         </is>
       </c>
-      <c r="L5" s="1" t="inlineStr">
+      <c r="L5" s="16" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="M5" s="1" t="inlineStr">
+      <c r="M5" s="16" t="inlineStr">
         <is>
           <t>Scalable framework that generates repository-level tasks from live GitHub PRs across 11 programming languages.</t>
         </is>
       </c>
-      <c r="N5" s="11" t="n">
+      <c r="N5" s="18" t="n">
         <v>46216</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="0" t="inlineStr">
         <is>
           <t>f37d4051</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>Terminal-Bench</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2601.11868</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>CISPA / Academic Researchers</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n"/>
+      <c r="E6" s="6" t="n"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H6" s="1" t="n">
+      <c r="H6" s="16" t="n">
         <v>2026</v>
       </c>
-      <c r="I6" s="1" t="n">
+      <c r="I6" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="J6" s="1" t="inlineStr">
+      <c r="J6" s="16" t="inlineStr">
         <is>
           <t>Whitepaper</t>
         </is>
       </c>
-      <c r="K6" s="1" t="inlineStr">
+      <c r="K6" s="16" t="inlineStr">
         <is>
           <t>Coding Agents</t>
         </is>
       </c>
-      <c r="L6" s="1" t="inlineStr">
+      <c r="L6" s="16" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="M6" s="1" t="inlineStr">
+      <c r="M6" s="16" t="inlineStr">
         <is>
           <t>Benchmarks agents on hard, realistic tasks within terminal/CLI environments.</t>
         </is>
       </c>
-      <c r="N6" s="11" t="n">
+      <c r="N6" s="18" t="n">
         <v>46216</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="0" t="inlineStr">
         <is>
           <t>acbc7354</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>c-CRAB</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2603.23448</t>
         </is>
       </c>
-      <c r="D7" s="1" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>Academic Researchers</t>
         </is>
       </c>
-      <c r="E7" s="3" t="n"/>
+      <c r="E7" s="6" t="n"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H7" s="1" t="n">
+      <c r="H7" s="16" t="n">
         <v>2026</v>
       </c>
-      <c r="I7" s="1" t="n">
+      <c r="I7" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="J7" s="1" t="inlineStr">
+      <c r="J7" s="16" t="inlineStr">
         <is>
           <t>Whitepaper</t>
         </is>
       </c>
-      <c r="K7" s="1" t="inlineStr">
+      <c r="K7" s="16" t="inlineStr">
         <is>
           <t>Coding Agents</t>
         </is>
       </c>
-      <c r="L7" s="1" t="inlineStr">
+      <c r="L7" s="16" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="M7" s="1" t="inlineStr">
+      <c r="M7" s="16" t="inlineStr">
         <is>
           <t>Benchmark specifically for evaluating the code review capabilities of AI agents.</t>
         </is>
       </c>
-      <c r="N7" s="11" t="n">
+      <c r="N7" s="18" t="n">
         <v>46216</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="0" t="inlineStr">
         <is>
           <t>edd19b89</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>SWE-Explore</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2606.07297</t>
         </is>
       </c>
-      <c r="D8" s="1" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>Academic Researchers</t>
         </is>
       </c>
-      <c r="E8" s="3" t="n"/>
+      <c r="E8" s="6" t="n"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H8" s="1" t="n">
+      <c r="H8" s="16" t="n">
         <v>2026</v>
       </c>
-      <c r="I8" s="1" t="n">
+      <c r="I8" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="J8" s="1" t="inlineStr">
+      <c r="J8" s="16" t="inlineStr">
         <is>
           <t>Whitepaper</t>
         </is>
       </c>
-      <c r="K8" s="1" t="inlineStr">
+      <c r="K8" s="16" t="inlineStr">
         <is>
           <t>Coding Agents</t>
         </is>
       </c>
-      <c r="L8" s="1" t="inlineStr">
+      <c r="L8" s="16" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="M8" s="1" t="inlineStr">
+      <c r="M8" s="16" t="inlineStr">
         <is>
           <t>Isolates the evaluation of repository exploration, context retrieval, and code localization capabilities.</t>
         </is>
       </c>
-      <c r="N8" s="11" t="n">
+      <c r="N8" s="18" t="n">
         <v>46216</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D1:D8">
-    <cfRule type="expression" priority="4" dxfId="3">
-      <formula>D1&gt;46151</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="J1:J8">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Emerging"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
       <formula>"Mature"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"Research"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1:D8">
+    <cfRule type="expression" priority="4" dxfId="3">
+      <formula>D1&gt;46151.0</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -3652,198 +3573,198 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="80" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" style="17" min="1" max="1"/>
+    <col width="34" customWidth="1" style="17" min="2" max="2"/>
+    <col width="46" customWidth="1" style="17" min="3" max="3"/>
+    <col width="18" customWidth="1" style="17" min="4" max="4"/>
+    <col width="10" customWidth="1" style="17" min="5" max="5"/>
+    <col width="80" customWidth="1" style="17" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>Position</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="19" t="inlineStr">
         <is>
           <t>Column Name</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="19" t="inlineStr">
         <is>
           <t>Applies To</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="19" t="inlineStr">
         <is>
           <t>Value Type</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="19" t="inlineStr">
         <is>
           <t>Separator</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="19" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="0" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="0" t="inlineStr">
         <is>
           <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="0" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="0" t="inlineStr">
         <is>
           <t>System-generated unique identifier, independent of Resource Name. Auto-assigned by xlsx_to_json.py the first time it sees a row with this cell blank (new rows, and every existing row during this migration) -- don't fill it in by hand. The one exception: when moving a row to a different sheet (e.g. Knowledgebase -&gt; Deprecated), copy its ID along with the rest of the row so the sync scripts recognize it as the same resource rather than a deletion plus a new entry.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25.5" customHeight="1">
-      <c r="A3" s="13" t="n">
+    <row r="3">
+      <c r="A3" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="20" t="inlineStr">
         <is>
           <t>Resource Name</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="20" t="inlineStr">
         <is>
           <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="20" t="inlineStr">
         <is>
           <t>free_text</t>
         </is>
       </c>
-      <c r="E3" s="13" t="n"/>
-      <c r="F3" s="13" t="inlineStr">
+      <c r="E3" s="20" t="inlineStr"/>
+      <c r="F3" s="20" t="inlineStr">
         <is>
           <t>Short, human-readable name. Also the natural key used to match a row across sync runs. Example: VS Code Copilot Agents Overview</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="25.5" customHeight="1">
-      <c r="A4" s="13" t="n">
+    <row r="4">
+      <c r="A4" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
         <is>
           <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="20" t="inlineStr">
         <is>
           <t>free_text</t>
         </is>
       </c>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="E4" s="20" t="inlineStr"/>
+      <c r="F4" s="20" t="inlineStr">
         <is>
           <t>Canonical link to the resource.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="25.5" customHeight="1">
-      <c r="A5" s="13" t="n">
+    <row r="5">
+      <c r="A5" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>Source Organization</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>free_text</t>
         </is>
       </c>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="13" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr"/>
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>Who maintains it? Examples: Microsoft, GitHub, OpenAI, Kaggle, Anthropic, Google, HuggingFace. This matters because some orgs update weekly, others yearly.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="25.5" customHeight="1">
-      <c r="A6" s="13" t="n">
+    <row r="6">
+      <c r="A6" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>Last Verified</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>Date a curator last checked the page. Set by a human during verification; cleared automatically when the row's content changes.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="25.5" customHeight="1">
-      <c r="A7" s="13" t="n">
+    <row r="7">
+      <c r="A7" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>Verified By</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
-      <c r="E7" s="13" t="n"/>
-      <c r="F7" s="13" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>Curator who last verified this row. Set by a human only, never by an agent; cleared automatically when the row's content changes.</t>
         </is>
@@ -3875,294 +3796,294 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="n">
+      <c r="A9" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>Last Updated</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>Knowledgebase; SOTA Coding Agents Benchmarks</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="E9" s="13" t="n"/>
-      <c r="F9" s="13" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr"/>
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>The page's own update timestamp. Helps track fast-moving agent ecosystems.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="38.25" customHeight="1">
-      <c r="A10" s="13" t="n">
+    <row r="10">
+      <c r="A10" s="20" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>Deprecation Date / Last Updated</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>Deprecated</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr"/>
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>Most recent known date for this row, whichever kind of event produced it: when the resource was confirmed deprecated, or, absent that, whenever the row was last touched. An exact deprecation date isn't always knowable at the time a row is added or edited.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="25.5" customHeight="1">
-      <c r="A11" s="13" t="n">
+    <row r="11">
+      <c r="A11" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="13" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr"/>
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>Version string of the resource or tool (e.g. 'v0.1 DRAFT', 'Pro'). Leave blank for article-type resources with no version - use Publication Date instead.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="25.5" customHeight="1">
-      <c r="A12" s="13" t="n">
+    <row r="12">
+      <c r="A12" s="20" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>controlled_single</t>
         </is>
       </c>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="13" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr"/>
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>What kind of resource this is. Helps teams filter by what they need.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="25.5" customHeight="1">
-      <c r="A13" s="13" t="n">
+    <row r="13">
+      <c r="A13" s="20" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>controlled_multi</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>;</t>
         </is>
       </c>
-      <c r="F13" s="13" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>Which agentic capabilities the resource covers. One of the most important columns.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="38.25" customHeight="1">
-      <c r="A14" s="13" t="n">
+    <row r="14">
+      <c r="A14" s="20" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>Knowledgebase; Deprecated</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>controlled_multi</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>;</t>
         </is>
       </c>
-      <c r="F14" s="13" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>Subject areas the resource addresses. Helps research IT teams quickly find relevant material. Primary vocabulary is EDAM; NIST AI RMF characteristics are available as an optional secondary axis.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="38.25" customHeight="1">
-      <c r="A15" s="13" t="n">
+    <row r="15">
+      <c r="A15" s="20" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>Relevance to Research Cyberinfrastructure</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>Knowledgebase; Deprecated</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>free_text</t>
         </is>
       </c>
-      <c r="E15" s="13" t="n"/>
-      <c r="F15" s="13" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr"/>
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>Free-text note on why this matters to research platforms. Example themes: workflow orchestration, data portal integration, metadata / provenance, multi-agent coordination, HPC / cloud hybrid workflows, reproducibility, federated analysis, user-facing agent interfaces.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="25.5" customHeight="1">
-      <c r="A16" s="13" t="n">
+    <row r="16">
+      <c r="A16" s="20" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>Maturity Level</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>controlled_single</t>
         </is>
       </c>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="13" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr"/>
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>Not about the website - about the technology described. Helps teams know whether something is stable enough to consider.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="38.25" customHeight="1">
-      <c r="A17" s="13" t="n">
+    <row r="17">
+      <c r="A17" s="20" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>Notes / Key Takeaways</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>free_text</t>
         </is>
       </c>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="13" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr"/>
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>Short free-text field: breaking changes, important patterns, new capabilities, relevance to agentic workflows, implications for research platforms. This is where institutional knowledge accumulates.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="n">
+      <c r="A18" s="20" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>Publication Date</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>Knowledgebase</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr"/>
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>Publication date for article-type resources that have no software version.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="25.5" customHeight="1">
-      <c r="A19" s="13" t="n">
+    <row r="19">
+      <c r="A19" s="20" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>Discovery Date</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="13" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr"/>
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>Date this resource first entered the VT Radar.</t>
         </is>
@@ -4180,1734 +4101,1735 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F77"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="80" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" style="17" min="1" max="1"/>
+    <col width="42" customWidth="1" style="17" min="2" max="2"/>
+    <col width="80" customWidth="1" style="17" min="3" max="3"/>
+    <col width="14" customWidth="1" style="17" min="4" max="4"/>
+    <col width="14" customWidth="1" style="17" min="5" max="5"/>
+    <col width="44" customWidth="1" style="17" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>Column Name</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="19" t="inlineStr">
         <is>
           <t>Term</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="19" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="19" t="inlineStr">
         <is>
           <t>Ontology</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="19" t="inlineStr">
         <is>
           <t>Ontology ID</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="19" t="inlineStr">
         <is>
           <t>Ontology URL</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="25.5" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="20" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="C2" s="20" t="inlineStr"/>
+      <c r="D2" s="20" t="inlineStr">
         <is>
           <t>Schema.org</t>
         </is>
       </c>
-      <c r="E2" s="13" t="inlineStr">
+      <c r="E2" s="20" t="inlineStr">
         <is>
           <t>schema:TechArticle</t>
         </is>
       </c>
-      <c r="F2" s="13" t="inlineStr">
+      <c r="F2" s="20" t="inlineStr">
         <is>
           <t>https://schema.org/TechArticle</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25.5" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="20" t="inlineStr">
         <is>
           <t>API Reference</t>
         </is>
       </c>
-      <c r="C3" s="13" t="n"/>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="C3" s="20" t="inlineStr"/>
+      <c r="D3" s="20" t="inlineStr">
         <is>
           <t>Schema.org</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" s="20" t="inlineStr">
         <is>
           <t>schema:APIReference</t>
         </is>
       </c>
-      <c r="F3" s="13" t="inlineStr">
+      <c r="F3" s="20" t="inlineStr">
         <is>
           <t>https://schema.org/APIReference</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="25.5" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>Specification</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr"/>
+      <c r="D4" s="20" t="inlineStr">
         <is>
           <t>Schema.org</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" s="20" t="inlineStr">
         <is>
           <t>schema:TechArticle</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="F4" s="20" t="inlineStr">
         <is>
           <t>https://schema.org/TechArticle</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="25.5" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>Whitepaper</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>Vendor or organization technical whitepaper.</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>Schema.org</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>schema:TechArticle</t>
         </is>
       </c>
-      <c r="F5" s="13" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>https://schema.org/TechArticle</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="25.5" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>Scientific Literature</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>Peer-reviewed publication or preprint. Distinct from a vendor Whitepaper.</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>Schema.org</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>schema:ScholarlyArticle</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>https://schema.org/ScholarlyArticle</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="25.5" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>Governance Guidance</t>
         </is>
       </c>
-      <c r="C7" s="13" t="n"/>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>Schema.org</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>schema:TechArticle</t>
         </is>
       </c>
-      <c r="F7" s="13" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>https://schema.org/TechArticle</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="25.5" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>Security Guidance &amp; Resources</t>
         </is>
       </c>
-      <c r="C8" s="13" t="n"/>
-      <c r="D8" s="13" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr"/>
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>Schema.org</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>schema:TechArticle</t>
         </is>
       </c>
-      <c r="F8" s="13" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>https://schema.org/TechArticle</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="25.5" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>Reference Architecture</t>
         </is>
       </c>
-      <c r="C9" s="13" t="n"/>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr"/>
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>Schema.org</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>schema:TechArticle</t>
         </is>
       </c>
-      <c r="F9" s="13" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>https://schema.org/TechArticle</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>Container Registry</t>
         </is>
       </c>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
+      <c r="C10" s="20" t="inlineStr"/>
+      <c r="D10" s="20" t="inlineStr"/>
+      <c r="E10" s="20" t="inlineStr"/>
+      <c r="F10" s="20" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>Enterprise Control Interface</t>
         </is>
       </c>
-      <c r="C11" s="13" t="n"/>
-      <c r="D11" s="13" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="13" t="n"/>
+      <c r="C11" s="20" t="inlineStr"/>
+      <c r="D11" s="20" t="inlineStr"/>
+      <c r="E11" s="20" t="inlineStr"/>
+      <c r="F11" s="20" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>Inference Framework</t>
         </is>
       </c>
-      <c r="C12" s="13" t="n"/>
-      <c r="D12" s="13" t="n"/>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="13" t="n"/>
+      <c r="C12" s="20" t="inlineStr"/>
+      <c r="D12" s="20" t="inlineStr"/>
+      <c r="E12" s="20" t="inlineStr"/>
+      <c r="F12" s="20" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>Local Application Sandbox</t>
         </is>
       </c>
-      <c r="C13" s="13" t="n"/>
-      <c r="D13" s="13" t="n"/>
-      <c r="E13" s="13" t="n"/>
-      <c r="F13" s="13" t="n"/>
-    </row>
-    <row r="14" ht="25.5" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr"/>
+      <c r="D13" s="20" t="inlineStr"/>
+      <c r="E13" s="20" t="inlineStr"/>
+      <c r="F13" s="20" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>Github Code Repository</t>
         </is>
       </c>
-      <c r="C14" s="13" t="n"/>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr"/>
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>Schema.org</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>schema:SoftwareSourceCode</t>
         </is>
       </c>
-      <c r="F14" s="13" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>https://schema.org/SoftwareSourceCode</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="25.5" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>Benchmark Collection</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>A curated collection of benchmarks or comparison studies.</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>Schema.org</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>schema:Dataset</t>
         </is>
       </c>
-      <c r="F15" s="13" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>https://schema.org/Dataset</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>Hooks</t>
         </is>
       </c>
-      <c r="C16" s="13" t="n"/>
-      <c r="D16" s="13" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="13" t="n"/>
+      <c r="C16" s="20" t="inlineStr"/>
+      <c r="D16" s="20" t="inlineStr"/>
+      <c r="E16" s="20" t="inlineStr"/>
+      <c r="F16" s="20" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>Skills</t>
         </is>
       </c>
-      <c r="C17" s="13" t="n"/>
-      <c r="D17" s="13" t="n"/>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="13" t="n"/>
+      <c r="C17" s="20" t="inlineStr"/>
+      <c r="D17" s="20" t="inlineStr"/>
+      <c r="E17" s="20" t="inlineStr"/>
+      <c r="F17" s="20" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>MCP</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>Model Context Protocol.</t>
         </is>
       </c>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="n"/>
+      <c r="D18" s="20" t="inlineStr"/>
+      <c r="E18" s="20" t="inlineStr"/>
+      <c r="F18" s="20" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>Agent frameworks</t>
         </is>
       </c>
-      <c r="C19" s="13" t="n"/>
-      <c r="D19" s="13" t="n"/>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="13" t="n"/>
+      <c r="C19" s="20" t="inlineStr"/>
+      <c r="D19" s="20" t="inlineStr"/>
+      <c r="E19" s="20" t="inlineStr"/>
+      <c r="F19" s="20" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>Agent Patterns</t>
         </is>
       </c>
-      <c r="C20" s="13" t="n"/>
-      <c r="D20" s="13" t="n"/>
-      <c r="E20" s="13" t="n"/>
-      <c r="F20" s="13" t="n"/>
+      <c r="C20" s="20" t="inlineStr"/>
+      <c r="D20" s="20" t="inlineStr"/>
+      <c r="E20" s="20" t="inlineStr"/>
+      <c r="F20" s="20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>Multi-Agent Patterns</t>
         </is>
       </c>
-      <c r="C21" s="13" t="n"/>
-      <c r="D21" s="13" t="n"/>
-      <c r="E21" s="13" t="n"/>
-      <c r="F21" s="13" t="n"/>
+      <c r="C21" s="20" t="inlineStr"/>
+      <c r="D21" s="20" t="inlineStr"/>
+      <c r="E21" s="20" t="inlineStr"/>
+      <c r="F21" s="20" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>Context window management</t>
         </is>
       </c>
-      <c r="C22" s="13" t="n"/>
-      <c r="D22" s="13" t="n"/>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="13" t="n"/>
+      <c r="C22" s="20" t="inlineStr"/>
+      <c r="D22" s="20" t="inlineStr"/>
+      <c r="E22" s="20" t="inlineStr"/>
+      <c r="F22" s="20" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>Deployment patterns</t>
         </is>
       </c>
-      <c r="C23" s="13" t="n"/>
-      <c r="D23" s="13" t="n"/>
-      <c r="E23" s="13" t="n"/>
-      <c r="F23" s="13" t="n"/>
+      <c r="C23" s="20" t="inlineStr"/>
+      <c r="D23" s="20" t="inlineStr"/>
+      <c r="E23" s="20" t="inlineStr"/>
+      <c r="F23" s="20" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>Safety / guardrails</t>
         </is>
       </c>
-      <c r="C24" s="13" t="n"/>
-      <c r="D24" s="13" t="n"/>
-      <c r="E24" s="13" t="n"/>
-      <c r="F24" s="13" t="n"/>
-    </row>
-    <row r="25" ht="102" customHeight="1">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr"/>
+      <c r="D24" s="20" t="inlineStr"/>
+      <c r="E24" s="20" t="inlineStr"/>
+      <c r="F24" s="20" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>Evaluation / testing</t>
         </is>
       </c>
-      <c r="C25" s="13" t="n"/>
-      <c r="D25" s="13" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr"/>
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>ACM-CCS</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>Software and its engineering~Software verification and validation~Software testing and debugging</t>
         </is>
       </c>
-      <c r="F25" s="13" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>https://dl.acm.org/ccs</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>Risk Controls</t>
         </is>
       </c>
-      <c r="C26" s="13" t="n"/>
-      <c r="D26" s="13" t="n"/>
-      <c r="E26" s="13" t="n"/>
-      <c r="F26" s="13" t="n"/>
+      <c r="C26" s="20" t="inlineStr"/>
+      <c r="D26" s="20" t="inlineStr"/>
+      <c r="E26" s="20" t="inlineStr"/>
+      <c r="F26" s="20" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>Safe Tool Use</t>
         </is>
       </c>
-      <c r="C27" s="13" t="n"/>
-      <c r="D27" s="13" t="n"/>
-      <c r="E27" s="13" t="n"/>
-      <c r="F27" s="13" t="n"/>
+      <c r="C27" s="20" t="inlineStr"/>
+      <c r="D27" s="20" t="inlineStr"/>
+      <c r="E27" s="20" t="inlineStr"/>
+      <c r="F27" s="20" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B28" s="13" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>Tools</t>
         </is>
       </c>
-      <c r="C28" s="13" t="n"/>
-      <c r="D28" s="13" t="n"/>
-      <c r="E28" s="13" t="n"/>
-      <c r="F28" s="13" t="n"/>
+      <c r="C28" s="20" t="inlineStr"/>
+      <c r="D28" s="20" t="inlineStr"/>
+      <c r="E28" s="20" t="inlineStr"/>
+      <c r="F28" s="20" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="inlineStr">
+      <c r="A29" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B29" s="13" t="inlineStr">
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>Tool-Ready Endpoints</t>
         </is>
       </c>
-      <c r="C29" s="13" t="n"/>
-      <c r="D29" s="13" t="n"/>
-      <c r="E29" s="13" t="n"/>
-      <c r="F29" s="13" t="n"/>
+      <c r="C29" s="20" t="inlineStr"/>
+      <c r="D29" s="20" t="inlineStr"/>
+      <c r="E29" s="20" t="inlineStr"/>
+      <c r="F29" s="20" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="13" t="inlineStr">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B30" s="13" t="inlineStr">
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>Coding Agents</t>
         </is>
       </c>
-      <c r="C30" s="13" t="n"/>
-      <c r="D30" s="13" t="n"/>
-      <c r="E30" s="13" t="n"/>
-      <c r="F30" s="13" t="n"/>
+      <c r="C30" s="20" t="inlineStr"/>
+      <c r="D30" s="20" t="inlineStr"/>
+      <c r="E30" s="20" t="inlineStr"/>
+      <c r="F30" s="20" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="A31" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B31" s="13" t="inlineStr">
+      <c r="B31" s="20" t="inlineStr">
         <is>
           <t>Notebook Agents</t>
         </is>
       </c>
-      <c r="C31" s="13" t="n"/>
-      <c r="D31" s="13" t="n"/>
-      <c r="E31" s="13" t="n"/>
-      <c r="F31" s="13" t="n"/>
+      <c r="C31" s="20" t="inlineStr"/>
+      <c r="D31" s="20" t="inlineStr"/>
+      <c r="E31" s="20" t="inlineStr"/>
+      <c r="F31" s="20" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="13" t="inlineStr">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B32" s="13" t="inlineStr">
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>Workflow Agents</t>
         </is>
       </c>
-      <c r="C32" s="13" t="n"/>
-      <c r="D32" s="13" t="n"/>
-      <c r="E32" s="13" t="n"/>
-      <c r="F32" s="13" t="n"/>
+      <c r="C32" s="20" t="inlineStr"/>
+      <c r="D32" s="20" t="inlineStr"/>
+      <c r="E32" s="20" t="inlineStr"/>
+      <c r="F32" s="20" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="13" t="inlineStr">
+      <c r="A33" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B33" s="13" t="inlineStr">
+      <c r="B33" s="20" t="inlineStr">
         <is>
           <t>Workflow Automation</t>
         </is>
       </c>
-      <c r="C33" s="13" t="n"/>
-      <c r="D33" s="13" t="n"/>
-      <c r="E33" s="13" t="n"/>
-      <c r="F33" s="13" t="n"/>
+      <c r="C33" s="20" t="inlineStr"/>
+      <c r="D33" s="20" t="inlineStr"/>
+      <c r="E33" s="20" t="inlineStr"/>
+      <c r="F33" s="20" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="13" t="inlineStr">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B34" s="13" t="inlineStr">
+      <c r="B34" s="20" t="inlineStr">
         <is>
           <t>Orchestration</t>
         </is>
       </c>
-      <c r="C34" s="13" t="n"/>
-      <c r="D34" s="13" t="n"/>
-      <c r="E34" s="13" t="n"/>
-      <c r="F34" s="13" t="n"/>
+      <c r="C34" s="20" t="inlineStr"/>
+      <c r="D34" s="20" t="inlineStr"/>
+      <c r="E34" s="20" t="inlineStr"/>
+      <c r="F34" s="20" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="13" t="inlineStr">
+      <c r="A35" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B35" s="13" t="inlineStr">
+      <c r="B35" s="20" t="inlineStr">
         <is>
           <t>Triggers</t>
         </is>
       </c>
-      <c r="C35" s="13" t="n"/>
-      <c r="D35" s="13" t="n"/>
-      <c r="E35" s="13" t="n"/>
-      <c r="F35" s="13" t="n"/>
-    </row>
-    <row r="36" ht="38.25" customHeight="1">
-      <c r="A36" s="13" t="inlineStr">
+      <c r="C35" s="20" t="inlineStr"/>
+      <c r="D35" s="20" t="inlineStr"/>
+      <c r="E35" s="20" t="inlineStr"/>
+      <c r="F35" s="20" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B36" s="13" t="inlineStr">
+      <c r="B36" s="20" t="inlineStr">
         <is>
           <t>Retrieval</t>
         </is>
       </c>
-      <c r="C36" s="13" t="n"/>
-      <c r="D36" s="13" t="inlineStr">
+      <c r="C36" s="20" t="inlineStr"/>
+      <c r="D36" s="20" t="inlineStr">
         <is>
           <t>ACM-CCS</t>
         </is>
       </c>
-      <c r="E36" s="13" t="inlineStr">
+      <c r="E36" s="20" t="inlineStr">
         <is>
           <t>Information systems~Information retrieval</t>
         </is>
       </c>
-      <c r="F36" s="13" t="inlineStr">
+      <c r="F36" s="20" t="inlineStr">
         <is>
           <t>https://dl.acm.org/ccs</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="38.25" customHeight="1">
-      <c r="A37" s="13" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B37" s="13" t="inlineStr">
+      <c r="B37" s="20" t="inlineStr">
         <is>
           <t>Retrieval Agents</t>
         </is>
       </c>
-      <c r="C37" s="13" t="n"/>
-      <c r="D37" s="13" t="inlineStr">
+      <c r="C37" s="20" t="inlineStr"/>
+      <c r="D37" s="20" t="inlineStr">
         <is>
           <t>ACM-CCS</t>
         </is>
       </c>
-      <c r="E37" s="13" t="inlineStr">
+      <c r="E37" s="20" t="inlineStr">
         <is>
           <t>Information systems~Information retrieval</t>
         </is>
       </c>
-      <c r="F37" s="13" t="inlineStr">
+      <c r="F37" s="20" t="inlineStr">
         <is>
           <t>https://dl.acm.org/ccs</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="13" t="inlineStr">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B38" s="13" t="inlineStr">
+      <c r="B38" s="20" t="inlineStr">
         <is>
           <t>Sandbox</t>
         </is>
       </c>
-      <c r="C38" s="13" t="n"/>
-      <c r="D38" s="13" t="n"/>
-      <c r="E38" s="13" t="n"/>
-      <c r="F38" s="13" t="n"/>
+      <c r="C38" s="20" t="inlineStr"/>
+      <c r="D38" s="20" t="inlineStr"/>
+      <c r="E38" s="20" t="inlineStr"/>
+      <c r="F38" s="20" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="13" t="inlineStr">
+      <c r="A39" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B39" s="13" t="inlineStr">
+      <c r="B39" s="20" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="C39" s="13" t="n"/>
-      <c r="D39" s="13" t="n"/>
-      <c r="E39" s="13" t="n"/>
-      <c r="F39" s="13" t="n"/>
-    </row>
-    <row r="40" ht="25.5" customHeight="1">
-      <c r="A40" s="13" t="inlineStr">
+      <c r="C39" s="20" t="inlineStr"/>
+      <c r="D39" s="20" t="inlineStr"/>
+      <c r="E39" s="20" t="inlineStr"/>
+      <c r="F39" s="20" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B40" s="13" t="inlineStr">
+      <c r="B40" s="20" t="inlineStr">
         <is>
           <t>Cybersecurity</t>
         </is>
       </c>
-      <c r="C40" s="13" t="n"/>
-      <c r="D40" s="13" t="inlineStr">
+      <c r="C40" s="20" t="inlineStr"/>
+      <c r="D40" s="20" t="inlineStr">
         <is>
           <t>ACM-CCS</t>
         </is>
       </c>
-      <c r="E40" s="13" t="inlineStr">
+      <c r="E40" s="20" t="inlineStr">
         <is>
           <t>Security and privacy</t>
         </is>
       </c>
-      <c r="F40" s="13" t="inlineStr">
+      <c r="F40" s="20" t="inlineStr">
         <is>
           <t>https://dl.acm.org/ccs</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="13" t="inlineStr">
+      <c r="A41" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B41" s="13" t="inlineStr">
+      <c r="B41" s="20" t="inlineStr">
         <is>
           <t>FAIR data</t>
         </is>
       </c>
-      <c r="C41" s="13" t="inlineStr">
+      <c r="C41" s="20" t="inlineStr">
         <is>
           <t>Findable, Accessible, Interoperable, Reusable data principles.</t>
         </is>
       </c>
-      <c r="D41" s="13" t="inlineStr">
+      <c r="D41" s="20" t="inlineStr">
         <is>
           <t>EDAM</t>
         </is>
       </c>
-      <c r="E41" s="13" t="inlineStr">
+      <c r="E41" s="20" t="inlineStr">
         <is>
           <t>topic_4012</t>
         </is>
       </c>
-      <c r="F41" s="13" t="inlineStr">
+      <c r="F41" s="20" t="inlineStr">
         <is>
           <t>http://edamontology.org/topic_4012</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="13" t="inlineStr">
+      <c r="A42" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B42" s="13" t="inlineStr">
+      <c r="B42" s="20" t="inlineStr">
         <is>
           <t>API Integration</t>
         </is>
       </c>
-      <c r="C42" s="13" t="n"/>
-      <c r="D42" s="13" t="n"/>
-      <c r="E42" s="13" t="n"/>
-      <c r="F42" s="13" t="n"/>
+      <c r="C42" s="20" t="inlineStr"/>
+      <c r="D42" s="20" t="inlineStr"/>
+      <c r="E42" s="20" t="inlineStr"/>
+      <c r="F42" s="20" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="13" t="inlineStr">
+      <c r="A43" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B43" s="13" t="inlineStr">
+      <c r="B43" s="20" t="inlineStr">
         <is>
           <t>Model Integration</t>
         </is>
       </c>
-      <c r="C43" s="13" t="n"/>
-      <c r="D43" s="13" t="n"/>
-      <c r="E43" s="13" t="n"/>
-      <c r="F43" s="13" t="n"/>
+      <c r="C43" s="20" t="inlineStr"/>
+      <c r="D43" s="20" t="inlineStr"/>
+      <c r="E43" s="20" t="inlineStr"/>
+      <c r="F43" s="20" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="13" t="inlineStr">
+      <c r="A44" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B44" s="13" t="inlineStr">
+      <c r="B44" s="20" t="inlineStr">
         <is>
           <t>Server Integration</t>
         </is>
       </c>
-      <c r="C44" s="13" t="n"/>
-      <c r="D44" s="13" t="n"/>
-      <c r="E44" s="13" t="n"/>
-      <c r="F44" s="13" t="n"/>
+      <c r="C44" s="20" t="inlineStr"/>
+      <c r="D44" s="20" t="inlineStr"/>
+      <c r="E44" s="20" t="inlineStr"/>
+      <c r="F44" s="20" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="13" t="inlineStr">
+      <c r="A45" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B45" s="13" t="inlineStr">
+      <c r="B45" s="20" t="inlineStr">
         <is>
           <t>Server Patterns</t>
         </is>
       </c>
-      <c r="C45" s="13" t="n"/>
-      <c r="D45" s="13" t="n"/>
-      <c r="E45" s="13" t="n"/>
-      <c r="F45" s="13" t="n"/>
-    </row>
-    <row r="46" ht="51" customHeight="1">
-      <c r="A46" s="13" t="inlineStr">
+      <c r="C45" s="20" t="inlineStr"/>
+      <c r="D45" s="20" t="inlineStr"/>
+      <c r="E45" s="20" t="inlineStr"/>
+      <c r="F45" s="20" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B46" s="13" t="inlineStr">
+      <c r="B46" s="20" t="inlineStr">
         <is>
           <t>Architecture</t>
         </is>
       </c>
-      <c r="C46" s="13" t="n"/>
-      <c r="D46" s="13" t="inlineStr">
+      <c r="C46" s="20" t="inlineStr"/>
+      <c r="D46" s="20" t="inlineStr">
         <is>
           <t>ACM-CCS</t>
         </is>
       </c>
-      <c r="E46" s="13" t="inlineStr">
+      <c r="E46" s="20" t="inlineStr">
         <is>
           <t>Computer systems organization~Architectures</t>
         </is>
       </c>
-      <c r="F46" s="13" t="inlineStr">
+      <c r="F46" s="20" t="inlineStr">
         <is>
           <t>https://dl.acm.org/ccs</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="25.5" customHeight="1">
-      <c r="A47" s="13" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B47" s="13" t="inlineStr">
+      <c r="B47" s="20" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="C47" s="13" t="n"/>
-      <c r="D47" s="13" t="inlineStr">
+      <c r="C47" s="20" t="inlineStr"/>
+      <c r="D47" s="20" t="inlineStr">
         <is>
           <t>ACM-CCS</t>
         </is>
       </c>
-      <c r="E47" s="13" t="inlineStr">
+      <c r="E47" s="20" t="inlineStr">
         <is>
           <t>Security and privacy</t>
         </is>
       </c>
-      <c r="F47" s="13" t="inlineStr">
+      <c r="F47" s="20" t="inlineStr">
         <is>
           <t>https://dl.acm.org/ccs</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="38.25" customHeight="1">
-      <c r="A48" s="13" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B48" s="13" t="inlineStr">
+      <c r="B48" s="20" t="inlineStr">
         <is>
           <t>Data governance</t>
         </is>
       </c>
-      <c r="C48" s="13" t="inlineStr">
+      <c r="C48" s="20" t="inlineStr">
         <is>
           <t>Focuses specifically on the technical protocols, access controls, data-line security, and de-identification standards used to protect the integrity, quality, and privacy of information throughout its lifecycle</t>
         </is>
       </c>
-      <c r="D48" s="13" t="inlineStr">
+      <c r="D48" s="20" t="inlineStr">
         <is>
           <t>EDAM</t>
         </is>
       </c>
-      <c r="E48" s="13" t="inlineStr">
+      <c r="E48" s="20" t="inlineStr">
         <is>
           <t>topic_3571</t>
         </is>
       </c>
-      <c r="F48" s="13" t="inlineStr">
+      <c r="F48" s="20" t="inlineStr">
         <is>
           <t>http://edamontology.org/topic_3571</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="38.25" customHeight="1">
-      <c r="A49" s="13" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B49" s="13" t="inlineStr">
+      <c r="B49" s="20" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="C49" s="13" t="inlineStr">
+      <c r="C49" s="20" t="inlineStr">
         <is>
           <t>The overarching organizational policies, compliance frameworks, and capital allocation strategies that dictate how an enterprise manages its broader IT infrastructure, risk tolerances, and vendor choices</t>
         </is>
       </c>
-      <c r="D49" s="13" t="n"/>
-      <c r="E49" s="13" t="n"/>
-      <c r="F49" s="13" t="n"/>
-    </row>
-    <row r="50" ht="76.5" customHeight="1">
-      <c r="A50" s="13" t="inlineStr">
+      <c r="D49" s="20" t="inlineStr"/>
+      <c r="E49" s="20" t="inlineStr"/>
+      <c r="F49" s="20" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B50" s="13" t="inlineStr">
+      <c r="B50" s="20" t="inlineStr">
         <is>
           <t>Implementation</t>
         </is>
       </c>
-      <c r="C50" s="13" t="n"/>
-      <c r="D50" s="13" t="inlineStr">
+      <c r="C50" s="20" t="inlineStr"/>
+      <c r="D50" s="20" t="inlineStr">
         <is>
           <t>ACM-CCS</t>
         </is>
       </c>
-      <c r="E50" s="13" t="inlineStr">
+      <c r="E50" s="20" t="inlineStr">
         <is>
           <t>Software and its engineering~Software creation and management</t>
         </is>
       </c>
-      <c r="F50" s="13" t="inlineStr">
+      <c r="F50" s="20" t="inlineStr">
         <is>
           <t>https://dl.acm.org/ccs</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="25.5" customHeight="1">
-      <c r="A51" s="13" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B51" s="13" t="inlineStr">
+      <c r="B51" s="20" t="inlineStr">
         <is>
           <t>Deployment</t>
         </is>
       </c>
-      <c r="C51" s="13" t="inlineStr">
+      <c r="C51" s="20" t="inlineStr">
         <is>
           <t>The tactical, hands-on execution of installing, configuring, provisioning, and launching software or hardware systems within a specific operational environment</t>
         </is>
       </c>
-      <c r="D51" s="13" t="inlineStr">
+      <c r="D51" s="20" t="inlineStr">
         <is>
           <t>NIST-AI-RMF</t>
         </is>
       </c>
-      <c r="E51" s="13" t="inlineStr">
+      <c r="E51" s="20" t="inlineStr">
         <is>
           <t>AI lifecycle stage: Deploy</t>
         </is>
       </c>
-      <c r="F51" s="13" t="inlineStr">
+      <c r="F51" s="20" t="inlineStr">
         <is>
           <t>https://nvlpubs.nist.gov/nistpubs/ai/NIST.AI.100-1.pdf</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="13" t="inlineStr">
+      <c r="A52" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B52" s="13" t="inlineStr">
+      <c r="B52" s="20" t="inlineStr">
         <is>
           <t>Workflows</t>
         </is>
       </c>
-      <c r="C52" s="13" t="n"/>
-      <c r="D52" s="13" t="inlineStr">
+      <c r="C52" s="20" t="inlineStr"/>
+      <c r="D52" s="20" t="inlineStr">
         <is>
           <t>EDAM</t>
         </is>
       </c>
-      <c r="E52" s="13" t="inlineStr">
+      <c r="E52" s="20" t="inlineStr">
         <is>
           <t>topic_0769</t>
         </is>
       </c>
-      <c r="F52" s="13" t="inlineStr">
+      <c r="F52" s="20" t="inlineStr">
         <is>
           <t>http://edamontology.org/topic_0769</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="13" t="inlineStr">
+      <c r="A53" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B53" s="13" t="inlineStr">
+      <c r="B53" s="20" t="inlineStr">
         <is>
           <t>Model selection</t>
         </is>
       </c>
-      <c r="C53" s="13" t="n"/>
-      <c r="D53" s="13" t="n"/>
-      <c r="E53" s="13" t="n"/>
-      <c r="F53" s="13" t="n"/>
-    </row>
-    <row r="54" ht="102" customHeight="1">
-      <c r="A54" s="13" t="inlineStr">
+      <c r="C53" s="20" t="inlineStr"/>
+      <c r="D53" s="20" t="inlineStr"/>
+      <c r="E53" s="20" t="inlineStr"/>
+      <c r="F53" s="20" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B54" s="13" t="inlineStr">
+      <c r="B54" s="20" t="inlineStr">
         <is>
           <t>Evaluation</t>
         </is>
       </c>
-      <c r="C54" s="13" t="n"/>
-      <c r="D54" s="13" t="inlineStr">
+      <c r="C54" s="20" t="inlineStr"/>
+      <c r="D54" s="20" t="inlineStr">
         <is>
           <t>ACM-CCS</t>
         </is>
       </c>
-      <c r="E54" s="13" t="inlineStr">
+      <c r="E54" s="20" t="inlineStr">
         <is>
           <t>Software and its engineering~Software verification and validation~Software testing and debugging</t>
         </is>
       </c>
-      <c r="F54" s="13" t="inlineStr">
+      <c r="F54" s="20" t="inlineStr">
         <is>
           <t>https://dl.acm.org/ccs</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="25.5" customHeight="1">
-      <c r="A55" s="13" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B55" s="13" t="inlineStr">
+      <c r="B55" s="20" t="inlineStr">
         <is>
           <t>Compute Infrastructure</t>
         </is>
       </c>
-      <c r="C55" s="13" t="inlineStr">
+      <c r="C55" s="20" t="inlineStr">
         <is>
           <t>Physical node topologies, hardware constraints, VRAM bounds, and localized compute execution profiles.</t>
         </is>
       </c>
-      <c r="D55" s="13" t="n"/>
-      <c r="E55" s="13" t="n"/>
-      <c r="F55" s="13" t="n"/>
-    </row>
-    <row r="56" ht="25.5" customHeight="1">
-      <c r="A56" s="13" t="inlineStr">
+      <c r="D55" s="20" t="inlineStr"/>
+      <c r="E55" s="20" t="inlineStr"/>
+      <c r="F55" s="20" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B56" s="13" t="inlineStr">
+      <c r="B56" s="20" t="inlineStr">
         <is>
           <t>Network Isolation</t>
         </is>
       </c>
-      <c r="C56" s="13" t="inlineStr">
+      <c r="C56" s="20" t="inlineStr">
         <is>
           <t>Non-egress boundaries, air-gapped artifact staging, localized cloud VPC containers, and firewalled local registries.</t>
         </is>
       </c>
-      <c r="D56" s="13" t="n"/>
-      <c r="E56" s="13" t="n"/>
-      <c r="F56" s="13" t="n"/>
-    </row>
-    <row r="57" ht="25.5" customHeight="1">
-      <c r="A57" s="13" t="inlineStr">
+      <c r="D56" s="20" t="inlineStr"/>
+      <c r="E56" s="20" t="inlineStr"/>
+      <c r="F56" s="20" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B57" s="13" t="inlineStr">
+      <c r="B57" s="20" t="inlineStr">
         <is>
           <t>Infrastructure Security</t>
         </is>
       </c>
-      <c r="C57" s="13" t="inlineStr">
+      <c r="C57" s="20" t="inlineStr">
         <is>
           <t>For on-prem LLM deployments, it captures the security of the compute stack as well as the data pipelines</t>
         </is>
       </c>
-      <c r="D57" s="13" t="n"/>
-      <c r="E57" s="13" t="n"/>
-      <c r="F57" s="13" t="n"/>
-    </row>
-    <row r="58" ht="25.5" customHeight="1">
-      <c r="A58" s="13" t="inlineStr">
+      <c r="D57" s="20" t="inlineStr"/>
+      <c r="E57" s="20" t="inlineStr"/>
+      <c r="F57" s="20" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B58" s="13" t="inlineStr">
+      <c r="B58" s="20" t="inlineStr">
         <is>
           <t>Self‑hosted AI</t>
         </is>
       </c>
-      <c r="C58" s="13" t="inlineStr">
+      <c r="C58" s="20" t="inlineStr">
         <is>
           <t>Self‑hosted, open‑weights models in contrast to API‑based models like OpenAI, Anthropic, or Gemini</t>
         </is>
       </c>
-      <c r="D58" s="13" t="n"/>
-      <c r="E58" s="13" t="n"/>
-      <c r="F58" s="13" t="n"/>
+      <c r="D58" s="20" t="inlineStr"/>
+      <c r="E58" s="20" t="inlineStr"/>
+      <c r="F58" s="20" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="13" t="inlineStr">
+      <c r="A59" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B59" s="13" t="inlineStr">
+      <c r="B59" s="20" t="inlineStr">
         <is>
           <t>Data Protection</t>
         </is>
       </c>
-      <c r="C59" s="13" t="inlineStr">
+      <c r="C59" s="20" t="inlineStr">
         <is>
           <t>Safeguarding sensitive data specifically. Distinct from the broader Security term.</t>
         </is>
       </c>
-      <c r="D59" s="13" t="inlineStr">
+      <c r="D59" s="20" t="inlineStr">
         <is>
           <t>EDAM</t>
         </is>
       </c>
-      <c r="E59" s="13" t="inlineStr">
+      <c r="E59" s="20" t="inlineStr">
         <is>
           <t>topic_4044</t>
         </is>
       </c>
-      <c r="F59" s="13" t="inlineStr">
+      <c r="F59" s="20" t="inlineStr">
         <is>
           <t>http://edamontology.org/topic_4044</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="13" t="inlineStr">
+      <c r="A60" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B60" s="13" t="inlineStr">
+      <c r="B60" s="20" t="inlineStr">
         <is>
           <t>FAIR data</t>
         </is>
       </c>
-      <c r="C60" s="13" t="inlineStr">
+      <c r="C60" s="20" t="inlineStr">
         <is>
           <t>Findable, Accessible, Interoperable, Reusable data principles.</t>
         </is>
       </c>
-      <c r="D60" s="13" t="inlineStr">
+      <c r="D60" s="20" t="inlineStr">
         <is>
           <t>EDAM</t>
         </is>
       </c>
-      <c r="E60" s="13" t="inlineStr">
+      <c r="E60" s="20" t="inlineStr">
         <is>
           <t>topic_4012</t>
         </is>
       </c>
-      <c r="F60" s="13" t="inlineStr">
+      <c r="F60" s="20" t="inlineStr">
         <is>
           <t>http://edamontology.org/topic_4012</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="13" t="inlineStr">
+      <c r="A61" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B61" s="13" t="inlineStr">
+      <c r="B61" s="20" t="inlineStr">
         <is>
           <t>Data quality management</t>
         </is>
       </c>
-      <c r="C61" s="13" t="n"/>
-      <c r="D61" s="13" t="inlineStr">
+      <c r="C61" s="20" t="inlineStr"/>
+      <c r="D61" s="20" t="inlineStr">
         <is>
           <t>EDAM</t>
         </is>
       </c>
-      <c r="E61" s="13" t="inlineStr">
+      <c r="E61" s="20" t="inlineStr">
         <is>
           <t>topic_3572</t>
         </is>
       </c>
-      <c r="F61" s="13" t="inlineStr">
+      <c r="F61" s="20" t="inlineStr">
         <is>
           <t>http://edamontology.org/topic_3572</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="13" t="inlineStr">
+      <c r="A62" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B62" s="13" t="inlineStr">
+      <c r="B62" s="20" t="inlineStr">
         <is>
           <t>Data curation and archival</t>
         </is>
       </c>
-      <c r="C62" s="13" t="n"/>
-      <c r="D62" s="13" t="inlineStr">
+      <c r="C62" s="20" t="inlineStr"/>
+      <c r="D62" s="20" t="inlineStr">
         <is>
           <t>EDAM</t>
         </is>
       </c>
-      <c r="E62" s="13" t="inlineStr">
+      <c r="E62" s="20" t="inlineStr">
         <is>
           <t>topic_0219</t>
         </is>
       </c>
-      <c r="F62" s="13" t="inlineStr">
+      <c r="F62" s="20" t="inlineStr">
         <is>
           <t>http://edamontology.org/topic_0219</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="13" t="inlineStr">
+      <c r="A63" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B63" s="13" t="inlineStr">
+      <c r="B63" s="20" t="inlineStr">
         <is>
           <t>Data integration and warehousing</t>
         </is>
       </c>
-      <c r="C63" s="13" t="n"/>
-      <c r="D63" s="13" t="inlineStr">
+      <c r="C63" s="20" t="inlineStr"/>
+      <c r="D63" s="20" t="inlineStr">
         <is>
           <t>EDAM</t>
         </is>
       </c>
-      <c r="E63" s="13" t="inlineStr">
+      <c r="E63" s="20" t="inlineStr">
         <is>
           <t>topic_3366</t>
         </is>
       </c>
-      <c r="F63" s="13" t="inlineStr">
+      <c r="F63" s="20" t="inlineStr">
         <is>
           <t>http://edamontology.org/topic_3366</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="13" t="inlineStr">
+      <c r="A64" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B64" s="13" t="inlineStr">
+      <c r="B64" s="20" t="inlineStr">
         <is>
           <t>Data architecture, analysis and design</t>
         </is>
       </c>
-      <c r="C64" s="13" t="n"/>
-      <c r="D64" s="13" t="inlineStr">
+      <c r="C64" s="20" t="inlineStr"/>
+      <c r="D64" s="20" t="inlineStr">
         <is>
           <t>EDAM</t>
         </is>
       </c>
-      <c r="E64" s="13" t="inlineStr">
+      <c r="E64" s="20" t="inlineStr">
         <is>
           <t>topic_3365</t>
         </is>
       </c>
-      <c r="F64" s="13" t="inlineStr">
+      <c r="F64" s="20" t="inlineStr">
         <is>
           <t>http://edamontology.org/topic_3365</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="13" t="inlineStr">
+      <c r="A65" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B65" s="13" t="inlineStr">
+      <c r="B65" s="20" t="inlineStr">
         <is>
           <t>Data identity and mapping</t>
         </is>
       </c>
-      <c r="C65" s="13" t="n"/>
-      <c r="D65" s="13" t="inlineStr">
+      <c r="C65" s="20" t="inlineStr"/>
+      <c r="D65" s="20" t="inlineStr">
         <is>
           <t>EDAM</t>
         </is>
       </c>
-      <c r="E65" s="13" t="inlineStr">
+      <c r="E65" s="20" t="inlineStr">
         <is>
           <t>topic_3345</t>
         </is>
       </c>
-      <c r="F65" s="13" t="inlineStr">
+      <c r="F65" s="20" t="inlineStr">
         <is>
           <t>http://edamontology.org/topic_3345</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="13" t="inlineStr">
+      <c r="A66" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B66" s="13" t="inlineStr">
+      <c r="B66" s="20" t="inlineStr">
         <is>
           <t>Data rescue</t>
         </is>
       </c>
-      <c r="C66" s="13" t="n"/>
-      <c r="D66" s="13" t="inlineStr">
+      <c r="C66" s="20" t="inlineStr"/>
+      <c r="D66" s="20" t="inlineStr">
         <is>
           <t>EDAM</t>
         </is>
       </c>
-      <c r="E66" s="13" t="inlineStr">
+      <c r="E66" s="20" t="inlineStr">
         <is>
           <t>topic_4011</t>
         </is>
       </c>
-      <c r="F66" s="13" t="inlineStr">
+      <c r="F66" s="20" t="inlineStr">
         <is>
           <t>http://edamontology.org/topic_4011</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="13" t="inlineStr">
+      <c r="A67" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B67" s="13" t="inlineStr">
+      <c r="B67" s="20" t="inlineStr">
         <is>
           <t>Valid and Reliable</t>
         </is>
       </c>
-      <c r="C67" s="13" t="inlineStr">
+      <c r="C67" s="20" t="inlineStr">
         <is>
           <t>NIST AI RMF trustworthy-AI characteristic.</t>
         </is>
       </c>
-      <c r="D67" s="13" t="inlineStr">
+      <c r="D67" s="20" t="inlineStr">
         <is>
           <t>NIST-AI-RMF</t>
         </is>
       </c>
-      <c r="E67" s="13" t="n"/>
-      <c r="F67" s="13" t="n"/>
+      <c r="E67" s="20" t="inlineStr"/>
+      <c r="F67" s="20" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="13" t="inlineStr">
+      <c r="A68" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B68" s="13" t="inlineStr">
+      <c r="B68" s="20" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
       </c>
-      <c r="C68" s="13" t="inlineStr">
+      <c r="C68" s="20" t="inlineStr">
         <is>
           <t>NIST AI RMF trustworthy-AI characteristic.</t>
         </is>
       </c>
-      <c r="D68" s="13" t="inlineStr">
+      <c r="D68" s="20" t="inlineStr">
         <is>
           <t>NIST-AI-RMF</t>
         </is>
       </c>
-      <c r="E68" s="13" t="n"/>
-      <c r="F68" s="13" t="n"/>
+      <c r="E68" s="20" t="inlineStr"/>
+      <c r="F68" s="20" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="13" t="inlineStr">
+      <c r="A69" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B69" s="13" t="inlineStr">
+      <c r="B69" s="20" t="inlineStr">
         <is>
           <t>Secure and Resilient</t>
         </is>
       </c>
-      <c r="C69" s="13" t="inlineStr">
+      <c r="C69" s="20" t="inlineStr">
         <is>
           <t>NIST AI RMF trustworthy-AI characteristic.</t>
         </is>
       </c>
-      <c r="D69" s="13" t="inlineStr">
+      <c r="D69" s="20" t="inlineStr">
         <is>
           <t>NIST-AI-RMF</t>
         </is>
       </c>
-      <c r="E69" s="13" t="n"/>
-      <c r="F69" s="13" t="n"/>
+      <c r="E69" s="20" t="inlineStr"/>
+      <c r="F69" s="20" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="13" t="inlineStr">
+      <c r="A70" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B70" s="13" t="inlineStr">
+      <c r="B70" s="20" t="inlineStr">
         <is>
           <t>Accountable and Transparent</t>
         </is>
       </c>
-      <c r="C70" s="13" t="inlineStr">
+      <c r="C70" s="20" t="inlineStr">
         <is>
           <t>NIST AI RMF trustworthy-AI characteristic.</t>
         </is>
       </c>
-      <c r="D70" s="13" t="inlineStr">
+      <c r="D70" s="20" t="inlineStr">
         <is>
           <t>NIST-AI-RMF</t>
         </is>
       </c>
-      <c r="E70" s="13" t="n"/>
-      <c r="F70" s="13" t="n"/>
+      <c r="E70" s="20" t="inlineStr"/>
+      <c r="F70" s="20" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="13" t="inlineStr">
+      <c r="A71" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B71" s="13" t="inlineStr">
+      <c r="B71" s="20" t="inlineStr">
         <is>
           <t>Explainable and Interpretable</t>
         </is>
       </c>
-      <c r="C71" s="13" t="inlineStr">
+      <c r="C71" s="20" t="inlineStr">
         <is>
           <t>NIST AI RMF trustworthy-AI characteristic.</t>
         </is>
       </c>
-      <c r="D71" s="13" t="inlineStr">
+      <c r="D71" s="20" t="inlineStr">
         <is>
           <t>NIST-AI-RMF</t>
         </is>
       </c>
-      <c r="E71" s="13" t="n"/>
-      <c r="F71" s="13" t="n"/>
+      <c r="E71" s="20" t="inlineStr"/>
+      <c r="F71" s="20" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="13" t="inlineStr">
+      <c r="A72" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B72" s="13" t="inlineStr">
+      <c r="B72" s="20" t="inlineStr">
         <is>
           <t>Privacy-Enhanced</t>
         </is>
       </c>
-      <c r="C72" s="13" t="inlineStr">
+      <c r="C72" s="20" t="inlineStr">
         <is>
           <t>NIST AI RMF trustworthy-AI characteristic.</t>
         </is>
       </c>
-      <c r="D72" s="13" t="inlineStr">
+      <c r="D72" s="20" t="inlineStr">
         <is>
           <t>NIST-AI-RMF</t>
         </is>
       </c>
-      <c r="E72" s="13" t="n"/>
-      <c r="F72" s="13" t="n"/>
-    </row>
-    <row r="73" ht="25.5" customHeight="1">
-      <c r="A73" s="13" t="inlineStr">
+      <c r="E72" s="20" t="inlineStr"/>
+      <c r="F72" s="20" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B73" s="13" t="inlineStr">
+      <c r="B73" s="20" t="inlineStr">
         <is>
           <t>Fair (harmful bias managed)</t>
         </is>
       </c>
-      <c r="C73" s="13" t="inlineStr">
+      <c r="C73" s="20" t="inlineStr">
         <is>
           <t>NIST AI RMF trustworthy-AI characteristic: algorithmic non-discrimination. NOT the same as 'FAIR data'.</t>
         </is>
       </c>
-      <c r="D73" s="13" t="inlineStr">
+      <c r="D73" s="20" t="inlineStr">
         <is>
           <t>NIST-AI-RMF</t>
         </is>
       </c>
-      <c r="E73" s="13" t="n"/>
-      <c r="F73" s="13" t="n"/>
+      <c r="E73" s="20" t="inlineStr"/>
+      <c r="F73" s="20" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="13" t="inlineStr">
+      <c r="A74" s="20" t="inlineStr">
         <is>
           <t>Maturity Level</t>
         </is>
       </c>
-      <c r="B74" s="13" t="inlineStr">
+      <c r="B74" s="20" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="C74" s="13" t="n"/>
-      <c r="D74" s="13" t="n"/>
-      <c r="E74" s="13" t="n"/>
-      <c r="F74" s="13" t="n"/>
+      <c r="C74" s="20" t="inlineStr"/>
+      <c r="D74" s="20" t="inlineStr"/>
+      <c r="E74" s="20" t="inlineStr"/>
+      <c r="F74" s="20" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="13" t="inlineStr">
+      <c r="A75" s="20" t="inlineStr">
         <is>
           <t>Maturity Level</t>
         </is>
       </c>
-      <c r="B75" s="13" t="inlineStr">
+      <c r="B75" s="20" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="C75" s="13" t="n"/>
-      <c r="D75" s="13" t="n"/>
-      <c r="E75" s="13" t="n"/>
-      <c r="F75" s="13" t="n"/>
+      <c r="C75" s="20" t="inlineStr"/>
+      <c r="D75" s="20" t="inlineStr"/>
+      <c r="E75" s="20" t="inlineStr"/>
+      <c r="F75" s="20" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="13" t="inlineStr">
+      <c r="A76" s="20" t="inlineStr">
         <is>
           <t>Maturity Level</t>
         </is>
       </c>
-      <c r="B76" s="13" t="inlineStr">
+      <c r="B76" s="20" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="C76" s="13" t="n"/>
-      <c r="D76" s="13" t="n"/>
-      <c r="E76" s="13" t="n"/>
-      <c r="F76" s="13" t="n"/>
+      <c r="C76" s="20" t="inlineStr"/>
+      <c r="D76" s="20" t="inlineStr"/>
+      <c r="E76" s="20" t="inlineStr"/>
+      <c r="F76" s="20" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="13" t="inlineStr">
+      <c r="A77" s="20" t="inlineStr">
         <is>
           <t>Maturity Level</t>
         </is>
       </c>
-      <c r="B77" s="13" t="inlineStr">
+      <c r="B77" s="20" t="inlineStr">
         <is>
           <t>Deprecated</t>
         </is>
       </c>
-      <c r="C77" s="13" t="n"/>
-      <c r="D77" s="13" t="n"/>
-      <c r="E77" s="13" t="n"/>
-      <c r="F77" s="13" t="n"/>
+      <c r="C77" s="20" t="inlineStr"/>
+      <c r="D77" s="20" t="inlineStr"/>
+      <c r="E77" s="20" t="inlineStr"/>
+      <c r="F77" s="20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5921,145 +5843,145 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="56" customWidth="1" min="4" max="4"/>
-    <col width="90" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" style="17" min="1" max="1"/>
+    <col width="40" customWidth="1" style="17" min="2" max="2"/>
+    <col width="10" customWidth="1" style="17" min="3" max="3"/>
+    <col width="56" customWidth="1" style="17" min="4" max="4"/>
+    <col width="90" customWidth="1" style="17" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>Standard ID</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="19" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="19" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="19" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="19" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="25.5" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="20" t="inlineStr">
         <is>
           <t>EDAM</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t>EDAM ontology (Data management branch)</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="20" t="inlineStr">
         <is>
           <t>current</t>
         </is>
       </c>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="D2" s="20" t="inlineStr">
         <is>
           <t>http://edamontology.org/topic_3071</t>
         </is>
       </c>
-      <c r="E2" s="13" t="inlineStr">
+      <c r="E2" s="20" t="inlineStr">
         <is>
           <t>Primary controlled vocabulary. Open OWL ontology with permanent per-term URIs. Browse: https://www.ebi.ac.uk/ols4/ontologies/edam - Download: http://edamontology.org/EDAM.owl</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="76.5" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>NIST-AI-RMF</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="20" t="inlineStr">
         <is>
           <t>NIST AI Risk Management Framework</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="20" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="20" t="inlineStr">
         <is>
           <t>https://nvlpubs.nist.gov/nistpubs/ai/NIST.AI.100-1.pdf</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" s="20" t="inlineStr">
         <is>
           <t>Optional secondary axis: the seven trustworthy-AI characteristics. Document-based, so individual characteristics have no per-term URIs. WARNING: NIST's 'Fair (harmful bias managed)' concerns algorithmic non-discrimination and is UNRELATED to EDAM's 'FAIR data' (Findable / Accessible / Interoperable / Reusable data principles) despite sharing the word - do not conflate the two. Also defines an AI lifecycle with named stages (plan, collect/process, build, verify, deploy, operate) -- cited here as e.g. "AI lifecycle stage: Deploy", distinct from the seven trustworthy-AI characteristics.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>ACM-CCS</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>ACM Computing Classification System (CCS 2012)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
         <is>
           <t>https://dl.acm.org/ccs</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="0" t="inlineStr">
         <is>
           <t>Cited by category path text (e.g. "Computer systems organization~Architectures"), not a numeric ID a human needs to look up -- confirmed against real paper citations. General computing/software-engineering taxonomy, not agentic-AI-specific -- predates MCP, agent frameworks, and tool-calling entirely, so it backs general CS terms (Architecture, Security, Evaluation, Retrieval) but not agent-specific ones (MCP, Hooks, Skills, Orchestration, ...). Path spellings below are from established domain knowledge, not a live verified fetch (dl.acm.org blocked automated access) -- worth spot-checking in a browser before treating as fully authoritative.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t>Schema.org</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>Schema.org (CreativeWork hierarchy)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>current</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="0" t="inlineStr">
         <is>
           <t>https://schema.org/CreativeWork</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="0" t="inlineStr">
         <is>
           <t>Universal web-metadata vocabulary. Exact-type matches applied directly (e.g. APIReference, BlogPosting, ScholarlyArticle, SoftwareSourceCode, Dataset). For highly specific AI-radar terms with no exact schema.org type, the broader parent type is applied instead (e.g. several terms map to TechArticle) -- this is schema.org's own intended usage pattern (broad type + a custom category property), not a forced fit, but it means several distinct Resource Type terms intentionally share one Ontology ID here, unlike EDAM/ACM-CCS/NIST-AI-RMF where each backed term has its own distinct match.</t>
         </is>

--- a/data/VANTAGE-Technology-Radar.xlsx
+++ b/data/VANTAGE-Technology-Radar.xlsx
@@ -2482,8 +2482,14 @@
           <t>Lenovo Press</t>
         </is>
       </c>
-      <c r="E29" s="3" t="n"/>
-      <c r="F29" s="1" t="n"/>
+      <c r="E29" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="F29" s="1" t="inlineStr">
+        <is>
+          <t>@pbuendia</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>@biddyman11</t>
@@ -2552,8 +2558,14 @@
           <t xml:space="preserve">Coalition for Secure AI (CoSAI) </t>
         </is>
       </c>
-      <c r="E30" s="9" t="n"/>
-      <c r="F30" s="1" t="n"/>
+      <c r="E30" s="9" t="n">
+        <v>46259</v>
+      </c>
+      <c r="F30" s="1" t="inlineStr">
+        <is>
+          <t>@pbuendia</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>@biddyman11</t>

--- a/data/VANTAGE-Technology-Radar.xlsx
+++ b/data/VANTAGE-Technology-Radar.xlsx
@@ -2,9 +2,6 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1515" yWindow="1515" windowWidth="24705" windowHeight="12345" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
   <sheets>
     <sheet name="Knowledgebase" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Deprecated" sheetId="2" state="visible" r:id="rId2"/>
@@ -14,21 +11,23 @@
     <sheet name="Standards" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm"/>
-    <numFmt numFmtId="166" formatCode="m\-d\-yyyy"/>
-    <numFmt numFmtId="167" formatCode="yyyy\-m"/>
-    <numFmt numFmtId="168" formatCode="mmmm\ d\,\ yyyy"/>
-    <numFmt numFmtId="169" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
+  <numFmts count="8">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm"/>
+    <numFmt numFmtId="166" formatCode="m/d/yyyy"/>
+    <numFmt numFmtId="167" formatCode="m-d-yyyy"/>
+    <numFmt numFmtId="168" formatCode="yyyy-m"/>
+    <numFmt numFmtId="169" formatCode="mmmm d, yyyy"/>
+    <numFmt numFmtId="170" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="171" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -38,32 +37,31 @@
     <font>
       <name val="Arial"/>
       <color theme="1"/>
-      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color theme="1"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <color rgb="FF0000FF"/>
-      <sz val="10"/>
       <u val="single"/>
     </font>
     <font>
-      <name val="Arial"/>
       <color rgb="FF0000FF"/>
-      <sz val="10"/>
       <u val="single"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color theme="10"/>
-      <sz val="10"/>
-      <u val="single"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -71,7 +69,7 @@
       <patternFill/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -81,189 +79,104 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="22">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="6">
     <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB7E1CD"/>
+          <bgColor rgb="FFB7E1CD"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFA4C2F4"/>
+          <bgColor rgb="FFA4C2F4"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFE599"/>
           <bgColor rgb="FFFFE599"/>
         </patternFill>
       </fill>
+      <border/>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFA4C2F4"/>
-          <bgColor rgb="FFA4C2F4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB7E1CD"/>
-          <bgColor rgb="FFB7E1CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
+      <font/>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFD9D2E9"/>
           <bgColor rgb="FFD9D2E9"/>
         </patternFill>
       </fill>
+      <border/>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFA4C2F4"/>
-          <bgColor rgb="FFA4C2F4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB7E1CD"/>
-          <bgColor rgb="FFB7E1CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
+      <font/>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFDD7E6B"/>
           <bgColor rgb="FFDD7E6B"/>
         </patternFill>
       </fill>
+      <border/>
     </dxf>
     <dxf>
+      <font/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFE599"/>
-          <bgColor rgb="FFFFE599"/>
+          <fgColor rgb="FFB4A7D6"/>
+          <bgColor rgb="FFB4A7D6"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFA4C2F4"/>
-          <bgColor rgb="FFA4C2F4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB7E1CD"/>
-          <bgColor rgb="FFB7E1CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFE599"/>
-          <bgColor rgb="FFFFE599"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB7E1CD"/>
-          <bgColor rgb="FFB7E1CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFE599"/>
-          <bgColor rgb="FFFFE599"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFA4C2F4"/>
-          <bgColor rgb="FFA4C2F4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB7E1CD"/>
-          <bgColor rgb="FFB7E1CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB7E1CD"/>
-          <bgColor rgb="FFB7E1CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
+      <border/>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -336,7 +249,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -526,8 +439,6 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -538,45 +449,45 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Q43"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="27.42578125" customWidth="1" min="2" max="2"/>
-    <col width="16.28515625" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="18.5703125" customWidth="1" min="8" max="8"/>
-    <col width="37.85546875" customWidth="1" min="9" max="9"/>
-    <col width="57.85546875" customWidth="1" min="10" max="10"/>
-    <col width="44.140625" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" style="17" min="1" max="1"/>
+    <col width="27.38" customWidth="1" style="17" min="2" max="2"/>
+    <col width="16.25" customWidth="1" style="17" min="3" max="3"/>
+    <col width="20" customWidth="1" style="17" min="7" max="7"/>
+    <col width="18.63" customWidth="1" style="17" min="8" max="8"/>
+    <col width="37.88" customWidth="1" style="17" min="9" max="9"/>
+    <col width="57.88" customWidth="1" style="17" min="10" max="10"/>
+    <col width="44.13" customWidth="1" style="17" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>Resource Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="16" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="16" t="inlineStr">
         <is>
           <t>Source Organization</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="16" t="inlineStr">
         <is>
           <t>Last Verified</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="16" t="inlineStr">
         <is>
           <t>Verified By</t>
         </is>
@@ -586,82 +497,82 @@
           <t>Added/Edited By</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="16" t="inlineStr">
         <is>
           <t>Last Updated</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="16" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="16" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="16" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="16" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="16" t="inlineStr">
         <is>
           <t>Relevance to Research Cyberinfrastructure</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="16" t="inlineStr">
         <is>
           <t>Maturity Level</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="16" t="inlineStr">
         <is>
           <t>Notes / Key Takeaways</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="0" t="inlineStr">
         <is>
           <t>Publication Date</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="0" t="inlineStr">
         <is>
           <t>Discovery Date</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>022e4e1c</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>VS Code Copilot Agents Overview</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>https://code.visualstudio.com/docs/copilot/agents/overview</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="6" t="n">
         <v>46157</v>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
@@ -671,72 +582,72 @@
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="H2" s="7" t="n">
         <v>46113</v>
       </c>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="I2" s="8" t="n"/>
+      <c r="J2" s="16" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="K2" s="16" t="inlineStr">
         <is>
           <t>Hooks; Skills; MCP; Agent frameworks</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="L2" s="16" t="inlineStr">
         <is>
           <t>Architecture; Implementation; Deployment</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="M2" s="16" t="inlineStr">
         <is>
           <t>IDE integration for agentic workflows</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="N2" s="16" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="O2" s="16" t="inlineStr">
         <is>
           <t>Canonical reference for VS Code agent capabilities.</t>
         </is>
       </c>
-      <c r="P2" s="11" t="n">
+      <c r="P2" s="18" t="n">
         <v>46162</v>
       </c>
-      <c r="Q2" s="11" t="n">
+      <c r="Q2" s="18" t="n">
         <v>46113</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>2e9b6b2d</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Data Director</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>https://docs.google.com/document/d/1mu1_U1cWqn1aP3vtW83JnX5-aGhzM49K/edit</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>Microsoft, RDA</t>
         </is>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="6" t="n">
         <v>46168</v>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
@@ -746,267 +657,267 @@
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="H3" s="7" t="n">
         <v>46168</v>
       </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="I3" s="16" t="inlineStr">
         <is>
           <t>v0.1 DRAFT</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
+      <c r="J3" s="16" t="inlineStr">
         <is>
           <t>Specification</t>
         </is>
       </c>
-      <c r="K3" s="1" t="inlineStr">
+      <c r="K3" s="16" t="inlineStr">
         <is>
           <t>FAIR data; Workflow Agents</t>
         </is>
       </c>
-      <c r="L3" s="1" t="inlineStr">
+      <c r="L3" s="16" t="inlineStr">
         <is>
           <t>Workflows; Implementation</t>
         </is>
       </c>
-      <c r="M3" s="1" t="inlineStr">
+      <c r="M3" s="16" t="inlineStr">
         <is>
           <t>Makes data outputs FAIR at the point of publication</t>
         </is>
       </c>
-      <c r="N3" s="1" t="inlineStr">
+      <c r="N3" s="16" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="O3" s="1" t="n"/>
-      <c r="Q3" s="11" t="n">
+      <c r="O3" s="16" t="n"/>
+      <c r="Q3" s="18" t="n">
         <v>46168</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>161f1860</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>Agentic AI Tool</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>https://docs.github.com/en/copilot/agents</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="4" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="7" t="n"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="H4" s="7" t="n">
         <v>46113</v>
       </c>
-      <c r="I4" s="1" t="n"/>
-      <c r="J4" s="1" t="inlineStr">
+      <c r="I4" s="16" t="n"/>
+      <c r="J4" s="16" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K4" s="1" t="inlineStr">
+      <c r="K4" s="16" t="inlineStr">
         <is>
           <t>Hooks; Skills; API Integration</t>
         </is>
       </c>
-      <c r="L4" s="1" t="inlineStr">
+      <c r="L4" s="16" t="inlineStr">
         <is>
           <t>Architecture; Governance; Security</t>
         </is>
       </c>
-      <c r="M4" s="1" t="inlineStr">
+      <c r="M4" s="16" t="inlineStr">
         <is>
           <t>Relevant for CI/CD and code-review automation</t>
         </is>
       </c>
-      <c r="N4" s="1" t="inlineStr">
+      <c r="N4" s="16" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="O4" s="1" t="inlineStr">
+      <c r="O4" s="16" t="inlineStr">
         <is>
           <t>Strong alignment with developer workflows.</t>
         </is>
       </c>
-      <c r="Q4" s="11" t="n">
+      <c r="Q4" s="18" t="n">
         <v>46113</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t>abbd844c</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>GitHub MCP Documentation</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>https://github.com/modelcontextprotocol</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>GitHub/OpenAI</t>
         </is>
       </c>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="4" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="7" t="n"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="H5" s="7" t="n">
         <v>46113</v>
       </c>
-      <c r="I5" s="1" t="n"/>
-      <c r="J5" s="1" t="inlineStr">
+      <c r="I5" s="16" t="n"/>
+      <c r="J5" s="16" t="inlineStr">
         <is>
           <t>API Reference</t>
         </is>
       </c>
-      <c r="K5" s="1" t="inlineStr">
+      <c r="K5" s="16" t="inlineStr">
         <is>
           <t>MCP; Tools; Server Integration</t>
         </is>
       </c>
-      <c r="L5" s="1" t="inlineStr">
+      <c r="L5" s="16" t="inlineStr">
         <is>
           <t>Architecture; Implementation</t>
         </is>
       </c>
-      <c r="M5" s="1" t="inlineStr">
+      <c r="M5" s="16" t="inlineStr">
         <is>
           <t>Key for interoperable agent tools</t>
         </is>
       </c>
-      <c r="N5" s="1" t="inlineStr">
+      <c r="N5" s="16" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="O5" s="1" t="inlineStr">
+      <c r="O5" s="16" t="inlineStr">
         <is>
           <t>Fast-moving ecosystem.</t>
         </is>
       </c>
-      <c r="Q5" s="11" t="n">
+      <c r="Q5" s="18" t="n">
         <v>46113</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="0" t="inlineStr">
         <is>
           <t>b71baded</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>OpenAI MCP Specification</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>https://spec.modelcontextprotocol.io</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="4" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="7" t="n"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="H6" s="7" t="n">
         <v>46113</v>
       </c>
-      <c r="I6" s="1" t="n"/>
-      <c r="J6" s="1" t="inlineStr">
+      <c r="I6" s="16" t="n"/>
+      <c r="J6" s="16" t="inlineStr">
         <is>
           <t>Specification</t>
         </is>
       </c>
-      <c r="K6" s="1" t="inlineStr">
+      <c r="K6" s="16" t="inlineStr">
         <is>
           <t>MCP; Tools; Server Patterns</t>
         </is>
       </c>
-      <c r="L6" s="1" t="inlineStr">
+      <c r="L6" s="16" t="inlineStr">
         <is>
           <t>Architecture; Governance</t>
         </is>
       </c>
-      <c r="M6" s="1" t="inlineStr">
+      <c r="M6" s="16" t="inlineStr">
         <is>
           <t>Critical for cross-platform agent interoperability</t>
         </is>
       </c>
-      <c r="N6" s="1" t="inlineStr">
+      <c r="N6" s="16" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="O6" s="1" t="inlineStr">
+      <c r="O6" s="16" t="inlineStr">
         <is>
           <t>Becoming a de facto standard.</t>
         </is>
       </c>
-      <c r="Q6" s="11" t="n">
+      <c r="Q6" s="18" t="n">
         <v>46113</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="0" t="inlineStr">
         <is>
           <t>2b23adbb</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>Anthropic Model Context Protocol</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">https://modelcontextprotocol.io/specification/2025-11-25 </t>
         </is>
       </c>
-      <c r="D7" s="1" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>Anthropic</t>
         </is>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="6" t="n">
         <v>46182</v>
       </c>
-      <c r="F7" s="1" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
@@ -1016,72 +927,72 @@
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="H7" s="7" t="n">
         <v>45962</v>
       </c>
-      <c r="I7" s="7" t="n"/>
-      <c r="J7" s="1" t="inlineStr">
+      <c r="I7" s="11" t="n"/>
+      <c r="J7" s="16" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K7" s="1" t="inlineStr">
+      <c r="K7" s="16" t="inlineStr">
         <is>
           <t>MCP; Agent Patterns</t>
         </is>
       </c>
-      <c r="L7" s="1" t="inlineStr">
+      <c r="L7" s="16" t="inlineStr">
         <is>
           <t>Architecture; Governance</t>
         </is>
       </c>
-      <c r="M7" s="1" t="inlineStr">
+      <c r="M7" s="16" t="inlineStr">
         <is>
           <t>Integration between LLM applications and external data sources and tools</t>
         </is>
       </c>
-      <c r="N7" s="1" t="inlineStr">
+      <c r="N7" s="16" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="O7" s="1" t="inlineStr">
+      <c r="O7" s="16" t="inlineStr">
         <is>
           <t>Strong safety emphasis.</t>
         </is>
       </c>
-      <c r="P7" s="11" t="n">
+      <c r="P7" s="18" t="n">
         <v>45972</v>
       </c>
-      <c r="Q7" s="11" t="n">
+      <c r="Q7" s="18" t="n">
         <v>45962</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="0" t="inlineStr">
         <is>
           <t>d6d28dfa</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>Kaggle Prototype to Production Whitepaper</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>https://www.kaggle.com/whitepaper-prototype-to-production</t>
         </is>
       </c>
-      <c r="D8" s="1" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>Kaggle/Google</t>
         </is>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="6" t="n">
         <v>46157</v>
       </c>
-      <c r="F8" s="1" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
@@ -1091,337 +1002,337 @@
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="H8" s="7" t="n">
         <v>45975</v>
       </c>
-      <c r="I8" s="1" t="inlineStr">
+      <c r="I8" s="16" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="J8" s="1" t="inlineStr">
+      <c r="J8" s="16" t="inlineStr">
         <is>
           <t>Whitepaper</t>
         </is>
       </c>
-      <c r="K8" s="1" t="inlineStr">
+      <c r="K8" s="16" t="inlineStr">
         <is>
           <t>Deployment patterns; Workflow Automation</t>
         </is>
       </c>
-      <c r="L8" s="1" t="inlineStr">
+      <c r="L8" s="16" t="inlineStr">
         <is>
           <t>Implementation; Security; Deployment</t>
         </is>
       </c>
-      <c r="M8" s="1" t="inlineStr">
+      <c r="M8" s="16" t="inlineStr">
         <is>
           <t>Helps teams move prototypes to production</t>
         </is>
       </c>
-      <c r="N8" s="1" t="inlineStr">
+      <c r="N8" s="16" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="O8" s="1" t="inlineStr">
+      <c r="O8" s="16" t="inlineStr">
         <is>
           <t>Technical guide to the operational life cycle of AI agents, focusing on deployment &amp; security</t>
         </is>
       </c>
-      <c r="Q8" s="11" t="n">
+      <c r="Q8" s="18" t="n">
         <v>45975</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="0" t="inlineStr">
         <is>
           <t>bfda8877</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>Google Vertex AI Agents Overview</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>https://cloud.google.com/vertex-ai/docs/agents</t>
         </is>
       </c>
-      <c r="D9" s="1" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="4" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="7" t="n"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H9" s="4" t="n">
+      <c r="H9" s="7" t="n">
         <v>46113</v>
       </c>
-      <c r="I9" s="1" t="n"/>
-      <c r="J9" s="1" t="inlineStr">
+      <c r="I9" s="16" t="n"/>
+      <c r="J9" s="16" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K9" s="1" t="inlineStr">
+      <c r="K9" s="16" t="inlineStr">
         <is>
           <t>Agent frameworks; Orchestration</t>
         </is>
       </c>
-      <c r="L9" s="1" t="inlineStr">
+      <c r="L9" s="16" t="inlineStr">
         <is>
           <t>Architecture; Deployment</t>
         </is>
       </c>
-      <c r="M9" s="1" t="inlineStr">
+      <c r="M9" s="16" t="inlineStr">
         <is>
           <t>Useful for cloud-based scientific workflows</t>
         </is>
       </c>
-      <c r="N9" s="1" t="inlineStr">
+      <c r="N9" s="16" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="O9" s="1" t="inlineStr">
+      <c r="O9" s="16" t="inlineStr">
         <is>
           <t>Strong enterprise alignment.</t>
         </is>
       </c>
-      <c r="Q9" s="11" t="n">
+      <c r="Q9" s="18" t="n">
         <v>46113</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="0" t="inlineStr">
         <is>
           <t>f488464f</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>HuggingFace Agents Documentation</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>https://huggingface.co/docs/agents</t>
         </is>
       </c>
-      <c r="D10" s="1" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>HuggingFace</t>
         </is>
       </c>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="4" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="7" t="n"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="H10" s="7" t="n">
         <v>46082</v>
       </c>
-      <c r="I10" s="1" t="n"/>
-      <c r="J10" s="1" t="inlineStr">
+      <c r="I10" s="16" t="n"/>
+      <c r="J10" s="16" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K10" s="1" t="inlineStr">
+      <c r="K10" s="16" t="inlineStr">
         <is>
           <t>Tools; Skills; Model Integration</t>
         </is>
       </c>
-      <c r="L10" s="1" t="inlineStr">
+      <c r="L10" s="16" t="inlineStr">
         <is>
           <t>Architecture; Implementation</t>
         </is>
       </c>
-      <c r="M10" s="1" t="inlineStr">
+      <c r="M10" s="16" t="inlineStr">
         <is>
           <t>Useful for open-source agent experimentation</t>
         </is>
       </c>
-      <c r="N10" s="1" t="inlineStr">
+      <c r="N10" s="16" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="O10" s="1" t="inlineStr">
+      <c r="O10" s="16" t="inlineStr">
         <is>
           <t>Rapidly evolving.</t>
         </is>
       </c>
-      <c r="Q10" s="11" t="n">
+      <c r="Q10" s="18" t="n">
         <v>46082</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="0" t="inlineStr">
         <is>
           <t>dbe3741e</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>LangChain Agents Overview</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>https://python.langchain.com/docs/modules/agents</t>
         </is>
       </c>
-      <c r="D11" s="1" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>LangChain</t>
         </is>
       </c>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="4" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="7" t="n"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="H11" s="7" t="n">
         <v>46113</v>
       </c>
-      <c r="I11" s="1" t="n"/>
-      <c r="J11" s="1" t="inlineStr">
+      <c r="I11" s="16" t="n"/>
+      <c r="J11" s="16" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K11" s="1" t="inlineStr">
+      <c r="K11" s="16" t="inlineStr">
         <is>
           <t>Tools; Skills; Multi-Agent Patterns</t>
         </is>
       </c>
-      <c r="L11" s="1" t="inlineStr">
+      <c r="L11" s="16" t="inlineStr">
         <is>
           <t>Architecture; Implementation</t>
         </is>
       </c>
-      <c r="M11" s="1" t="inlineStr">
+      <c r="M11" s="16" t="inlineStr">
         <is>
           <t>Relevant for workflow prototyping</t>
         </is>
       </c>
-      <c r="N11" s="1" t="inlineStr">
+      <c r="N11" s="16" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="O11" s="1" t="inlineStr">
+      <c r="O11" s="16" t="inlineStr">
         <is>
           <t>Widely used in research.</t>
         </is>
       </c>
-      <c r="Q11" s="11" t="n">
+      <c r="Q11" s="18" t="n">
         <v>46113</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="0" t="inlineStr">
         <is>
           <t>ddd42289</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>LlamaIndex Agents</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>https://docs.llamaindex.ai/en/stable/agent/</t>
         </is>
       </c>
-      <c r="D12" s="1" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>LlamaIndex</t>
         </is>
       </c>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="4" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="7" t="n"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H12" s="4" t="n">
+      <c r="H12" s="7" t="n">
         <v>46113</v>
       </c>
-      <c r="I12" s="1" t="n"/>
-      <c r="J12" s="1" t="inlineStr">
+      <c r="I12" s="16" t="n"/>
+      <c r="J12" s="16" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K12" s="1" t="inlineStr">
+      <c r="K12" s="16" t="inlineStr">
         <is>
           <t>Tools; Skills; Retrieval Agents</t>
         </is>
       </c>
-      <c r="L12" s="1" t="inlineStr">
+      <c r="L12" s="16" t="inlineStr">
         <is>
           <t>Architecture; Governance</t>
         </is>
       </c>
-      <c r="M12" s="1" t="inlineStr">
+      <c r="M12" s="16" t="inlineStr">
         <is>
           <t>Useful for data-rich research platforms</t>
         </is>
       </c>
-      <c r="N12" s="1" t="inlineStr">
+      <c r="N12" s="16" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="O12" s="1" t="inlineStr">
+      <c r="O12" s="16" t="inlineStr">
         <is>
           <t>Strong retrieval-centric design.</t>
         </is>
       </c>
-      <c r="Q12" s="11" t="n">
+      <c r="Q12" s="18" t="n">
         <v>46113</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="0" t="inlineStr">
         <is>
           <t>c7e95f61</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>Dagster Automation/Agent Patterns</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>https://docs.dagster.io/getting-started/ai-tools</t>
         </is>
       </c>
-      <c r="D13" s="1" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>Dagster Labs</t>
         </is>
       </c>
-      <c r="E13" s="14" t="n">
+      <c r="E13" s="21" t="n">
         <v>46082</v>
       </c>
-      <c r="F13" s="1" t="inlineStr">
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
@@ -1431,1208 +1342,1202 @@
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="H13" s="7" t="n">
         <v>46082</v>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>1.3.15</t>
         </is>
       </c>
-      <c r="J13" s="1" t="inlineStr">
+      <c r="J13" s="16" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K13" s="1" t="inlineStr">
+      <c r="K13" s="16" t="inlineStr">
         <is>
           <t>Workflow Automation; Orchestration</t>
         </is>
       </c>
-      <c r="L13" s="1" t="inlineStr">
+      <c r="L13" s="16" t="inlineStr">
         <is>
           <t>Architecture; Deployment</t>
         </is>
       </c>
-      <c r="M13" s="1" t="inlineStr">
+      <c r="M13" s="16" t="inlineStr">
         <is>
           <t>Relevant for scientific pipelines</t>
         </is>
       </c>
-      <c r="N13" s="1" t="inlineStr">
+      <c r="N13" s="16" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="O13" s="1" t="inlineStr">
+      <c r="O13" s="16" t="inlineStr">
         <is>
           <t>Strong reproducibility focus.</t>
         </is>
       </c>
-      <c r="Q13" s="11" t="n">
+      <c r="Q13" s="18" t="n">
         <v>46082</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="0" t="inlineStr">
         <is>
           <t>73426de0</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>Prefect Automations/Agents</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>https://docs.prefect.io/latest/concepts/automations/</t>
         </is>
       </c>
-      <c r="D14" s="1" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t>Prefect</t>
         </is>
       </c>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="4" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="7" t="n"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H14" s="4" t="n">
+      <c r="H14" s="7" t="n">
         <v>46082</v>
       </c>
-      <c r="I14" s="1" t="n"/>
-      <c r="J14" s="1" t="inlineStr">
+      <c r="I14" s="16" t="n"/>
+      <c r="J14" s="16" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K14" s="1" t="inlineStr">
+      <c r="K14" s="16" t="inlineStr">
         <is>
           <t>Workflow Agents; Triggers</t>
         </is>
       </c>
-      <c r="L14" s="1" t="inlineStr">
+      <c r="L14" s="16" t="inlineStr">
         <is>
           <t>Implementation; Deployment</t>
         </is>
       </c>
-      <c r="M14" s="1" t="inlineStr">
+      <c r="M14" s="16" t="inlineStr">
         <is>
           <t>Useful for data processing pipelines</t>
         </is>
       </c>
-      <c r="N14" s="1" t="inlineStr">
+      <c r="N14" s="16" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="O14" s="1" t="inlineStr">
+      <c r="O14" s="16" t="inlineStr">
         <is>
           <t>Good hybrid cloud/HPC support.</t>
         </is>
       </c>
-      <c r="Q14" s="11" t="n">
+      <c r="Q14" s="18" t="n">
         <v>46082</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="0" t="inlineStr">
         <is>
           <t>3294a13f</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>Jupyter AI</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>https://jupyter-ai.readthedocs.io</t>
         </is>
       </c>
-      <c r="D15" s="1" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>Project Jupyter</t>
         </is>
       </c>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="4" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="7" t="n"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H15" s="4" t="n">
+      <c r="H15" s="7" t="n">
         <v>46113</v>
       </c>
-      <c r="I15" s="1" t="n"/>
-      <c r="J15" s="1" t="inlineStr">
+      <c r="I15" s="16" t="n"/>
+      <c r="J15" s="16" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K15" s="1" t="inlineStr">
+      <c r="K15" s="16" t="inlineStr">
         <is>
           <t>Notebook Agents; Workflow Automation</t>
         </is>
       </c>
-      <c r="L15" s="1" t="inlineStr">
+      <c r="L15" s="16" t="inlineStr">
         <is>
           <t>Implementation; Data governance</t>
         </is>
       </c>
-      <c r="M15" s="1" t="inlineStr">
+      <c r="M15" s="16" t="inlineStr">
         <is>
           <t>Relevant for research notebooks</t>
         </is>
       </c>
-      <c r="N15" s="1" t="inlineStr">
+      <c r="N15" s="16" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="O15" s="1" t="inlineStr">
+      <c r="O15" s="16" t="inlineStr">
         <is>
           <t>Strong alignment with scientific workflows.</t>
         </is>
       </c>
-      <c r="Q15" s="11" t="n">
+      <c r="Q15" s="18" t="n">
         <v>46113</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="0" t="inlineStr">
         <is>
           <t>f51ea180</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>Anthropic Tools API</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>https://docs.anthropic.com/en/docs/tools</t>
         </is>
       </c>
-      <c r="D16" s="1" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>Anthropic</t>
         </is>
       </c>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="4" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="7" t="n"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H16" s="4" t="n">
+      <c r="H16" s="7" t="n">
         <v>46113</v>
       </c>
-      <c r="I16" s="1" t="n"/>
-      <c r="J16" s="1" t="inlineStr">
+      <c r="I16" s="16" t="n"/>
+      <c r="J16" s="16" t="inlineStr">
         <is>
           <t>API Reference</t>
         </is>
       </c>
-      <c r="K16" s="1" t="inlineStr">
+      <c r="K16" s="16" t="inlineStr">
         <is>
           <t>Tools; Skills</t>
         </is>
       </c>
-      <c r="L16" s="1" t="inlineStr">
+      <c r="L16" s="16" t="inlineStr">
         <is>
           <t>Architecture; Security</t>
         </is>
       </c>
-      <c r="M16" s="1" t="inlineStr">
+      <c r="M16" s="16" t="inlineStr">
         <is>
           <t>Useful for safe tool-calling agents</t>
         </is>
       </c>
-      <c r="N16" s="1" t="inlineStr">
+      <c r="N16" s="16" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="O16" s="1" t="inlineStr">
+      <c r="O16" s="16" t="inlineStr">
         <is>
           <t>Strong safety posture.</t>
         </is>
       </c>
-      <c r="Q16" s="11" t="n">
+      <c r="Q16" s="18" t="n">
         <v>46113</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="0" t="inlineStr">
         <is>
           <t>89f36cc1</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>Microsoft Semantic Kernel Agents</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t>https://learn.microsoft.com/semantic-kernel/agents</t>
         </is>
       </c>
-      <c r="D17" s="1" t="inlineStr">
+      <c r="D17" s="16" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="4" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="7" t="n"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H17" s="4" t="n">
+      <c r="H17" s="7" t="n">
         <v>46113</v>
       </c>
-      <c r="I17" s="1" t="n"/>
-      <c r="J17" s="1" t="inlineStr">
+      <c r="I17" s="16" t="n"/>
+      <c r="J17" s="16" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K17" s="1" t="inlineStr">
+      <c r="K17" s="16" t="inlineStr">
         <is>
           <t>Skills; Tools; Orchestration</t>
         </is>
       </c>
-      <c r="L17" s="1" t="inlineStr">
+      <c r="L17" s="16" t="inlineStr">
         <is>
           <t>Architecture; Implementation</t>
         </is>
       </c>
-      <c r="M17" s="1" t="inlineStr">
+      <c r="M17" s="16" t="inlineStr">
         <is>
           <t>Useful for enterprise-grade agent workflows</t>
         </is>
       </c>
-      <c r="N17" s="1" t="inlineStr">
+      <c r="N17" s="16" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="O17" s="1" t="inlineStr">
+      <c r="O17" s="16" t="inlineStr">
         <is>
           <t>Strong .NET + Python support.</t>
         </is>
       </c>
-      <c r="Q17" s="11" t="n">
+      <c r="Q17" s="18" t="n">
         <v>46113</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="0" t="inlineStr">
         <is>
           <t>4ccfda21</t>
         </is>
       </c>
-      <c r="B18" s="1" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>HuggingFace Inference Endpoints</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>https://huggingface.co/inference-endpoints</t>
         </is>
       </c>
-      <c r="D18" s="1" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>HuggingFace</t>
         </is>
       </c>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="4" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="7" t="n"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H18" s="4" t="n">
+      <c r="H18" s="7" t="n">
         <v>46082</v>
       </c>
-      <c r="I18" s="1" t="n"/>
-      <c r="J18" s="1" t="inlineStr">
+      <c r="I18" s="16" t="n"/>
+      <c r="J18" s="16" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K18" s="1" t="inlineStr">
+      <c r="K18" s="16" t="inlineStr">
         <is>
           <t>Model Integration; Tool-Ready Endpoints</t>
         </is>
       </c>
-      <c r="L18" s="1" t="inlineStr">
+      <c r="L18" s="16" t="inlineStr">
         <is>
           <t>Architecture; Deployment</t>
         </is>
       </c>
-      <c r="M18" s="1" t="inlineStr">
+      <c r="M18" s="16" t="inlineStr">
         <is>
           <t>Useful for hosted inference in research</t>
         </is>
       </c>
-      <c r="N18" s="1" t="inlineStr">
+      <c r="N18" s="16" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="O18" s="1" t="inlineStr">
+      <c r="O18" s="16" t="inlineStr">
         <is>
           <t>Good for reproducibility.</t>
         </is>
       </c>
-      <c r="Q18" s="11" t="n">
+      <c r="Q18" s="18" t="n">
         <v>46082</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="0" t="inlineStr">
         <is>
           <t>2e24be4d</t>
         </is>
       </c>
-      <c r="B19" s="1" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>OpenAI Evaluations (Evals)</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>https://platform.openai.com/docs/guides/evals</t>
         </is>
       </c>
-      <c r="D19" s="1" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="4" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="7" t="n"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H19" s="4" t="n">
+      <c r="H19" s="7" t="n">
         <v>46113</v>
       </c>
-      <c r="I19" s="1" t="n"/>
-      <c r="J19" s="1" t="inlineStr">
+      <c r="I19" s="16" t="n"/>
+      <c r="J19" s="16" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K19" s="1" t="inlineStr">
+      <c r="K19" s="16" t="inlineStr">
         <is>
           <t>Evaluation / testing; Safety / guardrails</t>
         </is>
       </c>
-      <c r="L19" s="1" t="inlineStr">
+      <c r="L19" s="16" t="inlineStr">
         <is>
           <t>Security; Governance</t>
         </is>
       </c>
-      <c r="M19" s="1" t="inlineStr">
+      <c r="M19" s="16" t="inlineStr">
         <is>
           <t>Relevant for agent safety in research platforms</t>
         </is>
       </c>
-      <c r="N19" s="1" t="inlineStr">
+      <c r="N19" s="16" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="O19" s="1" t="inlineStr">
+      <c r="O19" s="16" t="inlineStr">
         <is>
           <t>Useful for risk assessment.</t>
         </is>
       </c>
-      <c r="Q19" s="11" t="n">
+      <c r="Q19" s="18" t="n">
         <v>46113</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="0" t="inlineStr">
         <is>
           <t>6b9e7398</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>Anthropic Safety Guidelines</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr">
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>https://docs.anthropic.com/en/docs/safety</t>
         </is>
       </c>
-      <c r="D20" s="1" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>Anthropic</t>
         </is>
       </c>
-      <c r="E20" s="3" t="n"/>
-      <c r="F20" s="4" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="7" t="n"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H20" s="4" t="n">
+      <c r="H20" s="7" t="n">
         <v>46113</v>
       </c>
-      <c r="I20" s="1" t="n"/>
-      <c r="J20" s="1" t="inlineStr">
+      <c r="I20" s="16" t="n"/>
+      <c r="J20" s="16" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K20" s="1" t="inlineStr">
+      <c r="K20" s="16" t="inlineStr">
         <is>
           <t>Safety / guardrails; Safe Tool Use</t>
         </is>
       </c>
-      <c r="L20" s="1" t="inlineStr">
+      <c r="L20" s="16" t="inlineStr">
         <is>
           <t>Governance; Security</t>
         </is>
       </c>
-      <c r="M20" s="1" t="inlineStr">
+      <c r="M20" s="16" t="inlineStr">
         <is>
           <t>Useful for research governance teams</t>
         </is>
       </c>
-      <c r="N20" s="1" t="inlineStr">
+      <c r="N20" s="16" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="O20" s="1" t="inlineStr">
+      <c r="O20" s="16" t="inlineStr">
         <is>
           <t>Strong alignment with institutional risk controls.</t>
         </is>
       </c>
-      <c r="Q20" s="11" t="n">
+      <c r="Q20" s="18" t="n">
         <v>46113</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="0" t="inlineStr">
         <is>
           <t>69804f39</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>Microsoft Responsible AI Standard</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>https://www.microsoft.com/ai/responsible-ai</t>
         </is>
       </c>
-      <c r="D21" s="1" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="E21" s="3" t="n"/>
-      <c r="F21" s="8" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="12" t="n"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H21" s="8" t="n">
+      <c r="H21" s="12" t="n">
         <v>45992</v>
       </c>
-      <c r="I21" s="1" t="n"/>
-      <c r="J21" s="1" t="inlineStr">
+      <c r="I21" s="16" t="n"/>
+      <c r="J21" s="16" t="inlineStr">
         <is>
           <t>Governance Guidance</t>
         </is>
       </c>
-      <c r="K21" s="1" t="inlineStr">
+      <c r="K21" s="16" t="inlineStr">
         <is>
           <t>Safety / guardrails; Governance; Risk Controls</t>
         </is>
       </c>
-      <c r="L21" s="1" t="inlineStr">
+      <c r="L21" s="16" t="inlineStr">
         <is>
           <t>Data governance; Security</t>
         </is>
       </c>
-      <c r="M21" s="1" t="inlineStr">
+      <c r="M21" s="16" t="inlineStr">
         <is>
           <t>Relevant for institutional AI governance</t>
         </is>
       </c>
-      <c r="N21" s="1" t="inlineStr">
+      <c r="N21" s="16" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="O21" s="1" t="inlineStr">
+      <c r="O21" s="16" t="inlineStr">
         <is>
           <t>Widely adopted governance framework.</t>
         </is>
       </c>
-      <c r="Q21" s="11" t="n">
+      <c r="Q21" s="18" t="n">
         <v>45992</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="0" t="inlineStr">
         <is>
           <t>3758624e</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>vLLM Documentation</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
         <is>
           <t>https://docs.vllm.ai</t>
         </is>
       </c>
-      <c r="D22" s="1" t="inlineStr">
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t>vLLM Project Team</t>
         </is>
       </c>
-      <c r="E22" s="3" t="n"/>
+      <c r="E22" s="6" t="n"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H22" s="4" t="n">
+      <c r="H22" s="7" t="n">
         <v>46113</v>
       </c>
-      <c r="I22" s="1" t="n"/>
-      <c r="J22" s="1" t="inlineStr">
+      <c r="I22" s="16" t="n"/>
+      <c r="J22" s="16" t="inlineStr">
         <is>
           <t>Inference Framework</t>
         </is>
       </c>
-      <c r="K22" s="1" t="inlineStr">
+      <c r="K22" s="16" t="inlineStr">
         <is>
           <t>Deployment patterns; Tools</t>
         </is>
       </c>
-      <c r="L22" s="1" t="inlineStr">
+      <c r="L22" s="16" t="inlineStr">
         <is>
           <t>Self‑hosted AI; Architecture; Implementation; Deployment</t>
         </is>
       </c>
-      <c r="M22" s="1" t="inlineStr">
+      <c r="M22" s="16" t="inlineStr">
         <is>
           <t>High (Industry-standard VPC runtime engine)</t>
         </is>
       </c>
-      <c r="N22" s="1" t="inlineStr">
+      <c r="N22" s="16" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="O22" s="1" t="inlineStr">
+      <c r="O22" s="16" t="inlineStr">
         <is>
           <t>Essential for secure TLAs via PagedAttention and FP8/AWQ optimization. Capabilities: Parallel sampling &amp; tool-calling.</t>
         </is>
       </c>
-      <c r="Q22" s="11" t="n">
+      <c r="Q22" s="18" t="n">
         <v>46113</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="0" t="inlineStr">
         <is>
           <t>8a50b5eb</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>Ollama Documentation</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C23" s="16" t="inlineStr">
         <is>
           <t>https://github.com/ollama/ollama</t>
         </is>
       </c>
-      <c r="D23" s="1" t="inlineStr">
+      <c r="D23" s="16" t="inlineStr">
         <is>
           <t>Ollama Community</t>
         </is>
       </c>
-      <c r="E23" s="3" t="n"/>
+      <c r="E23" s="6" t="n"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H23" s="4" t="n">
+      <c r="H23" s="7" t="n">
         <v>46113</v>
       </c>
-      <c r="I23" s="1" t="n"/>
-      <c r="J23" s="1" t="inlineStr">
+      <c r="I23" s="16" t="n"/>
+      <c r="J23" s="16" t="inlineStr">
         <is>
           <t>Local Application Sandbox</t>
         </is>
       </c>
-      <c r="K23" s="1" t="inlineStr">
+      <c r="K23" s="16" t="inlineStr">
         <is>
           <t>Deployment patterns</t>
         </is>
       </c>
-      <c r="L23" s="1" t="inlineStr">
+      <c r="L23" s="16" t="inlineStr">
         <is>
           <t>Self‑hosted AI; Implementation; Deployment</t>
         </is>
       </c>
-      <c r="M23" s="1" t="inlineStr">
+      <c r="M23" s="16" t="inlineStr">
         <is>
           <t>Medium-High (Local workstation co-pilot)</t>
         </is>
       </c>
-      <c r="N23" s="1" t="inlineStr">
+      <c r="N23" s="16" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="O23" s="1" t="inlineStr">
+      <c r="O23" s="16" t="inlineStr">
         <is>
           <t>Eliminates network dependency errors by cleanly bundling open model weights. Capabilities: Local embedding &amp; zero-config tools.</t>
         </is>
       </c>
-      <c r="Q23" s="11" t="n">
+      <c r="Q23" s="18" t="n">
         <v>46113</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="0" t="inlineStr">
         <is>
           <t>763797cd</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Llama.cpp </t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>https://github.com/ggerganov/llama.cpp</t>
         </is>
       </c>
-      <c r="D24" s="1" t="inlineStr">
+      <c r="D24" s="16" t="inlineStr">
         <is>
           <t>Georgi Gerganov</t>
         </is>
       </c>
-      <c r="E24" s="3" t="n"/>
-      <c r="F24" s="1" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="16" t="n"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H24" s="9" t="n">
+      <c r="H24" s="14" t="n">
         <v>46162</v>
       </c>
-      <c r="I24" s="1" t="inlineStr">
+      <c r="I24" s="16" t="inlineStr">
         <is>
           <t>b9253</t>
         </is>
       </c>
-      <c r="J24" s="1" t="inlineStr">
+      <c r="J24" s="16" t="inlineStr">
         <is>
           <t>Github Code Repository</t>
         </is>
       </c>
-      <c r="K24" s="1" t="inlineStr">
+      <c r="K24" s="16" t="inlineStr">
         <is>
           <t>Deployment patterns</t>
         </is>
       </c>
-      <c r="L24" s="1" t="inlineStr">
+      <c r="L24" s="16" t="inlineStr">
         <is>
           <t>Self‑hosted AI; Architecture; Implementation; Deployment</t>
         </is>
       </c>
-      <c r="M24" s="1" t="inlineStr">
+      <c r="M24" s="16" t="inlineStr">
         <is>
           <t>High (Enables reasoning on variable local hardware)</t>
         </is>
       </c>
-      <c r="N24" s="1" t="inlineStr">
+      <c r="N24" s="16" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="O24" s="1" t="inlineStr">
+      <c r="O24" s="16" t="inlineStr">
         <is>
           <t>Grammar constraints ensure localized agentic pipelines always return valid JSON/code. Capabilities: Grammar-based constrained sampling.</t>
         </is>
       </c>
-      <c r="Q24" s="11" t="n">
+      <c r="Q24" s="18" t="n">
         <v>46162</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="0" t="inlineStr">
         <is>
           <t>2d2470f7</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
+      <c r="B25" s="16" t="inlineStr">
         <is>
           <t>Open WebUI Documentation</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C25" s="16" t="inlineStr">
         <is>
           <t>https://docs.openwebui.com</t>
         </is>
       </c>
-      <c r="D25" s="1" t="inlineStr">
+      <c r="D25" s="16" t="inlineStr">
         <is>
           <t>Open WebUI Core Team</t>
         </is>
       </c>
-      <c r="E25" s="3" t="n"/>
+      <c r="E25" s="6" t="n"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H25" s="4" t="n">
+      <c r="H25" s="7" t="n">
         <v>46113</v>
       </c>
-      <c r="I25" s="1" t="n"/>
-      <c r="J25" s="1" t="inlineStr">
+      <c r="I25" s="16" t="n"/>
+      <c r="J25" s="16" t="inlineStr">
         <is>
           <t>Enterprise Control Interface</t>
         </is>
       </c>
-      <c r="K25" s="1" t="inlineStr">
+      <c r="K25" s="16" t="inlineStr">
         <is>
           <t>Retrieval</t>
         </is>
       </c>
-      <c r="L25" s="1" t="inlineStr">
+      <c r="L25" s="16" t="inlineStr">
         <is>
           <t>Self‑hosted AI; Implementation; Deployment</t>
         </is>
       </c>
-      <c r="M25" s="1" t="inlineStr">
+      <c r="M25" s="16" t="inlineStr">
         <is>
           <t>High (Enterprise-grade firewall interface)</t>
         </is>
       </c>
-      <c r="N25" s="1" t="inlineStr">
+      <c r="N25" s="16" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="O25" s="1" t="inlineStr">
+      <c r="O25" s="16" t="inlineStr">
         <is>
           <t>Solves local file parsing/RAG bottlenecks entirely within secure client networks. Capabilities: Local RAG pipelines &amp; offline functions.</t>
         </is>
       </c>
-      <c r="Q25" s="11" t="n">
+      <c r="Q25" s="18" t="n">
         <v>46113</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="0" t="inlineStr">
         <is>
           <t>eb79015c</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t>NVIDIA NIM Air-Gap Deployment Guide</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C26" s="16" t="inlineStr">
         <is>
           <t>https://docs.nvidia.com/nim/large-language-models/latest/deploy-air-gap.html</t>
         </is>
       </c>
-      <c r="D26" s="1" t="inlineStr">
+      <c r="D26" s="16" t="inlineStr">
         <is>
           <t>NVIDIA</t>
         </is>
       </c>
-      <c r="E26" s="3" t="n"/>
+      <c r="E26" s="6" t="n"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H26" s="1" t="n">
+      <c r="H26" s="16" t="n">
         <v>2026</v>
       </c>
-      <c r="I26" s="1" t="n"/>
-      <c r="J26" s="1" t="inlineStr">
+      <c r="I26" s="16" t="n"/>
+      <c r="J26" s="16" t="inlineStr">
         <is>
           <t>Reference Architecture</t>
         </is>
       </c>
-      <c r="K26" s="1" t="inlineStr">
+      <c r="K26" s="16" t="inlineStr">
         <is>
           <t>Deployment patterns</t>
         </is>
       </c>
-      <c r="L26" s="1" t="inlineStr">
+      <c r="L26" s="16" t="inlineStr">
         <is>
           <t>Self‑hosted AI; Compute Infrastructure; Implementation; Network Isolation; Infrastructure Security</t>
         </is>
       </c>
-      <c r="M26" s="1" t="inlineStr">
+      <c r="M26" s="16" t="inlineStr">
         <is>
           <t>Critical (Standardizes secure distribution of optimized weights)</t>
         </is>
       </c>
-      <c r="N26" s="1" t="inlineStr">
+      <c r="N26" s="16" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="O26" s="1" t="inlineStr">
+      <c r="O26" s="16" t="inlineStr">
         <is>
           <t>Outlines the exact connected-to-disconnected asset transfer workflow for enterprise GPUs. Capabilities: Tensor-parallel caching &amp; optimized tool-calling.</t>
         </is>
       </c>
-      <c r="Q26" s="11" t="n">
+      <c r="Q26" s="18" t="n">
         <v>46150</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="0" t="inlineStr">
         <is>
           <t>80527de7</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>Harbor User Documentation</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C27" s="16" t="inlineStr">
         <is>
           <t>https://goharbor.io/docs/</t>
         </is>
       </c>
-      <c r="D27" s="1" t="inlineStr">
+      <c r="D27" s="16" t="inlineStr">
         <is>
           <t>Cloud Native Computing Foundation (CNCF)</t>
         </is>
       </c>
-      <c r="E27" s="3" t="n"/>
+      <c r="E27" s="6" t="n"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H27" s="1" t="n">
+      <c r="H27" s="16" t="n">
         <v>2026</v>
       </c>
-      <c r="I27" s="1" t="n"/>
-      <c r="J27" s="1" t="inlineStr">
+      <c r="I27" s="16" t="n"/>
+      <c r="J27" s="16" t="inlineStr">
         <is>
           <t>Container Registry</t>
         </is>
       </c>
-      <c r="K27" s="1" t="inlineStr">
+      <c r="K27" s="16" t="inlineStr">
         <is>
           <t>Deployment patterns</t>
         </is>
       </c>
-      <c r="L27" s="1" t="inlineStr">
+      <c r="L27" s="16" t="inlineStr">
         <is>
           <t>Self‑hosted AI; Implementation; Network Isolation; Infrastructure Security; Governance</t>
         </is>
       </c>
-      <c r="M27" s="1" t="inlineStr">
+      <c r="M27" s="16" t="inlineStr">
         <is>
           <t>High (Necessary foundation for secure cluster registries)</t>
         </is>
       </c>
-      <c r="N27" s="1" t="inlineStr">
+      <c r="N27" s="16" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="O27" s="1" t="inlineStr">
+      <c r="O27" s="16" t="inlineStr">
         <is>
           <t>Built-in vulnerability scanning ensures agent images remain clean behind the firewall. Capabilities: Artifact version-locking &amp; immutable tags.</t>
         </is>
       </c>
-      <c r="Q27" s="11" t="n">
+      <c r="Q27" s="18" t="n">
         <v>46150</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="0" t="inlineStr">
         <is>
           <t>b4b5a468</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>AI Engineering Blueprint for On-Premises RAG Systems</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C28" s="16" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2604.01395</t>
         </is>
       </c>
-      <c r="D28" s="1" t="inlineStr">
+      <c r="D28" s="16" t="inlineStr">
         <is>
           <t>arXiv (2604.01395)</t>
         </is>
       </c>
-      <c r="E28" s="3" t="n"/>
+      <c r="E28" s="6" t="n"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H28" s="1" t="n">
+      <c r="H28" s="16" t="n">
         <v>2026</v>
       </c>
-      <c r="I28" s="1" t="n"/>
-      <c r="J28" s="1" t="inlineStr">
+      <c r="I28" s="16" t="n"/>
+      <c r="J28" s="16" t="inlineStr">
         <is>
           <t>Scientific Literature</t>
         </is>
       </c>
-      <c r="K28" s="1" t="inlineStr">
+      <c r="K28" s="16" t="inlineStr">
         <is>
           <t>Deployment patterns; Retrieval</t>
         </is>
       </c>
-      <c r="L28" s="1" t="inlineStr">
+      <c r="L28" s="16" t="inlineStr">
         <is>
           <t>Self‑hosted AI; Infrastructure Security</t>
         </is>
       </c>
-      <c r="M28" s="1" t="inlineStr">
+      <c r="M28" s="16" t="inlineStr">
         <is>
           <t>High (Academic/industry validated system design blueprint)</t>
         </is>
       </c>
-      <c r="N28" s="1" t="inlineStr">
+      <c r="N28" s="16" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="O28" s="1" t="inlineStr">
+      <c r="O28" s="16" t="inlineStr">
         <is>
           <t>Moves past simple how-to guides into formal data isolation and local compliance frameworks. Capabilities: End-to-end local reference applications.</t>
         </is>
       </c>
-      <c r="Q28" s="11" t="n">
+      <c r="Q28" s="18" t="n">
         <v>46150</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="0" t="inlineStr">
         <is>
           <t>0d0a50a7</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>On-Premise vs Cloud: GenAI TCO (2026 Edition)</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">https://lenovopress.lenovo.com/lp2368-on-premise-vs-cloud-generative-ai-total-cost-of-ownership-2026-edition </t>
         </is>
       </c>
-      <c r="D29" s="1" t="inlineStr">
+      <c r="D29" s="16" t="inlineStr">
         <is>
           <t>Lenovo Press</t>
         </is>
       </c>
-      <c r="E29" s="3" t="n">
-        <v>46259</v>
-      </c>
-      <c r="F29" s="1" t="inlineStr">
-        <is>
-          <t>@pbuendia</t>
-        </is>
-      </c>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="16" t="n"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>@biddyman11</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="n">
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="n">
         <v>46054</v>
       </c>
-      <c r="I29" s="1" t="inlineStr">
+      <c r="I29" s="16" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="J29" s="1" t="inlineStr">
+      <c r="J29" s="16" t="inlineStr">
         <is>
           <t>Whitepaper</t>
         </is>
       </c>
-      <c r="K29" s="1" t="inlineStr">
+      <c r="K29" s="16" t="inlineStr">
         <is>
           <t>Deployment patterns</t>
         </is>
       </c>
-      <c r="L29" s="1" t="inlineStr">
+      <c r="L29" s="16" t="inlineStr">
         <is>
           <t>Self‑hosted AI; Architecture; Governance</t>
         </is>
       </c>
-      <c r="M29" s="1" t="inlineStr">
+      <c r="M29" s="16" t="inlineStr">
         <is>
           <t>High (Mandatory for spec'ing out server node VRAM limits)</t>
         </is>
       </c>
-      <c r="N29" s="1" t="inlineStr">
+      <c r="N29" s="16" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="O29" s="1" t="inlineStr">
-        <is>
-          <t>Discusses a "Token Economics" framework. Breaks down the "Memory Wall" economics showing an on-prem breakeven velocity of ~4 months. Capabilities: Hardware performance scaling &amp; VRAM sizing.</t>
-        </is>
-      </c>
-      <c r="Q29" s="11" t="n">
+      <c r="O29" s="16" t="inlineStr">
+        <is>
+          <t>Breaks down the "Memory Wall" economics showing an on-prem breakeven velocity of ~4 months. Capabilities: Hardware performance scaling &amp; VRAM sizing.</t>
+        </is>
+      </c>
+      <c r="Q29" s="18" t="n">
         <v>46054</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="0" t="inlineStr">
         <is>
           <t>359b5ac8</t>
         </is>
       </c>
-      <c r="B30" s="1" t="inlineStr">
+      <c r="B30" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Coalition for Secure AI (CoSAI) </t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>https://www.coalitionforsecureai.org/</t>
         </is>
       </c>
-      <c r="D30" s="1" t="inlineStr">
+      <c r="D30" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Coalition for Secure AI (CoSAI) </t>
         </is>
       </c>
-      <c r="E30" s="9" t="n">
-        <v>46259</v>
-      </c>
-      <c r="F30" s="1" t="inlineStr">
-        <is>
-          <t>@pbuendia</t>
+      <c r="E30" s="14" t="n">
+        <v>46174</v>
+      </c>
+      <c r="F30" s="16" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>@biddyman11</t>
-        </is>
-      </c>
-      <c r="H30" s="9" t="n">
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H30" s="14" t="n">
         <v>46174</v>
       </c>
-      <c r="J30" s="1" t="inlineStr">
+      <c r="J30" s="16" t="inlineStr">
         <is>
           <t>Security Guidance &amp; Resources</t>
         </is>
       </c>
-      <c r="K30" s="1" t="inlineStr">
+      <c r="K30" s="16" t="inlineStr">
         <is>
           <t>Safety / guardrails; Safe Tool Use</t>
         </is>
       </c>
-      <c r="L30" s="1" t="inlineStr">
+      <c r="L30" s="16" t="inlineStr">
         <is>
           <t>Infrastructure Security; Security</t>
         </is>
       </c>
-      <c r="M30" s="1" t="inlineStr">
+      <c r="M30" s="16" t="inlineStr">
         <is>
           <t>Relevant security expertise and best practices for secure AI development and deployment</t>
         </is>
       </c>
-      <c r="N30" s="1" t="inlineStr">
+      <c r="N30" s="16" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="O30" s="1" t="inlineStr">
-        <is>
-          <t>The Coalition for Secure AI (CoSAI) is an open ecosystem of AI and security experts. See https://github.com/cosai-oasis/ws2-defenders</t>
-        </is>
-      </c>
-      <c r="Q30" s="11" t="n">
+      <c r="O30" s="16" t="inlineStr">
+        <is>
+          <t>The Coalition for Secure AI (CoSAI) is an open ecosystem of AI and security experts</t>
+        </is>
+      </c>
+      <c r="Q30" s="18" t="n">
         <v>46174</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="0" t="inlineStr">
         <is>
           <t>5f3954c2</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
+      <c r="B31" s="16" t="inlineStr">
         <is>
           <t>Anthropic Project Glasswing</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>https://www.anthropic.com/glasswing</t>
         </is>
       </c>
-      <c r="D31" s="1" t="inlineStr">
+      <c r="D31" s="16" t="inlineStr">
         <is>
           <t>Anthropic</t>
         </is>
       </c>
-      <c r="E31" s="9" t="n">
+      <c r="E31" s="14" t="n">
         <v>46182</v>
       </c>
-      <c r="F31" s="1" t="inlineStr">
+      <c r="F31" s="16" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
@@ -2642,72 +2547,72 @@
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H31" s="9" t="n">
+      <c r="H31" s="14" t="n">
         <v>46119</v>
       </c>
-      <c r="I31" s="10" t="n"/>
-      <c r="J31" s="1" t="inlineStr">
+      <c r="I31" s="15" t="n"/>
+      <c r="J31" s="16" t="inlineStr">
         <is>
           <t>Security Guidance &amp; Resources</t>
         </is>
       </c>
-      <c r="K31" s="1" t="inlineStr">
+      <c r="K31" s="16" t="inlineStr">
         <is>
           <t>Cybersecurity</t>
         </is>
       </c>
-      <c r="L31" s="1" t="inlineStr">
+      <c r="L31" s="16" t="inlineStr">
         <is>
           <t>Infrastructure Security; Security</t>
         </is>
       </c>
-      <c r="M31" s="1" t="inlineStr">
+      <c r="M31" s="16" t="inlineStr">
         <is>
           <t>AI models that find high-severity vulnerabilities</t>
         </is>
       </c>
-      <c r="N31" s="1" t="inlineStr">
+      <c r="N31" s="16" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="O31" s="2" t="inlineStr">
+      <c r="O31" s="5" t="inlineStr">
         <is>
           <t>See Claude Mythos Preview</t>
         </is>
       </c>
-      <c r="P31" s="11" t="n">
+      <c r="P31" s="18" t="n">
         <v>46119</v>
       </c>
-      <c r="Q31" s="11" t="n">
+      <c r="Q31" s="18" t="n">
         <v>46119</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="0" t="inlineStr">
         <is>
           <t>1c277820</t>
         </is>
       </c>
-      <c r="B32" s="1" t="inlineStr">
+      <c r="B32" s="16" t="inlineStr">
         <is>
           <t>Docker AI Governance &amp; Sandboxes</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>https://docs.docker.com/ai/sandboxes/governance/org/</t>
         </is>
       </c>
-      <c r="D32" s="1" t="inlineStr">
+      <c r="D32" s="16" t="inlineStr">
         <is>
           <t>Docker</t>
         </is>
       </c>
-      <c r="E32" s="9" t="n">
+      <c r="E32" s="14" t="n">
         <v>46219</v>
       </c>
-      <c r="F32" s="1" t="inlineStr">
+      <c r="F32" s="16" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
@@ -2717,73 +2622,73 @@
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H32" s="9" t="n">
+      <c r="H32" s="14" t="n">
         <v>46213</v>
       </c>
-      <c r="I32" s="6" t="inlineStr">
+      <c r="I32" s="9" t="inlineStr">
         <is>
           <t>0.35.0</t>
         </is>
       </c>
-      <c r="J32" s="1" t="inlineStr">
+      <c r="J32" s="16" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K32" s="1" t="inlineStr">
+      <c r="K32" s="16" t="inlineStr">
         <is>
           <t>Sandbox; MCP</t>
         </is>
       </c>
-      <c r="L32" s="1" t="inlineStr">
+      <c r="L32" s="16" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="M32" s="1" t="inlineStr">
+      <c r="M32" s="16" t="inlineStr">
         <is>
           <t>Good AI governance topics</t>
         </is>
       </c>
-      <c r="N32" s="1" t="inlineStr">
+      <c r="N32" s="16" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="O32" s="1" t="inlineStr">
+      <c r="O32" s="16" t="inlineStr">
         <is>
           <t>See blog article: https://www.docker.com/blog/the-3cs-a-framework-for-ai-agent-security/</t>
         </is>
       </c>
-      <c r="Q32" s="11" t="n">
+      <c r="Q32" s="18" t="n">
         <v>46213</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="0" t="inlineStr">
         <is>
           <t>b39dc1d1</t>
         </is>
       </c>
-      <c r="B33" s="1" t="inlineStr">
+      <c r="B33" s="16" t="inlineStr">
         <is>
           <t>Responses API</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>https://developers.openai.com/api/docs/guides/migrate-to-responses</t>
         </is>
       </c>
-      <c r="D33" s="1" t="inlineStr">
+      <c r="D33" s="16" t="inlineStr">
         <is>
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="E33" s="9" t="n">
+      <c r="E33" s="14" t="n">
         <v>46220</v>
       </c>
-      <c r="F33" s="1" t="inlineStr">
+      <c r="F33" s="16" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
@@ -2793,98 +2698,98 @@
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H33" s="9" t="n">
+      <c r="H33" s="14" t="n">
         <v>46212</v>
       </c>
-      <c r="I33" s="1" t="inlineStr">
+      <c r="I33" s="16" t="inlineStr">
         <is>
           <t>GPT-5.6</t>
         </is>
       </c>
-      <c r="J33" s="1" t="inlineStr">
+      <c r="J33" s="16" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K33" s="1" t="inlineStr">
+      <c r="K33" s="16" t="inlineStr">
         <is>
           <t>Tools; Skills; Retrieval</t>
         </is>
       </c>
-      <c r="L33" s="1" t="inlineStr">
+      <c r="L33" s="16" t="inlineStr">
         <is>
           <t>Architecture</t>
         </is>
       </c>
-      <c r="M33" s="1" t="inlineStr">
+      <c r="M33" s="16" t="inlineStr">
         <is>
           <t>Useful for domain-specific agents</t>
         </is>
       </c>
-      <c r="N33" s="1" t="inlineStr">
+      <c r="N33" s="16" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="O33" s="1" t="inlineStr">
+      <c r="O33" s="16" t="inlineStr">
         <is>
           <t>MIgrated from API Assistants  - now deprecated.</t>
         </is>
       </c>
-      <c r="Q33" s="11" t="n">
+      <c r="Q33" s="18" t="n">
         <v>46212</v>
       </c>
     </row>
     <row r="34">
-      <c r="L34" s="1" t="n"/>
+      <c r="L34" s="16" t="n"/>
     </row>
     <row r="35">
-      <c r="L35" s="1" t="n"/>
+      <c r="L35" s="16" t="n"/>
     </row>
     <row r="36">
-      <c r="L36" s="1" t="n"/>
+      <c r="L36" s="16" t="n"/>
     </row>
     <row r="37">
-      <c r="L37" s="1" t="n"/>
+      <c r="L37" s="16" t="n"/>
     </row>
     <row r="38">
-      <c r="L38" s="1" t="n"/>
+      <c r="L38" s="16" t="n"/>
     </row>
     <row r="39">
-      <c r="L39" s="1" t="n"/>
+      <c r="L39" s="16" t="n"/>
     </row>
     <row r="40">
-      <c r="L40" s="1" t="n"/>
+      <c r="L40" s="16" t="n"/>
     </row>
     <row r="41">
-      <c r="L41" s="1" t="n"/>
+      <c r="L41" s="16" t="n"/>
     </row>
     <row r="42">
-      <c r="L42" s="1" t="n"/>
+      <c r="L42" s="16" t="n"/>
     </row>
     <row r="43">
-      <c r="L43" s="1" t="n"/>
+      <c r="L43" s="16" t="n"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D1:D12 D14:D994 F24 F30:F33 G32">
-    <cfRule type="expression" priority="4" dxfId="3">
-      <formula>D1&gt;46151</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J1:J994">
-    <cfRule type="notContainsBlanks" priority="5" dxfId="2">
-      <formula>LEN(TRIM(J1))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="L1:L994">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Emerging"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
       <formula>"Mature"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"Research"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1:D12 D14:D994 F24 F30:F33 G32">
+    <cfRule type="expression" priority="4" dxfId="3">
+      <formula>D1&gt;46151.0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J1:J994">
+    <cfRule type="notContainsBlanks" priority="5" dxfId="0">
+      <formula>LEN(TRIM(J1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -2894,15 +2799,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" location="0350" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" location="0350" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2915,40 +2819,40 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:P2"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="22.140625" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" style="17" min="1" max="1"/>
+    <col width="22.13" customWidth="1" style="17" min="2" max="2"/>
+    <col width="20" customWidth="1" style="17" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>Resource Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="16" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="16" t="inlineStr">
         <is>
           <t>Source Organization</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="16" t="inlineStr">
         <is>
           <t>Last Verified</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="16" t="inlineStr">
         <is>
           <t>Verified By</t>
         </is>
@@ -2958,77 +2862,77 @@
           <t>Added/Edited By</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="16" t="inlineStr">
         <is>
           <t>Deprecation Date / Last Updated</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="16" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="16" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="16" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="16" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="16" t="inlineStr">
         <is>
           <t>Relevance to Research Cyberinfrastructure</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="16" t="inlineStr">
         <is>
           <t>Maturity Level</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="16" t="inlineStr">
         <is>
           <t>Notes / Key Takeaways</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="0" t="inlineStr">
         <is>
           <t>Discovery Date</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>805047b4</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>OpenAI Assistants API</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>https://platform.openai.com/docs/assistants</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr">
         <is>
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="6" t="n">
         <v>46150</v>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
@@ -3038,84 +2942,89 @@
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="H2" s="7" t="n">
         <v>46260</v>
       </c>
-      <c r="I2" s="1" t="n"/>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="I2" s="16" t="n"/>
+      <c r="J2" s="16" t="inlineStr">
         <is>
           <t>API Reference</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="K2" s="16" t="inlineStr">
         <is>
           <t>Tools; Skills; Retrieval</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="L2" s="16" t="inlineStr">
         <is>
           <t>Architecture; Implementation</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="M2" s="16" t="inlineStr">
         <is>
           <t>Useful for domain-specific agents</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="N2" s="16" t="inlineStr">
         <is>
           <t>Deprecated</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="O2" s="16" t="inlineStr">
         <is>
           <t>Stable API surface.</t>
         </is>
       </c>
-      <c r="P2" s="11" t="n">
+      <c r="P2" s="18" t="n">
         <v>46150</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D1:D2">
-    <cfRule type="expression" priority="5" dxfId="3">
-      <formula>D1&gt;46151</formula>
+  <conditionalFormatting sqref="L2">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"Emerging"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"Mature"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L1:L2">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>"Research"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:J2">
-    <cfRule type="notContainsBlanks" priority="4" dxfId="2">
+    <cfRule type="notContainsBlanks" priority="4" dxfId="0">
       <formula>LEN(TRIM(J1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1">
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="0">
-      <formula>"Adolescent"</formula>
+  <conditionalFormatting sqref="D2">
+    <cfRule type="expression" priority="5" dxfId="3">
+      <formula>D2&gt;46151.0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:L1">
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
       <formula>"Emerging"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="7" operator="equal" dxfId="1">
       <formula>"Mature"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L1:L2">
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="0">
-      <formula>"Research"</formula>
+  <conditionalFormatting sqref="K1">
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="2">
+      <formula>"Adolescent"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1">
+    <cfRule type="expression" priority="9" dxfId="3">
+      <formula>D1&gt;46151.0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1:L993">
-    <cfRule type="cellIs" priority="10" operator="equal" dxfId="6">
+    <cfRule type="cellIs" priority="10" operator="equal" dxfId="4">
       <formula>"Deprecated"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="2">
-      <formula>"Emerging"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
-      <formula>"Mature"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -3137,40 +3046,40 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N8"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="29.85546875" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" style="17" min="1" max="1"/>
+    <col width="29.88" customWidth="1" style="17" min="3" max="3"/>
+    <col width="20" customWidth="1" style="17" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>Resource Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="16" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="16" t="inlineStr">
         <is>
           <t>Source Organization</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="16" t="inlineStr">
         <is>
           <t>Last Verified</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="16" t="inlineStr">
         <is>
           <t>Verified By</t>
         </is>
@@ -3180,67 +3089,67 @@
           <t>Added/Edited By</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="16" t="inlineStr">
         <is>
           <t>Last Updated</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="16" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="16" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="16" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="16" t="inlineStr">
         <is>
           <t>Maturity Level</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="16" t="inlineStr">
         <is>
           <t>Notes / Key Takeaways</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="0" t="inlineStr">
         <is>
           <t>Discovery Date</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>ba114fad</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>Databricks Coding Agent Benchmark</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>https://www.databricks.com/blog/benchmarking-coding-agents-databricks-multi-million-line-codebase</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr">
         <is>
           <t>Databricks</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="6" t="n">
         <v>46216</v>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
@@ -3250,63 +3159,63 @@
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H2" s="1" t="n">
+      <c r="H2" s="16" t="n">
         <v>2024</v>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="I2" s="16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="J2" s="16" t="inlineStr">
         <is>
           <t>Whitepaper</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="K2" s="16" t="inlineStr">
         <is>
           <t>Coding Agents</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="L2" s="16" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="M2" s="16" t="inlineStr">
         <is>
           <t>Evaluates State-Of-The-Art agent performance on multi-million line codebases to assess real-world software engineering capabilities.</t>
         </is>
       </c>
-      <c r="N2" s="11" t="n">
+      <c r="N2" s="18" t="n">
         <v>46216</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>4c170f7e</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Papers with Code </t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>https://paperswithcode.co/tasks/coding-agents</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>Hugging Face</t>
         </is>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="6" t="n">
         <v>46216</v>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
@@ -3316,332 +3225,332 @@
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H3" s="1" t="n">
+      <c r="H3" s="16" t="n">
         <v>2026</v>
       </c>
-      <c r="J3" s="1" t="inlineStr">
+      <c r="J3" s="16" t="inlineStr">
         <is>
           <t>Benchmark Collection</t>
         </is>
       </c>
-      <c r="K3" s="1" t="inlineStr">
+      <c r="K3" s="16" t="inlineStr">
         <is>
           <t>Coding Agents</t>
         </is>
       </c>
-      <c r="L3" s="1" t="inlineStr">
+      <c r="L3" s="16" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="M3" s="1" t="inlineStr">
+      <c r="M3" s="16" t="inlineStr">
         <is>
           <t>Papers with Code with State-Of-The-Art (SOTA) Codng Agent Benchmarks</t>
         </is>
       </c>
-      <c r="N3" s="11" t="n">
+      <c r="N3" s="18" t="n">
         <v>46216</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>b9ed03e7</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>SWE-Bench Pro</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>https://openreview.net/forum?id=9R2iUHhVfr</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>SWE-bench Team</t>
         </is>
       </c>
-      <c r="E4" s="3" t="n"/>
+      <c r="E4" s="6" t="n"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H4" s="1" t="n">
+      <c r="H4" s="16" t="n">
         <v>2025</v>
       </c>
-      <c r="I4" s="1" t="inlineStr">
+      <c r="I4" s="16" t="inlineStr">
         <is>
           <t>Pro</t>
         </is>
       </c>
-      <c r="J4" s="1" t="inlineStr">
+      <c r="J4" s="16" t="inlineStr">
         <is>
           <t>Whitepaper</t>
         </is>
       </c>
-      <c r="K4" s="1" t="inlineStr">
+      <c r="K4" s="16" t="inlineStr">
         <is>
           <t>Coding Agents</t>
         </is>
       </c>
-      <c r="L4" s="1" t="inlineStr">
+      <c r="L4" s="16" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="M4" s="1" t="inlineStr">
+      <c r="M4" s="16" t="inlineStr">
         <is>
           <t>Addresses limitations of original SWE-bench by focusing on long-horizon, complex, multi-file software engineering tasks.</t>
         </is>
       </c>
-      <c r="N4" s="11" t="n">
+      <c r="N4" s="18" t="n">
         <v>46216</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t>f487cdc5</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>SWE-Bench++</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2512.17419</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>Academic Researchers</t>
         </is>
       </c>
-      <c r="E5" s="3" t="n"/>
+      <c r="E5" s="6" t="n"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H5" s="1" t="n">
+      <c r="H5" s="16" t="n">
         <v>2025</v>
       </c>
-      <c r="J5" s="1" t="inlineStr">
+      <c r="J5" s="16" t="inlineStr">
         <is>
           <t>Whitepaper</t>
         </is>
       </c>
-      <c r="K5" s="1" t="inlineStr">
+      <c r="K5" s="16" t="inlineStr">
         <is>
           <t>Coding Agents</t>
         </is>
       </c>
-      <c r="L5" s="1" t="inlineStr">
+      <c r="L5" s="16" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="M5" s="1" t="inlineStr">
+      <c r="M5" s="16" t="inlineStr">
         <is>
           <t>Scalable framework that generates repository-level tasks from live GitHub PRs across 11 programming languages.</t>
         </is>
       </c>
-      <c r="N5" s="11" t="n">
+      <c r="N5" s="18" t="n">
         <v>46216</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="0" t="inlineStr">
         <is>
           <t>f37d4051</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>Terminal-Bench</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2601.11868</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>CISPA / Academic Researchers</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n"/>
+      <c r="E6" s="6" t="n"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H6" s="1" t="n">
+      <c r="H6" s="16" t="n">
         <v>2026</v>
       </c>
-      <c r="I6" s="1" t="n">
+      <c r="I6" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="J6" s="1" t="inlineStr">
+      <c r="J6" s="16" t="inlineStr">
         <is>
           <t>Whitepaper</t>
         </is>
       </c>
-      <c r="K6" s="1" t="inlineStr">
+      <c r="K6" s="16" t="inlineStr">
         <is>
           <t>Coding Agents</t>
         </is>
       </c>
-      <c r="L6" s="1" t="inlineStr">
+      <c r="L6" s="16" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="M6" s="1" t="inlineStr">
+      <c r="M6" s="16" t="inlineStr">
         <is>
           <t>Benchmarks agents on hard, realistic tasks within terminal/CLI environments.</t>
         </is>
       </c>
-      <c r="N6" s="11" t="n">
+      <c r="N6" s="18" t="n">
         <v>46216</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="0" t="inlineStr">
         <is>
           <t>acbc7354</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>c-CRAB</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2603.23448</t>
         </is>
       </c>
-      <c r="D7" s="1" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>Academic Researchers</t>
         </is>
       </c>
-      <c r="E7" s="3" t="n"/>
+      <c r="E7" s="6" t="n"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H7" s="1" t="n">
+      <c r="H7" s="16" t="n">
         <v>2026</v>
       </c>
-      <c r="I7" s="1" t="n">
+      <c r="I7" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="J7" s="1" t="inlineStr">
+      <c r="J7" s="16" t="inlineStr">
         <is>
           <t>Whitepaper</t>
         </is>
       </c>
-      <c r="K7" s="1" t="inlineStr">
+      <c r="K7" s="16" t="inlineStr">
         <is>
           <t>Coding Agents</t>
         </is>
       </c>
-      <c r="L7" s="1" t="inlineStr">
+      <c r="L7" s="16" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="M7" s="1" t="inlineStr">
+      <c r="M7" s="16" t="inlineStr">
         <is>
           <t>Benchmark specifically for evaluating the code review capabilities of AI agents.</t>
         </is>
       </c>
-      <c r="N7" s="11" t="n">
+      <c r="N7" s="18" t="n">
         <v>46216</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="0" t="inlineStr">
         <is>
           <t>edd19b89</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>SWE-Explore</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2606.07297</t>
         </is>
       </c>
-      <c r="D8" s="1" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>Academic Researchers</t>
         </is>
       </c>
-      <c r="E8" s="3" t="n"/>
+      <c r="E8" s="6" t="n"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H8" s="1" t="n">
+      <c r="H8" s="16" t="n">
         <v>2026</v>
       </c>
-      <c r="I8" s="1" t="n">
+      <c r="I8" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="J8" s="1" t="inlineStr">
+      <c r="J8" s="16" t="inlineStr">
         <is>
           <t>Whitepaper</t>
         </is>
       </c>
-      <c r="K8" s="1" t="inlineStr">
+      <c r="K8" s="16" t="inlineStr">
         <is>
           <t>Coding Agents</t>
         </is>
       </c>
-      <c r="L8" s="1" t="inlineStr">
+      <c r="L8" s="16" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="M8" s="1" t="inlineStr">
+      <c r="M8" s="16" t="inlineStr">
         <is>
           <t>Isolates the evaluation of repository exploration, context retrieval, and code localization capabilities.</t>
         </is>
       </c>
-      <c r="N8" s="11" t="n">
+      <c r="N8" s="18" t="n">
         <v>46216</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D1:D8">
-    <cfRule type="expression" priority="4" dxfId="3">
-      <formula>D1&gt;46151</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="J1:J8">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Emerging"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
       <formula>"Mature"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"Research"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1:D8">
+    <cfRule type="expression" priority="4" dxfId="3">
+      <formula>D1&gt;46151.0</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -3664,198 +3573,198 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="80" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" style="17" min="1" max="1"/>
+    <col width="34" customWidth="1" style="17" min="2" max="2"/>
+    <col width="46" customWidth="1" style="17" min="3" max="3"/>
+    <col width="18" customWidth="1" style="17" min="4" max="4"/>
+    <col width="10" customWidth="1" style="17" min="5" max="5"/>
+    <col width="80" customWidth="1" style="17" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>Position</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="19" t="inlineStr">
         <is>
           <t>Column Name</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="19" t="inlineStr">
         <is>
           <t>Applies To</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="19" t="inlineStr">
         <is>
           <t>Value Type</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="19" t="inlineStr">
         <is>
           <t>Separator</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="19" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="0" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="0" t="inlineStr">
         <is>
           <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="0" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="0" t="inlineStr">
         <is>
           <t>System-generated unique identifier, independent of Resource Name. Auto-assigned by xlsx_to_json.py the first time it sees a row with this cell blank (new rows, and every existing row during this migration) -- don't fill it in by hand. The one exception: when moving a row to a different sheet (e.g. Knowledgebase -&gt; Deprecated), copy its ID along with the rest of the row so the sync scripts recognize it as the same resource rather than a deletion plus a new entry.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25.5" customHeight="1">
-      <c r="A3" s="13" t="n">
+    <row r="3">
+      <c r="A3" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="20" t="inlineStr">
         <is>
           <t>Resource Name</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="20" t="inlineStr">
         <is>
           <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="20" t="inlineStr">
         <is>
           <t>free_text</t>
         </is>
       </c>
-      <c r="E3" s="13" t="n"/>
-      <c r="F3" s="13" t="inlineStr">
+      <c r="E3" s="20" t="inlineStr"/>
+      <c r="F3" s="20" t="inlineStr">
         <is>
           <t>Short, human-readable name. Also the natural key used to match a row across sync runs. Example: VS Code Copilot Agents Overview</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="25.5" customHeight="1">
-      <c r="A4" s="13" t="n">
+    <row r="4">
+      <c r="A4" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
         <is>
           <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="20" t="inlineStr">
         <is>
           <t>free_text</t>
         </is>
       </c>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="E4" s="20" t="inlineStr"/>
+      <c r="F4" s="20" t="inlineStr">
         <is>
           <t>Canonical link to the resource.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="25.5" customHeight="1">
-      <c r="A5" s="13" t="n">
+    <row r="5">
+      <c r="A5" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>Source Organization</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>free_text</t>
         </is>
       </c>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="13" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr"/>
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>Who maintains it? Examples: Microsoft, GitHub, OpenAI, Kaggle, Anthropic, Google, HuggingFace. This matters because some orgs update weekly, others yearly.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="25.5" customHeight="1">
-      <c r="A6" s="13" t="n">
+    <row r="6">
+      <c r="A6" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>Last Verified</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>Date a curator last checked the page. Set by a human during verification; cleared automatically when the row's content changes.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="25.5" customHeight="1">
-      <c r="A7" s="13" t="n">
+    <row r="7">
+      <c r="A7" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>Verified By</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
-      <c r="E7" s="13" t="n"/>
-      <c r="F7" s="13" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>Curator who last verified this row. Set by a human only, never by an agent; cleared automatically when the row's content changes.</t>
         </is>
@@ -3887,294 +3796,294 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="n">
+      <c r="A9" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>Last Updated</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>Knowledgebase; SOTA Coding Agents Benchmarks</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="E9" s="13" t="n"/>
-      <c r="F9" s="13" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr"/>
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>The page's own update timestamp. Helps track fast-moving agent ecosystems.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="38.25" customHeight="1">
-      <c r="A10" s="13" t="n">
+    <row r="10">
+      <c r="A10" s="20" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>Deprecation Date / Last Updated</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>Deprecated</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr"/>
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>Most recent known date for this row, whichever kind of event produced it: when the resource was confirmed deprecated, or, absent that, whenever the row was last touched. An exact deprecation date isn't always knowable at the time a row is added or edited.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="25.5" customHeight="1">
-      <c r="A11" s="13" t="n">
+    <row r="11">
+      <c r="A11" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="13" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr"/>
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>Version string of the resource or tool (e.g. 'v0.1 DRAFT', 'Pro'). Leave blank for article-type resources with no version - use Publication Date instead.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="25.5" customHeight="1">
-      <c r="A12" s="13" t="n">
+    <row r="12">
+      <c r="A12" s="20" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>controlled_single</t>
         </is>
       </c>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="13" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr"/>
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>What kind of resource this is. Helps teams filter by what they need.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="25.5" customHeight="1">
-      <c r="A13" s="13" t="n">
+    <row r="13">
+      <c r="A13" s="20" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>controlled_multi</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>;</t>
         </is>
       </c>
-      <c r="F13" s="13" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>Which agentic capabilities the resource covers. One of the most important columns.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="38.25" customHeight="1">
-      <c r="A14" s="13" t="n">
+    <row r="14">
+      <c r="A14" s="20" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>Knowledgebase; Deprecated</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>controlled_multi</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>;</t>
         </is>
       </c>
-      <c r="F14" s="13" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>Subject areas the resource addresses. Helps research IT teams quickly find relevant material. Primary vocabulary is EDAM; NIST AI RMF characteristics are available as an optional secondary axis.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="38.25" customHeight="1">
-      <c r="A15" s="13" t="n">
+    <row r="15">
+      <c r="A15" s="20" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>Relevance to Research Cyberinfrastructure</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>Knowledgebase; Deprecated</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>free_text</t>
         </is>
       </c>
-      <c r="E15" s="13" t="n"/>
-      <c r="F15" s="13" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr"/>
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>Free-text note on why this matters to research platforms. Example themes: workflow orchestration, data portal integration, metadata / provenance, multi-agent coordination, HPC / cloud hybrid workflows, reproducibility, federated analysis, user-facing agent interfaces.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="25.5" customHeight="1">
-      <c r="A16" s="13" t="n">
+    <row r="16">
+      <c r="A16" s="20" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>Maturity Level</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>controlled_single</t>
         </is>
       </c>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="13" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr"/>
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>Not about the website - about the technology described. Helps teams know whether something is stable enough to consider.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="38.25" customHeight="1">
-      <c r="A17" s="13" t="n">
+    <row r="17">
+      <c r="A17" s="20" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>Notes / Key Takeaways</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>free_text</t>
         </is>
       </c>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="13" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr"/>
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>Short free-text field: breaking changes, important patterns, new capabilities, relevance to agentic workflows, implications for research platforms. This is where institutional knowledge accumulates.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="n">
+      <c r="A18" s="20" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>Publication Date</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>Knowledgebase</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr"/>
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>Publication date for article-type resources that have no software version.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="25.5" customHeight="1">
-      <c r="A19" s="13" t="n">
+    <row r="19">
+      <c r="A19" s="20" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>Discovery Date</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="13" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr"/>
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>Date this resource first entered the VT Radar.</t>
         </is>
@@ -4192,1734 +4101,1735 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F77"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="80" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" style="17" min="1" max="1"/>
+    <col width="42" customWidth="1" style="17" min="2" max="2"/>
+    <col width="80" customWidth="1" style="17" min="3" max="3"/>
+    <col width="14" customWidth="1" style="17" min="4" max="4"/>
+    <col width="14" customWidth="1" style="17" min="5" max="5"/>
+    <col width="44" customWidth="1" style="17" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>Column Name</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="19" t="inlineStr">
         <is>
           <t>Term</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="19" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="19" t="inlineStr">
         <is>
           <t>Ontology</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="19" t="inlineStr">
         <is>
           <t>Ontology ID</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="19" t="inlineStr">
         <is>
           <t>Ontology URL</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="25.5" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="20" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="C2" s="20" t="inlineStr"/>
+      <c r="D2" s="20" t="inlineStr">
         <is>
           <t>Schema.org</t>
         </is>
       </c>
-      <c r="E2" s="13" t="inlineStr">
+      <c r="E2" s="20" t="inlineStr">
         <is>
           <t>schema:TechArticle</t>
         </is>
       </c>
-      <c r="F2" s="13" t="inlineStr">
+      <c r="F2" s="20" t="inlineStr">
         <is>
           <t>https://schema.org/TechArticle</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25.5" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="20" t="inlineStr">
         <is>
           <t>API Reference</t>
         </is>
       </c>
-      <c r="C3" s="13" t="n"/>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="C3" s="20" t="inlineStr"/>
+      <c r="D3" s="20" t="inlineStr">
         <is>
           <t>Schema.org</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" s="20" t="inlineStr">
         <is>
           <t>schema:APIReference</t>
         </is>
       </c>
-      <c r="F3" s="13" t="inlineStr">
+      <c r="F3" s="20" t="inlineStr">
         <is>
           <t>https://schema.org/APIReference</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="25.5" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>Specification</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr"/>
+      <c r="D4" s="20" t="inlineStr">
         <is>
           <t>Schema.org</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" s="20" t="inlineStr">
         <is>
           <t>schema:TechArticle</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="F4" s="20" t="inlineStr">
         <is>
           <t>https://schema.org/TechArticle</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="25.5" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>Whitepaper</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>Vendor or organization technical whitepaper.</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>Schema.org</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>schema:TechArticle</t>
         </is>
       </c>
-      <c r="F5" s="13" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>https://schema.org/TechArticle</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="25.5" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>Scientific Literature</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>Peer-reviewed publication or preprint. Distinct from a vendor Whitepaper.</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>Schema.org</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>schema:ScholarlyArticle</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>https://schema.org/ScholarlyArticle</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="25.5" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>Governance Guidance</t>
         </is>
       </c>
-      <c r="C7" s="13" t="n"/>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>Schema.org</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>schema:TechArticle</t>
         </is>
       </c>
-      <c r="F7" s="13" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>https://schema.org/TechArticle</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="25.5" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>Security Guidance &amp; Resources</t>
         </is>
       </c>
-      <c r="C8" s="13" t="n"/>
-      <c r="D8" s="13" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr"/>
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>Schema.org</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>schema:TechArticle</t>
         </is>
       </c>
-      <c r="F8" s="13" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>https://schema.org/TechArticle</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="25.5" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>Reference Architecture</t>
         </is>
       </c>
-      <c r="C9" s="13" t="n"/>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr"/>
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>Schema.org</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>schema:TechArticle</t>
         </is>
       </c>
-      <c r="F9" s="13" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>https://schema.org/TechArticle</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>Container Registry</t>
         </is>
       </c>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
+      <c r="C10" s="20" t="inlineStr"/>
+      <c r="D10" s="20" t="inlineStr"/>
+      <c r="E10" s="20" t="inlineStr"/>
+      <c r="F10" s="20" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>Enterprise Control Interface</t>
         </is>
       </c>
-      <c r="C11" s="13" t="n"/>
-      <c r="D11" s="13" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="13" t="n"/>
+      <c r="C11" s="20" t="inlineStr"/>
+      <c r="D11" s="20" t="inlineStr"/>
+      <c r="E11" s="20" t="inlineStr"/>
+      <c r="F11" s="20" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>Inference Framework</t>
         </is>
       </c>
-      <c r="C12" s="13" t="n"/>
-      <c r="D12" s="13" t="n"/>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="13" t="n"/>
+      <c r="C12" s="20" t="inlineStr"/>
+      <c r="D12" s="20" t="inlineStr"/>
+      <c r="E12" s="20" t="inlineStr"/>
+      <c r="F12" s="20" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>Local Application Sandbox</t>
         </is>
       </c>
-      <c r="C13" s="13" t="n"/>
-      <c r="D13" s="13" t="n"/>
-      <c r="E13" s="13" t="n"/>
-      <c r="F13" s="13" t="n"/>
-    </row>
-    <row r="14" ht="25.5" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr"/>
+      <c r="D13" s="20" t="inlineStr"/>
+      <c r="E13" s="20" t="inlineStr"/>
+      <c r="F13" s="20" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>Github Code Repository</t>
         </is>
       </c>
-      <c r="C14" s="13" t="n"/>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr"/>
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>Schema.org</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>schema:SoftwareSourceCode</t>
         </is>
       </c>
-      <c r="F14" s="13" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>https://schema.org/SoftwareSourceCode</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="25.5" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>Benchmark Collection</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>A curated collection of benchmarks or comparison studies.</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>Schema.org</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>schema:Dataset</t>
         </is>
       </c>
-      <c r="F15" s="13" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>https://schema.org/Dataset</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>Hooks</t>
         </is>
       </c>
-      <c r="C16" s="13" t="n"/>
-      <c r="D16" s="13" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="13" t="n"/>
+      <c r="C16" s="20" t="inlineStr"/>
+      <c r="D16" s="20" t="inlineStr"/>
+      <c r="E16" s="20" t="inlineStr"/>
+      <c r="F16" s="20" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>Skills</t>
         </is>
       </c>
-      <c r="C17" s="13" t="n"/>
-      <c r="D17" s="13" t="n"/>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="13" t="n"/>
+      <c r="C17" s="20" t="inlineStr"/>
+      <c r="D17" s="20" t="inlineStr"/>
+      <c r="E17" s="20" t="inlineStr"/>
+      <c r="F17" s="20" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>MCP</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>Model Context Protocol.</t>
         </is>
       </c>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="n"/>
+      <c r="D18" s="20" t="inlineStr"/>
+      <c r="E18" s="20" t="inlineStr"/>
+      <c r="F18" s="20" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>Agent frameworks</t>
         </is>
       </c>
-      <c r="C19" s="13" t="n"/>
-      <c r="D19" s="13" t="n"/>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="13" t="n"/>
+      <c r="C19" s="20" t="inlineStr"/>
+      <c r="D19" s="20" t="inlineStr"/>
+      <c r="E19" s="20" t="inlineStr"/>
+      <c r="F19" s="20" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>Agent Patterns</t>
         </is>
       </c>
-      <c r="C20" s="13" t="n"/>
-      <c r="D20" s="13" t="n"/>
-      <c r="E20" s="13" t="n"/>
-      <c r="F20" s="13" t="n"/>
+      <c r="C20" s="20" t="inlineStr"/>
+      <c r="D20" s="20" t="inlineStr"/>
+      <c r="E20" s="20" t="inlineStr"/>
+      <c r="F20" s="20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>Multi-Agent Patterns</t>
         </is>
       </c>
-      <c r="C21" s="13" t="n"/>
-      <c r="D21" s="13" t="n"/>
-      <c r="E21" s="13" t="n"/>
-      <c r="F21" s="13" t="n"/>
+      <c r="C21" s="20" t="inlineStr"/>
+      <c r="D21" s="20" t="inlineStr"/>
+      <c r="E21" s="20" t="inlineStr"/>
+      <c r="F21" s="20" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>Context window management</t>
         </is>
       </c>
-      <c r="C22" s="13" t="n"/>
-      <c r="D22" s="13" t="n"/>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="13" t="n"/>
+      <c r="C22" s="20" t="inlineStr"/>
+      <c r="D22" s="20" t="inlineStr"/>
+      <c r="E22" s="20" t="inlineStr"/>
+      <c r="F22" s="20" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>Deployment patterns</t>
         </is>
       </c>
-      <c r="C23" s="13" t="n"/>
-      <c r="D23" s="13" t="n"/>
-      <c r="E23" s="13" t="n"/>
-      <c r="F23" s="13" t="n"/>
+      <c r="C23" s="20" t="inlineStr"/>
+      <c r="D23" s="20" t="inlineStr"/>
+      <c r="E23" s="20" t="inlineStr"/>
+      <c r="F23" s="20" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>Safety / guardrails</t>
         </is>
       </c>
-      <c r="C24" s="13" t="n"/>
-      <c r="D24" s="13" t="n"/>
-      <c r="E24" s="13" t="n"/>
-      <c r="F24" s="13" t="n"/>
-    </row>
-    <row r="25" ht="102" customHeight="1">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr"/>
+      <c r="D24" s="20" t="inlineStr"/>
+      <c r="E24" s="20" t="inlineStr"/>
+      <c r="F24" s="20" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>Evaluation / testing</t>
         </is>
       </c>
-      <c r="C25" s="13" t="n"/>
-      <c r="D25" s="13" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr"/>
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>ACM-CCS</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>Software and its engineering~Software verification and validation~Software testing and debugging</t>
         </is>
       </c>
-      <c r="F25" s="13" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>https://dl.acm.org/ccs</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>Risk Controls</t>
         </is>
       </c>
-      <c r="C26" s="13" t="n"/>
-      <c r="D26" s="13" t="n"/>
-      <c r="E26" s="13" t="n"/>
-      <c r="F26" s="13" t="n"/>
+      <c r="C26" s="20" t="inlineStr"/>
+      <c r="D26" s="20" t="inlineStr"/>
+      <c r="E26" s="20" t="inlineStr"/>
+      <c r="F26" s="20" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>Safe Tool Use</t>
         </is>
       </c>
-      <c r="C27" s="13" t="n"/>
-      <c r="D27" s="13" t="n"/>
-      <c r="E27" s="13" t="n"/>
-      <c r="F27" s="13" t="n"/>
+      <c r="C27" s="20" t="inlineStr"/>
+      <c r="D27" s="20" t="inlineStr"/>
+      <c r="E27" s="20" t="inlineStr"/>
+      <c r="F27" s="20" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B28" s="13" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>Tools</t>
         </is>
       </c>
-      <c r="C28" s="13" t="n"/>
-      <c r="D28" s="13" t="n"/>
-      <c r="E28" s="13" t="n"/>
-      <c r="F28" s="13" t="n"/>
+      <c r="C28" s="20" t="inlineStr"/>
+      <c r="D28" s="20" t="inlineStr"/>
+      <c r="E28" s="20" t="inlineStr"/>
+      <c r="F28" s="20" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="inlineStr">
+      <c r="A29" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B29" s="13" t="inlineStr">
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>Tool-Ready Endpoints</t>
         </is>
       </c>
-      <c r="C29" s="13" t="n"/>
-      <c r="D29" s="13" t="n"/>
-      <c r="E29" s="13" t="n"/>
-      <c r="F29" s="13" t="n"/>
+      <c r="C29" s="20" t="inlineStr"/>
+      <c r="D29" s="20" t="inlineStr"/>
+      <c r="E29" s="20" t="inlineStr"/>
+      <c r="F29" s="20" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="13" t="inlineStr">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B30" s="13" t="inlineStr">
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>Coding Agents</t>
         </is>
       </c>
-      <c r="C30" s="13" t="n"/>
-      <c r="D30" s="13" t="n"/>
-      <c r="E30" s="13" t="n"/>
-      <c r="F30" s="13" t="n"/>
+      <c r="C30" s="20" t="inlineStr"/>
+      <c r="D30" s="20" t="inlineStr"/>
+      <c r="E30" s="20" t="inlineStr"/>
+      <c r="F30" s="20" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="A31" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B31" s="13" t="inlineStr">
+      <c r="B31" s="20" t="inlineStr">
         <is>
           <t>Notebook Agents</t>
         </is>
       </c>
-      <c r="C31" s="13" t="n"/>
-      <c r="D31" s="13" t="n"/>
-      <c r="E31" s="13" t="n"/>
-      <c r="F31" s="13" t="n"/>
+      <c r="C31" s="20" t="inlineStr"/>
+      <c r="D31" s="20" t="inlineStr"/>
+      <c r="E31" s="20" t="inlineStr"/>
+      <c r="F31" s="20" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="13" t="inlineStr">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B32" s="13" t="inlineStr">
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>Workflow Agents</t>
         </is>
       </c>
-      <c r="C32" s="13" t="n"/>
-      <c r="D32" s="13" t="n"/>
-      <c r="E32" s="13" t="n"/>
-      <c r="F32" s="13" t="n"/>
+      <c r="C32" s="20" t="inlineStr"/>
+      <c r="D32" s="20" t="inlineStr"/>
+      <c r="E32" s="20" t="inlineStr"/>
+      <c r="F32" s="20" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="13" t="inlineStr">
+      <c r="A33" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B33" s="13" t="inlineStr">
+      <c r="B33" s="20" t="inlineStr">
         <is>
           <t>Workflow Automation</t>
         </is>
       </c>
-      <c r="C33" s="13" t="n"/>
-      <c r="D33" s="13" t="n"/>
-      <c r="E33" s="13" t="n"/>
-      <c r="F33" s="13" t="n"/>
+      <c r="C33" s="20" t="inlineStr"/>
+      <c r="D33" s="20" t="inlineStr"/>
+      <c r="E33" s="20" t="inlineStr"/>
+      <c r="F33" s="20" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="13" t="inlineStr">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B34" s="13" t="inlineStr">
+      <c r="B34" s="20" t="inlineStr">
         <is>
           <t>Orchestration</t>
         </is>
       </c>
-      <c r="C34" s="13" t="n"/>
-      <c r="D34" s="13" t="n"/>
-      <c r="E34" s="13" t="n"/>
-      <c r="F34" s="13" t="n"/>
+      <c r="C34" s="20" t="inlineStr"/>
+      <c r="D34" s="20" t="inlineStr"/>
+      <c r="E34" s="20" t="inlineStr"/>
+      <c r="F34" s="20" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="13" t="inlineStr">
+      <c r="A35" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B35" s="13" t="inlineStr">
+      <c r="B35" s="20" t="inlineStr">
         <is>
           <t>Triggers</t>
         </is>
       </c>
-      <c r="C35" s="13" t="n"/>
-      <c r="D35" s="13" t="n"/>
-      <c r="E35" s="13" t="n"/>
-      <c r="F35" s="13" t="n"/>
-    </row>
-    <row r="36" ht="38.25" customHeight="1">
-      <c r="A36" s="13" t="inlineStr">
+      <c r="C35" s="20" t="inlineStr"/>
+      <c r="D35" s="20" t="inlineStr"/>
+      <c r="E35" s="20" t="inlineStr"/>
+      <c r="F35" s="20" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B36" s="13" t="inlineStr">
+      <c r="B36" s="20" t="inlineStr">
         <is>
           <t>Retrieval</t>
         </is>
       </c>
-      <c r="C36" s="13" t="n"/>
-      <c r="D36" s="13" t="inlineStr">
+      <c r="C36" s="20" t="inlineStr"/>
+      <c r="D36" s="20" t="inlineStr">
         <is>
           <t>ACM-CCS</t>
         </is>
       </c>
-      <c r="E36" s="13" t="inlineStr">
+      <c r="E36" s="20" t="inlineStr">
         <is>
           <t>Information systems~Information retrieval</t>
         </is>
       </c>
-      <c r="F36" s="13" t="inlineStr">
+      <c r="F36" s="20" t="inlineStr">
         <is>
           <t>https://dl.acm.org/ccs</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="38.25" customHeight="1">
-      <c r="A37" s="13" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B37" s="13" t="inlineStr">
+      <c r="B37" s="20" t="inlineStr">
         <is>
           <t>Retrieval Agents</t>
         </is>
       </c>
-      <c r="C37" s="13" t="n"/>
-      <c r="D37" s="13" t="inlineStr">
+      <c r="C37" s="20" t="inlineStr"/>
+      <c r="D37" s="20" t="inlineStr">
         <is>
           <t>ACM-CCS</t>
         </is>
       </c>
-      <c r="E37" s="13" t="inlineStr">
+      <c r="E37" s="20" t="inlineStr">
         <is>
           <t>Information systems~Information retrieval</t>
         </is>
       </c>
-      <c r="F37" s="13" t="inlineStr">
+      <c r="F37" s="20" t="inlineStr">
         <is>
           <t>https://dl.acm.org/ccs</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="13" t="inlineStr">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B38" s="13" t="inlineStr">
+      <c r="B38" s="20" t="inlineStr">
         <is>
           <t>Sandbox</t>
         </is>
       </c>
-      <c r="C38" s="13" t="n"/>
-      <c r="D38" s="13" t="n"/>
-      <c r="E38" s="13" t="n"/>
-      <c r="F38" s="13" t="n"/>
+      <c r="C38" s="20" t="inlineStr"/>
+      <c r="D38" s="20" t="inlineStr"/>
+      <c r="E38" s="20" t="inlineStr"/>
+      <c r="F38" s="20" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="13" t="inlineStr">
+      <c r="A39" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B39" s="13" t="inlineStr">
+      <c r="B39" s="20" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="C39" s="13" t="n"/>
-      <c r="D39" s="13" t="n"/>
-      <c r="E39" s="13" t="n"/>
-      <c r="F39" s="13" t="n"/>
-    </row>
-    <row r="40" ht="25.5" customHeight="1">
-      <c r="A40" s="13" t="inlineStr">
+      <c r="C39" s="20" t="inlineStr"/>
+      <c r="D39" s="20" t="inlineStr"/>
+      <c r="E39" s="20" t="inlineStr"/>
+      <c r="F39" s="20" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B40" s="13" t="inlineStr">
+      <c r="B40" s="20" t="inlineStr">
         <is>
           <t>Cybersecurity</t>
         </is>
       </c>
-      <c r="C40" s="13" t="n"/>
-      <c r="D40" s="13" t="inlineStr">
+      <c r="C40" s="20" t="inlineStr"/>
+      <c r="D40" s="20" t="inlineStr">
         <is>
           <t>ACM-CCS</t>
         </is>
       </c>
-      <c r="E40" s="13" t="inlineStr">
+      <c r="E40" s="20" t="inlineStr">
         <is>
           <t>Security and privacy</t>
         </is>
       </c>
-      <c r="F40" s="13" t="inlineStr">
+      <c r="F40" s="20" t="inlineStr">
         <is>
           <t>https://dl.acm.org/ccs</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="13" t="inlineStr">
+      <c r="A41" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B41" s="13" t="inlineStr">
+      <c r="B41" s="20" t="inlineStr">
         <is>
           <t>FAIR data</t>
         </is>
       </c>
-      <c r="C41" s="13" t="inlineStr">
+      <c r="C41" s="20" t="inlineStr">
         <is>
           <t>Findable, Accessible, Interoperable, Reusable data principles.</t>
         </is>
       </c>
-      <c r="D41" s="13" t="inlineStr">
+      <c r="D41" s="20" t="inlineStr">
         <is>
           <t>EDAM</t>
         </is>
       </c>
-      <c r="E41" s="13" t="inlineStr">
+      <c r="E41" s="20" t="inlineStr">
         <is>
           <t>topic_4012</t>
         </is>
       </c>
-      <c r="F41" s="13" t="inlineStr">
+      <c r="F41" s="20" t="inlineStr">
         <is>
           <t>http://edamontology.org/topic_4012</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="13" t="inlineStr">
+      <c r="A42" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B42" s="13" t="inlineStr">
+      <c r="B42" s="20" t="inlineStr">
         <is>
           <t>API Integration</t>
         </is>
       </c>
-      <c r="C42" s="13" t="n"/>
-      <c r="D42" s="13" t="n"/>
-      <c r="E42" s="13" t="n"/>
-      <c r="F42" s="13" t="n"/>
+      <c r="C42" s="20" t="inlineStr"/>
+      <c r="D42" s="20" t="inlineStr"/>
+      <c r="E42" s="20" t="inlineStr"/>
+      <c r="F42" s="20" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="13" t="inlineStr">
+      <c r="A43" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B43" s="13" t="inlineStr">
+      <c r="B43" s="20" t="inlineStr">
         <is>
           <t>Model Integration</t>
         </is>
       </c>
-      <c r="C43" s="13" t="n"/>
-      <c r="D43" s="13" t="n"/>
-      <c r="E43" s="13" t="n"/>
-      <c r="F43" s="13" t="n"/>
+      <c r="C43" s="20" t="inlineStr"/>
+      <c r="D43" s="20" t="inlineStr"/>
+      <c r="E43" s="20" t="inlineStr"/>
+      <c r="F43" s="20" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="13" t="inlineStr">
+      <c r="A44" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B44" s="13" t="inlineStr">
+      <c r="B44" s="20" t="inlineStr">
         <is>
           <t>Server Integration</t>
         </is>
       </c>
-      <c r="C44" s="13" t="n"/>
-      <c r="D44" s="13" t="n"/>
-      <c r="E44" s="13" t="n"/>
-      <c r="F44" s="13" t="n"/>
+      <c r="C44" s="20" t="inlineStr"/>
+      <c r="D44" s="20" t="inlineStr"/>
+      <c r="E44" s="20" t="inlineStr"/>
+      <c r="F44" s="20" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="13" t="inlineStr">
+      <c r="A45" s="20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B45" s="13" t="inlineStr">
+      <c r="B45" s="20" t="inlineStr">
         <is>
           <t>Server Patterns</t>
         </is>
       </c>
-      <c r="C45" s="13" t="n"/>
-      <c r="D45" s="13" t="n"/>
-      <c r="E45" s="13" t="n"/>
-      <c r="F45" s="13" t="n"/>
-    </row>
-    <row r="46" ht="51" customHeight="1">
-      <c r="A46" s="13" t="inlineStr">
+      <c r="C45" s="20" t="inlineStr"/>
+      <c r="D45" s="20" t="inlineStr"/>
+      <c r="E45" s="20" t="inlineStr"/>
+      <c r="F45" s="20" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B46" s="13" t="inlineStr">
+      <c r="B46" s="20" t="inlineStr">
         <is>
           <t>Architecture</t>
         </is>
       </c>
-      <c r="C46" s="13" t="n"/>
-      <c r="D46" s="13" t="inlineStr">
+      <c r="C46" s="20" t="inlineStr"/>
+      <c r="D46" s="20" t="inlineStr">
         <is>
           <t>ACM-CCS</t>
         </is>
       </c>
-      <c r="E46" s="13" t="inlineStr">
+      <c r="E46" s="20" t="inlineStr">
         <is>
           <t>Computer systems organization~Architectures</t>
         </is>
       </c>
-      <c r="F46" s="13" t="inlineStr">
+      <c r="F46" s="20" t="inlineStr">
         <is>
           <t>https://dl.acm.org/ccs</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="25.5" customHeight="1">
-      <c r="A47" s="13" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B47" s="13" t="inlineStr">
+      <c r="B47" s="20" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="C47" s="13" t="n"/>
-      <c r="D47" s="13" t="inlineStr">
+      <c r="C47" s="20" t="inlineStr"/>
+      <c r="D47" s="20" t="inlineStr">
         <is>
           <t>ACM-CCS</t>
         </is>
       </c>
-      <c r="E47" s="13" t="inlineStr">
+      <c r="E47" s="20" t="inlineStr">
         <is>
           <t>Security and privacy</t>
         </is>
       </c>
-      <c r="F47" s="13" t="inlineStr">
+      <c r="F47" s="20" t="inlineStr">
         <is>
           <t>https://dl.acm.org/ccs</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="38.25" customHeight="1">
-      <c r="A48" s="13" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B48" s="13" t="inlineStr">
+      <c r="B48" s="20" t="inlineStr">
         <is>
           <t>Data governance</t>
         </is>
       </c>
-      <c r="C48" s="13" t="inlineStr">
+      <c r="C48" s="20" t="inlineStr">
         <is>
           <t>Focuses specifically on the technical protocols, access controls, data-line security, and de-identification standards used to protect the integrity, quality, and privacy of information throughout its lifecycle</t>
         </is>
       </c>
-      <c r="D48" s="13" t="inlineStr">
+      <c r="D48" s="20" t="inlineStr">
         <is>
           <t>EDAM</t>
         </is>
       </c>
-      <c r="E48" s="13" t="inlineStr">
+      <c r="E48" s="20" t="inlineStr">
         <is>
           <t>topic_3571</t>
         </is>
       </c>
-      <c r="F48" s="13" t="inlineStr">
+      <c r="F48" s="20" t="inlineStr">
         <is>
           <t>http://edamontology.org/topic_3571</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="38.25" customHeight="1">
-      <c r="A49" s="13" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B49" s="13" t="inlineStr">
+      <c r="B49" s="20" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="C49" s="13" t="inlineStr">
+      <c r="C49" s="20" t="inlineStr">
         <is>
           <t>The overarching organizational policies, compliance frameworks, and capital allocation strategies that dictate how an enterprise manages its broader IT infrastructure, risk tolerances, and vendor choices</t>
         </is>
       </c>
-      <c r="D49" s="13" t="n"/>
-      <c r="E49" s="13" t="n"/>
-      <c r="F49" s="13" t="n"/>
-    </row>
-    <row r="50" ht="76.5" customHeight="1">
-      <c r="A50" s="13" t="inlineStr">
+      <c r="D49" s="20" t="inlineStr"/>
+      <c r="E49" s="20" t="inlineStr"/>
+      <c r="F49" s="20" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B50" s="13" t="inlineStr">
+      <c r="B50" s="20" t="inlineStr">
         <is>
           <t>Implementation</t>
         </is>
       </c>
-      <c r="C50" s="13" t="n"/>
-      <c r="D50" s="13" t="inlineStr">
+      <c r="C50" s="20" t="inlineStr"/>
+      <c r="D50" s="20" t="inlineStr">
         <is>
           <t>ACM-CCS</t>
         </is>
       </c>
-      <c r="E50" s="13" t="inlineStr">
+      <c r="E50" s="20" t="inlineStr">
         <is>
           <t>Software and its engineering~Software creation and management</t>
         </is>
       </c>
-      <c r="F50" s="13" t="inlineStr">
+      <c r="F50" s="20" t="inlineStr">
         <is>
           <t>https://dl.acm.org/ccs</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="25.5" customHeight="1">
-      <c r="A51" s="13" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B51" s="13" t="inlineStr">
+      <c r="B51" s="20" t="inlineStr">
         <is>
           <t>Deployment</t>
         </is>
       </c>
-      <c r="C51" s="13" t="inlineStr">
+      <c r="C51" s="20" t="inlineStr">
         <is>
           <t>The tactical, hands-on execution of installing, configuring, provisioning, and launching software or hardware systems within a specific operational environment</t>
         </is>
       </c>
-      <c r="D51" s="13" t="inlineStr">
+      <c r="D51" s="20" t="inlineStr">
         <is>
           <t>NIST-AI-RMF</t>
         </is>
       </c>
-      <c r="E51" s="13" t="inlineStr">
+      <c r="E51" s="20" t="inlineStr">
         <is>
           <t>AI lifecycle stage: Deploy</t>
         </is>
       </c>
-      <c r="F51" s="13" t="inlineStr">
+      <c r="F51" s="20" t="inlineStr">
         <is>
           <t>https://nvlpubs.nist.gov/nistpubs/ai/NIST.AI.100-1.pdf</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="13" t="inlineStr">
+      <c r="A52" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B52" s="13" t="inlineStr">
+      <c r="B52" s="20" t="inlineStr">
         <is>
           <t>Workflows</t>
         </is>
       </c>
-      <c r="C52" s="13" t="n"/>
-      <c r="D52" s="13" t="inlineStr">
+      <c r="C52" s="20" t="inlineStr"/>
+      <c r="D52" s="20" t="inlineStr">
         <is>
           <t>EDAM</t>
         </is>
       </c>
-      <c r="E52" s="13" t="inlineStr">
+      <c r="E52" s="20" t="inlineStr">
         <is>
           <t>topic_0769</t>
         </is>
       </c>
-      <c r="F52" s="13" t="inlineStr">
+      <c r="F52" s="20" t="inlineStr">
         <is>
           <t>http://edamontology.org/topic_0769</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="13" t="inlineStr">
+      <c r="A53" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B53" s="13" t="inlineStr">
+      <c r="B53" s="20" t="inlineStr">
         <is>
           <t>Model selection</t>
         </is>
       </c>
-      <c r="C53" s="13" t="n"/>
-      <c r="D53" s="13" t="n"/>
-      <c r="E53" s="13" t="n"/>
-      <c r="F53" s="13" t="n"/>
-    </row>
-    <row r="54" ht="102" customHeight="1">
-      <c r="A54" s="13" t="inlineStr">
+      <c r="C53" s="20" t="inlineStr"/>
+      <c r="D53" s="20" t="inlineStr"/>
+      <c r="E53" s="20" t="inlineStr"/>
+      <c r="F53" s="20" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B54" s="13" t="inlineStr">
+      <c r="B54" s="20" t="inlineStr">
         <is>
           <t>Evaluation</t>
         </is>
       </c>
-      <c r="C54" s="13" t="n"/>
-      <c r="D54" s="13" t="inlineStr">
+      <c r="C54" s="20" t="inlineStr"/>
+      <c r="D54" s="20" t="inlineStr">
         <is>
           <t>ACM-CCS</t>
         </is>
       </c>
-      <c r="E54" s="13" t="inlineStr">
+      <c r="E54" s="20" t="inlineStr">
         <is>
           <t>Software and its engineering~Software verification and validation~Software testing and debugging</t>
         </is>
       </c>
-      <c r="F54" s="13" t="inlineStr">
+      <c r="F54" s="20" t="inlineStr">
         <is>
           <t>https://dl.acm.org/ccs</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="25.5" customHeight="1">
-      <c r="A55" s="13" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B55" s="13" t="inlineStr">
+      <c r="B55" s="20" t="inlineStr">
         <is>
           <t>Compute Infrastructure</t>
         </is>
       </c>
-      <c r="C55" s="13" t="inlineStr">
+      <c r="C55" s="20" t="inlineStr">
         <is>
           <t>Physical node topologies, hardware constraints, VRAM bounds, and localized compute execution profiles.</t>
         </is>
       </c>
-      <c r="D55" s="13" t="n"/>
-      <c r="E55" s="13" t="n"/>
-      <c r="F55" s="13" t="n"/>
-    </row>
-    <row r="56" ht="25.5" customHeight="1">
-      <c r="A56" s="13" t="inlineStr">
+      <c r="D55" s="20" t="inlineStr"/>
+      <c r="E55" s="20" t="inlineStr"/>
+      <c r="F55" s="20" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B56" s="13" t="inlineStr">
+      <c r="B56" s="20" t="inlineStr">
         <is>
           <t>Network Isolation</t>
         </is>
       </c>
-      <c r="C56" s="13" t="inlineStr">
+      <c r="C56" s="20" t="inlineStr">
         <is>
           <t>Non-egress boundaries, air-gapped artifact staging, localized cloud VPC containers, and firewalled local registries.</t>
         </is>
       </c>
-      <c r="D56" s="13" t="n"/>
-      <c r="E56" s="13" t="n"/>
-      <c r="F56" s="13" t="n"/>
-    </row>
-    <row r="57" ht="25.5" customHeight="1">
-      <c r="A57" s="13" t="inlineStr">
+      <c r="D56" s="20" t="inlineStr"/>
+      <c r="E56" s="20" t="inlineStr"/>
+      <c r="F56" s="20" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B57" s="13" t="inlineStr">
+      <c r="B57" s="20" t="inlineStr">
         <is>
           <t>Infrastructure Security</t>
         </is>
       </c>
-      <c r="C57" s="13" t="inlineStr">
+      <c r="C57" s="20" t="inlineStr">
         <is>
           <t>For on-prem LLM deployments, it captures the security of the compute stack as well as the data pipelines</t>
         </is>
       </c>
-      <c r="D57" s="13" t="n"/>
-      <c r="E57" s="13" t="n"/>
-      <c r="F57" s="13" t="n"/>
-    </row>
-    <row r="58" ht="25.5" customHeight="1">
-      <c r="A58" s="13" t="inlineStr">
+      <c r="D57" s="20" t="inlineStr"/>
+      <c r="E57" s="20" t="inlineStr"/>
+      <c r="F57" s="20" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B58" s="13" t="inlineStr">
+      <c r="B58" s="20" t="inlineStr">
         <is>
           <t>Self‑hosted AI</t>
         </is>
       </c>
-      <c r="C58" s="13" t="inlineStr">
+      <c r="C58" s="20" t="inlineStr">
         <is>
           <t>Self‑hosted, open‑weights models in contrast to API‑based models like OpenAI, Anthropic, or Gemini</t>
         </is>
       </c>
-      <c r="D58" s="13" t="n"/>
-      <c r="E58" s="13" t="n"/>
-      <c r="F58" s="13" t="n"/>
+      <c r="D58" s="20" t="inlineStr"/>
+      <c r="E58" s="20" t="inlineStr"/>
+      <c r="F58" s="20" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="13" t="inlineStr">
+      <c r="A59" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B59" s="13" t="inlineStr">
+      <c r="B59" s="20" t="inlineStr">
         <is>
           <t>Data Protection</t>
         </is>
       </c>
-      <c r="C59" s="13" t="inlineStr">
+      <c r="C59" s="20" t="inlineStr">
         <is>
           <t>Safeguarding sensitive data specifically. Distinct from the broader Security term.</t>
         </is>
       </c>
-      <c r="D59" s="13" t="inlineStr">
+      <c r="D59" s="20" t="inlineStr">
         <is>
           <t>EDAM</t>
         </is>
       </c>
-      <c r="E59" s="13" t="inlineStr">
+      <c r="E59" s="20" t="inlineStr">
         <is>
           <t>topic_4044</t>
         </is>
       </c>
-      <c r="F59" s="13" t="inlineStr">
+      <c r="F59" s="20" t="inlineStr">
         <is>
           <t>http://edamontology.org/topic_4044</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="13" t="inlineStr">
+      <c r="A60" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B60" s="13" t="inlineStr">
+      <c r="B60" s="20" t="inlineStr">
         <is>
           <t>FAIR data</t>
         </is>
       </c>
-      <c r="C60" s="13" t="inlineStr">
+      <c r="C60" s="20" t="inlineStr">
         <is>
           <t>Findable, Accessible, Interoperable, Reusable data principles.</t>
         </is>
       </c>
-      <c r="D60" s="13" t="inlineStr">
+      <c r="D60" s="20" t="inlineStr">
         <is>
           <t>EDAM</t>
         </is>
       </c>
-      <c r="E60" s="13" t="inlineStr">
+      <c r="E60" s="20" t="inlineStr">
         <is>
           <t>topic_4012</t>
         </is>
       </c>
-      <c r="F60" s="13" t="inlineStr">
+      <c r="F60" s="20" t="inlineStr">
         <is>
           <t>http://edamontology.org/topic_4012</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="13" t="inlineStr">
+      <c r="A61" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B61" s="13" t="inlineStr">
+      <c r="B61" s="20" t="inlineStr">
         <is>
           <t>Data quality management</t>
         </is>
       </c>
-      <c r="C61" s="13" t="n"/>
-      <c r="D61" s="13" t="inlineStr">
+      <c r="C61" s="20" t="inlineStr"/>
+      <c r="D61" s="20" t="inlineStr">
         <is>
           <t>EDAM</t>
         </is>
       </c>
-      <c r="E61" s="13" t="inlineStr">
+      <c r="E61" s="20" t="inlineStr">
         <is>
           <t>topic_3572</t>
         </is>
       </c>
-      <c r="F61" s="13" t="inlineStr">
+      <c r="F61" s="20" t="inlineStr">
         <is>
           <t>http://edamontology.org/topic_3572</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="13" t="inlineStr">
+      <c r="A62" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B62" s="13" t="inlineStr">
+      <c r="B62" s="20" t="inlineStr">
         <is>
           <t>Data curation and archival</t>
         </is>
       </c>
-      <c r="C62" s="13" t="n"/>
-      <c r="D62" s="13" t="inlineStr">
+      <c r="C62" s="20" t="inlineStr"/>
+      <c r="D62" s="20" t="inlineStr">
         <is>
           <t>EDAM</t>
         </is>
       </c>
-      <c r="E62" s="13" t="inlineStr">
+      <c r="E62" s="20" t="inlineStr">
         <is>
           <t>topic_0219</t>
         </is>
       </c>
-      <c r="F62" s="13" t="inlineStr">
+      <c r="F62" s="20" t="inlineStr">
         <is>
           <t>http://edamontology.org/topic_0219</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="13" t="inlineStr">
+      <c r="A63" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B63" s="13" t="inlineStr">
+      <c r="B63" s="20" t="inlineStr">
         <is>
           <t>Data integration and warehousing</t>
         </is>
       </c>
-      <c r="C63" s="13" t="n"/>
-      <c r="D63" s="13" t="inlineStr">
+      <c r="C63" s="20" t="inlineStr"/>
+      <c r="D63" s="20" t="inlineStr">
         <is>
           <t>EDAM</t>
         </is>
       </c>
-      <c r="E63" s="13" t="inlineStr">
+      <c r="E63" s="20" t="inlineStr">
         <is>
           <t>topic_3366</t>
         </is>
       </c>
-      <c r="F63" s="13" t="inlineStr">
+      <c r="F63" s="20" t="inlineStr">
         <is>
           <t>http://edamontology.org/topic_3366</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="13" t="inlineStr">
+      <c r="A64" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B64" s="13" t="inlineStr">
+      <c r="B64" s="20" t="inlineStr">
         <is>
           <t>Data architecture, analysis and design</t>
         </is>
       </c>
-      <c r="C64" s="13" t="n"/>
-      <c r="D64" s="13" t="inlineStr">
+      <c r="C64" s="20" t="inlineStr"/>
+      <c r="D64" s="20" t="inlineStr">
         <is>
           <t>EDAM</t>
         </is>
       </c>
-      <c r="E64" s="13" t="inlineStr">
+      <c r="E64" s="20" t="inlineStr">
         <is>
           <t>topic_3365</t>
         </is>
       </c>
-      <c r="F64" s="13" t="inlineStr">
+      <c r="F64" s="20" t="inlineStr">
         <is>
           <t>http://edamontology.org/topic_3365</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="13" t="inlineStr">
+      <c r="A65" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B65" s="13" t="inlineStr">
+      <c r="B65" s="20" t="inlineStr">
         <is>
           <t>Data identity and mapping</t>
         </is>
       </c>
-      <c r="C65" s="13" t="n"/>
-      <c r="D65" s="13" t="inlineStr">
+      <c r="C65" s="20" t="inlineStr"/>
+      <c r="D65" s="20" t="inlineStr">
         <is>
           <t>EDAM</t>
         </is>
       </c>
-      <c r="E65" s="13" t="inlineStr">
+      <c r="E65" s="20" t="inlineStr">
         <is>
           <t>topic_3345</t>
         </is>
       </c>
-      <c r="F65" s="13" t="inlineStr">
+      <c r="F65" s="20" t="inlineStr">
         <is>
           <t>http://edamontology.org/topic_3345</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="13" t="inlineStr">
+      <c r="A66" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B66" s="13" t="inlineStr">
+      <c r="B66" s="20" t="inlineStr">
         <is>
           <t>Data rescue</t>
         </is>
       </c>
-      <c r="C66" s="13" t="n"/>
-      <c r="D66" s="13" t="inlineStr">
+      <c r="C66" s="20" t="inlineStr"/>
+      <c r="D66" s="20" t="inlineStr">
         <is>
           <t>EDAM</t>
         </is>
       </c>
-      <c r="E66" s="13" t="inlineStr">
+      <c r="E66" s="20" t="inlineStr">
         <is>
           <t>topic_4011</t>
         </is>
       </c>
-      <c r="F66" s="13" t="inlineStr">
+      <c r="F66" s="20" t="inlineStr">
         <is>
           <t>http://edamontology.org/topic_4011</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="13" t="inlineStr">
+      <c r="A67" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B67" s="13" t="inlineStr">
+      <c r="B67" s="20" t="inlineStr">
         <is>
           <t>Valid and Reliable</t>
         </is>
       </c>
-      <c r="C67" s="13" t="inlineStr">
+      <c r="C67" s="20" t="inlineStr">
         <is>
           <t>NIST AI RMF trustworthy-AI characteristic.</t>
         </is>
       </c>
-      <c r="D67" s="13" t="inlineStr">
+      <c r="D67" s="20" t="inlineStr">
         <is>
           <t>NIST-AI-RMF</t>
         </is>
       </c>
-      <c r="E67" s="13" t="n"/>
-      <c r="F67" s="13" t="n"/>
+      <c r="E67" s="20" t="inlineStr"/>
+      <c r="F67" s="20" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="13" t="inlineStr">
+      <c r="A68" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B68" s="13" t="inlineStr">
+      <c r="B68" s="20" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
       </c>
-      <c r="C68" s="13" t="inlineStr">
+      <c r="C68" s="20" t="inlineStr">
         <is>
           <t>NIST AI RMF trustworthy-AI characteristic.</t>
         </is>
       </c>
-      <c r="D68" s="13" t="inlineStr">
+      <c r="D68" s="20" t="inlineStr">
         <is>
           <t>NIST-AI-RMF</t>
         </is>
       </c>
-      <c r="E68" s="13" t="n"/>
-      <c r="F68" s="13" t="n"/>
+      <c r="E68" s="20" t="inlineStr"/>
+      <c r="F68" s="20" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="13" t="inlineStr">
+      <c r="A69" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B69" s="13" t="inlineStr">
+      <c r="B69" s="20" t="inlineStr">
         <is>
           <t>Secure and Resilient</t>
         </is>
       </c>
-      <c r="C69" s="13" t="inlineStr">
+      <c r="C69" s="20" t="inlineStr">
         <is>
           <t>NIST AI RMF trustworthy-AI characteristic.</t>
         </is>
       </c>
-      <c r="D69" s="13" t="inlineStr">
+      <c r="D69" s="20" t="inlineStr">
         <is>
           <t>NIST-AI-RMF</t>
         </is>
       </c>
-      <c r="E69" s="13" t="n"/>
-      <c r="F69" s="13" t="n"/>
+      <c r="E69" s="20" t="inlineStr"/>
+      <c r="F69" s="20" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="13" t="inlineStr">
+      <c r="A70" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B70" s="13" t="inlineStr">
+      <c r="B70" s="20" t="inlineStr">
         <is>
           <t>Accountable and Transparent</t>
         </is>
       </c>
-      <c r="C70" s="13" t="inlineStr">
+      <c r="C70" s="20" t="inlineStr">
         <is>
           <t>NIST AI RMF trustworthy-AI characteristic.</t>
         </is>
       </c>
-      <c r="D70" s="13" t="inlineStr">
+      <c r="D70" s="20" t="inlineStr">
         <is>
           <t>NIST-AI-RMF</t>
         </is>
       </c>
-      <c r="E70" s="13" t="n"/>
-      <c r="F70" s="13" t="n"/>
+      <c r="E70" s="20" t="inlineStr"/>
+      <c r="F70" s="20" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="13" t="inlineStr">
+      <c r="A71" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B71" s="13" t="inlineStr">
+      <c r="B71" s="20" t="inlineStr">
         <is>
           <t>Explainable and Interpretable</t>
         </is>
       </c>
-      <c r="C71" s="13" t="inlineStr">
+      <c r="C71" s="20" t="inlineStr">
         <is>
           <t>NIST AI RMF trustworthy-AI characteristic.</t>
         </is>
       </c>
-      <c r="D71" s="13" t="inlineStr">
+      <c r="D71" s="20" t="inlineStr">
         <is>
           <t>NIST-AI-RMF</t>
         </is>
       </c>
-      <c r="E71" s="13" t="n"/>
-      <c r="F71" s="13" t="n"/>
+      <c r="E71" s="20" t="inlineStr"/>
+      <c r="F71" s="20" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="13" t="inlineStr">
+      <c r="A72" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B72" s="13" t="inlineStr">
+      <c r="B72" s="20" t="inlineStr">
         <is>
           <t>Privacy-Enhanced</t>
         </is>
       </c>
-      <c r="C72" s="13" t="inlineStr">
+      <c r="C72" s="20" t="inlineStr">
         <is>
           <t>NIST AI RMF trustworthy-AI characteristic.</t>
         </is>
       </c>
-      <c r="D72" s="13" t="inlineStr">
+      <c r="D72" s="20" t="inlineStr">
         <is>
           <t>NIST-AI-RMF</t>
         </is>
       </c>
-      <c r="E72" s="13" t="n"/>
-      <c r="F72" s="13" t="n"/>
-    </row>
-    <row r="73" ht="25.5" customHeight="1">
-      <c r="A73" s="13" t="inlineStr">
+      <c r="E72" s="20" t="inlineStr"/>
+      <c r="F72" s="20" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="20" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B73" s="13" t="inlineStr">
+      <c r="B73" s="20" t="inlineStr">
         <is>
           <t>Fair (harmful bias managed)</t>
         </is>
       </c>
-      <c r="C73" s="13" t="inlineStr">
+      <c r="C73" s="20" t="inlineStr">
         <is>
           <t>NIST AI RMF trustworthy-AI characteristic: algorithmic non-discrimination. NOT the same as 'FAIR data'.</t>
         </is>
       </c>
-      <c r="D73" s="13" t="inlineStr">
+      <c r="D73" s="20" t="inlineStr">
         <is>
           <t>NIST-AI-RMF</t>
         </is>
       </c>
-      <c r="E73" s="13" t="n"/>
-      <c r="F73" s="13" t="n"/>
+      <c r="E73" s="20" t="inlineStr"/>
+      <c r="F73" s="20" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="13" t="inlineStr">
+      <c r="A74" s="20" t="inlineStr">
         <is>
           <t>Maturity Level</t>
         </is>
       </c>
-      <c r="B74" s="13" t="inlineStr">
+      <c r="B74" s="20" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="C74" s="13" t="n"/>
-      <c r="D74" s="13" t="n"/>
-      <c r="E74" s="13" t="n"/>
-      <c r="F74" s="13" t="n"/>
+      <c r="C74" s="20" t="inlineStr"/>
+      <c r="D74" s="20" t="inlineStr"/>
+      <c r="E74" s="20" t="inlineStr"/>
+      <c r="F74" s="20" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="13" t="inlineStr">
+      <c r="A75" s="20" t="inlineStr">
         <is>
           <t>Maturity Level</t>
         </is>
       </c>
-      <c r="B75" s="13" t="inlineStr">
+      <c r="B75" s="20" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="C75" s="13" t="n"/>
-      <c r="D75" s="13" t="n"/>
-      <c r="E75" s="13" t="n"/>
-      <c r="F75" s="13" t="n"/>
+      <c r="C75" s="20" t="inlineStr"/>
+      <c r="D75" s="20" t="inlineStr"/>
+      <c r="E75" s="20" t="inlineStr"/>
+      <c r="F75" s="20" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="13" t="inlineStr">
+      <c r="A76" s="20" t="inlineStr">
         <is>
           <t>Maturity Level</t>
         </is>
       </c>
-      <c r="B76" s="13" t="inlineStr">
+      <c r="B76" s="20" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="C76" s="13" t="n"/>
-      <c r="D76" s="13" t="n"/>
-      <c r="E76" s="13" t="n"/>
-      <c r="F76" s="13" t="n"/>
+      <c r="C76" s="20" t="inlineStr"/>
+      <c r="D76" s="20" t="inlineStr"/>
+      <c r="E76" s="20" t="inlineStr"/>
+      <c r="F76" s="20" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="13" t="inlineStr">
+      <c r="A77" s="20" t="inlineStr">
         <is>
           <t>Maturity Level</t>
         </is>
       </c>
-      <c r="B77" s="13" t="inlineStr">
+      <c r="B77" s="20" t="inlineStr">
         <is>
           <t>Deprecated</t>
         </is>
       </c>
-      <c r="C77" s="13" t="n"/>
-      <c r="D77" s="13" t="n"/>
-      <c r="E77" s="13" t="n"/>
-      <c r="F77" s="13" t="n"/>
+      <c r="C77" s="20" t="inlineStr"/>
+      <c r="D77" s="20" t="inlineStr"/>
+      <c r="E77" s="20" t="inlineStr"/>
+      <c r="F77" s="20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5933,145 +5843,145 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="56" customWidth="1" min="4" max="4"/>
-    <col width="90" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" style="17" min="1" max="1"/>
+    <col width="40" customWidth="1" style="17" min="2" max="2"/>
+    <col width="10" customWidth="1" style="17" min="3" max="3"/>
+    <col width="56" customWidth="1" style="17" min="4" max="4"/>
+    <col width="90" customWidth="1" style="17" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>Standard ID</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="19" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="19" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="19" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="19" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="25.5" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="20" t="inlineStr">
         <is>
           <t>EDAM</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t>EDAM ontology (Data management branch)</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="20" t="inlineStr">
         <is>
           <t>current</t>
         </is>
       </c>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="D2" s="20" t="inlineStr">
         <is>
           <t>http://edamontology.org/topic_3071</t>
         </is>
       </c>
-      <c r="E2" s="13" t="inlineStr">
+      <c r="E2" s="20" t="inlineStr">
         <is>
           <t>Primary controlled vocabulary. Open OWL ontology with permanent per-term URIs. Browse: https://www.ebi.ac.uk/ols4/ontologies/edam - Download: http://edamontology.org/EDAM.owl</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="76.5" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>NIST-AI-RMF</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="20" t="inlineStr">
         <is>
           <t>NIST AI Risk Management Framework</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="20" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="20" t="inlineStr">
         <is>
           <t>https://nvlpubs.nist.gov/nistpubs/ai/NIST.AI.100-1.pdf</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" s="20" t="inlineStr">
         <is>
           <t>Optional secondary axis: the seven trustworthy-AI characteristics. Document-based, so individual characteristics have no per-term URIs. WARNING: NIST's 'Fair (harmful bias managed)' concerns algorithmic non-discrimination and is UNRELATED to EDAM's 'FAIR data' (Findable / Accessible / Interoperable / Reusable data principles) despite sharing the word - do not conflate the two. Also defines an AI lifecycle with named stages (plan, collect/process, build, verify, deploy, operate) -- cited here as e.g. "AI lifecycle stage: Deploy", distinct from the seven trustworthy-AI characteristics.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>ACM-CCS</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>ACM Computing Classification System (CCS 2012)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
         <is>
           <t>https://dl.acm.org/ccs</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="0" t="inlineStr">
         <is>
           <t>Cited by category path text (e.g. "Computer systems organization~Architectures"), not a numeric ID a human needs to look up -- confirmed against real paper citations. General computing/software-engineering taxonomy, not agentic-AI-specific -- predates MCP, agent frameworks, and tool-calling entirely, so it backs general CS terms (Architecture, Security, Evaluation, Retrieval) but not agent-specific ones (MCP, Hooks, Skills, Orchestration, ...). Path spellings below are from established domain knowledge, not a live verified fetch (dl.acm.org blocked automated access) -- worth spot-checking in a browser before treating as fully authoritative.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t>Schema.org</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>Schema.org (CreativeWork hierarchy)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>current</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="0" t="inlineStr">
         <is>
           <t>https://schema.org/CreativeWork</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="0" t="inlineStr">
         <is>
           <t>Universal web-metadata vocabulary. Exact-type matches applied directly (e.g. APIReference, BlogPosting, ScholarlyArticle, SoftwareSourceCode, Dataset). For highly specific AI-radar terms with no exact schema.org type, the broader parent type is applied instead (e.g. several terms map to TechArticle) -- this is schema.org's own intended usage pattern (broad type + a custom category property), not a forced fit, but it means several distinct Resource Type terms intentionally share one Ontology ID here, unlike EDAM/ACM-CCS/NIST-AI-RMF where each backed term has its own distinct match.</t>
         </is>

--- a/data/VANTAGE-Technology-Radar.xlsx
+++ b/data/VANTAGE-Technology-Radar.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1515" yWindow="1515" windowWidth="24705" windowHeight="12345" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Knowledgebase" sheetId="1" state="visible" r:id="rId1"/>
@@ -14,70 +15,37 @@
     <sheet name="Standards" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm"/>
-    <numFmt numFmtId="166" formatCode="m\-d\-yyyy"/>
-    <numFmt numFmtId="167" formatCode="yyyy\-m"/>
-    <numFmt numFmtId="168" formatCode="mmmm\ d\,\ yyyy"/>
-    <numFmt numFmtId="169" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="3">
     <font>
-      <name val="Arial"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <color theme="1"/>
-      <sz val="10"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <color rgb="FF0000FF"/>
-      <sz val="10"/>
+      <color rgb="FF0563C1"/>
       <u val="single"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="FF0000FF"/>
-      <sz val="10"/>
-      <u val="single"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color theme="10"/>
-      <sz val="10"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor theme="0"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -89,40 +57,32 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="16">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFE599"/>
-          <bgColor rgb="FFFFE599"/>
+          <fgColor rgb="FFD9D2E9"/>
+          <bgColor rgb="FFD9D2E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB7E1CD"/>
+          <bgColor rgb="FFB7E1CD"/>
         </patternFill>
       </fill>
     </dxf>
@@ -137,40 +97,8 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFB7E1CD"/>
-          <bgColor rgb="FFB7E1CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFA4C2F4"/>
-          <bgColor rgb="FFA4C2F4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB7E1CD"/>
-          <bgColor rgb="FFB7E1CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDD7E6B"/>
-          <bgColor rgb="FFDD7E6B"/>
+          <fgColor rgb="FFB4A7D6"/>
+          <bgColor rgb="FFB4A7D6"/>
         </patternFill>
       </fill>
     </dxf>
@@ -185,85 +113,93 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFA4C2F4"/>
-          <bgColor rgb="FFA4C2F4"/>
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFB7E1CD"/>
-          <bgColor rgb="FFB7E1CD"/>
+          <fgColor rgb="FFD9EAD3"/>
+          <bgColor rgb="FFD9EAD3"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFE599"/>
-          <bgColor rgb="FFFFE599"/>
+          <fgColor rgb="FFEA9999"/>
+          <bgColor rgb="FFEA9999"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFB7E1CD"/>
-          <bgColor rgb="FFB7E1CD"/>
+          <fgColor rgb="FFC9DAF8"/>
+          <bgColor rgb="FFC9DAF8"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
+          <fgColor rgb="FFD0E0E3"/>
+          <bgColor rgb="FFD0E0E3"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFE599"/>
-          <bgColor rgb="FFFFE599"/>
+          <fgColor rgb="FFFCE5CD"/>
+          <bgColor rgb="FFFCE5CD"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFA4C2F4"/>
-          <bgColor rgb="FFA4C2F4"/>
+          <fgColor rgb="FFCFE2F3"/>
+          <bgColor rgb="FFCFE2F3"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFB7E1CD"/>
-          <bgColor rgb="FFB7E1CD"/>
+          <fgColor rgb="FFEAD1DC"/>
+          <bgColor rgb="FFEAD1DC"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFB7E1CD"/>
-          <bgColor rgb="FFB7E1CD"/>
+          <fgColor rgb="FFB6D7A8"/>
+          <bgColor rgb="FFB6D7A8"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
+          <fgColor rgb="FFE06666"/>
+          <bgColor rgb="FFE06666"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDD7E6B"/>
+          <bgColor rgb="FFDD7E6B"/>
         </patternFill>
       </fill>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -336,56 +272,114 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Sheets">
+    <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="000000"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4285F4"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="EA4335"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="FBBC04"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="34A853"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="FF6D01"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="46BDC6"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Sheets">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -397,131 +391,160 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -534,24 +557,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q43"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <dimension ref="A1:Q33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="27.42578125" customWidth="1" min="2" max="2"/>
-    <col width="16.28515625" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="18.5703125" customWidth="1" min="8" max="8"/>
-    <col width="37.85546875" customWidth="1" min="9" max="9"/>
-    <col width="57.85546875" customWidth="1" min="10" max="10"/>
-    <col width="44.140625" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="43" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="23" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
@@ -581,7 +613,7 @@
           <t>Verified By</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Added/Edited By</t>
         </is>
@@ -598,40 +630,40 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Publication/Version Date</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Relevance to Research Cyberinfrastructure</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Maturity Level</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Notes / Key Takeaways</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Publication Date</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Discovery Date</t>
         </is>
@@ -643,7 +675,7 @@
           <t>022e4e1c</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>VS Code Copilot Agents Overview</t>
         </is>
@@ -653,7 +685,7 @@
           <t>https://code.visualstudio.com/docs/copilot/agents/overview</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
@@ -661,7 +693,7 @@
       <c r="E2" s="3" t="n">
         <v>46157</v>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
@@ -671,44 +703,43 @@
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H2" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="H2" s="3" t="n">
+        <v>46157</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t>Hooks; Skills; MCP; Agent frameworks</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t>Architecture; Implementation; Deployment</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Hooks;Skills;MCP;Agent frameworks</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Architecture;Implementation;Deployment</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>IDE integration for agentic workflows</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>Canonical reference for VS Code agent capabilities.</t>
         </is>
       </c>
-      <c r="P2" s="11" t="n">
-        <v>46162</v>
-      </c>
-      <c r="Q2" s="11" t="n">
+      <c r="Q2" s="3" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -718,17 +749,17 @@
           <t>2e9b6b2d</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Data Director</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>https://docs.google.com/document/d/1mu1_U1cWqn1aP3vtW83JnX5-aGhzM49K/edit</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Microsoft, RDA</t>
         </is>
@@ -736,7 +767,7 @@
       <c r="E3" s="3" t="n">
         <v>46168</v>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
@@ -746,41 +777,40 @@
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="H3" s="3" t="n">
         <v>46168</v>
       </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>v0.1 DRAFT</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Specification</t>
         </is>
       </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>FAIR data; Workflow Agents</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Workflows; Implementation</t>
-        </is>
-      </c>
-      <c r="M3" s="1" t="inlineStr">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>FAIR data;Workflow Agents</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Workflows;Implementation</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>Makes data outputs FAIR at the point of publication</t>
         </is>
       </c>
-      <c r="N3" s="1" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="O3" s="1" t="n"/>
-      <c r="Q3" s="11" t="n">
+      <c r="Q3" s="3" t="n">
         <v>46168</v>
       </c>
     </row>
@@ -790,63 +820,57 @@
           <t>161f1860</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Agentic AI Tool</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>https://docs.github.com/en/copilot/agents</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="4" t="n"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H4" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="I4" s="1" t="n"/>
-      <c r="J4" s="1" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>Hooks; Skills; API Integration</t>
-        </is>
-      </c>
-      <c r="L4" s="1" t="inlineStr">
-        <is>
-          <t>Architecture; Governance; Security</t>
-        </is>
-      </c>
-      <c r="M4" s="1" t="inlineStr">
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Hooks;Skills;API Integration</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Architecture;Governance;Security</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>Relevant for CI/CD and code-review automation</t>
         </is>
       </c>
-      <c r="N4" s="1" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="O4" s="1" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>Strong alignment with developer workflows.</t>
         </is>
       </c>
-      <c r="Q4" s="11" t="n">
+      <c r="Q4" s="3" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -856,63 +880,57 @@
           <t>abbd844c</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>GitHub MCP Documentation</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>https://github.com/modelcontextprotocol</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>GitHub/OpenAI</t>
         </is>
       </c>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="4" t="n"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H5" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="I5" s="1" t="n"/>
-      <c r="J5" s="1" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>API Reference</t>
         </is>
       </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>MCP; Tools; Server Integration</t>
-        </is>
-      </c>
-      <c r="L5" s="1" t="inlineStr">
-        <is>
-          <t>Architecture; Implementation</t>
-        </is>
-      </c>
-      <c r="M5" s="1" t="inlineStr">
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>MCP;Tools;Server Integration</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Architecture;Implementation</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>Key for interoperable agent tools</t>
         </is>
       </c>
-      <c r="N5" s="1" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="O5" s="1" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>Fast-moving ecosystem.</t>
         </is>
       </c>
-      <c r="Q5" s="11" t="n">
+      <c r="Q5" s="3" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -922,63 +940,57 @@
           <t>b71baded</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>OpenAI MCP Specification</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>https://spec.modelcontextprotocol.io</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="4" t="n"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H6" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="I6" s="1" t="n"/>
-      <c r="J6" s="1" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Specification</t>
         </is>
       </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>MCP; Tools; Server Patterns</t>
-        </is>
-      </c>
-      <c r="L6" s="1" t="inlineStr">
-        <is>
-          <t>Architecture; Governance</t>
-        </is>
-      </c>
-      <c r="M6" s="1" t="inlineStr">
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>MCP;Tools;Server Patterns</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Architecture;Governance</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>Critical for cross-platform agent interoperability</t>
         </is>
       </c>
-      <c r="N6" s="1" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="O6" s="1" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>Becoming a de facto standard.</t>
         </is>
       </c>
-      <c r="Q6" s="11" t="n">
+      <c r="Q6" s="3" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -988,7 +1000,7 @@
           <t>2b23adbb</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Anthropic Model Context Protocol</t>
         </is>
@@ -998,7 +1010,7 @@
           <t xml:space="preserve">https://modelcontextprotocol.io/specification/2025-11-25 </t>
         </is>
       </c>
-      <c r="D7" s="1" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Anthropic</t>
         </is>
@@ -1006,7 +1018,7 @@
       <c r="E7" s="3" t="n">
         <v>46182</v>
       </c>
-      <c r="F7" s="1" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
@@ -1016,44 +1028,43 @@
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H7" s="4" t="n">
-        <v>45962</v>
-      </c>
-      <c r="I7" s="7" t="n"/>
-      <c r="J7" s="1" t="inlineStr">
+      <c r="H7" s="3" t="n">
+        <v>46182</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>45972</v>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>MCP; Agent Patterns</t>
-        </is>
-      </c>
-      <c r="L7" s="1" t="inlineStr">
-        <is>
-          <t>Architecture; Governance</t>
-        </is>
-      </c>
-      <c r="M7" s="1" t="inlineStr">
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>MCP;Agent Patterns</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Architecture;Governance</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>Integration between LLM applications and external data sources and tools</t>
         </is>
       </c>
-      <c r="N7" s="1" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="O7" s="1" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>Strong safety emphasis.</t>
         </is>
       </c>
-      <c r="P7" s="11" t="n">
-        <v>45972</v>
-      </c>
-      <c r="Q7" s="11" t="n">
+      <c r="Q7" s="3" t="n">
         <v>45962</v>
       </c>
     </row>
@@ -1063,7 +1074,7 @@
           <t>d6d28dfa</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Kaggle Prototype to Production Whitepaper</t>
         </is>
@@ -1073,7 +1084,7 @@
           <t>https://www.kaggle.com/whitepaper-prototype-to-production</t>
         </is>
       </c>
-      <c r="D8" s="1" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Kaggle/Google</t>
         </is>
@@ -1081,7 +1092,7 @@
       <c r="E8" s="3" t="n">
         <v>46157</v>
       </c>
-      <c r="F8" s="1" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
@@ -1091,45 +1102,45 @@
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H8" s="4" t="n">
-        <v>45975</v>
-      </c>
-      <c r="I8" s="1" t="inlineStr">
+      <c r="H8" s="3" t="n">
+        <v>46157</v>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="J8" s="1" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Whitepaper</t>
         </is>
       </c>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>Deployment patterns; Workflow Automation</t>
-        </is>
-      </c>
-      <c r="L8" s="1" t="inlineStr">
-        <is>
-          <t>Implementation; Security; Deployment</t>
-        </is>
-      </c>
-      <c r="M8" s="1" t="inlineStr">
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Deployment patterns;Workflow Automation</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Implementation;Security;Deployment</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>Helps teams move prototypes to production</t>
         </is>
       </c>
-      <c r="N8" s="1" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="O8" s="1" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>Technical guide to the operational life cycle of AI agents, focusing on deployment &amp; security</t>
         </is>
       </c>
-      <c r="Q8" s="11" t="n">
+      <c r="Q8" s="3" t="n">
         <v>45975</v>
       </c>
     </row>
@@ -1139,63 +1150,57 @@
           <t>bfda8877</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Google Vertex AI Agents Overview</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>https://cloud.google.com/vertex-ai/docs/agents</t>
         </is>
       </c>
-      <c r="D9" s="1" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="4" t="n"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H9" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="I9" s="1" t="n"/>
-      <c r="J9" s="1" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>Agent frameworks; Orchestration</t>
-        </is>
-      </c>
-      <c r="L9" s="1" t="inlineStr">
-        <is>
-          <t>Architecture; Deployment</t>
-        </is>
-      </c>
-      <c r="M9" s="1" t="inlineStr">
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Agent frameworks;Orchestration</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Architecture;Deployment</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>Useful for cloud-based scientific workflows</t>
         </is>
       </c>
-      <c r="N9" s="1" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="O9" s="1" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>Strong enterprise alignment.</t>
         </is>
       </c>
-      <c r="Q9" s="11" t="n">
+      <c r="Q9" s="3" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -1205,63 +1210,57 @@
           <t>f488464f</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>HuggingFace Agents Documentation</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>https://huggingface.co/docs/agents</t>
         </is>
       </c>
-      <c r="D10" s="1" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>HuggingFace</t>
         </is>
       </c>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="4" t="n"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H10" s="4" t="n">
-        <v>46082</v>
-      </c>
-      <c r="I10" s="1" t="n"/>
-      <c r="J10" s="1" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>Tools; Skills; Model Integration</t>
-        </is>
-      </c>
-      <c r="L10" s="1" t="inlineStr">
-        <is>
-          <t>Architecture; Implementation</t>
-        </is>
-      </c>
-      <c r="M10" s="1" t="inlineStr">
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Tools;Skills;Model Integration</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Architecture;Implementation</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>Useful for open-source agent experimentation</t>
         </is>
       </c>
-      <c r="N10" s="1" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="O10" s="1" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>Rapidly evolving.</t>
         </is>
       </c>
-      <c r="Q10" s="11" t="n">
+      <c r="Q10" s="3" t="n">
         <v>46082</v>
       </c>
     </row>
@@ -1271,63 +1270,57 @@
           <t>dbe3741e</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>LangChain Agents Overview</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>https://python.langchain.com/docs/modules/agents</t>
         </is>
       </c>
-      <c r="D11" s="1" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>LangChain</t>
         </is>
       </c>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="4" t="n"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H11" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="I11" s="1" t="n"/>
-      <c r="J11" s="1" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>Tools; Skills; Multi-Agent Patterns</t>
-        </is>
-      </c>
-      <c r="L11" s="1" t="inlineStr">
-        <is>
-          <t>Architecture; Implementation</t>
-        </is>
-      </c>
-      <c r="M11" s="1" t="inlineStr">
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Tools;Skills;Multi-Agent Patterns</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Architecture;Implementation</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>Relevant for workflow prototyping</t>
         </is>
       </c>
-      <c r="N11" s="1" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="O11" s="1" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>Widely used in research.</t>
         </is>
       </c>
-      <c r="Q11" s="11" t="n">
+      <c r="Q11" s="3" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -1337,63 +1330,57 @@
           <t>ddd42289</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>LlamaIndex Agents</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>https://docs.llamaindex.ai/en/stable/agent/</t>
         </is>
       </c>
-      <c r="D12" s="1" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>LlamaIndex</t>
         </is>
       </c>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="4" t="n"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H12" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="I12" s="1" t="n"/>
-      <c r="J12" s="1" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>Tools; Skills; Retrieval Agents</t>
-        </is>
-      </c>
-      <c r="L12" s="1" t="inlineStr">
-        <is>
-          <t>Architecture; Governance</t>
-        </is>
-      </c>
-      <c r="M12" s="1" t="inlineStr">
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Tools;Skills;Retrieval Agents</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Architecture;Governance</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>Useful for data-rich research platforms</t>
         </is>
       </c>
-      <c r="N12" s="1" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="O12" s="1" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>Strong retrieval-centric design.</t>
         </is>
       </c>
-      <c r="Q12" s="11" t="n">
+      <c r="Q12" s="3" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -1403,25 +1390,25 @@
           <t>c7e95f61</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Dagster Automation/Agent Patterns</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>https://docs.dagster.io/getting-started/ai-tools</t>
         </is>
       </c>
-      <c r="D13" s="1" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Dagster Labs</t>
         </is>
       </c>
-      <c r="E13" s="14" t="n">
+      <c r="E13" s="3" t="n">
         <v>46082</v>
       </c>
-      <c r="F13" s="1" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
@@ -1431,45 +1418,45 @@
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="H13" s="3" t="n">
         <v>46082</v>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>1.3.15</t>
         </is>
       </c>
-      <c r="J13" s="1" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>Workflow Automation; Orchestration</t>
-        </is>
-      </c>
-      <c r="L13" s="1" t="inlineStr">
-        <is>
-          <t>Architecture; Deployment</t>
-        </is>
-      </c>
-      <c r="M13" s="1" t="inlineStr">
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Workflow Automation;Orchestration</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Architecture;Deployment</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>Relevant for scientific pipelines</t>
         </is>
       </c>
-      <c r="N13" s="1" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="O13" s="1" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>Strong reproducibility focus.</t>
         </is>
       </c>
-      <c r="Q13" s="11" t="n">
+      <c r="Q13" s="3" t="n">
         <v>46082</v>
       </c>
     </row>
@@ -1479,63 +1466,57 @@
           <t>73426de0</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Prefect Automations/Agents</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>https://docs.prefect.io/latest/concepts/automations/</t>
         </is>
       </c>
-      <c r="D14" s="1" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Prefect</t>
         </is>
       </c>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="4" t="n"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Paty Buendia</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>46082</v>
-      </c>
-      <c r="I14" s="1" t="n"/>
-      <c r="J14" s="1" t="inlineStr">
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>Workflow Agents; Triggers</t>
-        </is>
-      </c>
-      <c r="L14" s="1" t="inlineStr">
-        <is>
-          <t>Implementation; Deployment</t>
-        </is>
-      </c>
-      <c r="M14" s="1" t="inlineStr">
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Workflow Agents;Triggers</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Implementation;Deployment</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>Useful for data processing pipelines</t>
         </is>
       </c>
-      <c r="N14" s="1" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="O14" s="1" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>Good hybrid cloud/HPC support.</t>
         </is>
       </c>
-      <c r="Q14" s="11" t="n">
+      <c r="Q14" s="3" t="n">
         <v>46082</v>
       </c>
     </row>
@@ -1545,63 +1526,57 @@
           <t>3294a13f</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Jupyter AI</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>https://jupyter-ai.readthedocs.io</t>
         </is>
       </c>
-      <c r="D15" s="1" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Project Jupyter</t>
         </is>
       </c>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="4" t="n"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Paty Buendia</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="I15" s="1" t="n"/>
-      <c r="J15" s="1" t="inlineStr">
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>Notebook Agents; Workflow Automation</t>
-        </is>
-      </c>
-      <c r="L15" s="1" t="inlineStr">
-        <is>
-          <t>Implementation; Data governance</t>
-        </is>
-      </c>
-      <c r="M15" s="1" t="inlineStr">
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Notebook Agents;Workflow Automation</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Implementation;Data governance</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>Relevant for research notebooks</t>
         </is>
       </c>
-      <c r="N15" s="1" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="O15" s="1" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>Strong alignment with scientific workflows.</t>
         </is>
       </c>
-      <c r="Q15" s="11" t="n">
+      <c r="Q15" s="3" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -1611,63 +1586,57 @@
           <t>f51ea180</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Anthropic Tools API</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>https://docs.anthropic.com/en/docs/tools</t>
         </is>
       </c>
-      <c r="D16" s="1" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Anthropic</t>
         </is>
       </c>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="4" t="n"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Paty Buendia</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="I16" s="1" t="n"/>
-      <c r="J16" s="1" t="inlineStr">
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>API Reference</t>
         </is>
       </c>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>Tools; Skills</t>
-        </is>
-      </c>
-      <c r="L16" s="1" t="inlineStr">
-        <is>
-          <t>Architecture; Security</t>
-        </is>
-      </c>
-      <c r="M16" s="1" t="inlineStr">
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Tools;Skills</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Architecture;Security</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>Useful for safe tool-calling agents</t>
         </is>
       </c>
-      <c r="N16" s="1" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="O16" s="1" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>Strong safety posture.</t>
         </is>
       </c>
-      <c r="Q16" s="11" t="n">
+      <c r="Q16" s="3" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -1677,63 +1646,57 @@
           <t>89f36cc1</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Microsoft Semantic Kernel Agents</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>https://learn.microsoft.com/semantic-kernel/agents</t>
         </is>
       </c>
-      <c r="D17" s="1" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="4" t="n"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Paty Buendia</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="I17" s="1" t="n"/>
-      <c r="J17" s="1" t="inlineStr">
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>Skills; Tools; Orchestration</t>
-        </is>
-      </c>
-      <c r="L17" s="1" t="inlineStr">
-        <is>
-          <t>Architecture; Implementation</t>
-        </is>
-      </c>
-      <c r="M17" s="1" t="inlineStr">
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Skills;Tools;Orchestration</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Architecture;Implementation</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t>Useful for enterprise-grade agent workflows</t>
         </is>
       </c>
-      <c r="N17" s="1" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="O17" s="1" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>Strong .NET + Python support.</t>
         </is>
       </c>
-      <c r="Q17" s="11" t="n">
+      <c r="Q17" s="3" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -1743,63 +1706,57 @@
           <t>4ccfda21</t>
         </is>
       </c>
-      <c r="B18" s="1" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>HuggingFace Inference Endpoints</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>https://huggingface.co/inference-endpoints</t>
         </is>
       </c>
-      <c r="D18" s="1" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>HuggingFace</t>
         </is>
       </c>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="4" t="n"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Paty Buendia</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>46082</v>
-      </c>
-      <c r="I18" s="1" t="n"/>
-      <c r="J18" s="1" t="inlineStr">
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>Model Integration; Tool-Ready Endpoints</t>
-        </is>
-      </c>
-      <c r="L18" s="1" t="inlineStr">
-        <is>
-          <t>Architecture; Deployment</t>
-        </is>
-      </c>
-      <c r="M18" s="1" t="inlineStr">
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Model Integration;Tool-Ready Endpoints</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Architecture;Deployment</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t>Useful for hosted inference in research</t>
         </is>
       </c>
-      <c r="N18" s="1" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="O18" s="1" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>Good for reproducibility.</t>
         </is>
       </c>
-      <c r="Q18" s="11" t="n">
+      <c r="Q18" s="3" t="n">
         <v>46082</v>
       </c>
     </row>
@@ -1809,63 +1766,57 @@
           <t>2e24be4d</t>
         </is>
       </c>
-      <c r="B19" s="1" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>OpenAI Evaluations (Evals)</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>https://platform.openai.com/docs/guides/evals</t>
         </is>
       </c>
-      <c r="D19" s="1" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="4" t="n"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Paty Buendia</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="I19" s="1" t="n"/>
-      <c r="J19" s="1" t="inlineStr">
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>Evaluation / testing; Safety / guardrails</t>
-        </is>
-      </c>
-      <c r="L19" s="1" t="inlineStr">
-        <is>
-          <t>Security; Governance</t>
-        </is>
-      </c>
-      <c r="M19" s="1" t="inlineStr">
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Evaluation / testing;Safety / guardrails</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Security;Governance</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t>Relevant for agent safety in research platforms</t>
         </is>
       </c>
-      <c r="N19" s="1" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="O19" s="1" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>Useful for risk assessment.</t>
         </is>
       </c>
-      <c r="Q19" s="11" t="n">
+      <c r="Q19" s="3" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -1875,63 +1826,57 @@
           <t>6b9e7398</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Anthropic Safety Guidelines</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>https://docs.anthropic.com/en/docs/safety</t>
         </is>
       </c>
-      <c r="D20" s="1" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Anthropic</t>
         </is>
       </c>
-      <c r="E20" s="3" t="n"/>
-      <c r="F20" s="4" t="n"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Paty Buendia</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="I20" s="1" t="n"/>
-      <c r="J20" s="1" t="inlineStr">
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>Safety / guardrails; Safe Tool Use</t>
-        </is>
-      </c>
-      <c r="L20" s="1" t="inlineStr">
-        <is>
-          <t>Governance; Security</t>
-        </is>
-      </c>
-      <c r="M20" s="1" t="inlineStr">
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Safety / guardrails;Safe Tool Use</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Governance;Security</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>Useful for research governance teams</t>
         </is>
       </c>
-      <c r="N20" s="1" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="O20" s="1" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>Strong alignment with institutional risk controls.</t>
         </is>
       </c>
-      <c r="Q20" s="11" t="n">
+      <c r="Q20" s="3" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -1941,63 +1886,57 @@
           <t>69804f39</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Microsoft Responsible AI Standard</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>https://www.microsoft.com/ai/responsible-ai</t>
         </is>
       </c>
-      <c r="D21" s="1" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="E21" s="3" t="n"/>
-      <c r="F21" s="8" t="n"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Paty Buendia</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="n">
-        <v>45992</v>
-      </c>
-      <c r="I21" s="1" t="n"/>
-      <c r="J21" s="1" t="inlineStr">
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>Governance Guidance</t>
         </is>
       </c>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>Safety / guardrails; Governance; Risk Controls</t>
-        </is>
-      </c>
-      <c r="L21" s="1" t="inlineStr">
-        <is>
-          <t>Data governance; Security</t>
-        </is>
-      </c>
-      <c r="M21" s="1" t="inlineStr">
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Safety / guardrails;Governance;Risk Controls</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Data governance;Security</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>Relevant for institutional AI governance</t>
         </is>
       </c>
-      <c r="N21" s="1" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="O21" s="1" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>Widely adopted governance framework.</t>
         </is>
       </c>
-      <c r="Q21" s="11" t="n">
+      <c r="Q21" s="3" t="n">
         <v>45992</v>
       </c>
     </row>
@@ -2007,62 +1946,57 @@
           <t>3758624e</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>vLLM Documentation</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>https://docs.vllm.ai</t>
         </is>
       </c>
-      <c r="D22" s="1" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>vLLM Project Team</t>
         </is>
       </c>
-      <c r="E22" s="3" t="n"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Paty Buendia</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="I22" s="1" t="n"/>
-      <c r="J22" s="1" t="inlineStr">
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>Inference Framework</t>
         </is>
       </c>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>Deployment patterns; Tools</t>
-        </is>
-      </c>
-      <c r="L22" s="1" t="inlineStr">
-        <is>
-          <t>Self‑hosted AI; Architecture; Implementation; Deployment</t>
-        </is>
-      </c>
-      <c r="M22" s="1" t="inlineStr">
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Deployment patterns;Tools</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Self‑hosted AI;Architecture;Implementation;Deployment</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>High (Industry-standard VPC runtime engine)</t>
         </is>
       </c>
-      <c r="N22" s="1" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="O22" s="1" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>Essential for secure TLAs via PagedAttention and FP8/AWQ optimization. Capabilities: Parallel sampling &amp; tool-calling.</t>
         </is>
       </c>
-      <c r="Q22" s="11" t="n">
+      <c r="Q22" s="3" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -2072,62 +2006,57 @@
           <t>8a50b5eb</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Ollama Documentation</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>https://github.com/ollama/ollama</t>
         </is>
       </c>
-      <c r="D23" s="1" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Ollama Community</t>
         </is>
       </c>
-      <c r="E23" s="3" t="n"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Paty Buendia</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="I23" s="1" t="n"/>
-      <c r="J23" s="1" t="inlineStr">
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>Local Application Sandbox</t>
         </is>
       </c>
-      <c r="K23" s="1" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>Deployment patterns</t>
         </is>
       </c>
-      <c r="L23" s="1" t="inlineStr">
-        <is>
-          <t>Self‑hosted AI; Implementation; Deployment</t>
-        </is>
-      </c>
-      <c r="M23" s="1" t="inlineStr">
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Self‑hosted AI;Implementation;Deployment</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>Medium-High (Local workstation co-pilot)</t>
         </is>
       </c>
-      <c r="N23" s="1" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="O23" s="1" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>Eliminates network dependency errors by cleanly bundling open model weights. Capabilities: Local embedding &amp; zero-config tools.</t>
         </is>
       </c>
-      <c r="Q23" s="11" t="n">
+      <c r="Q23" s="3" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -2137,7 +2066,7 @@
           <t>763797cd</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t xml:space="preserve">Llama.cpp </t>
         </is>
@@ -2147,57 +2076,52 @@
           <t>https://github.com/ggerganov/llama.cpp</t>
         </is>
       </c>
-      <c r="D24" s="1" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Georgi Gerganov</t>
         </is>
       </c>
-      <c r="E24" s="3" t="n"/>
-      <c r="F24" s="1" t="n"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Paty Buendia</t>
-        </is>
-      </c>
-      <c r="H24" s="9" t="n">
-        <v>46162</v>
-      </c>
-      <c r="I24" s="1" t="inlineStr">
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>b9253</t>
         </is>
       </c>
-      <c r="J24" s="1" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>Github Code Repository</t>
         </is>
       </c>
-      <c r="K24" s="1" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>Deployment patterns</t>
         </is>
       </c>
-      <c r="L24" s="1" t="inlineStr">
-        <is>
-          <t>Self‑hosted AI; Architecture; Implementation; Deployment</t>
-        </is>
-      </c>
-      <c r="M24" s="1" t="inlineStr">
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Self‑hosted AI;Architecture;Implementation;Deployment</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>High (Enables reasoning on variable local hardware)</t>
         </is>
       </c>
-      <c r="N24" s="1" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="O24" s="1" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>Grammar constraints ensure localized agentic pipelines always return valid JSON/code. Capabilities: Grammar-based constrained sampling.</t>
         </is>
       </c>
-      <c r="Q24" s="11" t="n">
+      <c r="Q24" s="3" t="n">
         <v>46162</v>
       </c>
     </row>
@@ -2207,62 +2131,57 @@
           <t>2d2470f7</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Open WebUI Documentation</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>https://docs.openwebui.com</t>
         </is>
       </c>
-      <c r="D25" s="1" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Open WebUI Core Team</t>
         </is>
       </c>
-      <c r="E25" s="3" t="n"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Paty Buendia</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="I25" s="1" t="n"/>
-      <c r="J25" s="1" t="inlineStr">
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>Enterprise Control Interface</t>
         </is>
       </c>
-      <c r="K25" s="1" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>Retrieval</t>
         </is>
       </c>
-      <c r="L25" s="1" t="inlineStr">
-        <is>
-          <t>Self‑hosted AI; Implementation; Deployment</t>
-        </is>
-      </c>
-      <c r="M25" s="1" t="inlineStr">
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Self‑hosted AI;Implementation;Deployment</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t>High (Enterprise-grade firewall interface)</t>
         </is>
       </c>
-      <c r="N25" s="1" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="O25" s="1" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>Solves local file parsing/RAG bottlenecks entirely within secure client networks. Capabilities: Local RAG pipelines &amp; offline functions.</t>
         </is>
       </c>
-      <c r="Q25" s="11" t="n">
+      <c r="Q25" s="3" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -2272,62 +2191,57 @@
           <t>eb79015c</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>NVIDIA NIM Air-Gap Deployment Guide</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>https://docs.nvidia.com/nim/large-language-models/latest/deploy-air-gap.html</t>
         </is>
       </c>
-      <c r="D26" s="1" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>NVIDIA</t>
         </is>
       </c>
-      <c r="E26" s="3" t="n"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Paty Buendia</t>
-        </is>
-      </c>
-      <c r="H26" s="1" t="n">
-        <v>2026</v>
-      </c>
-      <c r="I26" s="1" t="n"/>
-      <c r="J26" s="1" t="inlineStr">
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>Reference Architecture</t>
         </is>
       </c>
-      <c r="K26" s="1" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>Deployment patterns</t>
         </is>
       </c>
-      <c r="L26" s="1" t="inlineStr">
-        <is>
-          <t>Self‑hosted AI; Compute Infrastructure; Implementation; Network Isolation; Infrastructure Security</t>
-        </is>
-      </c>
-      <c r="M26" s="1" t="inlineStr">
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Self‑hosted AI;Compute Infrastructure;Implementation;Network Isolation;Infrastructure Security</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
         <is>
           <t>Critical (Standardizes secure distribution of optimized weights)</t>
         </is>
       </c>
-      <c r="N26" s="1" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="O26" s="1" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>Outlines the exact connected-to-disconnected asset transfer workflow for enterprise GPUs. Capabilities: Tensor-parallel caching &amp; optimized tool-calling.</t>
         </is>
       </c>
-      <c r="Q26" s="11" t="n">
+      <c r="Q26" s="3" t="n">
         <v>46150</v>
       </c>
     </row>
@@ -2337,62 +2251,57 @@
           <t>80527de7</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Harbor User Documentation</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>https://goharbor.io/docs/</t>
         </is>
       </c>
-      <c r="D27" s="1" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Cloud Native Computing Foundation (CNCF)</t>
         </is>
       </c>
-      <c r="E27" s="3" t="n"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Paty Buendia</t>
-        </is>
-      </c>
-      <c r="H27" s="1" t="n">
-        <v>2026</v>
-      </c>
-      <c r="I27" s="1" t="n"/>
-      <c r="J27" s="1" t="inlineStr">
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>Container Registry</t>
         </is>
       </c>
-      <c r="K27" s="1" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>Deployment patterns</t>
         </is>
       </c>
-      <c r="L27" s="1" t="inlineStr">
-        <is>
-          <t>Self‑hosted AI; Implementation; Network Isolation; Infrastructure Security; Governance</t>
-        </is>
-      </c>
-      <c r="M27" s="1" t="inlineStr">
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Self‑hosted AI;Implementation;Network Isolation;Infrastructure Security;Governance</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
         <is>
           <t>High (Necessary foundation for secure cluster registries)</t>
         </is>
       </c>
-      <c r="N27" s="1" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="O27" s="1" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>Built-in vulnerability scanning ensures agent images remain clean behind the firewall. Capabilities: Artifact version-locking &amp; immutable tags.</t>
         </is>
       </c>
-      <c r="Q27" s="11" t="n">
+      <c r="Q27" s="3" t="n">
         <v>46150</v>
       </c>
     </row>
@@ -2402,62 +2311,57 @@
           <t>b4b5a468</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>AI Engineering Blueprint for On-Premises RAG Systems</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2604.01395</t>
         </is>
       </c>
-      <c r="D28" s="1" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>arXiv (2604.01395)</t>
         </is>
       </c>
-      <c r="E28" s="3" t="n"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Paty Buendia</t>
-        </is>
-      </c>
-      <c r="H28" s="1" t="n">
-        <v>2026</v>
-      </c>
-      <c r="I28" s="1" t="n"/>
-      <c r="J28" s="1" t="inlineStr">
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
         <is>
           <t>Scientific Literature</t>
         </is>
       </c>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>Deployment patterns; Retrieval</t>
-        </is>
-      </c>
-      <c r="L28" s="1" t="inlineStr">
-        <is>
-          <t>Self‑hosted AI; Infrastructure Security</t>
-        </is>
-      </c>
-      <c r="M28" s="1" t="inlineStr">
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Deployment patterns;Retrieval</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Self‑hosted AI;Infrastructure Security</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
         <is>
           <t>High (Academic/industry validated system design blueprint)</t>
         </is>
       </c>
-      <c r="N28" s="1" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="O28" s="1" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>Moves past simple how-to guides into formal data isolation and local compliance frameworks. Capabilities: End-to-end local reference applications.</t>
         </is>
       </c>
-      <c r="Q28" s="11" t="n">
+      <c r="Q28" s="3" t="n">
         <v>46150</v>
       </c>
     </row>
@@ -2467,7 +2371,7 @@
           <t>0d0a50a7</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>On-Premise vs Cloud: GenAI TCO (2026 Edition)</t>
         </is>
@@ -2477,7 +2381,7 @@
           <t xml:space="preserve">https://lenovopress.lenovo.com/lp2368-on-premise-vs-cloud-generative-ai-total-cost-of-ownership-2026-edition </t>
         </is>
       </c>
-      <c r="D29" s="1" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Lenovo Press</t>
         </is>
@@ -2485,7 +2389,7 @@
       <c r="E29" s="3" t="n">
         <v>46259</v>
       </c>
-      <c r="F29" s="1" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>@pbuendia</t>
         </is>
@@ -2495,45 +2399,45 @@
           <t>@biddyman11</t>
         </is>
       </c>
-      <c r="H29" s="4" t="n">
-        <v>46054</v>
-      </c>
-      <c r="I29" s="1" t="inlineStr">
+      <c r="H29" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="I29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="J29" s="1" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>Whitepaper</t>
         </is>
       </c>
-      <c r="K29" s="1" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>Deployment patterns</t>
         </is>
       </c>
-      <c r="L29" s="1" t="inlineStr">
-        <is>
-          <t>Self‑hosted AI; Architecture; Governance</t>
-        </is>
-      </c>
-      <c r="M29" s="1" t="inlineStr">
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Self‑hosted AI;Architecture;Governance</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
         <is>
           <t>High (Mandatory for spec'ing out server node VRAM limits)</t>
         </is>
       </c>
-      <c r="N29" s="1" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="O29" s="1" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>Discusses a "Token Economics" framework. Breaks down the "Memory Wall" economics showing an on-prem breakeven velocity of ~4 months. Capabilities: Hardware performance scaling &amp; VRAM sizing.</t>
         </is>
       </c>
-      <c r="Q29" s="11" t="n">
+      <c r="Q29" s="3" t="n">
         <v>46054</v>
       </c>
     </row>
@@ -2543,25 +2447,25 @@
           <t>359b5ac8</t>
         </is>
       </c>
-      <c r="B30" s="1" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t xml:space="preserve">Coalition for Secure AI (CoSAI) </t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>https://www.coalitionforsecureai.org/</t>
         </is>
       </c>
-      <c r="D30" s="1" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t xml:space="preserve">Coalition for Secure AI (CoSAI) </t>
         </is>
       </c>
-      <c r="E30" s="9" t="n">
+      <c r="E30" s="3" t="n">
         <v>46259</v>
       </c>
-      <c r="F30" s="1" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>@pbuendia</t>
         </is>
@@ -2571,40 +2475,40 @@
           <t>@biddyman11</t>
         </is>
       </c>
-      <c r="H30" s="9" t="n">
-        <v>46174</v>
-      </c>
-      <c r="J30" s="1" t="inlineStr">
+      <c r="H30" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>Security Guidance &amp; Resources</t>
         </is>
       </c>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>Safety / guardrails; Safe Tool Use</t>
-        </is>
-      </c>
-      <c r="L30" s="1" t="inlineStr">
-        <is>
-          <t>Infrastructure Security; Security</t>
-        </is>
-      </c>
-      <c r="M30" s="1" t="inlineStr">
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Safety / guardrails;Safe Tool Use</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Infrastructure Security;Security</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t>Relevant security expertise and best practices for secure AI development and deployment</t>
         </is>
       </c>
-      <c r="N30" s="1" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="O30" s="1" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>The Coalition for Secure AI (CoSAI) is an open ecosystem of AI and security experts. See https://github.com/cosai-oasis/ws2-defenders</t>
         </is>
       </c>
-      <c r="Q30" s="11" t="n">
+      <c r="Q30" s="3" t="n">
         <v>46174</v>
       </c>
     </row>
@@ -2614,25 +2518,25 @@
           <t>5f3954c2</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Anthropic Project Glasswing</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>https://www.anthropic.com/glasswing</t>
         </is>
       </c>
-      <c r="D31" s="1" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>Anthropic</t>
         </is>
       </c>
-      <c r="E31" s="9" t="n">
+      <c r="E31" s="3" t="n">
         <v>46182</v>
       </c>
-      <c r="F31" s="1" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
@@ -2642,44 +2546,43 @@
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H31" s="9" t="n">
+      <c r="H31" s="3" t="n">
+        <v>46182</v>
+      </c>
+      <c r="J31" s="3" t="n">
         <v>46119</v>
       </c>
-      <c r="I31" s="10" t="n"/>
-      <c r="J31" s="1" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>Security Guidance &amp; Resources</t>
         </is>
       </c>
-      <c r="K31" s="1" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>Cybersecurity</t>
         </is>
       </c>
-      <c r="L31" s="1" t="inlineStr">
-        <is>
-          <t>Infrastructure Security; Security</t>
-        </is>
-      </c>
-      <c r="M31" s="1" t="inlineStr">
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Infrastructure Security;Security</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
         <is>
           <t>AI models that find high-severity vulnerabilities</t>
         </is>
       </c>
-      <c r="N31" s="1" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="O31" s="2" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>See Claude Mythos Preview</t>
         </is>
       </c>
-      <c r="P31" s="11" t="n">
-        <v>46119</v>
-      </c>
-      <c r="Q31" s="11" t="n">
+      <c r="Q31" s="3" t="n">
         <v>46119</v>
       </c>
     </row>
@@ -2689,25 +2592,25 @@
           <t>1c277820</t>
         </is>
       </c>
-      <c r="B32" s="1" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Docker AI Governance &amp; Sandboxes</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>https://docs.docker.com/ai/sandboxes/governance/org/</t>
         </is>
       </c>
-      <c r="D32" s="1" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Docker</t>
         </is>
       </c>
-      <c r="E32" s="9" t="n">
+      <c r="E32" s="3" t="n">
         <v>46219</v>
       </c>
-      <c r="F32" s="1" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
@@ -2717,45 +2620,45 @@
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H32" s="9" t="n">
-        <v>46213</v>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
+      <c r="H32" s="3" t="n">
+        <v>46219</v>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>0.35.0</t>
         </is>
       </c>
-      <c r="J32" s="1" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>Sandbox; MCP</t>
-        </is>
-      </c>
-      <c r="L32" s="1" t="inlineStr">
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Sandbox;MCP</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="M32" s="1" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>Good AI governance topics</t>
         </is>
       </c>
-      <c r="N32" s="1" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="O32" s="1" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>See blog article: https://www.docker.com/blog/the-3cs-a-framework-for-ai-agent-security/</t>
         </is>
       </c>
-      <c r="Q32" s="11" t="n">
+      <c r="Q32" s="3" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -2765,25 +2668,25 @@
           <t>b39dc1d1</t>
         </is>
       </c>
-      <c r="B33" s="1" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Responses API</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>https://developers.openai.com/api/docs/guides/migrate-to-responses</t>
         </is>
       </c>
-      <c r="D33" s="1" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="E33" s="9" t="n">
+      <c r="E33" s="3" t="n">
         <v>46220</v>
       </c>
-      <c r="F33" s="1" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
@@ -2793,116 +2696,150 @@
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H33" s="9" t="n">
+      <c r="H33" s="3" t="n">
+        <v>46220</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>GPT-5.6</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Tools;Skills;Retrieval</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Useful for domain-specific agents</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Emerging</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>MIgrated from API Assistants  - now deprecated.</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="n">
         <v>46212</v>
       </c>
-      <c r="I33" s="1" t="inlineStr">
-        <is>
-          <t>GPT-5.6</t>
-        </is>
-      </c>
-      <c r="J33" s="1" t="inlineStr">
-        <is>
-          <t>Documentation</t>
-        </is>
-      </c>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>Tools; Skills; Retrieval</t>
-        </is>
-      </c>
-      <c r="L33" s="1" t="inlineStr">
-        <is>
-          <t>Architecture</t>
-        </is>
-      </c>
-      <c r="M33" s="1" t="inlineStr">
-        <is>
-          <t>Useful for domain-specific agents</t>
-        </is>
-      </c>
-      <c r="N33" s="1" t="inlineStr">
-        <is>
-          <t>Emerging</t>
-        </is>
-      </c>
-      <c r="O33" s="1" t="inlineStr">
-        <is>
-          <t>MIgrated from API Assistants  - now deprecated.</t>
-        </is>
-      </c>
-      <c r="Q33" s="11" t="n">
-        <v>46212</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="L34" s="1" t="n"/>
-    </row>
-    <row r="35">
-      <c r="L35" s="1" t="n"/>
-    </row>
-    <row r="36">
-      <c r="L36" s="1" t="n"/>
-    </row>
-    <row r="37">
-      <c r="L37" s="1" t="n"/>
-    </row>
-    <row r="38">
-      <c r="L38" s="1" t="n"/>
-    </row>
-    <row r="39">
-      <c r="L39" s="1" t="n"/>
-    </row>
-    <row r="40">
-      <c r="L40" s="1" t="n"/>
-    </row>
-    <row r="41">
-      <c r="L41" s="1" t="n"/>
-    </row>
-    <row r="42">
-      <c r="L42" s="1" t="n"/>
-    </row>
-    <row r="43">
-      <c r="L43" s="1" t="n"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D1:D12 D14:D994 F24 F30:F33 G32">
-    <cfRule type="expression" priority="4" dxfId="3">
-      <formula>D1&gt;46151</formula>
+  <conditionalFormatting sqref="E2:E33">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>E2&gt;=DATE(2026,5,9)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J1:J994">
-    <cfRule type="notContainsBlanks" priority="5" dxfId="2">
-      <formula>LEN(TRIM(J1))&gt;0</formula>
+  <conditionalFormatting sqref="K2:K33">
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"Documentation"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>"API Reference"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
+      <formula>"Specification"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
+      <formula>"Whitepaper"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5">
+      <formula>"Scientific Literature"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="6">
+      <formula>"Governance Guidance"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="7">
+      <formula>"Security Guidance &amp; Resources"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="8">
+      <formula>"Reference Architecture"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="10" operator="equal" dxfId="9">
+      <formula>"Container Registry"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="11" operator="equal" dxfId="10">
+      <formula>"Enterprise Control Interface"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="12" operator="equal" dxfId="11">
+      <formula>"Inference Framework"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="13" operator="equal" dxfId="12">
+      <formula>"Local Application Sandbox"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="14" operator="equal" dxfId="13">
+      <formula>"Github Code Repository"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="15" operator="equal" dxfId="14">
+      <formula>"Benchmark Collection"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L1:L994">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="2">
+  <conditionalFormatting sqref="M2:M33">
+    <cfRule type="expression" priority="16" dxfId="1">
+      <formula>LEN(TRIM(M2))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O2:O33">
+    <cfRule type="cellIs" priority="17" operator="equal" dxfId="1">
       <formula>"Emerging"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="18" operator="equal" dxfId="4">
+      <formula>"Research"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="19" operator="equal" dxfId="2">
       <formula>"Mature"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="0">
-      <formula>"Research"</formula>
+    <cfRule type="cellIs" priority="20" operator="equal" dxfId="15">
+      <formula>"Deprecated"</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" location="0350" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2911,19 +2848,34 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <dimension ref="A1:R2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="22.140625" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="43" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="23" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
@@ -2953,14 +2905,14 @@
           <t>Verified By</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Added/Edited By</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Deprecation Date / Last Updated</t>
+          <t>Last Updated</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -2970,35 +2922,45 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Publication/Version Date</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Deprecation Date</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Relevance to Research Cyberinfrastructure</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Maturity Level</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Notes / Key Takeaways</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Discovery Date</t>
         </is>
@@ -3010,7 +2972,7 @@
           <t>805047b4</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>OpenAI Assistants API</t>
         </is>
@@ -3020,7 +2982,7 @@
           <t>https://platform.openai.com/docs/assistants</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>OpenAI</t>
         </is>
@@ -3028,7 +2990,7 @@
       <c r="E2" s="3" t="n">
         <v>46150</v>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
@@ -3038,93 +3000,114 @@
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H2" s="4" t="n">
-        <v>46260</v>
-      </c>
-      <c r="I2" s="1" t="n"/>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="H2" s="3" t="n">
+        <v>46150</v>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>API Reference</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t>Tools; Skills; Retrieval</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t>Architecture; Implementation</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Tools;Skills;Retrieval</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Architecture;Implementation</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>Useful for domain-specific agents</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>Deprecated</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Stable API surface.</t>
         </is>
       </c>
-      <c r="P2" s="11" t="n">
+      <c r="R2" s="3" t="n">
         <v>46150</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D1:D2">
-    <cfRule type="expression" priority="5" dxfId="3">
-      <formula>D1&gt;46151</formula>
+  <conditionalFormatting sqref="E2">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>E2&gt;=DATE(2026,5,9)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J1:J2">
-    <cfRule type="notContainsBlanks" priority="4" dxfId="2">
-      <formula>LEN(TRIM(J1))&gt;0</formula>
+  <conditionalFormatting sqref="L2">
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"Documentation"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>"API Reference"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
+      <formula>"Specification"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
+      <formula>"Whitepaper"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5">
+      <formula>"Scientific Literature"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="6">
+      <formula>"Governance Guidance"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="7">
+      <formula>"Security Guidance &amp; Resources"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="8">
+      <formula>"Reference Architecture"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="10" operator="equal" dxfId="9">
+      <formula>"Container Registry"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="11" operator="equal" dxfId="10">
+      <formula>"Enterprise Control Interface"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="12" operator="equal" dxfId="11">
+      <formula>"Inference Framework"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="13" operator="equal" dxfId="12">
+      <formula>"Local Application Sandbox"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="14" operator="equal" dxfId="13">
+      <formula>"Github Code Repository"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="15" operator="equal" dxfId="14">
+      <formula>"Benchmark Collection"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1">
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="0">
-      <formula>"Adolescent"</formula>
+  <conditionalFormatting sqref="N2">
+    <cfRule type="expression" priority="16" dxfId="1">
+      <formula>LEN(TRIM(N2))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:L1">
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="2">
+  <conditionalFormatting sqref="P2">
+    <cfRule type="cellIs" priority="17" operator="equal" dxfId="1">
       <formula>"Emerging"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="18" operator="equal" dxfId="4">
+      <formula>"Research"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="19" operator="equal" dxfId="2">
       <formula>"Mature"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L1:L2">
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="0">
-      <formula>"Research"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L1:L993">
-    <cfRule type="cellIs" priority="10" operator="equal" dxfId="6">
+    <cfRule type="cellIs" priority="20" operator="equal" dxfId="15">
       <formula>"Deprecated"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="2">
-      <formula>"Emerging"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
-      <formula>"Mature"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation sqref="J2" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>"Architecture,Deployment,Governance,Implementation,Security,Data Governance,Network Isolation,Infrastructure Security,Self‑hosted AI,Workflows,Architecture, Deployment,Architecture, Governance,Architecture, Governance, Security,Architecture, Implementation"&amp;",Architecture, Implementation, Deployment,Architecture, Security,Data Governance; Security,Governance; Security,Implementation, Data Governance,Implementation, Deployment,Implementation, Network Isolation, Infrastructure Security,Implementation, Network I"&amp;"solation, Infrastructure Security, Governance,Implementation, Security, Deployment,Security; Governance"</formula1>
-    </dataValidation>
-  </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3133,19 +3116,31 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <dimension ref="A1:O8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="29.85546875" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
@@ -3175,7 +3170,7 @@
           <t>Verified By</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Added/Edited By</t>
         </is>
@@ -3192,25 +3187,30 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Publication/Version Date</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Maturity Level</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Notes / Key Takeaways</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Discovery Date</t>
         </is>
@@ -3222,7 +3222,7 @@
           <t>ba114fad</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Databricks Coding Agent Benchmark</t>
         </is>
@@ -3232,7 +3232,7 @@
           <t>https://www.databricks.com/blog/benchmarking-coding-agents-databricks-multi-million-line-codebase</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Databricks</t>
         </is>
@@ -3240,7 +3240,7 @@
       <c r="E2" s="3" t="n">
         <v>46216</v>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
@@ -3250,35 +3250,35 @@
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H2" s="1" t="n">
-        <v>2024</v>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="H2" s="3" t="n">
+        <v>46216</v>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Whitepaper</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Coding Agents</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Evaluates State-Of-The-Art agent performance on multi-million line codebases to assess real-world software engineering capabilities.</t>
         </is>
       </c>
-      <c r="N2" s="11" t="n">
+      <c r="O2" s="3" t="n">
         <v>46216</v>
       </c>
     </row>
@@ -3288,17 +3288,17 @@
           <t>4c170f7e</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t xml:space="preserve">Papers with Code </t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>https://paperswithcode.co/tasks/coding-agents</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Hugging Face</t>
         </is>
@@ -3306,7 +3306,7 @@
       <c r="E3" s="3" t="n">
         <v>46216</v>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
@@ -3316,30 +3316,30 @@
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H3" s="1" t="n">
-        <v>2026</v>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
+      <c r="H3" s="3" t="n">
+        <v>46216</v>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>Benchmark Collection</t>
         </is>
       </c>
-      <c r="K3" s="1" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Coding Agents</t>
         </is>
       </c>
-      <c r="L3" s="1" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="M3" s="1" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Papers with Code with State-Of-The-Art (SOTA) Codng Agent Benchmarks</t>
         </is>
       </c>
-      <c r="N3" s="11" t="n">
+      <c r="O3" s="3" t="n">
         <v>46216</v>
       </c>
     </row>
@@ -3349,56 +3349,52 @@
           <t>b9ed03e7</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>SWE-Bench Pro</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>https://openreview.net/forum?id=9R2iUHhVfr</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>SWE-bench Team</t>
         </is>
       </c>
-      <c r="E4" s="3" t="n"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H4" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="I4" s="1" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Pro</t>
         </is>
       </c>
-      <c r="J4" s="1" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Whitepaper</t>
         </is>
       </c>
-      <c r="K4" s="1" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Coding Agents</t>
         </is>
       </c>
-      <c r="L4" s="1" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="M4" s="1" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Addresses limitations of original SWE-bench by focusing on long-horizon, complex, multi-file software engineering tasks.</t>
         </is>
       </c>
-      <c r="N4" s="11" t="n">
+      <c r="O4" s="3" t="n">
         <v>46216</v>
       </c>
     </row>
@@ -3408,7 +3404,7 @@
           <t>f487cdc5</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>SWE-Bench++</t>
         </is>
@@ -3418,41 +3414,37 @@
           <t>https://arxiv.org/abs/2512.17419</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Academic Researchers</t>
         </is>
       </c>
-      <c r="E5" s="3" t="n"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H5" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="J5" s="1" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Whitepaper</t>
         </is>
       </c>
-      <c r="K5" s="1" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Coding Agents</t>
         </is>
       </c>
-      <c r="L5" s="1" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="M5" s="1" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Scalable framework that generates repository-level tasks from live GitHub PRs across 11 programming languages.</t>
         </is>
       </c>
-      <c r="N5" s="11" t="n">
+      <c r="O5" s="3" t="n">
         <v>46216</v>
       </c>
     </row>
@@ -3462,54 +3454,52 @@
           <t>f37d4051</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Terminal-Bench</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2601.11868</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>CISPA / Academic Researchers</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H6" s="1" t="n">
-        <v>2026</v>
-      </c>
-      <c r="I6" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" s="1" t="inlineStr">
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>Whitepaper</t>
         </is>
       </c>
-      <c r="K6" s="1" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Coding Agents</t>
         </is>
       </c>
-      <c r="L6" s="1" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="M6" s="1" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Benchmarks agents on hard, realistic tasks within terminal/CLI environments.</t>
         </is>
       </c>
-      <c r="N6" s="11" t="n">
+      <c r="O6" s="3" t="n">
         <v>46216</v>
       </c>
     </row>
@@ -3519,7 +3509,7 @@
           <t>acbc7354</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>c-CRAB</t>
         </is>
@@ -3529,44 +3519,42 @@
           <t>https://arxiv.org/abs/2603.23448</t>
         </is>
       </c>
-      <c r="D7" s="1" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Academic Researchers</t>
         </is>
       </c>
-      <c r="E7" s="3" t="n"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H7" s="1" t="n">
-        <v>2026</v>
-      </c>
-      <c r="I7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="1" t="inlineStr">
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>Whitepaper</t>
         </is>
       </c>
-      <c r="K7" s="1" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Coding Agents</t>
         </is>
       </c>
-      <c r="L7" s="1" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="M7" s="1" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Benchmark specifically for evaluating the code review capabilities of AI agents.</t>
         </is>
       </c>
-      <c r="N7" s="11" t="n">
+      <c r="O7" s="3" t="n">
         <v>46216</v>
       </c>
     </row>
@@ -3576,82 +3564,127 @@
           <t>edd19b89</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>SWE-Explore</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2606.07297</t>
         </is>
       </c>
-      <c r="D8" s="1" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Academic Researchers</t>
         </is>
       </c>
-      <c r="E8" s="3" t="n"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H8" s="1" t="n">
-        <v>2026</v>
-      </c>
-      <c r="I8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="1" t="inlineStr">
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>Whitepaper</t>
         </is>
       </c>
-      <c r="K8" s="1" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Coding Agents</t>
         </is>
       </c>
-      <c r="L8" s="1" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="M8" s="1" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Isolates the evaluation of repository exploration, context retrieval, and code localization capabilities.</t>
         </is>
       </c>
-      <c r="N8" s="11" t="n">
+      <c r="O8" s="3" t="n">
         <v>46216</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D1:D8">
-    <cfRule type="expression" priority="4" dxfId="3">
-      <formula>D1&gt;46151</formula>
+  <conditionalFormatting sqref="E2:E8">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>E2&gt;=DATE(2026,5,9)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J1:J8">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="2">
+  <conditionalFormatting sqref="K2:K8">
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"Documentation"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>"API Reference"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
+      <formula>"Specification"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
+      <formula>"Whitepaper"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5">
+      <formula>"Scientific Literature"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="6">
+      <formula>"Governance Guidance"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="7">
+      <formula>"Security Guidance &amp; Resources"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="8">
+      <formula>"Reference Architecture"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="10" operator="equal" dxfId="9">
+      <formula>"Container Registry"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="11" operator="equal" dxfId="10">
+      <formula>"Enterprise Control Interface"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="12" operator="equal" dxfId="11">
+      <formula>"Inference Framework"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="13" operator="equal" dxfId="12">
+      <formula>"Local Application Sandbox"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="14" operator="equal" dxfId="13">
+      <formula>"Github Code Repository"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="15" operator="equal" dxfId="14">
+      <formula>"Benchmark Collection"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M8">
+    <cfRule type="cellIs" priority="16" operator="equal" dxfId="1">
       <formula>"Emerging"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="17" operator="equal" dxfId="4">
+      <formula>"Research"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="18" operator="equal" dxfId="2">
       <formula>"Mature"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="0">
-      <formula>"Research"</formula>
+    <cfRule type="cellIs" priority="19" operator="equal" dxfId="15">
+      <formula>"Deprecated"</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3663,46 +3696,52 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
     <col width="80" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Position</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Column Name</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Applies To</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Value Type</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Separator</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Description</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Colour</t>
         </is>
       </c>
     </row>
@@ -3731,131 +3770,131 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="25.5" customHeight="1">
-      <c r="A3" s="13" t="n">
+    <row r="3">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Resource Name</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>free_text</t>
         </is>
       </c>
-      <c r="E3" s="13" t="n"/>
-      <c r="F3" s="13" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Short, human-readable name. Also the natural key used to match a row across sync runs. Example: VS Code Copilot Agents Overview</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="25.5" customHeight="1">
-      <c r="A4" s="13" t="n">
+    <row r="4">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>free_text</t>
         </is>
       </c>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Canonical link to the resource.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="25.5" customHeight="1">
-      <c r="A5" s="13" t="n">
+    <row r="5">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Source Organization</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>free_text</t>
         </is>
       </c>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="13" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Who maintains it? Examples: Microsoft, GitHub, OpenAI, Kaggle, Anthropic, Google, HuggingFace. This matters because some orgs update weekly, others yearly.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="25.5" customHeight="1">
-      <c r="A6" s="13" t="n">
+    <row r="6">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Last Verified</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Date a curator last checked the page. Set by a human during verification; cleared automatically when the row's content changes.</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="25.5" customHeight="1">
-      <c r="A7" s="13" t="n">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>FFD9D2E9</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Verified By</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
-      <c r="E7" s="13" t="n"/>
-      <c r="F7" s="13" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Curator who last verified this row. Set by a human only, never by an agent; cleared automatically when the row's content changes.</t>
         </is>
@@ -3887,294 +3926,290 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="n">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Last Updated</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>Knowledgebase; SOTA Coding Agents Benchmarks</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="E9" s="13" t="n"/>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>The page's own update timestamp. Helps track fast-moving agent ecosystems.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="38.25" customHeight="1">
-      <c r="A10" s="13" t="n">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Date this row's content was last added or edited -- auto-stamped by the sync scripts whenever the row's content actually changes, alongside Added/Edited By. Not the resource's own date -- see Publication/Version Date for that.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>Deprecation Date / Last Updated</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>version</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Version string of the resource or tool (e.g. 'v0.1 DRAFT', 'Pro'). Leave blank for a resource with no version -- use Publication/Version Date instead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Publication/Version Date</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>The resource's own date -- publication date, or a page's own last-updated date -- used in place of Version when the resource has no version string. Distinct from Last Updated, which is about this row, not the resource.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Deprecation Date</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>Deprecated</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="inlineStr">
-        <is>
-          <t>Most recent known date for this row, whichever kind of event produced it: when the resource was confirmed deprecated, or, absent that, whenever the row was last touched. An exact deprecation date isn't always knowable at the time a row is added or edited.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="25.5" customHeight="1">
-      <c r="A11" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Date the resource was confirmed deprecated, if known. Often blank -- an exact deprecation date isn't always knowable. Distinct from Last Updated, which is when this row itself was last touched (e.g. when it was moved here).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Resource Type</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>version</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="13" t="inlineStr">
-        <is>
-          <t>Version string of the resource or tool (e.g. 'v0.1 DRAFT', 'Pro'). Leave blank for article-type resources with no version - use Publication Date instead.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="25.5" customHeight="1">
-      <c r="A12" s="13" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>Resource Type</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>controlled_single</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>What kind of resource this is. Helps teams filter by what they need.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Agentic Features Covered</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>controlled_multi</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>;</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Which agentic capabilities the resource covers. One of the most important columns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Topic Focus</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Knowledgebase; Deprecated</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>controlled_multi</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>;</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Subject areas the resource addresses. Helps research IT teams quickly find relevant material. Primary vocabulary is EDAM; NIST AI RMF characteristics are available as an optional secondary axis.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>FFB7E1CD</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Relevance to Research Cyberinfrastructure</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Knowledgebase; Deprecated</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Free-text note on why this matters to research platforms. Example themes: workflow orchestration, data portal integration, metadata / provenance, multi-agent coordination, HPC / cloud hybrid workflows, reproducibility, federated analysis, user-facing agent interfaces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Maturity Level</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>controlled_single</t>
         </is>
       </c>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>What kind of resource this is. Helps teams filter by what they need.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="25.5" customHeight="1">
-      <c r="A13" s="13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>Agentic Features Covered</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Not about the website - about the technology described. Helps teams know whether something is stable enough to consider.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Notes / Key Takeaways</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>controlled_multi</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
-        <is>
-          <t>;</t>
-        </is>
-      </c>
-      <c r="F13" s="13" t="inlineStr">
-        <is>
-          <t>Which agentic capabilities the resource covers. One of the most important columns.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="38.25" customHeight="1">
-      <c r="A14" s="13" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>Topic Focus</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>Knowledgebase; Deprecated</t>
-        </is>
-      </c>
-      <c r="D14" s="13" t="inlineStr">
-        <is>
-          <t>controlled_multi</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="inlineStr">
-        <is>
-          <t>;</t>
-        </is>
-      </c>
-      <c r="F14" s="13" t="inlineStr">
-        <is>
-          <t>Subject areas the resource addresses. Helps research IT teams quickly find relevant material. Primary vocabulary is EDAM; NIST AI RMF characteristics are available as an optional secondary axis.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="38.25" customHeight="1">
-      <c r="A15" s="13" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>Relevance to Research Cyberinfrastructure</t>
-        </is>
-      </c>
-      <c r="C15" s="13" t="inlineStr">
-        <is>
-          <t>Knowledgebase; Deprecated</t>
-        </is>
-      </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>free_text</t>
         </is>
       </c>
-      <c r="E15" s="13" t="n"/>
-      <c r="F15" s="13" t="inlineStr">
-        <is>
-          <t>Free-text note on why this matters to research platforms. Example themes: workflow orchestration, data portal integration, metadata / provenance, multi-agent coordination, HPC / cloud hybrid workflows, reproducibility, federated analysis, user-facing agent interfaces.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="25.5" customHeight="1">
-      <c r="A16" s="13" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>Maturity Level</t>
-        </is>
-      </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Short free-text field: breaking changes, important patterns, new capabilities, relevance to agentic workflows, implications for research platforms. This is where institutional knowledge accumulates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Discovery Date</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
-        <is>
-          <t>controlled_single</t>
-        </is>
-      </c>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="13" t="inlineStr">
-        <is>
-          <t>Not about the website - about the technology described. Helps teams know whether something is stable enough to consider.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="38.25" customHeight="1">
-      <c r="A17" s="13" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>Notes / Key Takeaways</t>
-        </is>
-      </c>
-      <c r="C17" s="13" t="inlineStr">
-        <is>
-          <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
-        </is>
-      </c>
-      <c r="D17" s="13" t="inlineStr">
-        <is>
-          <t>free_text</t>
-        </is>
-      </c>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="13" t="inlineStr">
-        <is>
-          <t>Short free-text field: breaking changes, important patterns, new capabilities, relevance to agentic workflows, implications for research platforms. This is where institutional knowledge accumulates.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="13" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>Publication Date</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="inlineStr">
-        <is>
-          <t>Knowledgebase</t>
-        </is>
-      </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="inlineStr">
-        <is>
-          <t>Publication date for article-type resources that have no software version.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="25.5" customHeight="1">
-      <c r="A19" s="13" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>Discovery Date</t>
-        </is>
-      </c>
-      <c r="C19" s="13" t="inlineStr">
-        <is>
-          <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
-        </is>
-      </c>
-      <c r="D19" s="13" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="13" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Date this resource first entered the VT Radar.</t>
         </is>
@@ -4191,1735 +4226,1646 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F77"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
+  <dimension ref="A1:G77"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="80" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Column Name</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Term</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Ontology</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Ontology ID</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Ontology URL</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="25.5" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Colour</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Schema.org</t>
         </is>
       </c>
-      <c r="E2" s="13" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>schema:TechArticle</t>
         </is>
       </c>
-      <c r="F2" s="13" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>https://schema.org/TechArticle</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="25.5" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>FFB7E1CD</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>API Reference</t>
         </is>
       </c>
-      <c r="C3" s="13" t="n"/>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Schema.org</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>schema:APIReference</t>
         </is>
       </c>
-      <c r="F3" s="13" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>https://schema.org/APIReference</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="25.5" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>FFA4C2F4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Specification</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Schema.org</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>schema:TechArticle</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>https://schema.org/TechArticle</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="25.5" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>FFB4A7D6</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Whitepaper</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Vendor or organization technical whitepaper.</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Schema.org</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>schema:TechArticle</t>
         </is>
       </c>
-      <c r="F5" s="13" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>https://schema.org/TechArticle</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="25.5" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>FFFFE599</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Scientific Literature</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Peer-reviewed publication or preprint. Distinct from a vendor Whitepaper.</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Schema.org</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>schema:ScholarlyArticle</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>https://schema.org/ScholarlyArticle</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="25.5" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>FFF4CCCC</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Governance Guidance</t>
         </is>
       </c>
-      <c r="C7" s="13" t="n"/>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Schema.org</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>schema:TechArticle</t>
         </is>
       </c>
-      <c r="F7" s="13" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>https://schema.org/TechArticle</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="25.5" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>FFD9EAD3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Security Guidance &amp; Resources</t>
         </is>
       </c>
-      <c r="C8" s="13" t="n"/>
-      <c r="D8" s="13" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Schema.org</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>schema:TechArticle</t>
         </is>
       </c>
-      <c r="F8" s="13" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>https://schema.org/TechArticle</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="25.5" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>FFEA9999</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Reference Architecture</t>
         </is>
       </c>
-      <c r="C9" s="13" t="n"/>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Schema.org</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>schema:TechArticle</t>
         </is>
       </c>
-      <c r="F9" s="13" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>https://schema.org/TechArticle</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>FFC9DAF8</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Container Registry</t>
         </is>
       </c>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>FFD0E0E3</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Enterprise Control Interface</t>
         </is>
       </c>
-      <c r="C11" s="13" t="n"/>
-      <c r="D11" s="13" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="13" t="n"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>FFFCE5CD</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Inference Framework</t>
         </is>
       </c>
-      <c r="C12" s="13" t="n"/>
-      <c r="D12" s="13" t="n"/>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="13" t="n"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>FFCFE2F3</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Local Application Sandbox</t>
         </is>
       </c>
-      <c r="C13" s="13" t="n"/>
-      <c r="D13" s="13" t="n"/>
-      <c r="E13" s="13" t="n"/>
-      <c r="F13" s="13" t="n"/>
-    </row>
-    <row r="14" ht="25.5" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>FFEAD1DC</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Github Code Repository</t>
         </is>
       </c>
-      <c r="C14" s="13" t="n"/>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Schema.org</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>schema:SoftwareSourceCode</t>
         </is>
       </c>
-      <c r="F14" s="13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>https://schema.org/SoftwareSourceCode</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="25.5" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>FFB6D7A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Resource Type</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Benchmark Collection</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>A curated collection of benchmarks or comparison studies.</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Schema.org</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>schema:Dataset</t>
         </is>
       </c>
-      <c r="F15" s="13" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>https://schema.org/Dataset</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>FFE06666</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Hooks</t>
         </is>
       </c>
-      <c r="C16" s="13" t="n"/>
-      <c r="D16" s="13" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="13" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Skills</t>
         </is>
       </c>
-      <c r="C17" s="13" t="n"/>
-      <c r="D17" s="13" t="n"/>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="13" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>MCP</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Model Context Protocol.</t>
         </is>
       </c>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Agent frameworks</t>
         </is>
       </c>
-      <c r="C19" s="13" t="n"/>
-      <c r="D19" s="13" t="n"/>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="13" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Agent Patterns</t>
         </is>
       </c>
-      <c r="C20" s="13" t="n"/>
-      <c r="D20" s="13" t="n"/>
-      <c r="E20" s="13" t="n"/>
-      <c r="F20" s="13" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Multi-Agent Patterns</t>
         </is>
       </c>
-      <c r="C21" s="13" t="n"/>
-      <c r="D21" s="13" t="n"/>
-      <c r="E21" s="13" t="n"/>
-      <c r="F21" s="13" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Context window management</t>
         </is>
       </c>
-      <c r="C22" s="13" t="n"/>
-      <c r="D22" s="13" t="n"/>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="13" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Deployment patterns</t>
         </is>
       </c>
-      <c r="C23" s="13" t="n"/>
-      <c r="D23" s="13" t="n"/>
-      <c r="E23" s="13" t="n"/>
-      <c r="F23" s="13" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Safety / guardrails</t>
         </is>
       </c>
-      <c r="C24" s="13" t="n"/>
-      <c r="D24" s="13" t="n"/>
-      <c r="E24" s="13" t="n"/>
-      <c r="F24" s="13" t="n"/>
-    </row>
-    <row r="25" ht="102" customHeight="1">
-      <c r="A25" s="13" t="inlineStr">
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Evaluation / testing</t>
         </is>
       </c>
-      <c r="C25" s="13" t="n"/>
-      <c r="D25" s="13" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>ACM-CCS</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Software and its engineering~Software verification and validation~Software testing and debugging</t>
         </is>
       </c>
-      <c r="F25" s="13" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>https://dl.acm.org/ccs</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Risk Controls</t>
         </is>
       </c>
-      <c r="C26" s="13" t="n"/>
-      <c r="D26" s="13" t="n"/>
-      <c r="E26" s="13" t="n"/>
-      <c r="F26" s="13" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Safe Tool Use</t>
         </is>
       </c>
-      <c r="C27" s="13" t="n"/>
-      <c r="D27" s="13" t="n"/>
-      <c r="E27" s="13" t="n"/>
-      <c r="F27" s="13" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B28" s="13" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Tools</t>
         </is>
       </c>
-      <c r="C28" s="13" t="n"/>
-      <c r="D28" s="13" t="n"/>
-      <c r="E28" s="13" t="n"/>
-      <c r="F28" s="13" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B29" s="13" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Tool-Ready Endpoints</t>
         </is>
       </c>
-      <c r="C29" s="13" t="n"/>
-      <c r="D29" s="13" t="n"/>
-      <c r="E29" s="13" t="n"/>
-      <c r="F29" s="13" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="13" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B30" s="13" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Coding Agents</t>
         </is>
       </c>
-      <c r="C30" s="13" t="n"/>
-      <c r="D30" s="13" t="n"/>
-      <c r="E30" s="13" t="n"/>
-      <c r="F30" s="13" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B31" s="13" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Notebook Agents</t>
         </is>
       </c>
-      <c r="C31" s="13" t="n"/>
-      <c r="D31" s="13" t="n"/>
-      <c r="E31" s="13" t="n"/>
-      <c r="F31" s="13" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="13" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B32" s="13" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Workflow Agents</t>
         </is>
       </c>
-      <c r="C32" s="13" t="n"/>
-      <c r="D32" s="13" t="n"/>
-      <c r="E32" s="13" t="n"/>
-      <c r="F32" s="13" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="13" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B33" s="13" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Workflow Automation</t>
         </is>
       </c>
-      <c r="C33" s="13" t="n"/>
-      <c r="D33" s="13" t="n"/>
-      <c r="E33" s="13" t="n"/>
-      <c r="F33" s="13" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="13" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B34" s="13" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Orchestration</t>
         </is>
       </c>
-      <c r="C34" s="13" t="n"/>
-      <c r="D34" s="13" t="n"/>
-      <c r="E34" s="13" t="n"/>
-      <c r="F34" s="13" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="13" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B35" s="13" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Triggers</t>
         </is>
       </c>
-      <c r="C35" s="13" t="n"/>
-      <c r="D35" s="13" t="n"/>
-      <c r="E35" s="13" t="n"/>
-      <c r="F35" s="13" t="n"/>
-    </row>
-    <row r="36" ht="38.25" customHeight="1">
-      <c r="A36" s="13" t="inlineStr">
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B36" s="13" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>Retrieval</t>
         </is>
       </c>
-      <c r="C36" s="13" t="n"/>
-      <c r="D36" s="13" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>ACM-CCS</t>
         </is>
       </c>
-      <c r="E36" s="13" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Information systems~Information retrieval</t>
         </is>
       </c>
-      <c r="F36" s="13" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>https://dl.acm.org/ccs</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="38.25" customHeight="1">
-      <c r="A37" s="13" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B37" s="13" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Retrieval Agents</t>
         </is>
       </c>
-      <c r="C37" s="13" t="n"/>
-      <c r="D37" s="13" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>ACM-CCS</t>
         </is>
       </c>
-      <c r="E37" s="13" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Information systems~Information retrieval</t>
         </is>
       </c>
-      <c r="F37" s="13" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>https://dl.acm.org/ccs</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="13" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B38" s="13" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Sandbox</t>
         </is>
       </c>
-      <c r="C38" s="13" t="n"/>
-      <c r="D38" s="13" t="n"/>
-      <c r="E38" s="13" t="n"/>
-      <c r="F38" s="13" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="13" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B39" s="13" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="C39" s="13" t="n"/>
-      <c r="D39" s="13" t="n"/>
-      <c r="E39" s="13" t="n"/>
-      <c r="F39" s="13" t="n"/>
-    </row>
-    <row r="40" ht="25.5" customHeight="1">
-      <c r="A40" s="13" t="inlineStr">
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B40" s="13" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Cybersecurity</t>
         </is>
       </c>
-      <c r="C40" s="13" t="n"/>
-      <c r="D40" s="13" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>ACM-CCS</t>
         </is>
       </c>
-      <c r="E40" s="13" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Security and privacy</t>
         </is>
       </c>
-      <c r="F40" s="13" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>https://dl.acm.org/ccs</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="13" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B41" s="13" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>FAIR data</t>
         </is>
       </c>
-      <c r="C41" s="13" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Findable, Accessible, Interoperable, Reusable data principles.</t>
         </is>
       </c>
-      <c r="D41" s="13" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>EDAM</t>
         </is>
       </c>
-      <c r="E41" s="13" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>topic_4012</t>
         </is>
       </c>
-      <c r="F41" s="13" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>http://edamontology.org/topic_4012</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="13" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B42" s="13" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>API Integration</t>
         </is>
       </c>
-      <c r="C42" s="13" t="n"/>
-      <c r="D42" s="13" t="n"/>
-      <c r="E42" s="13" t="n"/>
-      <c r="F42" s="13" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="13" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B43" s="13" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Model Integration</t>
         </is>
       </c>
-      <c r="C43" s="13" t="n"/>
-      <c r="D43" s="13" t="n"/>
-      <c r="E43" s="13" t="n"/>
-      <c r="F43" s="13" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="13" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B44" s="13" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>Server Integration</t>
         </is>
       </c>
-      <c r="C44" s="13" t="n"/>
-      <c r="D44" s="13" t="n"/>
-      <c r="E44" s="13" t="n"/>
-      <c r="F44" s="13" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="13" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>Agentic Features Covered</t>
         </is>
       </c>
-      <c r="B45" s="13" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>Server Patterns</t>
         </is>
       </c>
-      <c r="C45" s="13" t="n"/>
-      <c r="D45" s="13" t="n"/>
-      <c r="E45" s="13" t="n"/>
-      <c r="F45" s="13" t="n"/>
-    </row>
-    <row r="46" ht="51" customHeight="1">
-      <c r="A46" s="13" t="inlineStr">
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B46" s="13" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>Architecture</t>
         </is>
       </c>
-      <c r="C46" s="13" t="n"/>
-      <c r="D46" s="13" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>ACM-CCS</t>
         </is>
       </c>
-      <c r="E46" s="13" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>Computer systems organization~Architectures</t>
         </is>
       </c>
-      <c r="F46" s="13" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>https://dl.acm.org/ccs</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="25.5" customHeight="1">
-      <c r="A47" s="13" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B47" s="13" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="C47" s="13" t="n"/>
-      <c r="D47" s="13" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>ACM-CCS</t>
         </is>
       </c>
-      <c r="E47" s="13" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Security and privacy</t>
         </is>
       </c>
-      <c r="F47" s="13" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>https://dl.acm.org/ccs</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="38.25" customHeight="1">
-      <c r="A48" s="13" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B48" s="13" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>Data governance</t>
         </is>
       </c>
-      <c r="C48" s="13" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Focuses specifically on the technical protocols, access controls, data-line security, and de-identification standards used to protect the integrity, quality, and privacy of information throughout its lifecycle</t>
         </is>
       </c>
-      <c r="D48" s="13" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>EDAM</t>
         </is>
       </c>
-      <c r="E48" s="13" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>topic_3571</t>
         </is>
       </c>
-      <c r="F48" s="13" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>http://edamontology.org/topic_3571</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="38.25" customHeight="1">
-      <c r="A49" s="13" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B49" s="13" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="C49" s="13" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>The overarching organizational policies, compliance frameworks, and capital allocation strategies that dictate how an enterprise manages its broader IT infrastructure, risk tolerances, and vendor choices</t>
         </is>
       </c>
-      <c r="D49" s="13" t="n"/>
-      <c r="E49" s="13" t="n"/>
-      <c r="F49" s="13" t="n"/>
-    </row>
-    <row r="50" ht="76.5" customHeight="1">
-      <c r="A50" s="13" t="inlineStr">
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B50" s="13" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>Implementation</t>
         </is>
       </c>
-      <c r="C50" s="13" t="n"/>
-      <c r="D50" s="13" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>ACM-CCS</t>
         </is>
       </c>
-      <c r="E50" s="13" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>Software and its engineering~Software creation and management</t>
         </is>
       </c>
-      <c r="F50" s="13" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>https://dl.acm.org/ccs</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="25.5" customHeight="1">
-      <c r="A51" s="13" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B51" s="13" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>Deployment</t>
         </is>
       </c>
-      <c r="C51" s="13" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>The tactical, hands-on execution of installing, configuring, provisioning, and launching software or hardware systems within a specific operational environment</t>
         </is>
       </c>
-      <c r="D51" s="13" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>NIST-AI-RMF</t>
         </is>
       </c>
-      <c r="E51" s="13" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>AI lifecycle stage: Deploy</t>
         </is>
       </c>
-      <c r="F51" s="13" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>https://nvlpubs.nist.gov/nistpubs/ai/NIST.AI.100-1.pdf</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="13" t="inlineStr">
+      <c r="A52" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B52" s="13" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>Workflows</t>
         </is>
       </c>
-      <c r="C52" s="13" t="n"/>
-      <c r="D52" s="13" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>EDAM</t>
         </is>
       </c>
-      <c r="E52" s="13" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>topic_0769</t>
         </is>
       </c>
-      <c r="F52" s="13" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>http://edamontology.org/topic_0769</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="13" t="inlineStr">
+      <c r="A53" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B53" s="13" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>Model selection</t>
         </is>
       </c>
-      <c r="C53" s="13" t="n"/>
-      <c r="D53" s="13" t="n"/>
-      <c r="E53" s="13" t="n"/>
-      <c r="F53" s="13" t="n"/>
-    </row>
-    <row r="54" ht="102" customHeight="1">
-      <c r="A54" s="13" t="inlineStr">
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B54" s="13" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>Evaluation</t>
         </is>
       </c>
-      <c r="C54" s="13" t="n"/>
-      <c r="D54" s="13" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>ACM-CCS</t>
         </is>
       </c>
-      <c r="E54" s="13" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>Software and its engineering~Software verification and validation~Software testing and debugging</t>
         </is>
       </c>
-      <c r="F54" s="13" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>https://dl.acm.org/ccs</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="25.5" customHeight="1">
-      <c r="A55" s="13" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B55" s="13" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>Compute Infrastructure</t>
         </is>
       </c>
-      <c r="C55" s="13" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Physical node topologies, hardware constraints, VRAM bounds, and localized compute execution profiles.</t>
         </is>
       </c>
-      <c r="D55" s="13" t="n"/>
-      <c r="E55" s="13" t="n"/>
-      <c r="F55" s="13" t="n"/>
-    </row>
-    <row r="56" ht="25.5" customHeight="1">
-      <c r="A56" s="13" t="inlineStr">
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B56" s="13" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>Network Isolation</t>
         </is>
       </c>
-      <c r="C56" s="13" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Non-egress boundaries, air-gapped artifact staging, localized cloud VPC containers, and firewalled local registries.</t>
         </is>
       </c>
-      <c r="D56" s="13" t="n"/>
-      <c r="E56" s="13" t="n"/>
-      <c r="F56" s="13" t="n"/>
-    </row>
-    <row r="57" ht="25.5" customHeight="1">
-      <c r="A57" s="13" t="inlineStr">
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B57" s="13" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>Infrastructure Security</t>
         </is>
       </c>
-      <c r="C57" s="13" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>For on-prem LLM deployments, it captures the security of the compute stack as well as the data pipelines</t>
         </is>
       </c>
-      <c r="D57" s="13" t="n"/>
-      <c r="E57" s="13" t="n"/>
-      <c r="F57" s="13" t="n"/>
-    </row>
-    <row r="58" ht="25.5" customHeight="1">
-      <c r="A58" s="13" t="inlineStr">
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B58" s="13" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>Self‑hosted AI</t>
         </is>
       </c>
-      <c r="C58" s="13" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Self‑hosted, open‑weights models in contrast to API‑based models like OpenAI, Anthropic, or Gemini</t>
         </is>
       </c>
-      <c r="D58" s="13" t="n"/>
-      <c r="E58" s="13" t="n"/>
-      <c r="F58" s="13" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="13" t="inlineStr">
+      <c r="A59" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B59" s="13" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>Data Protection</t>
         </is>
       </c>
-      <c r="C59" s="13" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Safeguarding sensitive data specifically. Distinct from the broader Security term.</t>
         </is>
       </c>
-      <c r="D59" s="13" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>EDAM</t>
         </is>
       </c>
-      <c r="E59" s="13" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>topic_4044</t>
         </is>
       </c>
-      <c r="F59" s="13" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>http://edamontology.org/topic_4044</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="13" t="inlineStr">
+      <c r="A60" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B60" s="13" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>FAIR data</t>
         </is>
       </c>
-      <c r="C60" s="13" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>Findable, Accessible, Interoperable, Reusable data principles.</t>
         </is>
       </c>
-      <c r="D60" s="13" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>EDAM</t>
         </is>
       </c>
-      <c r="E60" s="13" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>topic_4012</t>
         </is>
       </c>
-      <c r="F60" s="13" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>http://edamontology.org/topic_4012</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="13" t="inlineStr">
+      <c r="A61" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B61" s="13" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>Data quality management</t>
         </is>
       </c>
-      <c r="C61" s="13" t="n"/>
-      <c r="D61" s="13" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>EDAM</t>
         </is>
       </c>
-      <c r="E61" s="13" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>topic_3572</t>
         </is>
       </c>
-      <c r="F61" s="13" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>http://edamontology.org/topic_3572</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="13" t="inlineStr">
+      <c r="A62" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B62" s="13" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>Data curation and archival</t>
         </is>
       </c>
-      <c r="C62" s="13" t="n"/>
-      <c r="D62" s="13" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>EDAM</t>
         </is>
       </c>
-      <c r="E62" s="13" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>topic_0219</t>
         </is>
       </c>
-      <c r="F62" s="13" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>http://edamontology.org/topic_0219</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="13" t="inlineStr">
+      <c r="A63" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B63" s="13" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>Data integration and warehousing</t>
         </is>
       </c>
-      <c r="C63" s="13" t="n"/>
-      <c r="D63" s="13" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>EDAM</t>
         </is>
       </c>
-      <c r="E63" s="13" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>topic_3366</t>
         </is>
       </c>
-      <c r="F63" s="13" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>http://edamontology.org/topic_3366</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="13" t="inlineStr">
+      <c r="A64" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B64" s="13" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>Data architecture, analysis and design</t>
         </is>
       </c>
-      <c r="C64" s="13" t="n"/>
-      <c r="D64" s="13" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>EDAM</t>
         </is>
       </c>
-      <c r="E64" s="13" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>topic_3365</t>
         </is>
       </c>
-      <c r="F64" s="13" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>http://edamontology.org/topic_3365</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="13" t="inlineStr">
+      <c r="A65" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B65" s="13" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>Data identity and mapping</t>
         </is>
       </c>
-      <c r="C65" s="13" t="n"/>
-      <c r="D65" s="13" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>EDAM</t>
         </is>
       </c>
-      <c r="E65" s="13" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>topic_3345</t>
         </is>
       </c>
-      <c r="F65" s="13" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>http://edamontology.org/topic_3345</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="13" t="inlineStr">
+      <c r="A66" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B66" s="13" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>Data rescue</t>
         </is>
       </c>
-      <c r="C66" s="13" t="n"/>
-      <c r="D66" s="13" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>EDAM</t>
         </is>
       </c>
-      <c r="E66" s="13" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>topic_4011</t>
         </is>
       </c>
-      <c r="F66" s="13" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>http://edamontology.org/topic_4011</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="13" t="inlineStr">
+      <c r="A67" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B67" s="13" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>Valid and Reliable</t>
         </is>
       </c>
-      <c r="C67" s="13" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>NIST AI RMF trustworthy-AI characteristic.</t>
         </is>
       </c>
-      <c r="D67" s="13" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>NIST-AI-RMF</t>
         </is>
       </c>
-      <c r="E67" s="13" t="n"/>
-      <c r="F67" s="13" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="13" t="inlineStr">
+      <c r="A68" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B68" s="13" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
       </c>
-      <c r="C68" s="13" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>NIST AI RMF trustworthy-AI characteristic.</t>
         </is>
       </c>
-      <c r="D68" s="13" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>NIST-AI-RMF</t>
         </is>
       </c>
-      <c r="E68" s="13" t="n"/>
-      <c r="F68" s="13" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="13" t="inlineStr">
+      <c r="A69" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B69" s="13" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>Secure and Resilient</t>
         </is>
       </c>
-      <c r="C69" s="13" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>NIST AI RMF trustworthy-AI characteristic.</t>
         </is>
       </c>
-      <c r="D69" s="13" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>NIST-AI-RMF</t>
         </is>
       </c>
-      <c r="E69" s="13" t="n"/>
-      <c r="F69" s="13" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="13" t="inlineStr">
+      <c r="A70" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B70" s="13" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>Accountable and Transparent</t>
         </is>
       </c>
-      <c r="C70" s="13" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>NIST AI RMF trustworthy-AI characteristic.</t>
         </is>
       </c>
-      <c r="D70" s="13" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>NIST-AI-RMF</t>
         </is>
       </c>
-      <c r="E70" s="13" t="n"/>
-      <c r="F70" s="13" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="13" t="inlineStr">
+      <c r="A71" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B71" s="13" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>Explainable and Interpretable</t>
         </is>
       </c>
-      <c r="C71" s="13" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>NIST AI RMF trustworthy-AI characteristic.</t>
         </is>
       </c>
-      <c r="D71" s="13" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>NIST-AI-RMF</t>
         </is>
       </c>
-      <c r="E71" s="13" t="n"/>
-      <c r="F71" s="13" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="13" t="inlineStr">
+      <c r="A72" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B72" s="13" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>Privacy-Enhanced</t>
         </is>
       </c>
-      <c r="C72" s="13" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>NIST AI RMF trustworthy-AI characteristic.</t>
         </is>
       </c>
-      <c r="D72" s="13" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>NIST-AI-RMF</t>
         </is>
       </c>
-      <c r="E72" s="13" t="n"/>
-      <c r="F72" s="13" t="n"/>
-    </row>
-    <row r="73" ht="25.5" customHeight="1">
-      <c r="A73" s="13" t="inlineStr">
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
         <is>
           <t>Topic Focus</t>
         </is>
       </c>
-      <c r="B73" s="13" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>Fair (harmful bias managed)</t>
         </is>
       </c>
-      <c r="C73" s="13" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>NIST AI RMF trustworthy-AI characteristic: algorithmic non-discrimination. NOT the same as 'FAIR data'.</t>
         </is>
       </c>
-      <c r="D73" s="13" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>NIST-AI-RMF</t>
         </is>
       </c>
-      <c r="E73" s="13" t="n"/>
-      <c r="F73" s="13" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="13" t="inlineStr">
+      <c r="A74" t="inlineStr">
         <is>
           <t>Maturity Level</t>
         </is>
       </c>
-      <c r="B74" s="13" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="C74" s="13" t="n"/>
-      <c r="D74" s="13" t="n"/>
-      <c r="E74" s="13" t="n"/>
-      <c r="F74" s="13" t="n"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>FFB7E1CD</t>
+        </is>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" s="13" t="inlineStr">
+      <c r="A75" t="inlineStr">
         <is>
           <t>Maturity Level</t>
         </is>
       </c>
-      <c r="B75" s="13" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="C75" s="13" t="n"/>
-      <c r="D75" s="13" t="n"/>
-      <c r="E75" s="13" t="n"/>
-      <c r="F75" s="13" t="n"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>FFFFE599</t>
+        </is>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" s="13" t="inlineStr">
+      <c r="A76" t="inlineStr">
         <is>
           <t>Maturity Level</t>
         </is>
       </c>
-      <c r="B76" s="13" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="C76" s="13" t="n"/>
-      <c r="D76" s="13" t="n"/>
-      <c r="E76" s="13" t="n"/>
-      <c r="F76" s="13" t="n"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>FFA4C2F4</t>
+        </is>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" s="13" t="inlineStr">
+      <c r="A77" t="inlineStr">
         <is>
           <t>Maturity Level</t>
         </is>
       </c>
-      <c r="B77" s="13" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>Deprecated</t>
         </is>
       </c>
-      <c r="C77" s="13" t="n"/>
-      <c r="D77" s="13" t="n"/>
-      <c r="E77" s="13" t="n"/>
-      <c r="F77" s="13" t="n"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>FFDD7E6B</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5933,91 +5879,91 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="56" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="90" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Standard ID</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="25.5" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>EDAM</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>EDAM ontology (Data management branch)</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>current</t>
         </is>
       </c>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>http://edamontology.org/topic_3071</t>
         </is>
       </c>
-      <c r="E2" s="13" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Primary controlled vocabulary. Open OWL ontology with permanent per-term URIs. Browse: https://www.ebi.ac.uk/ols4/ontologies/edam - Download: http://edamontology.org/EDAM.owl</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="76.5" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>NIST-AI-RMF</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>NIST AI Risk Management Framework</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>https://nvlpubs.nist.gov/nistpubs/ai/NIST.AI.100-1.pdf</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Optional secondary axis: the seven trustworthy-AI characteristics. Document-based, so individual characteristics have no per-term URIs. WARNING: NIST's 'Fair (harmful bias managed)' concerns algorithmic non-discrimination and is UNRELATED to EDAM's 'FAIR data' (Findable / Accessible / Interoperable / Reusable data principles) despite sharing the word - do not conflate the two. Also defines an AI lifecycle with named stages (plan, collect/process, build, verify, deploy, operate) -- cited here as e.g. "AI lifecycle stage: Deploy", distinct from the seven trustworthy-AI characteristics.</t>
         </is>

--- a/data/VANTAGE-Technology-Radar.xlsx
+++ b/data/VANTAGE-Technology-Radar.xlsx
@@ -1184,6 +1184,14 @@
           <t>GitHub</t>
         </is>
       </c>
+      <c r="E4" s="4" t="n">
+        <v>46262</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>@pbuendia</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>@biddyman11</t>

--- a/data/VANTAGE-Technology-Radar.xlsx
+++ b/data/VANTAGE-Technology-Radar.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1515" yWindow="1515" windowWidth="24705" windowHeight="12345" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Knowledgebase" sheetId="1" state="visible" r:id="rId1"/>
@@ -14,15 +15,14 @@
     <sheet name="Standards" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -33,14 +33,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <color rgb="FF0563C1"/>
-      <sz val="11"/>
       <u val="single"/>
     </font>
   </fonts>
@@ -64,22 +60,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="59">
+  <dxfs count="16">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFDD7E6B"/>
-          <bgColor rgb="FFDD7E6B"/>
+          <fgColor rgb="FFD9D2E9"/>
+          <bgColor rgb="FFD9D2E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB7E1CD"/>
+          <bgColor rgb="FFB7E1CD"/>
         </patternFill>
       </fill>
     </dxf>
@@ -94,6 +97,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFB4A7D6"/>
+          <bgColor rgb="FFB4A7D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFE599"/>
           <bgColor rgb="FFFFE599"/>
         </patternFill>
@@ -102,8 +113,72 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFB7E1CD"/>
-          <bgColor rgb="FFB7E1CD"/>
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9EAD3"/>
+          <bgColor rgb="FFD9EAD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEA9999"/>
+          <bgColor rgb="FFEA9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC9DAF8"/>
+          <bgColor rgb="FFC9DAF8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD0E0E3"/>
+          <bgColor rgb="FFD0E0E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE5CD"/>
+          <bgColor rgb="FFFCE5CD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCFE2F3"/>
+          <bgColor rgb="FFCFE2F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEAD1DC"/>
+          <bgColor rgb="FFEAD1DC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB6D7A8"/>
+          <bgColor rgb="FFB6D7A8"/>
         </patternFill>
       </fill>
     </dxf>
@@ -118,432 +193,8 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFB6D7A8"/>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEAD1DC"/>
-          <bgColor rgb="FFEAD1DC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD0E0E3"/>
-          <bgColor rgb="FFD0E0E3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC9DAF8"/>
-          <bgColor rgb="FFC9DAF8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEA9999"/>
-          <bgColor rgb="FFEA9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-          <bgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFE599"/>
-          <bgColor rgb="FFFFE599"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB4A7D6"/>
-          <bgColor rgb="FFB4A7D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFA4C2F4"/>
-          <bgColor rgb="FFA4C2F4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB7E1CD"/>
-          <bgColor rgb="FFB7E1CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
           <fgColor rgb="FFDD7E6B"/>
           <bgColor rgb="FFDD7E6B"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFA4C2F4"/>
-          <bgColor rgb="FFA4C2F4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFE599"/>
-          <bgColor rgb="FFFFE599"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB7E1CD"/>
-          <bgColor rgb="FFB7E1CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB7E1CD"/>
-          <bgColor rgb="FFB7E1CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE06666"/>
-          <bgColor rgb="FFE06666"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB6D7A8"/>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEAD1DC"/>
-          <bgColor rgb="FFEAD1DC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD0E0E3"/>
-          <bgColor rgb="FFD0E0E3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC9DAF8"/>
-          <bgColor rgb="FFC9DAF8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEA9999"/>
-          <bgColor rgb="FFEA9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-          <bgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFE599"/>
-          <bgColor rgb="FFFFE599"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB4A7D6"/>
-          <bgColor rgb="FFB4A7D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFA4C2F4"/>
-          <bgColor rgb="FFA4C2F4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB7E1CD"/>
-          <bgColor rgb="FFB7E1CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDD7E6B"/>
-          <bgColor rgb="FFDD7E6B"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFA4C2F4"/>
-          <bgColor rgb="FFA4C2F4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFE599"/>
-          <bgColor rgb="FFFFE599"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB7E1CD"/>
-          <bgColor rgb="FFB7E1CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB7E1CD"/>
-          <bgColor rgb="FFB7E1CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE06666"/>
-          <bgColor rgb="FFE06666"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB6D7A8"/>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEAD1DC"/>
-          <bgColor rgb="FFEAD1DC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD0E0E3"/>
-          <bgColor rgb="FFD0E0E3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC9DAF8"/>
-          <bgColor rgb="FFC9DAF8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEA9999"/>
-          <bgColor rgb="FFEA9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-          <bgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFE599"/>
-          <bgColor rgb="FFFFE599"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB4A7D6"/>
-          <bgColor rgb="FFB4A7D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFA4C2F4"/>
-          <bgColor rgb="FFA4C2F4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB7E1CD"/>
-          <bgColor rgb="FFB7E1CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
         </patternFill>
       </fill>
     </dxf>
@@ -909,12 +560,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q33"/>
+  <dimension ref="A1:R34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="26.5703125" customWidth="1" min="2" max="2"/>
-    <col width="37.28515625" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
@@ -925,10 +576,11 @@
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="26" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="43" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="23" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="43" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="23" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -999,20 +651,25 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>ALAF Checklist Mapping</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>Relevance to Research Cyberinfrastructure</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Maturity Level</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Notes / Key Takeaways</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Discovery Date</t>
         </is>
@@ -1073,22 +730,22 @@
           <t>Architecture;Implementation;Deployment</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>IDE integration for agentic workflows</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Canonical reference for VS Code agent capabilities.</t>
         </is>
       </c>
-      <c r="Q2" s="3" t="n">
+      <c r="R2" s="3" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -1149,17 +806,17 @@
           <t>Workflows;Implementation</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Makes data outputs FAIR at the point of publication</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="Q3" s="3" t="n">
+      <c r="R3" s="3" t="n">
         <v>46168</v>
       </c>
     </row>
@@ -1184,7 +841,7 @@
           <t>GitHub</t>
         </is>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="3" t="n">
         <v>46262</v>
       </c>
       <c r="F4" t="inlineStr">
@@ -1197,7 +854,7 @@
           <t>@biddyman11</t>
         </is>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="H4" s="3" t="n">
         <v>46262</v>
       </c>
       <c r="K4" t="inlineStr">
@@ -1215,22 +872,22 @@
           <t>Architecture;Governance;Security</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Relevant for CI/CD and code-review automation</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Strong alignment with developer workflows.</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="R4" s="3" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -1275,22 +932,22 @@
           <t>Architecture;Implementation</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Key for interoperable agent tools</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Fast-moving ecosystem.</t>
         </is>
       </c>
-      <c r="Q5" s="3" t="n">
+      <c r="R5" s="3" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -1335,22 +992,22 @@
           <t>Architecture;Governance</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Critical for cross-platform agent interoperability</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Becoming a de facto standard.</t>
         </is>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="R6" s="3" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -1409,22 +1066,22 @@
           <t>Architecture;Governance</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Integration between LLM applications and external data sources and tools</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Strong safety emphasis.</t>
         </is>
       </c>
-      <c r="Q7" s="3" t="n">
+      <c r="R7" s="3" t="n">
         <v>45962</v>
       </c>
     </row>
@@ -1485,50 +1142,53 @@
           <t>Implementation;Security;Deployment</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Helps teams move prototypes to production</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Technical guide to the operational life cycle of AI agents, focusing on deployment &amp; security</t>
         </is>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="R8" s="3" t="n">
         <v>45975</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>bfda8877</t>
+          <t>f488464f</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Google Vertex AI Agents Overview</t>
+          <t>HuggingFace Agents Documentation</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>https://cloud.google.com/vertex-ai/docs/agents</t>
+          <t>https://huggingface.co/docs/hub/en/agents</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>HuggingFace</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Paty Buendia</t>
-        </is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>46265</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1537,52 +1197,52 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Agent frameworks;Orchestration</t>
+          <t>Tools;Skills;Model Integration</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Architecture;Deployment</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Useful for cloud-based scientific workflows</t>
+          <t>Architecture;Implementation</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>Useful for open-source agent experimentation</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Strong enterprise alignment.</t>
-        </is>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>46113</v>
+          <t>Emerging</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Rapidly evolving.</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>46082</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>f488464f</t>
+          <t>dbe3741e</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HuggingFace Agents Documentation</t>
+          <t>LangChain Agents Overview</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>https://huggingface.co/docs/agents</t>
+          <t>https://python.langchain.com/docs/modules/agents</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HuggingFace</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1597,7 +1257,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Tools;Skills;Model Integration</t>
+          <t>Tools;Skills;Multi-Agent Patterns</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1605,44 +1265,44 @@
           <t>Architecture;Implementation</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Useful for open-source agent experimentation</t>
-        </is>
-      </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Emerging</t>
+          <t>Relevant for workflow prototyping</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rapidly evolving.</t>
-        </is>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>46082</v>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Widely used in research.</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>46113</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>dbe3741e</t>
+          <t>ddd42289</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LangChain Agents Overview</t>
+          <t>LlamaIndex Agents</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>https://python.langchain.com/docs/modules/agents</t>
+          <t>https://docs.llamaindex.ai/en/stable/agent/</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LangChain</t>
+          <t>LlamaIndex</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1657,52 +1317,60 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Tools;Skills;Multi-Agent Patterns</t>
+          <t>Tools;Skills;Retrieval Agents</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Architecture;Implementation</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Relevant for workflow prototyping</t>
+          <t>Architecture;Governance</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
+          <t>Useful for data-rich research platforms</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Widely used in research.</t>
-        </is>
-      </c>
-      <c r="Q11" s="3" t="n">
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Strong retrieval-centric design.</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="n">
         <v>46113</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ddd42289</t>
+          <t>c7e95f61</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LlamaIndex Agents</t>
+          <t>Dagster Automation/Agent Patterns</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>https://docs.llamaindex.ai/en/stable/agent/</t>
+          <t>https://docs.dagster.io/getting-started/ai-tools</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LlamaIndex</t>
+          <t>Dagster Labs</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1710,6 +1378,14 @@
           <t>Paty Buendia</t>
         </is>
       </c>
+      <c r="H12" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1.3.15</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>Documentation</t>
@@ -1717,73 +1393,57 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Tools;Skills;Retrieval Agents</t>
+          <t>Workflow Automation;Orchestration</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Architecture;Governance</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Useful for data-rich research platforms</t>
+          <t>Architecture;Deployment</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>Relevant for scientific pipelines</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Strong retrieval-centric design.</t>
-        </is>
-      </c>
-      <c r="Q12" s="3" t="n">
-        <v>46113</v>
+          <t>Mature</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Strong reproducibility focus.</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>46082</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>c7e95f61</t>
+          <t>73426de0</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dagster Automation/Agent Patterns</t>
+          <t>Prefect Automations/Agents</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>https://docs.dagster.io/getting-started/ai-tools</t>
+          <t>https://docs.prefect.io/latest/concepts/automations/</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Dagster Labs</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>46082</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Paty Buendia</t>
+          <t>Prefect</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Paty Buendia</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>46082</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1.3.15</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1793,57 +1453,57 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Workflow Automation;Orchestration</t>
+          <t>Workflow Agents;Triggers</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Architecture;Deployment</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Relevant for scientific pipelines</t>
+          <t>Implementation;Deployment</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
+          <t>Useful for data processing pipelines</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Strong reproducibility focus.</t>
-        </is>
-      </c>
-      <c r="Q13" s="3" t="n">
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Good hybrid cloud/HPC support.</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="n">
         <v>46082</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>73426de0</t>
+          <t>3294a13f</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Prefect Automations/Agents</t>
+          <t>Jupyter AI</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>https://docs.prefect.io/latest/concepts/automations/</t>
+          <t>https://jupyter-ai.readthedocs.io</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Prefect</t>
+          <t>Project Jupyter</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1853,177 +1513,177 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Workflow Agents;Triggers</t>
+          <t>Notebook Agents;Workflow Automation</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Implementation;Deployment</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Useful for data processing pipelines</t>
+          <t>Implementation;Data governance</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Mature</t>
+          <t>Relevant for research notebooks</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Good hybrid cloud/HPC support.</t>
-        </is>
-      </c>
-      <c r="Q14" s="3" t="n">
-        <v>46082</v>
+          <t>Emerging</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Strong alignment with scientific workflows.</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>46113</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3294a13f</t>
+          <t>f51ea180</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jupyter AI</t>
+          <t>Anthropic Tools API</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>https://jupyter-ai.readthedocs.io</t>
+          <t>https://docs.anthropic.com/en/docs/tools</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Project Jupyter</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>API Reference</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Notebook Agents;Workflow Automation</t>
+          <t>Tools;Skills</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Implementation;Data governance</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Relevant for research notebooks</t>
+          <t>Architecture;Security</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
+          <t>Useful for safe tool-calling agents</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Strong alignment with scientific workflows.</t>
-        </is>
-      </c>
-      <c r="Q15" s="3" t="n">
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Strong safety posture.</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="n">
         <v>46113</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>f51ea180</t>
+          <t>89f36cc1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Anthropic Tools API</t>
+          <t>Microsoft Semantic Kernel Agents</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>https://docs.anthropic.com/en/docs/tools</t>
+          <t>https://learn.microsoft.com/semantic-kernel/agents</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>API Reference</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Tools;Skills</t>
+          <t>Skills;Tools;Orchestration</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Architecture;Security</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Useful for safe tool-calling agents</t>
+          <t>Architecture;Implementation</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Emerging</t>
+          <t>Useful for enterprise-grade agent workflows</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Strong safety posture.</t>
-        </is>
-      </c>
-      <c r="Q16" s="3" t="n">
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Strong .NET + Python support.</t>
+        </is>
+      </c>
+      <c r="R16" s="3" t="n">
         <v>46113</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>89f36cc1</t>
+          <t>4ccfda21</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Microsoft Semantic Kernel Agents</t>
+          <t>HuggingFace Inference Endpoints</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/semantic-kernel/agents</t>
+          <t>https://huggingface.co/inference-endpoints</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>HuggingFace</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2033,57 +1693,57 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Skills;Tools;Orchestration</t>
+          <t>Model Integration;Tool-Ready Endpoints</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Architecture;Implementation</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Useful for enterprise-grade agent workflows</t>
+          <t>Architecture;Deployment</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>Useful for hosted inference in research</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Strong .NET + Python support.</t>
-        </is>
-      </c>
-      <c r="Q17" s="3" t="n">
-        <v>46113</v>
+          <t>Mature</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Good for reproducibility.</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>46082</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4ccfda21</t>
+          <t>2e24be4d</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HuggingFace Inference Endpoints</t>
+          <t>OpenAI Evaluations (Evals)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>https://huggingface.co/inference-endpoints</t>
+          <t>https://platform.openai.com/docs/guides/evals</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>HuggingFace</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2093,57 +1753,57 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Model Integration;Tool-Ready Endpoints</t>
+          <t>Evaluation / testing;Safety / guardrails</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Architecture;Deployment</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Useful for hosted inference in research</t>
+          <t>Security;Governance</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Mature</t>
+          <t>Relevant for agent safety in research platforms</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Good for reproducibility.</t>
-        </is>
-      </c>
-      <c r="Q18" s="3" t="n">
-        <v>46082</v>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Useful for risk assessment.</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>46113</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2e24be4d</t>
+          <t>6b9e7398</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>OpenAI Evaluations (Evals)</t>
+          <t>Anthropic Safety Guidelines</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>https://platform.openai.com/docs/guides/evals</t>
+          <t>https://docs.anthropic.com/en/docs/safety</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2153,242 +1813,257 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Evaluation / testing;Safety / guardrails</t>
+          <t>Safety / guardrails;Safe Tool Use</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Security;Governance</t>
+          <t>Governance;Security</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Relevant for agent safety in research platforms</t>
+          <t>Agent Manifesto</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>Useful for research governance teams</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Useful for risk assessment.</t>
-        </is>
-      </c>
-      <c r="Q19" s="3" t="n">
+          <t>Mature</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Strong alignment with institutional risk controls.</t>
+        </is>
+      </c>
+      <c r="R19" s="3" t="n">
         <v>46113</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6b9e7398</t>
+          <t>69804f39</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Anthropic Safety Guidelines</t>
+          <t>Microsoft Responsible AI Standard</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>https://docs.anthropic.com/en/docs/safety</t>
+          <t>https://www.microsoft.com/ai/responsible-ai</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Governance Guidance</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Safety / guardrails;Safe Tool Use</t>
+          <t>Safety / guardrails;Governance;Risk Controls</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Governance;Security</t>
+          <t>Data governance;Security</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Useful for research governance teams</t>
+          <t>Agent Manifesto;Human Approval Gate</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
+          <t>Relevant for institutional AI governance</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Strong alignment with institutional risk controls.</t>
-        </is>
-      </c>
-      <c r="Q20" s="3" t="n">
-        <v>46113</v>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Widely adopted governance framework.</t>
+        </is>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45992</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>69804f39</t>
+          <t>3758624e</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Microsoft Responsible AI Standard</t>
+          <t>vLLM Documentation</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>https://www.microsoft.com/ai/responsible-ai</t>
+          <t>https://docs.vllm.ai</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>vLLM Project Team</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Governance Guidance</t>
+          <t>Inference Framework</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Safety / guardrails;Governance;Risk Controls</t>
+          <t>Deployment patterns;Tools</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Data governance;Security</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Relevant for institutional AI governance</t>
+          <t>Self‑hosted AI;Architecture;Implementation;Deployment</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
+          <t>High (Industry-standard VPC runtime engine)</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Widely adopted governance framework.</t>
-        </is>
-      </c>
-      <c r="Q21" s="3" t="n">
-        <v>45992</v>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Essential for secure TLAs via PagedAttention and FP8/AWQ optimization. Capabilities: Parallel sampling &amp; tool-calling.</t>
+        </is>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>46113</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3758624e</t>
+          <t>8a50b5eb</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>vLLM Documentation</t>
+          <t>Ollama Documentation</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>https://docs.vllm.ai</t>
+          <t>https://github.com/ollama/ollama</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>vLLM Project Team</t>
+          <t>Ollama Community</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Inference Framework</t>
+          <t>Local Application Sandbox</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Deployment patterns;Tools</t>
+          <t>Deployment patterns</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Self‑hosted AI;Architecture;Implementation;Deployment</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>High (Industry-standard VPC runtime engine)</t>
+          <t>Self‑hosted AI;Implementation;Deployment</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
+          <t>Medium-High (Local workstation co-pilot)</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Essential for secure TLAs via PagedAttention and FP8/AWQ optimization. Capabilities: Parallel sampling &amp; tool-calling.</t>
-        </is>
-      </c>
-      <c r="Q22" s="3" t="n">
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Eliminates network dependency errors by cleanly bundling open model weights. Capabilities: Local embedding &amp; zero-config tools.</t>
+        </is>
+      </c>
+      <c r="R22" s="3" t="n">
         <v>46113</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>8a50b5eb</t>
+          <t>763797cd</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ollama Documentation</t>
+          <t xml:space="preserve">Llama.cpp </t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/ollama/ollama</t>
+          <t>https://github.com/ggerganov/llama.cpp</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Ollama Community</t>
+          <t>Georgi Gerganov</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>b9253</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Local Application Sandbox</t>
+          <t>Github Code Repository</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2398,182 +2073,182 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Self‑hosted AI;Implementation;Deployment</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Medium-High (Local workstation co-pilot)</t>
+          <t>Self‑hosted AI;Architecture;Implementation;Deployment</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
+          <t>High (Enables reasoning on variable local hardware)</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Eliminates network dependency errors by cleanly bundling open model weights. Capabilities: Local embedding &amp; zero-config tools.</t>
-        </is>
-      </c>
-      <c r="Q23" s="3" t="n">
-        <v>46113</v>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Grammar constraints ensure localized agentic pipelines always return valid JSON/code. Capabilities: Grammar-based constrained sampling.</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>46162</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>763797cd</t>
+          <t>2d2470f7</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Llama.cpp </t>
+          <t>Open WebUI Documentation</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/ggerganov/llama.cpp</t>
+          <t>https://docs.openwebui.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Georgi Gerganov</t>
+          <t>Open WebUI Core Team</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>claude</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>b9253</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Github Code Repository</t>
+          <t>Enterprise Control Interface</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Deployment patterns</t>
+          <t>Retrieval</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Self‑hosted AI;Architecture;Implementation;Deployment</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>High (Enables reasoning on variable local hardware)</t>
+          <t>Self‑hosted AI;Implementation;Deployment</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
+          <t>High (Enterprise-grade firewall interface)</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Grammar constraints ensure localized agentic pipelines always return valid JSON/code. Capabilities: Grammar-based constrained sampling.</t>
-        </is>
-      </c>
-      <c r="Q24" s="3" t="n">
-        <v>46162</v>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Solves local file parsing/RAG bottlenecks entirely within secure client networks. Capabilities: Local RAG pipelines &amp; offline functions.</t>
+        </is>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>46113</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2d2470f7</t>
+          <t>eb79015c</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Open WebUI Documentation</t>
+          <t>NVIDIA NIM Air-Gap Deployment Guide</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>https://docs.openwebui.com</t>
+          <t>https://docs.nvidia.com/nim/large-language-models/latest/deploy-air-gap.html</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Open WebUI Core Team</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Enterprise Control Interface</t>
+          <t>Reference Architecture</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Retrieval</t>
+          <t>Deployment patterns</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Self‑hosted AI;Implementation;Deployment</t>
+          <t>Self‑hosted AI;Compute Infrastructure;Implementation;Network Isolation;Infrastructure Security</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>High (Enterprise-grade firewall interface)</t>
+          <t>Remediate Oversharing</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
+          <t>Critical (Standardizes secure distribution of optimized weights)</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Solves local file parsing/RAG bottlenecks entirely within secure client networks. Capabilities: Local RAG pipelines &amp; offline functions.</t>
-        </is>
-      </c>
-      <c r="Q25" s="3" t="n">
-        <v>46113</v>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Outlines the exact connected-to-disconnected asset transfer workflow for enterprise GPUs. Capabilities: Tensor-parallel caching &amp; optimized tool-calling.</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>46150</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>eb79015c</t>
+          <t>80527de7</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NVIDIA NIM Air-Gap Deployment Guide</t>
+          <t>Harbor User Documentation</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>https://docs.nvidia.com/nim/large-language-models/latest/deploy-air-gap.html</t>
+          <t>https://goharbor.io/docs/</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Cloud Native Computing Foundation (CNCF)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Reference Architecture</t>
+          <t>Container Registry</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2583,167 +2258,193 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Self‑hosted AI;Compute Infrastructure;Implementation;Network Isolation;Infrastructure Security</t>
+          <t>Self‑hosted AI;Implementation;Network Isolation;Infrastructure Security;Governance</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Critical (Standardizes secure distribution of optimized weights)</t>
+          <t>Provenance and Reversibility</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
+          <t>High (Necessary foundation for secure cluster registries)</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Outlines the exact connected-to-disconnected asset transfer workflow for enterprise GPUs. Capabilities: Tensor-parallel caching &amp; optimized tool-calling.</t>
-        </is>
-      </c>
-      <c r="Q26" s="3" t="n">
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Built-in vulnerability scanning ensures agent images remain clean behind the firewall. Capabilities: Artifact version-locking &amp; immutable tags.</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="n">
         <v>46150</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>80527de7</t>
+          <t>b4b5a468</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Harbor User Documentation</t>
+          <t>AI Engineering Blueprint for On-Premises RAG Systems</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>https://goharbor.io/docs/</t>
+          <t>https://arxiv.org/abs/2604.01395</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Cloud Native Computing Foundation (CNCF)</t>
+          <t>arXiv (2604.01395)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Container Registry</t>
+          <t>Scientific Literature</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Deployment patterns</t>
+          <t>Deployment patterns;Retrieval</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Self‑hosted AI;Implementation;Network Isolation;Infrastructure Security;Governance</t>
+          <t>Self‑hosted AI;Infrastructure Security</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>High (Necessary foundation for secure cluster registries)</t>
+          <t>Remediate Oversharing</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Mature</t>
+          <t>High (Academic/industry validated system design blueprint)</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Built-in vulnerability scanning ensures agent images remain clean behind the firewall. Capabilities: Artifact version-locking &amp; immutable tags.</t>
-        </is>
-      </c>
-      <c r="Q27" s="3" t="n">
+          <t>Emerging</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Moves past simple how-to guides into formal data isolation and local compliance frameworks. Capabilities: End-to-end local reference applications.</t>
+        </is>
+      </c>
+      <c r="R27" s="3" t="n">
         <v>46150</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>b4b5a468</t>
+          <t>0d0a50a7</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AI Engineering Blueprint for On-Premises RAG Systems</t>
+          <t>On-Premise vs Cloud: GenAI TCO (2026 Edition)</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2604.01395</t>
+          <t xml:space="preserve">https://lenovopress.lenovo.com/lp2368-on-premise-vs-cloud-generative-ai-total-cost-of-ownership-2026-edition </t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>arXiv (2604.01395)</t>
+          <t>Lenovo Press</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>@pbuendia</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>@biddyman11</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Scientific Literature</t>
+          <t>Whitepaper</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Deployment patterns;Retrieval</t>
+          <t>Deployment patterns</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Self‑hosted AI;Infrastructure Security</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>High (Academic/industry validated system design blueprint)</t>
+          <t>Self‑hosted AI;Architecture;Governance</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Emerging</t>
+          <t>High (Mandatory for spec'ing out server node VRAM limits)</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Moves past simple how-to guides into formal data isolation and local compliance frameworks. Capabilities: End-to-end local reference applications.</t>
-        </is>
-      </c>
-      <c r="Q28" s="3" t="n">
-        <v>46150</v>
+          <t>Mature</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Discusses a "Token Economics" framework. Breaks down the "Memory Wall" economics showing an on-prem breakeven velocity of ~4 months. Capabilities: Hardware performance scaling &amp; VRAM sizing.</t>
+        </is>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>46054</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0d0a50a7</t>
+          <t>359b5ac8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>On-Premise vs Cloud: GenAI TCO (2026 Edition)</t>
+          <t xml:space="preserve">Coalition for Secure AI (CoSAI) </t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://lenovopress.lenovo.com/lp2368-on-premise-vs-cloud-generative-ai-total-cost-of-ownership-2026-edition </t>
+          <t>https://www.coalitionforsecureai.org/</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Lenovo Press</t>
+          <t xml:space="preserve">Coalition for Secure AI (CoSAI) </t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
@@ -2762,81 +2463,84 @@
       <c r="H29" s="3" t="n">
         <v>46259</v>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Whitepaper</t>
+          <t>Security Guidance &amp; Resources</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Deployment patterns</t>
+          <t>Safety / guardrails;Safe Tool Use</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Self‑hosted AI;Architecture;Governance</t>
+          <t>Infrastructure Security;Security</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>High (Mandatory for spec'ing out server node VRAM limits)</t>
+          <t>Agent Manifesto</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Mature</t>
+          <t>Relevant security expertise and best practices for secure AI development and deployment</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Discusses a "Token Economics" framework. Breaks down the "Memory Wall" economics showing an on-prem breakeven velocity of ~4 months. Capabilities: Hardware performance scaling &amp; VRAM sizing.</t>
-        </is>
-      </c>
-      <c r="Q29" s="3" t="n">
-        <v>46054</v>
+          <t>Emerging</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>The Coalition for Secure AI (CoSAI) is an open ecosystem of AI and security experts. See https://github.com/cosai-oasis/ws2-defenders</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>359b5ac8</t>
+          <t>5f3954c2</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coalition for Secure AI (CoSAI) </t>
+          <t>Anthropic Project Glasswing</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>https://www.coalitionforsecureai.org/</t>
+          <t>https://www.anthropic.com/glasswing</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coalition for Secure AI (CoSAI) </t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>46259</v>
+        <v>46182</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>@pbuendia</t>
+          <t>Paty Buendia</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>@biddyman11</t>
+          <t>Paty Buendia</t>
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>46259</v>
+        <v>46182</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>46119</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2845,7 +2549,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Safety / guardrails;Safe Tool Use</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2853,48 +2557,48 @@
           <t>Infrastructure Security;Security</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>Relevant security expertise and best practices for secure AI development and deployment</t>
-        </is>
-      </c>
       <c r="O30" t="inlineStr">
         <is>
+          <t>AI models that find high-severity vulnerabilities</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>The Coalition for Secure AI (CoSAI) is an open ecosystem of AI and security experts. See https://github.com/cosai-oasis/ws2-defenders</t>
-        </is>
-      </c>
-      <c r="Q30" s="3" t="n">
-        <v>46174</v>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>See Claude Mythos Preview</t>
+        </is>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>46119</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5f3954c2</t>
+          <t>1c277820</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Anthropic Project Glasswing</t>
+          <t>Docker AI Governance &amp; Sandboxes</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>https://www.anthropic.com/glasswing</t>
+          <t>https://docs.docker.com/ai/sandboxes/governance/org/</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Docker</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>46182</v>
+        <v>46219</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2907,68 +2611,75 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>46182</v>
-      </c>
-      <c r="J31" s="3" t="n">
-        <v>46119</v>
+        <v>46219</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0.35.0</t>
+        </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Security Guidance &amp; Resources</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Sandbox;MCP</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Infrastructure Security;Security</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>AI models that find high-severity vulnerabilities</t>
+          <t>Remediate Oversharing;Human Approval Gate</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Emerging</t>
+          <t>Good AI governance topics</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>See Claude Mythos Preview</t>
-        </is>
-      </c>
-      <c r="Q31" s="3" t="n">
-        <v>46119</v>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>See blog article: https://www.docker.com/blog/the-3cs-a-framework-for-ai-agent-security/</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>46213</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1c277820</t>
+          <t>b39dc1d1</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Docker AI Governance &amp; Sandboxes</t>
+          <t>Responses API</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>https://docs.docker.com/ai/sandboxes/governance/org/</t>
+          <t>https://developers.openai.com/api/docs/guides/migrate-to-responses</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Docker</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2981,11 +2692,11 @@
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.35.0</t>
+          <t>GPT-5.6</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2995,56 +2706,56 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Sandbox;MCP</t>
+          <t>Tools;Skills;Retrieval</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Security</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Good AI governance topics</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>Useful for domain-specific agents</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>See blog article: https://www.docker.com/blog/the-3cs-a-framework-for-ai-agent-security/</t>
-        </is>
-      </c>
-      <c r="Q32" s="3" t="n">
-        <v>46213</v>
+          <t>Emerging</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>MIgrated from API Assistants  - now deprecated.</t>
+        </is>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>46212</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>b39dc1d1</t>
+          <t>9717f0f1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Responses API</t>
+          <t>OWASP Top 10 for Agentic Applications 2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>https://developers.openai.com/api/docs/guides/migrate-to-responses</t>
+          <t>https://genai.owasp.org/resource/owasp-top-10-for-agentic-applications-for-2026/</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>OWASP GenAI Security Project</t>
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>46220</v>
+        <v>46265</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3053,117 +2764,198 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Security Guidance &amp; Resources</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Safety / guardrails;Risk Controls;Safe Tool Use;Cybersecurity</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Security;Governance;Secure and Resilient</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Runtime PII Screening;Human Approval Gate</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Threat catalog for autonomous agents; names the risks a research platform must design against</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Emerging</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Ten risk categories (ASI01-ASI10) for agents that plan, hold memory, and call tools, with threats and mitigations for each. Released December 2025, globally peer-reviewed. CC BY-SA 4.0, so it can be adapted with attribution. Initiative: https://github.com/genai-security-project/</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>c580e5f8</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>NIST AI RMF Playbook</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>https://airc.nist.gov/airmf-resources/playbook/</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NIST</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="H33" s="3" t="n">
-        <v>46220</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>GPT-5.6</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Documentation</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>Tools;Skills;Retrieval</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>Architecture</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>Useful for domain-specific agents</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>Emerging</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>MIgrated from API Assistants  - now deprecated.</t>
-        </is>
-      </c>
-      <c r="Q33" s="3" t="n">
-        <v>46212</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Governance Guidance</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Governance;Risk Controls;Evaluation / testing</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Governance;Accountable and Transparent;Valid and Reliable</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Agent Manifesto;Human Approval Gate;Provenance and Reversibility</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Focuses on 4 functions: Govern, Map, Measure, Manage. The Playbook is the companion document. NIST AI RMF 1.0 is used in this project's own vocabulary </t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Mature</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Companion to NIST AI RMF 1.0. Voluntary, free, and organised around Govern, Map, Measure and Manage, with suggested actions and references per outcome. Organisations take as many or as few suggestions as apply.</t>
+        </is>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>46265</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:E33">
-    <cfRule type="expression" priority="1" dxfId="18">
+  <conditionalFormatting sqref="E2:E34">
+    <cfRule type="expression" priority="1" dxfId="0">
       <formula>E2&gt;=DATE(2026,5,9)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K33">
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="3">
+  <conditionalFormatting sqref="K2:K34">
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
       <formula>"Documentation"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"API Reference"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="15">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
       <formula>"Specification"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
       <formula>"Whitepaper"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="13">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5">
       <formula>"Scientific Literature"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="12">
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="6">
       <formula>"Governance Guidance"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="11">
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="7">
       <formula>"Security Guidance &amp; Resources"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="9" operator="equal" dxfId="10">
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="8">
       <formula>"Reference Architecture"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="10" operator="equal" dxfId="9">
       <formula>"Container Registry"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="11" operator="equal" dxfId="8">
+    <cfRule type="cellIs" priority="11" operator="equal" dxfId="10">
       <formula>"Enterprise Control Interface"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="12" operator="equal" dxfId="7">
+    <cfRule type="cellIs" priority="12" operator="equal" dxfId="11">
       <formula>"Inference Framework"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="13" operator="equal" dxfId="6">
+    <cfRule type="cellIs" priority="13" operator="equal" dxfId="12">
       <formula>"Local Application Sandbox"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="14" operator="equal" dxfId="5">
+    <cfRule type="cellIs" priority="14" operator="equal" dxfId="13">
       <formula>"Github Code Repository"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="15" operator="equal" dxfId="4">
+    <cfRule type="cellIs" priority="15" operator="equal" dxfId="14">
       <formula>"Benchmark Collection"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M33">
-    <cfRule type="expression" priority="16" dxfId="3">
+  <conditionalFormatting sqref="M2:M34">
+    <cfRule type="expression" priority="16" dxfId="1">
       <formula>LEN(TRIM(M2))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O33">
-    <cfRule type="cellIs" priority="17" operator="equal" dxfId="3">
+  <conditionalFormatting sqref="P2:P34">
+    <cfRule type="cellIs" priority="17" operator="equal" dxfId="1">
       <formula>"Emerging"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="18" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="18" operator="equal" dxfId="4">
       <formula>"Research"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="19" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="19" operator="equal" dxfId="2">
       <formula>"Mature"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="20" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="20" operator="equal" dxfId="15">
       <formula>"Deprecated"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3200,6 +2992,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3211,7 +3004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3228,10 +3021,11 @@
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="26" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="43" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="23" customWidth="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="43" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="23" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3307,20 +3101,25 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>ALAF Checklist Mapping</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>Relevance to Research Cyberinfrastructure</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Maturity Level</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Notes / Key Takeaways</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Discovery Date</t>
         </is>
@@ -3347,127 +3146,195 @@
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="3" t="n"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>API Reference</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Tools;Skills;Retrieval</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Architecture;Implementation</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Useful for domain-specific agents</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Deprecated</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Stable API surface. Migrated to the `Responses API`.</t>
+        </is>
+      </c>
+      <c r="S2" s="3" t="n">
         <v>46150</v>
       </c>
-      <c r="F2" t="inlineStr">
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>bfda8877</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Google Vertex AI Agents Overview</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>https://cloud.google.com/vertex-ai/docs/agents</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Paty Buendia</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>46150</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>API Reference</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Tools;Skills;Retrieval</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Architecture;Implementation</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Useful for domain-specific agents</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Agent frameworks;Orchestration</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Architecture;Deployment</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Useful for cloud-based scientific workflows</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Deprecated</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Stable API surface.</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>46150</v>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Documentation URL no longer resolves: cloud.google.com/vertex-ai/docs/agents 301-redirects to docs.cloud.google.com/vertex-ai/docs/agents, which returns 404. Google's agent tooling has moved to Agent Builder. Needs a replacement resource.</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>46113</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E2">
-    <cfRule type="expression" priority="1" dxfId="18">
+  <conditionalFormatting sqref="E2:E3">
+    <cfRule type="expression" priority="1" dxfId="0">
       <formula>E2&gt;=DATE(2026,5,9)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2">
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="3">
+  <conditionalFormatting sqref="L2:L3">
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
       <formula>"Documentation"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"API Reference"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="15">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
       <formula>"Specification"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
       <formula>"Whitepaper"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="13">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5">
       <formula>"Scientific Literature"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="12">
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="6">
       <formula>"Governance Guidance"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="11">
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="7">
       <formula>"Security Guidance &amp; Resources"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="9" operator="equal" dxfId="10">
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="8">
       <formula>"Reference Architecture"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="10" operator="equal" dxfId="9">
       <formula>"Container Registry"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="11" operator="equal" dxfId="8">
+    <cfRule type="cellIs" priority="11" operator="equal" dxfId="10">
       <formula>"Enterprise Control Interface"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="12" operator="equal" dxfId="7">
+    <cfRule type="cellIs" priority="12" operator="equal" dxfId="11">
       <formula>"Inference Framework"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="13" operator="equal" dxfId="6">
+    <cfRule type="cellIs" priority="13" operator="equal" dxfId="12">
       <formula>"Local Application Sandbox"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="14" operator="equal" dxfId="5">
+    <cfRule type="cellIs" priority="14" operator="equal" dxfId="13">
       <formula>"Github Code Repository"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="15" operator="equal" dxfId="4">
+    <cfRule type="cellIs" priority="15" operator="equal" dxfId="14">
       <formula>"Benchmark Collection"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2">
-    <cfRule type="expression" priority="16" dxfId="3">
+  <conditionalFormatting sqref="N2:N3">
+    <cfRule type="expression" priority="16" dxfId="1">
       <formula>LEN(TRIM(N2))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2">
-    <cfRule type="cellIs" priority="17" operator="equal" dxfId="3">
+  <conditionalFormatting sqref="Q2:Q3">
+    <cfRule type="cellIs" priority="17" operator="equal" dxfId="1">
       <formula>"Emerging"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="18" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="18" operator="equal" dxfId="4">
       <formula>"Research"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="19" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="19" operator="equal" dxfId="2">
       <formula>"Mature"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="20" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="20" operator="equal" dxfId="15">
       <formula>"Deprecated"</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3479,7 +3346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3494,9 +3361,10 @@
     <col width="26" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="26" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="23" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3562,15 +3430,20 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>ALAF Checklist Mapping</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Maturity Level</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Notes / Key Takeaways</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Discovery Date</t>
         </is>
@@ -3628,17 +3501,17 @@
           <t>Coding Agents</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Evaluates State-Of-The-Art agent performance on multi-million line codebases to assess real-world software engineering capabilities.</t>
         </is>
       </c>
-      <c r="O2" s="3" t="n">
+      <c r="P2" s="3" t="n">
         <v>46216</v>
       </c>
     </row>
@@ -3689,17 +3562,17 @@
           <t>Coding Agents</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Papers with Code with State-Of-The-Art (SOTA) Codng Agent Benchmarks</t>
         </is>
       </c>
-      <c r="O3" s="3" t="n">
+      <c r="P3" s="3" t="n">
         <v>46216</v>
       </c>
     </row>
@@ -3744,17 +3617,17 @@
           <t>Coding Agents</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Addresses limitations of original SWE-bench by focusing on long-horizon, complex, multi-file software engineering tasks.</t>
         </is>
       </c>
-      <c r="O4" s="3" t="n">
+      <c r="P4" s="3" t="n">
         <v>46216</v>
       </c>
     </row>
@@ -3794,17 +3667,17 @@
           <t>Coding Agents</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Scalable framework that generates repository-level tasks from live GitHub PRs across 11 programming languages.</t>
         </is>
       </c>
-      <c r="O5" s="3" t="n">
+      <c r="P5" s="3" t="n">
         <v>46216</v>
       </c>
     </row>
@@ -3849,17 +3722,17 @@
           <t>Coding Agents</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Mature</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Benchmarks agents on hard, realistic tasks within terminal/CLI environments.</t>
         </is>
       </c>
-      <c r="O6" s="3" t="n">
+      <c r="P6" s="3" t="n">
         <v>46216</v>
       </c>
     </row>
@@ -3904,17 +3777,17 @@
           <t>Coding Agents</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Benchmark specifically for evaluating the code review capabilities of AI agents.</t>
         </is>
       </c>
-      <c r="O7" s="3" t="n">
+      <c r="P7" s="3" t="n">
         <v>46216</v>
       </c>
     </row>
@@ -3959,81 +3832,81 @@
           <t>Coding Agents</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Isolates the evaluation of repository exploration, context retrieval, and code localization capabilities.</t>
         </is>
       </c>
-      <c r="O8" s="3" t="n">
+      <c r="P8" s="3" t="n">
         <v>46216</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E2:E8">
-    <cfRule type="expression" priority="1" dxfId="18">
+    <cfRule type="expression" priority="1" dxfId="0">
       <formula>E2&gt;=DATE(2026,5,9)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K8">
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="3">
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
       <formula>"Documentation"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"API Reference"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="15">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
       <formula>"Specification"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
       <formula>"Whitepaper"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="13">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5">
       <formula>"Scientific Literature"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="12">
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="6">
       <formula>"Governance Guidance"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="11">
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="7">
       <formula>"Security Guidance &amp; Resources"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="9" operator="equal" dxfId="10">
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="8">
       <formula>"Reference Architecture"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="10" operator="equal" dxfId="9">
       <formula>"Container Registry"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="11" operator="equal" dxfId="8">
+    <cfRule type="cellIs" priority="11" operator="equal" dxfId="10">
       <formula>"Enterprise Control Interface"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="12" operator="equal" dxfId="7">
+    <cfRule type="cellIs" priority="12" operator="equal" dxfId="11">
       <formula>"Inference Framework"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="13" operator="equal" dxfId="6">
+    <cfRule type="cellIs" priority="13" operator="equal" dxfId="12">
       <formula>"Local Application Sandbox"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="14" operator="equal" dxfId="5">
+    <cfRule type="cellIs" priority="14" operator="equal" dxfId="13">
       <formula>"Github Code Repository"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="15" operator="equal" dxfId="4">
+    <cfRule type="cellIs" priority="15" operator="equal" dxfId="14">
       <formula>"Benchmark Collection"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M8">
-    <cfRule type="cellIs" priority="16" operator="equal" dxfId="3">
+  <conditionalFormatting sqref="N2:N8">
+    <cfRule type="cellIs" priority="16" operator="equal" dxfId="1">
       <formula>"Emerging"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="17" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="17" operator="equal" dxfId="4">
       <formula>"Research"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="18" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="18" operator="equal" dxfId="2">
       <formula>"Mature"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="19" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="19" operator="equal" dxfId="15">
       <formula>"Deprecated"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4056,12 +3929,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="4"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="80" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -4480,22 +4354,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Relevance to Research Cyberinfrastructure</t>
+          <t>ALAF Checklist Mapping</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Knowledgebase; Deprecated</t>
+          <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>free_text</t>
+          <t>controlled_multi</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>;</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Free-text note on why this matters to research platforms. Example themes: workflow orchestration, data portal integration, metadata / provenance, multi-agent coordination, HPC / cloud hybrid workflows, reproducibility, federated analysis, user-facing agent interfaces.</t>
+          <t>Which readiness items from the ALAF Checklist this resource helps an organization satisfy. One or more terms, separated by ';'. Blank means the resource is not specific to any checklist item.</t>
         </is>
       </c>
     </row>
@@ -4505,22 +4384,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Maturity Level</t>
+          <t>Relevance to Research Cyberinfrastructure</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
+          <t>Knowledgebase; Deprecated</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>controlled_single</t>
+          <t>free_text</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Not about the website - about the technology described. Helps teams know whether something is stable enough to consider.</t>
+          <t>Free-text note on why this matters to research platforms. Example themes: workflow orchestration, data portal integration, metadata / provenance, multi-agent coordination, HPC / cloud hybrid workflows, reproducibility, federated analysis, user-facing agent interfaces.</t>
         </is>
       </c>
     </row>
@@ -4530,7 +4409,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Notes / Key Takeaways</t>
+          <t>Maturity Level</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -4540,12 +4419,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>free_text</t>
+          <t>controlled_single</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Short free-text field: breaking changes, important patterns, new capabilities, relevance to agentic workflows, implications for research platforms. This is where institutional knowledge accumulates.</t>
+          <t>Not about the website - about the technology described. Helps teams know whether something is stable enough to consider.</t>
         </is>
       </c>
     </row>
@@ -4555,20 +4434,45 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>Notes / Key Takeaways</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Short free-text field: breaking changes, important patterns, new capabilities, relevance to agentic workflows, implications for research platforms. This is where institutional knowledge accumulates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>Discovery Date</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Knowledgebase; Deprecated; SOTA Coding Agents Benchmarks</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Date this resource first entered the VT Radar.</t>
         </is>
@@ -4585,7 +4489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6161,66 +6065,168 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Maturity Level</t>
+          <t>ALAF Checklist Mapping</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Emerging</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>FFB7E1CD</t>
+          <t>Remediate Oversharing</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Item (1): audit and tighten every mechanism that can grant access to the data, before the agent gets it.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Maturity Level</t>
+          <t>ALAF Checklist Mapping</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>FFFFE599</t>
+          <t>Deidentify Data</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Item (2): find and remove or hide sensitive information in the data before agents can reach it.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Maturity Level</t>
+          <t>ALAF Checklist Mapping</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Mature</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>FFA4C2F4</t>
+          <t>Agent Manifesto</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Item (3): the written rules governing agents, which they must read before tasks touching new data.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>ALAF Checklist Mapping</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Runtime PII Screening</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Item (4): a check between the agent and each new data source, with findings written where the agent cannot read them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>ALAF Checklist Mapping</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Human Approval Gate</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Item (5): a named human must approve consequential actions, and the agent cannot bypass the gate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>ALAF Checklist Mapping</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Provenance and Reversibility</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Item (6): a record of what the agent did and who approved it, plus the ability to undo it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
           <t>Maturity Level</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Emerging</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>FFB7E1CD</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Maturity Level</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>FFFFE599</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Maturity Level</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Mature</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>FFA4C2F4</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Maturity Level</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
         <is>
           <t>Deprecated</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>FFDD7E6B</t>
         </is>
@@ -6241,7 +6247,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="4"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="90" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>

--- a/data/VANTAGE-Technology-Radar.xlsx
+++ b/data/VANTAGE-Technology-Radar.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="19090" yWindow="-690" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Knowledgebase" sheetId="1" state="visible" r:id="rId1"/>
@@ -15,16 +14,16 @@
     <sheet name="Standards" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,11 +32,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <color rgb="FF0563C1"/>
+      <sz val="11"/>
       <u val="single"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -57,24 +68,43 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="59">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
+          <fgColor rgb="FFDD7E6B"/>
+          <bgColor rgb="FFDD7E6B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFA4C2F4"/>
+          <bgColor rgb="FFA4C2F4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFE599"/>
+          <bgColor rgb="FFFFE599"/>
         </patternFill>
       </fill>
     </dxf>
@@ -89,8 +119,88 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFA4C2F4"/>
-          <bgColor rgb="FFA4C2F4"/>
+          <fgColor rgb="FFE06666"/>
+          <bgColor rgb="FFE06666"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB6D7A8"/>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEAD1DC"/>
+          <bgColor rgb="FFEAD1DC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCFE2F3"/>
+          <bgColor rgb="FFCFE2F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE5CD"/>
+          <bgColor rgb="FFFCE5CD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD0E0E3"/>
+          <bgColor rgb="FFD0E0E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC9DAF8"/>
+          <bgColor rgb="FFC9DAF8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEA9999"/>
+          <bgColor rgb="FFEA9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9EAD3"/>
+          <bgColor rgb="FFD9EAD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFE599"/>
+          <bgColor rgb="FFFFE599"/>
         </patternFill>
       </fill>
     </dxf>
@@ -105,8 +215,136 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFA4C2F4"/>
+          <bgColor rgb="FFA4C2F4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB7E1CD"/>
+          <bgColor rgb="FFB7E1CD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D2E9"/>
+          <bgColor rgb="FFD9D2E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDD7E6B"/>
+          <bgColor rgb="FFDD7E6B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFA4C2F4"/>
+          <bgColor rgb="FFA4C2F4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFE599"/>
           <bgColor rgb="FFFFE599"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB7E1CD"/>
+          <bgColor rgb="FFB7E1CD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB7E1CD"/>
+          <bgColor rgb="FFB7E1CD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE06666"/>
+          <bgColor rgb="FFE06666"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB6D7A8"/>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEAD1DC"/>
+          <bgColor rgb="FFEAD1DC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCFE2F3"/>
+          <bgColor rgb="FFCFE2F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE5CD"/>
+          <bgColor rgb="FFFCE5CD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD0E0E3"/>
+          <bgColor rgb="FFD0E0E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC9DAF8"/>
+          <bgColor rgb="FFC9DAF8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEA9999"/>
+          <bgColor rgb="FFEA9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9EAD3"/>
+          <bgColor rgb="FFD9EAD3"/>
         </patternFill>
       </fill>
     </dxf>
@@ -121,8 +359,136 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-          <bgColor rgb="FFD9EAD3"/>
+          <fgColor rgb="FFFFE599"/>
+          <bgColor rgb="FFFFE599"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB4A7D6"/>
+          <bgColor rgb="FFB4A7D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFA4C2F4"/>
+          <bgColor rgb="FFA4C2F4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB7E1CD"/>
+          <bgColor rgb="FFB7E1CD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D2E9"/>
+          <bgColor rgb="FFD9D2E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDD7E6B"/>
+          <bgColor rgb="FFDD7E6B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFA4C2F4"/>
+          <bgColor rgb="FFA4C2F4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFE599"/>
+          <bgColor rgb="FFFFE599"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB7E1CD"/>
+          <bgColor rgb="FFB7E1CD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB7E1CD"/>
+          <bgColor rgb="FFB7E1CD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE06666"/>
+          <bgColor rgb="FFE06666"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB6D7A8"/>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEAD1DC"/>
+          <bgColor rgb="FFEAD1DC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCFE2F3"/>
+          <bgColor rgb="FFCFE2F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE5CD"/>
+          <bgColor rgb="FFFCE5CD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD0E0E3"/>
+          <bgColor rgb="FFD0E0E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC9DAF8"/>
+          <bgColor rgb="FFC9DAF8"/>
         </patternFill>
       </fill>
     </dxf>
@@ -137,64 +503,56 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFC9DAF8"/>
-          <bgColor rgb="FFC9DAF8"/>
+          <fgColor rgb="FFD9EAD3"/>
+          <bgColor rgb="FFD9EAD3"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFD0E0E3"/>
-          <bgColor rgb="FFD0E0E3"/>
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
+          <fgColor rgb="FFFFE599"/>
+          <bgColor rgb="FFFFE599"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
+          <fgColor rgb="FFB4A7D6"/>
+          <bgColor rgb="FFB4A7D6"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFEAD1DC"/>
-          <bgColor rgb="FFEAD1DC"/>
+          <fgColor rgb="FFA4C2F4"/>
+          <bgColor rgb="FFA4C2F4"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFB6D7A8"/>
-          <bgColor rgb="FFB6D7A8"/>
+          <fgColor rgb="FFB7E1CD"/>
+          <bgColor rgb="FFB7E1CD"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFE06666"/>
-          <bgColor rgb="FFE06666"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDD7E6B"/>
-          <bgColor rgb="FFDD7E6B"/>
+          <fgColor rgb="FFD9D2E9"/>
+          <bgColor rgb="FFD9D2E9"/>
         </patternFill>
       </fill>
     </dxf>
@@ -564,7 +922,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="36.5703125" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
@@ -757,12 +1115,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Data Director</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>https://docs.google.com/document/d/1mu1_U1cWqn1aP3vtW83JnX5-aGhzM49K/edit</t>
+          <t>RDA Data Director Agentic AI Blueprint</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>https://www.rd-alliance.org/groups/data-director-agentic-ai-blueprint/outputs/data-director-agentic-ai-tool-blueprint/</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -771,7 +1129,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>46168</v>
+        <v>46266</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -784,7 +1142,7 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>46168</v>
+        <v>46266</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -1788,12 +2146,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Anthropic Safety Guidelines</t>
+          <t>Anthropic Security Safeguards</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>https://docs.anthropic.com/en/docs/safety</t>
+          <t>https://code.claude.com/docs/en/security</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1801,11 +2159,22 @@
           <t>Anthropic</t>
         </is>
       </c>
+      <c r="E19" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>Claude</t>
         </is>
       </c>
+      <c r="H19" s="3" t="n">
+        <v>46266</v>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>Documentation</t>
@@ -1823,7 +2192,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Agent Manifesto</t>
+          <t>Agent Manifesto;Zero Data Retention</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2892,70 +3261,70 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E2:E34">
-    <cfRule type="expression" priority="1" dxfId="0">
+    <cfRule type="expression" priority="1" dxfId="18">
       <formula>E2&gt;=DATE(2026,5,9)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K34">
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="3">
       <formula>"Documentation"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1">
       <formula>"API Reference"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="15">
       <formula>"Specification"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="2">
       <formula>"Whitepaper"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="13">
       <formula>"Scientific Literature"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="6">
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="12">
       <formula>"Governance Guidance"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="7">
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="11">
       <formula>"Security Guidance &amp; Resources"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="9" operator="equal" dxfId="8">
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="10">
       <formula>"Reference Architecture"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="10" operator="equal" dxfId="9">
       <formula>"Container Registry"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="11" operator="equal" dxfId="10">
+    <cfRule type="cellIs" priority="11" operator="equal" dxfId="8">
       <formula>"Enterprise Control Interface"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="12" operator="equal" dxfId="11">
+    <cfRule type="cellIs" priority="12" operator="equal" dxfId="7">
       <formula>"Inference Framework"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="13" operator="equal" dxfId="12">
+    <cfRule type="cellIs" priority="13" operator="equal" dxfId="6">
       <formula>"Local Application Sandbox"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="14" operator="equal" dxfId="13">
+    <cfRule type="cellIs" priority="14" operator="equal" dxfId="5">
       <formula>"Github Code Repository"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="15" operator="equal" dxfId="14">
+    <cfRule type="cellIs" priority="15" operator="equal" dxfId="4">
       <formula>"Benchmark Collection"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M34">
-    <cfRule type="expression" priority="16" dxfId="1">
+    <cfRule type="expression" priority="16" dxfId="3">
       <formula>LEN(TRIM(M2))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P34">
-    <cfRule type="cellIs" priority="17" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="17" operator="equal" dxfId="3">
       <formula>"Emerging"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="18" operator="equal" dxfId="4">
+    <cfRule type="cellIs" priority="18" operator="equal" dxfId="2">
       <formula>"Research"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="19" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="19" operator="equal" dxfId="1">
       <formula>"Mature"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="20" operator="equal" dxfId="15">
+    <cfRule type="cellIs" priority="20" operator="equal" dxfId="0">
       <formula>"Deprecated"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3146,7 +3515,14 @@
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n"/>
+      <c r="E2" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Paty Buendia</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Paty Buendia</t>
@@ -3265,70 +3641,70 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E2:E3">
-    <cfRule type="expression" priority="1" dxfId="0">
+    <cfRule type="expression" priority="1" dxfId="18">
       <formula>E2&gt;=DATE(2026,5,9)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L3">
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="3">
       <formula>"Documentation"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1">
       <formula>"API Reference"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="15">
       <formula>"Specification"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="2">
       <formula>"Whitepaper"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="13">
       <formula>"Scientific Literature"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="6">
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="12">
       <formula>"Governance Guidance"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="7">
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="11">
       <formula>"Security Guidance &amp; Resources"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="9" operator="equal" dxfId="8">
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="10">
       <formula>"Reference Architecture"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="10" operator="equal" dxfId="9">
       <formula>"Container Registry"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="11" operator="equal" dxfId="10">
+    <cfRule type="cellIs" priority="11" operator="equal" dxfId="8">
       <formula>"Enterprise Control Interface"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="12" operator="equal" dxfId="11">
+    <cfRule type="cellIs" priority="12" operator="equal" dxfId="7">
       <formula>"Inference Framework"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="13" operator="equal" dxfId="12">
+    <cfRule type="cellIs" priority="13" operator="equal" dxfId="6">
       <formula>"Local Application Sandbox"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="14" operator="equal" dxfId="13">
+    <cfRule type="cellIs" priority="14" operator="equal" dxfId="5">
       <formula>"Github Code Repository"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="15" operator="equal" dxfId="14">
+    <cfRule type="cellIs" priority="15" operator="equal" dxfId="4">
       <formula>"Benchmark Collection"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N3">
-    <cfRule type="expression" priority="16" dxfId="1">
+    <cfRule type="expression" priority="16" dxfId="3">
       <formula>LEN(TRIM(N2))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q3">
-    <cfRule type="cellIs" priority="17" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="17" operator="equal" dxfId="3">
       <formula>"Emerging"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="18" operator="equal" dxfId="4">
+    <cfRule type="cellIs" priority="18" operator="equal" dxfId="2">
       <formula>"Research"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="19" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="19" operator="equal" dxfId="1">
       <formula>"Mature"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="20" operator="equal" dxfId="15">
+    <cfRule type="cellIs" priority="20" operator="equal" dxfId="0">
       <formula>"Deprecated"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3848,65 +4224,65 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E2:E8">
-    <cfRule type="expression" priority="1" dxfId="0">
+    <cfRule type="expression" priority="1" dxfId="18">
       <formula>E2&gt;=DATE(2026,5,9)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K8">
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="3">
       <formula>"Documentation"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1">
       <formula>"API Reference"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="15">
       <formula>"Specification"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="2">
       <formula>"Whitepaper"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="13">
       <formula>"Scientific Literature"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="6">
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="12">
       <formula>"Governance Guidance"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="7">
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="11">
       <formula>"Security Guidance &amp; Resources"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="9" operator="equal" dxfId="8">
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="10">
       <formula>"Reference Architecture"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="10" operator="equal" dxfId="9">
       <formula>"Container Registry"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="11" operator="equal" dxfId="10">
+    <cfRule type="cellIs" priority="11" operator="equal" dxfId="8">
       <formula>"Enterprise Control Interface"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="12" operator="equal" dxfId="11">
+    <cfRule type="cellIs" priority="12" operator="equal" dxfId="7">
       <formula>"Inference Framework"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="13" operator="equal" dxfId="12">
+    <cfRule type="cellIs" priority="13" operator="equal" dxfId="6">
       <formula>"Local Application Sandbox"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="14" operator="equal" dxfId="13">
+    <cfRule type="cellIs" priority="14" operator="equal" dxfId="5">
       <formula>"Github Code Repository"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="15" operator="equal" dxfId="14">
+    <cfRule type="cellIs" priority="15" operator="equal" dxfId="4">
       <formula>"Benchmark Collection"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N8">
-    <cfRule type="cellIs" priority="16" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="16" operator="equal" dxfId="3">
       <formula>"Emerging"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="17" operator="equal" dxfId="4">
+    <cfRule type="cellIs" priority="17" operator="equal" dxfId="2">
       <formula>"Research"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="18" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="18" operator="equal" dxfId="1">
       <formula>"Mature"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="19" operator="equal" dxfId="15">
+    <cfRule type="cellIs" priority="19" operator="equal" dxfId="0">
       <formula>"Deprecated"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3934,8 +4310,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="3" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="80" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -4489,7 +4864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6075,7 +6450,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Item (1): audit and tighten every mechanism that can grant access to the data, before the agent gets it.</t>
+          <t>Audit and tighten every mechanism that can grant access to the data, before the agent gets it.</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6467,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Item (2): find and remove or hide sensitive information in the data before agents can reach it.</t>
+          <t>Find and remove or hide sensitive information in the data before agents can reach it.</t>
         </is>
       </c>
     </row>
@@ -6109,7 +6484,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Item (3): the written rules governing agents, which they must read before tasks touching new data.</t>
+          <t>The written rules governing agents, which they must read before tasks touching new data.</t>
         </is>
       </c>
     </row>
@@ -6126,7 +6501,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Item (4): a check between the agent and each new data source, with findings written where the agent cannot read them.</t>
+          <t>A check between the agent and each new data source, with findings written where the agent cannot read them.</t>
         </is>
       </c>
     </row>
@@ -6143,7 +6518,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Item (5): a named human must approve consequential actions, and the agent cannot bypass the gate.</t>
+          <t>A named human must approve consequential actions, and the agent cannot bypass the gate.</t>
         </is>
       </c>
     </row>
@@ -6160,24 +6535,24 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Item (6): a record of what the agent did and who approved it, plus the ability to undo it.</t>
+          <t>A record of what the agent did and who approved it, plus the ability to undo it.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Maturity Level</t>
+          <t>ALAF Checklist Mapping</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Emerging</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>FFB7E1CD</t>
+          <t>Zero Data Retention</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Third-party AI APIs configured for zero data retention, with the prompt caching TTL checked separately.</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6564,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>Emerging</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>FFFFE599</t>
+          <t>FFB7E1CD</t>
         </is>
       </c>
     </row>
@@ -6206,12 +6581,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Mature</t>
+          <t>Research</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>FFA4C2F4</t>
+          <t>FFFFE599</t>
         </is>
       </c>
     </row>
@@ -6223,10 +6598,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
+          <t>Mature</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>FFA4C2F4</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Maturity Level</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
           <t>Deprecated</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>FFDD7E6B</t>
         </is>
@@ -6247,9 +6639,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="2" max="4"/>
     <col width="90" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
